--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608804702759</t>
+    <t xml:space="preserve">12.7608823776245</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
@@ -47,52 +47,52 @@
     <t xml:space="preserve">12.784628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7767124176025</t>
+    <t xml:space="preserve">12.7767133712769</t>
   </si>
   <si>
     <t xml:space="preserve">12.4758987426758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9930114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742694854736</t>
+    <t xml:space="preserve">11.9930124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742685317993</t>
   </si>
   <si>
     <t xml:space="preserve">12.2700786590576</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5233964920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746160507202</t>
+    <t xml:space="preserve">12.5233945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746179580688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075635910034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4125699996948</t>
+    <t xml:space="preserve">12.4125690460205</t>
   </si>
   <si>
     <t xml:space="preserve">12.6738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0563411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3729887008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1750831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413248062134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713575363159</t>
+    <t xml:space="preserve">12.056339263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3729877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1750841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413228988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909170150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713584899902</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367835998535</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">10.9955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4626264572144</t>
+    <t xml:space="preserve">11.462628364563</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063995361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417890548706</t>
+    <t xml:space="preserve">11.4942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417900085449</t>
   </si>
   <si>
     <t xml:space="preserve">11.3597173690796</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
+    <t xml:space="preserve">11.858437538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159471511841</t>
   </si>
   <si>
     <t xml:space="preserve">11.8346872329712</t>
@@ -143,37 +143,37 @@
     <t xml:space="preserve">11.3992986679077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1855611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3888216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4284000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2304973602295</t>
+    <t xml:space="preserve">11.1855602264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692621231079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.388819694519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4284009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2304964065552</t>
   </si>
   <si>
     <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1513347625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.982533454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950870513916</t>
+    <t xml:space="preserve">12.1513366699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9825325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508695602417</t>
   </si>
   <si>
     <t xml:space="preserve">13.1408576965332</t>
@@ -185,52 +185,52 @@
     <t xml:space="preserve">13.3704261779785</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3387632369995</t>
+    <t xml:space="preserve">13.3387613296509</t>
   </si>
   <si>
     <t xml:space="preserve">13.4575042724609</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5762481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625116348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379467010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7529649734497</t>
+    <t xml:space="preserve">13.576247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379476547241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752965927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.1171073913574</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1091909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1962699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9904499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221166610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933609008789</t>
+    <t xml:space="preserve">13.1091928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1962690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9904479980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221147537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933618545532</t>
   </si>
   <si>
     <t xml:space="preserve">13.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0300302505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975526809692</t>
+    <t xml:space="preserve">13.0300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975517272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.602557182312</t>
@@ -239,61 +239,61 @@
     <t xml:space="preserve">12.6500539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8637914657593</t>
+    <t xml:space="preserve">12.8637924194336</t>
   </si>
   <si>
     <t xml:space="preserve">12.5867233276367</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650732040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493883132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9884691238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218017578125</t>
+    <t xml:space="preserve">12.467981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650712966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788078308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493902206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9240999221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218008041382</t>
   </si>
   <si>
     <t xml:space="preserve">12.2298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620315551758</t>
+    <t xml:space="preserve">12.2942161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620306015015</t>
   </si>
   <si>
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126064300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.809157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735246658325</t>
+    <t xml:space="preserve">12.4953641891479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126054763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263986587524</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">12.865478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172016143799</t>
+    <t xml:space="preserve">12.8172025680542</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999622344971</t>
@@ -314,22 +314,22 @@
     <t xml:space="preserve">12.3666286468506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3103055953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390451431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011163711548</t>
+    <t xml:space="preserve">12.3103084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390441894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011144638062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8781280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792770385742</t>
+    <t xml:space="preserve">10.8781290054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792760848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.6022634506226</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">11.3689308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4896202087402</t>
+    <t xml:space="preserve">11.4896211624146</t>
   </si>
   <si>
     <t xml:space="preserve">10.757438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4597387313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424932479858</t>
+    <t xml:space="preserve">10.0735330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424942016602</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264039993286</t>
+    <t xml:space="preserve">11.2321491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827241897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.92640209198</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160568237305</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">11.5700798034668</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8919191360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861721038818</t>
+    <t xml:space="preserve">11.8919172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861711502075</t>
   </si>
   <si>
     <t xml:space="preserve">11.8758268356323</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">11.7953653335571</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1896181106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309959411621</t>
+    <t xml:space="preserve">12.1896162033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309968948364</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896169662476</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0505352020264</t>
+    <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
     <t xml:space="preserve">12.9942121505737</t>
@@ -416,121 +416,121 @@
     <t xml:space="preserve">13.1229486465454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1551332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861679077148</t>
+    <t xml:space="preserve">13.1551313400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861660003662</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746736526489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3482351303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.24937915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459329605103</t>
+    <t xml:space="preserve">13.3482341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.249382019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459358215332</t>
   </si>
   <si>
     <t xml:space="preserve">13.8551292419434</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1608762741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643232345581</t>
+    <t xml:space="preserve">14.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919088363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643241882324</t>
   </si>
   <si>
     <t xml:space="preserve">14.6275424957275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8206443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562770843506</t>
+    <t xml:space="preserve">14.8206462860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562761306763</t>
   </si>
   <si>
     <t xml:space="preserve">15.1183452606201</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1505289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1263904571533</t>
+    <t xml:space="preserve">15.1505260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1263875961304</t>
   </si>
   <si>
     <t xml:space="preserve">15.08616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0459318161011</t>
+    <t xml:space="preserve">15.0459327697754</t>
   </si>
   <si>
     <t xml:space="preserve">15.295355796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4240913391113</t>
+    <t xml:space="preserve">15.424090385437</t>
   </si>
   <si>
     <t xml:space="preserve">15.4562759399414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873096466064</t>
+    <t xml:space="preserve">15.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873086929321</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7240924835205</t>
+    <t xml:space="preserve">14.7240915298462</t>
   </si>
   <si>
     <t xml:space="preserve">14.8367357254028</t>
   </si>
   <si>
-    <t xml:space="preserve">14.788459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930597305298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4884605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401836395264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148971557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045530319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3919076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2551259994507</t>
+    <t xml:space="preserve">14.7884607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4884586334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401826858521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045520782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3919048309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.255126953125</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666212081909</t>
@@ -539,40 +539,40 @@
     <t xml:space="preserve">15.5286874771118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2229423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0137481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.311448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677682876587</t>
+    <t xml:space="preserve">15.2229413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0137500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1988010406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.367769241333</t>
   </si>
   <si>
     <t xml:space="preserve">15.3034009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1827154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436338424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654722213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470827102661</t>
+    <t xml:space="preserve">15.182713508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654741287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470798492432</t>
   </si>
   <si>
     <t xml:space="preserve">14.8286895751953</t>
@@ -584,49 +584,49 @@
     <t xml:space="preserve">14.5551290512085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1125993728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263935089111</t>
+    <t xml:space="preserve">14.1126012802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263906478882</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815656661987</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2172002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103021621704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.563175201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585781097412</t>
+    <t xml:space="preserve">14.4827136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171964645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5631761550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585762023926</t>
   </si>
   <si>
     <t xml:space="preserve">14.305703163147</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1045541763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217935562134</t>
+    <t xml:space="preserve">14.1045560836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217945098877</t>
   </si>
   <si>
     <t xml:space="preserve">13.9516830444336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6781187057495</t>
+    <t xml:space="preserve">13.6781196594238</t>
   </si>
   <si>
     <t xml:space="preserve">13.4045562744141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3643264770508</t>
+    <t xml:space="preserve">13.3643274307251</t>
   </si>
   <si>
     <t xml:space="preserve">13.1873149871826</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">12.9539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3160514831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5896139144897</t>
+    <t xml:space="preserve">13.3160495758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5896129608154</t>
   </si>
   <si>
     <t xml:space="preserve">13.7746706008911</t>
@@ -650,22 +650,22 @@
     <t xml:space="preserve">14.2011041641235</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9999580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9815664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.716046333313</t>
+    <t xml:space="preserve">13.9999561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9815645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160482406616</t>
   </si>
   <si>
     <t xml:space="preserve">14.8447847366333</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9171981811523</t>
+    <t xml:space="preserve">14.9171962738037</t>
   </si>
   <si>
     <t xml:space="preserve">15.2631711959839</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">15.6010999679565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5528268814087</t>
+    <t xml:space="preserve">15.5528259277344</t>
   </si>
   <si>
     <t xml:space="preserve">15.5367345809937</t>
@@ -683,58 +683,58 @@
     <t xml:space="preserve">15.4643220901489</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3838605880737</t>
+    <t xml:space="preserve">15.3838634490967</t>
   </si>
   <si>
     <t xml:space="preserve">15.6091470718384</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5045499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079990386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1102991104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068500518799</t>
+    <t xml:space="preserve">15.5045528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.407998085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1103000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068529129028</t>
   </si>
   <si>
     <t xml:space="preserve">15.8263874053955</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8907556533813</t>
+    <t xml:space="preserve">15.8907566070557</t>
   </si>
   <si>
     <t xml:space="preserve">15.8988027572632</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9470796585083</t>
+    <t xml:space="preserve">15.947075843811</t>
   </si>
   <si>
     <t xml:space="preserve">16.0114479064941</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493728637695</t>
+    <t xml:space="preserve">16.3493747711182</t>
   </si>
   <si>
     <t xml:space="preserve">16.301097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5344314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5827102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3332843780518</t>
+    <t xml:space="preserve">16.5344295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5827083587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1723651885986</t>
+    <t xml:space="preserve">16.1723670959473</t>
   </si>
   <si>
     <t xml:space="preserve">16.156270980835</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">15.7700681686401</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0919055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
+    <t xml:space="preserve">16.0919017791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0033950805664</t>
   </si>
   <si>
     <t xml:space="preserve">16.0436305999756</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">16.4781112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8964996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769611358643</t>
+    <t xml:space="preserve">16.8965015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769592285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.0413284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3792591094971</t>
+    <t xml:space="preserve">17.3792572021484</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160388946533</t>
@@ -776,19 +776,19 @@
     <t xml:space="preserve">17.773509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470664978027</t>
+    <t xml:space="preserve">18.3850021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470684051514</t>
   </si>
   <si>
     <t xml:space="preserve">18.7229328155518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2700576782227</t>
+    <t xml:space="preserve">19.0206336975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2700595855713</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907451629639</t>
@@ -797,109 +797,109 @@
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470710754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033893585205</t>
+    <t xml:space="preserve">19.4470672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033912658691</t>
   </si>
   <si>
     <t xml:space="preserve">19.6079864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321201324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125854492188</t>
+    <t xml:space="preserve">19.6321258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125835418701</t>
   </si>
   <si>
     <t xml:space="preserve">19.3827018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5838489532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3102874755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436191558838</t>
+    <t xml:space="preserve">19.5838470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3102855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436210632324</t>
   </si>
   <si>
     <t xml:space="preserve">19.4631576538086</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0689105987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0769500732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286769866943</t>
+    <t xml:space="preserve">19.0689086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0769519805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286750793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.9723567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5620136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5056896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6183319091797</t>
+    <t xml:space="preserve">18.56201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
     <t xml:space="preserve">19.1654586791992</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8171806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.259708404541</t>
+    <t xml:space="preserve">19.8171768188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2597103118896</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585582733154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5574073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9539318084717</t>
+    <t xml:space="preserve">20.557409286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.953929901123</t>
   </si>
   <si>
     <t xml:space="preserve">21.1818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9213733673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5726184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.538761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5550422668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4899158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
+    <t xml:space="preserve">20.9213714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7667007446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0027770996094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5726203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5387630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5550441741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.489917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922309875488</t>
   </si>
   <si>
     <t xml:space="preserve">20.3271045684814</t>
@@ -917,37 +917,37 @@
     <t xml:space="preserve">20.9946365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.937650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1248836517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353374481201</t>
+    <t xml:space="preserve">20.9376468658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.124885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353393554688</t>
   </si>
   <si>
     <t xml:space="preserve">20.8399639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8155422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.15744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945423126221</t>
+    <t xml:space="preserve">20.815544128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1574478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2945442199707</t>
   </si>
   <si>
     <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3189659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0828857421875</t>
+    <t xml:space="preserve">20.3189640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386707305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0828876495361</t>
   </si>
   <si>
     <t xml:space="preserve">20.1480102539062</t>
@@ -959,136 +959,136 @@
     <t xml:space="preserve">20.1317310333252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3678092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3583736419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1874179840088</t>
+    <t xml:space="preserve">20.3678073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3583717346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1874198913574</t>
   </si>
   <si>
     <t xml:space="preserve">18.9757633209229</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8048114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338577270508</t>
+    <t xml:space="preserve">18.8048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7071228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338596343994</t>
   </si>
   <si>
     <t xml:space="preserve">19.1304359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4804840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049961090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816829681396</t>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049980163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816848754883</t>
   </si>
   <si>
     <t xml:space="preserve">20.1805744171143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2375564575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.78297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050884246826</t>
+    <t xml:space="preserve">20.2375583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050941467285</t>
   </si>
   <si>
     <t xml:space="preserve">20.677152633667</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1655902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2795562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.043478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260864257812</t>
+    <t xml:space="preserve">21.1655864715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2795581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0434799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6852931976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1004638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260902404785</t>
   </si>
   <si>
     <t xml:space="preserve">21.5319156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7842769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4993534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935260772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7761325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6214637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691967010498</t>
+    <t xml:space="preserve">21.3202590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9226665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7842750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4993515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7761344909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6214618682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691986083984</t>
   </si>
   <si>
     <t xml:space="preserve">21.7110080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5169277191162</t>
+    <t xml:space="preserve">22.5169258117676</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.630895614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0542087554932</t>
+    <t xml:space="preserve">22.6308975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0542106628418</t>
   </si>
   <si>
     <t xml:space="preserve">22.9890823364258</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">23.168176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4693794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8601322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298793792725</t>
+    <t xml:space="preserve">23.1681785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4693832397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298774719238</t>
   </si>
   <si>
     <t xml:space="preserve">24.0310840606689</t>
@@ -1115,13 +1115,13 @@
     <t xml:space="preserve">23.9659576416016</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008350372314</t>
+    <t xml:space="preserve">24.0229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">23.599630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159133911133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2346000671387</t>
+    <t xml:space="preserve">23.5263633728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9822406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.23459815979</t>
   </si>
   <si>
     <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916744232178</t>
+    <t xml:space="preserve">24.9916763305664</t>
   </si>
   <si>
     <t xml:space="preserve">25.0568008422852</t>
@@ -1154,40 +1154,40 @@
     <t xml:space="preserve">25.0079555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.87770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6660480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6497707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999111175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9604053497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4801120758057</t>
+    <t xml:space="preserve">24.8777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288650512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6660499572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999092102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9604091644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1613311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602226257324</t>
+    <t xml:space="preserve">24.1613330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602245330811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765037536621</t>
+    <t xml:space="preserve">24.5765056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.4556903839111</t>
@@ -1196,46 +1196,46 @@
     <t xml:space="preserve">26.2778911590576</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9848289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1082363128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7676239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3850135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209995269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071239471436</t>
+    <t xml:space="preserve">25.9848308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1082324981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7676258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3850154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9209976196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071277618408</t>
   </si>
   <si>
     <t xml:space="preserve">27.0105476379395</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6930637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032367706299</t>
+    <t xml:space="preserve">26.6930618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032386779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.617208480835</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2440319061279</t>
+    <t xml:space="preserve">24.584644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2440338134766</t>
   </si>
   <si>
     <t xml:space="preserve">24.8451442718506</t>
@@ -1244,31 +1244,31 @@
     <t xml:space="preserve">24.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951923370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5859413146973</t>
+    <t xml:space="preserve">25.1951942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6429233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5859394073486</t>
   </si>
   <si>
     <t xml:space="preserve">25.7243328094482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.691764831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5452365875244</t>
+    <t xml:space="preserve">25.6917667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5452346801758</t>
   </si>
   <si>
     <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5208168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3173007965088</t>
+    <t xml:space="preserve">25.5208129882812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3173027038574</t>
   </si>
   <si>
     <t xml:space="preserve">25.3987045288086</t>
@@ -1277,25 +1277,25 @@
     <t xml:space="preserve">25.5126762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7650337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2033290863037</t>
+    <t xml:space="preserve">25.7650318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.049955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2033309936523</t>
   </si>
   <si>
     <t xml:space="preserve">25.0486602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4625339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242404937744</t>
+    <t xml:space="preserve">24.4625358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242366790771</t>
   </si>
   <si>
     <t xml:space="preserve">25.3824234008789</t>
@@ -1304,19 +1304,19 @@
     <t xml:space="preserve">25.0893611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7148933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6836242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7419052124023</t>
+    <t xml:space="preserve">24.7148990631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6836261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">26.5790977478027</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3931560516357</t>
+    <t xml:space="preserve">27.3931579589844</t>
   </si>
   <si>
     <t xml:space="preserve">26.6604995727539</t>
@@ -1328,76 +1328,76 @@
     <t xml:space="preserve">26.1313591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6022205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127666473389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941722869873</t>
+    <t xml:space="preserve">25.602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127685546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2941741943359</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826099395752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117504119873</t>
+    <t xml:space="preserve">27.31174659729</t>
   </si>
   <si>
     <t xml:space="preserve">27.8815937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2303428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8233165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6253452301025</t>
+    <t xml:space="preserve">27.2303466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.823314666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6197986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6253471374512</t>
   </si>
   <si>
     <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9740982055664</t>
+    <t xml:space="preserve">23.974100112915</t>
   </si>
   <si>
     <t xml:space="preserve">25.5615196228027</t>
   </si>
   <si>
-    <t xml:space="preserve">25.358003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358951568604</t>
+    <t xml:space="preserve">25.3580017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358932495117</t>
   </si>
   <si>
     <t xml:space="preserve">23.3635540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218330383301</t>
+    <t xml:space="preserve">24.4218311309814</t>
   </si>
   <si>
     <t xml:space="preserve">26.2534713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6891765594482</t>
+    <t xml:space="preserve">23.6891784667969</t>
   </si>
   <si>
     <t xml:space="preserve">23.5670700073242</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1887149810791</t>
+    <t xml:space="preserve">20.1887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">20.6364479064941</t>
@@ -1409,40 +1409,40 @@
     <t xml:space="preserve">19.7002811431885</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736366271973</t>
+    <t xml:space="preserve">20.4736347198486</t>
   </si>
   <si>
     <t xml:space="preserve">21.2062911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6540222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273834228516</t>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">21.816837310791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505100250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284015655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680881500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1831665039062</t>
+    <t xml:space="preserve">20.8806629180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680862426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1831645965576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5901947021484</t>
@@ -1457,40 +1457,40 @@
     <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077709197998</t>
+    <t xml:space="preserve">22.7123069763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077747344971</t>
   </si>
   <si>
     <t xml:space="preserve">25.8057346343994</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7067565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3811283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2183151245117</t>
+    <t xml:space="preserve">24.7067527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3811302185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.218318939209</t>
   </si>
   <si>
     <t xml:space="preserve">24.1776161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2997226715088</t>
+    <t xml:space="preserve">24.2997245788574</t>
   </si>
   <si>
     <t xml:space="preserve">24.7881603240967</t>
   </si>
   <si>
-    <t xml:space="preserve">24.705394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1260414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640110015869</t>
+    <t xml:space="preserve">24.7053966522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1260375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640129089355</t>
   </si>
   <si>
     <t xml:space="preserve">24.9123096466064</t>
@@ -1502,124 +1502,124 @@
     <t xml:space="preserve">25.4089012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7813415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7399578094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3261337280273</t>
+    <t xml:space="preserve">25.7813396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7399597167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.326135635376</t>
   </si>
   <si>
     <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1469688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400539398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951694488525</t>
+    <t xml:space="preserve">27.1469650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9400501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951675415039</t>
   </si>
   <si>
     <t xml:space="preserve">25.491662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5330448150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778331756592</t>
+    <t xml:space="preserve">25.5330467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778369903564</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675174713135</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6985759735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847499847412</t>
+    <t xml:space="preserve">25.6985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847518920898</t>
   </si>
   <si>
     <t xml:space="preserve">25.6571941375732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9468688964844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0710182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9054889678955</t>
+    <t xml:space="preserve">26.1537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9468727111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0710201263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9054908752441</t>
   </si>
   <si>
     <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2501850128174</t>
+    <t xml:space="preserve">27.0642051696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.022819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.250186920166</t>
   </si>
   <si>
     <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0432739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3811511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7949752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8777446746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9191226959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2088012695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329544067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4502811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8641109466553</t>
+    <t xml:space="preserve">23.7535972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0432720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3811531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7949771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.877742767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9191265106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2088069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4502830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262298583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
     <t xml:space="preserve">26.0296382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5676078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5744285583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6089916229248</t>
+    <t xml:space="preserve">26.5676116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.574426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6089935302734</t>
   </si>
   <si>
     <t xml:space="preserve">26.9814338684082</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">25.9882564544678</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4434642791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6503791809082</t>
+    <t xml:space="preserve">26.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6503772735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.3606967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4984836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0914745330811</t>
+    <t xml:space="preserve">24.4984798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0914764404297</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258491516113</t>
@@ -1652,49 +1652,49 @@
     <t xml:space="preserve">21.8913803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7740516662598</t>
+    <t xml:space="preserve">20.7740535736084</t>
   </si>
   <si>
     <t xml:space="preserve">21.6430816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4775543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1051120758057</t>
+    <t xml:space="preserve">21.4775562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.105110168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6981010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9395809173584</t>
+    <t xml:space="preserve">19.6981029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.939582824707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9327640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0569095611572</t>
+    <t xml:space="preserve">22.0569114685059</t>
   </si>
   <si>
     <t xml:space="preserve">22.9259433746338</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2638206481934</t>
+    <t xml:space="preserve">22.263822555542</t>
   </si>
   <si>
     <t xml:space="preserve">18.0014190673828</t>
@@ -1703,28 +1703,28 @@
     <t xml:space="preserve">17.4634475708008</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5462093353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2083301544189</t>
+    <t xml:space="preserve">17.5462112426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6703548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2083320617676</t>
   </si>
   <si>
     <t xml:space="preserve">18.498010635376</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7049217224121</t>
+    <t xml:space="preserve">18.7049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">18.8290691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6221580505371</t>
+    <t xml:space="preserve">18.6221561431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
@@ -1733,88 +1733,88 @@
     <t xml:space="preserve">19.3670425415039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.491189956665</t>
+    <t xml:space="preserve">19.5325756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187496185303</t>
+    <t xml:space="preserve">19.1187477111816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.794506072998</t>
+    <t xml:space="preserve">17.7945041656494</t>
   </si>
   <si>
     <t xml:space="preserve">16.8427066802979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7531261444092</t>
+    <t xml:space="preserve">17.7531242370605</t>
   </si>
   <si>
     <t xml:space="preserve">17.1737670898438</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806781768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9668560028076</t>
+    <t xml:space="preserve">17.3806819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.966854095459</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8840885162354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5530300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2497158050537</t>
+    <t xml:space="preserve">16.7599430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5530242919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2497119903564</t>
   </si>
   <si>
     <t xml:space="preserve">18.4152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4084281921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4498081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050178527832</t>
+    <t xml:space="preserve">19.1601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.40842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4498062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050140380859</t>
   </si>
   <si>
     <t xml:space="preserve">19.8222522735596</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5257549285889</t>
+    <t xml:space="preserve">20.5257511138916</t>
   </si>
   <si>
     <t xml:space="preserve">20.6499061584473</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1119270324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808704376221</t>
+    <t xml:space="preserve">20.3188438415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1119289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808685302734</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842769622803</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">20.0291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567192077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9463977813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3256607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.035982131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2979145050049</t>
+    <t xml:space="preserve">19.6567211151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9463996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2428932189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.325662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0359840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2979125976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364761352539</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">16.48681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4537086486816</t>
+    <t xml:space="preserve">16.4537105560303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0910015106201</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">18.0593528747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6455268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.248254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289749145508</t>
+    <t xml:space="preserve">17.645528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289730072021</t>
   </si>
   <si>
     <t xml:space="preserve">18.07590675354</t>
@@ -1898,16 +1898,16 @@
     <t xml:space="preserve">17.7779541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2248859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861339569092</t>
+    <t xml:space="preserve">17.9765911102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2248840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7613964080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861358642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.6192417144775</t>
@@ -1916,10 +1916,10 @@
     <t xml:space="preserve">16.5033702850342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274215698242</t>
+    <t xml:space="preserve">15.5101881027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274234771729</t>
   </si>
   <si>
     <t xml:space="preserve">15.2701711654663</t>
@@ -1928,28 +1928,28 @@
     <t xml:space="preserve">14.8397903442383</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6328763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6742582321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322929382324</t>
+    <t xml:space="preserve">14.6328783035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322900772095</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632562637329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467042922974</t>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467023849487</t>
   </si>
   <si>
     <t xml:space="preserve">14.6659832000732</t>
@@ -1961,55 +1961,55 @@
     <t xml:space="preserve">15.3255767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3426027297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.712553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6444396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.806209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5422697067261</t>
+    <t xml:space="preserve">15.3426036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7125539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402681350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614675521851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6444387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8062086105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5422687530518</t>
   </si>
   <si>
     <t xml:space="preserve">14.8913507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661443710327</t>
+    <t xml:space="preserve">15.9811677932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661415100098</t>
   </si>
   <si>
     <t xml:space="preserve">14.9083795547485</t>
   </si>
   <si>
-    <t xml:space="preserve">14.525239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741535186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2017002105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3890132904053</t>
+    <t xml:space="preserve">14.5252389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741544723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2017011642456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.389012336731</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018686294556</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315843582153</t>
+    <t xml:space="preserve">14.4315824508667</t>
   </si>
   <si>
     <t xml:space="preserve">14.2357549667358</t>
@@ -2021,55 +2021,55 @@
     <t xml:space="preserve">14.1846714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.831750869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507822036743</t>
+    <t xml:space="preserve">14.8317499160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55078125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3208990097046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7295808792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020351409912</t>
+    <t xml:space="preserve">14.7295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020370483398</t>
   </si>
   <si>
     <t xml:space="preserve">14.4230709075928</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3379278182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3549556732178</t>
+    <t xml:space="preserve">14.3379287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3549566268921</t>
   </si>
   <si>
     <t xml:space="preserve">13.9462728500366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6908464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6312475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948534011841</t>
+    <t xml:space="preserve">13.6908473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6312484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948543548584</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821655273438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3975276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0995292663574</t>
+    <t xml:space="preserve">14.3975286483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0995283126831</t>
   </si>
   <si>
     <t xml:space="preserve">13.8866739273071</t>
@@ -2078,16 +2078,16 @@
     <t xml:space="preserve">13.8185596466064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801620483398</t>
+    <t xml:space="preserve">13.2225656509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.520562171936</t>
+    <t xml:space="preserve">13.5205640792847</t>
   </si>
   <si>
     <t xml:space="preserve">13.1799945831299</t>
@@ -2096,61 +2096,61 @@
     <t xml:space="preserve">13.1544523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2140512466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1668043136597</t>
+    <t xml:space="preserve">13.2140522003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.166802406311</t>
   </si>
   <si>
     <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9748153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491037368774</t>
+    <t xml:space="preserve">10.9748163223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491046905518</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1706409454346</t>
+    <t xml:space="preserve">11.1706418991089</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0344152450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.162127494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811588287354</t>
+    <t xml:space="preserve">11.0344142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1621265411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7619609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251106262207</t>
+    <t xml:space="preserve">10.7619600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2511072158813</t>
   </si>
   <si>
     <t xml:space="preserve">11.0599565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8471002578735</t>
+    <t xml:space="preserve">10.8471021652222</t>
   </si>
   <si>
     <t xml:space="preserve">10.6683025360107</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7279024124146</t>
+    <t xml:space="preserve">10.7279033660889</t>
   </si>
   <si>
     <t xml:space="preserve">11.3664703369141</t>
@@ -2159,16 +2159,16 @@
     <t xml:space="preserve">11.53675365448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6644659042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6900081634521</t>
+    <t xml:space="preserve">11.6644639968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6900091171265</t>
   </si>
   <si>
     <t xml:space="preserve">11.7410926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7496089935303</t>
+    <t xml:space="preserve">11.749608039856</t>
   </si>
   <si>
     <t xml:space="preserve">12.1838331222534</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">11.8177223205566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4601249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5026960372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981857299805</t>
+    <t xml:space="preserve">11.7751493453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4601240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5026950836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1451005935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981866836548</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2132139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7108745574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4724779129028</t>
+    <t xml:space="preserve">11.2132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7108755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4724769592285</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597881317139</t>
@@ -2219,22 +2219,22 @@
     <t xml:space="preserve">11.0855007171631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.051441192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280708312988</t>
+    <t xml:space="preserve">11.0514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280698776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0088729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2642974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6985216140747</t>
+    <t xml:space="preserve">11.0088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2642984390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.698522567749</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814947128296</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1970233917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5120477676392</t>
+    <t xml:space="preserve">13.1970243453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.239595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5120496749878</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5461053848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4145536422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8526191711426</t>
+    <t xml:space="preserve">13.546106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4145555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8526182174683</t>
   </si>
   <si>
     <t xml:space="preserve">14.218729019165</t>
@@ -2276,19 +2276,19 @@
     <t xml:space="preserve">13.775990486145</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4439353942871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8441028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4486122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254083633423</t>
+    <t xml:space="preserve">13.4439344406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8441038131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4486112594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6274118423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9254102706909</t>
   </si>
   <si>
     <t xml:space="preserve">15.504373550415</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">14.5933523178101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5592975616455</t>
+    <t xml:space="preserve">14.5592985153198</t>
   </si>
   <si>
     <t xml:space="preserve">14.9424362182617</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">14.9679794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6870107650757</t>
+    <t xml:space="preserve">14.6870088577271</t>
   </si>
   <si>
     <t xml:space="preserve">15.019063949585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1467761993408</t>
+    <t xml:space="preserve">15.1467800140381</t>
   </si>
   <si>
     <t xml:space="preserve">15.3170614242554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6405992507935</t>
+    <t xml:space="preserve">15.6406030654907</t>
   </si>
   <si>
     <t xml:space="preserve">15.461802482605</t>
@@ -2330,34 +2330,34 @@
     <t xml:space="preserve">14.363471031189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3294134140015</t>
+    <t xml:space="preserve">14.3294124603271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1506156921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1335878372192</t>
+    <t xml:space="preserve">14.1506147384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1335868835449</t>
   </si>
   <si>
     <t xml:space="preserve">14.5763254165649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1165571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804979324341</t>
+    <t xml:space="preserve">14.1165580749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4911832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804988861084</t>
   </si>
   <si>
     <t xml:space="preserve">14.499698638916</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7721519470215</t>
+    <t xml:space="preserve">14.7721509933472</t>
   </si>
   <si>
     <t xml:space="preserve">13.7078762054443</t>
@@ -2366,19 +2366,19 @@
     <t xml:space="preserve">13.9292449951172</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5035352706909</t>
+    <t xml:space="preserve">13.5035343170166</t>
   </si>
   <si>
     <t xml:space="preserve">13.3162231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5631351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375928878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4060401916504</t>
+    <t xml:space="preserve">13.5631341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4060411453247</t>
   </si>
   <si>
     <t xml:space="preserve">14.2698135375977</t>
@@ -2390,49 +2390,49 @@
     <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.758960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4183931350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5584573745728</t>
+    <t xml:space="preserve">14.5167255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.176157951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931858062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7589616775513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4183940887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5584583282471</t>
   </si>
   <si>
     <t xml:space="preserve">12.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010293960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9880056381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6218938827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430952072144</t>
+    <t xml:space="preserve">12.6010274887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9880065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6218948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430961608887</t>
   </si>
   <si>
     <t xml:space="preserve">10.3277349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82539653778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42522811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74025344848633</t>
+    <t xml:space="preserve">9.82539749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4252290725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74025440216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.08424186706543</t>
@@ -2444,34 +2444,34 @@
     <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078491210938</t>
+    <t xml:space="preserve">8.31412506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078538894653</t>
   </si>
   <si>
     <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11020469665527</t>
+    <t xml:space="preserve">9.11020278930664</t>
   </si>
   <si>
     <t xml:space="preserve">9.00803279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41671371459961</t>
+    <t xml:space="preserve">9.41671562194824</t>
   </si>
   <si>
     <t xml:space="preserve">9.47631359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225692749023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46780109405518</t>
+    <t xml:space="preserve">9.57848358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225788116455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
     <t xml:space="preserve">9.09317493438721</t>
@@ -2495,25 +2495,25 @@
     <t xml:space="preserve">10.1319074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0467672348022</t>
+    <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87648296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97013854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0552806854248</t>
+    <t xml:space="preserve">9.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.970139503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0552797317505</t>
   </si>
   <si>
     <t xml:space="preserve">10.2936792373657</t>
   </si>
   <si>
-    <t xml:space="preserve">10.319221496582</t>
+    <t xml:space="preserve">10.3192205429077</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299058914185</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9616231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85945320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78282451629639</t>
+    <t xml:space="preserve">9.96162414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85945415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7828254699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.3060302734375</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">9.5103702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51888561248779</t>
+    <t xml:space="preserve">9.51888465881348</t>
   </si>
   <si>
     <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26345825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25494575500488</t>
+    <t xml:space="preserve">9.26345920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25494384765625</t>
   </si>
   <si>
     <t xml:space="preserve">9.36562919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8632926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93140602111816</t>
+    <t xml:space="preserve">8.86329078674316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93140411376953</t>
   </si>
   <si>
     <t xml:space="preserve">8.85477638244629</t>
@@ -2570,16 +2570,16 @@
     <t xml:space="preserve">9.28048706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70619869232178</t>
+    <t xml:space="preserve">9.70619773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.62957000732422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85093975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187671661377</t>
+    <t xml:space="preserve">9.85093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300743103027</t>
@@ -2588,10 +2588,10 @@
     <t xml:space="preserve">10.5405902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2340793609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254119873047</t>
+    <t xml:space="preserve">10.2340784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61254215240479</t>
   </si>
   <si>
     <t xml:space="preserve">9.9638843536377</t>
@@ -2600,16 +2600,16 @@
     <t xml:space="preserve">10.2435731887817</t>
   </si>
   <si>
-    <t xml:space="preserve">10.182391166687</t>
+    <t xml:space="preserve">10.1823902130127</t>
   </si>
   <si>
     <t xml:space="preserve">10.1998720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1649112701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0600280761719</t>
+    <t xml:space="preserve">10.1649103164673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0600271224976</t>
   </si>
   <si>
     <t xml:space="preserve">10.444598197937</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">9.90270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72789764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64049530029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28214550018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56183338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41324806213379</t>
+    <t xml:space="preserve">9.72789859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64049434661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28214454650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56183242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41324901580811</t>
   </si>
   <si>
     <t xml:space="preserve">9.52687168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49190998077393</t>
+    <t xml:space="preserve">9.49191188812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.40450954437256</t>
@@ -2648,19 +2648,19 @@
     <t xml:space="preserve">9.15978145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99371719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01993846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90631294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57931423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20348262786865</t>
+    <t xml:space="preserve">8.99371814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01993751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9063138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57931232452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20348167419434</t>
   </si>
   <si>
     <t xml:space="preserve">9.36080741882324</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">9.33458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22096347808838</t>
+    <t xml:space="preserve">9.2209644317627</t>
   </si>
   <si>
     <t xml:space="preserve">9.44821071624756</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">9.29088592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01119709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3484554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358568191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9777545928955</t>
+    <t xml:space="preserve">9.01119804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3484573364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271192550659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9777536392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001176834106</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">11.4672069549561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0826377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8903522491455</t>
+    <t xml:space="preserve">11.0826368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8903512954712</t>
   </si>
   <si>
     <t xml:space="preserve">10.7942094802856</t>
@@ -2720,22 +2720,22 @@
     <t xml:space="preserve">10.5494804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299505233765</t>
+    <t xml:space="preserve">10.2872743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299495697021</t>
   </si>
   <si>
     <t xml:space="preserve">9.98136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93766498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.094988822937</t>
+    <t xml:space="preserve">9.93766403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0949878692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.1124687194824</t>
@@ -2744,46 +2744,46 @@
     <t xml:space="preserve">10.0250673294067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95514583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78034019470215</t>
+    <t xml:space="preserve">9.95514488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78033924102783</t>
   </si>
   <si>
     <t xml:space="preserve">9.75411891937256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6579761505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7453784942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99884414672852</t>
+    <t xml:space="preserve">9.65797519683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74537944793701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99884605407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222351074219</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7330265045166</t>
+    <t xml:space="preserve">10.7330255508423</t>
   </si>
   <si>
     <t xml:space="preserve">10.7505073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4620800018311</t>
+    <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3834171295166</t>
+    <t xml:space="preserve">10.3834161758423</t>
   </si>
   <si>
     <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4970407485962</t>
+    <t xml:space="preserve">10.4970397949219</t>
   </si>
   <si>
     <t xml:space="preserve">10.6893253326416</t>
@@ -2801,16 +2801,16 @@
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5582218170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4708185195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81529998779297</t>
+    <t xml:space="preserve">10.5232610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5582208633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4708194732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81530094146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">9.6142749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00245761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82765293121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36878967285156</t>
+    <t xml:space="preserve">9.0024585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82765197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36878776550293</t>
   </si>
   <si>
     <t xml:space="preserve">8.53485298156738</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">9.12482070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16852283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883399963379</t>
+    <t xml:space="preserve">9.16852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883495330811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98497676849365</t>
@@ -2858,46 +2858,46 @@
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078321456909</t>
+    <t xml:space="preserve">9.69293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078311920166</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350774765015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3587131500244</t>
+    <t xml:space="preserve">11.6070508956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3587141036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.5597381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867406845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4810752868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1926488876343</t>
+    <t xml:space="preserve">11.886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4810762405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.19264793396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0702857971191</t>
+    <t xml:space="preserve">12.2101278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857137680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0702848434448</t>
   </si>
   <si>
     <t xml:space="preserve">11.9741411209106</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">12.0615453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314678192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440635681152</t>
+    <t xml:space="preserve">12.1314668655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440645217896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0091028213501</t>
+    <t xml:space="preserve">12.0091037750244</t>
   </si>
   <si>
     <t xml:space="preserve">12.0178442001343</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">12.6558809280396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6733617782593</t>
+    <t xml:space="preserve">12.673360824585</t>
   </si>
   <si>
     <t xml:space="preserve">12.4898166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4198951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684795379639</t>
+    <t xml:space="preserve">12.4198961257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684785842896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5422592163086</t>
@@ -2954,22 +2954,22 @@
     <t xml:space="preserve">12.4461154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5160369873047</t>
+    <t xml:space="preserve">12.516037940979</t>
   </si>
   <si>
     <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132066726685</t>
+    <t xml:space="preserve">12.2713108062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132057189941</t>
   </si>
   <si>
     <t xml:space="preserve">12.8394269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093494415283</t>
+    <t xml:space="preserve">12.9093503952026</t>
   </si>
   <si>
     <t xml:space="preserve">12.821946144104</t>
@@ -2981,28 +2981,28 @@
     <t xml:space="preserve">13.0229721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114004135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2152576446533</t>
+    <t xml:space="preserve">13.3113994598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2152585983276</t>
   </si>
   <si>
     <t xml:space="preserve">13.2502193450928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607650756836</t>
+    <t xml:space="preserve">12.7607660293579</t>
   </si>
   <si>
     <t xml:space="preserve">12.6296615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9530506134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9792718887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355707168579</t>
+    <t xml:space="preserve">12.953049659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9792728424072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355688095093</t>
   </si>
   <si>
     <t xml:space="preserve">13.3026609420776</t>
@@ -3014,31 +3014,31 @@
     <t xml:space="preserve">13.1890363693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2239971160889</t>
+    <t xml:space="preserve">13.2239980697632</t>
   </si>
   <si>
     <t xml:space="preserve">13.800853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0281000137329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1067628860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.395191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500075340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5612554550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2116451263428</t>
+    <t xml:space="preserve">14.0281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1067638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5000743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5612564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2116470336914</t>
   </si>
   <si>
     <t xml:space="preserve">13.7484130859375</t>
@@ -3047,7 +3047,7 @@
     <t xml:space="preserve">14.0980215072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221927642822</t>
+    <t xml:space="preserve">13.7221918106079</t>
   </si>
   <si>
     <t xml:space="preserve">14.3864498138428</t>
@@ -3056,79 +3056,79 @@
     <t xml:space="preserve">14.6661396026611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7098398208618</t>
+    <t xml:space="preserve">14.7098407745361</t>
   </si>
   <si>
     <t xml:space="preserve">14.6224374771118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0157489776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818141937256</t>
+    <t xml:space="preserve">15.0157499313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818151473999</t>
   </si>
   <si>
     <t xml:space="preserve">15.3653593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1206312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.456374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6136960983276</t>
+    <t xml:space="preserve">15.1206321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4563751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6136951446533</t>
   </si>
   <si>
     <t xml:space="preserve">14.7622814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3442668914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7550601959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373327255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.915994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9247369766235</t>
+    <t xml:space="preserve">16.3442687988281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7550563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946546554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373336791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9159965515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
     <t xml:space="preserve">15.9422149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.13450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4352807998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.330397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2429962158203</t>
+    <t xml:space="preserve">16.1344985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.43528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5663843154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.356616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.242995262146</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255144119263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.286696434021</t>
+    <t xml:space="preserve">15.2866973876953</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779579162598</t>
@@ -3137,73 +3137,73 @@
     <t xml:space="preserve">15.2517347335815</t>
   </si>
   <si>
-    <t xml:space="preserve">15.068190574646</t>
+    <t xml:space="preserve">15.0681896209717</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381130218506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4265403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.024489402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8933868408203</t>
+    <t xml:space="preserve">15.4265422821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0244903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.893385887146</t>
   </si>
   <si>
     <t xml:space="preserve">14.8234634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0856714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.919605255127</t>
+    <t xml:space="preserve">15.0856704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196062088013</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9370861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1468515396118</t>
+    <t xml:space="preserve">14.937087059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1468524932861</t>
   </si>
   <si>
     <t xml:space="preserve">14.849684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.26047706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041772842407</t>
+    <t xml:space="preserve">15.1031513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2604751586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.304178237915</t>
   </si>
   <si>
     <t xml:space="preserve">14.8409433364868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4214115142822</t>
+    <t xml:space="preserve">14.4214124679565</t>
   </si>
   <si>
     <t xml:space="preserve">14.5962181091309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7812786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4367980957031</t>
+    <t xml:space="preserve">16.7812824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4368000030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.4630184173584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2846031188965</t>
+    <t xml:space="preserve">18.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2846050262451</t>
   </si>
   <si>
     <t xml:space="preserve">18.8397483825684</t>
@@ -3215,16 +3215,16 @@
     <t xml:space="preserve">18.7340087890625</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4696502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8573741912842</t>
+    <t xml:space="preserve">18.4696521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8573722839355</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3684616088867</t>
+    <t xml:space="preserve">19.3684597015381</t>
   </si>
   <si>
     <t xml:space="preserve">18.9631175994873</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">19.1217288970947</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0688571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9807376861572</t>
+    <t xml:space="preserve">19.0688591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.8749961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5753955841064</t>
+    <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
     <t xml:space="preserve">18.2052955627441</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">18.2405433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7163848876953</t>
+    <t xml:space="preserve">18.7163829803467</t>
   </si>
   <si>
     <t xml:space="preserve">18.2934150695801</t>
@@ -3266,19 +3266,19 @@
     <t xml:space="preserve">18.2581672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1524257659912</t>
+    <t xml:space="preserve">18.1524276733398</t>
   </si>
   <si>
     <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9056949615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8880672454834</t>
+    <t xml:space="preserve">17.8175735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9056930541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708427429199</t>
+    <t xml:space="preserve">17.5708446502686</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589603424072</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">17.526782989502</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3681678771973</t>
+    <t xml:space="preserve">17.3681697845459</t>
   </si>
   <si>
     <t xml:space="preserve">17.1478710174561</t>
@@ -3311,16 +3311,16 @@
     <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.482723236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2007446289062</t>
+    <t xml:space="preserve">17.4827213287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">16.3724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1256980895996</t>
+    <t xml:space="preserve">16.125696182251</t>
   </si>
   <si>
     <t xml:space="preserve">16.5222301483154</t>
@@ -3344,7 +3344,7 @@
     <t xml:space="preserve">17.7823276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7470798492432</t>
+    <t xml:space="preserve">17.7470779418945</t>
   </si>
   <si>
     <t xml:space="preserve">17.5355949401855</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">17.6237125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747062683105</t>
+    <t xml:space="preserve">16.8747043609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861911773682</t>
@@ -3365,19 +3365,19 @@
     <t xml:space="preserve">17.3417339324951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1654968261719</t>
+    <t xml:space="preserve">17.1654949188232</t>
   </si>
   <si>
     <t xml:space="preserve">16.9540119171143</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3593597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9716358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249050140381</t>
+    <t xml:space="preserve">17.3593578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9716377258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249031066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3386,13 +3386,13 @@
     <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4869823455811</t>
+    <t xml:space="preserve">16.4869842529297</t>
   </si>
   <si>
     <t xml:space="preserve">16.8042125701904</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2183685302734</t>
+    <t xml:space="preserve">17.2183704376221</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704471588135</t>
@@ -3404,13 +3404,13 @@
     <t xml:space="preserve">17.5796546936035</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5972785949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2888622283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0421314239502</t>
+    <t xml:space="preserve">17.5972766876221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2888641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0421295166016</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425270080566</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957962036133</t>
+    <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
@@ -3428,7 +3428,7 @@
     <t xml:space="preserve">16.3900527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3019371032715</t>
+    <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
     <t xml:space="preserve">15.99351978302</t>
@@ -3443,7 +3443,7 @@
     <t xml:space="preserve">16.5134201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.31955909729</t>
+    <t xml:space="preserve">16.3195610046387</t>
   </si>
   <si>
     <t xml:space="preserve">15.7732229232788</t>
@@ -3452,13 +3452,13 @@
     <t xml:space="preserve">15.5176792144775</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4119367599487</t>
+    <t xml:space="preserve">15.411937713623</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590669631958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0330286026001</t>
+    <t xml:space="preserve">15.0330276489258</t>
   </si>
   <si>
     <t xml:space="preserve">15.3150062561035</t>
@@ -3467,10 +3467,10 @@
     <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2180776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1828289031982</t>
+    <t xml:space="preserve">15.2180767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1828279495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242137908936</t>
@@ -3479,7 +3479,7 @@
     <t xml:space="preserve">15.1123352050781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1035213470459</t>
+    <t xml:space="preserve">15.1035223007202</t>
   </si>
   <si>
     <t xml:space="preserve">15.4912443161011</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">15.1475820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0858993530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9801559448242</t>
+    <t xml:space="preserve">15.085898399353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9801568984985</t>
   </si>
   <si>
     <t xml:space="preserve">14.8215436935425</t>
@@ -3506,10 +3506,10 @@
     <t xml:space="preserve">14.0020418167114</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0725345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8434267044067</t>
+    <t xml:space="preserve">14.0725355148315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8434276580811</t>
   </si>
   <si>
     <t xml:space="preserve">13.8962993621826</t>
@@ -3521,7 +3521,7 @@
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104543685913</t>
+    <t xml:space="preserve">14.3104553222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.345703125</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">13.9491701126099</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1080722808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5483751296997</t>
+    <t xml:space="preserve">16.1080741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.548376083374</t>
   </si>
   <si>
     <t xml:space="preserve">14.4778804779053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1870899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254081726074</t>
+    <t xml:space="preserve">14.1870889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254072189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4028329849243</t>
+    <t xml:space="preserve">13.0327367782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4028339385986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1296663284302</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">12.9446172714233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3852090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5350122451782</t>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5350112915039</t>
   </si>
   <si>
     <t xml:space="preserve">13.5614471435547</t>
@@ -3593,7 +3593,7 @@
     <t xml:space="preserve">13.2265968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6231298446655</t>
+    <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
     <t xml:space="preserve">13.314715385437</t>
@@ -3602,19 +3602,19 @@
     <t xml:space="preserve">13.2618446350098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557056427002</t>
+    <t xml:space="preserve">13.4557046890259</t>
   </si>
   <si>
     <t xml:space="preserve">13.438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4645166397095</t>
+    <t xml:space="preserve">13.4645175933838</t>
   </si>
   <si>
     <t xml:space="preserve">13.4997644424438</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4821405410767</t>
+    <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
     <t xml:space="preserve">13.5878829956055</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">13.7112503051758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4468936920166</t>
+    <t xml:space="preserve">13.4468927383423</t>
   </si>
   <si>
     <t xml:space="preserve">13.1649141311646</t>
@@ -3644,19 +3644,19 @@
     <t xml:space="preserve">12.6978845596313</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6890735626221</t>
+    <t xml:space="preserve">12.6890726089478</t>
   </si>
   <si>
     <t xml:space="preserve">12.5128364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5568952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273908615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.40709400177</t>
+    <t xml:space="preserve">12.5568962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273918151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4070949554443</t>
   </si>
   <si>
     <t xml:space="preserve">11.6492757797241</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">11.8078880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9048194885254</t>
+    <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
     <t xml:space="preserve">11.8431348800659</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">12.1427383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841260910034</t>
+    <t xml:space="preserve">11.9841251373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.5347204208374</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">11.464225769043</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1117506027222</t>
+    <t xml:space="preserve">11.1117515563965</t>
   </si>
   <si>
     <t xml:space="preserve">10.9090795516968</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">10.8033361434937</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1910581588745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3937311172485</t>
+    <t xml:space="preserve">11.1910591125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3937301635742</t>
   </si>
   <si>
     <t xml:space="preserve">11.1822452545166</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">10.2393770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710155487061</t>
+    <t xml:space="preserve">9.73710060119629</t>
   </si>
   <si>
     <t xml:space="preserve">9.54324054718018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56967544555664</t>
+    <t xml:space="preserve">9.56967639923096</t>
   </si>
   <si>
     <t xml:space="preserve">10.0455160140991</t>
@@ -3755,13 +3755,13 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868709564209</t>
+    <t xml:space="preserve">9.42868614196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.61373519897461</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64883708953857</t>
+    <t xml:space="preserve">8.64883804321289</t>
   </si>
   <si>
     <t xml:space="preserve">9.01452922821045</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">8.89116382598877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87353992462158</t>
+    <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
     <t xml:space="preserve">9.25244998931885</t>
@@ -3803,13 +3803,13 @@
     <t xml:space="preserve">8.2787389755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24349117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43735313415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35363864898682</t>
+    <t xml:space="preserve">8.24349212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43735218048096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
     <t xml:space="preserve">8.27433395385742</t>
@@ -3821,10 +3821,10 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31398582458496</t>
+    <t xml:space="preserve">8.36245155334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31398677825928</t>
   </si>
   <si>
     <t xml:space="preserve">8.42413520812988</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">8.08487796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01878929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20824432373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01438331604004</t>
+    <t xml:space="preserve">8.01879024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20824337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.8866114616394</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">8.02760219573975</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89542388916016</t>
+    <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
@@ -3866,13 +3866,13 @@
     <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69275140762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66190958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527545928955</t>
+    <t xml:space="preserve">7.69275045394897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66190910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527593612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.67512702941895</t>
@@ -70712,7 +70712,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495023148</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>77689</v>
@@ -70733,6 +70733,32 @@
         <v>1874</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6493865741</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>58187</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>4.38500022888184</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>4.42999982833862</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>1882</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -38,106 +38,106 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608804702759</t>
+    <t xml:space="preserve">12.7608833312988</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767124176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758977890015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742685317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.270076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075635910034</t>
+    <t xml:space="preserve">12.784628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767114639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742694854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700796127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075626373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.4125690460205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563402175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3729867935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.175085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413228988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.19091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713594436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367835998535</t>
+    <t xml:space="preserve">12.6738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0563411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3729877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1750841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
   </si>
   <si>
     <t xml:space="preserve">11.9850959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1380624771118</t>
+    <t xml:space="preserve">11.1380643844604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9955739974976</t>
   </si>
   <si>
-    <t xml:space="preserve">11.462628364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1063995361328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942922592163</t>
+    <t xml:space="preserve">11.4626264572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1064004898071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942941665649</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417900085449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3597173690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584356307983</t>
+    <t xml:space="preserve">11.3597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8584365844727</t>
   </si>
   <si>
     <t xml:space="preserve">11.5180406570435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7159442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346881866455</t>
+    <t xml:space="preserve">11.7159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346872329712</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684494018555</t>
+    <t xml:space="preserve">11.6684484481812</t>
   </si>
   <si>
     <t xml:space="preserve">11.3992977142334</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2304964065552</t>
+    <t xml:space="preserve">12.4284009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2304954528809</t>
   </si>
   <si>
     <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1513357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9508695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408576965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754344940186</t>
+    <t xml:space="preserve">12.1513347625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242120742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508676528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408596038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754316329956</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704252243042</t>
@@ -188,70 +188,70 @@
     <t xml:space="preserve">13.3387613296509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5762462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999946594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.752965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.196270942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9904479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221166610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300312042236</t>
+    <t xml:space="preserve">13.4575061798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762491226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7529649734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1962728500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9904508590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0300321578979</t>
   </si>
   <si>
     <t xml:space="preserve">12.6975517272949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6025562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.650053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8637924194336</t>
+    <t xml:space="preserve">12.602557182312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6500539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.863790512085</t>
   </si>
   <si>
     <t xml:space="preserve">12.586724281311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788087844849</t>
+    <t xml:space="preserve">12.4679832458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650732040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788097381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.7286958694458</t>
@@ -260,55 +260,55 @@
     <t xml:space="preserve">12.1493892669678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1091594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9884691238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218008041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620325088501</t>
+    <t xml:space="preserve">12.1091575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218027114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.22984790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620315551758</t>
   </si>
   <si>
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953632354736</t>
+    <t xml:space="preserve">12.4953651428223</t>
   </si>
   <si>
     <t xml:space="preserve">12.7126045227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0263977050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252468109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.865478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172006607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999622344971</t>
+    <t xml:space="preserve">12.809157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735227584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0263967514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">12.3666296005249</t>
@@ -317,49 +317,49 @@
     <t xml:space="preserve">12.3103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390441894531</t>
+    <t xml:space="preserve">11.7390432357788</t>
   </si>
   <si>
     <t xml:space="preserve">11.4011135101318</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8781290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022644042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689287185669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103096008301</t>
+    <t xml:space="preserve">11.2884721755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8781280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689296722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103086471558</t>
   </si>
   <si>
     <t xml:space="preserve">11.3689308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4896202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7574396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735321044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4597387313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229539871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424942016602</t>
+    <t xml:space="preserve">11.4896211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424922943115</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344480514526</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">11.2321500778198</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9827251434326</t>
+    <t xml:space="preserve">10.9827260971069</t>
   </si>
   <si>
     <t xml:space="preserve">10.92640209198</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">11.2160577774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7229528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470922470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5700798034668</t>
+    <t xml:space="preserve">11.7229537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470903396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5700807571411</t>
   </si>
   <si>
     <t xml:space="preserve">11.8919172286987</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">11.5861711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8758277893066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953643798828</t>
+    <t xml:space="preserve">11.8758268356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953653335571</t>
   </si>
   <si>
     <t xml:space="preserve">12.1896181106567</t>
@@ -404,193 +404,193 @@
     <t xml:space="preserve">12.4309959411621</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896169662476</t>
+    <t xml:space="preserve">12.8896160125732</t>
   </si>
   <si>
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1229486465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1551322937012</t>
+    <t xml:space="preserve">12.9942140579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1229496002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1551332473755</t>
   </si>
   <si>
     <t xml:space="preserve">12.9861669540405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0746736526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482351303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2493801116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459339141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8551292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643232345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275424957275</t>
+    <t xml:space="preserve">13.0746726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459329605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919069290161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275415420532</t>
   </si>
   <si>
     <t xml:space="preserve">14.8206453323364</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6034049987793</t>
+    <t xml:space="preserve">14.603404045105</t>
   </si>
   <si>
     <t xml:space="preserve">14.4022550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3137502670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516790390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505289077759</t>
+    <t xml:space="preserve">14.3137512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516771316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562780380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183481216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505279541016</t>
   </si>
   <si>
     <t xml:space="preserve">15.1263914108276</t>
   </si>
   <si>
-    <t xml:space="preserve">15.08616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0459327697754</t>
+    <t xml:space="preserve">15.0861616134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0459318161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.295355796814</t>
   </si>
   <si>
-    <t xml:space="preserve">15.424090385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597230911255</t>
+    <t xml:space="preserve">15.4240894317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562711715698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597240447998</t>
   </si>
   <si>
     <t xml:space="preserve">15.2873115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689184188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240905761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367357254028</t>
+    <t xml:space="preserve">14.8689193725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367347717285</t>
   </si>
   <si>
     <t xml:space="preserve">14.7884607315063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8930606842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4884586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.80455493927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3919076919556</t>
+    <t xml:space="preserve">14.8930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4884576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401817321777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045511245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3919057846069</t>
   </si>
   <si>
     <t xml:space="preserve">15.2551259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1666212081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0137491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.198802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114461898804</t>
+    <t xml:space="preserve">15.1666202545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0137481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1988039016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.311448097229</t>
   </si>
   <si>
     <t xml:space="preserve">15.3677682876587</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3034029006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827116012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470808029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5390367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263925552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2815656661987</t>
+    <t xml:space="preserve">15.3033990859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827096939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654731750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5390357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1126012802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815637588501</t>
   </si>
   <si>
     <t xml:space="preserve">14.4827146530151</t>
@@ -602,124 +602,124 @@
     <t xml:space="preserve">14.4103012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5631761550903</t>
+    <t xml:space="preserve">14.5631732940674</t>
   </si>
   <si>
     <t xml:space="preserve">14.4585762023926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3057022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.321795463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9516830444336</t>
+    <t xml:space="preserve">14.305703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045551300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217964172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951681137085</t>
   </si>
   <si>
     <t xml:space="preserve">13.6781196594238</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4045572280884</t>
+    <t xml:space="preserve">13.404559135437</t>
   </si>
   <si>
     <t xml:space="preserve">13.3643274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1873149871826</t>
+    <t xml:space="preserve">13.1873159408569</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.31605052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5896129608154</t>
+    <t xml:space="preserve">13.3160514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">13.7746725082397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9114532470703</t>
+    <t xml:space="preserve">13.911452293396</t>
   </si>
   <si>
     <t xml:space="preserve">14.2011070251465</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9999570846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9815626144409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160482406616</t>
+    <t xml:space="preserve">13.9999561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378847122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.716046333313</t>
   </si>
   <si>
     <t xml:space="preserve">14.844780921936</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9171981811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6010999679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1103000640869</t>
+    <t xml:space="preserve">14.917197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011018753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528249740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367364883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045518875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4080009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.110297203064</t>
   </si>
   <si>
     <t xml:space="preserve">15.2068510055542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8263874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.89075756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470777511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114459991455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3493747711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3010997772217</t>
+    <t xml:space="preserve">15.8263902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8987998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.947078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114440917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.301097869873</t>
   </si>
   <si>
     <t xml:space="preserve">16.5344333648682</t>
@@ -728,40 +728,40 @@
     <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4539756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1723651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.156270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700672149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436267852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4781112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8965015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769611358643</t>
+    <t xml:space="preserve">16.3332824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1562728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792613983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919075012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4781093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8964996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769592285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.0413284301758</t>
@@ -773,22 +773,22 @@
     <t xml:space="preserve">17.5160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7735080718994</t>
+    <t xml:space="preserve">17.7735118865967</t>
   </si>
   <si>
     <t xml:space="preserve">18.3850040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7470684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229309082031</t>
+    <t xml:space="preserve">18.7470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229290008545</t>
   </si>
   <si>
     <t xml:space="preserve">19.0206317901611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.270055770874</t>
+    <t xml:space="preserve">19.2700576782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907470703125</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">19.4068393707275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033912658691</t>
+    <t xml:space="preserve">19.4470653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033893585205</t>
   </si>
   <si>
     <t xml:space="preserve">19.6079864501953</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6321220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.382698059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5838508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436172485352</t>
+    <t xml:space="preserve">19.6321239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125835418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3826999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5838470458984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3102855682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436229705811</t>
   </si>
   <si>
     <t xml:space="preserve">19.4631595611572</t>
@@ -833,31 +833,31 @@
     <t xml:space="preserve">19.0689067840576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0769519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.972354888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5620136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5056915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.618335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171806335449</t>
+    <t xml:space="preserve">19.0769538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9723567962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5620098114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171787261963</t>
   </si>
   <si>
     <t xml:space="preserve">20.2597064971924</t>
@@ -866,16 +866,16 @@
     <t xml:space="preserve">20.7585582733154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.557409286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213714599609</t>
+    <t xml:space="preserve">20.5574054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818675994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0841827392578</t>
@@ -884,7 +884,7 @@
     <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0027770996094</t>
+    <t xml:space="preserve">21.0027751922607</t>
   </si>
   <si>
     <t xml:space="preserve">21.5726203918457</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">20.538761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5550384521484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.489917755127</t>
+    <t xml:space="preserve">20.5550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899158477783</t>
   </si>
   <si>
     <t xml:space="preserve">20.3922290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3271064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3515281677246</t>
+    <t xml:space="preserve">20.3271045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.351526260376</t>
   </si>
   <si>
     <t xml:space="preserve">20.5143394470215</t>
@@ -917,19 +917,19 @@
     <t xml:space="preserve">20.9946365356445</t>
   </si>
   <si>
-    <t xml:space="preserve">20.937650680542</t>
+    <t xml:space="preserve">20.9376487731934</t>
   </si>
   <si>
     <t xml:space="preserve">21.124885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0353393554688</t>
+    <t xml:space="preserve">21.0353374481201</t>
   </si>
   <si>
     <t xml:space="preserve">20.8399639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8155422210693</t>
+    <t xml:space="preserve">20.815544128418</t>
   </si>
   <si>
     <t xml:space="preserve">21.1574478149414</t>
@@ -938,76 +938,76 @@
     <t xml:space="preserve">20.2945423126221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5957469940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3189659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0828857421875</t>
+    <t xml:space="preserve">20.5957450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3189640045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0828876495361</t>
   </si>
   <si>
     <t xml:space="preserve">20.1480121612549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9851989746094</t>
+    <t xml:space="preserve">19.9851970672607</t>
   </si>
   <si>
     <t xml:space="preserve">20.1317310333252</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3678092956543</t>
+    <t xml:space="preserve">20.3678073883057</t>
   </si>
   <si>
     <t xml:space="preserve">20.7259941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.310827255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3583736419678</t>
+    <t xml:space="preserve">20.3108253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3583717346191</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874198913574</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9757614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8048133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7071228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338577270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1304378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049942016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816848754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805763244629</t>
+    <t xml:space="preserve">18.9757652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8048114776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338558197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1304340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805744171143</t>
   </si>
   <si>
     <t xml:space="preserve">20.2375564575195</t>
@@ -1016,25 +1016,25 @@
     <t xml:space="preserve">20.78297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7748374938965</t>
+    <t xml:space="preserve">20.7748413085938</t>
   </si>
   <si>
     <t xml:space="preserve">20.9050884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.677152633667</t>
+    <t xml:space="preserve">20.6771507263184</t>
   </si>
   <si>
     <t xml:space="preserve">21.1655883789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2795581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0434761047363</t>
+    <t xml:space="preserve">21.2795562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0434799194336</t>
   </si>
   <si>
     <t xml:space="preserve">20.6852931976318</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">21.1004638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5400562286377</t>
+    <t xml:space="preserve">21.540060043335</t>
   </si>
   <si>
     <t xml:space="preserve">21.4260864257812</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">21.5319175720215</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202610015869</t>
+    <t xml:space="preserve">21.3202590942383</t>
   </si>
   <si>
     <t xml:space="preserve">21.922664642334</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">21.7842750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4993534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935241699219</t>
+    <t xml:space="preserve">21.4993553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935260772705</t>
   </si>
   <si>
     <t xml:space="preserve">21.7761344909668</t>
@@ -1073,70 +1073,70 @@
     <t xml:space="preserve">21.6214599609375</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169315338135</t>
+    <t xml:space="preserve">22.0691947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7110118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169296264648</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6308975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0542106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.989086151123</t>
+    <t xml:space="preserve">22.630895614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0542087554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9890823364258</t>
   </si>
   <si>
     <t xml:space="preserve">23.2007389068604</t>
   </si>
   <si>
-    <t xml:space="preserve">23.168176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4693813323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8601303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310821533203</t>
+    <t xml:space="preserve">23.1681785583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4693794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310859680176</t>
   </si>
   <si>
     <t xml:space="preserve">23.9659595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008350372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9903812408447</t>
+    <t xml:space="preserve">24.0229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008331298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9903793334961</t>
   </si>
   <si>
     <t xml:space="preserve">23.599630355835</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5263633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9822387695312</t>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9822368621826</t>
   </si>
   <si>
     <t xml:space="preserve">24.23459815979</t>
@@ -1145,37 +1145,37 @@
     <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0568008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0079536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8777046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288631439209</t>
+    <t xml:space="preserve">24.9916725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0567989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.87770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6497688293457</t>
+    <t xml:space="preserve">24.649772644043</t>
   </si>
   <si>
     <t xml:space="preserve">25.6999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9604091644287</t>
+    <t xml:space="preserve">25.9604053497314</t>
   </si>
   <si>
     <t xml:space="preserve">25.4801120758057</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1789112091064</t>
+    <t xml:space="preserve">25.1789093017578</t>
   </si>
   <si>
     <t xml:space="preserve">24.1613330841064</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">24.5765037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4556903839111</t>
+    <t xml:space="preserve">25.4556922912598</t>
   </si>
   <si>
     <t xml:space="preserve">26.2778911590576</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">27.7676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3850154876709</t>
+    <t xml:space="preserve">27.3850135803223</t>
   </si>
   <si>
     <t xml:space="preserve">26.9210014343262</t>
@@ -1214,37 +1214,37 @@
     <t xml:space="preserve">27.5071258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0105457305908</t>
+    <t xml:space="preserve">27.0105476379395</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2765941619873</t>
+    <t xml:space="preserve">25.2765960693359</t>
   </si>
   <si>
     <t xml:space="preserve">24.9102687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5032386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6172065734863</t>
+    <t xml:space="preserve">24.5032367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.617208480835</t>
   </si>
   <si>
     <t xml:space="preserve">24.5846462249756</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2440319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8451442718506</t>
+    <t xml:space="preserve">25.2440357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8451461791992</t>
   </si>
   <si>
     <t xml:space="preserve">24.739315032959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951923370361</t>
+    <t xml:space="preserve">25.1951904296875</t>
   </si>
   <si>
     <t xml:space="preserve">25.6429252624512</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">25.7243309020996</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6917686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5452365875244</t>
+    <t xml:space="preserve">25.6917667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.545238494873</t>
   </si>
   <si>
     <t xml:space="preserve">25.756893157959</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">25.3173007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.512674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7650337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.049955368042</t>
+    <t xml:space="preserve">25.3987083435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5126724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7650356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499534606934</t>
   </si>
   <si>
     <t xml:space="preserve">25.2033309936523</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">25.6836261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7419052124023</t>
+    <t xml:space="preserve">26.7419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">26.5790939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3931560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6604995727539</t>
+    <t xml:space="preserve">27.393159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6605033874512</t>
   </si>
   <si>
     <t xml:space="preserve">26.497688293457</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">26.1313591003418</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6022205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127666473389</t>
+    <t xml:space="preserve">25.602222442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127685546875</t>
   </si>
   <si>
     <t xml:space="preserve">26.2941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7826118469238</t>
+    <t xml:space="preserve">26.7826099395752</t>
   </si>
   <si>
     <t xml:space="preserve">27.3117485046387</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">27.881591796875</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2303428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720657348633</t>
+    <t xml:space="preserve">27.2303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6197967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.172061920166</t>
   </si>
   <si>
     <t xml:space="preserve">25.0730819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6253452301025</t>
+    <t xml:space="preserve">24.6253471374512</t>
   </si>
   <si>
     <t xml:space="preserve">23.8519897460938</t>
@@ -1370,22 +1370,22 @@
     <t xml:space="preserve">23.9740982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3580017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3635540008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4218311309814</t>
+    <t xml:space="preserve">25.5615196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.358003616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358913421631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3635520935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4218330383301</t>
   </si>
   <si>
     <t xml:space="preserve">26.2534713745117</t>
@@ -1394,49 +1394,49 @@
     <t xml:space="preserve">23.6891784667969</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1887130737305</t>
+    <t xml:space="preserve">23.5670700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7002792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4736347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540260314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273815155029</t>
+    <t xml:space="preserve">20.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7002811431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540241241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273834228516</t>
   </si>
   <si>
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6947250366211</t>
+    <t xml:space="preserve">20.8806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284034729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.4680862426758</t>
@@ -1445,46 +1445,46 @@
     <t xml:space="preserve">22.1831645965576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5901947021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0203533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3459739685059</t>
+    <t xml:space="preserve">22.5901966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0203514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3459758758545</t>
   </si>
   <si>
     <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8057403564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7067565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3811321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.218318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1776142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2997207641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.788158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7053928375244</t>
+    <t xml:space="preserve">22.7123050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8057384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7067546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3811283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2183170318604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1776123046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2997245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7881603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
     <t xml:space="preserve">24.1260395050049</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">24.6640110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9123077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019844055176</t>
+    <t xml:space="preserve">24.9123096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019863128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.408899307251</t>
@@ -1511,61 +1511,61 @@
     <t xml:space="preserve">25.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2779312133789</t>
+    <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
     <t xml:space="preserve">27.1469669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9400539398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951675415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5330467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778369903564</t>
+    <t xml:space="preserve">26.9400520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951637268066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.491662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5330486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778388977051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675155639648</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6985740661621</t>
+    <t xml:space="preserve">25.6985759735107</t>
   </si>
   <si>
     <t xml:space="preserve">25.2847499847412</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6571941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1537857055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9468727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0710201263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9054889678955</t>
+    <t xml:space="preserve">25.6571960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9468746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0710182189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9054908752441</t>
   </si>
   <si>
     <t xml:space="preserve">26.3193168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0642032623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0228176116943</t>
+    <t xml:space="preserve">27.0641994476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.022819519043</t>
   </si>
   <si>
     <t xml:space="preserve">24.250186920166</t>
@@ -1574,55 +1574,55 @@
     <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535972595215</t>
+    <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">24.0432720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363609313965</t>
+    <t xml:space="preserve">23.8363590240479</t>
   </si>
   <si>
     <t xml:space="preserve">23.3811511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7949810028076</t>
+    <t xml:space="preserve">23.7949771881104</t>
   </si>
   <si>
     <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9191246032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2088031768799</t>
+    <t xml:space="preserve">23.9191265106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2088012695312</t>
   </si>
   <si>
     <t xml:space="preserve">24.332950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262260437012</t>
+    <t xml:space="preserve">25.4502830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262279510498</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0296363830566</t>
+    <t xml:space="preserve">26.0296382904053</t>
   </si>
   <si>
     <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5744285583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6089954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9814357757568</t>
+    <t xml:space="preserve">25.5744323730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6089973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9814338684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.9882526397705</t>
@@ -1631,52 +1631,52 @@
     <t xml:space="preserve">26.4434642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606948852539</t>
+    <t xml:space="preserve">26.6503772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3606986999512</t>
   </si>
   <si>
     <t xml:space="preserve">24.4984817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0914726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7258491516113</t>
+    <t xml:space="preserve">23.0914745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.72585105896</t>
   </si>
   <si>
     <t xml:space="preserve">21.4361724853516</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8913822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7740535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6430835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4775543212891</t>
+    <t xml:space="preserve">21.8913803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7740516662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6430854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4775562286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.1051120758057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8154315948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6981029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636322021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360744476318</t>
+    <t xml:space="preserve">20.8154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6980991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360763549805</t>
   </si>
   <si>
     <t xml:space="preserve">21.8086166381836</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">21.9327640533447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0569076538086</t>
+    <t xml:space="preserve">22.0569095611572</t>
   </si>
   <si>
     <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2638263702393</t>
+    <t xml:space="preserve">22.2638244628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.0014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4634475708008</t>
+    <t xml:space="preserve">17.4634456634521</t>
   </si>
   <si>
     <t xml:space="preserve">17.5462093353271</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">17.6703586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877269744873</t>
+    <t xml:space="preserve">17.8772716522217</t>
   </si>
   <si>
     <t xml:space="preserve">18.2083320617676</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8290710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6221580505371</t>
+    <t xml:space="preserve">18.8290691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6221542358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
@@ -1736,43 +1736,43 @@
     <t xml:space="preserve">19.5325717926025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4911918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0773639678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187496185303</t>
+    <t xml:space="preserve">19.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0773658752441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187477111816</t>
   </si>
   <si>
     <t xml:space="preserve">18.0427989959717</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7945041656494</t>
+    <t xml:space="preserve">17.794506072998</t>
   </si>
   <si>
     <t xml:space="preserve">16.8427066802979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7531223297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737651824951</t>
+    <t xml:space="preserve">17.7531242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737670898438</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8840885162354</t>
+    <t xml:space="preserve">16.966854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357936859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5530281066895</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">18.4152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1601295471191</t>
+    <t xml:space="preserve">19.1601314544678</t>
   </si>
   <si>
     <t xml:space="preserve">19.40842628479</t>
@@ -1793,25 +1793,25 @@
     <t xml:space="preserve">19.57395362854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4498100280762</t>
+    <t xml:space="preserve">19.4498081207275</t>
   </si>
   <si>
     <t xml:space="preserve">19.9050159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8222541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6499061584473</t>
+    <t xml:space="preserve">19.8222503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6499042510986</t>
   </si>
   <si>
     <t xml:space="preserve">20.3188419342041</t>
   </si>
   <si>
-    <t xml:space="preserve">20.111930847168</t>
+    <t xml:space="preserve">20.1119289398193</t>
   </si>
   <si>
     <t xml:space="preserve">19.7808685302734</t>
@@ -1832,49 +1832,49 @@
     <t xml:space="preserve">19.2428951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">19.325662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0359802246094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2979164123535</t>
+    <t xml:space="preserve">19.3256607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0359840393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.48681640625</t>
+    <t xml:space="preserve">16.5944118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4868183135986</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910034179688</t>
+    <t xml:space="preserve">17.0910015106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.364128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6056041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3407573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0593528747559</t>
+    <t xml:space="preserve">17.331018447876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6056022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3407535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0593566894531</t>
   </si>
   <si>
     <t xml:space="preserve">17.6455268859863</t>
@@ -1889,85 +1889,85 @@
     <t xml:space="preserve">18.07590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1255664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6620807647705</t>
+    <t xml:space="preserve">18.1255645751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765892028809</t>
+    <t xml:space="preserve">17.9765911102295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2248840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861339569092</t>
+    <t xml:space="preserve">17.7614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861358642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.6192417144775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5033702850342</t>
+    <t xml:space="preserve">16.5033683776855</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274234771729</t>
+    <t xml:space="preserve">15.4274215698242</t>
   </si>
   <si>
     <t xml:space="preserve">15.2701692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8397912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328783035278</t>
+    <t xml:space="preserve">14.839789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328773498535</t>
   </si>
   <si>
     <t xml:space="preserve">14.6742582321167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177845001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322872161865</t>
+    <t xml:space="preserve">15.6177816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322900772095</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632553100586</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659832000732</t>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659822463989</t>
   </si>
   <si>
     <t xml:space="preserve">14.8232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3255767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.712553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402652740479</t>
+    <t xml:space="preserve">15.3255748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.342601776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7125539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402671813965</t>
   </si>
   <si>
     <t xml:space="preserve">14.6614656448364</t>
@@ -1976,28 +1976,28 @@
     <t xml:space="preserve">14.6444396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8062086105347</t>
+    <t xml:space="preserve">14.806209564209</t>
   </si>
   <si>
     <t xml:space="preserve">14.5422687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8913488388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083795547485</t>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083805084229</t>
   </si>
   <si>
     <t xml:space="preserve">14.525239944458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741544723511</t>
+    <t xml:space="preserve">14.4741554260254</t>
   </si>
   <si>
     <t xml:space="preserve">14.2017011642456</t>
@@ -2006,43 +2006,40 @@
     <t xml:space="preserve">14.3890142440796</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018676757812</t>
+    <t xml:space="preserve">14.6018667221069</t>
   </si>
   <si>
     <t xml:space="preserve">14.4315853118896</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2357549667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846714019775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507831573486</t>
+    <t xml:space="preserve">14.2357559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0484437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8317518234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55078125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3208990097046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232374191284</t>
+    <t xml:space="preserve">14.7295818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020360946655</t>
   </si>
   <si>
     <t xml:space="preserve">14.4230690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3379287719727</t>
+    <t xml:space="preserve">14.3379278182983</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549547195435</t>
@@ -2054,37 +2051,37 @@
     <t xml:space="preserve">13.6908473968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7419328689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930192947388</t>
+    <t xml:space="preserve">13.7419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
     <t xml:space="preserve">13.6312484741211</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0995292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8866729736328</t>
+    <t xml:space="preserve">13.0948534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0995302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8866739273071</t>
   </si>
   <si>
     <t xml:space="preserve">13.8185606002808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801630020142</t>
+    <t xml:space="preserve">13.2225666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801639556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
@@ -2093,28 +2090,28 @@
     <t xml:space="preserve">13.5205640792847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1799945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2140522003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1668033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663000106812</t>
+    <t xml:space="preserve">13.1799955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2140531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1668043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
     <t xml:space="preserve">10.974814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491046905518</t>
+    <t xml:space="preserve">10.9492712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491037368774</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449312210083</t>
@@ -2129,10 +2126,10 @@
     <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811597824097</t>
+    <t xml:space="preserve">11.1621284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8811588287354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -2141,16 +2138,16 @@
     <t xml:space="preserve">10.7619609832764</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2511072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599565505981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6683025360107</t>
+    <t xml:space="preserve">10.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471021652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6683034896851</t>
   </si>
   <si>
     <t xml:space="preserve">10.7279024124146</t>
@@ -2159,40 +2156,40 @@
     <t xml:space="preserve">11.3664693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5367527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6644649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6900091171265</t>
+    <t xml:space="preserve">11.5367517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6644668579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6900081634521</t>
   </si>
   <si>
     <t xml:space="preserve">11.7410936355591</t>
   </si>
   <si>
-    <t xml:space="preserve">11.749608039856</t>
+    <t xml:space="preserve">11.7496089935303</t>
   </si>
   <si>
     <t xml:space="preserve">12.1838331222534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9028635025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8177223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4601259231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5026960372925</t>
+    <t xml:space="preserve">11.9028625488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8177213668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751512527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4601249694824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5026950836182</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450996398926</t>
@@ -2204,10 +2201,10 @@
     <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2132139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7108755111694</t>
+    <t xml:space="preserve">11.2132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7108745574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4724760055542</t>
@@ -2216,22 +2213,22 @@
     <t xml:space="preserve">10.6597890853882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0173864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0854997634888</t>
+    <t xml:space="preserve">11.0173845291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0855007171631</t>
   </si>
   <si>
     <t xml:space="preserve">11.0514421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280717849731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0003576278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088729858398</t>
+    <t xml:space="preserve">11.1280698776245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0003566741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088720321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.2642984390259</t>
@@ -2240,13 +2237,13 @@
     <t xml:space="preserve">11.6985235214233</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814937591553</t>
+    <t xml:space="preserve">11.6814956665039</t>
   </si>
   <si>
     <t xml:space="preserve">11.8092079162598</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3247375488281</t>
+    <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
     <t xml:space="preserve">13.1970243453979</t>
@@ -2261,7 +2258,7 @@
     <t xml:space="preserve">13.6738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.546106338501</t>
+    <t xml:space="preserve">13.5461072921753</t>
   </si>
   <si>
     <t xml:space="preserve">14.4145545959473</t>
@@ -2270,10 +2267,10 @@
     <t xml:space="preserve">13.8526182174683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2187280654907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8781585693359</t>
+    <t xml:space="preserve">14.2187271118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8781595230103</t>
   </si>
   <si>
     <t xml:space="preserve">13.775990486145</t>
@@ -2288,58 +2285,58 @@
     <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274118423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254083633423</t>
+    <t xml:space="preserve">14.6274089813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.925407409668</t>
   </si>
   <si>
     <t xml:space="preserve">15.5043725967407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5933532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942437171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.967978477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.019063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467790603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.640604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4618043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656391143799</t>
+    <t xml:space="preserve">14.5933542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592975616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9679803848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656410217285</t>
   </si>
   <si>
     <t xml:space="preserve">14.363471031189</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3294143676758</t>
+    <t xml:space="preserve">14.3294124603271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.150616645813</t>
+    <t xml:space="preserve">14.1506156921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335868835449</t>
@@ -2348,55 +2345,55 @@
     <t xml:space="preserve">14.5763254165649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1165580749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804998397827</t>
+    <t xml:space="preserve">14.1165599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4911823272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804979324341</t>
   </si>
   <si>
     <t xml:space="preserve">14.4996995925903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7721538543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7078771591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292459487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3162231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.563136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375909805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2698154449463</t>
+    <t xml:space="preserve">14.7721548080444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7078762054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292449951172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5035352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3162221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4060411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2698135375977</t>
   </si>
   <si>
     <t xml:space="preserve">14.2953567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5082120895386</t>
+    <t xml:space="preserve">14.5082130432129</t>
   </si>
   <si>
     <t xml:space="preserve">14.5167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1761560440063</t>
+    <t xml:space="preserve">14.176157951355</t>
   </si>
   <si>
     <t xml:space="preserve">14.1931858062744</t>
@@ -2405,7 +2402,7 @@
     <t xml:space="preserve">13.758960723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4183921813965</t>
+    <t xml:space="preserve">13.4183931350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.5584583282471</t>
@@ -2414,64 +2411,64 @@
     <t xml:space="preserve">12.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010284423828</t>
+    <t xml:space="preserve">12.6010293960571</t>
   </si>
   <si>
     <t xml:space="preserve">11.9880056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6218948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3277359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82539749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42522811889648</t>
+    <t xml:space="preserve">11.6218957901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4252290725708</t>
   </si>
   <si>
     <t xml:space="preserve">9.74025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0842399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7355785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2715539932251</t>
+    <t xml:space="preserve">8.08424186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73557758331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27155303955078</t>
   </si>
   <si>
     <t xml:space="preserve">8.31412506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11020278930664</t>
+    <t xml:space="preserve">7.96078491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278743743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11020374298096</t>
   </si>
   <si>
     <t xml:space="preserve">9.00803279876709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41671466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225788116455</t>
+    <t xml:space="preserve">9.41671562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4763126373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225692749023</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
@@ -2480,25 +2477,25 @@
     <t xml:space="preserve">9.09317493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16980361938477</t>
+    <t xml:space="preserve">9.16980171203613</t>
   </si>
   <si>
     <t xml:space="preserve">9.53591346740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48482894897461</t>
+    <t xml:space="preserve">9.48482799530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.62105560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.089337348938</t>
+    <t xml:space="preserve">10.0893363952637</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0467653274536</t>
+    <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.75728321075439</t>
@@ -2510,10 +2507,10 @@
     <t xml:space="preserve">9.97013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0552806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2936782836914</t>
+    <t xml:space="preserve">10.0552797317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2936773300171</t>
   </si>
   <si>
     <t xml:space="preserve">10.3192205429077</t>
@@ -2525,16 +2522,16 @@
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961832046509</t>
+    <t xml:space="preserve">11.1961841583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96162509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85945320129395</t>
+    <t xml:space="preserve">9.96162414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85945415496826</t>
   </si>
   <si>
     <t xml:space="preserve">9.7828254699707</t>
@@ -2543,16 +2540,16 @@
     <t xml:space="preserve">9.3060302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51037120819092</t>
+    <t xml:space="preserve">9.5103702545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888561248779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22940254211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26345920562744</t>
+    <t xml:space="preserve">9.22940158843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26346015930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.25494575500488</t>
@@ -2564,10 +2561,10 @@
     <t xml:space="preserve">8.86329174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93140506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85477542877197</t>
+    <t xml:space="preserve">8.93140602111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85477733612061</t>
   </si>
   <si>
     <t xml:space="preserve">9.28048706054688</t>
@@ -2576,13 +2573,13 @@
     <t xml:space="preserve">9.70619773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62957096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876707077026</t>
+    <t xml:space="preserve">9.62957000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8509407043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.187671661377</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300743103027</t>
@@ -2591,7 +2588,7 @@
     <t xml:space="preserve">10.5405902862549</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2340793609619</t>
+    <t xml:space="preserve">10.2340803146362</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254119873047</t>
@@ -2600,16 +2597,16 @@
     <t xml:space="preserve">9.9638843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2435731887817</t>
+    <t xml:space="preserve">10.2435722351074</t>
   </si>
   <si>
     <t xml:space="preserve">10.182391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1998720169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1649103164673</t>
+    <t xml:space="preserve">10.1998710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1649112701416</t>
   </si>
   <si>
     <t xml:space="preserve">10.0600280761719</t>
@@ -2618,34 +2615,34 @@
     <t xml:space="preserve">10.444598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90270233154297</t>
+    <t xml:space="preserve">10.0163269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90270328521729</t>
   </si>
   <si>
     <t xml:space="preserve">9.72789764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64049625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28214454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56183242797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41324996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49190998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40450954437256</t>
+    <t xml:space="preserve">9.64049530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28214550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56183433532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41324806213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52687168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49191188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40450763702393</t>
   </si>
   <si>
     <t xml:space="preserve">9.15978145599365</t>
@@ -2657,19 +2654,19 @@
     <t xml:space="preserve">9.01993751525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9063138961792</t>
+    <t xml:space="preserve">8.90631484985352</t>
   </si>
   <si>
     <t xml:space="preserve">9.57931423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20348262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36080837249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18600273132324</t>
+    <t xml:space="preserve">9.20348358154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36080646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18600177764893</t>
   </si>
   <si>
     <t xml:space="preserve">9.33458709716797</t>
@@ -2678,82 +2675,85 @@
     <t xml:space="preserve">9.22096347808838</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29088592529297</t>
+    <t xml:space="preserve">9.44821071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29088497161865</t>
   </si>
   <si>
     <t xml:space="preserve">9.01119804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3484563827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9777536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001167297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3186225891113</t>
+    <t xml:space="preserve">10.3484554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9777555465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001176834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.31862449646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4672079086304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0826368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8903522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6281433105469</t>
+    <t xml:space="preserve">11.0826377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8903503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.5494823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872743606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226092338562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299495697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98136615753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93766307830811</t>
+    <t xml:space="preserve">10.2872734069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260913848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299486160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98136520385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">10.094988822937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1124687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250663757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95514488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75411987304688</t>
+    <t xml:space="preserve">10.1124696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250673294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8764820098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95514392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78033924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75411796569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.6579761505127</t>
@@ -2762,49 +2762,49 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3222360610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7330255508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.750506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2785339355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3834161758423</t>
+    <t xml:space="preserve">9.99884605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7505073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2785348892212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4970397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6893262863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106624603271</t>
+    <t xml:space="preserve">10.4970407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6893253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106634140015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4795598983765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5757036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669622421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5232601165771</t>
+    <t xml:space="preserve">10.5757026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.5582218170166</t>
@@ -2813,19 +2813,19 @@
     <t xml:space="preserve">10.4708185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81529998779297</t>
+    <t xml:space="preserve">9.81530094146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9901065826416</t>
+    <t xml:space="preserve">9.99010562896729</t>
   </si>
   <si>
     <t xml:space="preserve">9.82404041290283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86774253845215</t>
+    <t xml:space="preserve">9.86774158477783</t>
   </si>
   <si>
     <t xml:space="preserve">9.6142749786377</t>
@@ -2834,19 +2834,19 @@
     <t xml:space="preserve">9.00245761871338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8276538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53485488891602</t>
+    <t xml:space="preserve">8.82765197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5348539352417</t>
   </si>
   <si>
     <t xml:space="preserve">8.6441068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12482070922852</t>
+    <t xml:space="preserve">9.12482166290283</t>
   </si>
   <si>
     <t xml:space="preserve">9.16852283477783</t>
@@ -2855,7 +2855,7 @@
     <t xml:space="preserve">8.88883399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98497581481934</t>
+    <t xml:space="preserve">8.98497676849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
@@ -2864,61 +2864,61 @@
     <t xml:space="preserve">9.69293689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078321456909</t>
+    <t xml:space="preserve">10.9078311920166</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350784301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324928283691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3587141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8867406845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4810762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.19264793396</t>
+    <t xml:space="preserve">11.6070508956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324918746948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3587131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.559739112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8867387771606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4810771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1926488876343</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857128143311</t>
+    <t xml:space="preserve">12.2101278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857147216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.0702848434448</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9741411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.991623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9479207992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061544418335</t>
+    <t xml:space="preserve">11.9741430282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9916229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9479217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0615453720093</t>
   </si>
   <si>
     <t xml:space="preserve">12.1314678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440635681152</t>
+    <t xml:space="preserve">12.0440645217896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954801559448</t>
@@ -2927,16 +2927,16 @@
     <t xml:space="preserve">12.0091037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.01784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6558818817139</t>
+    <t xml:space="preserve">12.0178451538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6558809280396</t>
   </si>
   <si>
     <t xml:space="preserve">12.6733617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4898157119751</t>
+    <t xml:space="preserve">12.4898176193237</t>
   </si>
   <si>
     <t xml:space="preserve">12.4198942184448</t>
@@ -2945,28 +2945,28 @@
     <t xml:space="preserve">12.5684795379639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5422592163086</t>
+    <t xml:space="preserve">12.5422582626343</t>
   </si>
   <si>
     <t xml:space="preserve">12.778244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2363510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4461164474487</t>
+    <t xml:space="preserve">12.236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4461154937744</t>
   </si>
   <si>
     <t xml:space="preserve">12.516037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5509996414185</t>
+    <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8132057189941</t>
+    <t xml:space="preserve">12.8132047653198</t>
   </si>
   <si>
     <t xml:space="preserve">12.8394269943237</t>
@@ -2975,28 +2975,28 @@
     <t xml:space="preserve">12.9093494415283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8219470977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9880104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0229721069336</t>
+    <t xml:space="preserve">12.8219451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9880113601685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0229711532593</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.215256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2502193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7607641220093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6296606063843</t>
+    <t xml:space="preserve">13.2152576446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2502183914185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7607650756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6296615600586</t>
   </si>
   <si>
     <t xml:space="preserve">12.9530506134033</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">12.9355697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3026609420776</t>
+    <t xml:space="preserve">13.3026599884033</t>
   </si>
   <si>
     <t xml:space="preserve">13.407543182373</t>
@@ -3020,22 +3020,22 @@
     <t xml:space="preserve">13.2239980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8008527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1067638397217</t>
+    <t xml:space="preserve">13.8008546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1067628860474</t>
   </si>
   <si>
     <t xml:space="preserve">14.395191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5000734329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039306640625</t>
+    <t xml:space="preserve">14.500075340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039316177368</t>
   </si>
   <si>
     <t xml:space="preserve">14.5612564086914</t>
@@ -3047,13 +3047,13 @@
     <t xml:space="preserve">13.7484121322632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980215072632</t>
+    <t xml:space="preserve">14.0980224609375</t>
   </si>
   <si>
     <t xml:space="preserve">13.7221918106079</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3864498138428</t>
+    <t xml:space="preserve">14.3864526748657</t>
   </si>
   <si>
     <t xml:space="preserve">14.6661386489868</t>
@@ -3062,67 +3062,67 @@
     <t xml:space="preserve">14.7098407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6224374771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157489776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653593063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1206302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.456374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3442668914795</t>
+    <t xml:space="preserve">14.6224365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157480239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818151473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653612136841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1206331253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4563722610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7622804641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3442687988281</t>
   </si>
   <si>
     <t xml:space="preserve">16.7550582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.915994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9247350692749</t>
+    <t xml:space="preserve">15.9946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9159917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247360229492</t>
   </si>
   <si>
     <t xml:space="preserve">15.9422149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1344985961914</t>
+    <t xml:space="preserve">16.1345024108887</t>
   </si>
   <si>
     <t xml:space="preserve">15.43528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5663843154907</t>
+    <t xml:space="preserve">15.566385269165</t>
   </si>
   <si>
     <t xml:space="preserve">15.3566179275513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4440221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303985595703</t>
+    <t xml:space="preserve">15.4440212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330397605896</t>
   </si>
   <si>
     <t xml:space="preserve">15.2429962158203</t>
@@ -3131,73 +3131,73 @@
     <t xml:space="preserve">15.2255153656006</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2866954803467</t>
+    <t xml:space="preserve">15.2866973876953</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2517366409302</t>
+    <t xml:space="preserve">15.2517375946045</t>
   </si>
   <si>
     <t xml:space="preserve">15.0681896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1381120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265394210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.893385887146</t>
+    <t xml:space="preserve">15.1381139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265413284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0244913101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8933868408203</t>
   </si>
   <si>
     <t xml:space="preserve">14.8234634399414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0856714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196062088013</t>
+    <t xml:space="preserve">15.08567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196071624756</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9370880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1468524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8496837615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031541824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041772842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4214124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5962181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7812786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4367961883545</t>
+    <t xml:space="preserve">14.937087059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.849684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.26047706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3041801452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4214115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5962171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7812805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4368000030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.463020324707</t>
@@ -3206,22 +3206,22 @@
     <t xml:space="preserve">18.074836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2846012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8397483825684</t>
+    <t xml:space="preserve">18.2846031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.839750289917</t>
   </si>
   <si>
     <t xml:space="preserve">18.5048999786377</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7340087890625</t>
+    <t xml:space="preserve">18.7340068817139</t>
   </si>
   <si>
     <t xml:space="preserve">18.4696502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573722839355</t>
+    <t xml:space="preserve">18.8573741912842</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">19.3684597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9631175994873</t>
+    <t xml:space="preserve">18.9631156921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.1217288970947</t>
@@ -3239,22 +3239,22 @@
     <t xml:space="preserve">19.0688571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9807415008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8749980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5753917694092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2052955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987590789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5401496887207</t>
+    <t xml:space="preserve">18.9807395935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8749942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5753936767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2052974700928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987609863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
     <t xml:space="preserve">18.2405433654785</t>
@@ -3266,55 +3266,55 @@
     <t xml:space="preserve">18.2934150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1524257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0290603637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8175735473633</t>
+    <t xml:space="preserve">18.2581653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1524238586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0290584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8175754547119</t>
   </si>
   <si>
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8880672454834</t>
+    <t xml:space="preserve">17.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647018432617</t>
   </si>
   <si>
-    <t xml:space="preserve">17.64133644104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5708446502686</t>
+    <t xml:space="preserve">17.6413383483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5708427429199</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589603424072</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5267810821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3681678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1478710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4650993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9761867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8351993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.482723236084</t>
+    <t xml:space="preserve">17.526782989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3681697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1478729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4651012420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.976188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8351974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4827251434326</t>
   </si>
   <si>
     <t xml:space="preserve">17.2007446289062</t>
@@ -3332,61 +3332,61 @@
     <t xml:space="preserve">16.6367855072021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2448024749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3769798278809</t>
+    <t xml:space="preserve">17.3857917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2448043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3769817352295</t>
   </si>
   <si>
     <t xml:space="preserve">17.4122276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7823295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7470779418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5355930328369</t>
+    <t xml:space="preserve">17.7823276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7470798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5355949401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6237125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747043609619</t>
+    <t xml:space="preserve">16.8747062683105</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1743106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417358398438</t>
+    <t xml:space="preserve">17.1743087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417339324951</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9540100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3593597412109</t>
+    <t xml:space="preserve">16.9540119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3593578338623</t>
   </si>
   <si>
     <t xml:space="preserve">16.9716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7249011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6720314025879</t>
+    <t xml:space="preserve">16.7249050140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
     <t xml:space="preserve">16.4869842529297</t>
@@ -3395,79 +3395,79 @@
     <t xml:space="preserve">16.8042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2183704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8704452514648</t>
+    <t xml:space="preserve">17.2183685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8704471588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765842437744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5796527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2888622283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0421314239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7425289154053</t>
+    <t xml:space="preserve">17.5796546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5972785949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2888641357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0421295166016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.495792388916</t>
+    <t xml:space="preserve">16.4957962036133</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3900547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3019351959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9935207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8613433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2402534484863</t>
+    <t xml:space="preserve">16.3900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3019332885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.99351978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8613424301147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2402515411377</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7732229232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176820755005</t>
+    <t xml:space="preserve">16.31955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7732248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176792144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.4119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3590650558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0330276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3150053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154037475586</t>
+    <t xml:space="preserve">15.3590679168701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0330286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3150081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
     <t xml:space="preserve">15.2180767059326</t>
@@ -3476,10 +3476,10 @@
     <t xml:space="preserve">15.1828289031982</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0242147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1123342514038</t>
+    <t xml:space="preserve">15.0242156982422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1123352050781</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035223007202</t>
@@ -3488,10 +3488,10 @@
     <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.085898399353</t>
+    <t xml:space="preserve">15.1475820541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0858993530273</t>
   </si>
   <si>
     <t xml:space="preserve">14.9801568984985</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.8215436935425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6188688278198</t>
+    <t xml:space="preserve">14.6188707351685</t>
   </si>
   <si>
     <t xml:space="preserve">14.3985738754272</t>
@@ -3518,13 +3518,13 @@
     <t xml:space="preserve">13.8962984085083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1959018707275</t>
+    <t xml:space="preserve">14.1959009170532</t>
   </si>
   <si>
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104553222656</t>
+    <t xml:space="preserve">14.3104543685913</t>
   </si>
   <si>
     <t xml:space="preserve">14.3457040786743</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">13.9491691589355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1080741882324</t>
+    <t xml:space="preserve">16.1080760955811</t>
   </si>
   <si>
     <t xml:space="preserve">14.548376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4778804779053</t>
+    <t xml:space="preserve">14.4778814315796</t>
   </si>
   <si>
     <t xml:space="preserve">14.1870899200439</t>
@@ -3548,25 +3548,25 @@
     <t xml:space="preserve">14.1254062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0637235641479</t>
+    <t xml:space="preserve">14.0637226104736</t>
   </si>
   <si>
     <t xml:space="preserve">13.8169918060303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6055059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.772931098938</t>
+    <t xml:space="preserve">13.6055068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7729320526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.032735824585</t>
+    <t xml:space="preserve">13.1384782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
@@ -3584,13 +3584,13 @@
     <t xml:space="preserve">13.6583776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5350112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1913499832153</t>
+    <t xml:space="preserve">13.5350122451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.561448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.191349029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.2265968322754</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.314715385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2618446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557056427002</t>
+    <t xml:space="preserve">13.3147163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2618436813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557046890259</t>
   </si>
   <si>
     <t xml:space="preserve">13.4380807876587</t>
@@ -3614,67 +3614,67 @@
     <t xml:space="preserve">13.4645166397095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4997644424438</t>
+    <t xml:space="preserve">13.4997634887695</t>
   </si>
   <si>
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878839492798</t>
+    <t xml:space="preserve">13.5878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.5702590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7112503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468936920166</t>
+    <t xml:space="preserve">13.7112493515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468946456909</t>
   </si>
   <si>
     <t xml:space="preserve">13.1649141311646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8388748168945</t>
+    <t xml:space="preserve">12.8388757705688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710531234741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948169708252</t>
+    <t xml:space="preserve">12.7948160171509</t>
   </si>
   <si>
     <t xml:space="preserve">12.6978855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6890745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5128364562988</t>
+    <t xml:space="preserve">12.6890735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5128374099731</t>
   </si>
   <si>
     <t xml:space="preserve">12.5568962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273908615112</t>
+    <t xml:space="preserve">12.6273918151855</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492738723755</t>
+    <t xml:space="preserve">11.6492748260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078870773315</t>
+    <t xml:space="preserve">11.8078880310059</t>
   </si>
   <si>
     <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431358337402</t>
+    <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3695,37 +3695,37 @@
     <t xml:space="preserve">10.9090785980225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263059616089</t>
+    <t xml:space="preserve">11.2263050079346</t>
   </si>
   <si>
     <t xml:space="preserve">11.1293745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0412569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033380508423</t>
+    <t xml:space="preserve">11.0412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.803337097168</t>
   </si>
   <si>
     <t xml:space="preserve">11.1910572052002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3937320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1822452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355134963989</t>
+    <t xml:space="preserve">11.3937301635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1822462081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9619493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355154037476</t>
   </si>
   <si>
     <t xml:space="preserve">10.6975936889648</t>
@@ -3740,13 +3740,13 @@
     <t xml:space="preserve">10.75927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2393779754639</t>
+    <t xml:space="preserve">10.2393770217896</t>
   </si>
   <si>
     <t xml:space="preserve">9.73710155487061</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54324054718018</t>
+    <t xml:space="preserve">9.54324150085449</t>
   </si>
   <si>
     <t xml:space="preserve">9.56967544555664</t>
@@ -3758,28 +3758,28 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64883613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87353897094727</t>
+    <t xml:space="preserve">9.42868709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373615264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64883708953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01452922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89116382598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87353992462158</t>
   </si>
   <si>
     <t xml:space="preserve">9.25244998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04977607727051</t>
+    <t xml:space="preserve">9.04977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.83829212188721</t>
@@ -3794,28 +3794,28 @@
     <t xml:space="preserve">8.74576759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68848991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62680721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61359024047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2787389755249</t>
+    <t xml:space="preserve">8.68849086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62680816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6135892868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27873992919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43735218048096</t>
+    <t xml:space="preserve">8.43735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433395385742</t>
+    <t xml:space="preserve">8.27433300018311</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3824,22 +3824,22 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31398677825928</t>
+    <t xml:space="preserve">8.36245250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31398773193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.42413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08487796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01878929138184</t>
+    <t xml:space="preserve">8.13334465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08487892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01879024505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.20824432373047</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8866114616394</t>
+    <t xml:space="preserve">7.88661241531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
@@ -3860,7 +3860,7 @@
     <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93067169189453</t>
+    <t xml:space="preserve">7.93067121505737</t>
   </si>
   <si>
     <t xml:space="preserve">7.80730533599854</t>
@@ -3869,49 +3869,49 @@
     <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69275093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66190958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527593612671</t>
+    <t xml:space="preserve">7.69275140762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66190910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527641296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803880691528</t>
   </si>
   <si>
     <t xml:space="preserve">7.6751275062561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62037038803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03561210632324</t>
+    <t xml:space="preserve">7.62036943435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03561115264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.06299114227295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34133911132812</t>
+    <t xml:space="preserve">8.34134006500244</t>
   </si>
   <si>
     <t xml:space="preserve">8.08124256134033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92609739303589</t>
+    <t xml:space="preserve">7.92609786987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.89871835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64774894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82570934295654</t>
+    <t xml:space="preserve">7.6477484703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8257098197937</t>
   </si>
   <si>
     <t xml:space="preserve">7.67969036102295</t>
@@ -3926,7 +3926,7 @@
     <t xml:space="preserve">7.20056486129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96784734725952</t>
+    <t xml:space="preserve">6.96784687042236</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
@@ -3935,34 +3935,34 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03629398345947</t>
+    <t xml:space="preserve">7.03629350662231</t>
   </si>
   <si>
     <t xml:space="preserve">6.98153686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76250791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90396404266357</t>
+    <t xml:space="preserve">6.76250743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90396356582642</t>
   </si>
   <si>
     <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80357599258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69406175613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46590709686279</t>
+    <t xml:space="preserve">6.80357551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69406127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46590614318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.48872232437134</t>
@@ -3977,19 +3977,19 @@
     <t xml:space="preserve">6.36095523834229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50697469711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53891611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260562896729</t>
+    <t xml:space="preserve">6.50697422027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53891658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260515213013</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2605676651001</t>
+    <t xml:space="preserve">6.26056718826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -3998,19 +3998,19 @@
     <t xml:space="preserve">6.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29250907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51153802871704</t>
+    <t xml:space="preserve">6.29250955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51153755187988</t>
   </si>
   <si>
     <t xml:space="preserve">6.46134376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63474130630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58454751968384</t>
+    <t xml:space="preserve">6.63474082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58454704284668</t>
   </si>
   <si>
     <t xml:space="preserve">6.56173181533813</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">6.49328517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64843034744263</t>
+    <t xml:space="preserve">6.64843082427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.80813884735107</t>
@@ -4034,16 +4034,16 @@
     <t xml:space="preserve">6.81726503372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4059042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3602728843689</t>
+    <t xml:space="preserve">7.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36027336120605</t>
   </si>
   <si>
     <t xml:space="preserve">7.17318677902222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19143867492676</t>
+    <t xml:space="preserve">7.19143915176392</t>
   </si>
   <si>
     <t xml:space="preserve">6.94046831130981</t>
@@ -4052,7 +4052,7 @@
     <t xml:space="preserve">7.02260446548462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01347780227661</t>
+    <t xml:space="preserve">7.01347827911377</t>
   </si>
   <si>
     <t xml:space="preserve">6.99978876113892</t>
@@ -4061,19 +4061,19 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13668203353882</t>
+    <t xml:space="preserve">7.13668155670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.18687582015991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5747389793396</t>
+    <t xml:space="preserve">7.57473945617676</t>
   </si>
   <si>
     <t xml:space="preserve">8.12687301635742</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">8.21357250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90784454345703</t>
+    <t xml:space="preserve">7.90784502029419</t>
   </si>
   <si>
     <t xml:space="preserve">7.81658220291138</t>
@@ -4094,10 +4094,10 @@
     <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89415502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49260330200195</t>
+    <t xml:space="preserve">7.89415550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49260282516479</t>
   </si>
   <si>
     <t xml:space="preserve">7.37396240234375</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910804748535</t>
+    <t xml:space="preserve">7.52910757064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4124,34 +4124,34 @@
     <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21037292480469</t>
+    <t xml:space="preserve">6.21037340164185</t>
   </si>
   <si>
     <t xml:space="preserve">6.27425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04610204696655</t>
+    <t xml:space="preserve">6.0506649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.73581123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95940351486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25144100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37008142471313</t>
+    <t xml:space="preserve">5.9594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25144147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37008190155029</t>
   </si>
   <si>
     <t xml:space="preserve">6.34270286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.392897605896</t>
+    <t xml:space="preserve">6.39289712905884</t>
   </si>
   <si>
     <t xml:space="preserve">6.28794574737549</t>
@@ -4160,22 +4160,22 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.27881956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54347896575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57085800170898</t>
+    <t xml:space="preserve">6.54347944259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57085752487183</t>
   </si>
   <si>
     <t xml:space="preserve">6.47959613800049</t>
@@ -4184,31 +4184,31 @@
     <t xml:space="preserve">6.51610040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65755701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79901218414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09105062484741</t>
+    <t xml:space="preserve">6.65755653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79901266098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09105110168457</t>
   </si>
   <si>
     <t xml:space="preserve">7.02716732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84008026123047</t>
+    <t xml:space="preserve">6.84008073806763</t>
   </si>
   <si>
     <t xml:space="preserve">6.57542085647583</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68949794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83095455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.68949842453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83095407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4220,13 +4220,13 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17706775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12230968475342</t>
+    <t xml:space="preserve">7.93978595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17706680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12231063842773</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
@@ -4235,10 +4235,10 @@
     <t xml:space="preserve">7.69794321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7663893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72988414764404</t>
+    <t xml:space="preserve">7.76638841629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72988367080688</t>
   </si>
   <si>
     <t xml:space="preserve">7.66600036621094</t>
@@ -4250,19 +4250,19 @@
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9169716835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86677694320679</t>
+    <t xml:space="preserve">7.91697120666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86677742004395</t>
   </si>
   <si>
     <t xml:space="preserve">7.72075796127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57017517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62949514389038</t>
+    <t xml:space="preserve">7.57017612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">7.31464242935181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28270101547241</t>
+    <t xml:space="preserve">7.28270053863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.1777491569519</t>
@@ -4286,13 +4286,13 @@
     <t xml:space="preserve">7.35571050643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27813768386841</t>
+    <t xml:space="preserve">7.27813816070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4560980796814</t>
+    <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.46978807449341</t>
@@ -4301,10 +4301,10 @@
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959360122681</t>
+    <t xml:space="preserve">7.79376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959312438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.38696956634521</t>
@@ -4319,7 +4319,7 @@
     <t xml:space="preserve">8.8159008026123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94366836547852</t>
+    <t xml:space="preserve">8.9436674118042</t>
   </si>
   <si>
     <t xml:space="preserve">8.68813419342041</t>
@@ -4328,7 +4328,7 @@
     <t xml:space="preserve">8.66531848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82959079742432</t>
+    <t xml:space="preserve">8.82958984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.8067741394043</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347457885742</t>
+    <t xml:space="preserve">8.84327983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347362518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4352,7 +4352,7 @@
     <t xml:space="preserve">8.7292013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71094989776611</t>
+    <t xml:space="preserve">8.7109489440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.72463893890381</t>
@@ -4376,28 +4376,28 @@
     <t xml:space="preserve">8.21813488006592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25007629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949398040771</t>
+    <t xml:space="preserve">8.25007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99910688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83483457565308</t>
+    <t xml:space="preserve">7.99910640716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83483505249023</t>
   </si>
   <si>
     <t xml:space="preserve">7.68881607055664</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51085519790649</t>
+    <t xml:space="preserve">7.51085567474365</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4406,7 +4406,7 @@
     <t xml:space="preserve">8.05386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97172784805298</t>
+    <t xml:space="preserve">7.97172832489014</t>
   </si>
   <si>
     <t xml:space="preserve">7.92153406143188</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">8.08580589294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15425300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96716499328613</t>
+    <t xml:space="preserve">8.15425205230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96716547012329</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4439,10 +4439,10 @@
     <t xml:space="preserve">7.21425437927246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35114765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24163246154785</t>
+    <t xml:space="preserve">7.35114717483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24163293838501</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
@@ -4457,10 +4457,10 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745929718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13211822509766</t>
+    <t xml:space="preserve">6.86745882034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13211870193481</t>
   </si>
   <si>
     <t xml:space="preserve">6.88114833831787</t>
@@ -4469,19 +4469,19 @@
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78076028823853</t>
+    <t xml:space="preserve">6.78075981140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74881839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73512935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90852737426758</t>
+    <t xml:space="preserve">6.74881887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73512983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90852689743042</t>
   </si>
   <si>
     <t xml:space="preserve">6.76707124710083</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">6.62561511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62105226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43852758407593</t>
+    <t xml:space="preserve">6.62105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43852853775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50606966018677</t>
+    <t xml:space="preserve">6.50607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4535,28 +4535,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.677659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812562942505</t>
+    <t xml:space="preserve">6.67765855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86354637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924697875977</t>
+    <t xml:space="preserve">6.92550897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8635458946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924745559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6156964302063</t>
+    <t xml:space="preserve">6.61569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4571,19 +4571,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887351989746</t>
+    <t xml:space="preserve">6.44887399673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279872894287</t>
+    <t xml:space="preserve">6.57279920578003</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541585922241</t>
+    <t xml:space="preserve">6.31541538238525</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214492797852</t>
+    <t xml:space="preserve">6.38214445114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915433883667</t>
+    <t xml:space="preserve">6.23915386199951</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999631881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7863507270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167762756348</t>
+    <t xml:space="preserve">5.60999584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74821996688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78635120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167810440063</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803298950195</t>
+    <t xml:space="preserve">6.05803251266479</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878087997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401393890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597654342651</t>
+    <t xml:space="preserve">5.83878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653745651245</t>
+    <t xml:space="preserve">5.98653793334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4685,13 +4685,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26298570632935</t>
+    <t xml:space="preserve">6.2629861831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728509902954</t>
+    <t xml:space="preserve">6.27728462219238</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532321929932</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532274246216</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859367370605</t>
+    <t xml:space="preserve">5.63859415054321</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4742,16 +4742,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7720513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78158473968506</t>
+    <t xml:space="preserve">5.68625736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77205181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476182937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7815842628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4763,10 +4763,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541635513306</t>
+    <t xml:space="preserve">5.42887449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541683197021</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18102407455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943565368652</t>
+    <t xml:space="preserve">5.1810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943517684937</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812732696533</t>
+    <t xml:space="preserve">5.13812685012817</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336061477661</t>
+    <t xml:space="preserve">5.64336013793945</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71962213516235</t>
+    <t xml:space="preserve">5.7196216583252</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027618408203</t>
+    <t xml:space="preserve">5.40027666091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4829,13 +4829,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569692611694</t>
+    <t xml:space="preserve">5.59569644927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775241851807</t>
+    <t xml:space="preserve">5.75775289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569667816162</t>
+    <t xml:space="preserve">6.10569620132446</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382743835449</t>
+    <t xml:space="preserve">6.14382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4865,61 +4865,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635047912598</t>
+    <t xml:space="preserve">6.24868679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4679388999939</t>
+    <t xml:space="preserve">6.41074323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46793937683105</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896760940552</t>
+    <t xml:space="preserve">6.03896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177146911621</t>
+    <t xml:space="preserve">5.98177099227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644456863403</t>
+    <t xml:space="preserve">5.8530797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420066833496</t>
+    <t xml:space="preserve">6.03420114517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79111671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7768177986145</t>
+    <t xml:space="preserve">5.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7911171913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77681827545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4931,28 +4931,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186460494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69578981399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5194354057312</t>
+    <t xml:space="preserve">5.53850030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51943492889404</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560308456421</t>
+    <t xml:space="preserve">5.49560356140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410875320435</t>
+    <t xml:space="preserve">4.91410827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4976,22 +4976,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354711532593</t>
+    <t xml:space="preserve">5.33354759216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691236495972</t>
+    <t xml:space="preserve">5.36691188812256</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457557678223</t>
+    <t xml:space="preserve">5.67195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457509994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438884735107</t>
+    <t xml:space="preserve">5.21438837051392</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44317388534546</t>
+    <t xml:space="preserve">5.4431734085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709909439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027545928955</t>
+    <t xml:space="preserve">5.56709861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027593612671</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86261224746704</t>
+    <t xml:space="preserve">5.8626127243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -29295,7 +29295,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G894" t="s">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G895" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G896" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G897" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G898" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G899" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G900" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G903" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G904" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G906" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G907" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G908" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G909" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G910" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>16</v>
       </c>
       <c r="G912" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G913" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G914" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G915" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G916" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G917" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G918" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G919" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G920" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G921" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G922" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G923" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G924" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G925" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G926" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G927" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G928" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G929" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G930" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G931" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G932" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G933" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G934" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G936" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G937" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G938" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G939" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G940" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G941" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G942" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G943" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G944" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G945" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G947" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G948" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G949" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G950" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G951" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G952" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G953" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G954" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G955" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G956" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G957" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G958" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G959" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G960" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G961" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G962" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G963" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G964" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G965" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G966" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G967" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G968" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G969" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G970" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G971" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G972" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G974" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G975" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G976" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>15.5</v>
       </c>
       <c r="G979" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G980" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G981" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G982" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G983" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G984" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G986" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G988" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G990" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G991" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G992" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G994" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G995" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G996" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G997" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G998" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1002" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>17.25</v>
       </c>
       <c r="G1003" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G1006" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1007" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1008" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1009" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1011" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1012" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1013" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1014" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1015" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1018" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32571,7 +32571,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32597,7 +32597,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1021" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32623,7 +32623,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1022" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1023" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32701,7 +32701,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1025" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1028" t="s">
-        <v>674</v>
+        <v>647</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32805,7 +32805,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1029" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32831,7 +32831,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1030" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1031" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1032" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1033" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1034" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1035" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1036" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1037" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G1038" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1039" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G1040" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1042" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1043" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1045" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1046" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1047" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G1050" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1051" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1052" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>14.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1054" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1055" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1056" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1058" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1059" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1060" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1061" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1062" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1063" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1065" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>9.49499988555908</v>
       </c>
       <c r="G1066" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1067" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1068" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1069" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1070" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>9</v>
       </c>
       <c r="G1071" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1073" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1074" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1075" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>11.25</v>
       </c>
       <c r="G1076" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1077" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1078" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1079" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1080" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1082" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1084" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1086" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1087" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1088" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1089" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1090" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1091" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1093" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1094" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>12.25</v>
       </c>
       <c r="G1095" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1096" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1097" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1099" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1101" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1103" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1104" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G1105" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1106" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1107" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1108" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G1109" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>11</v>
       </c>
       <c r="G1110" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>11</v>
       </c>
       <c r="G1111" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1112" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1113" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1115" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1117" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1119" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1122" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1123" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1124" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1125" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1126" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1127" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1128" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1130" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1131" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1132" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1133" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1134" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G1135" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1136" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1137" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1138" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1139" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1140" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1141" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1142" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1143" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1144" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1146" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1147" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1148" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1149" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1150" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1151" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1152" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1153" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -36055,7 +36055,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1154" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -36081,7 +36081,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1155" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1156" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1158" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G1159" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -36211,7 +36211,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1160" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1161" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1162" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1163" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1164" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -36341,7 +36341,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1165" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -36367,7 +36367,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1166" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1167" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1168" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1169" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -36471,7 +36471,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1170" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -36497,7 +36497,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1171" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -36523,7 +36523,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1172" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1173" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -36575,7 +36575,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1174" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -36601,7 +36601,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1175" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -36627,7 +36627,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1176" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -36653,7 +36653,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1177" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -36679,7 +36679,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1178" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -36705,7 +36705,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1179" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36731,7 +36731,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1180" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36757,7 +36757,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1181" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36783,7 +36783,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1182" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36809,7 +36809,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1183" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36835,7 +36835,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G1184" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36861,7 +36861,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>830</v>
+        <v>910</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -37017,7 +37017,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1191" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37095,7 +37095,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1194" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -37121,7 +37121,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1195" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -37277,7 +37277,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1201" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -37433,7 +37433,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1207" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -37667,7 +37667,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -37693,7 +37693,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1217" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -37875,7 +37875,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1224" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -38213,7 +38213,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1237" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -70773,7 +70773,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6495138889</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>46347</v>
@@ -70794,6 +70794,32 @@
         <v>1902</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6493055556</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>50735</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>4.54500007629395</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>4.47499990463257</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>1885</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1904" uniqueCount="1904">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="1905">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608795166016</t>
+    <t xml:space="preserve">12.7608833312988</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">12.7846279144287</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7767114639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758996963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930105209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.270076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125690460205</t>
+    <t xml:space="preserve">12.7767124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930114746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742685317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700777053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125680923462</t>
   </si>
   <si>
     <t xml:space="preserve">12.6738023757935</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">12.0563411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3729877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1750831604004</t>
+    <t xml:space="preserve">12.3729887008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1750841140747</t>
   </si>
   <si>
     <t xml:space="preserve">12.3413238525391</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">11.6367826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9850959777832</t>
+    <t xml:space="preserve">11.9850940704346</t>
   </si>
   <si>
     <t xml:space="preserve">11.1380643844604</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">11.1064004898071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942932128906</t>
+    <t xml:space="preserve">11.4942922592163</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417900085449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3597173690796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.858437538147</t>
+    <t xml:space="preserve">11.3597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8584365844727</t>
   </si>
   <si>
     <t xml:space="preserve">11.5180406570435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7159471511841</t>
+    <t xml:space="preserve">11.7159452438354</t>
   </si>
   <si>
     <t xml:space="preserve">11.8346872329712</t>
@@ -137,70 +137,70 @@
     <t xml:space="preserve">11.6763648986816</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684474945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3992977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1855611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692611694336</t>
+    <t xml:space="preserve">11.6684484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3992967605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1855592727661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692640304565</t>
   </si>
   <si>
     <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2304973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117544174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1513338088989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704271316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387632369995</t>
+    <t xml:space="preserve">12.4284009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2304964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117534637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1513357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242130279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508686065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754325866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387613296509</t>
   </si>
   <si>
     <t xml:space="preserve">13.4575052261353</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5762462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.362512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379476547241</t>
+    <t xml:space="preserve">13.576247215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379467010498</t>
   </si>
   <si>
     <t xml:space="preserve">12.752965927124</t>
@@ -212,79 +212,79 @@
     <t xml:space="preserve">13.1091938018799</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1962699890137</t>
+    <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9904499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0221166610718</t>
+    <t xml:space="preserve">13.0221157073975</t>
   </si>
   <si>
     <t xml:space="preserve">13.0933618545532</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0775289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300302505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.602557182312</t>
+    <t xml:space="preserve">13.0775299072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975526809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6025562286377</t>
   </si>
   <si>
     <t xml:space="preserve">12.6500549316406</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8637924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679832458496</t>
+    <t xml:space="preserve">12.8637914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.586724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650722503662</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5788068771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493883132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091575622559</t>
+    <t xml:space="preserve">12.5788097381592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493892669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091594696045</t>
   </si>
   <si>
     <t xml:space="preserve">11.9884691238403</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9241008758545</t>
+    <t xml:space="preserve">11.9240999221802</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942142486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620315551758</t>
+    <t xml:space="preserve">12.2298488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620306015015</t>
   </si>
   <si>
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953651428223</t>
+    <t xml:space="preserve">12.4953641891479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7126045227051</t>
@@ -296,61 +296,61 @@
     <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0263957977295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999603271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8781290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022624969482</t>
+    <t xml:space="preserve">13.0263977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172006607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103075027466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884721755981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8781299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792779922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689287185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6103096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3689308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4896202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7574377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735321044922</t>
+    <t xml:space="preserve">11.6103105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3689298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4896211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.45973777771</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321481704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827251434326</t>
+    <t xml:space="preserve">11.2321491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827241897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9264030456543</t>
@@ -380,16 +380,16 @@
     <t xml:space="preserve">11.7229528427124</t>
   </si>
   <si>
-    <t xml:space="preserve">11.747091293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5700798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8919162750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861730575562</t>
+    <t xml:space="preserve">11.7470903396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5700788497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8919172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861701965332</t>
   </si>
   <si>
     <t xml:space="preserve">11.875825881958</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">12.1896181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896150588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0505332946777</t>
+    <t xml:space="preserve">12.4309968948364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0505361557007</t>
   </si>
   <si>
     <t xml:space="preserve">12.9942121505737</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1229467391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1551322937012</t>
+    <t xml:space="preserve">13.1229476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1551313400269</t>
   </si>
   <si>
     <t xml:space="preserve">12.9861669540405</t>
@@ -425,121 +425,121 @@
     <t xml:space="preserve">13.0746726989746</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3482332229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.249382019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194965362549</t>
+    <t xml:space="preserve">13.3482341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194974899292</t>
   </si>
   <si>
     <t xml:space="preserve">14.3459339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8551301956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.691912651062</t>
+    <t xml:space="preserve">13.8551292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608762741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919097900391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7643241882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6275434494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206443786621</t>
+    <t xml:space="preserve">14.6275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206472396851</t>
   </si>
   <si>
     <t xml:space="preserve">14.6034030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4022541046143</t>
+    <t xml:space="preserve">14.4022560119629</t>
   </si>
   <si>
     <t xml:space="preserve">14.3137502670288</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6516790390015</t>
+    <t xml:space="preserve">14.6516780853271</t>
   </si>
   <si>
     <t xml:space="preserve">14.7562770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1183443069458</t>
+    <t xml:space="preserve">15.1183452606201</t>
   </si>
   <si>
     <t xml:space="preserve">15.1505289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1263904571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.086163520813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0459337234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2953548431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562759399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873077392578</t>
+    <t xml:space="preserve">15.126389503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.08616065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0459327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.424090385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562749862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873096466064</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689203262329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7240915298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367357254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4884586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401845932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3919067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2551250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1666202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286865234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229413986206</t>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4884605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401865005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148971557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3919048309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.255126953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1666212081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229433059692</t>
   </si>
   <si>
     <t xml:space="preserve">15.013747215271</t>
@@ -548,43 +548,43 @@
     <t xml:space="preserve">14.8850126266479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1988048553467</t>
+    <t xml:space="preserve">15.198802947998</t>
   </si>
   <si>
     <t xml:space="preserve">15.3275375366211</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3114500045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677701950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034019470215</t>
+    <t xml:space="preserve">15.311448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034000396729</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6436347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654731750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470788955688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286905288696</t>
+    <t xml:space="preserve">14.6436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286914825439</t>
   </si>
   <si>
     <t xml:space="preserve">14.5390367507935</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5551300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126041412354</t>
+    <t xml:space="preserve">14.5551271438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.112603187561</t>
   </si>
   <si>
     <t xml:space="preserve">14.4263935089111</t>
@@ -596,52 +596,52 @@
     <t xml:space="preserve">14.4827156066895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2171993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4102983474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585762023926</t>
+    <t xml:space="preserve">14.2171983718872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103021621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5631761550903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585752487183</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057041168213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1045560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217964172363</t>
+    <t xml:space="preserve">14.1045541763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217945098877</t>
   </si>
   <si>
     <t xml:space="preserve">13.951681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045562744141</t>
+    <t xml:space="preserve">13.6781196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045572280884</t>
   </si>
   <si>
     <t xml:space="preserve">13.3643264770508</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1873149871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9539842605591</t>
+    <t xml:space="preserve">13.1873140335083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9539852142334</t>
   </si>
   <si>
     <t xml:space="preserve">13.3160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5896139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746725082397</t>
+    <t xml:space="preserve">13.5896129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746696472168</t>
   </si>
   <si>
     <t xml:space="preserve">13.9114542007446</t>
@@ -650,118 +650,118 @@
     <t xml:space="preserve">14.2011051177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9999580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9815664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160472869873</t>
+    <t xml:space="preserve">13.9999589920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160453796387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8447828292847</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9171962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528268814087</t>
+    <t xml:space="preserve">14.9171953201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552827835083</t>
   </si>
   <si>
     <t xml:space="preserve">15.5367345809937</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4643220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3838624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091470718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079999923706</t>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045528411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4079971313477</t>
   </si>
   <si>
     <t xml:space="preserve">15.1102991104126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2068529129028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.890754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470748901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114459991455</t>
+    <t xml:space="preserve">15.2068481445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470796585083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114440917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.3493766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3011035919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5344314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5827045440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3332843780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4539756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1723651885986</t>
+    <t xml:space="preserve">16.3010997772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5344295501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5827083587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3332824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17236328125</t>
   </si>
   <si>
     <t xml:space="preserve">16.156270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9792623519897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700681686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.003396987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436305999756</t>
+    <t xml:space="preserve">15.9792633056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0033988952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043628692627</t>
   </si>
   <si>
     <t xml:space="preserve">16.4781093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8965015411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769611358643</t>
+    <t xml:space="preserve">16.8964977264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769592285156</t>
   </si>
   <si>
     <t xml:space="preserve">17.0413284301758</t>
@@ -770,22 +770,22 @@
     <t xml:space="preserve">17.3792591094971</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5160388946533</t>
+    <t xml:space="preserve">17.516040802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206317901611</t>
+    <t xml:space="preserve">18.3850021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206298828125</t>
   </si>
   <si>
     <t xml:space="preserve">19.2700595855713</t>
@@ -794,52 +794,52 @@
     <t xml:space="preserve">19.3907451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4068393707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4470691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
+    <t xml:space="preserve">19.4068355560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4470653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
   </si>
   <si>
     <t xml:space="preserve">19.5033893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">19.6079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
   </si>
   <si>
     <t xml:space="preserve">19.7125835418701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3827018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5838470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3102836608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436210632324</t>
+    <t xml:space="preserve">19.382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5838508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3102874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436191558838</t>
   </si>
   <si>
     <t xml:space="preserve">19.4631595611572</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0689067840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0769519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286769866943</t>
+    <t xml:space="preserve">19.0689086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0769538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286750793457</t>
   </si>
   <si>
     <t xml:space="preserve">18.972354888916</t>
@@ -848,40 +848,40 @@
     <t xml:space="preserve">18.5620136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5056915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.618335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2597045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5574073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666988372803</t>
+    <t xml:space="preserve">18.5056896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171806335449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2597064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585601806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.557409286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539356231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027751922607</t>
@@ -890,31 +890,31 @@
     <t xml:space="preserve">21.5726184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5387630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5550441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271064758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5143394470215</t>
+    <t xml:space="preserve">20.538761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5550403594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.351526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5143413543701</t>
   </si>
   <si>
     <t xml:space="preserve">20.9864959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9946384429932</t>
+    <t xml:space="preserve">20.9946365356445</t>
   </si>
   <si>
     <t xml:space="preserve">20.9376487731934</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">20.8399639129639</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8155403137207</t>
+    <t xml:space="preserve">20.8155422210693</t>
   </si>
   <si>
     <t xml:space="preserve">21.1574478149414</t>
@@ -941,73 +941,73 @@
     <t xml:space="preserve">20.5957469940186</t>
   </si>
   <si>
-    <t xml:space="preserve">20.318962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8386707305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0828876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480121612549</t>
+    <t xml:space="preserve">20.3189659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8386669158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0828857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480102539062</t>
   </si>
   <si>
     <t xml:space="preserve">19.9851970672607</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1317291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3678092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259941101074</t>
+    <t xml:space="preserve">20.1317310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3678073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">20.3108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9770584106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3583736419678</t>
+    <t xml:space="preserve">19.9770603179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3583717346191</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874179840088</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9757633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8048133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978717803955</t>
+    <t xml:space="preserve">18.9757595062256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8048114776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7071228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978698730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.6338577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1304359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804801940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049961090088</t>
+    <t xml:space="preserve">19.1304340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049980163574</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805744171143</t>
+    <t xml:space="preserve">20.1805763244629</t>
   </si>
   <si>
     <t xml:space="preserve">20.2375602722168</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">20.78297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7748413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050884246826</t>
+    <t xml:space="preserve">20.7748374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.905086517334</t>
   </si>
   <si>
     <t xml:space="preserve">20.6771507263184</t>
@@ -1031,52 +1031,52 @@
     <t xml:space="preserve">21.2795562744141</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0597629547119</t>
+    <t xml:space="preserve">21.0597591400146</t>
   </si>
   <si>
     <t xml:space="preserve">21.0434799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6852893829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1004657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260883331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319156646729</t>
+    <t xml:space="preserve">20.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1004638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260864257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319137573242</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">21.922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7842750549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4993534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935241699219</t>
+    <t xml:space="preserve">21.9226627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4993515014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935260772705</t>
   </si>
   <si>
     <t xml:space="preserve">21.7761325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6214618682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110080718994</t>
+    <t xml:space="preserve">21.6214637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.711009979248</t>
   </si>
   <si>
     <t xml:space="preserve">22.5169296264648</t>
@@ -1085,19 +1085,19 @@
     <t xml:space="preserve">22.9809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6308937072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0542087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9890842437744</t>
+    <t xml:space="preserve">22.6308994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0542106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.989086151123</t>
   </si>
   <si>
     <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
-    <t xml:space="preserve">23.168176651001</t>
+    <t xml:space="preserve">23.1681804656982</t>
   </si>
   <si>
     <t xml:space="preserve">23.4693813323975</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">23.8601303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7298812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008369445801</t>
+    <t xml:space="preserve">23.7298793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229396820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263652801514</t>
+    <t xml:space="preserve">23.5996322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263633728027</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159114837646</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">25.0079574584961</t>
   </si>
   <si>
-    <t xml:space="preserve">24.87770652771</t>
+    <t xml:space="preserve">24.8777046203613</t>
   </si>
   <si>
     <t xml:space="preserve">24.8288631439209</t>
@@ -1163,31 +1163,31 @@
     <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.649772644043</t>
+    <t xml:space="preserve">24.6497707366943</t>
   </si>
   <si>
     <t xml:space="preserve">25.6999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9604091644287</t>
+    <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
     <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1789112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613349914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602207183838</t>
+    <t xml:space="preserve">25.1789073944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602226257324</t>
   </si>
   <si>
     <t xml:space="preserve">24.7474575042725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765037536621</t>
+    <t xml:space="preserve">24.5765056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.4556903839111</t>
@@ -1196,115 +1196,115 @@
     <t xml:space="preserve">26.2778911590576</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9848308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1082324981689</t>
+    <t xml:space="preserve">25.984827041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1082363128662</t>
   </si>
   <si>
     <t xml:space="preserve">27.7676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3850154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209995269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071239471436</t>
+    <t xml:space="preserve">27.3850135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9210033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071258544922</t>
   </si>
   <si>
     <t xml:space="preserve">27.0105457305908</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6930618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765960693359</t>
+    <t xml:space="preserve">26.6930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765941619873</t>
   </si>
   <si>
     <t xml:space="preserve">24.9102687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5032367706299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6172046661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2440319061279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8451461791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7393169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1951904296875</t>
+    <t xml:space="preserve">24.5032405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5846481323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2440357208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8451480865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.739315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1951885223389</t>
   </si>
   <si>
     <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5859432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7243309020996</t>
+    <t xml:space="preserve">25.5859413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7243328094482</t>
   </si>
   <si>
     <t xml:space="preserve">25.6917667388916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5452365875244</t>
+    <t xml:space="preserve">25.5452346801758</t>
   </si>
   <si>
     <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5208168029785</t>
+    <t xml:space="preserve">25.5208148956299</t>
   </si>
   <si>
     <t xml:space="preserve">25.3173007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3987083435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.512674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7650299072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499534606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2033290863037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486621856689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4625339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661422729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148933410645</t>
+    <t xml:space="preserve">25.3987064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5126762390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7650337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.049955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2033309936523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486583709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4625358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661460876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824253082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
@@ -1313,52 +1313,52 @@
     <t xml:space="preserve">26.7419033050537</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5790939331055</t>
+    <t xml:space="preserve">26.5790958404541</t>
   </si>
   <si>
     <t xml:space="preserve">27.3931560516357</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6604995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4976902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7826118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815956115723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720657348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730819702148</t>
+    <t xml:space="preserve">26.6605033874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4976844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313591003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2941741943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7826080322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.881591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2303466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.619800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730800628662</t>
   </si>
   <si>
     <t xml:space="preserve">24.6253490447998</t>
@@ -1370,43 +1370,43 @@
     <t xml:space="preserve">23.974100112915</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615177154541</t>
+    <t xml:space="preserve">25.5615196228027</t>
   </si>
   <si>
     <t xml:space="preserve">25.3580017089844</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1137866973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358932495117</t>
+    <t xml:space="preserve">25.1137828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358951568604</t>
   </si>
   <si>
     <t xml:space="preserve">23.3635540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2534694671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6891803741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1887111663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6364498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7002811431885</t>
+    <t xml:space="preserve">24.4218311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2534713745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6891765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5670719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1887149810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6364479064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7178573608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7002792358398</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736347198486</t>
@@ -1418,64 +1418,64 @@
     <t xml:space="preserve">21.6540279388428</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7354297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273834228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8168334960938</t>
+    <t xml:space="preserve">21.7354335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.816837310791</t>
   </si>
   <si>
     <t xml:space="preserve">20.8806667327881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.450511932373</t>
+    <t xml:space="preserve">21.4505100250244</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284015655518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6947269439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680881500244</t>
+    <t xml:space="preserve">21.6947288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680824279785</t>
   </si>
   <si>
     <t xml:space="preserve">22.1831645965576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5901966094971</t>
+    <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.0203533172607</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3459758758545</t>
+    <t xml:space="preserve">22.3459777832031</t>
   </si>
   <si>
     <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077690124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.805736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7067565917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3811302185059</t>
+    <t xml:space="preserve">22.7123031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8057384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7067546844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3811283111572</t>
   </si>
   <si>
     <t xml:space="preserve">24.218318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1776161193848</t>
+    <t xml:space="preserve">24.1776123046875</t>
   </si>
   <si>
     <t xml:space="preserve">24.2997245788574</t>
@@ -1484,67 +1484,67 @@
     <t xml:space="preserve">24.7881622314453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7053928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1260375976562</t>
+    <t xml:space="preserve">24.705394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">24.6640110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4089012145996</t>
+    <t xml:space="preserve">24.9123096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019863128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.408899307251</t>
   </si>
   <si>
     <t xml:space="preserve">25.7813415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7399597167969</t>
+    <t xml:space="preserve">25.7399616241455</t>
   </si>
   <si>
     <t xml:space="preserve">25.326135635376</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2779331207275</t>
+    <t xml:space="preserve">26.2779350280762</t>
   </si>
   <si>
     <t xml:space="preserve">27.1469650268555</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9400539398193</t>
+    <t xml:space="preserve">26.9400520324707</t>
   </si>
   <si>
     <t xml:space="preserve">26.1951694488525</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4916648864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5330448150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778369903564</t>
+    <t xml:space="preserve">25.491662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5330467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778388977051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675174713135</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6985778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6571922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1537857055664</t>
+    <t xml:space="preserve">25.6985759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6571960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.153787612915</t>
   </si>
   <si>
     <t xml:space="preserve">25.8227252960205</t>
@@ -1553,28 +1553,28 @@
     <t xml:space="preserve">25.9468727111816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0710220336914</t>
+    <t xml:space="preserve">26.0710201263428</t>
   </si>
   <si>
     <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3193111419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0642013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.022819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.250186920166</t>
+    <t xml:space="preserve">26.319314956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0642032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0228214263916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2501850128174</t>
   </si>
   <si>
     <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535972595215</t>
+    <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">24.0432739257812</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">23.3811531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7949752807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8777446746826</t>
+    <t xml:space="preserve">23.7949771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
     <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2088031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3329486846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4502792358398</t>
+    <t xml:space="preserve">24.2088050842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329524993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4502830505371</t>
   </si>
   <si>
     <t xml:space="preserve">26.5262279510498</t>
@@ -1610,25 +1610,25 @@
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.029634475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5676078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.574426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6089992523193</t>
+    <t xml:space="preserve">26.0296382904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5676097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5744304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6089935302734</t>
   </si>
   <si>
     <t xml:space="preserve">26.9814357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9882545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4434623718262</t>
+    <t xml:space="preserve">25.9882564544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4434642791748</t>
   </si>
   <si>
     <t xml:space="preserve">26.6503753662109</t>
@@ -1637,16 +1637,16 @@
     <t xml:space="preserve">26.3606967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4984836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0914726257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.72585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4361686706543</t>
+    <t xml:space="preserve">24.4984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7258491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4361705780029</t>
   </si>
   <si>
     <t xml:space="preserve">21.8913803100586</t>
@@ -1655,25 +1655,25 @@
     <t xml:space="preserve">20.7740497589111</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6430835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4775543212891</t>
+    <t xml:space="preserve">21.6430854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4775524139404</t>
   </si>
   <si>
     <t xml:space="preserve">21.1051120758057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8154335021973</t>
+    <t xml:space="preserve">20.8154315948486</t>
   </si>
   <si>
     <t xml:space="preserve">19.6981029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8636341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602256774902</t>
+    <t xml:space="preserve">19.8636360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602237701416</t>
   </si>
   <si>
     <t xml:space="preserve">20.2360763549805</t>
@@ -1682,16 +1682,16 @@
     <t xml:space="preserve">21.808614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">20.939582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9327621459961</t>
+    <t xml:space="preserve">20.9395790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">22.0569095611572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9259471893311</t>
+    <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
     <t xml:space="preserve">22.263822555542</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">18.0014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4634456634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6703605651855</t>
+    <t xml:space="preserve">17.4634418487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462093353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6703548431396</t>
   </si>
   <si>
     <t xml:space="preserve">17.8772716522217</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">18.2083301544189</t>
   </si>
   <si>
-    <t xml:space="preserve">18.498010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7049236297607</t>
+    <t xml:space="preserve">18.4980068206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
     <t xml:space="preserve">18.8290691375732</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">18.6221561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">18.870454788208</t>
+    <t xml:space="preserve">18.8704509735107</t>
   </si>
   <si>
     <t xml:space="preserve">19.3670425415039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4911918640137</t>
+    <t xml:space="preserve">19.5325756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4911880493164</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773639678955</t>
@@ -1745,55 +1745,55 @@
     <t xml:space="preserve">19.1187477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0428028106689</t>
+    <t xml:space="preserve">18.0427989959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.794506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8427085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806800842285</t>
+    <t xml:space="preserve">16.8427066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806762695312</t>
   </si>
   <si>
     <t xml:space="preserve">16.966854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6357955932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599430084229</t>
+    <t xml:space="preserve">16.6357975006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599411010742</t>
   </si>
   <si>
     <t xml:space="preserve">16.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5530300140381</t>
+    <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497119903564</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4152450561523</t>
+    <t xml:space="preserve">18.4152431488037</t>
   </si>
   <si>
     <t xml:space="preserve">19.1601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4084243774414</t>
+    <t xml:space="preserve">19.40842628479</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4498062133789</t>
+    <t xml:space="preserve">19.4498081207275</t>
   </si>
   <si>
     <t xml:space="preserve">19.9050178527832</t>
@@ -1802,52 +1802,52 @@
     <t xml:space="preserve">19.8222541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5257549285889</t>
+    <t xml:space="preserve">20.5257530212402</t>
   </si>
   <si>
     <t xml:space="preserve">20.64990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188400268555</t>
+    <t xml:space="preserve">20.3188381195068</t>
   </si>
   <si>
     <t xml:space="preserve">20.111930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7808685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2842788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0291652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9463977813721</t>
+    <t xml:space="preserve">19.7808666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2842769622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0291633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567192077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9463996887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.2428970336914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3256607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0359802246094</t>
+    <t xml:space="preserve">19.325662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0359840393066</t>
   </si>
   <si>
     <t xml:space="preserve">17.2979125976562</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364780426025</t>
+    <t xml:space="preserve">16.5364761352539</t>
   </si>
   <si>
     <t xml:space="preserve">16.594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.48681640625</t>
+    <t xml:space="preserve">16.4868183135986</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
@@ -1859,34 +1859,34 @@
     <t xml:space="preserve">17.2151489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.364128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6056022644043</t>
+    <t xml:space="preserve">17.3310222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6056041717529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3407535552979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0593528747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.645528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.248254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0759048461914</t>
+    <t xml:space="preserve">18.0593547821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6455268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289730072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.07590675354</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255645751953</t>
@@ -1898,55 +1898,55 @@
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2248840332031</t>
+    <t xml:space="preserve">17.9765872955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2248859405518</t>
   </si>
   <si>
     <t xml:space="preserve">17.7613983154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5861339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6192378997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274234771729</t>
+    <t xml:space="preserve">16.5861377716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6192417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101881027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274225234985</t>
   </si>
   <si>
     <t xml:space="preserve">15.270170211792</t>
   </si>
   <si>
-    <t xml:space="preserve">14.839789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328783035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6742601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322891235352</t>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177825927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322910308838</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632572174072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549802780151</t>
+    <t xml:space="preserve">15.0549793243408</t>
   </si>
   <si>
     <t xml:space="preserve">15.0467014312744</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">15.3255767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3426036834717</t>
+    <t xml:space="preserve">15.3426027297974</t>
   </si>
   <si>
     <t xml:space="preserve">14.712553024292</t>
@@ -1970,28 +1970,28 @@
     <t xml:space="preserve">14.8402652740479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6614665985107</t>
+    <t xml:space="preserve">14.6614685058594</t>
   </si>
   <si>
     <t xml:space="preserve">14.6444396972656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.806209564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5422687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811725616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661415100098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083776473999</t>
+    <t xml:space="preserve">14.8062076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5422677993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811677932739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661443710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083805084229</t>
   </si>
   <si>
     <t xml:space="preserve">14.5252389907837</t>
@@ -2006,34 +2006,34 @@
     <t xml:space="preserve">14.3890132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315843582153</t>
+    <t xml:space="preserve">14.6018667221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.431583404541</t>
   </si>
   <si>
     <t xml:space="preserve">14.2357549667358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0484447479248</t>
+    <t xml:space="preserve">14.0484428405762</t>
   </si>
   <si>
     <t xml:space="preserve">14.1846704483032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8317527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3208999633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020351409912</t>
+    <t xml:space="preserve">14.8317499160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3208980560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7295780181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020360946655</t>
   </si>
   <si>
     <t xml:space="preserve">14.8232374191284</t>
@@ -2042,70 +2042,70 @@
     <t xml:space="preserve">14.4230699539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3379278182983</t>
+    <t xml:space="preserve">14.337926864624</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549556732178</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462728500366</t>
+    <t xml:space="preserve">13.9462718963623</t>
   </si>
   <si>
     <t xml:space="preserve">13.6908473968506</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7419338226318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6312494277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821655273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0995292663574</t>
+    <t xml:space="preserve">13.7419319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6312475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821664810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975267410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0995283126831</t>
   </si>
   <si>
     <t xml:space="preserve">13.8866729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8185606002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801630020142</t>
+    <t xml:space="preserve">13.8185596466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801620483398</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5205640792847</t>
+    <t xml:space="preserve">13.5205631256104</t>
   </si>
   <si>
     <t xml:space="preserve">13.1799955368042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2140512466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1668043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663000106812</t>
+    <t xml:space="preserve">13.1544532775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2140531539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1668033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748153686523</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">10.9492721557617</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5491056442261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449321746826</t>
+    <t xml:space="preserve">10.5491037368774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449312210083</t>
   </si>
   <si>
     <t xml:space="preserve">11.1706409454346</t>
@@ -2126,13 +2126,13 @@
     <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0344142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811597824097</t>
+    <t xml:space="preserve">11.0344152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.162127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -2141,43 +2141,43 @@
     <t xml:space="preserve">10.7619600296021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2511072158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6683025360107</t>
+    <t xml:space="preserve">10.2511081695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471021652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6683034896851</t>
   </si>
   <si>
     <t xml:space="preserve">10.7279024124146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.53675365448</t>
+    <t xml:space="preserve">11.3664703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5367527008057</t>
   </si>
   <si>
     <t xml:space="preserve">11.6644659042358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.749608039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1838331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9028635025024</t>
+    <t xml:space="preserve">11.6900091171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7496070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1838321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9028644561768</t>
   </si>
   <si>
     <t xml:space="preserve">11.8177223205566</t>
@@ -2192,13 +2192,13 @@
     <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026960372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981866836548</t>
+    <t xml:space="preserve">11.5026969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981876373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898416519165</t>
@@ -2210,34 +2210,34 @@
     <t xml:space="preserve">10.7108745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4724769592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0173864364624</t>
+    <t xml:space="preserve">10.4724760055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597890853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0173845291138</t>
   </si>
   <si>
     <t xml:space="preserve">11.0854997634888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0514421463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280717849731</t>
+    <t xml:space="preserve">11.0514430999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280708312988</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0088729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2642984390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6985235214233</t>
+    <t xml:space="preserve">11.0088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2642974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.698522567749</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814947128296</t>
@@ -2249,103 +2249,103 @@
     <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1970224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5120487213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6738185882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5461053848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4145545959473</t>
+    <t xml:space="preserve">13.1970243453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.239595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5120496749878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6738176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.546106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4145555496216</t>
   </si>
   <si>
     <t xml:space="preserve">13.8526182174683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.218729019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8781595230103</t>
+    <t xml:space="preserve">14.2187309265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8781604766846</t>
   </si>
   <si>
     <t xml:space="preserve">13.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4439344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8441038131714</t>
+    <t xml:space="preserve">13.4439363479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8441028594971</t>
   </si>
   <si>
     <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254093170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.504373550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592966079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9424362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9679794311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870079040527</t>
+    <t xml:space="preserve">14.6274099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9254064559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5043706893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424333572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9679765701294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870098114014</t>
   </si>
   <si>
     <t xml:space="preserve">15.0190629959106</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1467761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6406030654907</t>
+    <t xml:space="preserve">15.1467771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406021118164</t>
   </si>
   <si>
     <t xml:space="preserve">15.461802482605</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4656391143799</t>
+    <t xml:space="preserve">14.4656400680542</t>
   </si>
   <si>
     <t xml:space="preserve">14.3634700775146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3294143676758</t>
+    <t xml:space="preserve">14.3294134140015</t>
   </si>
   <si>
     <t xml:space="preserve">14.4826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.150616645813</t>
+    <t xml:space="preserve">14.1506147384644</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5763254165649</t>
+    <t xml:space="preserve">14.5763263702393</t>
   </si>
   <si>
     <t xml:space="preserve">14.1165580749512</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">14.4911851882935</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3804988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996995925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721529006958</t>
+    <t xml:space="preserve">14.3804969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4996967315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721509933472</t>
   </si>
   <si>
     <t xml:space="preserve">13.7078762054443</t>
@@ -2369,22 +2369,22 @@
     <t xml:space="preserve">13.9292459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3162221908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5631351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375900268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2698154449463</t>
+    <t xml:space="preserve">13.5035352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3162231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4060411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.269814491272</t>
   </si>
   <si>
     <t xml:space="preserve">14.2953567504883</t>
@@ -2396,16 +2396,16 @@
     <t xml:space="preserve">14.5167245864868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1761560440063</t>
+    <t xml:space="preserve">14.1761589050293</t>
   </si>
   <si>
     <t xml:space="preserve">14.1931858062744</t>
   </si>
   <si>
-    <t xml:space="preserve">13.758960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4183921813965</t>
+    <t xml:space="preserve">13.7589597702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4183931350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.5584573745728</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">12.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010293960571</t>
+    <t xml:space="preserve">12.6010284423828</t>
   </si>
   <si>
     <t xml:space="preserve">11.9880056381226</t>
@@ -2429,43 +2429,43 @@
     <t xml:space="preserve">10.3277359008789</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82539653778076</t>
+    <t xml:space="preserve">9.82539749145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.4252290725708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74025440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0842399597168</t>
+    <t xml:space="preserve">9.74025535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08424091339111</t>
   </si>
   <si>
     <t xml:space="preserve">8.7355785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27155303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31412410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078491210938</t>
+    <t xml:space="preserve">8.2715539932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31412506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078538894653</t>
   </si>
   <si>
     <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00803279876709</t>
+    <t xml:space="preserve">9.11020183563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00803184509277</t>
   </si>
   <si>
     <t xml:space="preserve">9.41671562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47631359100342</t>
+    <t xml:space="preserve">9.4763126373291</t>
   </si>
   <si>
     <t xml:space="preserve">9.57848453521729</t>
@@ -2474,13 +2474,13 @@
     <t xml:space="preserve">9.44225788116455</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46780014038086</t>
+    <t xml:space="preserve">9.46780109405518</t>
   </si>
   <si>
     <t xml:space="preserve">9.09317493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16980457305908</t>
+    <t xml:space="preserve">9.16980361938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.53591346740723</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">9.48482894897461</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62105655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0893383026123</t>
+    <t xml:space="preserve">9.62105560302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.089337348938</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319074630737</t>
@@ -2504,16 +2504,16 @@
     <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87648296356201</t>
+    <t xml:space="preserve">9.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.97013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2936792373657</t>
+    <t xml:space="preserve">10.0552806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.29368019104</t>
   </si>
   <si>
     <t xml:space="preserve">10.319221496582</t>
@@ -2528,22 +2528,22 @@
     <t xml:space="preserve">11.1961832046509</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9407577514648</t>
+    <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
     <t xml:space="preserve">9.96162414550781</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85945415496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7828254699707</t>
+    <t xml:space="preserve">9.85945320129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78282642364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.3060302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51037120819092</t>
+    <t xml:space="preserve">9.51037216186523</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888561248779</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26345920562744</t>
+    <t xml:space="preserve">9.26345825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.25494480133057</t>
@@ -2570,37 +2570,37 @@
     <t xml:space="preserve">8.85477638244629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28048801422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70619869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62957096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85093975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876697540283</t>
+    <t xml:space="preserve">9.28048706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70619773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62957000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5405902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340793609619</t>
+    <t xml:space="preserve">10.5405912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340784072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254215240479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96388530731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435731887817</t>
+    <t xml:space="preserve">9.9638843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435722351074</t>
   </si>
   <si>
     <t xml:space="preserve">10.182391166687</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">10.1649103164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0600280761719</t>
+    <t xml:space="preserve">10.0600271224976</t>
   </si>
   <si>
     <t xml:space="preserve">10.444598197937</t>
@@ -2621,25 +2621,25 @@
     <t xml:space="preserve">10.0163259506226</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90270233154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72789764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64049625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28214454650879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56183338165283</t>
+    <t xml:space="preserve">9.90270328521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72789859771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64049530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28214550018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56183433532715</t>
   </si>
   <si>
     <t xml:space="preserve">9.41324996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5268726348877</t>
+    <t xml:space="preserve">9.52687168121338</t>
   </si>
   <si>
     <t xml:space="preserve">9.49191093444824</t>
@@ -2654,10 +2654,10 @@
     <t xml:space="preserve">8.99371719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01993846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90631484985352</t>
+    <t xml:space="preserve">9.01993656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9063138961792</t>
   </si>
   <si>
     <t xml:space="preserve">9.57931423187256</t>
@@ -2675,58 +2675,58 @@
     <t xml:space="preserve">9.33458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44821071624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29088497161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01119709014893</t>
+    <t xml:space="preserve">9.2209644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44820976257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29088592529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01119899749756</t>
   </si>
   <si>
     <t xml:space="preserve">10.3484563827515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4358577728271</t>
+    <t xml:space="preserve">10.4358587265015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9777536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001176834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3186225891113</t>
+    <t xml:space="preserve">10.9777526855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.318621635437</t>
   </si>
   <si>
     <t xml:space="preserve">11.4672069549561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0826368331909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8903522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6281433105469</t>
+    <t xml:space="preserve">11.0826377868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8903512954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
     <t xml:space="preserve">10.5494813919067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872743606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226092338562</t>
+    <t xml:space="preserve">10.2872753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260913848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.1299495697021</t>
@@ -2738,22 +2738,22 @@
     <t xml:space="preserve">9.93766307830811</t>
   </si>
   <si>
-    <t xml:space="preserve">10.094988822937</t>
+    <t xml:space="preserve">10.0949897766113</t>
   </si>
   <si>
     <t xml:space="preserve">10.1124687194824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0250663757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95514488220215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75411891937256</t>
+    <t xml:space="preserve">10.0250673294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95514583587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78033924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75411796569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.6579761505127</t>
@@ -2762,34 +2762,34 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884510040283</t>
+    <t xml:space="preserve">9.99884414672852</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222360610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7505073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620800018311</t>
+    <t xml:space="preserve">10.7330255508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.750506401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3834171295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3659362792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4970407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6893262863159</t>
+    <t xml:space="preserve">10.3834161758423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3659353256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4970397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6893253326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106624603271</t>
@@ -2801,10 +2801,10 @@
     <t xml:space="preserve">10.5757036209106</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5669631958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5232610702515</t>
+    <t xml:space="preserve">10.5669622421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5232601165771</t>
   </si>
   <si>
     <t xml:space="preserve">10.5582218170166</t>
@@ -2843,19 +2843,19 @@
     <t xml:space="preserve">8.5348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6441068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1248197555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16852188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98497581481934</t>
+    <t xml:space="preserve">8.64410781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12482070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1685209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98497676849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">9.69293689727783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078311920166</t>
+    <t xml:space="preserve">10.9078321456909</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350774765015</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">11.6070518493652</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3324928283691</t>
+    <t xml:space="preserve">12.3324918746948</t>
   </si>
   <si>
     <t xml:space="preserve">12.3587141036987</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">12.5597381591797</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867406845093</t>
+    <t xml:space="preserve">11.886739730835</t>
   </si>
   <si>
     <t xml:space="preserve">12.4810762405396</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">12.19264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139860153198</t>
+    <t xml:space="preserve">12.1139850616455</t>
   </si>
   <si>
     <t xml:space="preserve">12.210129737854</t>
@@ -2900,34 +2900,34 @@
     <t xml:space="preserve">11.6857137680054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0702857971191</t>
+    <t xml:space="preserve">12.0702848434448</t>
   </si>
   <si>
     <t xml:space="preserve">11.974142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.991623878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9479207992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.061544418335</t>
+    <t xml:space="preserve">11.9916229248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9479217529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0615453720093</t>
   </si>
   <si>
     <t xml:space="preserve">12.1314678192139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8954801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0091037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.01784324646</t>
+    <t xml:space="preserve">12.0440645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8954792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178442001343</t>
   </si>
   <si>
     <t xml:space="preserve">12.6558818817139</t>
@@ -2939,49 +2939,49 @@
     <t xml:space="preserve">12.4898166656494</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4198951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684795379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5422592163086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.778244972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2363510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4461154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.516037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5509986877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2713108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132066726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8394269943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9093494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8219470977783</t>
+    <t xml:space="preserve">12.4198942184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684785842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5422582626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7782468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4461145401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5509996414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2713117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.839427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.909348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8219451904297</t>
   </si>
   <si>
     <t xml:space="preserve">12.9880104064941</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0229721069336</t>
+    <t xml:space="preserve">13.0229730606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.3113994598389</t>
@@ -2990,22 +2990,22 @@
     <t xml:space="preserve">13.215256690979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2502193450928</t>
+    <t xml:space="preserve">13.2502183914185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7607641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6296615600586</t>
+    <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
     <t xml:space="preserve">12.9530506134033</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9792709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355707168579</t>
+    <t xml:space="preserve">12.9792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355688095093</t>
   </si>
   <si>
     <t xml:space="preserve">13.3026609420776</t>
@@ -3017,25 +3017,25 @@
     <t xml:space="preserve">13.1890363693237</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2239980697632</t>
+    <t xml:space="preserve">13.2239990234375</t>
   </si>
   <si>
     <t xml:space="preserve">13.8008527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1067638397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5000743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039306640625</t>
+    <t xml:space="preserve">14.0281000137329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.106761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.395191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5000734329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039316177368</t>
   </si>
   <si>
     <t xml:space="preserve">14.5612554550171</t>
@@ -3047,31 +3047,31 @@
     <t xml:space="preserve">13.7484130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7221918106079</t>
+    <t xml:space="preserve">14.0980234146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7221927642822</t>
   </si>
   <si>
     <t xml:space="preserve">14.3864498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6661396026611</t>
+    <t xml:space="preserve">14.6661386489868</t>
   </si>
   <si>
     <t xml:space="preserve">14.7098407745361</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6224365234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157489776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653593063354</t>
+    <t xml:space="preserve">14.6224374771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157499313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653583526611</t>
   </si>
   <si>
     <t xml:space="preserve">15.1206302642822</t>
@@ -3080,58 +3080,58 @@
     <t xml:space="preserve">14.456374168396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3442668914795</t>
+    <t xml:space="preserve">14.613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7622814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3442687988281</t>
   </si>
   <si>
     <t xml:space="preserve">16.7550582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373336791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.915994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9247350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9422149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1344985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.43528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5663862228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2429962158203</t>
+    <t xml:space="preserve">15.9946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9159936904907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247331619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.13450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4352798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.566385269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.356616973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3304014205933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.242995262146</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">15.286696434021</t>
+    <t xml:space="preserve">15.2866954803467</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779569625854</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">15.2517366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0681886672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265394210815</t>
+    <t xml:space="preserve">15.068190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265403747559</t>
   </si>
   <si>
     <t xml:space="preserve">15.024489402771</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">14.8933868408203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234634399414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.08567237854</t>
+    <t xml:space="preserve">14.8234643936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0856704711914</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196062088013</t>
@@ -3167,31 +3167,31 @@
     <t xml:space="preserve">14.99827003479</t>
   </si>
   <si>
-    <t xml:space="preserve">14.937087059021</t>
+    <t xml:space="preserve">14.9370880126953</t>
   </si>
   <si>
     <t xml:space="preserve">15.1468524932861</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8496837615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4214124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5962190628052</t>
+    <t xml:space="preserve">14.849684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2604761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3041772842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409433364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4214134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5962181091309</t>
   </si>
   <si>
     <t xml:space="preserve">16.7812805175781</t>
@@ -3203,25 +3203,25 @@
     <t xml:space="preserve">17.463020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">18.074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2846031188965</t>
+    <t xml:space="preserve">18.0748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2846012115479</t>
   </si>
   <si>
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7340068817139</t>
+    <t xml:space="preserve">18.5048980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340087890625</t>
   </si>
   <si>
     <t xml:space="preserve">18.4696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573722839355</t>
+    <t xml:space="preserve">18.8573741912842</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2052955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987609863281</t>
+    <t xml:space="preserve">18.2052936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987590789795</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2405452728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7163829803467</t>
+    <t xml:space="preserve">18.2405433654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7163848876953</t>
   </si>
   <si>
     <t xml:space="preserve">18.2934150695801</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8880672454834</t>
+    <t xml:space="preserve">17.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589603424072</t>
+    <t xml:space="preserve">17.5708427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589622497559</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">17.3681697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4650974273682</t>
+    <t xml:space="preserve">17.1478729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4650993347168</t>
   </si>
   <si>
     <t xml:space="preserve">17.9761867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8351993560791</t>
+    <t xml:space="preserve">17.8351974487305</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">16.3724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1256980895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5222339630127</t>
+    <t xml:space="preserve">16.125696182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5222320556641</t>
   </si>
   <si>
     <t xml:space="preserve">16.6367855072021</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">17.3857936859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2448043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3769798278809</t>
+    <t xml:space="preserve">17.2448024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3769817352295</t>
   </si>
   <si>
     <t xml:space="preserve">17.4122276306152</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1743106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417358398438</t>
+    <t xml:space="preserve">17.1743087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417339324951</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">16.9540100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3593597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9716358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249011993408</t>
+    <t xml:space="preserve">17.3593578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9716377258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249031066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">16.4869842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2183685302734</t>
+    <t xml:space="preserve">16.8042125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2183704376221</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765842437744</t>
+    <t xml:space="preserve">17.676586151123</t>
   </si>
   <si>
     <t xml:space="preserve">17.5796527862549</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927257537842</t>
+    <t xml:space="preserve">16.5927276611328</t>
   </si>
   <si>
     <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3988666534424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3900527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3019351959229</t>
+    <t xml:space="preserve">16.3988647460938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3900547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3019371032715</t>
   </si>
   <si>
     <t xml:space="preserve">15.9935188293457</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">16.3195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7732229232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176811218262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119367599487</t>
+    <t xml:space="preserve">15.7732238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176820755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119358062744</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590660095215</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150043487549</t>
+    <t xml:space="preserve">15.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2180776596069</t>
+    <t xml:space="preserve">15.2180767059326</t>
   </si>
   <si>
     <t xml:space="preserve">15.1828279495239</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123352050781</t>
+    <t xml:space="preserve">15.1123332977295</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035223007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4912443161011</t>
+    <t xml:space="preserve">15.4912433624268</t>
   </si>
   <si>
     <t xml:space="preserve">15.1475820541382</t>
@@ -3494,16 +3494,16 @@
     <t xml:space="preserve">15.0858993530273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9801559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8215436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6188697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3985738754272</t>
+    <t xml:space="preserve">14.9801568984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8215427398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6188688278198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3985748291016</t>
   </si>
   <si>
     <t xml:space="preserve">14.0020408630371</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3457040786743</t>
+    <t xml:space="preserve">14.3104543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.345703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.548376083374</t>
+    <t xml:space="preserve">14.5483770370483</t>
   </si>
   <si>
     <t xml:space="preserve">14.4778804779053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1870899200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254062652588</t>
+    <t xml:space="preserve">14.1870889663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254072189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3557,58 +3557,58 @@
     <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.772931098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0856075286865</t>
+    <t xml:space="preserve">13.7729320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0856084823608</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0327367782593</t>
+    <t xml:space="preserve">13.032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1296663284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9446172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852109909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583766937256</t>
+    <t xml:space="preserve">13.1296672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9446182250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583776473999</t>
   </si>
   <si>
     <t xml:space="preserve">13.5350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.191349029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2265977859497</t>
+    <t xml:space="preserve">13.561448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1913509368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2265968322754</t>
   </si>
   <si>
     <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.314715385437</t>
+    <t xml:space="preserve">13.3147163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.2618436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557065963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4380807876587</t>
+    <t xml:space="preserve">13.4557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.438081741333</t>
   </si>
   <si>
     <t xml:space="preserve">13.4645166397095</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5702600479126</t>
+    <t xml:space="preserve">13.5878839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5702590942383</t>
   </si>
   <si>
     <t xml:space="preserve">13.7112503051758</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">13.4468936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388738632202</t>
+    <t xml:space="preserve">13.1649131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388748168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710540771484</t>
@@ -3650,22 +3650,22 @@
     <t xml:space="preserve">12.6890745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5128364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273908615112</t>
+    <t xml:space="preserve">12.5128374099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273918151855</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5875911712646</t>
+    <t xml:space="preserve">11.6492757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.587592124939</t>
   </si>
   <si>
     <t xml:space="preserve">11.8078870773315</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431358337402</t>
+    <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347194671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4642248153687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1117506027222</t>
+    <t xml:space="preserve">11.5347204208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.464225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1117515563965</t>
   </si>
   <si>
     <t xml:space="preserve">10.9090795516968</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">11.2263050079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1293754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0412559509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209600448608</t>
+    <t xml:space="preserve">11.1293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0412549972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209590911865</t>
   </si>
   <si>
     <t xml:space="preserve">10.803337097168</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">11.1822452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355134963989</t>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.961950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355144500732</t>
   </si>
   <si>
     <t xml:space="preserve">10.6975936889648</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">10.2393779754639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710155487061</t>
+    <t xml:space="preserve">9.73710250854492</t>
   </si>
   <si>
     <t xml:space="preserve">9.54324054718018</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373519897461</t>
+    <t xml:space="preserve">9.42868709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373615264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.64883613586426</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25244998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83829212188721</t>
+    <t xml:space="preserve">9.25244903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977798461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83829307556152</t>
   </si>
   <si>
     <t xml:space="preserve">8.70611381530762</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">9.24363708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74576759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68848991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62680816650391</t>
+    <t xml:space="preserve">8.74576854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68849086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62680721282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2787389755249</t>
+    <t xml:space="preserve">8.27873992919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349212646484</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433395385742</t>
+    <t xml:space="preserve">8.27433300018311</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245059967041</t>
+    <t xml:space="preserve">8.36245155334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">8.42413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08487892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01879024505615</t>
+    <t xml:space="preserve">8.13334369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08487796783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01878929138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.20824432373047</t>
@@ -3848,43 +3848,43 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8866114616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12453174591064</t>
+    <t xml:space="preserve">7.88661193847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12453269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.02760124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89542293548584</t>
+    <t xml:space="preserve">7.89542388916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80730485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819747924805</t>
+    <t xml:space="preserve">7.80730438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819700241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527593612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512798309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512702941895</t>
+    <t xml:space="preserve">7.66190910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527641296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6751275062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512655258179</t>
   </si>
   <si>
     <t xml:space="preserve">7.62037038803101</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124256134033</t>
+    <t xml:space="preserve">8.08124160766602</t>
   </si>
   <si>
     <t xml:space="preserve">7.92609739303589</t>
@@ -3911,16 +3911,16 @@
     <t xml:space="preserve">7.64774894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67969036102295</t>
+    <t xml:space="preserve">7.82570886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67968988418579</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736042022705</t>
+    <t xml:space="preserve">7.54736089706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">6.90396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444980621338</t>
+    <t xml:space="preserve">6.79444932937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406175613403</t>
+    <t xml:space="preserve">6.69406127929688</t>
   </si>
   <si>
     <t xml:space="preserve">6.46590709686279</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212102890015</t>
+    <t xml:space="preserve">6.19212055206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891611099243</t>
+    <t xml:space="preserve">6.53891658782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.55260562896729</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474130630493</t>
+    <t xml:space="preserve">6.46134328842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474082946777</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173181533813</t>
+    <t xml:space="preserve">6.56173133850098</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813884735107</t>
+    <t xml:space="preserve">6.80813837051392</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12687301635742</t>
+    <t xml:space="preserve">8.12687397003174</t>
   </si>
   <si>
     <t xml:space="preserve">8.35046482086182</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">7.81658220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03104877471924</t>
+    <t xml:space="preserve">8.03104972839355</t>
   </si>
   <si>
     <t xml:space="preserve">7.89415502548218</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910804748535</t>
+    <t xml:space="preserve">7.52910852432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775079727173</t>
+    <t xml:space="preserve">6.48415899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775032043457</t>
   </si>
   <si>
     <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05066537857056</t>
+    <t xml:space="preserve">6.27425718307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0506649017334</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610204696655</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.27881956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901218414307</t>
+    <t xml:space="preserve">6.79901266098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978691101074</t>
+    <t xml:space="preserve">7.93978595733643</t>
   </si>
   <si>
     <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12230968475342</t>
+    <t xml:space="preserve">8.12231063842773</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7663893699646</t>
+    <t xml:space="preserve">7.69794273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76638889312744</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7709527015686</t>
+    <t xml:space="preserve">7.77095317840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9169716835022</t>
+    <t xml:space="preserve">7.91697216033936</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4262,22 +4262,22 @@
     <t xml:space="preserve">7.57017517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62949514389038</t>
+    <t xml:space="preserve">7.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5519232749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31464242935181</t>
+    <t xml:space="preserve">7.55192279815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31464290618896</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1777491569519</t>
+    <t xml:space="preserve">7.17774963378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4560980796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46978807449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79376792907715</t>
+    <t xml:space="preserve">7.45609855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46978855133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59755373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79376745223999</t>
   </si>
   <si>
     <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38696956634521</t>
+    <t xml:space="preserve">8.38697052001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">8.36871719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8159008026123</t>
+    <t xml:space="preserve">8.81589984893799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94366836547852</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9801721572876</t>
+    <t xml:space="preserve">8.98017311096191</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">8.8432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89347457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77939605712891</t>
+    <t xml:space="preserve">8.89347362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77939510345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.7292013168335</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41891193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40978527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44172668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22726249694824</t>
+    <t xml:space="preserve">8.41891288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40978622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44172763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22726154327393</t>
   </si>
   <si>
     <t xml:space="preserve">8.21813488006592</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949398040771</t>
+    <t xml:space="preserve">8.24551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68881607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085519790649</t>
+    <t xml:space="preserve">7.83483505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6888165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085472106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580589294434</t>
+    <t xml:space="preserve">8.09493255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580493927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716499328613</t>
+    <t xml:space="preserve">7.96716451644897</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24163246154785</t>
+    <t xml:space="preserve">7.24163293838501</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804113388062</t>
+    <t xml:space="preserve">7.01804161071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745929718018</t>
+    <t xml:space="preserve">6.86745882034302</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88114833831787</t>
+    <t xml:space="preserve">6.88114786148071</t>
   </si>
   <si>
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78076028823853</t>
+    <t xml:space="preserve">6.78075981140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">6.90852737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62105226516724</t>
+    <t xml:space="preserve">6.76707077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561559677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">6.43852758407593</t>
@@ -5724,6 +5724,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.5149998664856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59999990463257</t>
   </si>
 </sst>
 </file>
@@ -70854,7 +70857,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6506944444</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>42233</v>
@@ -70875,6 +70878,32 @@
         <v>1903</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494791667</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>39306</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>4.59000015258789</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>4.49499988555908</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1904</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -47,25 +47,25 @@
     <t xml:space="preserve">12.784628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7767114639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758968353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930105209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742694854736</t>
+    <t xml:space="preserve">12.7767133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758996963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742685317993</t>
   </si>
   <si>
     <t xml:space="preserve">12.2700777053833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5233964920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746160507202</t>
+    <t xml:space="preserve">12.5233945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746179580688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075635910034</t>
@@ -74,22 +74,22 @@
     <t xml:space="preserve">12.4125699996948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6738042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563411712646</t>
+    <t xml:space="preserve">12.6738023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.056342124939</t>
   </si>
   <si>
     <t xml:space="preserve">12.3729877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1750831604004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909170150757</t>
+    <t xml:space="preserve">12.1750860214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413228988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909141540527</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713584899902</t>
@@ -98,40 +98,40 @@
     <t xml:space="preserve">11.6367826461792</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9850959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380634307861</t>
+    <t xml:space="preserve">11.9850940704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380643844604</t>
   </si>
   <si>
     <t xml:space="preserve">10.9955730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.46262550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1064004898071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942922592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346872329712</t>
+    <t xml:space="preserve">11.4626274108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1063985824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942932128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.858437538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346881866455</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763639450073</t>
@@ -140,37 +140,37 @@
     <t xml:space="preserve">11.6684484481812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3992986679077</t>
+    <t xml:space="preserve">11.3992977142334</t>
   </si>
   <si>
     <t xml:space="preserve">11.1855621337891</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9692630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.388819694519</t>
+    <t xml:space="preserve">11.9692640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3888206481934</t>
   </si>
   <si>
     <t xml:space="preserve">12.4284019470215</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2304973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117553710938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1513357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196699142456</t>
+    <t xml:space="preserve">12.2304964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117544174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1513347625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196718215942</t>
   </si>
   <si>
     <t xml:space="preserve">12.8242111206055</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9825325012207</t>
+    <t xml:space="preserve">12.9825353622437</t>
   </si>
   <si>
     <t xml:space="preserve">12.9508695602417</t>
@@ -179,46 +179,46 @@
     <t xml:space="preserve">13.1408576965332</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2754325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704252243042</t>
+    <t xml:space="preserve">13.2754344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704271316528</t>
   </si>
   <si>
     <t xml:space="preserve">13.3387613296509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4575033187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5762491226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999956130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379457473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7529649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091918945312</t>
+    <t xml:space="preserve">13.4575052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999965667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091909408569</t>
   </si>
   <si>
     <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9904499053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221147537231</t>
+    <t xml:space="preserve">12.9904508590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221166610718</t>
   </si>
   <si>
     <t xml:space="preserve">13.0933618545532</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">13.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0300302505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975536346436</t>
+    <t xml:space="preserve">13.0300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975517272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.6025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6500539779663</t>
+    <t xml:space="preserve">12.6500549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.8637914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.586724281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650703430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493892669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091575622559</t>
+    <t xml:space="preserve">12.586727142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650712966919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788087844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091585159302</t>
   </si>
   <si>
     <t xml:space="preserve">11.988468170166</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">11.9241018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2218027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942152023315</t>
+    <t xml:space="preserve">12.2218008041382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.22984790802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942142486572</t>
   </si>
   <si>
     <t xml:space="preserve">12.2620315551758</t>
@@ -287,64 +287,64 @@
     <t xml:space="preserve">12.4953641891479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7126054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735246658325</t>
+    <t xml:space="preserve">12.7126045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735256195068</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172044754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666286468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103075027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390451431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884731292725</t>
+    <t xml:space="preserve">12.8252477645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.865478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390470504761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
     <t xml:space="preserve">10.8781290054321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0792779922485</t>
+    <t xml:space="preserve">11.0792760848999</t>
   </si>
   <si>
     <t xml:space="preserve">11.6022634506226</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103105545044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3689308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4896211624146</t>
+    <t xml:space="preserve">12.0689277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103096008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3689317703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4896202087402</t>
   </si>
   <si>
     <t xml:space="preserve">10.757438659668</t>
@@ -353,34 +353,34 @@
     <t xml:space="preserve">10.0735321044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.45973777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229539871216</t>
+    <t xml:space="preserve">10.4597387313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229549407959</t>
   </si>
   <si>
     <t xml:space="preserve">11.6424932479858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344470977783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827251434326</t>
+    <t xml:space="preserve">11.6344480514526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827241897583</t>
   </si>
   <si>
     <t xml:space="preserve">10.9264030456543</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2160568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229518890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.747091293335</t>
+    <t xml:space="preserve">11.2160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229528427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470922470093</t>
   </si>
   <si>
     <t xml:space="preserve">11.5700798034668</t>
@@ -389,16 +389,16 @@
     <t xml:space="preserve">11.891918182373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.875825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1896181106567</t>
+    <t xml:space="preserve">11.5861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8758268356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1896171569824</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309968948364</t>
@@ -410,118 +410,118 @@
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9942121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1229486465454</t>
+    <t xml:space="preserve">12.9942140579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1229476928711</t>
   </si>
   <si>
     <t xml:space="preserve">13.1551332473755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9861660003662</t>
+    <t xml:space="preserve">12.9861669540405</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746736526489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3482370376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.249382019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459339141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275415420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137512207031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516771316528</t>
+    <t xml:space="preserve">13.3482360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194955825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459300994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919097900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643241882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022531509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516780853271</t>
   </si>
   <si>
     <t xml:space="preserve">14.7562770843506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1183452606201</t>
+    <t xml:space="preserve">15.1183462142944</t>
   </si>
   <si>
     <t xml:space="preserve">15.1505298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1263904571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0861625671387</t>
+    <t xml:space="preserve">15.126389503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0861616134644</t>
   </si>
   <si>
     <t xml:space="preserve">15.0459308624268</t>
   </si>
   <si>
-    <t xml:space="preserve">15.295355796814</t>
+    <t xml:space="preserve">15.2953577041626</t>
   </si>
   <si>
     <t xml:space="preserve">15.424090385437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4562749862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597221374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873106002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689203262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240924835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4884605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401817321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148962020874</t>
+    <t xml:space="preserve">15.4562740325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240905761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930587768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4884595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401836395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045530319214</t>
@@ -530,103 +530,103 @@
     <t xml:space="preserve">15.3919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2551250457764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1666202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286893844604</t>
+    <t xml:space="preserve">15.2551240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1666231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286846160889</t>
   </si>
   <si>
     <t xml:space="preserve">15.2229433059692</t>
   </si>
   <si>
-    <t xml:space="preserve">15.013747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850164413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988039016724</t>
+    <t xml:space="preserve">15.0137481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198802947998</t>
   </si>
   <si>
     <t xml:space="preserve">15.3275394439697</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3114461898804</t>
+    <t xml:space="preserve">15.3114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">15.3677673339844</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3034000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827125549316</t>
+    <t xml:space="preserve">15.3034019470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827116012573</t>
   </si>
   <si>
     <t xml:space="preserve">14.6436347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9654703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470808029175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.828688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5390367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551300048828</t>
+    <t xml:space="preserve">14.9654722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470827102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286914825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5390348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551280975342</t>
   </si>
   <si>
     <t xml:space="preserve">14.1126012802124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4263925552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2815647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827156066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171983718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585771560669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045532226562</t>
+    <t xml:space="preserve">14.4263935089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5631742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585742950439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045570373535</t>
   </si>
   <si>
     <t xml:space="preserve">14.321795463562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9516830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781187057495</t>
+    <t xml:space="preserve">13.951681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781196594238</t>
   </si>
   <si>
     <t xml:space="preserve">13.4045562744141</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3643283843994</t>
+    <t xml:space="preserve">13.3643274307251</t>
   </si>
   <si>
     <t xml:space="preserve">13.1873140335083</t>
@@ -635,184 +635,184 @@
     <t xml:space="preserve">12.9539842605591</t>
   </si>
   <si>
-    <t xml:space="preserve">13.31605052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5896129608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746706008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9114503860474</t>
+    <t xml:space="preserve">13.3160514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5896139144897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746696472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.911452293396</t>
   </si>
   <si>
     <t xml:space="preserve">14.2011051177979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9999561309814</t>
+    <t xml:space="preserve">13.9999570846558</t>
   </si>
   <si>
     <t xml:space="preserve">14.9815635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0378847122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.917197227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631731033325</t>
+    <t xml:space="preserve">15.0378856658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.844783782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9171943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631702423096</t>
   </si>
   <si>
     <t xml:space="preserve">15.6010999679565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5528268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5367307662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3838624954224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079990386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.110297203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8907556533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8987989425659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470777511597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114479064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3493747711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3010997772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5344314575195</t>
+    <t xml:space="preserve">15.552827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.609148979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.407998085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1103000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907566070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470767974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3010959625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5344333648682</t>
   </si>
   <si>
     <t xml:space="preserve">16.5827102661133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4539756774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1723670959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1562728881836</t>
+    <t xml:space="preserve">16.3332824707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1723613739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1562747955322</t>
   </si>
   <si>
     <t xml:space="preserve">15.9792613983154</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7700681686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436344146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4781112670898</t>
+    <t xml:space="preserve">15.7700653076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4781093597412</t>
   </si>
   <si>
     <t xml:space="preserve">16.8964996337891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9769592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0413246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792591094971</t>
+    <t xml:space="preserve">16.9769611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0413284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7735080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3850021362305</t>
+    <t xml:space="preserve">17.773509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3850002288818</t>
   </si>
   <si>
     <t xml:space="preserve">18.7470684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7229309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.270055770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3907451629639</t>
+    <t xml:space="preserve">18.7229328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2700576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3907470703125</t>
   </si>
   <si>
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470691680908</t>
+    <t xml:space="preserve">19.4470710754395</t>
   </si>
   <si>
     <t xml:space="preserve">19.7528114318848</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5033893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079883575439</t>
+    <t xml:space="preserve">19.5033855438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079864501953</t>
   </si>
   <si>
     <t xml:space="preserve">19.6321220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7125854492188</t>
+    <t xml:space="preserve">19.7125835418701</t>
   </si>
   <si>
     <t xml:space="preserve">19.382698059082</t>
@@ -824,34 +824,34 @@
     <t xml:space="preserve">19.3102874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5436172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631576538086</t>
+    <t xml:space="preserve">19.5436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631595611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.0689105987549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0769538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286769866943</t>
+    <t xml:space="preserve">19.0769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286808013916</t>
   </si>
   <si>
     <t xml:space="preserve">18.972354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5620136260986</t>
+    <t xml:space="preserve">18.56201171875</t>
   </si>
   <si>
     <t xml:space="preserve">18.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6183319091797</t>
+    <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
     <t xml:space="preserve">19.1654586791992</t>
@@ -863,19 +863,19 @@
     <t xml:space="preserve">20.259708404541</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585544586182</t>
+    <t xml:space="preserve">20.7585563659668</t>
   </si>
   <si>
     <t xml:space="preserve">20.5574073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.953929901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213714599609</t>
+    <t xml:space="preserve">20.9539318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0841827392578</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">21.0027732849121</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5726184844971</t>
+    <t xml:space="preserve">21.5726165771484</t>
   </si>
   <si>
     <t xml:space="preserve">20.538761138916</t>
@@ -896,13 +896,13 @@
     <t xml:space="preserve">20.5550422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4899158477783</t>
+    <t xml:space="preserve">20.489917755127</t>
   </si>
   <si>
     <t xml:space="preserve">20.3922290802002</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3271045684814</t>
+    <t xml:space="preserve">20.3271064758301</t>
   </si>
   <si>
     <t xml:space="preserve">20.351526260376</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">20.9376487731934</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1248874664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8399639129639</t>
+    <t xml:space="preserve">21.124885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353393554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8399620056152</t>
   </si>
   <si>
     <t xml:space="preserve">20.8155403137207</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">21.1574459075928</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7585563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945423126221</t>
+    <t xml:space="preserve">20.7585582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2945442199707</t>
   </si>
   <si>
     <t xml:space="preserve">20.5957450866699</t>
@@ -947,67 +947,67 @@
     <t xml:space="preserve">20.3189640045166</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0828857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9851989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317291259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3678073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259960174561</t>
+    <t xml:space="preserve">19.8386707305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9852027893066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259922027588</t>
   </si>
   <si>
     <t xml:space="preserve">20.3108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9770584106445</t>
+    <t xml:space="preserve">19.9770603179932</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9757652282715</t>
+    <t xml:space="preserve">19.1874179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9757633209229</t>
   </si>
   <si>
     <t xml:space="preserve">18.8048114776611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338577270508</t>
+    <t xml:space="preserve">18.7071228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338558197021</t>
   </si>
   <si>
     <t xml:space="preserve">19.1304359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4804821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293235778809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049980163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.781681060791</t>
+    <t xml:space="preserve">19.4804840087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293254852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049961090088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
     <t xml:space="preserve">20.1805744171143</t>
@@ -1016,52 +1016,52 @@
     <t xml:space="preserve">20.2375583648682</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7829780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050922393799</t>
+    <t xml:space="preserve">20.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050903320312</t>
   </si>
   <si>
     <t xml:space="preserve">20.6771507263184</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1655883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2795581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.043478012085</t>
+    <t xml:space="preserve">21.1655902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2795562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0434799194336</t>
   </si>
   <si>
     <t xml:space="preserve">20.6852931976318</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1004657745361</t>
+    <t xml:space="preserve">21.1004619598389</t>
   </si>
   <si>
     <t xml:space="preserve">21.5400562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319137573242</t>
+    <t xml:space="preserve">21.4260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319156646729</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202610015869</t>
   </si>
   <si>
-    <t xml:space="preserve">21.922664642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.784273147583</t>
+    <t xml:space="preserve">21.9226665496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7842769622803</t>
   </si>
   <si>
     <t xml:space="preserve">21.4993534088135</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">21.3935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7761306762695</t>
+    <t xml:space="preserve">21.7761344909668</t>
   </si>
   <si>
     <t xml:space="preserve">21.6214618682861</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">22.0691967010498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.711009979248</t>
+    <t xml:space="preserve">21.7110080718994</t>
   </si>
   <si>
     <t xml:space="preserve">22.5169277191162</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">22.9809417724609</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6308975219727</t>
+    <t xml:space="preserve">22.6308994293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.0542106628418</t>
@@ -1097,46 +1097,46 @@
     <t xml:space="preserve">22.9890842437744</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2007427215576</t>
+    <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
     <t xml:space="preserve">23.1681785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4693813323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.86012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229415893555</t>
+    <t xml:space="preserve">23.4693832397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659614562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229454040527</t>
   </si>
   <si>
     <t xml:space="preserve">24.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9008350372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9903774261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5996322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159133911133</t>
+    <t xml:space="preserve">23.9008312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159076690674</t>
   </si>
   <si>
     <t xml:space="preserve">23.9822387695312</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">24.2346000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4394073486328</t>
+    <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
     <t xml:space="preserve">24.9916763305664</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">25.0568008422852</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.87770652771</t>
+    <t xml:space="preserve">25.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8777046203613</t>
   </si>
   <si>
     <t xml:space="preserve">24.8288631439209</t>
@@ -1175,28 +1175,28 @@
     <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4801082611084</t>
+    <t xml:space="preserve">25.4801120758057</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1613311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602226257324</t>
+    <t xml:space="preserve">24.1613349914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602245330811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2778911590576</t>
+    <t xml:space="preserve">24.5765056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4556884765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2778930664062</t>
   </si>
   <si>
     <t xml:space="preserve">25.9848289489746</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">27.7676258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3850135803223</t>
+    <t xml:space="preserve">27.3850154876709</t>
   </si>
   <si>
     <t xml:space="preserve">26.9209995269775</t>
@@ -1217,13 +1217,13 @@
     <t xml:space="preserve">27.5071258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0105495452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6930618286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765960693359</t>
+    <t xml:space="preserve">27.0105476379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6930637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765979766846</t>
   </si>
   <si>
     <t xml:space="preserve">24.9102687835693</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">24.5032386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.617208480835</t>
+    <t xml:space="preserve">24.6172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">24.5846462249756</t>
@@ -1241,85 +1241,85 @@
     <t xml:space="preserve">25.2440338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.845142364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7393131256104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6429233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5859432220459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7243309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6917667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5452365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7568950653076</t>
+    <t xml:space="preserve">24.8451442718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.739315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1951923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6429252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5859413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.724328994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6917686462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.545238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3987045288086</t>
+    <t xml:space="preserve">25.3172969818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987064361572</t>
   </si>
   <si>
     <t xml:space="preserve">25.5126762390137</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7650337219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2033309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486583709717</t>
+    <t xml:space="preserve">25.7650318145752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.049955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.203332901001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486602783203</t>
   </si>
   <si>
     <t xml:space="preserve">24.4625339508057</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3661460876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242385864258</t>
+    <t xml:space="preserve">25.3661403656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242366790771</t>
   </si>
   <si>
     <t xml:space="preserve">25.3824253082275</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148952484131</t>
+    <t xml:space="preserve">25.0893611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.741907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5790958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931579589844</t>
+    <t xml:space="preserve">26.7419033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5790939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3931560516357</t>
   </si>
   <si>
     <t xml:space="preserve">26.6605014801025</t>
@@ -1328,19 +1328,19 @@
     <t xml:space="preserve">26.497688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1313591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6022243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127647399902</t>
+    <t xml:space="preserve">26.1313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.2941722869873</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7826080322266</t>
+    <t xml:space="preserve">26.7826118469238</t>
   </si>
   <si>
     <t xml:space="preserve">27.3117504119873</t>
@@ -1349,25 +1349,25 @@
     <t xml:space="preserve">27.8815937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2303428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730819702148</t>
+    <t xml:space="preserve">27.2303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6198024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730800628662</t>
   </si>
   <si>
     <t xml:space="preserve">24.6253471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8519897460938</t>
+    <t xml:space="preserve">23.8519878387451</t>
   </si>
   <si>
     <t xml:space="preserve">23.974100112915</t>
@@ -1376,25 +1376,25 @@
     <t xml:space="preserve">25.5615177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3580055236816</t>
+    <t xml:space="preserve">25.358003616333</t>
   </si>
   <si>
     <t xml:space="preserve">25.1137828826904</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358913421631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3635578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4218330383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2534694671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6891784667969</t>
+    <t xml:space="preserve">25.2358951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3635540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4218311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2534713745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6891746520996</t>
   </si>
   <si>
     <t xml:space="preserve">23.5670680999756</t>
@@ -1406,16 +1406,16 @@
     <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7002773284912</t>
+    <t xml:space="preserve">20.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2062931060791</t>
+    <t xml:space="preserve">21.2062911987305</t>
   </si>
   <si>
     <t xml:space="preserve">21.6540260314941</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">21.7354316711426</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4273834228516</t>
+    <t xml:space="preserve">22.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">21.816837310791</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">20.8806667327881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3284015655518</t>
+    <t xml:space="preserve">21.4505100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284034729004</t>
   </si>
   <si>
     <t xml:space="preserve">21.6947269439697</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4680862426758</t>
+    <t xml:space="preserve">22.4680881500244</t>
   </si>
   <si>
     <t xml:space="preserve">22.1831645965576</t>
@@ -1457,49 +1457,49 @@
     <t xml:space="preserve">22.3459777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1600379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7123031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.805736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7067546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3811321258545</t>
+    <t xml:space="preserve">23.160041809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7123050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077709197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8057384490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7067565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3811302185059</t>
   </si>
   <si>
     <t xml:space="preserve">24.2183170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1776161193848</t>
+    <t xml:space="preserve">24.1776142120361</t>
   </si>
   <si>
     <t xml:space="preserve">24.2997245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7881622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7053966522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1260375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019863128662</t>
+    <t xml:space="preserve">24.788158416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.705394744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1260356903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019844055176</t>
   </si>
   <si>
     <t xml:space="preserve">25.408899307251</t>
@@ -1508,22 +1508,22 @@
     <t xml:space="preserve">25.7813415527344</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7399578094482</t>
+    <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
     <t xml:space="preserve">25.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2779312133789</t>
+    <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
     <t xml:space="preserve">27.1469669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951675415039</t>
+    <t xml:space="preserve">26.940055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951656341553</t>
   </si>
   <si>
     <t xml:space="preserve">25.491662979126</t>
@@ -1532,22 +1532,22 @@
     <t xml:space="preserve">25.5330448150635</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0778350830078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3675174713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6985759735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847518920898</t>
+    <t xml:space="preserve">25.0778388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3675136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6985778808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847499847412</t>
   </si>
   <si>
     <t xml:space="preserve">25.6571941375732</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1537837982178</t>
+    <t xml:space="preserve">26.1537857055664</t>
   </si>
   <si>
     <t xml:space="preserve">25.8227252960205</t>
@@ -1556,19 +1556,19 @@
     <t xml:space="preserve">25.946870803833</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0710182189941</t>
+    <t xml:space="preserve">26.0710201263428</t>
   </si>
   <si>
     <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3193168640137</t>
+    <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
     <t xml:space="preserve">27.0642032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0228176116943</t>
+    <t xml:space="preserve">27.0228214263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2501850128174</t>
@@ -1577,19 +1577,19 @@
     <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535953521729</t>
+    <t xml:space="preserve">23.7535972595215</t>
   </si>
   <si>
     <t xml:space="preserve">24.0432739257812</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363628387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3811492919922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7949771881104</t>
+    <t xml:space="preserve">23.8363609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3811511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.794979095459</t>
   </si>
   <si>
     <t xml:space="preserve">23.8777446746826</t>
@@ -1598,28 +1598,28 @@
     <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2088050842285</t>
+    <t xml:space="preserve">24.2088069915771</t>
   </si>
   <si>
     <t xml:space="preserve">24.332950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502811431885</t>
+    <t xml:space="preserve">25.4502792358398</t>
   </si>
   <si>
     <t xml:space="preserve">26.5262279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.864107131958</t>
+    <t xml:space="preserve">25.8641033172607</t>
   </si>
   <si>
     <t xml:space="preserve">26.0296382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">26.56760597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5744285583496</t>
+    <t xml:space="preserve">26.5676078796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.574426651001</t>
   </si>
   <si>
     <t xml:space="preserve">26.6089935302734</t>
@@ -1628,94 +1628,94 @@
     <t xml:space="preserve">26.9814338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9882564544678</t>
+    <t xml:space="preserve">25.9882526397705</t>
   </si>
   <si>
     <t xml:space="preserve">26.4434642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503791809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606967926025</t>
+    <t xml:space="preserve">26.6503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3607006072998</t>
   </si>
   <si>
     <t xml:space="preserve">24.4984836578369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0914726257324</t>
+    <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
     <t xml:space="preserve">21.72585105896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4361705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8913803100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7740535736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6430816650391</t>
+    <t xml:space="preserve">21.4361686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.89137840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7740516662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6430835723877</t>
   </si>
   <si>
     <t xml:space="preserve">21.4775562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1051139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8154335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6981010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602256774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
+    <t xml:space="preserve">21.105110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6981029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602275848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
   </si>
   <si>
     <t xml:space="preserve">20.9395809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9327640533447</t>
+    <t xml:space="preserve">21.9327621459961</t>
   </si>
   <si>
     <t xml:space="preserve">22.0569095611572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9259433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.263822555542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4634456634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6703586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2083301544189</t>
+    <t xml:space="preserve">22.9259452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2638206481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0014171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4634437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462093353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6703567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2083320617676</t>
   </si>
   <si>
     <t xml:space="preserve">18.4980087280273</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8290710449219</t>
+    <t xml:space="preserve">18.8290729522705</t>
   </si>
   <si>
     <t xml:space="preserve">18.6221580505371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704528808594</t>
+    <t xml:space="preserve">18.8704509735107</t>
   </si>
   <si>
     <t xml:space="preserve">19.3670425415039</t>
@@ -1739,31 +1739,31 @@
     <t xml:space="preserve">19.5325736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4911861419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0773658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0427989959717</t>
+    <t xml:space="preserve">19.4911918640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0773639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.118745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.042797088623</t>
   </si>
   <si>
     <t xml:space="preserve">17.794506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8427047729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531223297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806800842285</t>
+    <t xml:space="preserve">16.8427085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531242370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806781768799</t>
   </si>
   <si>
     <t xml:space="preserve">16.966854095459</t>
@@ -1778,19 +1778,19 @@
     <t xml:space="preserve">16.884090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5530300140381</t>
+    <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4084281921387</t>
+    <t xml:space="preserve">18.4152431488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4084243774414</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739574432373</t>
@@ -1802,7 +1802,7 @@
     <t xml:space="preserve">19.9050159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8222522735596</t>
+    <t xml:space="preserve">19.8222503662109</t>
   </si>
   <si>
     <t xml:space="preserve">20.5257530212402</t>
@@ -1811,7 +1811,7 @@
     <t xml:space="preserve">20.6499042510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188419342041</t>
+    <t xml:space="preserve">20.3188438415527</t>
   </si>
   <si>
     <t xml:space="preserve">20.1119289398193</t>
@@ -1820,25 +1820,25 @@
     <t xml:space="preserve">19.7808685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2842750549316</t>
+    <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
     <t xml:space="preserve">20.0291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567211151123</t>
+    <t xml:space="preserve">19.6567230224609</t>
   </si>
   <si>
     <t xml:space="preserve">19.9464015960693</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.325662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.035982131958</t>
+    <t xml:space="preserve">19.2428951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3256587982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0359840393066</t>
   </si>
   <si>
     <t xml:space="preserve">17.2979145050049</t>
@@ -1850,10 +1850,10 @@
     <t xml:space="preserve">16.594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4868183135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4537086486816</t>
+    <t xml:space="preserve">16.48681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.453706741333</t>
   </si>
   <si>
     <t xml:space="preserve">17.0910015106201</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">17.2151489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3641300201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910976409912</t>
+    <t xml:space="preserve">17.3310222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910957336426</t>
   </si>
   <si>
     <t xml:space="preserve">18.6056041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3407592773438</t>
+    <t xml:space="preserve">18.3407573699951</t>
   </si>
   <si>
     <t xml:space="preserve">18.0593528747559</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">17.6289749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">18.07590675354</t>
+    <t xml:space="preserve">18.0759048461914</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255664825439</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765872955322</t>
+    <t xml:space="preserve">17.9765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2248859405518</t>
@@ -1910,52 +1910,52 @@
     <t xml:space="preserve">17.7613983154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5861339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6192398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033683776855</t>
+    <t xml:space="preserve">16.5861377716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6192417144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033702850342</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101881027222</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.270170211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.839789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328783035278</t>
+    <t xml:space="preserve">15.4274206161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2701692581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328773498535</t>
   </si>
   <si>
     <t xml:space="preserve">14.674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177806854248</t>
+    <t xml:space="preserve">15.6177797317505</t>
   </si>
   <si>
     <t xml:space="preserve">16.0233325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9322929382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632543563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549783706665</t>
+    <t xml:space="preserve">15.9322891235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0632562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549812316895</t>
   </si>
   <si>
     <t xml:space="preserve">15.0467042922974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6659832000732</t>
+    <t xml:space="preserve">14.6659822463989</t>
   </si>
   <si>
     <t xml:space="preserve">14.8232374191284</t>
@@ -1967,7 +1967,7 @@
     <t xml:space="preserve">15.3426027297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.712553024292</t>
+    <t xml:space="preserve">14.7125539779663</t>
   </si>
   <si>
     <t xml:space="preserve">14.8402671813965</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">14.6614665985107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6444396972656</t>
+    <t xml:space="preserve">14.6444406509399</t>
   </si>
   <si>
     <t xml:space="preserve">14.806209564209</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5422697067261</t>
+    <t xml:space="preserve">14.5422677993774</t>
   </si>
   <si>
     <t xml:space="preserve">14.8913507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661443710327</t>
+    <t xml:space="preserve">15.9811697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661462783813</t>
   </si>
   <si>
     <t xml:space="preserve">14.9083795547485</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">14.525239944458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741535186768</t>
+    <t xml:space="preserve">14.4741554260254</t>
   </si>
   <si>
     <t xml:space="preserve">14.2017002105713</t>
@@ -2009,10 +2009,10 @@
     <t xml:space="preserve">14.3890132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018686294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315843582153</t>
+    <t xml:space="preserve">14.6018676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315853118896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2357549667358</t>
@@ -2024,49 +2024,49 @@
     <t xml:space="preserve">14.1846714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.831750869751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3208990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7295808792114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020351409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4230709075928</t>
+    <t xml:space="preserve">14.8317527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5507831573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3208999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020370483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4230690002441</t>
   </si>
   <si>
     <t xml:space="preserve">14.3379278182983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549556732178</t>
+    <t xml:space="preserve">14.3549566268921</t>
   </si>
   <si>
     <t xml:space="preserve">13.9462728500366</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6908464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419338226318</t>
+    <t xml:space="preserve">13.6908483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419328689575</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930192947388</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312475204468</t>
+    <t xml:space="preserve">13.6312484741211</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948534011841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821655273438</t>
+    <t xml:space="preserve">13.2821664810181</t>
   </si>
   <si>
     <t xml:space="preserve">14.3975276947021</t>
@@ -2075,58 +2075,58 @@
     <t xml:space="preserve">14.0995292663574</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8866739273071</t>
+    <t xml:space="preserve">13.8866729736328</t>
   </si>
   <si>
     <t xml:space="preserve">13.8185596466064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801620483398</t>
+    <t xml:space="preserve">13.2225656509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.520562171936</t>
+    <t xml:space="preserve">13.5205631256104</t>
   </si>
   <si>
     <t xml:space="preserve">13.1799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544523239136</t>
+    <t xml:space="preserve">13.1544513702393</t>
   </si>
   <si>
     <t xml:space="preserve">13.2140512466431</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1668043136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663009643555</t>
+    <t xml:space="preserve">12.1668033599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663000106812</t>
   </si>
   <si>
     <t xml:space="preserve">10.9748153686523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491037368774</t>
+    <t xml:space="preserve">10.949273109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491046905518</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1706409454346</t>
+    <t xml:space="preserve">11.1706418991089</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0344152450562</t>
+    <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
     <t xml:space="preserve">11.162127494812</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">10.8811588287354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7875022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7619609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251106262207</t>
+    <t xml:space="preserve">10.7875032424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7619600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2511072158813</t>
   </si>
   <si>
     <t xml:space="preserve">11.0599565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8471002578735</t>
+    <t xml:space="preserve">10.8471021652222</t>
   </si>
   <si>
     <t xml:space="preserve">10.6683025360107</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">10.7279024124146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664703369141</t>
+    <t xml:space="preserve">11.3664684295654</t>
   </si>
   <si>
     <t xml:space="preserve">11.53675365448</t>
@@ -2165,13 +2165,13 @@
     <t xml:space="preserve">11.6644659042358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7496089935303</t>
+    <t xml:space="preserve">11.6900091171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410945892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.749608039856</t>
   </si>
   <si>
     <t xml:space="preserve">12.1838331222534</t>
@@ -2180,25 +2180,25 @@
     <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8177223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751502990723</t>
+    <t xml:space="preserve">11.8177213668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751493453979</t>
   </si>
   <si>
     <t xml:space="preserve">12.0476045608521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4601249694824</t>
+    <t xml:space="preserve">11.4601240158081</t>
   </si>
   <si>
     <t xml:space="preserve">11.5026960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1450986862183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981857299805</t>
+    <t xml:space="preserve">11.1450996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981876373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898406982422</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">10.4724779129028</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597881317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0173845291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0855007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.051441192627</t>
+    <t xml:space="preserve">10.6597890853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0173854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0854997634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280708312988</t>
@@ -2231,19 +2231,19 @@
     <t xml:space="preserve">11.0003576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0088729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2642974853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6985216140747</t>
+    <t xml:space="preserve">11.0088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2642984390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6985235214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8092079162598</t>
+    <t xml:space="preserve">11.8092060089111</t>
   </si>
   <si>
     <t xml:space="preserve">13.3247365951538</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">13.1970233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2395944595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5120477676392</t>
+    <t xml:space="preserve">13.239595413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5120487213135</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738185882568</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">13.5461053848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4145536422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8526191711426</t>
+    <t xml:space="preserve">14.4145545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8526182174683</t>
   </si>
   <si>
     <t xml:space="preserve">14.218729019165</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">13.8781585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.775990486145</t>
+    <t xml:space="preserve">13.7759885787964</t>
   </si>
   <si>
     <t xml:space="preserve">13.4439353942871</t>
@@ -2288,43 +2288,43 @@
     <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254083633423</t>
+    <t xml:space="preserve">14.6274099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9254093170166</t>
   </si>
   <si>
     <t xml:space="preserve">15.504373550415</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5933523178101</t>
+    <t xml:space="preserve">14.5933532714844</t>
   </si>
   <si>
     <t xml:space="preserve">14.5592975616455</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9424362182617</t>
+    <t xml:space="preserve">14.9424352645874</t>
   </si>
   <si>
     <t xml:space="preserve">14.9679794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6870107650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.019063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467761993408</t>
+    <t xml:space="preserve">14.6870098114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467781066895</t>
   </si>
   <si>
     <t xml:space="preserve">15.3170614242554</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6405992507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.461802482605</t>
+    <t xml:space="preserve">15.6406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618015289307</t>
   </si>
   <si>
     <t xml:space="preserve">14.4656400680542</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">14.3294134140015</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4826698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1506156921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1335878372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5763254165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1165571212769</t>
+    <t xml:space="preserve">14.4826707839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1506147384644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1335868835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5763244628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1165580749512</t>
   </si>
   <si>
     <t xml:space="preserve">14.4911842346191</t>
@@ -2366,22 +2366,22 @@
     <t xml:space="preserve">13.7078762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292449951172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5035352706909</t>
+    <t xml:space="preserve">13.9292459487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5035343170166</t>
   </si>
   <si>
     <t xml:space="preserve">13.3162231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5631351470947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375928878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4060401916504</t>
+    <t xml:space="preserve">13.5631341934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375919342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4060411453247</t>
   </si>
   <si>
     <t xml:space="preserve">14.2698135375977</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.758960723877</t>
+    <t xml:space="preserve">14.5167255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761560440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931858062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7589616775513</t>
   </si>
   <si>
     <t xml:space="preserve">13.4183931350708</t>
@@ -2414,7 +2414,7 @@
     <t xml:space="preserve">12.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010293960571</t>
+    <t xml:space="preserve">12.6010284423828</t>
   </si>
   <si>
     <t xml:space="preserve">11.9880056381226</t>
@@ -2432,22 +2432,22 @@
     <t xml:space="preserve">9.82539653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42522811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74025344848633</t>
+    <t xml:space="preserve">9.4252290725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74025535583496</t>
   </si>
   <si>
     <t xml:space="preserve">8.08424186706543</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73557758331299</t>
+    <t xml:space="preserve">8.7355785369873</t>
   </si>
   <si>
     <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412410736084</t>
+    <t xml:space="preserve">8.31412506103516</t>
   </si>
   <si>
     <t xml:space="preserve">7.96078491210938</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11020469665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00803279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41671371459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47631359100342</t>
+    <t xml:space="preserve">9.11020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00803184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41671562194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47631454467773</t>
   </si>
   <si>
     <t xml:space="preserve">9.5784854888916</t>
@@ -2474,7 +2474,7 @@
     <t xml:space="preserve">9.44225692749023</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46780109405518</t>
+    <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
     <t xml:space="preserve">9.09317493438721</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">10.0893383026123</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1319074630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0467672348022</t>
+    <t xml:space="preserve">10.131908416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87648296356201</t>
+    <t xml:space="preserve">9.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.97013854980469</t>
@@ -2513,25 +2513,25 @@
     <t xml:space="preserve">10.0552806854248</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2936792373657</t>
+    <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
     <t xml:space="preserve">10.319221496582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299058914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9322452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1961832046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9407587051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9616231918335</t>
+    <t xml:space="preserve">10.4299068450928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9322443008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1961841583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9407577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96162414550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.85945320129395</t>
@@ -2546,52 +2546,52 @@
     <t xml:space="preserve">9.5103702545166</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51888561248779</t>
+    <t xml:space="preserve">9.51888465881348</t>
   </si>
   <si>
     <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26345825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25494575500488</t>
+    <t xml:space="preserve">9.26346015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25494480133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.36562919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8632926940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93140602111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85477638244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28048706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70619869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62957000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85093975067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187671661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8300743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5405902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340793609619</t>
+    <t xml:space="preserve">8.86329174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93140506744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85477733612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28048610687256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70619773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62957096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85093879699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8300733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5405912399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340784072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254119873047</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">10.1998720169067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1649112701416</t>
+    <t xml:space="preserve">10.1649103164673</t>
   </si>
   <si>
     <t xml:space="preserve">10.0600280761719</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">10.444598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163259506226</t>
+    <t xml:space="preserve">10.0163269042969</t>
   </si>
   <si>
     <t xml:space="preserve">9.90270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72789764404297</t>
+    <t xml:space="preserve">9.72789859771729</t>
   </si>
   <si>
     <t xml:space="preserve">9.64049530029297</t>
@@ -2636,13 +2636,13 @@
     <t xml:space="preserve">9.56183338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41324806213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52687168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49190998077393</t>
+    <t xml:space="preserve">9.41324901580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52687072753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49191093444824</t>
   </si>
   <si>
     <t xml:space="preserve">9.40450954437256</t>
@@ -2654,13 +2654,13 @@
     <t xml:space="preserve">8.99371719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01993846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90631294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57931423187256</t>
+    <t xml:space="preserve">9.01993751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90631484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57931327819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.20348262786865</t>
@@ -2669,7 +2669,7 @@
     <t xml:space="preserve">9.36080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18600177764893</t>
+    <t xml:space="preserve">9.18600273132324</t>
   </si>
   <si>
     <t xml:space="preserve">9.33458709716797</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">9.44821071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29088592529297</t>
+    <t xml:space="preserve">9.29088687896729</t>
   </si>
   <si>
     <t xml:space="preserve">9.01119709014893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3484554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358568191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271183013916</t>
+    <t xml:space="preserve">10.3484563827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271192550659</t>
   </si>
   <si>
     <t xml:space="preserve">10.9777545928955</t>
@@ -2702,43 +2702,43 @@
     <t xml:space="preserve">11.1001176834106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3186235427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4672069549561</t>
+    <t xml:space="preserve">11.3186225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4672079086304</t>
   </si>
   <si>
     <t xml:space="preserve">11.0826377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8903522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6281423568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5494804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299505233765</t>
+    <t xml:space="preserve">10.8903512954712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6281433105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5494813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299495697021</t>
   </si>
   <si>
     <t xml:space="preserve">9.98136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93766498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.094988822937</t>
+    <t xml:space="preserve">9.93766403198242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0949878692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.1124687194824</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">10.0250673294067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95514583587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75411891937256</t>
+    <t xml:space="preserve">9.95514488220215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78033924102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75411796569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.6579761505127</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884414672852</t>
+    <t xml:space="preserve">9.99884605407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222351074219</t>
@@ -2771,10 +2771,10 @@
     <t xml:space="preserve">10.7330265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7505073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620800018311</t>
+    <t xml:space="preserve">10.7505083084106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4970407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6893253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106624603271</t>
+    <t xml:space="preserve">10.4970397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6893243789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106634140015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4795598983765</t>
@@ -2804,7 +2804,7 @@
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232601165771</t>
+    <t xml:space="preserve">10.5232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.5582218170166</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">10.4708185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81529998779297</t>
+    <t xml:space="preserve">9.81529903411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
@@ -2825,7 +2825,7 @@
     <t xml:space="preserve">9.82404041290283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86774253845215</t>
+    <t xml:space="preserve">9.86774158477783</t>
   </si>
   <si>
     <t xml:space="preserve">9.6142749786377</t>
@@ -2837,22 +2837,22 @@
     <t xml:space="preserve">8.82765293121338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36878967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53485298156738</t>
+    <t xml:space="preserve">8.36878871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5348539352417</t>
   </si>
   <si>
     <t xml:space="preserve">8.64410781860352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12482070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16852283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883399963379</t>
+    <t xml:space="preserve">9.12482166290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883304595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.98497676849365</t>
@@ -2861,31 +2861,31 @@
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078321456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350774765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070518493652</t>
+    <t xml:space="preserve">9.69293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078311920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070508956909</t>
   </si>
   <si>
     <t xml:space="preserve">12.3324928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3587131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5597381591797</t>
+    <t xml:space="preserve">12.3587141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.559739112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867406845093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4810752868652</t>
+    <t xml:space="preserve">12.4810762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.1926488876343</t>
@@ -2897,13 +2897,13 @@
     <t xml:space="preserve">12.210129737854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6857128143311</t>
+    <t xml:space="preserve">11.6857137680054</t>
   </si>
   <si>
     <t xml:space="preserve">12.0702857971191</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9741411209106</t>
+    <t xml:space="preserve">11.974142074585</t>
   </si>
   <si>
     <t xml:space="preserve">11.9916229248047</t>
@@ -2915,16 +2915,16 @@
     <t xml:space="preserve">12.0615453720093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314678192139</t>
+    <t xml:space="preserve">12.1314668655396</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8954801559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0091028213501</t>
+    <t xml:space="preserve">11.8954792022705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0091037750244</t>
   </si>
   <si>
     <t xml:space="preserve">12.0178442001343</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">12.4461154937744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5160369873047</t>
+    <t xml:space="preserve">12.516037940979</t>
   </si>
   <si>
     <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713098526001</t>
+    <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132066726685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8394269943237</t>
+    <t xml:space="preserve">12.8394260406494</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093494415283</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">12.821946144104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9880113601685</t>
+    <t xml:space="preserve">12.9880104064941</t>
   </si>
   <si>
     <t xml:space="preserve">13.0229721069336</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">12.7607650756836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9530506134033</t>
+    <t xml:space="preserve">12.6296606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953049659729</t>
   </si>
   <si>
     <t xml:space="preserve">12.9792718887329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9355707168579</t>
+    <t xml:space="preserve">12.9355697631836</t>
   </si>
   <si>
     <t xml:space="preserve">13.3026609420776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.407543182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1890363693237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2239971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.800853729248</t>
+    <t xml:space="preserve">13.4075441360474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.189037322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2239980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8008546829224</t>
   </si>
   <si>
     <t xml:space="preserve">14.0281000137329</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">14.4039316177368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5612554550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2116451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7484130859375</t>
+    <t xml:space="preserve">14.5612564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2116460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7484121322632</t>
   </si>
   <si>
     <t xml:space="preserve">14.0980215072632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3864498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6661396026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7098398208618</t>
+    <t xml:space="preserve">13.7221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3864507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6661405563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7098407745361</t>
   </si>
   <si>
     <t xml:space="preserve">14.6224374771118</t>
@@ -3068,10 +3068,10 @@
     <t xml:space="preserve">15.0157489776611</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653593063354</t>
+    <t xml:space="preserve">15.1818132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">15.1206312179565</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">16.7550601959229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946575164795</t>
+    <t xml:space="preserve">15.9946565628052</t>
   </si>
   <si>
     <t xml:space="preserve">15.8373327255249</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9247369766235</t>
+    <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
     <t xml:space="preserve">15.9422149658203</t>
@@ -3110,7 +3110,7 @@
     <t xml:space="preserve">16.13450050354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4352807998657</t>
+    <t xml:space="preserve">15.43528175354</t>
   </si>
   <si>
     <t xml:space="preserve">15.566385269165</t>
@@ -3122,37 +3122,37 @@
     <t xml:space="preserve">15.4440212249756</t>
   </si>
   <si>
-    <t xml:space="preserve">15.330397605896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2429962158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2255144119263</t>
+    <t xml:space="preserve">15.3303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2429971694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2255163192749</t>
   </si>
   <si>
     <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779579162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517347335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.068190574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.024489402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8933868408203</t>
+    <t xml:space="preserve">15.2779560089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517366409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0681896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265394210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0244903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.893385887146</t>
   </si>
   <si>
     <t xml:space="preserve">14.8234634399414</t>
@@ -3161,25 +3161,25 @@
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.919605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9982690811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9370861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1468515396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.849684715271</t>
+    <t xml:space="preserve">14.9196062088013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9982681274414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9370880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8496837615967</t>
   </si>
   <si>
     <t xml:space="preserve">15.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">15.26047706604</t>
+    <t xml:space="preserve">15.2604742050171</t>
   </si>
   <si>
     <t xml:space="preserve">15.3041772842407</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">14.5962181091309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7812786102295</t>
+    <t xml:space="preserve">16.7812805175781</t>
   </si>
   <si>
     <t xml:space="preserve">17.4367980957031</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">17.4630184173584</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748386383057</t>
+    <t xml:space="preserve">18.074836730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2846031188965</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">18.4696502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573741912842</t>
+    <t xml:space="preserve">18.8573722839355</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
@@ -3239,13 +3239,13 @@
     <t xml:space="preserve">19.0688571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9807376861572</t>
+    <t xml:space="preserve">18.9807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.8749961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5753955841064</t>
+    <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
     <t xml:space="preserve">18.2052955627441</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2405433654785</t>
+    <t xml:space="preserve">18.2405452728271</t>
   </si>
   <si>
     <t xml:space="preserve">18.7163848876953</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">17.8175754547119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9056949615479</t>
+    <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
     <t xml:space="preserve">17.8880672454834</t>
@@ -3290,7 +3290,7 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708427429199</t>
+    <t xml:space="preserve">17.5708446502686</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589603424072</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">17.3681678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478710174561</t>
+    <t xml:space="preserve">17.1478691101074</t>
   </si>
   <si>
     <t xml:space="preserve">17.4651012420654</t>
@@ -3326,10 +3326,10 @@
     <t xml:space="preserve">16.1256980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5222301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6367855072021</t>
+    <t xml:space="preserve">16.5222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6367874145508</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857936859131</t>
@@ -3356,16 +3356,16 @@
     <t xml:space="preserve">17.6237125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747062683105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861911773682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1743087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417339324951</t>
+    <t xml:space="preserve">16.8747043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1743106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417358398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3380,28 +3380,28 @@
     <t xml:space="preserve">16.9716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896572113037</t>
+    <t xml:space="preserve">16.7249031066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896553039551</t>
   </si>
   <si>
     <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4869823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8042125701904</t>
+    <t xml:space="preserve">16.4869842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8042106628418</t>
   </si>
   <si>
     <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8704471588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.676586151123</t>
+    <t xml:space="preserve">17.8704452514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6765842437744</t>
   </si>
   <si>
     <t xml:space="preserve">17.5796546936035</t>
@@ -3428,19 +3428,19 @@
     <t xml:space="preserve">16.3988647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3900527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3019371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.99351978302</t>
+    <t xml:space="preserve">16.3900547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3019351959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9935207366943</t>
   </si>
   <si>
     <t xml:space="preserve">15.8613433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2402515411377</t>
+    <t xml:space="preserve">16.2402534484863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
@@ -3452,16 +3452,16 @@
     <t xml:space="preserve">15.7732229232788</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5176792144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119367599487</t>
+    <t xml:space="preserve">15.5176801681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.411937713623</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590669631958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0330286026001</t>
+    <t xml:space="preserve">15.0330276489258</t>
   </si>
   <si>
     <t xml:space="preserve">15.3150062561035</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">15.2180776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1828289031982</t>
+    <t xml:space="preserve">15.1828298568726</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242137908936</t>
@@ -3482,7 +3482,7 @@
     <t xml:space="preserve">15.1123352050781</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1035213470459</t>
+    <t xml:space="preserve">15.1035203933716</t>
   </si>
   <si>
     <t xml:space="preserve">15.4912443161011</t>
@@ -3491,7 +3491,7 @@
     <t xml:space="preserve">15.1475820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0858993530273</t>
+    <t xml:space="preserve">15.085898399353</t>
   </si>
   <si>
     <t xml:space="preserve">14.9801559448242</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.8215436935425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6188707351685</t>
+    <t xml:space="preserve">14.6188697814941</t>
   </si>
   <si>
     <t xml:space="preserve">14.3985738754272</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">13.8434267044067</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8962993621826</t>
+    <t xml:space="preserve">13.8962984085083</t>
   </si>
   <si>
     <t xml:space="preserve">14.1959018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2840194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3104543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9491701126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1080722808838</t>
+    <t xml:space="preserve">14.2840185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3457040786743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9491691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
     <t xml:space="preserve">14.5483751296997</t>
@@ -3545,7 +3545,7 @@
     <t xml:space="preserve">14.1870899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1254081726074</t>
+    <t xml:space="preserve">14.1254072189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3560,40 +3560,40 @@
     <t xml:space="preserve">13.7729320526123</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0856084823608</t>
+    <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.032735824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4028329849243</t>
+    <t xml:space="preserve">13.0327367782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4028339385986</t>
   </si>
   <si>
     <t xml:space="preserve">13.1296663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9446172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852090835571</t>
+    <t xml:space="preserve">12.944616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
     <t xml:space="preserve">13.6583776473999</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5350122451782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614471435547</t>
+    <t xml:space="preserve">13.5350112915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.561448097229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1913499832153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2265968322754</t>
+    <t xml:space="preserve">13.2265977859497</t>
   </si>
   <si>
     <t xml:space="preserve">13.6231298446655</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">12.9710540771484</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948160171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6978845596313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6890735626221</t>
+    <t xml:space="preserve">12.7948169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6978855133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6890745162964</t>
   </si>
   <si>
     <t xml:space="preserve">12.5128364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5568952560425</t>
+    <t xml:space="preserve">12.5568962097168</t>
   </si>
   <si>
     <t xml:space="preserve">12.6273908615112</t>
@@ -3662,22 +3662,22 @@
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492757797241</t>
+    <t xml:space="preserve">11.6492748260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078880310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9048194885254</t>
+    <t xml:space="preserve">11.8078870773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
     <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1427383422852</t>
+    <t xml:space="preserve">12.1427373886108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9841260910034</t>
@@ -3704,13 +3704,13 @@
     <t xml:space="preserve">11.0412559509277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8209600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033361434937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1910581588745</t>
+    <t xml:space="preserve">10.8209590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.803337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1910572052002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3937311172485</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">10.7416534423828</t>
   </si>
   <si>
-    <t xml:space="preserve">10.961950302124</t>
+    <t xml:space="preserve">10.9619493484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.9355134963989</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">10.2393770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710155487061</t>
+    <t xml:space="preserve">9.73710250854492</t>
   </si>
   <si>
     <t xml:space="preserve">9.54324054718018</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373519897461</t>
+    <t xml:space="preserve">9.42868614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373615264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.64883708953857</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">9.25244998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83829307556152</t>
+    <t xml:space="preserve">9.04977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83829212188721</t>
   </si>
   <si>
     <t xml:space="preserve">8.70611381530762</t>
@@ -3806,10 +3806,10 @@
     <t xml:space="preserve">8.2787389755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24349117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43735313415527</t>
+    <t xml:space="preserve">8.24349212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43735218048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.35363864898682</t>
@@ -3824,10 +3824,10 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31398582458496</t>
+    <t xml:space="preserve">8.36245155334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31398677825928</t>
   </si>
   <si>
     <t xml:space="preserve">8.42413520812988</t>
@@ -3845,7 +3845,7 @@
     <t xml:space="preserve">8.20824432373047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01438331604004</t>
+    <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
     <t xml:space="preserve">7.8866114616394</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89542388916016</t>
+    <t xml:space="preserve">8.02760124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">7.67512702941895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803880691528</t>
+    <t xml:space="preserve">7.95803928375244</t>
   </si>
   <si>
     <t xml:space="preserve">7.62036991119385</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">8.08124160766602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92609786987305</t>
+    <t xml:space="preserve">7.92609834671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.89871835708618</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">7.6477484703064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8257098197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67969036102295</t>
+    <t xml:space="preserve">7.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67968988418579</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
@@ -3920,10 +3920,10 @@
     <t xml:space="preserve">7.54736089706421</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20056438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96784687042236</t>
+    <t xml:space="preserve">7.20056486129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96784734725952</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
@@ -3932,19 +3932,19 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833311080933</t>
+    <t xml:space="preserve">6.85833263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03629350662231</t>
+    <t xml:space="preserve">7.03629398345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.98153686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76250743865967</t>
+    <t xml:space="preserve">6.76250791549683</t>
   </si>
   <si>
     <t xml:space="preserve">6.90396356582642</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80357551574707</t>
+    <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
     <t xml:space="preserve">6.69406127929688</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">6.46590662002563</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48872184753418</t>
+    <t xml:space="preserve">6.48872232437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.41571283340454</t>
@@ -3977,16 +3977,16 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260515213013</t>
+    <t xml:space="preserve">6.53891611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260562896729</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26056718826294</t>
+    <t xml:space="preserve">6.2605676651001</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -4001,25 +4001,25 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474082946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58454751968384</t>
+    <t xml:space="preserve">6.46134328842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474130630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58454704284668</t>
   </si>
   <si>
     <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49328470230103</t>
+    <t xml:space="preserve">6.49328517913818</t>
   </si>
   <si>
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813884735107</t>
+    <t xml:space="preserve">6.80813932418823</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4028,22 +4028,22 @@
     <t xml:space="preserve">6.83551740646362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81726503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4059042930603</t>
+    <t xml:space="preserve">6.81726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40590381622314</t>
   </si>
   <si>
     <t xml:space="preserve">7.3602728843689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17318677902222</t>
+    <t xml:space="preserve">7.17318630218506</t>
   </si>
   <si>
     <t xml:space="preserve">7.19143915176392</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94046878814697</t>
+    <t xml:space="preserve">6.94046831130981</t>
   </si>
   <si>
     <t xml:space="preserve">7.02260446548462</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231248855591</t>
+    <t xml:space="preserve">7.18231296539307</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4070,28 +4070,28 @@
     <t xml:space="preserve">7.18687582015991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57473945617676</t>
+    <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
     <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3504638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21357345581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90784502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81658315658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03104877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89415550231934</t>
+    <t xml:space="preserve">8.35046482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21357250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90784454345703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81658267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03104972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89415502548218</t>
   </si>
   <si>
     <t xml:space="preserve">7.49260330200195</t>
@@ -4100,13 +4100,13 @@
     <t xml:space="preserve">7.37396287918091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25532245635986</t>
+    <t xml:space="preserve">7.25532197952271</t>
   </si>
   <si>
     <t xml:space="preserve">7.3465838432312</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910804748535</t>
+    <t xml:space="preserve">7.52910757064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.59299087524414</t>
@@ -4121,19 +4121,19 @@
     <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21037340164185</t>
+    <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
     <t xml:space="preserve">6.27425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0506649017334</t>
+    <t xml:space="preserve">6.05066537857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73581123352051</t>
+    <t xml:space="preserve">5.73581171035767</t>
   </si>
   <si>
     <t xml:space="preserve">5.9594030380249</t>
@@ -4157,19 +4157,19 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27881956100464</t>
+    <t xml:space="preserve">6.2788200378418</t>
   </si>
   <si>
     <t xml:space="preserve">6.32445049285889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39746046066284</t>
+    <t xml:space="preserve">6.39745998382568</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54347991943359</t>
+    <t xml:space="preserve">6.54347944259644</t>
   </si>
   <si>
     <t xml:space="preserve">6.57085752487183</t>
@@ -4184,19 +4184,19 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901266098022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09105110168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02716732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84008073806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57542037963867</t>
+    <t xml:space="preserve">6.79901218414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09105062484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02716684341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84008026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57542085647583</t>
   </si>
   <si>
     <t xml:space="preserve">6.68949842453003</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959449768066</t>
+    <t xml:space="preserve">6.94959497451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4220,13 +4220,13 @@
     <t xml:space="preserve">7.93978595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17706680297852</t>
+    <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.12230968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78920364379883</t>
+    <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
     <t xml:space="preserve">7.69794321060181</t>
@@ -4238,25 +4238,25 @@
     <t xml:space="preserve">7.7298846244812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66600036621094</t>
+    <t xml:space="preserve">7.6660008430481</t>
   </si>
   <si>
     <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71163129806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91697120666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86677646636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72075843811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57017612457275</t>
+    <t xml:space="preserve">7.71163177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91697072982788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86677694320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72075796127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5701756477356</t>
   </si>
   <si>
     <t xml:space="preserve">7.62949514389038</t>
@@ -4271,13 +4271,13 @@
     <t xml:space="preserve">7.31464290618896</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28270053863525</t>
+    <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
     <t xml:space="preserve">7.1777491569519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04998302459717</t>
+    <t xml:space="preserve">7.04998254776001</t>
   </si>
   <si>
     <t xml:space="preserve">7.35571050643921</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46978807449341</t>
+    <t xml:space="preserve">7.46978759765625</t>
   </si>
   <si>
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959312438965</t>
+    <t xml:space="preserve">7.79376792907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
     <t xml:space="preserve">8.38696956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34590244293213</t>
+    <t xml:space="preserve">8.34590339660645</t>
   </si>
   <si>
     <t xml:space="preserve">8.36871814727783</t>
@@ -4325,10 +4325,10 @@
     <t xml:space="preserve">8.66531848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8067741394043</t>
+    <t xml:space="preserve">8.82959079742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80677509307861</t>
   </si>
   <si>
     <t xml:space="preserve">8.9801721572876</t>
@@ -4337,10 +4337,10 @@
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84327983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347362518311</t>
+    <t xml:space="preserve">8.8432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347457885742</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4355,7 +4355,7 @@
     <t xml:space="preserve">8.72463893890381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51473617553711</t>
+    <t xml:space="preserve">8.51473712921143</t>
   </si>
   <si>
     <t xml:space="preserve">8.41891193389893</t>
@@ -4385,10 +4385,10 @@
     <t xml:space="preserve">8.00367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99910736083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83483600616455</t>
+    <t xml:space="preserve">7.99910688400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83483552932739</t>
   </si>
   <si>
     <t xml:space="preserve">7.6888165473938</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">8.05386447906494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97172832489014</t>
+    <t xml:space="preserve">7.97172784805298</t>
   </si>
   <si>
     <t xml:space="preserve">7.9215350151062</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">8.15425205230713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716451644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12755584716797</t>
+    <t xml:space="preserve">7.96716499328613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12755537033081</t>
   </si>
   <si>
     <t xml:space="preserve">6.96328401565552</t>
@@ -4433,16 +4433,16 @@
     <t xml:space="preserve">7.3283314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21425485610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35114717483521</t>
+    <t xml:space="preserve">7.21425437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
     <t xml:space="preserve">7.24163246154785</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11842918395996</t>
+    <t xml:space="preserve">7.11842966079712</t>
   </si>
   <si>
     <t xml:space="preserve">7.01804161071777</t>
@@ -4451,13 +4451,13 @@
     <t xml:space="preserve">7.00435209274292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73969268798828</t>
+    <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
     <t xml:space="preserve">6.86745929718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13211917877197</t>
+    <t xml:space="preserve">7.13211870193481</t>
   </si>
   <si>
     <t xml:space="preserve">6.88114833831787</t>
@@ -4475,22 +4475,22 @@
     <t xml:space="preserve">6.74881887435913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73512983322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90852689743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76707077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561559677124</t>
+    <t xml:space="preserve">6.73512935638428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90852737426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561511993408</t>
   </si>
   <si>
     <t xml:space="preserve">6.62105226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43852806091309</t>
+    <t xml:space="preserve">6.43852758407593</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50607013702393</t>
+    <t xml:space="preserve">6.50606966018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4532,28 +4532,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67765855789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812610626221</t>
+    <t xml:space="preserve">6.677659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812562942505</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550897598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8635458946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924745559692</t>
+    <t xml:space="preserve">6.92550849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86354637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924697875977</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61569595336914</t>
+    <t xml:space="preserve">6.6156964302063</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4568,19 +4568,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887399673462</t>
+    <t xml:space="preserve">6.44887351989746</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279920578003</t>
+    <t xml:space="preserve">6.57279872894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541538238525</t>
+    <t xml:space="preserve">6.31541585922241</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214445114136</t>
+    <t xml:space="preserve">6.38214492797852</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915386199951</t>
+    <t xml:space="preserve">6.23915433883667</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4634,22 +4634,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74821996688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78635120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167810440063</t>
+    <t xml:space="preserve">5.60999631881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7863507270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167762756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803251266479</t>
+    <t xml:space="preserve">6.05803298950195</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401441574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597702026367</t>
+    <t xml:space="preserve">5.83878087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401393890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597654342651</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653793334961</t>
+    <t xml:space="preserve">5.98653745651245</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4682,13 +4682,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2629861831665</t>
+    <t xml:space="preserve">6.26298570632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728462219238</t>
+    <t xml:space="preserve">6.27728509902954</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71485567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532274246216</t>
+    <t xml:space="preserve">5.7148551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532321929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859415054321</t>
+    <t xml:space="preserve">5.63859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77205181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476182937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7815842628479</t>
+    <t xml:space="preserve">5.68625783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7720513343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78158473968506</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887449264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541683197021</t>
+    <t xml:space="preserve">5.42887496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4775,16 +4775,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1810245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943517684937</t>
+    <t xml:space="preserve">5.18102407455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943565368652</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812685012817</t>
+    <t xml:space="preserve">5.13812732696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4799,19 +4799,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336013793945</t>
+    <t xml:space="preserve">5.64336061477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7196216583252</t>
+    <t xml:space="preserve">5.71962213516235</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027666091919</t>
+    <t xml:space="preserve">5.40027618408203</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569644927979</t>
+    <t xml:space="preserve">5.59569692611694</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775289535522</t>
+    <t xml:space="preserve">5.75775241851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569620132446</t>
+    <t xml:space="preserve">6.10569667816162</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382696151733</t>
+    <t xml:space="preserve">6.14382743835449</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4862,61 +4862,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635000228882</t>
+    <t xml:space="preserve">6.24868631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635047912598</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46793937683105</t>
+    <t xml:space="preserve">6.41074275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4679388999939</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896713256836</t>
+    <t xml:space="preserve">6.03896760940552</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177099227905</t>
+    <t xml:space="preserve">5.98177146911621</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8530797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644409179688</t>
+    <t xml:space="preserve">5.85307931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644456863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420114517212</t>
+    <t xml:space="preserve">6.03420066833496</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7911171913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77681827545166</t>
+    <t xml:space="preserve">5.80541610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79111671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7768177986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4928,28 +4928,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850030899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51943492889404</t>
+    <t xml:space="preserve">5.53850078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186460494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69578981399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5194354057312</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560356140137</t>
+    <t xml:space="preserve">5.49560308456421</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410827636719</t>
+    <t xml:space="preserve">4.91410875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4973,22 +4973,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354759216309</t>
+    <t xml:space="preserve">5.33354711532593</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691188812256</t>
+    <t xml:space="preserve">5.36691236495972</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457509994507</t>
+    <t xml:space="preserve">5.67195844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457557678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438837051392</t>
+    <t xml:space="preserve">5.21438884735107</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4431734085083</t>
+    <t xml:space="preserve">5.44317388534546</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5039,16 +5039,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027593612671</t>
+    <t xml:space="preserve">5.56709909439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027545928955</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8626127243042</t>
+    <t xml:space="preserve">5.86261224746704</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -70909,7 +70909,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6495486111</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>36571</v>
@@ -70918,7 +70918,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="D2495" t="n">
-        <v>4.55499982833862</v>
+        <v>4.53499984741211</v>
       </c>
       <c r="E2495" t="n">
         <v>4.59999990463257</v>
@@ -70930,6 +70930,32 @@
         <v>1904</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6496064815</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>17038</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>4.59499979019165</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>4.50500011444092</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>4.59499979019165</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>4.57499980926514</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>1860</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="1908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1909" uniqueCount="1909">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608814239502</t>
+    <t xml:space="preserve">12.7608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767124176025</t>
+    <t xml:space="preserve">12.784628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767133712769</t>
   </si>
   <si>
     <t xml:space="preserve">12.4758977890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9930114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2700786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746179580688</t>
+    <t xml:space="preserve">11.9930105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.270076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233945846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746160507202</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075635910034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4125671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6738014221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563430786133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.372989654541</t>
+    <t xml:space="preserve">12.4125690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0563411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3729887008667</t>
   </si>
   <si>
     <t xml:space="preserve">12.1750841140747</t>
@@ -92,19 +92,19 @@
     <t xml:space="preserve">12.1909160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9850959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955730438232</t>
+    <t xml:space="preserve">11.7713565826416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9850950241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955720901489</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626274108887</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">11.1063995361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942903518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3597183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584365844727</t>
+    <t xml:space="preserve">11.4942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3597164154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.858434677124</t>
   </si>
   <si>
     <t xml:space="preserve">11.5180416107178</t>
@@ -134,37 +134,37 @@
     <t xml:space="preserve">11.8346872329712</t>
   </si>
   <si>
-    <t xml:space="preserve">11.676362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684484481812</t>
+    <t xml:space="preserve">11.6763639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684465408325</t>
   </si>
   <si>
     <t xml:space="preserve">11.3992977142334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1855611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3888206481934</t>
+    <t xml:space="preserve">11.1855621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692611694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
     <t xml:space="preserve">12.4284009933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2304973602295</t>
+    <t xml:space="preserve">12.2304964065552</t>
   </si>
   <si>
     <t xml:space="preserve">12.1117534637451</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1513347625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196718215942</t>
+    <t xml:space="preserve">12.1513357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196708679199</t>
   </si>
   <si>
     <t xml:space="preserve">12.8242101669312</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">12.9508686065674</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1408567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704271316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387632369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.576247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625087738037</t>
+    <t xml:space="preserve">13.1408586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575061798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999956130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379467010498</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">13.1091918945312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1962699890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9904479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300312042236</t>
+    <t xml:space="preserve">13.196270942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9904508590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0300302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.6975517272949</t>
@@ -236,76 +236,76 @@
     <t xml:space="preserve">12.6025581359863</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6500520706177</t>
+    <t xml:space="preserve">12.6500539779663</t>
   </si>
   <si>
     <t xml:space="preserve">12.8637914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.586724281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650722503662</t>
+    <t xml:space="preserve">12.5867252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650703430176</t>
   </si>
   <si>
     <t xml:space="preserve">12.5788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7286968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493892669678</t>
+    <t xml:space="preserve">12.7286958694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493873596191</t>
   </si>
   <si>
     <t xml:space="preserve">12.1091585159302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9884691238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241008758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218027114868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2298469543457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942142486572</t>
+    <t xml:space="preserve">11.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241018295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2298488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942152023315</t>
   </si>
   <si>
     <t xml:space="preserve">12.2620306015015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2861709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953632354736</t>
+    <t xml:space="preserve">12.2861700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953641891479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7126045227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735246658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0263986587524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8252477645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.865478515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172025680542</t>
+    <t xml:space="preserve">12.809157371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735237121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0263977050781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8252487182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654775619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172035217285</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999622344971</t>
@@ -314,19 +314,19 @@
     <t xml:space="preserve">12.3666286468506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3103075027466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011144638062</t>
+    <t xml:space="preserve">12.3103065490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011154174805</t>
   </si>
   <si>
     <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8781280517578</t>
+    <t xml:space="preserve">10.8781270980835</t>
   </si>
   <si>
     <t xml:space="preserve">11.0792779922485</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">11.6022644042969</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689296722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103115081787</t>
+    <t xml:space="preserve">12.0689277648926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103105545044</t>
   </si>
   <si>
     <t xml:space="preserve">11.3689308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4896202087402</t>
+    <t xml:space="preserve">11.4896192550659</t>
   </si>
   <si>
     <t xml:space="preserve">10.7574377059937</t>
@@ -353,16 +353,16 @@
     <t xml:space="preserve">10.0735321044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4597396850586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424951553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.634449005127</t>
+    <t xml:space="preserve">10.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424932479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.634446144104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2321500778198</t>
@@ -371,19 +371,19 @@
     <t xml:space="preserve">10.9827251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9264039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229518890381</t>
+    <t xml:space="preserve">10.92640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229528427124</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700807571411</t>
+    <t xml:space="preserve">11.5700788497925</t>
   </si>
   <si>
     <t xml:space="preserve">11.891918182373</t>
@@ -392,16 +392,16 @@
     <t xml:space="preserve">11.5861711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.875825881958</t>
+    <t xml:space="preserve">11.8758249282837</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953672409058</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1896181106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309968948364</t>
+    <t xml:space="preserve">12.1896171569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309959411621</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896169662476</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9942140579224</t>
+    <t xml:space="preserve">12.994213104248</t>
   </si>
   <si>
     <t xml:space="preserve">13.1229486465454</t>
@@ -419,16 +419,16 @@
     <t xml:space="preserve">13.1551332473755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746726989746</t>
+    <t xml:space="preserve">12.9861679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0746736526489</t>
   </si>
   <si>
     <t xml:space="preserve">13.3482360839844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.249382019043</t>
+    <t xml:space="preserve">14.2493810653687</t>
   </si>
   <si>
     <t xml:space="preserve">13.9194974899292</t>
@@ -437,79 +437,79 @@
     <t xml:space="preserve">14.3459339141846</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8551301956177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
+    <t xml:space="preserve">13.855128288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608762741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919097900391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7643222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6275405883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034021377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516790390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183452606201</t>
+    <t xml:space="preserve">14.6275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206453323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603404045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022569656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183443069458</t>
   </si>
   <si>
     <t xml:space="preserve">15.1505279541016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1263904571533</t>
+    <t xml:space="preserve">15.126389503479</t>
   </si>
   <si>
     <t xml:space="preserve">15.0861597061157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0459299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240915298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
+    <t xml:space="preserve">15.0459327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4240913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597211837769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930578231812</t>
@@ -521,85 +521,85 @@
     <t xml:space="preserve">15.4401836395264</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2148942947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045520782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3919067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.255126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1666212081909</t>
+    <t xml:space="preserve">15.2148962020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045530319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3919057846069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2551250457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1666193008423</t>
   </si>
   <si>
     <t xml:space="preserve">15.5286865234375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2229413986206</t>
+    <t xml:space="preserve">15.2229423522949</t>
   </si>
   <si>
     <t xml:space="preserve">15.0137462615967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8850135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.327540397644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114461898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677701950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827144622803</t>
+    <t xml:space="preserve">14.8850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.367769241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034000396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827125549316</t>
   </si>
   <si>
     <t xml:space="preserve">14.6436347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9654722213745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470798492432</t>
+    <t xml:space="preserve">14.9654712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470808029175</t>
   </si>
   <si>
     <t xml:space="preserve">14.8286895751953</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5390377044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551300048828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126012802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263925552368</t>
+    <t xml:space="preserve">14.5390367507935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551290512085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1126003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263935089111</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815647125244</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4827165603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171983718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103002548218</t>
+    <t xml:space="preserve">14.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4102993011475</t>
   </si>
   <si>
     <t xml:space="preserve">14.563175201416</t>
@@ -611,25 +611,25 @@
     <t xml:space="preserve">14.3057050704956</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1045541763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9516820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781196594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045572280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3643274307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1873159408569</t>
+    <t xml:space="preserve">14.1045551300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3643283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1873149871826</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539833068848</t>
@@ -638,13 +638,13 @@
     <t xml:space="preserve">13.31605052948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5896139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9114513397217</t>
+    <t xml:space="preserve">13.5896129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">14.2011051177979</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">13.9999570846558</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9815645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378866195679</t>
+    <t xml:space="preserve">14.9815654754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378856658936</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160472869873</t>
@@ -665,70 +665,70 @@
     <t xml:space="preserve">14.844783782959</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9171962738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631711959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5367364883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045528411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4080009460449</t>
+    <t xml:space="preserve">14.917197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631702423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528230667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.383861541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045480728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4079971313477</t>
   </si>
   <si>
     <t xml:space="preserve">15.110297203064</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2068510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.89075756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988018035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.947075843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3493766784668</t>
+    <t xml:space="preserve">15.2068490982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8987989425659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470777511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3493747711182</t>
   </si>
   <si>
     <t xml:space="preserve">16.3010997772217</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5344333648682</t>
+    <t xml:space="preserve">16.5344295501709</t>
   </si>
   <si>
     <t xml:space="preserve">16.582706451416</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3332805633545</t>
+    <t xml:space="preserve">16.3332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.453971862793</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">16.1562728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9792652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700691223145</t>
+    <t xml:space="preserve">15.9792633056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700700759888</t>
   </si>
   <si>
     <t xml:space="preserve">16.0919055938721</t>
@@ -755,40 +755,40 @@
     <t xml:space="preserve">16.0436325073242</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4781112670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8965034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0413265228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5160427093506</t>
+    <t xml:space="preserve">16.4781074523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8964996337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0413284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5160388946533</t>
   </si>
   <si>
     <t xml:space="preserve">17.773509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229290008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206317901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2700576782227</t>
+    <t xml:space="preserve">18.3850040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229328155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206298828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.270055770874</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907470703125</t>
@@ -797,115 +797,115 @@
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470653533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
+    <t xml:space="preserve">19.4470672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079883575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
   </si>
   <si>
     <t xml:space="preserve">19.7125835418701</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3827018737793</t>
+    <t xml:space="preserve">19.3826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">19.5838489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3102855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436153411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0689067840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0769538879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355712890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286750793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9723529815674</t>
+    <t xml:space="preserve">19.31028175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0689086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0769500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.972354888916</t>
   </si>
   <si>
     <t xml:space="preserve">18.5620136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5056934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6183338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654586791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2597045898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.557409286499</t>
+    <t xml:space="preserve">18.5056915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171825408936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.259708404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585582733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5574073791504</t>
   </si>
   <si>
     <t xml:space="preserve">20.9539318084717</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1818714141846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841827392578</t>
+    <t xml:space="preserve">21.1818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841846466064</t>
   </si>
   <si>
     <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5726222991943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5387649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5550403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922271728516</t>
+    <t xml:space="preserve">21.0027732849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5726184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5387630462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922290802002</t>
   </si>
   <si>
     <t xml:space="preserve">20.3271045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3515281677246</t>
+    <t xml:space="preserve">20.351526260376</t>
   </si>
   <si>
     <t xml:space="preserve">20.5143394470215</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">20.9864959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9946384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.937650680542</t>
+    <t xml:space="preserve">20.9946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9376487731934</t>
   </si>
   <si>
     <t xml:space="preserve">21.1248874664307</t>
@@ -932,67 +932,67 @@
     <t xml:space="preserve">20.8155422210693</t>
   </si>
   <si>
-    <t xml:space="preserve">21.15744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585582733154</t>
+    <t xml:space="preserve">21.1574478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585601806641</t>
   </si>
   <si>
     <t xml:space="preserve">20.2945423126221</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5957450866699</t>
+    <t xml:space="preserve">20.5957469940186</t>
   </si>
   <si>
     <t xml:space="preserve">20.318962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386669158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0828857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480102539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9851970672607</t>
+    <t xml:space="preserve">19.8386688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480140686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.985200881958</t>
   </si>
   <si>
     <t xml:space="preserve">20.1317329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3678073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259960174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770603179932</t>
+    <t xml:space="preserve">20.3678092956543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108234405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770584106445</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874179840088</t>
+    <t xml:space="preserve">19.1874217987061</t>
   </si>
   <si>
     <t xml:space="preserve">18.9757652282715</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8048114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7071208953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338577270508</t>
+    <t xml:space="preserve">18.8048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338596343994</t>
   </si>
   <si>
     <t xml:space="preserve">19.1304359436035</t>
@@ -1001,28 +1001,28 @@
     <t xml:space="preserve">19.4804821014404</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5293235778809</t>
+    <t xml:space="preserve">19.5293254852295</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049942016602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7816829681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805744171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375602722168</t>
+    <t xml:space="preserve">19.7816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805763244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375583648682</t>
   </si>
   <si>
     <t xml:space="preserve">20.78297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7748413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050903320312</t>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050846099854</t>
   </si>
   <si>
     <t xml:space="preserve">20.677152633667</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">21.1655883789062</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2795543670654</t>
+    <t xml:space="preserve">21.2795562744141</t>
   </si>
   <si>
     <t xml:space="preserve">21.0597610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">21.043478012085</t>
+    <t xml:space="preserve">21.0434799194336</t>
   </si>
   <si>
     <t xml:space="preserve">20.6852931976318</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">21.1004638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5400562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319156646729</t>
+    <t xml:space="preserve">21.5400543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319175720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202610015869</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">21.9226684570312</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7842750549316</t>
+    <t xml:space="preserve">21.7842769622803</t>
   </si>
   <si>
     <t xml:space="preserve">21.4993534088135</t>
@@ -1070,19 +1070,19 @@
     <t xml:space="preserve">21.3935241699219</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7761363983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6214599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691928863525</t>
+    <t xml:space="preserve">21.7761325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6214618682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691986083984</t>
   </si>
   <si>
     <t xml:space="preserve">21.711009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5169315338135</t>
+    <t xml:space="preserve">22.5169277191162</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
@@ -1091,7 +1091,7 @@
     <t xml:space="preserve">22.6308975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0542087554932</t>
+    <t xml:space="preserve">23.0542106628418</t>
   </si>
   <si>
     <t xml:space="preserve">22.9890842437744</t>
@@ -1103,61 +1103,61 @@
     <t xml:space="preserve">23.1681785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4693813323975</t>
+    <t xml:space="preserve">23.4693794250488</t>
   </si>
   <si>
     <t xml:space="preserve">23.8601303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7298812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008331298828</t>
+    <t xml:space="preserve">23.7298793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648490905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5996322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263614654541</t>
+    <t xml:space="preserve">23.599630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263633728027</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159114837646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9822406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.23459815979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4394111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0568027496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0079536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8777046203613</t>
+    <t xml:space="preserve">23.9822368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2346000671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4394073486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0568008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0079517364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8777084350586</t>
   </si>
   <si>
     <t xml:space="preserve">24.8288631439209</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6497688293457</t>
+    <t xml:space="preserve">24.6497707366943</t>
   </si>
   <si>
     <t xml:space="preserve">25.6999073028564</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">25.9604091644287</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4801120758057</t>
+    <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1613330841064</t>
+    <t xml:space="preserve">24.1613349914551</t>
   </si>
   <si>
     <t xml:space="preserve">24.5602207183838</t>
@@ -1190,40 +1190,40 @@
     <t xml:space="preserve">24.7474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765037536621</t>
+    <t xml:space="preserve">24.5765056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.4556884765625</t>
   </si>
   <si>
-    <t xml:space="preserve">26.277889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9848308563232</t>
+    <t xml:space="preserve">26.2778911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9848289489746</t>
   </si>
   <si>
     <t xml:space="preserve">27.1082324981689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7676239013672</t>
+    <t xml:space="preserve">27.7676258087158</t>
   </si>
   <si>
     <t xml:space="preserve">27.3850135803223</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9210014343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071239471436</t>
+    <t xml:space="preserve">26.9209995269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071258544922</t>
   </si>
   <si>
     <t xml:space="preserve">27.0105495452881</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6930637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765941619873</t>
+    <t xml:space="preserve">26.6930618286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765979766846</t>
   </si>
   <si>
     <t xml:space="preserve">24.9102687835693</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">25.2440338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8451442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7393169403076</t>
+    <t xml:space="preserve">24.8451461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.739315032959</t>
   </si>
   <si>
     <t xml:space="preserve">25.1951904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6429252624512</t>
+    <t xml:space="preserve">25.6429233551025</t>
   </si>
   <si>
     <t xml:space="preserve">25.5859394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7243309020996</t>
+    <t xml:space="preserve">25.724328994751</t>
   </si>
   <si>
     <t xml:space="preserve">25.6917667388916</t>
@@ -1265,37 +1265,37 @@
     <t xml:space="preserve">25.545238494873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7568950653076</t>
+    <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208148956299</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.39870262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5126762390137</t>
+    <t xml:space="preserve">25.3172988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987045288086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.512674331665</t>
   </si>
   <si>
     <t xml:space="preserve">25.7650318145752</t>
   </si>
   <si>
-    <t xml:space="preserve">26.049955368042</t>
+    <t xml:space="preserve">26.0499534606934</t>
   </si>
   <si>
     <t xml:space="preserve">25.2033290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.462532043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661441802979</t>
+    <t xml:space="preserve">25.0486621856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4625339508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661422729492</t>
   </si>
   <si>
     <t xml:space="preserve">25.0242366790771</t>
@@ -1307,28 +1307,28 @@
     <t xml:space="preserve">25.0893630981445</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7148933410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6836242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.741907119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5790958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6604995727539</t>
+    <t xml:space="preserve">24.7148952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6836261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7419052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5790939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3931560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6604976654053</t>
   </si>
   <si>
     <t xml:space="preserve">26.497688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1313571929932</t>
+    <t xml:space="preserve">26.1313591003418</t>
   </si>
   <si>
     <t xml:space="preserve">25.602222442627</t>
@@ -1337,16 +1337,16 @@
     <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2941741943359</t>
+    <t xml:space="preserve">26.2941722869873</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815937042236</t>
+    <t xml:space="preserve">27.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8815956115723</t>
   </si>
   <si>
     <t xml:space="preserve">27.2303428649902</t>
@@ -1355,25 +1355,25 @@
     <t xml:space="preserve">26.8233127593994</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6197967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730800628662</t>
+    <t xml:space="preserve">26.6197986602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730819702148</t>
   </si>
   <si>
     <t xml:space="preserve">24.6253490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8519897460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.974100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5615177154541</t>
+    <t xml:space="preserve">23.8519916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9740982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5615196228027</t>
   </si>
   <si>
     <t xml:space="preserve">25.3580017089844</t>
@@ -1382,73 +1382,73 @@
     <t xml:space="preserve">25.1137866973877</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358951568604</t>
+    <t xml:space="preserve">25.2358913421631</t>
   </si>
   <si>
     <t xml:space="preserve">23.3635540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218330383301</t>
+    <t xml:space="preserve">24.4218311309814</t>
   </si>
   <si>
     <t xml:space="preserve">26.2534694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1887130737305</t>
+    <t xml:space="preserve">23.6891803741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5670700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1887149810791</t>
   </si>
   <si>
     <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7002773284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4736366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540222167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273834228516</t>
+    <t xml:space="preserve">20.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7002792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6947269439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680862426758</t>
+    <t xml:space="preserve">20.8806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680881500244</t>
   </si>
   <si>
     <t xml:space="preserve">22.1831645965576</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5901927947998</t>
+    <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.0203514099121</t>
@@ -1457,7 +1457,7 @@
     <t xml:space="preserve">22.3459758758545</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1600399017334</t>
+    <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
     <t xml:space="preserve">22.7123031616211</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">23.6077709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.805736541748</t>
+    <t xml:space="preserve">25.8057346343994</t>
   </si>
   <si>
     <t xml:space="preserve">24.7067546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3811321258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2183170318604</t>
+    <t xml:space="preserve">24.3811302185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.218318939209</t>
   </si>
   <si>
     <t xml:space="preserve">24.1776161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2997226715088</t>
+    <t xml:space="preserve">24.2997264862061</t>
   </si>
   <si>
     <t xml:space="preserve">24.7881622314453</t>
@@ -1496,13 +1496,13 @@
     <t xml:space="preserve">24.6640110015869</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9123058319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.408899307251</t>
+    <t xml:space="preserve">24.9123077392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4089012145996</t>
   </si>
   <si>
     <t xml:space="preserve">25.7813415527344</t>
@@ -1511,19 +1511,19 @@
     <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3261337280273</t>
+    <t xml:space="preserve">25.3261318206787</t>
   </si>
   <si>
     <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1469669342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400539398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951656341553</t>
+    <t xml:space="preserve">27.1469688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9400520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951675415039</t>
   </si>
   <si>
     <t xml:space="preserve">25.491662979126</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">25.5330486297607</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0778369903564</t>
+    <t xml:space="preserve">25.0778388977051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6985740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6571960449219</t>
+    <t xml:space="preserve">25.6985759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6571941375732</t>
   </si>
   <si>
     <t xml:space="preserve">26.1537857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8227214813232</t>
+    <t xml:space="preserve">25.8227233886719</t>
   </si>
   <si>
     <t xml:space="preserve">25.9468727111816</t>
@@ -1571,43 +1571,43 @@
     <t xml:space="preserve">27.022819519043</t>
   </si>
   <si>
-    <t xml:space="preserve">24.250186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6294498443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7535972595215</t>
+    <t xml:space="preserve">24.2501850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6294479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">24.0432720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363609313965</t>
+    <t xml:space="preserve">23.8363590240479</t>
   </si>
   <si>
     <t xml:space="preserve">23.3811511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7949771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8777446746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9191226959229</t>
+    <t xml:space="preserve">23.794979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.877742767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9191246032715</t>
   </si>
   <si>
     <t xml:space="preserve">24.2088031768799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329524993896</t>
+    <t xml:space="preserve">24.332950592041</t>
   </si>
   <si>
     <t xml:space="preserve">25.4502830505371</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5262279510498</t>
+    <t xml:space="preserve">26.5262260437012</t>
   </si>
   <si>
     <t xml:space="preserve">25.8641090393066</t>
@@ -1616,13 +1616,13 @@
     <t xml:space="preserve">26.0296382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5676078796387</t>
+    <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">25.5744285583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6089935302734</t>
+    <t xml:space="preserve">26.6089916229248</t>
   </si>
   <si>
     <t xml:space="preserve">26.9814357757568</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">26.6503753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3606986999512</t>
+    <t xml:space="preserve">26.3606967926025</t>
   </si>
   <si>
     <t xml:space="preserve">24.4984817504883</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0914726257324</t>
+    <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258491516113</t>
@@ -1676,37 +1676,37 @@
     <t xml:space="preserve">19.8636341094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3602256774902</t>
+    <t xml:space="preserve">20.3602237701416</t>
   </si>
   <si>
     <t xml:space="preserve">20.2360763549805</t>
   </si>
   <si>
-    <t xml:space="preserve">21.8086128234863</t>
+    <t xml:space="preserve">21.8086166381836</t>
   </si>
   <si>
     <t xml:space="preserve">20.9395809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9327659606934</t>
+    <t xml:space="preserve">21.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">22.0569095611572</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9259433746338</t>
+    <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
     <t xml:space="preserve">22.263822555542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4634456634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462112426758</t>
+    <t xml:space="preserve">18.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4634475708008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
     <t xml:space="preserve">17.6703567504883</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">17.8772678375244</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2083301544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4980087280273</t>
+    <t xml:space="preserve">18.2083282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.498010635376</t>
   </si>
   <si>
     <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8290691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6221561431885</t>
+    <t xml:space="preserve">18.8290710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6221580505371</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704528808594</t>
@@ -1739,7 +1739,7 @@
     <t xml:space="preserve">19.5325736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.491189956665</t>
+    <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773658752441</t>
@@ -1748,61 +1748,61 @@
     <t xml:space="preserve">19.1187477111816</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0428009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7945041656494</t>
+    <t xml:space="preserve">18.0427989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.794506072998</t>
   </si>
   <si>
     <t xml:space="preserve">16.8427066802979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737670898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806800842285</t>
+    <t xml:space="preserve">17.7531204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737651824951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806781768799</t>
   </si>
   <si>
     <t xml:space="preserve">16.966854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6357936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599430084229</t>
+    <t xml:space="preserve">16.6357955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599411010742</t>
   </si>
   <si>
     <t xml:space="preserve">16.884090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5530300140381</t>
+    <t xml:space="preserve">16.5530319213867</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4152450561523</t>
+    <t xml:space="preserve">18.415246963501</t>
   </si>
   <si>
     <t xml:space="preserve">19.1601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.40842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4498081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222522735596</t>
+    <t xml:space="preserve">19.4084281921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4498100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222541809082</t>
   </si>
   <si>
     <t xml:space="preserve">20.5257530212402</t>
@@ -1811,22 +1811,22 @@
     <t xml:space="preserve">20.6499042510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1119289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808685302734</t>
+    <t xml:space="preserve">20.3188419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808704376221</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0291633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567211151123</t>
+    <t xml:space="preserve">20.0291652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567249298096</t>
   </si>
   <si>
     <t xml:space="preserve">19.9464015960693</t>
@@ -1835,13 +1835,13 @@
     <t xml:space="preserve">19.2428970336914</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3256607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0359840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2979145050049</t>
+    <t xml:space="preserve">19.325662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.035982131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2979125976562</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364761352539</t>
@@ -1850,13 +1850,13 @@
     <t xml:space="preserve">16.594409942627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4868144989014</t>
+    <t xml:space="preserve">16.48681640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910034179688</t>
+    <t xml:space="preserve">17.0909996032715</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151489257812</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">17.3310222625732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.364128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910957336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6056022644043</t>
+    <t xml:space="preserve">17.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6056041717529</t>
   </si>
   <si>
     <t xml:space="preserve">18.3407573699951</t>
@@ -1880,34 +1880,34 @@
     <t xml:space="preserve">18.0593528747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.645528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2482528686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289730072021</t>
+    <t xml:space="preserve">17.6455268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">18.07590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1255645751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6620807647705</t>
+    <t xml:space="preserve">18.1255664825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6620826721191</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765872955322</t>
+    <t xml:space="preserve">17.9765892028809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2248840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7614002227783</t>
+    <t xml:space="preserve">17.7613983154297</t>
   </si>
   <si>
     <t xml:space="preserve">16.5861320495605</t>
@@ -1916,28 +1916,28 @@
     <t xml:space="preserve">16.6192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5033721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701711654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.839789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328783035278</t>
+    <t xml:space="preserve">16.5033702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101900100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2701692581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328763961792</t>
   </si>
   <si>
     <t xml:space="preserve">14.6742582321167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177845001221</t>
+    <t xml:space="preserve">15.6177806854248</t>
   </si>
   <si>
     <t xml:space="preserve">16.0233345031738</t>
@@ -1949,10 +1949,10 @@
     <t xml:space="preserve">15.0632562637329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467023849487</t>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.046703338623</t>
   </si>
   <si>
     <t xml:space="preserve">14.6659822463989</t>
@@ -1961,22 +1961,22 @@
     <t xml:space="preserve">14.8232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3255767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426055908203</t>
+    <t xml:space="preserve">15.3255758285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3426065444946</t>
   </si>
   <si>
     <t xml:space="preserve">14.7125539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8402671813965</t>
+    <t xml:space="preserve">14.8402652740479</t>
   </si>
   <si>
     <t xml:space="preserve">14.6614665985107</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6444396972656</t>
+    <t xml:space="preserve">14.6444387435913</t>
   </si>
   <si>
     <t xml:space="preserve">14.8062076568604</t>
@@ -1985,16 +1985,16 @@
     <t xml:space="preserve">14.5422687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811706542969</t>
+    <t xml:space="preserve">14.8913488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811687469482</t>
   </si>
   <si>
     <t xml:space="preserve">15.6661434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9083786010742</t>
+    <t xml:space="preserve">14.9083795547485</t>
   </si>
   <si>
     <t xml:space="preserve">14.5252389907837</t>
@@ -2012,25 +2012,25 @@
     <t xml:space="preserve">14.6018667221069</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315853118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2357559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0484437942505</t>
+    <t xml:space="preserve">14.431586265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2357568740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0484447479248</t>
   </si>
   <si>
     <t xml:space="preserve">14.1846714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8317499160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3208990097046</t>
+    <t xml:space="preserve">14.831750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3208980560303</t>
   </si>
   <si>
     <t xml:space="preserve">14.7295808792114</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">15.0020370483398</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4230680465698</t>
+    <t xml:space="preserve">14.4230690002441</t>
   </si>
   <si>
     <t xml:space="preserve">14.3379278182983</t>
@@ -2051,7 +2051,7 @@
     <t xml:space="preserve">13.9462738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6908473968506</t>
+    <t xml:space="preserve">13.6908464431763</t>
   </si>
   <si>
     <t xml:space="preserve">13.7419328689575</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821636199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975257873535</t>
+    <t xml:space="preserve">13.6312484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948514938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975267410278</t>
   </si>
   <si>
     <t xml:space="preserve">14.0995292663574</t>
@@ -2081,10 +2081,10 @@
     <t xml:space="preserve">13.8185606002808</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801630020142</t>
+    <t xml:space="preserve">13.2225646972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801620483398</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
@@ -2099,16 +2099,16 @@
     <t xml:space="preserve">13.1544513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2140522003174</t>
+    <t xml:space="preserve">13.2140512466431</t>
   </si>
   <si>
     <t xml:space="preserve">12.1668043136597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9663009643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748153686523</t>
+    <t xml:space="preserve">10.9663000106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748163223267</t>
   </si>
   <si>
     <t xml:space="preserve">10.9492721557617</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.881157875061</t>
+    <t xml:space="preserve">11.162127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8811588287354</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">10.7619600296021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471021652222</t>
+    <t xml:space="preserve">10.2511072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599565505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471012115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.6683025360107</t>
@@ -2156,10 +2156,10 @@
     <t xml:space="preserve">10.7279024124146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664684295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5367527008057</t>
+    <t xml:space="preserve">11.3664693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.53675365448</t>
   </si>
   <si>
     <t xml:space="preserve">11.6644659042358</t>
@@ -2174,25 +2174,25 @@
     <t xml:space="preserve">11.749608039856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838331222534</t>
+    <t xml:space="preserve">12.1838321685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8177213668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751512527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4601249694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5026950836182</t>
+    <t xml:space="preserve">11.817720413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476045608521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4601240158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5026960372925</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450986862183</t>
@@ -2201,7 +2201,7 @@
     <t xml:space="preserve">10.8981866836548</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2898416519165</t>
+    <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.2132129669189</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">10.7108755111694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4724779129028</t>
+    <t xml:space="preserve">10.4724769592285</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597890853882</t>
@@ -2219,28 +2219,28 @@
     <t xml:space="preserve">11.0173854827881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0854997634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0514430999756</t>
+    <t xml:space="preserve">11.0854988098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088729858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2642965316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.698522567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814947128296</t>
+    <t xml:space="preserve">11.0003576278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2642974853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6985235214233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814937591553</t>
   </si>
   <si>
     <t xml:space="preserve">11.8092079162598</t>
@@ -2249,31 +2249,31 @@
     <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1970243453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.239595413208</t>
+    <t xml:space="preserve">13.1970233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
     <t xml:space="preserve">13.5120487213135</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6738185882568</t>
+    <t xml:space="preserve">13.6738195419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5461053848267</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4145545959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8526191711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.218729019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8781585693359</t>
+    <t xml:space="preserve">14.4145555496216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8526182174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2187280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8781595230103</t>
   </si>
   <si>
     <t xml:space="preserve">13.7759895324707</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">13.4439353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8441047668457</t>
+    <t xml:space="preserve">13.8441028594971</t>
   </si>
   <si>
     <t xml:space="preserve">14.4486131668091</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">14.9254083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.504373550415</t>
+    <t xml:space="preserve">15.5043745040894</t>
   </si>
   <si>
     <t xml:space="preserve">14.5933532714844</t>
@@ -2303,16 +2303,16 @@
     <t xml:space="preserve">14.5592966079712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9424343109131</t>
+    <t xml:space="preserve">14.9424352645874</t>
   </si>
   <si>
     <t xml:space="preserve">14.9679794311523</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6870098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0190629959106</t>
+    <t xml:space="preserve">14.6870088577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190649032593</t>
   </si>
   <si>
     <t xml:space="preserve">15.1467771530151</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">15.3170604705811</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6406011581421</t>
+    <t xml:space="preserve">15.6406021118164</t>
   </si>
   <si>
     <t xml:space="preserve">15.461802482605</t>
@@ -2330,16 +2330,16 @@
     <t xml:space="preserve">14.4656391143799</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3634700775146</t>
+    <t xml:space="preserve">14.363471031189</t>
   </si>
   <si>
     <t xml:space="preserve">14.3294143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4826688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1506156921387</t>
+    <t xml:space="preserve">14.4826679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.150616645813</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335868835449</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">14.1165571212769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4911832809448</t>
+    <t xml:space="preserve">14.4911842346191</t>
   </si>
   <si>
     <t xml:space="preserve">14.3804979324341</t>
@@ -2366,19 +2366,19 @@
     <t xml:space="preserve">13.7078762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292440414429</t>
+    <t xml:space="preserve">13.9292459487915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5035343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3162231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.563136100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375909805298</t>
+    <t xml:space="preserve">13.3162221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631351470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375919342041</t>
   </si>
   <si>
     <t xml:space="preserve">14.406042098999</t>
@@ -2390,31 +2390,31 @@
     <t xml:space="preserve">14.2953567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5167245864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761560440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7589597702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4183921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5584573745728</t>
+    <t xml:space="preserve">14.5082139968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5167236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761569976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931858062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.758960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4183931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5584564208984</t>
   </si>
   <si>
     <t xml:space="preserve">12.3370885848999</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010284423828</t>
+    <t xml:space="preserve">12.6010293960571</t>
   </si>
   <si>
     <t xml:space="preserve">11.9880056381226</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">11.4430961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3277359008789</t>
+    <t xml:space="preserve">10.3277349472046</t>
   </si>
   <si>
     <t xml:space="preserve">9.82539653778076</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">9.42522811889648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74025344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08424091339111</t>
+    <t xml:space="preserve">9.74025440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0842399597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.73557758331299</t>
@@ -2447,19 +2447,19 @@
     <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078491210938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278839111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00803184509277</t>
+    <t xml:space="preserve">8.31412410736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11020374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00803279876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.41671466827393</t>
@@ -2468,64 +2468,64 @@
     <t xml:space="preserve">9.47631359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57848453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225883483887</t>
+    <t xml:space="preserve">9.5784854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225788116455</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16980457305908</t>
+    <t xml:space="preserve">9.09317398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16980361938477</t>
   </si>
   <si>
     <t xml:space="preserve">9.53591346740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48482799530029</t>
+    <t xml:space="preserve">9.48482894897461</t>
   </si>
   <si>
     <t xml:space="preserve">9.62105560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.089337348938</t>
+    <t xml:space="preserve">10.0893363952637</t>
   </si>
   <si>
     <t xml:space="preserve">10.1319074630737</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0467672348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75728416442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97013759613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2936792373657</t>
+    <t xml:space="preserve">10.0467662811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75728321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87648296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.970139503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0552806854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
     <t xml:space="preserve">10.3192205429077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299058914185</t>
+    <t xml:space="preserve">10.4299049377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961832046509</t>
+    <t xml:space="preserve">11.1961822509766</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">9.3060302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5103702545166</t>
+    <t xml:space="preserve">9.51037120819092</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888561248779</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">9.26345825195312</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25494384765625</t>
+    <t xml:space="preserve">9.25494480133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.36562824249268</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">8.86329174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93140602111816</t>
+    <t xml:space="preserve">8.93140506744385</t>
   </si>
   <si>
     <t xml:space="preserve">8.85477638244629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28048801422119</t>
+    <t xml:space="preserve">9.28048706054688</t>
   </si>
   <si>
     <t xml:space="preserve">9.70619869232178</t>
@@ -2582,16 +2582,16 @@
     <t xml:space="preserve">9.85093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876707077026</t>
+    <t xml:space="preserve">11.1876697540283</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5405912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340803146362</t>
+    <t xml:space="preserve">10.5405902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340793609619</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254215240479</t>
@@ -2600,7 +2600,7 @@
     <t xml:space="preserve">9.96388530731201</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2435731887817</t>
+    <t xml:space="preserve">10.2435741424561</t>
   </si>
   <si>
     <t xml:space="preserve">10.182391166687</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">10.444598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163259506226</t>
+    <t xml:space="preserve">10.0163269042969</t>
   </si>
   <si>
     <t xml:space="preserve">9.90270328521729</t>
@@ -2627,19 +2627,19 @@
     <t xml:space="preserve">9.72789764404297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64049530029297</t>
+    <t xml:space="preserve">9.64049625396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.28214454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56183338165283</t>
+    <t xml:space="preserve">9.56183242797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.41324996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52687168121338</t>
+    <t xml:space="preserve">9.5268726348877</t>
   </si>
   <si>
     <t xml:space="preserve">9.49191093444824</t>
@@ -2672,13 +2672,13 @@
     <t xml:space="preserve">9.18600273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33458709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2209644317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44821071624756</t>
+    <t xml:space="preserve">9.33458614349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22096347808838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44820976257324</t>
   </si>
   <si>
     <t xml:space="preserve">9.29088497161865</t>
@@ -2690,13 +2690,13 @@
     <t xml:space="preserve">10.3484563827515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4358568191528</t>
+    <t xml:space="preserve">10.4358577728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9777545928955</t>
+    <t xml:space="preserve">10.9777536392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001176834106</t>
@@ -2708,25 +2708,25 @@
     <t xml:space="preserve">11.4672069549561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0826377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8903512954712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7942094802856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6281433105469</t>
+    <t xml:space="preserve">11.0826368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8903522491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7942085266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6281423568726</t>
   </si>
   <si>
     <t xml:space="preserve">10.5494813919067</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260913848877</t>
+    <t xml:space="preserve">10.2872743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226092338562</t>
   </si>
   <si>
     <t xml:space="preserve">10.1299505233765</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2785348892212</t>
+    <t xml:space="preserve">10.2785339355469</t>
   </si>
   <si>
     <t xml:space="preserve">10.3834171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3659353256226</t>
+    <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
     <t xml:space="preserve">10.4970407485962</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">10.6893253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106634140015</t>
+    <t xml:space="preserve">10.6106624603271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4795598983765</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">9.81529998779297</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0687694549561</t>
+    <t xml:space="preserve">10.0687685012817</t>
   </si>
   <si>
     <t xml:space="preserve">9.9901065826416</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">9.86774253845215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6142749786377</t>
+    <t xml:space="preserve">9.61427402496338</t>
   </si>
   <si>
     <t xml:space="preserve">9.00245761871338</t>
@@ -2843,10 +2843,10 @@
     <t xml:space="preserve">8.5348539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64410781860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12482070922852</t>
+    <t xml:space="preserve">8.6441068649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1248197555542</t>
   </si>
   <si>
     <t xml:space="preserve">9.16852283477783</t>
@@ -2870,22 +2870,22 @@
     <t xml:space="preserve">11.1350774765015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6070508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324918746948</t>
+    <t xml:space="preserve">11.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324928283691</t>
   </si>
   <si>
     <t xml:space="preserve">12.3587131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5597372055054</t>
+    <t xml:space="preserve">12.5597381591797</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867406845093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4810752868652</t>
+    <t xml:space="preserve">12.4810762405396</t>
   </si>
   <si>
     <t xml:space="preserve">12.19264793396</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">12.1139860153198</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2101287841797</t>
+    <t xml:space="preserve">12.210129737854</t>
   </si>
   <si>
     <t xml:space="preserve">11.6857137680054</t>
@@ -2909,7 +2909,7 @@
     <t xml:space="preserve">11.9916229248047</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9479217529297</t>
+    <t xml:space="preserve">11.9479207992554</t>
   </si>
   <si>
     <t xml:space="preserve">12.061544418335</t>
@@ -2921,13 +2921,13 @@
     <t xml:space="preserve">12.0440626144409</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8954792022705</t>
+    <t xml:space="preserve">11.8954801559448</t>
   </si>
   <si>
     <t xml:space="preserve">12.0091037750244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0178442001343</t>
+    <t xml:space="preserve">12.01784324646</t>
   </si>
   <si>
     <t xml:space="preserve">12.6558818817139</t>
@@ -2972,7 +2972,7 @@
     <t xml:space="preserve">12.8394260406494</t>
   </si>
   <si>
-    <t xml:space="preserve">12.909348487854</t>
+    <t xml:space="preserve">12.9093494415283</t>
   </si>
   <si>
     <t xml:space="preserve">12.8219470977783</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">13.0229721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114004135132</t>
+    <t xml:space="preserve">13.3113994598389</t>
   </si>
   <si>
     <t xml:space="preserve">13.215256690979</t>
@@ -2993,28 +2993,28 @@
     <t xml:space="preserve">13.2502193450928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607650756836</t>
+    <t xml:space="preserve">12.7607641220093</t>
   </si>
   <si>
     <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.953049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9792718887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355688095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3026599884033</t>
+    <t xml:space="preserve">12.9530506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9792709350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3026609420776</t>
   </si>
   <si>
     <t xml:space="preserve">13.407543182373</t>
   </si>
   <si>
-    <t xml:space="preserve">13.189037322998</t>
+    <t xml:space="preserve">13.1890363693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2239971160889</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">14.0281000137329</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1067628860474</t>
+    <t xml:space="preserve">14.1067638397217</t>
   </si>
   <si>
     <t xml:space="preserve">14.395191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5000762939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039316177368</t>
+    <t xml:space="preserve">14.500075340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039306640625</t>
   </si>
   <si>
     <t xml:space="preserve">14.5612573623657</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">14.3864517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6661405563354</t>
+    <t xml:space="preserve">14.6661415100098</t>
   </si>
   <si>
     <t xml:space="preserve">14.7098407745361</t>
@@ -3071,28 +3071,28 @@
     <t xml:space="preserve">15.1818132400513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3653583526611</t>
+    <t xml:space="preserve">15.3653593063354</t>
   </si>
   <si>
     <t xml:space="preserve">15.1206302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">14.456374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.613697052002</t>
+    <t xml:space="preserve">14.4563751220703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6136960983276</t>
   </si>
   <si>
     <t xml:space="preserve">14.7622814178467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3442687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7550601959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946556091309</t>
+    <t xml:space="preserve">16.3442668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7550582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946575164795</t>
   </si>
   <si>
     <t xml:space="preserve">15.8373336791992</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9247369766235</t>
+    <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
     <t xml:space="preserve">15.9422149658203</t>
@@ -3116,22 +3116,22 @@
     <t xml:space="preserve">15.5663843154907</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.242995262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2866954803467</t>
+    <t xml:space="preserve">15.3566188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440202713013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330397605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2429962158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2255144119263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779569625854</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">15.2517366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0681915283203</t>
+    <t xml:space="preserve">15.068190574646</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381120681763</t>
@@ -3155,10 +3155,10 @@
     <t xml:space="preserve">14.8933877944946</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0856733322144</t>
+    <t xml:space="preserve">14.8234634399414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.08567237854</t>
   </si>
   <si>
     <t xml:space="preserve">14.9196062088013</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">14.937087059021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1468534469604</t>
+    <t xml:space="preserve">15.1468524932861</t>
   </si>
   <si>
     <t xml:space="preserve">14.8496837615967</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">15.2604751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3041772842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409442901611</t>
+    <t xml:space="preserve">15.3041763305664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409433364868</t>
   </si>
   <si>
     <t xml:space="preserve">14.4214124679565</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">17.463020324707</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0748386383057</t>
+    <t xml:space="preserve">18.074836730957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2846031188965</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048980712891</t>
+    <t xml:space="preserve">18.5048999786377</t>
   </si>
   <si>
     <t xml:space="preserve">18.7340068817139</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">18.8573722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8221263885498</t>
+    <t xml:space="preserve">18.8221244812012</t>
   </si>
   <si>
     <t xml:space="preserve">19.3684597015381</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">18.2052955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6987590789795</t>
+    <t xml:space="preserve">18.6987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">18.7163829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2934131622314</t>
+    <t xml:space="preserve">18.2934150695801</t>
   </si>
   <si>
     <t xml:space="preserve">18.2581672668457</t>
@@ -3275,25 +3275,25 @@
     <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8175735473633</t>
+    <t xml:space="preserve">17.8175754547119</t>
   </si>
   <si>
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.888069152832</t>
+    <t xml:space="preserve">17.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6413383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5708427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589622497559</t>
+    <t xml:space="preserve">17.64133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5708446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589603424072</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
@@ -3302,7 +3302,7 @@
     <t xml:space="preserve">17.3681678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478729248047</t>
+    <t xml:space="preserve">17.1478710174561</t>
   </si>
   <si>
     <t xml:space="preserve">17.4650993347168</t>
@@ -3311,7 +3311,7 @@
     <t xml:space="preserve">17.9761867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8351974487305</t>
+    <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">17.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.125696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5222301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6367874145508</t>
+    <t xml:space="preserve">16.3724308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1256980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6367855072021</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857917785645</t>
   </si>
   <si>
-    <t xml:space="preserve">17.244800567627</t>
+    <t xml:space="preserve">17.2448024749756</t>
   </si>
   <si>
     <t xml:space="preserve">17.3769798278809</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.7470779418945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5355930328369</t>
+    <t xml:space="preserve">17.5355949401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6237144470215</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">16.8747043609619</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861873626709</t>
+    <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
     <t xml:space="preserve">17.1743087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3417339324951</t>
+    <t xml:space="preserve">17.3417358398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">16.9716377258301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7249050140381</t>
+    <t xml:space="preserve">16.7249031066895</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2183704376221</t>
+    <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">16.7425289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927276611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4957962036133</t>
+    <t xml:space="preserve">16.5927257537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">16.3900547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3019371032715</t>
+    <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
     <t xml:space="preserve">15.9935188293457</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">15.8613433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2402515411377</t>
+    <t xml:space="preserve">16.2402534484863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">16.3195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7732238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119358062744</t>
+    <t xml:space="preserve">15.7732248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176792144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590660095215</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150072097778</t>
+    <t xml:space="preserve">15.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154056549072</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">15.2180757522583</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1828289031982</t>
+    <t xml:space="preserve">15.1828298568726</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242147445679</t>
@@ -3485,25 +3485,25 @@
     <t xml:space="preserve">15.1035223007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4912433624268</t>
+    <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.1475820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0859003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9801578521729</t>
+    <t xml:space="preserve">15.0858993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9801568984985</t>
   </si>
   <si>
     <t xml:space="preserve">14.8215427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6188716888428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3985748291016</t>
+    <t xml:space="preserve">14.6188707351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3985738754272</t>
   </si>
   <si>
     <t xml:space="preserve">14.0020408630371</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">14.3104553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.345703125</t>
+    <t xml:space="preserve">14.3457040786743</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3536,37 +3536,37 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483770370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4778814315796</t>
+    <t xml:space="preserve">14.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4778804779053</t>
   </si>
   <si>
     <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1254062652588</t>
+    <t xml:space="preserve">14.1254053115845</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8169918060303</t>
+    <t xml:space="preserve">13.816990852356</t>
   </si>
   <si>
     <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0856084823608</t>
+    <t xml:space="preserve">13.772931098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.032735824585</t>
+    <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
@@ -3578,25 +3578,25 @@
     <t xml:space="preserve">12.944616317749</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3852090835571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583776473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5350103378296</t>
+    <t xml:space="preserve">13.3852100372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583766937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5350112915039</t>
   </si>
   <si>
     <t xml:space="preserve">13.5614471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1913499832153</t>
+    <t xml:space="preserve">13.191349029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.2265968322754</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6231298446655</t>
+    <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
     <t xml:space="preserve">13.3147144317627</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">13.2618436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557046890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.438081741333</t>
+    <t xml:space="preserve">13.4557056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4380807876587</t>
   </si>
   <si>
     <t xml:space="preserve">13.4645166397095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4997634887695</t>
+    <t xml:space="preserve">13.4997644424438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4821405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878829956055</t>
+    <t xml:space="preserve">13.5878820419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5702590942383</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">13.7112493515015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4468936920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649122238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388748168945</t>
+    <t xml:space="preserve">13.4468927383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710531234741</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">12.5568952560425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273908615112</t>
+    <t xml:space="preserve">12.6273899078369</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492748260498</t>
+    <t xml:space="preserve">11.6492738723755</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">11.8078870773315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9048185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8431348800659</t>
+    <t xml:space="preserve">11.9048175811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8431358337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427373886108</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4642267227173</t>
+    <t xml:space="preserve">11.5347194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.464225769043</t>
   </si>
   <si>
     <t xml:space="preserve">11.1117506027222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9090785980225</t>
+    <t xml:space="preserve">10.9090795516968</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263050079346</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">11.1293754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0412549972534</t>
+    <t xml:space="preserve">11.0412559509277</t>
   </si>
   <si>
     <t xml:space="preserve">10.8209590911865</t>
@@ -3728,10 +3728,10 @@
     <t xml:space="preserve">10.9355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6975946426392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0500679016113</t>
+    <t xml:space="preserve">10.6975936889648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0500688552856</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772977828979</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977798461914</t>
+    <t xml:space="preserve">9.25244998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.83829212188721</t>
@@ -3797,13 +3797,13 @@
     <t xml:space="preserve">8.68848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62680721282959</t>
+    <t xml:space="preserve">8.62680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27873992919922</t>
+    <t xml:space="preserve">8.2787389755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349117279053</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433300018311</t>
+    <t xml:space="preserve">8.27433395385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245250701904</t>
+    <t xml:space="preserve">8.36245155334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3848,40 +3848,40 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88661193847656</t>
+    <t xml:space="preserve">7.88661241531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.895423412323</t>
+    <t xml:space="preserve">8.02760124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819700241089</t>
+    <t xml:space="preserve">7.80730485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527545928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512655258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95803880691528</t>
+    <t xml:space="preserve">7.6619086265564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527498245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803928375244</t>
   </si>
   <si>
     <t xml:space="preserve">7.62037038803101</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124160766602</t>
+    <t xml:space="preserve">8.08124256134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.92609739303589</t>
@@ -3908,16 +3908,16 @@
     <t xml:space="preserve">7.64774894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570886611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67968988418579</t>
+    <t xml:space="preserve">7.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736089706421</t>
+    <t xml:space="preserve">7.54736042022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833311080933</t>
+    <t xml:space="preserve">6.85833263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3950,13 +3950,13 @@
     <t xml:space="preserve">6.90396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444932937622</t>
+    <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406127929688</t>
+    <t xml:space="preserve">6.69406175613403</t>
   </si>
   <si>
     <t xml:space="preserve">6.46590709686279</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212055206299</t>
+    <t xml:space="preserve">6.19212102890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891658782959</t>
+    <t xml:space="preserve">6.53891611099243</t>
   </si>
   <si>
     <t xml:space="preserve">6.55260562896729</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474082946777</t>
+    <t xml:space="preserve">6.46134376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474130630493</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173133850098</t>
+    <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813837051392</t>
+    <t xml:space="preserve">6.80813884735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231248855591</t>
+    <t xml:space="preserve">7.18231296539307</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12687397003174</t>
+    <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
     <t xml:space="preserve">8.35046482086182</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">7.81658220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03104972839355</t>
+    <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
     <t xml:space="preserve">7.89415502548218</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910852432251</t>
+    <t xml:space="preserve">7.52910804748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4115,19 +4115,19 @@
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775032043457</t>
+    <t xml:space="preserve">6.48415851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
     <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27425718307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0506649017334</t>
+    <t xml:space="preserve">6.27425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05066537857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610204696655</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27881956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445049285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746046066284</t>
+    <t xml:space="preserve">6.2788200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39745998382568</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901266098022</t>
+    <t xml:space="preserve">6.79901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959449768066</t>
+    <t xml:space="preserve">6.94959497451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978595733643</t>
+    <t xml:space="preserve">7.93978691101074</t>
   </si>
   <si>
     <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12231063842773</t>
+    <t xml:space="preserve">8.12230968475342</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76638889312744</t>
+    <t xml:space="preserve">7.69794321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7663893699646</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77095317840576</t>
+    <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91697216033936</t>
+    <t xml:space="preserve">7.9169716835022</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4259,22 +4259,22 @@
     <t xml:space="preserve">7.57017517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62949562072754</t>
+    <t xml:space="preserve">7.62949514389038</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55192279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31464290618896</t>
+    <t xml:space="preserve">7.5519232749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17774963378906</t>
+    <t xml:space="preserve">7.1777491569519</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4289,22 +4289,22 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45609855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46978855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59755373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79376745223999</t>
+    <t xml:space="preserve">7.4560980796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46978807449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79376792907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38697052001953</t>
+    <t xml:space="preserve">8.38696956634521</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">8.36871719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81589984893799</t>
+    <t xml:space="preserve">8.8159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.94366836547852</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98017311096191</t>
+    <t xml:space="preserve">8.9801721572876</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">8.8432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89347362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77939510345459</t>
+    <t xml:space="preserve">8.89347457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77939605712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.7292013168335</t>
@@ -4358,16 +4358,16 @@
     <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41891288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40978622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44172763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22726154327393</t>
+    <t xml:space="preserve">8.41891193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40978527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44172668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.21813488006592</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949493408203</t>
+    <t xml:space="preserve">8.24551296234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949398040771</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085472106934</t>
+    <t xml:space="preserve">7.83483457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68881607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085519790649</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580493927002</t>
+    <t xml:space="preserve">8.09493160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580589294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716451644897</t>
+    <t xml:space="preserve">7.96716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24163293838501</t>
+    <t xml:space="preserve">7.24163246154785</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804161071777</t>
+    <t xml:space="preserve">7.01804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745882034302</t>
+    <t xml:space="preserve">6.86745929718018</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88114786148071</t>
+    <t xml:space="preserve">6.88114833831787</t>
   </si>
   <si>
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78075981140137</t>
+    <t xml:space="preserve">6.78076028823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">6.90852737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76707077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561559677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62105178833008</t>
+    <t xml:space="preserve">6.76707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62105226516724</t>
   </si>
   <si>
     <t xml:space="preserve">6.43852758407593</t>
@@ -5736,6 +5736,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.59000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53999996185303</t>
   </si>
 </sst>
 </file>
@@ -71100,7 +71103,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6912615741</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>41955</v>
@@ -71121,6 +71124,32 @@
         <v>1907</v>
       </c>
       <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6911226852</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>171130</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>4.59999990463257</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>4.55999994277954</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>4.53999996185303</v>
+      </c>
+      <c r="G2503" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608814239502</t>
+    <t xml:space="preserve">12.7608823776245</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767143249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758987426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742685317993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.270076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233955383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125680923462</t>
+    <t xml:space="preserve">12.7846279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758977890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700777053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075626373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125699996948</t>
   </si>
   <si>
     <t xml:space="preserve">12.6738042831421</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">12.0563402175903</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3729877471924</t>
+    <t xml:space="preserve">12.3729887008667</t>
   </si>
   <si>
     <t xml:space="preserve">12.175085067749</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">11.7713594436646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6367835998535</t>
+    <t xml:space="preserve">11.6367826461792</t>
   </si>
   <si>
     <t xml:space="preserve">11.9850950241089</t>
@@ -104,61 +104,61 @@
     <t xml:space="preserve">11.1380634307861</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9955739974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4626264572144</t>
+    <t xml:space="preserve">10.9955720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.462628364563</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063995361328</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942922592163</t>
+    <t xml:space="preserve">11.494291305542</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.359715461731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763648986816</t>
+    <t xml:space="preserve">11.3597173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.858434677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159442901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346872329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.676362991333</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684484481812</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3992967605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1855621337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692621231079</t>
+    <t xml:space="preserve">11.3992977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1855611801147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692630767822</t>
   </si>
   <si>
     <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2304973602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1117534637451</t>
+    <t xml:space="preserve">12.4284009933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2304964065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1117553710938</t>
   </si>
   <si>
     <t xml:space="preserve">12.1513357162476</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">12.8242101669312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9508686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408557891846</t>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408576965332</t>
   </si>
   <si>
     <t xml:space="preserve">13.2754325866699</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3704261779785</t>
+    <t xml:space="preserve">13.3704271316528</t>
   </si>
   <si>
     <t xml:space="preserve">13.3387622833252</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4575052261353</t>
+    <t xml:space="preserve">13.4575061798096</t>
   </si>
   <si>
     <t xml:space="preserve">13.5762462615967</t>
@@ -197,31 +197,31 @@
     <t xml:space="preserve">13.5999965667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.362509727478</t>
+    <t xml:space="preserve">13.3625087738037</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379457473755</t>
   </si>
   <si>
-    <t xml:space="preserve">12.752965927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171083450317</t>
+    <t xml:space="preserve">12.7529649734497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171092987061</t>
   </si>
   <si>
     <t xml:space="preserve">13.1091928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1962699890137</t>
+    <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9904499053955</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0221128463745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933599472046</t>
+    <t xml:space="preserve">13.0221157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933618545532</t>
   </si>
   <si>
     <t xml:space="preserve">13.0775270462036</t>
@@ -230,40 +230,40 @@
     <t xml:space="preserve">13.0300312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6975507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6025562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6500539779663</t>
+    <t xml:space="preserve">12.6975517272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6025590896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.650053024292</t>
   </si>
   <si>
     <t xml:space="preserve">12.863790512085</t>
   </si>
   <si>
-    <t xml:space="preserve">12.586724281311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650722503662</t>
+    <t xml:space="preserve">12.5867233276367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679832458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650712966919</t>
   </si>
   <si>
     <t xml:space="preserve">12.5788097381592</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7286949157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493902206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091575622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.988468170166</t>
+    <t xml:space="preserve">12.7286968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884691238403</t>
   </si>
   <si>
     <t xml:space="preserve">11.9241018295288</t>
@@ -278,61 +278,61 @@
     <t xml:space="preserve">12.2942142486572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2620306015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2861700057983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735237121582</t>
+    <t xml:space="preserve">12.2620315551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.286169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735246658325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263967514038</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252487182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8654775619507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172016143799</t>
+    <t xml:space="preserve">12.8252468109131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8654766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172035217285</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999612808228</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666286468506</t>
+    <t xml:space="preserve">12.3666296005249</t>
   </si>
   <si>
     <t xml:space="preserve">12.3103084564209</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011154174805</t>
+    <t xml:space="preserve">11.7390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011135101318</t>
   </si>
   <si>
     <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8781299591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792770385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022624969482</t>
+    <t xml:space="preserve">10.8781280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792779922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689277648926</t>
@@ -344,19 +344,19 @@
     <t xml:space="preserve">11.3689308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4896211624146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7574377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735330581665</t>
+    <t xml:space="preserve">11.4896202087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.45973777771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0229549407959</t>
+    <t xml:space="preserve">11.0229539871216</t>
   </si>
   <si>
     <t xml:space="preserve">11.6424932479858</t>
@@ -365,43 +365,43 @@
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827241897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470922470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5700798034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8919172286987</t>
+    <t xml:space="preserve">11.2321500778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.982723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229518890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470903396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5700807571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8919191360474</t>
   </si>
   <si>
     <t xml:space="preserve">11.5861721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8758268356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953662872314</t>
+    <t xml:space="preserve">11.8758249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953672409058</t>
   </si>
   <si>
     <t xml:space="preserve">12.1896190643311</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309949874878</t>
+    <t xml:space="preserve">12.4309959411621</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896160125732</t>
@@ -410,13 +410,13 @@
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1229476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1551342010498</t>
+    <t xml:space="preserve">12.9942111968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1229486465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1551322937012</t>
   </si>
   <si>
     <t xml:space="preserve">12.9861669540405</t>
@@ -428,13 +428,13 @@
     <t xml:space="preserve">13.3482351303101</t>
   </si>
   <si>
-    <t xml:space="preserve">14.249382019043</t>
+    <t xml:space="preserve">14.24937915802</t>
   </si>
   <si>
     <t xml:space="preserve">13.9194965362549</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3459348678589</t>
+    <t xml:space="preserve">14.3459339141846</t>
   </si>
   <si>
     <t xml:space="preserve">13.8551301956177</t>
@@ -443,85 +443,85 @@
     <t xml:space="preserve">14.1608762741089</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919059753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643222808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137502670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562732696533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1263885498047</t>
+    <t xml:space="preserve">14.6919078826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643232345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206434249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034030914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516790390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562770843506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1263904571533</t>
   </si>
   <si>
     <t xml:space="preserve">15.0861597061157</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0459327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240894317627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873086929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689165115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367376327515</t>
+    <t xml:space="preserve">15.0459308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953548431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.424090385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367366790771</t>
   </si>
   <si>
     <t xml:space="preserve">14.7884616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8930587768555</t>
+    <t xml:space="preserve">14.8930578231812</t>
   </si>
   <si>
     <t xml:space="preserve">15.4884605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4401826858521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148952484131</t>
+    <t xml:space="preserve">15.440185546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045530319214</t>
@@ -530,37 +530,37 @@
     <t xml:space="preserve">15.3919057846069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.255126953125</t>
+    <t xml:space="preserve">15.2551259994507</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286884307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229404449463</t>
+    <t xml:space="preserve">15.5286893844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229433059692</t>
   </si>
   <si>
     <t xml:space="preserve">15.013747215271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988019943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.311448097229</t>
+    <t xml:space="preserve">14.885009765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198805809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114461898804</t>
   </si>
   <si>
     <t xml:space="preserve">15.3677711486816</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3034009933472</t>
+    <t xml:space="preserve">15.3034029006958</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827144622803</t>
@@ -569,73 +569,73 @@
     <t xml:space="preserve">14.6436347961426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9654712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286895751953</t>
+    <t xml:space="preserve">14.9654731750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470788955688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286905288696</t>
   </si>
   <si>
     <t xml:space="preserve">14.5390348434448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5551290512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126012802124</t>
+    <t xml:space="preserve">14.5551261901855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1126003265381</t>
   </si>
   <si>
     <t xml:space="preserve">14.4263935089111</t>
   </si>
   <si>
-    <t xml:space="preserve">14.281566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827146530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171974182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585752487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057050704956</t>
+    <t xml:space="preserve">14.2815675735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2172002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103021621704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.563175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305703163147</t>
   </si>
   <si>
     <t xml:space="preserve">14.1045541763306</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3217926025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9516820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045553207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3643264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1873168945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9539833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3160514831543</t>
+    <t xml:space="preserve">14.3217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.951681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3643293380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1873159408569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9539842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3160495758057</t>
   </si>
   <si>
     <t xml:space="preserve">13.5896139144897</t>
@@ -644,76 +644,76 @@
     <t xml:space="preserve">13.7746715545654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9114542007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9999561309814</t>
+    <t xml:space="preserve">13.9114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011079788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9999580383301</t>
   </si>
   <si>
     <t xml:space="preserve">14.9815645217896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160491943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.917197227478</t>
+    <t xml:space="preserve">15.0378866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9171962738037</t>
   </si>
   <si>
     <t xml:space="preserve">15.2631721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528268814087</t>
+    <t xml:space="preserve">15.6011028289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528249740601</t>
   </si>
   <si>
     <t xml:space="preserve">15.5367336273193</t>
   </si>
   <si>
-    <t xml:space="preserve">15.464319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.609148979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045490264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4080009460449</t>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838624954224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045537948608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4079961776733</t>
   </si>
   <si>
     <t xml:space="preserve">15.1102991104126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2068471908569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8907566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8987998962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470767974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114421844482</t>
+    <t xml:space="preserve">15.2068500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8988018035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.947078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114440917969</t>
   </si>
   <si>
     <t xml:space="preserve">16.3493747711182</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3332862854004</t>
+    <t xml:space="preserve">16.3332824707031</t>
   </si>
   <si>
     <t xml:space="preserve">16.4539737701416</t>
@@ -737,52 +737,52 @@
     <t xml:space="preserve">16.1723651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1562728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792623519897</t>
+    <t xml:space="preserve">16.156270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792633056641</t>
   </si>
   <si>
     <t xml:space="preserve">15.7700662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0919055938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436325073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4781112670898</t>
+    <t xml:space="preserve">16.0919036865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.003396987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4781093597412</t>
   </si>
   <si>
     <t xml:space="preserve">16.8964996337891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9769592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0413265228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5160388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.773509979248</t>
+    <t xml:space="preserve">16.9769630432129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0413284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.516040802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.3850021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229328155518</t>
+    <t xml:space="preserve">18.7470703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229309082031</t>
   </si>
   <si>
     <t xml:space="preserve">19.0206317901611</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470672607422</t>
+    <t xml:space="preserve">19.4470634460449</t>
   </si>
   <si>
     <t xml:space="preserve">19.7528114318848</t>
@@ -812,28 +812,28 @@
     <t xml:space="preserve">19.6321239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7125816345215</t>
+    <t xml:space="preserve">19.7125835418701</t>
   </si>
   <si>
     <t xml:space="preserve">19.382698059082</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5838470458984</t>
+    <t xml:space="preserve">19.5838489532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.3102855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5436172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0689086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0769500732422</t>
+    <t xml:space="preserve">19.5436229705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631576538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0689067840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0769538879395</t>
   </si>
   <si>
     <t xml:space="preserve">18.8355751037598</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">19.0286769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.972354888916</t>
+    <t xml:space="preserve">18.9723567962646</t>
   </si>
   <si>
     <t xml:space="preserve">18.56201171875</t>
@@ -854,139 +854,139 @@
     <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1654567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171787261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.259708404541</t>
+    <t xml:space="preserve">19.1654605865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2597064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5574054718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841808319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0027713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5726184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5387592315674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5550403594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922290802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271064758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3515243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5143375396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9864959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.937650680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1248874664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353374481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8155422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1574459075928</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585582733154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5574073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9539318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0027770996094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5726203918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5387630462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5550441741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922271728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.351526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5143375396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9864959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.937650680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.124885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8399658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8155403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1574459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585563659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945423126221</t>
+    <t xml:space="preserve">20.2945404052734</t>
   </si>
   <si>
     <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3189640045166</t>
+    <t xml:space="preserve">20.3189659118652</t>
   </si>
   <si>
     <t xml:space="preserve">19.8386707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828876495361</t>
+    <t xml:space="preserve">20.0828857421875</t>
   </si>
   <si>
     <t xml:space="preserve">20.1480102539062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9851970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317310333252</t>
+    <t xml:space="preserve">19.9851989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317291259766</t>
   </si>
   <si>
     <t xml:space="preserve">20.3678092956543</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3583755493164</t>
+    <t xml:space="preserve">20.7259922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3583717346191</t>
   </si>
   <si>
     <t xml:space="preserve">19.1874217987061</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9757614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8048133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7071208953857</t>
+    <t xml:space="preserve">18.9757633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7071228027344</t>
   </si>
   <si>
     <t xml:space="preserve">19.0978717803955</t>
@@ -995,37 +995,37 @@
     <t xml:space="preserve">18.6338577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1304359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804821014404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049942016602</t>
+    <t xml:space="preserve">19.1304378509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804801940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293235778809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049961090088</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375621795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.78297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6771507263184</t>
+    <t xml:space="preserve">20.1805744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748413085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6771488189697</t>
   </si>
   <si>
     <t xml:space="preserve">21.1655864715576</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">21.2795562744141</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0597591400146</t>
+    <t xml:space="preserve">21.0597648620605</t>
   </si>
   <si>
     <t xml:space="preserve">21.0434799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6852931976318</t>
+    <t xml:space="preserve">20.6852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">21.1004638671875</t>
@@ -1049,10 +1049,10 @@
     <t xml:space="preserve">21.5400543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319175720215</t>
+    <t xml:space="preserve">21.4260845184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319156646729</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202590942383</t>
@@ -1064,79 +1064,79 @@
     <t xml:space="preserve">21.7842750549316</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4993534088135</t>
+    <t xml:space="preserve">21.4993515014648</t>
   </si>
   <si>
     <t xml:space="preserve">21.3935279846191</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7761344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6214580535889</t>
+    <t xml:space="preserve">21.7761363983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6214618682861</t>
   </si>
   <si>
     <t xml:space="preserve">22.0691947937012</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7110061645508</t>
+    <t xml:space="preserve">21.7110080718994</t>
   </si>
   <si>
     <t xml:space="preserve">22.5169277191162</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9809455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6308975219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0542087554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.989086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.200740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.168176651001</t>
+    <t xml:space="preserve">22.9809436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6308994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0542125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9890842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1681804656982</t>
   </si>
   <si>
     <t xml:space="preserve">23.4693794250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8601303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298812866211</t>
+    <t xml:space="preserve">23.86012840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298793792725</t>
   </si>
   <si>
     <t xml:space="preserve">24.0310840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9659595489502</t>
+    <t xml:space="preserve">23.9659576416016</t>
   </si>
   <si>
     <t xml:space="preserve">24.0229434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3648490905762</t>
+    <t xml:space="preserve">24.3648471832275</t>
   </si>
   <si>
     <t xml:space="preserve">23.9008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9903793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159114837646</t>
+    <t xml:space="preserve">23.9903831481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159133911133</t>
   </si>
   <si>
     <t xml:space="preserve">23.9822406768799</t>
@@ -1154,16 +1154,16 @@
     <t xml:space="preserve">25.0568008422852</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0079574584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.87770652771</t>
+    <t xml:space="preserve">25.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8777046203613</t>
   </si>
   <si>
     <t xml:space="preserve">24.8288631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6660537719727</t>
+    <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
     <t xml:space="preserve">24.6497707366943</t>
@@ -1172,109 +1172,109 @@
     <t xml:space="preserve">25.6999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9604091644287</t>
+    <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
     <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1789112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613311767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602207183838</t>
+    <t xml:space="preserve">25.1789093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613330841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602245330811</t>
   </si>
   <si>
     <t xml:space="preserve">24.7474575042725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.277889251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9848308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1082344055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7676258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3850116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209995269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0105476379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6930637359619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765960693359</t>
+    <t xml:space="preserve">24.5765037536621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2778911590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9848327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1082305908203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7676239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3850154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9210014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071220397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0105457305908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6930656433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765979766846</t>
   </si>
   <si>
     <t xml:space="preserve">24.910270690918</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5032386779785</t>
+    <t xml:space="preserve">24.5032367706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.6172046661377</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5846481323242</t>
+    <t xml:space="preserve">24.5846462249756</t>
   </si>
   <si>
     <t xml:space="preserve">25.2440357208252</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8451442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7393169403076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1951885223389</t>
+    <t xml:space="preserve">24.8451461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.739315032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1951923370361</t>
   </si>
   <si>
     <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5859413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7243309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6917667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5452365875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7568912506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208129882812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3173007965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3987083435059</t>
+    <t xml:space="preserve">25.5859355926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7243328094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6917686462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5452346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7568893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208148956299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3172988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987064361572</t>
   </si>
   <si>
     <t xml:space="preserve">25.512674331665</t>
@@ -1283,43 +1283,43 @@
     <t xml:space="preserve">25.7650337219238</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0499534606934</t>
+    <t xml:space="preserve">26.0499572753906</t>
   </si>
   <si>
     <t xml:space="preserve">25.2033309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486621856689</t>
+    <t xml:space="preserve">25.0486583709717</t>
   </si>
   <si>
     <t xml:space="preserve">24.4625339508057</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3661403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148952484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.683629989624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7419013977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5790939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931560516357</t>
+    <t xml:space="preserve">25.3661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893592834473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148933410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6836261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7419052124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.393159866333</t>
   </si>
   <si>
     <t xml:space="preserve">26.6604995727539</t>
@@ -1328,58 +1328,58 @@
     <t xml:space="preserve">26.497688293457</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1313629150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941722869873</t>
+    <t xml:space="preserve">26.1313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022243499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.29416847229</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826099395752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815937042236</t>
+    <t xml:space="preserve">27.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.881591796875</t>
   </si>
   <si>
     <t xml:space="preserve">27.2303447723389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8233108520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197986602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720638275146</t>
+    <t xml:space="preserve">26.8233127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6197967529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720657348633</t>
   </si>
   <si>
     <t xml:space="preserve">25.0730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6253490447998</t>
+    <t xml:space="preserve">24.6253471374512</t>
   </si>
   <si>
     <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9740982055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5615196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.358003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137828826904</t>
+    <t xml:space="preserve">23.974100112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5615177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3580017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137847900391</t>
   </si>
   <si>
     <t xml:space="preserve">25.2358932495117</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">23.3635520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218311309814</t>
+    <t xml:space="preserve">24.4218330383301</t>
   </si>
   <si>
     <t xml:space="preserve">26.2534694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6891803741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5670700073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1887149810791</t>
+    <t xml:space="preserve">23.6891765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5670680999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">20.6364479064941</t>
@@ -1418,31 +1418,31 @@
     <t xml:space="preserve">21.2062911987305</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6540279388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273834228516</t>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806705474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.694730758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680881500244</t>
+    <t xml:space="preserve">20.8806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680862426758</t>
   </si>
   <si>
     <t xml:space="preserve">22.1831645965576</t>
@@ -1451,61 +1451,61 @@
     <t xml:space="preserve">22.5901966094971</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0203514099121</t>
+    <t xml:space="preserve">22.0203495025635</t>
   </si>
   <si>
     <t xml:space="preserve">22.3459777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1600379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7123012542725</t>
+    <t xml:space="preserve">23.1600360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7123031616211</t>
   </si>
   <si>
     <t xml:space="preserve">23.6077690124512</t>
   </si>
   <si>
-    <t xml:space="preserve">25.805736541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7067546844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3811283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2183170318604</t>
+    <t xml:space="preserve">25.8057346343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7067565917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3811302185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2183151245117</t>
   </si>
   <si>
     <t xml:space="preserve">24.1776142120361</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2997245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7881622314453</t>
+    <t xml:space="preserve">24.2997226715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7881603240967</t>
   </si>
   <si>
     <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1260395050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123077392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019882202148</t>
+    <t xml:space="preserve">24.1260375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019863128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.4089012145996</t>
   </si>
   <si>
-    <t xml:space="preserve">25.781343460083</t>
+    <t xml:space="preserve">25.7813415527344</t>
   </si>
   <si>
     <t xml:space="preserve">25.7399597167969</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">25.326135635376</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2779312133789</t>
+    <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
     <t xml:space="preserve">27.1469650268555</t>
@@ -1523,19 +1523,19 @@
     <t xml:space="preserve">26.9400539398193</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1951694488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4916610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5330448150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778388977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3675174713135</t>
+    <t xml:space="preserve">26.1951675415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.491662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5330467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778369903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3675136566162</t>
   </si>
   <si>
     <t xml:space="preserve">25.6985759735107</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">25.2847518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6571941375732</t>
+    <t xml:space="preserve">25.6571922302246</t>
   </si>
   <si>
     <t xml:space="preserve">26.1537857055664</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">24.250186920166</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6294479370117</t>
+    <t xml:space="preserve">23.6294498443604</t>
   </si>
   <si>
     <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0432739257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363590240479</t>
+    <t xml:space="preserve">24.043270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363609313965</t>
   </si>
   <si>
     <t xml:space="preserve">23.3811531066895</t>
@@ -1595,37 +1595,37 @@
     <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9191246032715</t>
+    <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
     <t xml:space="preserve">24.2088031768799</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329524993896</t>
+    <t xml:space="preserve">24.332950592041</t>
   </si>
   <si>
     <t xml:space="preserve">25.4502811431885</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5262298583984</t>
+    <t xml:space="preserve">26.5262279510498</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0296382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5676136016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.574426651001</t>
+    <t xml:space="preserve">26.0296401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5676097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5744285583496</t>
   </si>
   <si>
     <t xml:space="preserve">26.6089954376221</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9814376831055</t>
+    <t xml:space="preserve">26.9814338684082</t>
   </si>
   <si>
     <t xml:space="preserve">25.9882545471191</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">26.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4984836578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0914726257324</t>
+    <t xml:space="preserve">26.6503772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3607006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4984817504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
     <t xml:space="preserve">21.7258491516113</t>
@@ -1655,16 +1655,16 @@
     <t xml:space="preserve">21.8913803100586</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7740516662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6430854797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4775543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.105110168457</t>
+    <t xml:space="preserve">20.7740497589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6430835723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4775562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1051120758057</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154335021973</t>
@@ -1673,40 +1673,40 @@
     <t xml:space="preserve">19.6981029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8636341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602256774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086128234863</t>
+    <t xml:space="preserve">19.8636322021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602237701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086166381836</t>
   </si>
   <si>
     <t xml:space="preserve">20.9395809173584</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9327640533447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0569133758545</t>
+    <t xml:space="preserve">21.9327621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0569114685059</t>
   </si>
   <si>
     <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.263822555542</t>
+    <t xml:space="preserve">22.2638206481934</t>
   </si>
   <si>
     <t xml:space="preserve">18.0014171600342</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4634437561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462112426758</t>
+    <t xml:space="preserve">17.4634456634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
     <t xml:space="preserve">17.6703586578369</t>
@@ -1727,40 +1727,40 @@
     <t xml:space="preserve">18.8290691375732</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6221542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.870454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3670406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4911880493164</t>
+    <t xml:space="preserve">18.6221580505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3670425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5325717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187496185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0428009033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7945022583008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8427085876465</t>
+    <t xml:space="preserve">19.118745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0427989959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7945041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8427047729492</t>
   </si>
   <si>
     <t xml:space="preserve">17.7531223297119</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1737689971924</t>
+    <t xml:space="preserve">17.1737651824951</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806800842285</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">16.966854095459</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6357936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8840885162354</t>
+    <t xml:space="preserve">16.6357955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8840866088867</t>
   </si>
   <si>
     <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1601314544678</t>
+    <t xml:space="preserve">18.2497138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.415246963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1601333618164</t>
   </si>
   <si>
     <t xml:space="preserve">19.40842628479</t>
@@ -1796,28 +1796,28 @@
     <t xml:space="preserve">19.5739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4498081207275</t>
+    <t xml:space="preserve">19.4498100280762</t>
   </si>
   <si>
     <t xml:space="preserve">19.9050159454346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8222503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.64990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808685302734</t>
+    <t xml:space="preserve">19.8222522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6499042510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3188419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1119289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808704376221</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842769622803</t>
@@ -1826,10 +1826,10 @@
     <t xml:space="preserve">20.0291652679443</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6567230224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9463996887207</t>
+    <t xml:space="preserve">19.6567211151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9464015960693</t>
   </si>
   <si>
     <t xml:space="preserve">19.2428951263428</t>
@@ -1847,25 +1847,25 @@
     <t xml:space="preserve">16.5364742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5944080352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4868144989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4537105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0910034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2151489257812</t>
+    <t xml:space="preserve">16.5944118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.48681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4537086486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0910015106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2151470184326</t>
   </si>
   <si>
     <t xml:space="preserve">17.3310222625732</t>
   </si>
   <si>
-    <t xml:space="preserve">17.364128112793</t>
+    <t xml:space="preserve">17.3641242980957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2910976409912</t>
@@ -1874,223 +1874,223 @@
     <t xml:space="preserve">18.6056022644043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3407535552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0593528747559</t>
+    <t xml:space="preserve">18.3407573699951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0593566894531</t>
   </si>
   <si>
     <t xml:space="preserve">17.645528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.248254776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289768218994</t>
+    <t xml:space="preserve">17.2482566833496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">18.07590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1255664825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6620788574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779521942139</t>
+    <t xml:space="preserve">18.1255683898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6620807647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779502868652</t>
   </si>
   <si>
     <t xml:space="preserve">17.9765892028809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2248840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7614002227783</t>
+    <t xml:space="preserve">18.2248859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7613983154297</t>
   </si>
   <si>
     <t xml:space="preserve">16.5861358642578</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6192417144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033721923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101881027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.270170211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.839789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674259185791</t>
+    <t xml:space="preserve">16.6192378997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274234771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2701692581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6742601394653</t>
   </si>
   <si>
     <t xml:space="preserve">15.6177835464478</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0233325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322910308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549802780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.046703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659832000732</t>
+    <t xml:space="preserve">16.0233306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322900772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0632553100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659812927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232374191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3255777359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3426027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.712553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6444396972656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8062076568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5422677993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811687469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5252389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741554260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.201699256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3890132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315843582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2357568740845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0484437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8317527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3208999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020360946655</t>
   </si>
   <si>
     <t xml:space="preserve">14.8232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3255748748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426027297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.712553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6444396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5422677993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811697006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661443710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083814620972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5252389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741544723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2017011642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.389012336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018676757812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315843582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2357559204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0484437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317518234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.55078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.320897102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020380020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232374191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4230690002441</t>
+    <t xml:space="preserve">14.4230699539185</t>
   </si>
   <si>
     <t xml:space="preserve">14.3379278182983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462728500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6908473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930173873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6312484741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948534011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821664810181</t>
+    <t xml:space="preserve">14.3549556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6908464431763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930183410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6312494277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821655273438</t>
   </si>
   <si>
     <t xml:space="preserve">14.3975267410278</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0995292663574</t>
+    <t xml:space="preserve">14.0995302200317</t>
   </si>
   <si>
     <t xml:space="preserve">13.8866739273071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8185606002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6227331161499</t>
+    <t xml:space="preserve">13.8185615539551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6227350234985</t>
   </si>
   <si>
     <t xml:space="preserve">13.5205640792847</t>
@@ -2099,109 +2099,109 @@
     <t xml:space="preserve">13.1799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2140522003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.166802406311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491037368774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7449312210083</t>
+    <t xml:space="preserve">13.1544523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2140512466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1668043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748163223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492712020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491056442261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7449321746826</t>
   </si>
   <si>
     <t xml:space="preserve">11.1706409454346</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0344152450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.162127494812</t>
+    <t xml:space="preserve">10.7534446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0344142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1621284484863</t>
   </si>
   <si>
     <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7875022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7619609832764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471021652222</t>
+    <t xml:space="preserve">10.7875032424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7619600296021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2511072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599565505981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471012115479</t>
   </si>
   <si>
     <t xml:space="preserve">10.6683034896851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7279024124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5367527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6644659042358</t>
+    <t xml:space="preserve">10.7279033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664674758911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.53675365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6644649505615</t>
   </si>
   <si>
     <t xml:space="preserve">11.6900081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7410936355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7496089935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1838331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9028635025024</t>
+    <t xml:space="preserve">11.7410926818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7496070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1838321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9028625488281</t>
   </si>
   <si>
     <t xml:space="preserve">11.8177213668823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476045608521</t>
+    <t xml:space="preserve">11.7751512527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476055145264</t>
   </si>
   <si>
     <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026969909668</t>
+    <t xml:space="preserve">11.5026950836182</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450996398926</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8981885910034</t>
+    <t xml:space="preserve">10.8981876373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898406982422</t>
@@ -2213,22 +2213,22 @@
     <t xml:space="preserve">10.7108745574951</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4724769592285</t>
+    <t xml:space="preserve">10.4724750518799</t>
   </si>
   <si>
     <t xml:space="preserve">10.6597900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0173845291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0855007171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0514440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280708312988</t>
+    <t xml:space="preserve">11.0173854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0854997634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280698776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003576278687</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">11.6985216140747</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6814956665039</t>
+    <t xml:space="preserve">11.6814947128296</t>
   </si>
   <si>
     <t xml:space="preserve">11.8092079162598</t>
@@ -2258,7 +2258,7 @@
     <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5120477676392</t>
+    <t xml:space="preserve">13.5120496749878</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738185882568</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">13.546106338501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4145555496216</t>
+    <t xml:space="preserve">14.4145545959473</t>
   </si>
   <si>
     <t xml:space="preserve">13.8526172637939</t>
@@ -2276,115 +2276,115 @@
     <t xml:space="preserve">14.2187299728394</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8781604766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7759914398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4439344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8441028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4486122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6274108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254064559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043706893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9424343109131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9679756164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870088577271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.019063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467771530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6406002044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.461802482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656391143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3634700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3294124603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4826688766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1506147384644</t>
+    <t xml:space="preserve">13.8781585693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.775990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4439353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8441038131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4486112594604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6274099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.925407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.504373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933542251587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9679794311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170604705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.363471031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3294115066528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4826669692993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.150616645813</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5763254165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1165590286255</t>
+    <t xml:space="preserve">14.5763263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1165571212769</t>
   </si>
   <si>
     <t xml:space="preserve">14.4911832809448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3804979324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721519470215</t>
+    <t xml:space="preserve">14.3804998397827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4996976852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721538543701</t>
   </si>
   <si>
     <t xml:space="preserve">13.7078762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292459487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3162231445312</t>
+    <t xml:space="preserve">13.9292469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5035352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3162240982056</t>
   </si>
   <si>
     <t xml:space="preserve">13.5631341934204</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4060430526733</t>
+    <t xml:space="preserve">13.5375909805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4060401916504</t>
   </si>
   <si>
     <t xml:space="preserve">14.269814491272</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167264938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.176157951355</t>
+    <t xml:space="preserve">14.5167245864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761569976807</t>
   </si>
   <si>
     <t xml:space="preserve">14.1931858062744</t>
@@ -2414,13 +2414,13 @@
     <t xml:space="preserve">12.5584573745728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010293960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9880046844482</t>
+    <t xml:space="preserve">12.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6010284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9880065917969</t>
   </si>
   <si>
     <t xml:space="preserve">11.6218938827515</t>
@@ -2435,79 +2435,79 @@
     <t xml:space="preserve">9.82539653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4252290725708</t>
+    <t xml:space="preserve">9.42522811889648</t>
   </si>
   <si>
     <t xml:space="preserve">9.74025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08424186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7355785369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27155303955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31412506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278743743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11020183563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00803279876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41671562194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47631359100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57848358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225597381592</t>
+    <t xml:space="preserve">8.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73557758331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2715539932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31412601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278886795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11020278930664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00803184509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41671466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47631549835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225788116455</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16980361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53591346740723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48482894897461</t>
+    <t xml:space="preserve">9.09317493438721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16980171203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53591442108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48482799530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.62105560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319074630737</t>
+    <t xml:space="preserve">10.089337348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.131908416748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75728225708008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87648296356201</t>
+    <t xml:space="preserve">9.75728321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.97013759613037</t>
@@ -2519,37 +2519,37 @@
     <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3192205429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4299049377441</t>
+    <t xml:space="preserve">10.3192195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4299068450928</t>
   </si>
   <si>
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961832046509</t>
+    <t xml:space="preserve">11.1961841583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9616231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85945320129395</t>
+    <t xml:space="preserve">9.96162414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85945415496826</t>
   </si>
   <si>
     <t xml:space="preserve">9.78282451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3060302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51037120819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51888656616211</t>
+    <t xml:space="preserve">9.30602931976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51037216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51888561248779</t>
   </si>
   <si>
     <t xml:space="preserve">9.22940254211426</t>
@@ -2567,34 +2567,34 @@
     <t xml:space="preserve">8.86329078674316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93140506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85477638244629</t>
+    <t xml:space="preserve">8.93140316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85477542877197</t>
   </si>
   <si>
     <t xml:space="preserve">9.28048706054688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70619869232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62957000732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.187671661377</t>
+    <t xml:space="preserve">9.70619773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62957096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85093975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5405893325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340793609619</t>
+    <t xml:space="preserve">10.5405902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340774536133</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254215240479</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">9.90270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72789764404297</t>
+    <t xml:space="preserve">9.7278995513916</t>
   </si>
   <si>
     <t xml:space="preserve">9.64049530029297</t>
@@ -2642,37 +2642,37 @@
     <t xml:space="preserve">9.41324901580811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5268726348877</t>
+    <t xml:space="preserve">9.52687168121338</t>
   </si>
   <si>
     <t xml:space="preserve">9.49191093444824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40450859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15978145599365</t>
+    <t xml:space="preserve">9.40450954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15978050231934</t>
   </si>
   <si>
     <t xml:space="preserve">8.99371719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01993656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90631294250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57931423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18600273132324</t>
+    <t xml:space="preserve">9.01993751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90631484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57931518554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36080837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18600368499756</t>
   </si>
   <si>
     <t xml:space="preserve">9.33458709716797</t>
@@ -2687,10 +2687,10 @@
     <t xml:space="preserve">9.29088592529297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01119709014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3484563827515</t>
+    <t xml:space="preserve">9.01119804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3484554290771</t>
   </si>
   <si>
     <t xml:space="preserve">10.4358577728271</t>
@@ -2705,67 +2705,67 @@
     <t xml:space="preserve">11.1001167297363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3186235427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4672079086304</t>
+    <t xml:space="preserve">11.3186225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4672069549561</t>
   </si>
   <si>
     <t xml:space="preserve">11.0826377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8903522491455</t>
+    <t xml:space="preserve">10.8903503417969</t>
   </si>
   <si>
     <t xml:space="preserve">10.7942085266113</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6281433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5494823455811</t>
+    <t xml:space="preserve">10.6281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5494813919067</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299505233765</t>
+    <t xml:space="preserve">10.2260932922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299486160278</t>
   </si>
   <si>
     <t xml:space="preserve">9.98136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93766403198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.094988822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250673294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95514488220215</t>
+    <t xml:space="preserve">9.93766498565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0949878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1124696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250663757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95514583587646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78033924102783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75411891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65797519683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74537754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.99884510040283</t>
+    <t xml:space="preserve">9.75411796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6579761505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7453784942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.99884605407715</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222360610962</t>
@@ -2777,7 +2777,7 @@
     <t xml:space="preserve">10.7505073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4620780944824</t>
+    <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
@@ -2786,43 +2786,43 @@
     <t xml:space="preserve">10.3834171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3659353256226</t>
+    <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
     <t xml:space="preserve">10.4970407485962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6893243789673</t>
+    <t xml:space="preserve">10.6893253326416</t>
   </si>
   <si>
     <t xml:space="preserve">10.6106643676758</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4795589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5757026672363</t>
+    <t xml:space="preserve">10.4795598983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5757036209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5582218170166</t>
+    <t xml:space="preserve">10.5232601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5582208633423</t>
   </si>
   <si>
     <t xml:space="preserve">10.4708185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81530094146729</t>
+    <t xml:space="preserve">9.81529903411865</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99010562896729</t>
+    <t xml:space="preserve">9.9901065826416</t>
   </si>
   <si>
     <t xml:space="preserve">9.82404041290283</t>
@@ -2831,7 +2831,7 @@
     <t xml:space="preserve">9.86774253845215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6142749786377</t>
+    <t xml:space="preserve">9.61427593231201</t>
   </si>
   <si>
     <t xml:space="preserve">9.00245761871338</t>
@@ -2843,7 +2843,7 @@
     <t xml:space="preserve">8.36878967285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5348539352417</t>
+    <t xml:space="preserve">8.53485488891602</t>
   </si>
   <si>
     <t xml:space="preserve">8.64410781860352</t>
@@ -2852,13 +2852,13 @@
     <t xml:space="preserve">9.1248197555542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16852188110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883495330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98497581481934</t>
+    <t xml:space="preserve">9.1685209274292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98497676849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">9.69293785095215</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9078302383423</t>
+    <t xml:space="preserve">10.9078311920166</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350774765015</t>
@@ -2876,31 +2876,31 @@
     <t xml:space="preserve">11.6070508956909</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3324918746948</t>
+    <t xml:space="preserve">12.3324928283691</t>
   </si>
   <si>
     <t xml:space="preserve">12.3587131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5597381591797</t>
+    <t xml:space="preserve">12.559739112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.886739730835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4810762405396</t>
+    <t xml:space="preserve">12.4810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">12.19264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139860153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2101306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857137680054</t>
+    <t xml:space="preserve">12.1139869689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.210129737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857147216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.0702857971191</t>
@@ -2909,31 +2909,31 @@
     <t xml:space="preserve">11.974142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916219711304</t>
+    <t xml:space="preserve">11.9916229248047</t>
   </si>
   <si>
     <t xml:space="preserve">11.947922706604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0615453720093</t>
+    <t xml:space="preserve">12.061544418335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1314668655396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0440645217896</t>
+    <t xml:space="preserve">12.0440626144409</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954792022705</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0091037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0178451538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6558828353882</t>
+    <t xml:space="preserve">12.0091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6558818817139</t>
   </si>
   <si>
     <t xml:space="preserve">12.6733617782593</t>
@@ -2942,40 +2942,40 @@
     <t xml:space="preserve">12.4898176193237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4198951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684785842896</t>
+    <t xml:space="preserve">12.4198942184448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684795379639</t>
   </si>
   <si>
     <t xml:space="preserve">12.5422592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7782459259033</t>
+    <t xml:space="preserve">12.778244972229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2363500595093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4461154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.516037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5509996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2713117599487</t>
+    <t xml:space="preserve">12.4461164474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5509986877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132066726685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8394260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9093503952026</t>
+    <t xml:space="preserve">12.8394269943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9093494415283</t>
   </si>
   <si>
     <t xml:space="preserve">12.821946144104</t>
@@ -2984,13 +2984,13 @@
     <t xml:space="preserve">12.9880113601685</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0229721069336</t>
+    <t xml:space="preserve">13.0229730606079</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2152576446533</t>
+    <t xml:space="preserve">13.215256690979</t>
   </si>
   <si>
     <t xml:space="preserve">13.2502193450928</t>
@@ -3002,10 +3002,10 @@
     <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.953049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9792709350586</t>
+    <t xml:space="preserve">12.9530506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9792718887329</t>
   </si>
   <si>
     <t xml:space="preserve">12.9355697631836</t>
@@ -3020,52 +3020,52 @@
     <t xml:space="preserve">13.1890382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2239990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.800853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0280990600586</t>
+    <t xml:space="preserve">13.2239980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8008546829224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0281009674072</t>
   </si>
   <si>
     <t xml:space="preserve">14.1067628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.395191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.500075340271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5612564086914</t>
+    <t xml:space="preserve">14.3951902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5000743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5612573623657</t>
   </si>
   <si>
     <t xml:space="preserve">14.2116460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7484121322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980234146118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7221927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3864507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6661405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7098407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6224384307861</t>
+    <t xml:space="preserve">13.7484130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3864517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6661396026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7098398208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6224374771118</t>
   </si>
   <si>
     <t xml:space="preserve">15.0157480239868</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">15.3653602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1206302642822</t>
+    <t xml:space="preserve">15.1206312179565</t>
   </si>
   <si>
     <t xml:space="preserve">14.456374168396</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">14.6136980056763</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7622804641724</t>
+    <t xml:space="preserve">14.762282371521</t>
   </si>
   <si>
     <t xml:space="preserve">16.3442668914795</t>
@@ -3101,13 +3101,13 @@
     <t xml:space="preserve">15.8373327255249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9159936904907</t>
+    <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9422159194946</t>
+    <t xml:space="preserve">15.9422149658203</t>
   </si>
   <si>
     <t xml:space="preserve">16.13450050354</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">15.43528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440212249756</t>
+    <t xml:space="preserve">15.5663843154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3566198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440231323242</t>
   </si>
   <si>
     <t xml:space="preserve">15.330397605896</t>
@@ -3131,25 +3131,25 @@
     <t xml:space="preserve">15.2429971694946</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2255153656006</t>
+    <t xml:space="preserve">15.2255163192749</t>
   </si>
   <si>
     <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779569625854</t>
+    <t xml:space="preserve">15.2779560089111</t>
   </si>
   <si>
     <t xml:space="preserve">15.2517366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0681896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.138111114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265403747559</t>
+    <t xml:space="preserve">15.0681915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265413284302</t>
   </si>
   <si>
     <t xml:space="preserve">15.0244903564453</t>
@@ -3158,13 +3158,13 @@
     <t xml:space="preserve">14.8933868408203</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234624862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0856704711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9196071624756</t>
+    <t xml:space="preserve">14.8234615325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.08567237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9196081161499</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
@@ -3173,25 +3173,25 @@
     <t xml:space="preserve">14.937087059021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1468524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.849684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.304178237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4214124679565</t>
+    <t xml:space="preserve">15.1468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8496856689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2604742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3041772842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409433364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4214115142822</t>
   </si>
   <si>
     <t xml:space="preserve">14.5962181091309</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">16.7812805175781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4367961883545</t>
+    <t xml:space="preserve">17.4368000030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.4630184173584</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048980712891</t>
+    <t xml:space="preserve">18.5048999786377</t>
   </si>
   <si>
     <t xml:space="preserve">18.7340068817139</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">18.4696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573741912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8221263885498</t>
+    <t xml:space="preserve">18.8573722839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8221244812012</t>
   </si>
   <si>
     <t xml:space="preserve">19.3684597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.96311378479</t>
+    <t xml:space="preserve">18.9631156921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.1217308044434</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">19.0688571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9807395935059</t>
+    <t xml:space="preserve">18.9807415008545</t>
   </si>
   <si>
     <t xml:space="preserve">18.8749961853027</t>
@@ -3254,22 +3254,22 @@
     <t xml:space="preserve">18.2052955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6987590789795</t>
+    <t xml:space="preserve">18.6987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2405433654785</t>
+    <t xml:space="preserve">18.2405452728271</t>
   </si>
   <si>
     <t xml:space="preserve">18.7163829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2934131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2581672668457</t>
+    <t xml:space="preserve">18.2934150695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2581691741943</t>
   </si>
   <si>
     <t xml:space="preserve">18.1524257659912</t>
@@ -3278,13 +3278,13 @@
     <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8175754547119</t>
+    <t xml:space="preserve">17.8175735473633</t>
   </si>
   <si>
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.888069152832</t>
+    <t xml:space="preserve">17.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
@@ -3293,7 +3293,7 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708427429199</t>
+    <t xml:space="preserve">17.5708446502686</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589603424072</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">17.3681678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478729248047</t>
+    <t xml:space="preserve">17.1478710174561</t>
   </si>
   <si>
     <t xml:space="preserve">17.4650993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9761867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8351974487305</t>
+    <t xml:space="preserve">17.976188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8352012634277</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
@@ -3323,19 +3323,19 @@
     <t xml:space="preserve">17.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.125696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5222301483154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6367855072021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3857936859131</t>
+    <t xml:space="preserve">16.3724308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1256980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5222320556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6367874145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3857917785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.2448024749756</t>
@@ -3347,19 +3347,19 @@
     <t xml:space="preserve">17.4122276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7823257446289</t>
+    <t xml:space="preserve">17.7823276519775</t>
   </si>
   <si>
     <t xml:space="preserve">17.7470779418945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5355949401855</t>
+    <t xml:space="preserve">17.5355930328369</t>
   </si>
   <si>
     <t xml:space="preserve">17.6237144470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747062683105</t>
+    <t xml:space="preserve">16.8747043609619</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861892700195</t>
@@ -3368,7 +3368,7 @@
     <t xml:space="preserve">17.1743087768555</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3417339324951</t>
+    <t xml:space="preserve">17.3417358398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3380,37 +3380,37 @@
     <t xml:space="preserve">17.3593597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9716377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249050140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6720333099365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4869823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8042125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2183704376221</t>
+    <t xml:space="preserve">16.9716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249031066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6720314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4869842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.676586151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5796527862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5972785949707</t>
+    <t xml:space="preserve">17.6765823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5796546936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5972766876221</t>
   </si>
   <si>
     <t xml:space="preserve">17.2888641357422</t>
@@ -3419,10 +3419,10 @@
     <t xml:space="preserve">17.0421314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425289154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5927276611328</t>
+    <t xml:space="preserve">16.7425270080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
     <t xml:space="preserve">16.4957962036133</t>
@@ -3434,13 +3434,13 @@
     <t xml:space="preserve">16.3900547027588</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3019371032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9935188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8613414764404</t>
+    <t xml:space="preserve">16.3019351959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9935207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8613433837891</t>
   </si>
   <si>
     <t xml:space="preserve">16.2402534484863</t>
@@ -3452,46 +3452,46 @@
     <t xml:space="preserve">16.31955909729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7732238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176782608032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119358062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3590679168701</t>
+    <t xml:space="preserve">15.7732248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176801681519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.411937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3590669631958</t>
   </si>
   <si>
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154047012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2180757522583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1828298568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0242166519165</t>
+    <t xml:space="preserve">15.3150062561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2180767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1828308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
     <t xml:space="preserve">15.1123342514038</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1035223007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4912452697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1475820541382</t>
+    <t xml:space="preserve">15.1035213470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4912443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1475830078125</t>
   </si>
   <si>
     <t xml:space="preserve">15.0858993530273</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">14.9801568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8215417861938</t>
+    <t xml:space="preserve">14.8215427398682</t>
   </si>
   <si>
     <t xml:space="preserve">14.6188707351685</t>
@@ -3515,25 +3515,25 @@
     <t xml:space="preserve">14.0725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8434267044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8962984085083</t>
+    <t xml:space="preserve">13.8434276580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.896297454834</t>
   </si>
   <si>
     <t xml:space="preserve">14.1959018707275</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2840194702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3104543685913</t>
+    <t xml:space="preserve">14.2840185165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3104553222656</t>
   </si>
   <si>
     <t xml:space="preserve">14.345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9491701126099</t>
+    <t xml:space="preserve">13.9491691589355</t>
   </si>
   <si>
     <t xml:space="preserve">16.1080741882324</t>
@@ -3545,19 +3545,19 @@
     <t xml:space="preserve">14.4778804779053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254072189331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0637245178223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8169918060303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6055068969727</t>
+    <t xml:space="preserve">14.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0637235641479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.816990852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.7729320526123</t>
@@ -3575,13 +3575,13 @@
     <t xml:space="preserve">13.4028348922729</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1296672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9446172714233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852090835571</t>
+    <t xml:space="preserve">13.1296663284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.944616317749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
     <t xml:space="preserve">13.6583776473999</t>
@@ -3593,10 +3593,10 @@
     <t xml:space="preserve">13.561448097229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2265968322754</t>
+    <t xml:space="preserve">13.1913499832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2265977859497</t>
   </si>
   <si>
     <t xml:space="preserve">13.6231307983398</t>
@@ -3614,10 +3614,10 @@
     <t xml:space="preserve">13.438081741333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4645175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4997634887695</t>
+    <t xml:space="preserve">13.4645166397095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4997644424438</t>
   </si>
   <si>
     <t xml:space="preserve">13.4821405410767</t>
@@ -3635,43 +3635,43 @@
     <t xml:space="preserve">13.4468936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649131774902</t>
+    <t xml:space="preserve">13.1649141311646</t>
   </si>
   <si>
     <t xml:space="preserve">12.8388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9710540771484</t>
+    <t xml:space="preserve">12.9710531234741</t>
   </si>
   <si>
     <t xml:space="preserve">12.7948169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6978855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6890735626221</t>
+    <t xml:space="preserve">12.69788646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6890745162964</t>
   </si>
   <si>
     <t xml:space="preserve">12.5128364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5568952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273918151855</t>
+    <t xml:space="preserve">12.5568962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492748260498</t>
+    <t xml:space="preserve">11.6492738723755</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078880310059</t>
+    <t xml:space="preserve">11.8078870773315</t>
   </si>
   <si>
     <t xml:space="preserve">11.9048185348511</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">11.8431358337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1427383422852</t>
+    <t xml:space="preserve">12.1427373886108</t>
   </si>
   <si>
     <t xml:space="preserve">11.9841260910034</t>
@@ -3689,13 +3689,13 @@
     <t xml:space="preserve">11.5347194671631</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4642267227173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1117515563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9090785980225</t>
+    <t xml:space="preserve">11.464225769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1117506027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9090795516968</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263050079346</t>
@@ -3704,28 +3704,28 @@
     <t xml:space="preserve">11.1293754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0412549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209600448608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.803337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1910591125488</t>
+    <t xml:space="preserve">11.0412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033380508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1910572052002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3937311172485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1822462081909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.961950302124</t>
+    <t xml:space="preserve">11.1822452545166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9619493484497</t>
   </si>
   <si>
     <t xml:space="preserve">10.9355134963989</t>
@@ -3746,46 +3746,46 @@
     <t xml:space="preserve">10.2393770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710155487061</t>
+    <t xml:space="preserve">9.73710250854492</t>
   </si>
   <si>
     <t xml:space="preserve">9.54324054718018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56967735290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85165500640869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42868709564209</t>
+    <t xml:space="preserve">9.56967639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0455160140991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85165596008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42868614196777</t>
   </si>
   <si>
     <t xml:space="preserve">9.61373615264893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64883613586426</t>
+    <t xml:space="preserve">8.64883708953857</t>
   </si>
   <si>
     <t xml:space="preserve">9.01452922821045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89116287231445</t>
+    <t xml:space="preserve">8.89116382598877</t>
   </si>
   <si>
     <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977703094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83829307556152</t>
+    <t xml:space="preserve">9.25244998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977607727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83829116821289</t>
   </si>
   <si>
     <t xml:space="preserve">8.70611381530762</t>
@@ -3806,19 +3806,19 @@
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27874088287354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24349117279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43735313415527</t>
+    <t xml:space="preserve">8.27873992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24349212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43735218048096</t>
   </si>
   <si>
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433300018311</t>
+    <t xml:space="preserve">8.27433395385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3827,10 +3827,10 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245250701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31398677825928</t>
+    <t xml:space="preserve">8.36245155334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31398773193359</t>
   </si>
   <si>
     <t xml:space="preserve">8.4241361618042</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">8.08487796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01879024505615</t>
+    <t xml:space="preserve">8.01878929138184</t>
   </si>
   <si>
     <t xml:space="preserve">8.20824432373047</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88661193847656</t>
+    <t xml:space="preserve">7.88661241531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
@@ -3860,34 +3860,34 @@
     <t xml:space="preserve">8.02760124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.895423412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93067073822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819747924805</t>
+    <t xml:space="preserve">7.89542293548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93067169189453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80730438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819700241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190910339355</t>
+    <t xml:space="preserve">7.6619086265564</t>
   </si>
   <si>
     <t xml:space="preserve">7.78527545928955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6751275062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95803880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62036943435669</t>
+    <t xml:space="preserve">7.67512702941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62036991119385</t>
   </si>
   <si>
     <t xml:space="preserve">8.03561115264893</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124256134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92609739303589</t>
+    <t xml:space="preserve">8.08124160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92609834671021</t>
   </si>
   <si>
     <t xml:space="preserve">7.89871835708618</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">7.6477484703064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570886611938</t>
+    <t xml:space="preserve">7.82570934295654</t>
   </si>
   <si>
     <t xml:space="preserve">7.67968988418579</t>
@@ -3920,22 +3920,22 @@
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736042022705</t>
+    <t xml:space="preserve">7.54736089706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96784687042236</t>
+    <t xml:space="preserve">6.96784734725952</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04085636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85833311080933</t>
+    <t xml:space="preserve">7.04085683822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85833263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">6.90396356582642</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444932937622</t>
+    <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212102890015</t>
+    <t xml:space="preserve">6.19212055206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3980,16 +3980,16 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260515213013</t>
+    <t xml:space="preserve">6.53891611099243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260562896729</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26056718826294</t>
+    <t xml:space="preserve">6.2605676651001</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -3998,49 +3998,49 @@
     <t xml:space="preserve">6.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29250955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51153755187988</t>
+    <t xml:space="preserve">6.29250907897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
     <t xml:space="preserve">6.46134328842163</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63474082946777</t>
+    <t xml:space="preserve">6.63474130630493</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454704284668</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173133850098</t>
+    <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64843082427979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80813884735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92677974700928</t>
+    <t xml:space="preserve">6.64843034744263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80813932418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92677927017212</t>
   </si>
   <si>
     <t xml:space="preserve">6.83551740646362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81726503372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40590476989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36027336120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17318677902222</t>
+    <t xml:space="preserve">6.81726455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40590381622314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3602728843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17318630218506</t>
   </si>
   <si>
     <t xml:space="preserve">7.19143915176392</t>
@@ -4049,19 +4049,19 @@
     <t xml:space="preserve">6.94046831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02260398864746</t>
+    <t xml:space="preserve">7.02260446548462</t>
   </si>
   <si>
     <t xml:space="preserve">7.01347827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99978923797607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82182836532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18231248855591</t>
+    <t xml:space="preserve">6.99978876113892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82182788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18231296539307</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4079,34 +4079,34 @@
     <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35046577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21357154846191</t>
+    <t xml:space="preserve">8.35046482086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21357250213623</t>
   </si>
   <si>
     <t xml:space="preserve">7.90784454345703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81658220291138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03104877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89415597915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49260282516479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37396240234375</t>
+    <t xml:space="preserve">7.81658267974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03104972839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89415502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49260330200195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37396287918091</t>
   </si>
   <si>
     <t xml:space="preserve">7.25532197952271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34658432006836</t>
+    <t xml:space="preserve">7.3465838432312</t>
   </si>
   <si>
     <t xml:space="preserve">7.52910757064819</t>
@@ -4121,25 +4121,25 @@
     <t xml:space="preserve">6.48415899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70775032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21037340164185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27425718307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0506649017334</t>
+    <t xml:space="preserve">6.70775079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21037292480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05066537857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73581123352051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95940351486206</t>
+    <t xml:space="preserve">5.73581171035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">6.25144100189209</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">6.34270286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39289712905884</t>
+    <t xml:space="preserve">6.392897605896</t>
   </si>
   <si>
     <t xml:space="preserve">6.28794574737549</t>
@@ -4160,55 +4160,55 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27881956100464</t>
+    <t xml:space="preserve">6.2788200378418</t>
   </si>
   <si>
     <t xml:space="preserve">6.32445049285889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39746046066284</t>
+    <t xml:space="preserve">6.39745998382568</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54347896575928</t>
+    <t xml:space="preserve">6.54347944259644</t>
   </si>
   <si>
     <t xml:space="preserve">6.57085752487183</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47959566116333</t>
+    <t xml:space="preserve">6.47959613800049</t>
   </si>
   <si>
     <t xml:space="preserve">6.51610040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65755653381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79901266098022</t>
+    <t xml:space="preserve">6.65755701065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02716732025146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84008073806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57542133331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68949794769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83095407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94959449768066</t>
+    <t xml:space="preserve">7.02716684341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84008026123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57542085647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68949842453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83095455169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94959497451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4217,13 +4217,13 @@
     <t xml:space="preserve">7.10017728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2872633934021</t>
+    <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
     <t xml:space="preserve">7.93978595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17706680297852</t>
+    <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
     <t xml:space="preserve">8.12230968475342</t>
@@ -4232,25 +4232,25 @@
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794273376465</t>
+    <t xml:space="preserve">7.69794321060181</t>
   </si>
   <si>
     <t xml:space="preserve">7.76638889312744</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72988414764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66600036621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77095222473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7116322517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91697120666504</t>
+    <t xml:space="preserve">7.7298846244812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6660008430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7709527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71163177490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91697072982788</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">7.72075796127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57017612457275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62949562072754</t>
+    <t xml:space="preserve">7.5701756477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62949514389038</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
@@ -4271,16 +4271,16 @@
     <t xml:space="preserve">7.5519232749939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31464242935181</t>
+    <t xml:space="preserve">7.31464290618896</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17774963378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04998302459717</t>
+    <t xml:space="preserve">7.1777491569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04998254776001</t>
   </si>
   <si>
     <t xml:space="preserve">7.35571050643921</t>
@@ -4289,43 +4289,43 @@
     <t xml:space="preserve">7.27813768386841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51998138427734</t>
+    <t xml:space="preserve">7.5199818611145</t>
   </si>
   <si>
     <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46978807449341</t>
+    <t xml:space="preserve">7.46978759765625</t>
   </si>
   <si>
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376745223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959264755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38697052001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34590244293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36871719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8159008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94366836547852</t>
+    <t xml:space="preserve">7.79376792907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959360122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38696956634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34590339660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36871814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81589984893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9436674118042</t>
   </si>
   <si>
     <t xml:space="preserve">8.68813514709473</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66531944274902</t>
+    <t xml:space="preserve">8.66531848907471</t>
   </si>
   <si>
     <t xml:space="preserve">8.82959079742432</t>
@@ -4334,16 +4334,16 @@
     <t xml:space="preserve">8.80677509307861</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98017311096191</t>
+    <t xml:space="preserve">8.9801721572876</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84327983856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347267150879</t>
+    <t xml:space="preserve">8.8432788848877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347457885742</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">8.7292013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7109489440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72463989257812</t>
+    <t xml:space="preserve">8.71094989776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72463893890381</t>
   </si>
   <si>
     <t xml:space="preserve">8.51473712921143</t>
@@ -4364,7 +4364,7 @@
     <t xml:space="preserve">8.41891193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40978622436523</t>
+    <t xml:space="preserve">8.40978527069092</t>
   </si>
   <si>
     <t xml:space="preserve">8.44172668457031</t>
@@ -4373,76 +4373,76 @@
     <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21813488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25007629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24551486968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949588775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00366973876953</t>
+    <t xml:space="preserve">8.21813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949493408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00367069244385</t>
   </si>
   <si>
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483505249023</t>
+    <t xml:space="preserve">7.83483552932739</t>
   </si>
   <si>
     <t xml:space="preserve">7.6888165473938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51085567474365</t>
+    <t xml:space="preserve">7.51085519790649</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05386352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97172880172729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92153406143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017448425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580493927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.15425300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96716547012329</t>
+    <t xml:space="preserve">8.05386447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97172784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9215350151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04017543792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09493160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.15425205230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96328449249268</t>
+    <t xml:space="preserve">6.96328401565552</t>
   </si>
   <si>
     <t xml:space="preserve">7.3283314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2142539024353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35114717483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24163293838501</t>
+    <t xml:space="preserve">7.21425437927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35114765167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24163246154785</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842966079712</t>
@@ -4451,16 +4451,16 @@
     <t xml:space="preserve">7.01804161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00435161590576</t>
+    <t xml:space="preserve">7.00435209274292</t>
   </si>
   <si>
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745882034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13211822509766</t>
+    <t xml:space="preserve">6.86745929718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13211870193481</t>
   </si>
   <si>
     <t xml:space="preserve">6.88114833831787</t>
@@ -4490,16 +4490,16 @@
     <t xml:space="preserve">6.62561511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62105178833008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43852806091309</t>
+    <t xml:space="preserve">6.62105226516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43852758407593</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30619812011719</t>
+    <t xml:space="preserve">6.30619859695435</t>
   </si>
   <si>
     <t xml:space="preserve">6.42027568817139</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50607013702393</t>
+    <t xml:space="preserve">6.50606966018677</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4535,28 +4535,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67765855789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812610626221</t>
+    <t xml:space="preserve">6.677659034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812562942505</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550897598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8635458946228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924745559692</t>
+    <t xml:space="preserve">6.92550849914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86354637145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924697875977</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61569595336914</t>
+    <t xml:space="preserve">6.6156964302063</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4571,19 +4571,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887399673462</t>
+    <t xml:space="preserve">6.44887351989746</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279920578003</t>
+    <t xml:space="preserve">6.57279872894287</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541538238525</t>
+    <t xml:space="preserve">6.31541585922241</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214445114136</t>
+    <t xml:space="preserve">6.38214492797852</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915386199951</t>
+    <t xml:space="preserve">6.23915433883667</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4637,22 +4637,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74821996688843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78635120391846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167810440063</t>
+    <t xml:space="preserve">5.60999631881714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74822044372559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7863507270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167762756348</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803251266479</t>
+    <t xml:space="preserve">6.05803298950195</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4661,13 +4661,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878040313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401441574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597702026367</t>
+    <t xml:space="preserve">5.83878087997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401393890381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597654342651</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4676,7 +4676,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653793334961</t>
+    <t xml:space="preserve">5.98653745651245</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4685,13 +4685,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2629861831665</t>
+    <t xml:space="preserve">6.26298570632935</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728462219238</t>
+    <t xml:space="preserve">6.27728509902954</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4712,10 +4712,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71485567092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532274246216</t>
+    <t xml:space="preserve">5.7148551940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532321929932</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859415054321</t>
+    <t xml:space="preserve">5.63859367370605</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4742,16 +4742,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625736236572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77205181121826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476182937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7815842628479</t>
+    <t xml:space="preserve">5.68625783920288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7720513343811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476230621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78158473968506</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4763,10 +4763,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887449264526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541683197021</t>
+    <t xml:space="preserve">5.42887496948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541635513306</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4778,16 +4778,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1810245513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943517684937</t>
+    <t xml:space="preserve">5.18102407455444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943565368652</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812685012817</t>
+    <t xml:space="preserve">5.13812732696533</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4802,19 +4802,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336013793945</t>
+    <t xml:space="preserve">5.64336061477661</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7196216583252</t>
+    <t xml:space="preserve">5.71962213516235</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027666091919</t>
+    <t xml:space="preserve">5.40027618408203</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4829,13 +4829,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569644927979</t>
+    <t xml:space="preserve">5.59569692611694</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775289535522</t>
+    <t xml:space="preserve">5.75775241851807</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569620132446</t>
+    <t xml:space="preserve">6.10569667816162</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4853,7 +4853,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382696151733</t>
+    <t xml:space="preserve">6.14382743835449</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4865,61 +4865,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868679046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635000228882</t>
+    <t xml:space="preserve">6.24868631362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635047912598</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074323654175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46793937683105</t>
+    <t xml:space="preserve">6.41074275970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4679388999939</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896713256836</t>
+    <t xml:space="preserve">6.03896760940552</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177099227905</t>
+    <t xml:space="preserve">5.98177146911621</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8530797958374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644409179688</t>
+    <t xml:space="preserve">5.85307931900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644456863403</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420114517212</t>
+    <t xml:space="preserve">6.03420066833496</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541658401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7911171913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728534698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77681827545166</t>
+    <t xml:space="preserve">5.80541610717773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79111671447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728582382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7768177986145</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4931,28 +4931,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850030899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952877044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186508178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69579029083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.51943492889404</t>
+    <t xml:space="preserve">5.53850078582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952829360962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186460494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69578981399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5194354057312</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560356140137</t>
+    <t xml:space="preserve">5.49560308456421</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4967,7 +4967,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410827636719</t>
+    <t xml:space="preserve">4.91410875320435</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4976,22 +4976,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354759216309</t>
+    <t xml:space="preserve">5.33354711532593</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691188812256</t>
+    <t xml:space="preserve">5.36691236495972</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457509994507</t>
+    <t xml:space="preserve">5.67195844650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457557678223</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5015,7 +5015,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438837051392</t>
+    <t xml:space="preserve">5.21438884735107</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5027,7 +5027,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4431734085083</t>
+    <t xml:space="preserve">5.44317388534546</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5042,16 +5042,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027593612671</t>
+    <t xml:space="preserve">5.56709909439087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027545928955</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8626127243042</t>
+    <t xml:space="preserve">5.86261224746704</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -71158,7 +71158,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6911342593</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>83203</v>
@@ -71179,6 +71179,32 @@
         <v>1874</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6912268518</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>131160</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>4.51000022888184</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>4.43499994277954</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>4.44500017166138</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>4.48000001907349</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1876</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1916">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608804702759</t>
+    <t xml:space="preserve">12.7608823776245</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.784628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767133712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758987426758</t>
+    <t xml:space="preserve">12.7846279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767114639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758977890015</t>
   </si>
   <si>
     <t xml:space="preserve">11.9930114746094</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8742694854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.270076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233964920044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746160507202</t>
+    <t xml:space="preserve">11.8742685317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700757980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746170043945</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075626373291</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4125690460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6738014221191</t>
+    <t xml:space="preserve">12.4125680923462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6738042831421</t>
   </si>
   <si>
     <t xml:space="preserve">12.0563411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3729877471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.175085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909141540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713594436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367835998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9850959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955749511719</t>
+    <t xml:space="preserve">12.372989654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1750841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413219451904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9850940704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955739974976</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626274108887</t>
@@ -116,37 +116,37 @@
     <t xml:space="preserve">11.4942922592163</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5417909622192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3597164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346881866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763639450073</t>
+    <t xml:space="preserve">11.5417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3597183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8584356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159471511841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346872329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.676362991333</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3992986679077</t>
+    <t xml:space="preserve">11.3992967605591</t>
   </si>
   <si>
     <t xml:space="preserve">11.1855611801147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9692640304565</t>
+    <t xml:space="preserve">11.9692630767822</t>
   </si>
   <si>
     <t xml:space="preserve">12.388819694519</t>
@@ -158,37 +158,37 @@
     <t xml:space="preserve">12.2304964065552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1117553710938</t>
+    <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
     <t xml:space="preserve">12.1513366699219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9825344085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950870513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575052261353</t>
+    <t xml:space="preserve">12.1196699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242111206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508714675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575033187866</t>
   </si>
   <si>
     <t xml:space="preserve">13.5762462615967</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">13.5999965667725</t>
   </si>
   <si>
-    <t xml:space="preserve">13.362509727478</t>
+    <t xml:space="preserve">13.3625087738037</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379476547241</t>
@@ -206,67 +206,67 @@
     <t xml:space="preserve">12.752965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1171102523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091918945312</t>
+    <t xml:space="preserve">13.1171092987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091938018799</t>
   </si>
   <si>
     <t xml:space="preserve">13.1962699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9904489517212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221157073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.602557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6500549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8637914657593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679832458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091585159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.988468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241008758545</t>
+    <t xml:space="preserve">12.9904508590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221176147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975526809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6025562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6500539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8637924194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.586724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.467981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788087844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091594696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241018295288</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218017578125</t>
@@ -275,82 +275,82 @@
     <t xml:space="preserve">12.2298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620306015015</t>
+    <t xml:space="preserve">12.2942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620315551758</t>
   </si>
   <si>
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953651428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126035690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.809154510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735237121582</t>
+    <t xml:space="preserve">12.4953632354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735227584839</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252487182617</t>
+    <t xml:space="preserve">12.8252468109131</t>
   </si>
   <si>
     <t xml:space="preserve">12.865478515625</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172006607056</t>
+    <t xml:space="preserve">12.8172025680542</t>
   </si>
   <si>
     <t xml:space="preserve">12.5999622344971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103084564209</t>
+    <t xml:space="preserve">12.3666286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103094100952</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390451431274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4011154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884721755981</t>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
     <t xml:space="preserve">10.8781280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0792779922485</t>
+    <t xml:space="preserve">11.0792770385742</t>
   </si>
   <si>
     <t xml:space="preserve">11.6022624969482</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0689296722412</t>
+    <t xml:space="preserve">12.0689277648926</t>
   </si>
   <si>
     <t xml:space="preserve">11.6103105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3689298629761</t>
+    <t xml:space="preserve">11.368932723999</t>
   </si>
   <si>
     <t xml:space="preserve">11.4896202087402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7574396133423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735330581665</t>
+    <t xml:space="preserve">10.757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.45973777771</t>
@@ -359,37 +359,37 @@
     <t xml:space="preserve">11.0229539871216</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6424922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6344480514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.92640209198</t>
+    <t xml:space="preserve">11.6424942016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6344470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321500778198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.982723236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264039993286</t>
   </si>
   <si>
     <t xml:space="preserve">11.2160577774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7229528427124</t>
+    <t xml:space="preserve">11.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700788497925</t>
+    <t xml:space="preserve">11.5700807571411</t>
   </si>
   <si>
     <t xml:space="preserve">11.8919172286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861721038818</t>
+    <t xml:space="preserve">11.5861711502075</t>
   </si>
   <si>
     <t xml:space="preserve">11.875825881958</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">12.1896171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309968948364</t>
+    <t xml:space="preserve">12.4309959411621</t>
   </si>
   <si>
     <t xml:space="preserve">12.8896169662476</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">13.1229476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861679077148</t>
+    <t xml:space="preserve">13.1551332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861660003662</t>
   </si>
   <si>
     <t xml:space="preserve">13.0746736526489</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3482341766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2493801116943</t>
+    <t xml:space="preserve">13.3482351303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493829727173</t>
   </si>
   <si>
     <t xml:space="preserve">13.9194965362549</t>
@@ -437,88 +437,88 @@
     <t xml:space="preserve">14.3459348678589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8551292419434</t>
+    <t xml:space="preserve">13.8551301956177</t>
   </si>
   <si>
     <t xml:space="preserve">14.1608772277832</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6919078826904</t>
+    <t xml:space="preserve">14.6919097900391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7643232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6275434494019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206453323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034069061279</t>
+    <t xml:space="preserve">14.6275424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206472396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.603404045105</t>
   </si>
   <si>
     <t xml:space="preserve">14.4022560119629</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3137493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516780853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1263885498047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0861625671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0459337234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2953548431396</t>
+    <t xml:space="preserve">14.3137483596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516790390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183462142944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505279541016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1263904571533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0861616134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0459327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.295355796814</t>
   </si>
   <si>
     <t xml:space="preserve">15.424090385437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4562730789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597230911255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873096466064</t>
+    <t xml:space="preserve">15.4562740325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873086929321</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689193725586</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7240934371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367395401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7884588241577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930587768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4884605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401836395264</t>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884569168091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930568695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4884567260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401845932007</t>
   </si>
   <si>
     <t xml:space="preserve">15.2148971557617</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">14.8045530319214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3919067382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.255126953125</t>
+    <t xml:space="preserve">15.3919086456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2551240921021</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666212081909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286884307861</t>
+    <t xml:space="preserve">15.5286874771118</t>
   </si>
   <si>
     <t xml:space="preserve">15.2229433059692</t>
@@ -545,91 +545,91 @@
     <t xml:space="preserve">15.013747215271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8850116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275365829468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114461898804</t>
+    <t xml:space="preserve">14.8850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198805809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114500045776</t>
   </si>
   <si>
     <t xml:space="preserve">15.3677701950073</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3034038543701</t>
+    <t xml:space="preserve">15.3034029006958</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827125549316</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6436347961426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470808029175</t>
+    <t xml:space="preserve">14.6436357498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470798492432</t>
   </si>
   <si>
     <t xml:space="preserve">14.8286905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5390367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551280975342</t>
+    <t xml:space="preserve">14.5390348434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551271438599</t>
   </si>
   <si>
     <t xml:space="preserve">14.1126022338867</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4263916015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.281566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827127456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2172002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103021621704</t>
+    <t xml:space="preserve">14.4263944625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815647125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103002548218</t>
   </si>
   <si>
     <t xml:space="preserve">14.563175201416</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057022094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045570373535</t>
+    <t xml:space="preserve">14.4585752487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045541763306</t>
   </si>
   <si>
     <t xml:space="preserve">14.3217945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9516830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781206130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045572280884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3643264770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1873149871826</t>
+    <t xml:space="preserve">13.9516839981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3643274307251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1873140335083</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539842605591</t>
@@ -638,112 +638,112 @@
     <t xml:space="preserve">13.31605052948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5896129608154</t>
+    <t xml:space="preserve">13.5896120071411</t>
   </si>
   <si>
     <t xml:space="preserve">13.7746725082397</t>
   </si>
   <si>
-    <t xml:space="preserve">13.911452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011060714722</t>
+    <t xml:space="preserve">13.9114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011051177979</t>
   </si>
   <si>
     <t xml:space="preserve">13.9999561309814</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9815635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.844783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9171943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5367336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.609148979187</t>
+    <t xml:space="preserve">14.9815654754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378818511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160472869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447828292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.917197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631721496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.536732673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643211364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091470718384</t>
   </si>
   <si>
     <t xml:space="preserve">15.5045518875122</t>
   </si>
   <si>
-    <t xml:space="preserve">15.407998085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263874053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8907566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.947078704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114440917969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3493766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3010997772217</t>
+    <t xml:space="preserve">15.4080009460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1102991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068510055542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.890754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8987998962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470777511597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114459991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3493747711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.301097869873</t>
   </si>
   <si>
     <t xml:space="preserve">16.5344314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5827102661133</t>
+    <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3332824707031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1723651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1562728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700653076172</t>
+    <t xml:space="preserve">16.4539737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.156270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700662612915</t>
   </si>
   <si>
     <t xml:space="preserve">16.0919036865234</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">16.0033988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.043628692627</t>
+    <t xml:space="preserve">16.0436305999756</t>
   </si>
   <si>
     <t xml:space="preserve">16.4781112670898</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">16.8965015411377</t>
   </si>
   <si>
-    <t xml:space="preserve">16.976957321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0413284301758</t>
+    <t xml:space="preserve">16.9769611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0413303375244</t>
   </si>
   <si>
     <t xml:space="preserve">17.3792572021484</t>
@@ -773,55 +773,55 @@
     <t xml:space="preserve">17.516040802002</t>
   </si>
   <si>
-    <t xml:space="preserve">17.773509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3850040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229309082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2700576782227</t>
+    <t xml:space="preserve">17.7735061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3850021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229347229004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.270055770874</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4068374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4470691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321258544922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125816345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3827018737793</t>
+    <t xml:space="preserve">19.4068393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4470653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.752815246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079883575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">19.5838489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3102874755859</t>
+    <t xml:space="preserve">19.3102855682373</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436191558838</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">19.0689067840576</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0769519805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.028678894043</t>
+    <t xml:space="preserve">19.0769538879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8355731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286769866943</t>
   </si>
   <si>
     <t xml:space="preserve">18.972354888916</t>
   </si>
   <si>
-    <t xml:space="preserve">18.56201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.505687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6183319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654567718506</t>
+    <t xml:space="preserve">18.5620136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654586791992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8171787261963</t>
   </si>
   <si>
-    <t xml:space="preserve">20.259708404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5574073791504</t>
+    <t xml:space="preserve">20.2597064971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7585563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.557409286499</t>
   </si>
   <si>
     <t xml:space="preserve">20.9539337158203</t>
@@ -875,34 +875,34 @@
     <t xml:space="preserve">21.1818714141846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9213714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666988372803</t>
+    <t xml:space="preserve">20.9213733673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5726203918457</t>
+    <t xml:space="preserve">21.5726184844971</t>
   </si>
   <si>
     <t xml:space="preserve">20.538761138916</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5550403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271064758301</t>
+    <t xml:space="preserve">20.5550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922309875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271026611328</t>
   </si>
   <si>
     <t xml:space="preserve">20.3515281677246</t>
@@ -911,58 +911,58 @@
     <t xml:space="preserve">20.5143394470215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9864959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9376487731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1248893737793</t>
+    <t xml:space="preserve">20.9864921569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946327209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9376525878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1248836517334</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8399620056152</t>
+    <t xml:space="preserve">20.8399658203125</t>
   </si>
   <si>
     <t xml:space="preserve">20.8155403137207</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1574459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945423126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957431793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3189640045166</t>
+    <t xml:space="preserve">21.1574478149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2945442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3189659118652</t>
   </si>
   <si>
     <t xml:space="preserve">19.8386707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.985200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317272186279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3678073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259922027588</t>
+    <t xml:space="preserve">20.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9851989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317310333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259960174561</t>
   </si>
   <si>
     <t xml:space="preserve">20.3108234405518</t>
@@ -974,28 +974,28 @@
     <t xml:space="preserve">19.3583736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874179840088</t>
+    <t xml:space="preserve">19.1874198913574</t>
   </si>
   <si>
     <t xml:space="preserve">18.9757633209229</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8048114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7071228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338558197021</t>
+    <t xml:space="preserve">18.8048076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978698730469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338577270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.1304340362549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4804821014404</t>
+    <t xml:space="preserve">19.4804840087891</t>
   </si>
   <si>
     <t xml:space="preserve">19.5293254852295</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">20.2049961090088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7816829681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375583648682</t>
+    <t xml:space="preserve">19.7816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375602722168</t>
   </si>
   <si>
     <t xml:space="preserve">20.7829780578613</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">20.7748394012451</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6771507263184</t>
+    <t xml:space="preserve">20.905086517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.677152633667</t>
   </si>
   <si>
     <t xml:space="preserve">21.1655883789062</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">21.2795543670654</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0597610473633</t>
+    <t xml:space="preserve">21.0597591400146</t>
   </si>
   <si>
     <t xml:space="preserve">21.043478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6852951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1004619598389</t>
+    <t xml:space="preserve">20.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1004638671875</t>
   </si>
   <si>
     <t xml:space="preserve">21.5400562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4260902404785</t>
+    <t xml:space="preserve">21.4260883331299</t>
   </si>
   <si>
     <t xml:space="preserve">21.5319156646729</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">21.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7842769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4993515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935241699219</t>
+    <t xml:space="preserve">21.784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4993534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935260772705</t>
   </si>
   <si>
     <t xml:space="preserve">21.7761325836182</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6214599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6308994293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0542087554932</t>
+    <t xml:space="preserve">21.6214618682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.711009979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169258117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9809436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6308975219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0542106628418</t>
   </si>
   <si>
     <t xml:space="preserve">22.989086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.200740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1681785583496</t>
+    <t xml:space="preserve">23.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.168176651001</t>
   </si>
   <si>
     <t xml:space="preserve">23.4693813323975</t>
@@ -1106,31 +1106,31 @@
     <t xml:space="preserve">23.8601303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7298812866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008331298828</t>
+    <t xml:space="preserve">23.7298793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008350372314</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263633728027</t>
+    <t xml:space="preserve">23.5996284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159114837646</t>
@@ -1145,10 +1145,10 @@
     <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0567989349365</t>
+    <t xml:space="preserve">24.991678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0568008422852</t>
   </si>
   <si>
     <t xml:space="preserve">25.0079555511475</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">24.87770652771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8288612365723</t>
+    <t xml:space="preserve">24.8288631439209</t>
   </si>
   <si>
     <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
-    <t xml:space="preserve">24.649772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9604091644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4801120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1789131164551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613311767578</t>
+    <t xml:space="preserve">24.6497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9604072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.480110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1789112091064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613330841064</t>
   </si>
   <si>
     <t xml:space="preserve">24.5602226257324</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">25.4556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2778911590576</t>
+    <t xml:space="preserve">26.277889251709</t>
   </si>
   <si>
     <t xml:space="preserve">25.9848289489746</t>
@@ -1202,34 +1202,34 @@
     <t xml:space="preserve">27.1082324981689</t>
   </si>
   <si>
-    <t xml:space="preserve">27.7676258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3850135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209995269775</t>
+    <t xml:space="preserve">27.7676277160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3850173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9209976196289</t>
   </si>
   <si>
     <t xml:space="preserve">27.5071239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0105457305908</t>
+    <t xml:space="preserve">27.0105476379395</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2765979766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032386779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.617208480835</t>
+    <t xml:space="preserve">25.2765998840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032405853271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6172065734863</t>
   </si>
   <si>
     <t xml:space="preserve">24.584644317627</t>
@@ -1238,121 +1238,121 @@
     <t xml:space="preserve">25.2440338134766</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8451442718506</t>
+    <t xml:space="preserve">24.8451404571533</t>
   </si>
   <si>
     <t xml:space="preserve">24.7393169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6429252624512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5859394073486</t>
+    <t xml:space="preserve">25.1951923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6429233551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5859432220459</t>
   </si>
   <si>
     <t xml:space="preserve">25.724328994751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6917686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.545238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7568950653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5208148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3172988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3987064361572</t>
+    <t xml:space="preserve">25.691764831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5452365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7568912506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5208168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987045288086</t>
   </si>
   <si>
     <t xml:space="preserve">25.512674331665</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7650318145752</t>
+    <t xml:space="preserve">25.7650337219238</t>
   </si>
   <si>
     <t xml:space="preserve">26.0499534606934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2033309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0486583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4625339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661422729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148952484131</t>
+    <t xml:space="preserve">25.2033290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4625358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661441802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.7419052124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5790939331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931541442871</t>
+    <t xml:space="preserve">26.7419013977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3931560516357</t>
   </si>
   <si>
     <t xml:space="preserve">26.6604995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4976863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313591003418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.602222442627</t>
+    <t xml:space="preserve">26.497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022243499756</t>
   </si>
   <si>
     <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2941703796387</t>
+    <t xml:space="preserve">26.2941722869873</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.8233165740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197986602783</t>
+    <t xml:space="preserve">27.31174659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8815898895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2303409576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.619800567627</t>
   </si>
   <si>
     <t xml:space="preserve">26.1720638275146</t>
@@ -1361,13 +1361,13 @@
     <t xml:space="preserve">25.0730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6253471374512</t>
+    <t xml:space="preserve">24.6253509521484</t>
   </si>
   <si>
     <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9740982055664</t>
+    <t xml:space="preserve">23.974100112915</t>
   </si>
   <si>
     <t xml:space="preserve">25.5615177154541</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">25.2358932495117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3635520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4218311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2534713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6891746520996</t>
+    <t xml:space="preserve">23.3635540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4218330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2534694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6891784667969</t>
   </si>
   <si>
     <t xml:space="preserve">23.5670700073242</t>
@@ -1400,79 +1400,79 @@
     <t xml:space="preserve">20.1887130737305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6364479064941</t>
+    <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
     <t xml:space="preserve">20.7178535461426</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7002792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4736366271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062892913818</t>
+    <t xml:space="preserve">19.7002773284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062911987305</t>
   </si>
   <si>
     <t xml:space="preserve">21.6540260314941</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7354316711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273853302002</t>
+    <t xml:space="preserve">21.7354335784912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273815155029</t>
   </si>
   <si>
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806667327881</t>
+    <t xml:space="preserve">20.8806648254395</t>
   </si>
   <si>
     <t xml:space="preserve">21.4505100250244</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3283996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6947269439697</t>
+    <t xml:space="preserve">21.3284015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
   </si>
   <si>
     <t xml:space="preserve">22.4680862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">22.183162689209</t>
+    <t xml:space="preserve">22.1831645965576</t>
   </si>
   <si>
     <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0203514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3459796905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1600379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7123050689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8057384490967</t>
+    <t xml:space="preserve">22.0203533172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3459777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1600360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7123031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.805736541748</t>
   </si>
   <si>
     <t xml:space="preserve">24.7067565917969</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3811302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2183170318604</t>
+    <t xml:space="preserve">24.3811283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.218318939209</t>
   </si>
   <si>
     <t xml:space="preserve">24.1776161193848</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">24.2997226715088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.788158416748</t>
+    <t xml:space="preserve">24.7881622314453</t>
   </si>
   <si>
     <t xml:space="preserve">24.705394744873</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">24.1260414123535</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6640110015869</t>
+    <t xml:space="preserve">24.6640129089355</t>
   </si>
   <si>
     <t xml:space="preserve">24.9123058319092</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2019844055176</t>
+    <t xml:space="preserve">25.2019863128662</t>
   </si>
   <si>
     <t xml:space="preserve">25.4088973999023</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3261318206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2779331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1469688415527</t>
+    <t xml:space="preserve">25.326135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2779312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1469631195068</t>
   </si>
   <si>
     <t xml:space="preserve">26.9400539398193</t>
@@ -1523,43 +1523,43 @@
     <t xml:space="preserve">26.1951675415039</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4916610717773</t>
+    <t xml:space="preserve">25.491662979126</t>
   </si>
   <si>
     <t xml:space="preserve">25.5330467224121</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0778369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3675136566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6985778808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847480773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6571922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9468727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0710201263428</t>
+    <t xml:space="preserve">25.0778388977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3675155639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6985740661621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847518920898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6571941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.153787612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9468746185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0710182189941</t>
   </si>
   <si>
     <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3193130493164</t>
+    <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
     <t xml:space="preserve">27.0642032623291</t>
@@ -1574,10 +1574,10 @@
     <t xml:space="preserve">23.6294460296631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535953521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0432739257812</t>
+    <t xml:space="preserve">23.7535972595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0432720184326</t>
   </si>
   <si>
     <t xml:space="preserve">23.8363590240479</t>
@@ -1592,25 +1592,25 @@
     <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9191246032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2088069915771</t>
+    <t xml:space="preserve">23.9191265106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2088031768799</t>
   </si>
   <si>
     <t xml:space="preserve">24.3329524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262279510498</t>
+    <t xml:space="preserve">25.4502811431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262298583984</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0296382904053</t>
+    <t xml:space="preserve">26.0296363830566</t>
   </si>
   <si>
     <t xml:space="preserve">26.5676078796387</t>
@@ -1619,121 +1619,121 @@
     <t xml:space="preserve">25.5744285583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6089935302734</t>
+    <t xml:space="preserve">26.6089954376221</t>
   </si>
   <si>
     <t xml:space="preserve">26.9814357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9882526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4434642791748</t>
+    <t xml:space="preserve">25.9882545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4434661865234</t>
   </si>
   <si>
     <t xml:space="preserve">26.6503753662109</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3606986999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4984817504883</t>
+    <t xml:space="preserve">26.3606967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4984798431396</t>
   </si>
   <si>
     <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4361724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.89137840271</t>
+    <t xml:space="preserve">21.72585105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4361743927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8913803100586</t>
   </si>
   <si>
     <t xml:space="preserve">20.7740516662598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6430835723877</t>
+    <t xml:space="preserve">21.6430854797363</t>
   </si>
   <si>
     <t xml:space="preserve">21.4775562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1051120758057</t>
+    <t xml:space="preserve">21.105110168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6981029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636360168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602275848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360801696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086128234863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9395809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9327621459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0569114685059</t>
+    <t xml:space="preserve">19.6981048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636341094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.939582824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9327640533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0569095611572</t>
   </si>
   <si>
     <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2638244628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4634456634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462112426758</t>
+    <t xml:space="preserve">22.263822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4634437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462131500244</t>
   </si>
   <si>
     <t xml:space="preserve">17.6703567504883</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2083320617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4980087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7049217224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8290691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6221580505371</t>
+    <t xml:space="preserve">17.8772716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2083301544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.498010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7049236297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6221561431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3670444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5325756072998</t>
+    <t xml:space="preserve">19.3670425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5325736999512</t>
   </si>
   <si>
     <t xml:space="preserve">19.491189956665</t>
@@ -1742,43 +1742,43 @@
     <t xml:space="preserve">19.0773639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187496185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0427989959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7945041656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8427085876465</t>
+    <t xml:space="preserve">19.1187477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0428009033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7945079803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8427066802979</t>
   </si>
   <si>
     <t xml:space="preserve">17.7531204223633</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1737670898438</t>
+    <t xml:space="preserve">17.1737651824951</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806800842285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.966854095459</t>
+    <t xml:space="preserve">16.9668521881104</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357936859131</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5530300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2497138977051</t>
+    <t xml:space="preserve">16.7599391937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8840885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5530281066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2497119903564</t>
   </si>
   <si>
     <t xml:space="preserve">18.4152431488037</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">19.1601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.40842628479</t>
+    <t xml:space="preserve">19.4084281921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739555358887</t>
@@ -1796,10 +1796,10 @@
     <t xml:space="preserve">19.4498081207275</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9050159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222522735596</t>
+    <t xml:space="preserve">19.9050140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222541809082</t>
   </si>
   <si>
     <t xml:space="preserve">20.5257549285889</t>
@@ -1808,25 +1808,25 @@
     <t xml:space="preserve">20.6499042510986</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188438415527</t>
+    <t xml:space="preserve">20.3188419342041</t>
   </si>
   <si>
     <t xml:space="preserve">20.111930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7808685302734</t>
+    <t xml:space="preserve">19.7808704376221</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.029167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567211151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9463996887207</t>
+    <t xml:space="preserve">20.0291633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567230224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9463977813721</t>
   </si>
   <si>
     <t xml:space="preserve">19.2428951263428</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364761352539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4868144989014</t>
+    <t xml:space="preserve">16.5364742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5944080352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4868183135986</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910015106201</t>
+    <t xml:space="preserve">17.0909996032715</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151489257812</t>
@@ -1862,10 +1862,10 @@
     <t xml:space="preserve">17.3310203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.364128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910976409912</t>
+    <t xml:space="preserve">17.3641300201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910957336426</t>
   </si>
   <si>
     <t xml:space="preserve">18.6056041717529</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">18.3407535552979</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0593528747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6455268859863</t>
+    <t xml:space="preserve">18.0593547821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.645528793335</t>
   </si>
   <si>
     <t xml:space="preserve">17.2482566833496</t>
@@ -1889,7 +1889,7 @@
     <t xml:space="preserve">18.07590675354</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1255664825439</t>
+    <t xml:space="preserve">18.1255683898926</t>
   </si>
   <si>
     <t xml:space="preserve">17.6620807647705</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765892028809</t>
+    <t xml:space="preserve">17.9765872955322</t>
   </si>
   <si>
     <t xml:space="preserve">18.2248840332031</t>
@@ -1913,160 +1913,160 @@
     <t xml:space="preserve">16.6192417144775</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5033702850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101881027222</t>
+    <t xml:space="preserve">16.5033683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101861953735</t>
   </si>
   <si>
     <t xml:space="preserve">15.4274225234985</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2701711654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8397903442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328783035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6742601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233345031738</t>
+    <t xml:space="preserve">15.2701683044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328773498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177845001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233325958252</t>
   </si>
   <si>
     <t xml:space="preserve">15.9322891235352</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0632543563843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467023849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659822463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3255767822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426027297974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7125539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402633666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6444396972656</t>
+    <t xml:space="preserve">15.0632572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.046703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232374191284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3255748748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.342604637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.712553024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614685058594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6444387435913</t>
   </si>
   <si>
     <t xml:space="preserve">14.8062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5422677993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811697006226</t>
+    <t xml:space="preserve">14.5422687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811677932739</t>
   </si>
   <si>
     <t xml:space="preserve">15.6661424636841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9083786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5252389907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741554260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.201699256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.389012336731</t>
+    <t xml:space="preserve">14.9083776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5252408981323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741544723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2017002105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3890142440796</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.431586265564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2357549667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0484457015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317518234253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507841110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3208980560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020360946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4230699539185</t>
+    <t xml:space="preserve">14.4315843582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2357559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0484428405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846723556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8317527770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3208999633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7295827865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020351409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4230690002441</t>
   </si>
   <si>
     <t xml:space="preserve">14.3379278182983</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462728500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6908483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419328689575</t>
+    <t xml:space="preserve">14.3549547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462738037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6908473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419319152832</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312494277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821664810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975257873535</t>
+    <t xml:space="preserve">13.6312475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975267410278</t>
   </si>
   <si>
     <t xml:space="preserve">14.0995283126831</t>
@@ -2075,28 +2075,28 @@
     <t xml:space="preserve">13.8866739273071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8185596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801639556885</t>
+    <t xml:space="preserve">13.8185606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5205631256104</t>
+    <t xml:space="preserve">13.5205640792847</t>
   </si>
   <si>
     <t xml:space="preserve">13.1799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2140512466431</t>
+    <t xml:space="preserve">13.1544523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2140522003174</t>
   </si>
   <si>
     <t xml:space="preserve">12.1668043136597</t>
@@ -2108,28 +2108,28 @@
     <t xml:space="preserve">10.974814414978</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491056442261</t>
+    <t xml:space="preserve">10.949273109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491037368774</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449312210083</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1706409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7534446716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0344142913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811597824097</t>
+    <t xml:space="preserve">11.1706418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7534456253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0344152450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1621284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -2138,16 +2138,16 @@
     <t xml:space="preserve">10.7619600296021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2511081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471021652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6683025360107</t>
+    <t xml:space="preserve">10.251106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471012115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6683034896851</t>
   </si>
   <si>
     <t xml:space="preserve">10.7279033660889</t>
@@ -2156,22 +2156,22 @@
     <t xml:space="preserve">11.3664684295654</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5367527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6644659042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6900072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410936355591</t>
+    <t xml:space="preserve">11.5367517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6644649505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6900091171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410945892334</t>
   </si>
   <si>
     <t xml:space="preserve">11.7496070861816</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838331222534</t>
+    <t xml:space="preserve">12.1838321685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9028635025024</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">11.8177223205566</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751493453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476055145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4601249694824</t>
+    <t xml:space="preserve">11.7751512527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476064682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4601240158081</t>
   </si>
   <si>
     <t xml:space="preserve">11.5026969909668</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">11.1450986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8981876373291</t>
+    <t xml:space="preserve">10.8981885910034</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898406982422</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">10.4724760055542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597900390625</t>
+    <t xml:space="preserve">10.6597890853882</t>
   </si>
   <si>
     <t xml:space="preserve">11.0173854827881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0854997634888</t>
+    <t xml:space="preserve">11.0855007171631</t>
   </si>
   <si>
     <t xml:space="preserve">11.0514421463013</t>
@@ -2225,10 +2225,10 @@
     <t xml:space="preserve">11.1280708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088710784912</t>
+    <t xml:space="preserve">11.0003576278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088720321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.2642984390259</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">11.6814947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8092069625854</t>
+    <t xml:space="preserve">11.8092079162598</t>
   </si>
   <si>
     <t xml:space="preserve">13.3247365951538</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5120496749878</t>
+    <t xml:space="preserve">13.5120506286621</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738185882568</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">13.546106338501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4145565032959</t>
+    <t xml:space="preserve">14.4145555496216</t>
   </si>
   <si>
     <t xml:space="preserve">13.8526182174683</t>
@@ -2273,16 +2273,16 @@
     <t xml:space="preserve">13.8781595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7759885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4439344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8441028594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4486131668091</t>
+    <t xml:space="preserve">13.775990486145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4439353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8441038131714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
     <t xml:space="preserve">14.6274099349976</t>
@@ -2291,76 +2291,76 @@
     <t xml:space="preserve">14.9254083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043716430664</t>
+    <t xml:space="preserve">15.5043725967407</t>
   </si>
   <si>
     <t xml:space="preserve">14.5933532714844</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5592956542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9424362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9679794311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870079040527</t>
+    <t xml:space="preserve">14.5592966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424352645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9679775238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870098114014</t>
   </si>
   <si>
     <t xml:space="preserve">15.019063949585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.317063331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6406021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4618015289307</t>
+    <t xml:space="preserve">15.1467800140381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406002044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.461802482605</t>
   </si>
   <si>
     <t xml:space="preserve">14.4656410217285</t>
   </si>
   <si>
-    <t xml:space="preserve">14.363471031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3294143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4826698303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1506147384644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1335868835449</t>
+    <t xml:space="preserve">14.3634719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3294134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4826679229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.15061378479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1335859298706</t>
   </si>
   <si>
     <t xml:space="preserve">14.5763263702393</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1165580749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996995925903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721529006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7078762054443</t>
+    <t xml:space="preserve">14.1165599822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4911832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7078771591187</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292459487915</t>
@@ -2369,46 +2369,46 @@
     <t xml:space="preserve">13.5035343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3162221908569</t>
+    <t xml:space="preserve">13.3162231445312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5631351470947</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375909805298</t>
+    <t xml:space="preserve">13.5375919342041</t>
   </si>
   <si>
     <t xml:space="preserve">14.4060401916504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.269814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2953567504883</t>
+    <t xml:space="preserve">14.2698135375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2953577041626</t>
   </si>
   <si>
     <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167264938354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761560440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931858062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7589597702026</t>
+    <t xml:space="preserve">14.5167255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761569976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931867599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.758960723877</t>
   </si>
   <si>
     <t xml:space="preserve">13.4183921813965</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5584573745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3370876312256</t>
+    <t xml:space="preserve">12.5584583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">12.6010284423828</t>
@@ -2417,28 +2417,28 @@
     <t xml:space="preserve">11.9880056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6218957901001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3277349472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82539558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4252290725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74025535583496</t>
+    <t xml:space="preserve">11.6218948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.443097114563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3277339935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82539749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42523002624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74025344848633</t>
   </si>
   <si>
     <t xml:space="preserve">8.08424091339111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73557949066162</t>
+    <t xml:space="preserve">8.7355785369873</t>
   </si>
   <si>
     <t xml:space="preserve">8.2715539932251</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">8.31412506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278839111328</t>
+    <t xml:space="preserve">7.96078443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278743743896</t>
   </si>
   <si>
     <t xml:space="preserve">9.11020278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00803184509277</t>
+    <t xml:space="preserve">9.00803279876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.41671562194824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47631454467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5784854888916</t>
+    <t xml:space="preserve">9.47631359100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57848358154297</t>
   </si>
   <si>
     <t xml:space="preserve">9.44225692749023</t>
@@ -2474,43 +2474,43 @@
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317493438721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16980361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53591442108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48482799530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62105560302734</t>
+    <t xml:space="preserve">9.09317588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16980266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53591346740723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48482894897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62105655670166</t>
   </si>
   <si>
     <t xml:space="preserve">10.089337348938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.131908416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0467672348022</t>
+    <t xml:space="preserve">10.1319074630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
     <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8764820098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97013854980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0552816390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2936782836914</t>
+    <t xml:space="preserve">9.87648296356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97013759613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0552797317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2936792373657</t>
   </si>
   <si>
     <t xml:space="preserve">10.319221496582</t>
@@ -2519,28 +2519,28 @@
     <t xml:space="preserve">10.4299058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9322452545166</t>
+    <t xml:space="preserve">10.932243347168</t>
   </si>
   <si>
     <t xml:space="preserve">11.1961841583252</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9407596588135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96162509918213</t>
+    <t xml:space="preserve">10.9407577514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96162414550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.85945415496826</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78282451629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3060302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51037120819092</t>
+    <t xml:space="preserve">9.7828254699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30602931976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5103702545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888561248779</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26345920562744</t>
+    <t xml:space="preserve">9.26345825195312</t>
   </si>
   <si>
     <t xml:space="preserve">9.25494575500488</t>
@@ -2573,37 +2573,37 @@
     <t xml:space="preserve">9.70619678497314</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62957096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876697540283</t>
+    <t xml:space="preserve">9.62957000732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85093975067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300733566284</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5405912399292</t>
+    <t xml:space="preserve">10.5405902862549</t>
   </si>
   <si>
     <t xml:space="preserve">10.2340793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61254215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96388339996338</t>
+    <t xml:space="preserve">9.6125431060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9638843536377</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435722351074</t>
   </si>
   <si>
-    <t xml:space="preserve">10.182391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1998720169067</t>
+    <t xml:space="preserve">10.1823921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1998710632324</t>
   </si>
   <si>
     <t xml:space="preserve">10.1649103164673</t>
@@ -2612,7 +2612,7 @@
     <t xml:space="preserve">10.0600280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.444598197937</t>
+    <t xml:space="preserve">10.4445991516113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0163259506226</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">9.72789859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64049530029297</t>
+    <t xml:space="preserve">9.64049625396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.28214454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56183338165283</t>
+    <t xml:space="preserve">9.56183242797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.41324996948242</t>
@@ -2645,52 +2645,52 @@
     <t xml:space="preserve">9.40450859069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15978145599365</t>
+    <t xml:space="preserve">9.15978240966797</t>
   </si>
   <si>
     <t xml:space="preserve">8.99371719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01993846893311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90631484985352</t>
+    <t xml:space="preserve">9.01993751525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9063138961792</t>
   </si>
   <si>
     <t xml:space="preserve">9.57931423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36080837249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18600368499756</t>
+    <t xml:space="preserve">9.20348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36080741882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18600177764893</t>
   </si>
   <si>
     <t xml:space="preserve">9.33458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44820976257324</t>
+    <t xml:space="preserve">9.22096252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44821071624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.29088497161865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01119804382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3484563827515</t>
+    <t xml:space="preserve">9.01119709014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3484554290771</t>
   </si>
   <si>
     <t xml:space="preserve">10.4358577728271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4271192550659</t>
+    <t xml:space="preserve">10.4271183013916</t>
   </si>
   <si>
     <t xml:space="preserve">10.9777536392212</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5494823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260932922363</t>
+    <t xml:space="preserve">10.5494813919067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260913848877</t>
   </si>
   <si>
     <t xml:space="preserve">10.1299495697021</t>
@@ -2732,16 +2732,16 @@
     <t xml:space="preserve">9.98136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93766307830811</t>
+    <t xml:space="preserve">9.93766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">10.094988822937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1124687194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250663757324</t>
+    <t xml:space="preserve">10.1124696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250673294067</t>
   </si>
   <si>
     <t xml:space="preserve">9.95514488220215</t>
@@ -2759,22 +2759,22 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3222360610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.750506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2785339355469</t>
+    <t xml:space="preserve">9.99884510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7330274581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7505073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2785329818726</t>
   </si>
   <si>
     <t xml:space="preserve">10.3834171295166</t>
@@ -2789,28 +2789,28 @@
     <t xml:space="preserve">10.6893253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106634140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4795589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5757036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669622421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5232620239258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5582208633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4708194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81530094146729</t>
+    <t xml:space="preserve">10.6106643676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4795598983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5757026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5232601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5582227706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4708185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81529998779297</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">9.99010562896729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82404136657715</t>
+    <t xml:space="preserve">9.82404041290283</t>
   </si>
   <si>
     <t xml:space="preserve">9.86774253845215</t>
@@ -2828,16 +2828,16 @@
     <t xml:space="preserve">9.6142749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00245761871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82765197753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5348539352417</t>
+    <t xml:space="preserve">9.0024585723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82765293121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53485298156738</t>
   </si>
   <si>
     <t xml:space="preserve">8.6441068649292</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">9.12482070922852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16852188110352</t>
+    <t xml:space="preserve">9.1685209274292</t>
   </si>
   <si>
     <t xml:space="preserve">8.88883399963379</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">8.98497676849365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94640350341797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69293689727783</t>
+    <t xml:space="preserve">9.94640445709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69293785095215</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078311920166</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">11.1350784301758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6070508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3587141036987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5597381591797</t>
+    <t xml:space="preserve">11.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3587131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.559739112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.8867406845093</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">12.4810762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.19264793396</t>
+    <t xml:space="preserve">12.1926498413086</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139860153198</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">12.210129737854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6857137680054</t>
+    <t xml:space="preserve">11.6857147216797</t>
   </si>
   <si>
     <t xml:space="preserve">12.0702848434448</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">11.9479217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0615434646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314678192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440645217896</t>
+    <t xml:space="preserve">12.0615453720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314668655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440635681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954801559448</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">12.5684795379639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5422592163086</t>
+    <t xml:space="preserve">12.5422582626343</t>
   </si>
   <si>
     <t xml:space="preserve">12.778244972229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2363500595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4461164474487</t>
+    <t xml:space="preserve">12.236349105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4461145401001</t>
   </si>
   <si>
     <t xml:space="preserve">12.516037940979</t>
@@ -2960,28 +2960,28 @@
     <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713108062744</t>
+    <t xml:space="preserve">12.2713098526001</t>
   </si>
   <si>
     <t xml:space="preserve">12.8132057189941</t>
   </si>
   <si>
-    <t xml:space="preserve">12.839427947998</t>
+    <t xml:space="preserve">12.8394269943237</t>
   </si>
   <si>
     <t xml:space="preserve">12.9093494415283</t>
   </si>
   <si>
-    <t xml:space="preserve">12.821946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9880104064941</t>
+    <t xml:space="preserve">12.8219451904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9880113601685</t>
   </si>
   <si>
     <t xml:space="preserve">13.0229721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114013671875</t>
+    <t xml:space="preserve">13.3113994598389</t>
   </si>
   <si>
     <t xml:space="preserve">13.2152576446533</t>
@@ -2990,34 +2990,34 @@
     <t xml:space="preserve">13.2502193450928</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7607641220093</t>
+    <t xml:space="preserve">12.7607650756836</t>
   </si>
   <si>
     <t xml:space="preserve">12.6296615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.953049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9792718887329</t>
+    <t xml:space="preserve">12.9530506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9792709350586</t>
   </si>
   <si>
     <t xml:space="preserve">12.9355697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3026609420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075422286987</t>
+    <t xml:space="preserve">13.302661895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075441360474</t>
   </si>
   <si>
     <t xml:space="preserve">13.189037322998</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2239990234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.800853729248</t>
+    <t xml:space="preserve">13.2239980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8008546829224</t>
   </si>
   <si>
     <t xml:space="preserve">14.0281000137329</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">14.1067628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3951902389526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5000743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5612554550171</t>
+    <t xml:space="preserve">14.3951921463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500075340271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5612564086914</t>
   </si>
   <si>
     <t xml:space="preserve">14.2116460800171</t>
@@ -3044,85 +3044,85 @@
     <t xml:space="preserve">13.7484130859375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980224609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7221918106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3864498138428</t>
+    <t xml:space="preserve">14.0980234146118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7221927642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3864507675171</t>
   </si>
   <si>
     <t xml:space="preserve">14.6661386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7098417282104</t>
+    <t xml:space="preserve">14.7098398208618</t>
   </si>
   <si>
     <t xml:space="preserve">14.6224374771118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0157489776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818141937256</t>
+    <t xml:space="preserve">15.0157499313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818151473999</t>
   </si>
   <si>
     <t xml:space="preserve">15.3653602600098</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1206312179565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.456374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6136960983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3442687988281</t>
+    <t xml:space="preserve">15.1206321716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4563732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7622814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3442668914795</t>
   </si>
   <si>
     <t xml:space="preserve">16.7550582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946565628052</t>
+    <t xml:space="preserve">15.9946584701538</t>
   </si>
   <si>
     <t xml:space="preserve">15.8373327255249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9159927368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9247331619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9422149658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1344985961914</t>
+    <t xml:space="preserve">15.9159917831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.942214012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1345024108887</t>
   </si>
   <si>
     <t xml:space="preserve">15.43528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440212249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3304004669189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.242995262146</t>
+    <t xml:space="preserve">15.5663843154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3566188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330397605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2429962158203</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255153656006</t>
@@ -3131,64 +3131,64 @@
     <t xml:space="preserve">15.2866954803467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517356872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0681896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265394210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0244913101196</t>
+    <t xml:space="preserve">15.2779550552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517366409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.068190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1381120681763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0244903564453</t>
   </si>
   <si>
     <t xml:space="preserve">14.893385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234634399414</t>
+    <t xml:space="preserve">14.8234624862671</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196071624756</t>
+    <t xml:space="preserve">14.919605255127</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9370889663696</t>
+    <t xml:space="preserve">14.9370861053467</t>
   </si>
   <si>
     <t xml:space="preserve">15.1468524932861</t>
   </si>
   <si>
-    <t xml:space="preserve">14.849684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041763305664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409433364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4214134216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5962171554565</t>
+    <t xml:space="preserve">14.8496837615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2604761123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.304178237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4214115142822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5962162017822</t>
   </si>
   <si>
     <t xml:space="preserve">16.7812824249268</t>
@@ -3197,37 +3197,37 @@
     <t xml:space="preserve">17.4367980957031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4630184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2846012115479</t>
+    <t xml:space="preserve">17.463020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2846031188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048999786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7340087890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4696502685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8573722839355</t>
+    <t xml:space="preserve">18.5048980712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340068817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4696521759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8573741912842</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3684597015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9631175994873</t>
+    <t xml:space="preserve">19.3684616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9631156921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.1217288970947</t>
@@ -3239,10 +3239,10 @@
     <t xml:space="preserve">18.9807415008545</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8749980926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5753917694092</t>
+    <t xml:space="preserve">18.8749961853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
     <t xml:space="preserve">18.2052955627441</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">18.6987590789795</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5401496887207</t>
+    <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
     <t xml:space="preserve">18.2405433654785</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7163829803467</t>
+    <t xml:space="preserve">18.7163848876953</t>
   </si>
   <si>
     <t xml:space="preserve">18.2934150695801</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">18.1524257659912</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0290603637695</t>
+    <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
     <t xml:space="preserve">17.8175735473633</t>
@@ -3278,40 +3278,40 @@
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7647018432617</t>
+    <t xml:space="preserve">17.888069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7647037506104</t>
   </si>
   <si>
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589603424072</t>
+    <t xml:space="preserve">17.5708408355713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589622497559</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3681678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1478710174561</t>
+    <t xml:space="preserve">17.3681697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">17.4650993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9761867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8351993560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.482723236084</t>
+    <t xml:space="preserve">17.976188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8351974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4827251434326</t>
   </si>
   <si>
     <t xml:space="preserve">17.2007446289062</t>
@@ -3329,79 +3329,79 @@
     <t xml:space="preserve">16.6367855072021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857936859131</t>
+    <t xml:space="preserve">17.3857917785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.2448024749756</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3769798278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4122276306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7823295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7470779418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5355930328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6237125396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8747043609619</t>
+    <t xml:space="preserve">17.3769817352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4122295379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7823257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7470798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5355949401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6237144470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8747062683105</t>
   </si>
   <si>
     <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1743106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417358398438</t>
+    <t xml:space="preserve">17.1743087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417339324951</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9540100097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3593597412109</t>
+    <t xml:space="preserve">16.9540119171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3593578338623</t>
   </si>
   <si>
     <t xml:space="preserve">16.9716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7249011993408</t>
+    <t xml:space="preserve">16.7249050140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6720314025879</t>
+    <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
     <t xml:space="preserve">16.4869842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2183704376221</t>
+    <t xml:space="preserve">16.8042125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6765842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5796527862549</t>
+    <t xml:space="preserve">17.676586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5796546936035</t>
   </si>
   <si>
     <t xml:space="preserve">17.5972766876221</t>
@@ -3410,16 +3410,16 @@
     <t xml:space="preserve">17.2888622283936</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0421314239502</t>
+    <t xml:space="preserve">17.0421295166016</t>
   </si>
   <si>
     <t xml:space="preserve">16.7425289154053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.495792388916</t>
+    <t xml:space="preserve">16.5927276611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
@@ -3434,7 +3434,7 @@
     <t xml:space="preserve">15.9935207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8613433837891</t>
+    <t xml:space="preserve">15.8613414764404</t>
   </si>
   <si>
     <t xml:space="preserve">16.2402534484863</t>
@@ -3443,70 +3443,70 @@
     <t xml:space="preserve">16.5134201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7732229232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176820755005</t>
+    <t xml:space="preserve">16.31955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7732238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176801681519</t>
   </si>
   <si>
     <t xml:space="preserve">15.4119358062744</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3590650558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0330276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3150053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154037475586</t>
+    <t xml:space="preserve">15.3590660095215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0330286026001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3150081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
     <t xml:space="preserve">15.2180767059326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1828289031982</t>
+    <t xml:space="preserve">15.1828279495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123342514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035223007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4912443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.085898399353</t>
+    <t xml:space="preserve">15.1123332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035232543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4912452697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1475820541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0858993530273</t>
   </si>
   <si>
     <t xml:space="preserve">14.9801568984985</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8215436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6188688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3985738754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0020408630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0725355148315</t>
+    <t xml:space="preserve">14.8215446472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6188707351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3985748291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0020399093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0725345611572</t>
   </si>
   <si>
     <t xml:space="preserve">13.8434267044067</t>
@@ -3515,16 +3515,16 @@
     <t xml:space="preserve">13.8962984085083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1959018707275</t>
+    <t xml:space="preserve">14.1959009170532</t>
   </si>
   <si>
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3457040786743</t>
+    <t xml:space="preserve">14.3104543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.345703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3533,13 +3533,13 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.548376083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4778804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870899200439</t>
+    <t xml:space="preserve">14.5483770370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4778814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870889663696</t>
   </si>
   <si>
     <t xml:space="preserve">14.1254062652588</t>
@@ -3551,28 +3551,28 @@
     <t xml:space="preserve">13.8169918060303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6055059432983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.772931098938</t>
+    <t xml:space="preserve">13.6055068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7729320526123</t>
   </si>
   <si>
     <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1384792327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.032735824585</t>
+    <t xml:space="preserve">13.1384782791138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1296663284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9446172714233</t>
+    <t xml:space="preserve">13.1296672821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9446182250977</t>
   </si>
   <si>
     <t xml:space="preserve">13.3852100372314</t>
@@ -3590,25 +3590,25 @@
     <t xml:space="preserve">13.1913499832153</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2265968322754</t>
+    <t xml:space="preserve">13.2265958786011</t>
   </si>
   <si>
     <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.314715385437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2618446350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4380807876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4645166397095</t>
+    <t xml:space="preserve">13.3147163391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2618436813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4557046890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.438081741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4645175933838</t>
   </si>
   <si>
     <t xml:space="preserve">13.4997644424438</t>
@@ -3629,40 +3629,40 @@
     <t xml:space="preserve">13.4468936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649141311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388748168945</t>
+    <t xml:space="preserve">13.1649131774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388757705688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710531234741</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6978855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6890745162964</t>
+    <t xml:space="preserve">12.7948160171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.69788646698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6890735626221</t>
   </si>
   <si>
     <t xml:space="preserve">12.5128364562988</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5568962097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273908615112</t>
+    <t xml:space="preserve">12.5568952560425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273918151855</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492738723755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5875911712646</t>
+    <t xml:space="preserve">11.6492757797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.587592124939</t>
   </si>
   <si>
     <t xml:space="preserve">11.8078870773315</t>
@@ -3671,7 +3671,7 @@
     <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431358337402</t>
+    <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3680,7 +3680,7 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347204208374</t>
+    <t xml:space="preserve">11.5347194671631</t>
   </si>
   <si>
     <t xml:space="preserve">11.464225769043</t>
@@ -3689,43 +3689,43 @@
     <t xml:space="preserve">11.1117515563965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9090785980225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2263059616089</t>
+    <t xml:space="preserve">10.9090795516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2263050079346</t>
   </si>
   <si>
     <t xml:space="preserve">11.1293745040894</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0412569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8033380508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1910572052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3937320709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1822452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619483947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6975936889648</t>
+    <t xml:space="preserve">11.0412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.803337097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1910581588745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3937301635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1822462081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.961950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6975946426392</t>
   </si>
   <si>
     <t xml:space="preserve">11.0500688552856</t>
@@ -3734,55 +3734,55 @@
     <t xml:space="preserve">10.4772977828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.75927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2393779754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73710155487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54324054718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56967544555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0455160140991</t>
+    <t xml:space="preserve">10.7592763900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2393770217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73710250854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54324150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56967639923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0455169677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373519897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64883613586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01453018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87353897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25244998931885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977607727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83829212188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70611381530762</t>
+    <t xml:space="preserve">9.42868709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373710632324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64883708953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01452922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87353992462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25244903564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83829307556152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70611476898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.24363803863525</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">8.74576759338379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68848991394043</t>
+    <t xml:space="preserve">8.68849086761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62680721282959</t>
@@ -3800,40 +3800,40 @@
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2787389755249</t>
+    <t xml:space="preserve">8.27874088287354</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43735218048096</t>
+    <t xml:space="preserve">8.43735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26552200317383</t>
+    <t xml:space="preserve">8.27433300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26552104949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245059967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31398677825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42413520812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08487796783447</t>
+    <t xml:space="preserve">8.36245250701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31398773193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4241361618042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13334369659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08487892150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.01878929138184</t>
@@ -3845,49 +3845,49 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8866114616394</t>
+    <t xml:space="preserve">7.88661193847656</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89542293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93067169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819747924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69275093078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66190958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527593612671</t>
+    <t xml:space="preserve">8.02760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.895423412323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93067073822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80730438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819700241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69275140762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66190910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527641296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512655258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803880691528</t>
   </si>
   <si>
     <t xml:space="preserve">7.6751275062561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62037038803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03561210632324</t>
+    <t xml:space="preserve">7.62036943435669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03561115264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.06299114227295</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">7.89871835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64774894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67969036102295</t>
+    <t xml:space="preserve">7.6477484703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82570886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67968988418579</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
@@ -3923,16 +3923,16 @@
     <t xml:space="preserve">7.20056486129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96784734725952</t>
+    <t xml:space="preserve">6.96784687042236</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04085683822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">7.04085636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3947,19 +3947,19 @@
     <t xml:space="preserve">6.76250791549683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90396404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79444980621338</t>
+    <t xml:space="preserve">6.90396356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79444932937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406175613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46590709686279</t>
+    <t xml:space="preserve">6.69406127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46590662002563</t>
   </si>
   <si>
     <t xml:space="preserve">6.48872232437134</t>
@@ -3977,16 +3977,16 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260562896729</t>
+    <t xml:space="preserve">6.53891658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260515213013</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2605676651001</t>
+    <t xml:space="preserve">6.26056718826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -3995,34 +3995,34 @@
     <t xml:space="preserve">6.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29250907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51153802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46134376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474130630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58454751968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.56173181533813</t>
+    <t xml:space="preserve">6.29250955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51153755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46134328842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474082946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58454704284668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.56173133850098</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64843034744263</t>
+    <t xml:space="preserve">6.64843082427979</t>
   </si>
   <si>
     <t xml:space="preserve">6.80813884735107</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92677927017212</t>
+    <t xml:space="preserve">6.92677974700928</t>
   </si>
   <si>
     <t xml:space="preserve">6.83551740646362</t>
@@ -4031,34 +4031,34 @@
     <t xml:space="preserve">6.81726503372192</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4059042930603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3602728843689</t>
+    <t xml:space="preserve">7.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36027336120605</t>
   </si>
   <si>
     <t xml:space="preserve">7.17318677902222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19143867492676</t>
+    <t xml:space="preserve">7.19143915176392</t>
   </si>
   <si>
     <t xml:space="preserve">6.94046831130981</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02260446548462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01347780227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99978876113892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82182788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.02260398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01347827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99978923797607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82182836532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4076,10 +4076,10 @@
     <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35046482086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21357250213623</t>
+    <t xml:space="preserve">8.35046577453613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21357154846191</t>
   </si>
   <si>
     <t xml:space="preserve">7.90784454345703</t>
@@ -4091,10 +4091,10 @@
     <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89415502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49260330200195</t>
+    <t xml:space="preserve">7.89415597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49260282516479</t>
   </si>
   <si>
     <t xml:space="preserve">7.37396240234375</t>
@@ -4106,31 +4106,31 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910804748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5929913520813</t>
+    <t xml:space="preserve">7.52910757064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59299087524414</t>
   </si>
   <si>
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21037292480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04610204696655</t>
+    <t xml:space="preserve">6.48415899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21037340164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27425718307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0506649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.73581123352051</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">6.34270286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.392897605896</t>
+    <t xml:space="preserve">6.39289712905884</t>
   </si>
   <si>
     <t xml:space="preserve">6.28794574737549</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.27881956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4172,19 +4172,19 @@
     <t xml:space="preserve">6.54347896575928</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57085800170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47959613800049</t>
+    <t xml:space="preserve">6.57085752487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47959566116333</t>
   </si>
   <si>
     <t xml:space="preserve">6.51610040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65755701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79901218414307</t>
+    <t xml:space="preserve">6.65755653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79901266098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4193,19 +4193,19 @@
     <t xml:space="preserve">7.02716732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84008026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57542085647583</t>
+    <t xml:space="preserve">6.84008073806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57542133331299</t>
   </si>
   <si>
     <t xml:space="preserve">6.68949794769287</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83095455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.83095407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4214,13 +4214,13 @@
     <t xml:space="preserve">7.10017728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28726387023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93978691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17706775665283</t>
+    <t xml:space="preserve">7.2872633934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93978595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17706680297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.12230968475342</t>
@@ -4229,10 +4229,10 @@
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7663893699646</t>
+    <t xml:space="preserve">7.69794273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76638889312744</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7709527015686</t>
+    <t xml:space="preserve">7.77095222473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9169716835022</t>
+    <t xml:space="preserve">7.91697120666504</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4256,10 +4256,10 @@
     <t xml:space="preserve">7.72075796127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57017517089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62949514389038</t>
+    <t xml:space="preserve">7.57017612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
@@ -4274,7 +4274,7 @@
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1777491569519</t>
+    <t xml:space="preserve">7.17774963378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4560980796814</t>
+    <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.46978807449341</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959360122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38696956634521</t>
+    <t xml:space="preserve">7.79376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959264755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38697052001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4319,28 +4319,28 @@
     <t xml:space="preserve">8.94366836547852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68813419342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66531848907471</t>
+    <t xml:space="preserve">8.68813514709473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66531944274902</t>
   </si>
   <si>
     <t xml:space="preserve">8.82959079742432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8067741394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9801721572876</t>
+    <t xml:space="preserve">8.80677509307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98017311096191</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347457885742</t>
+    <t xml:space="preserve">8.84327983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347267150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4349,19 +4349,19 @@
     <t xml:space="preserve">8.7292013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71094989776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72463893890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51473617553711</t>
+    <t xml:space="preserve">8.7109489440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72463989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51473712921143</t>
   </si>
   <si>
     <t xml:space="preserve">8.41891193389893</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40978527069092</t>
+    <t xml:space="preserve">8.40978622436523</t>
   </si>
   <si>
     <t xml:space="preserve">8.44172668457031</t>
@@ -4376,25 +4376,25 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949398040771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00367069244385</t>
+    <t xml:space="preserve">8.24551486968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949588775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00366973876953</t>
   </si>
   <si>
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68881607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085519790649</t>
+    <t xml:space="preserve">7.83483505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6888165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085567474365</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4403,7 +4403,7 @@
     <t xml:space="preserve">8.05386352539062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97172784805298</t>
+    <t xml:space="preserve">7.97172880172729</t>
   </si>
   <si>
     <t xml:space="preserve">7.92153406143188</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580589294434</t>
+    <t xml:space="preserve">8.09493255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580493927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716499328613</t>
+    <t xml:space="preserve">7.96716547012329</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4433,28 +4433,28 @@
     <t xml:space="preserve">7.3283314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21425437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35114765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11842918395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01804113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00435209274292</t>
+    <t xml:space="preserve">7.2142539024353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35114717483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24163293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11842966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01804161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00435161590576</t>
   </si>
   <si>
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745929718018</t>
+    <t xml:space="preserve">6.86745882034302</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">6.95415782928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74881839752197</t>
+    <t xml:space="preserve">6.74881887435913</t>
   </si>
   <si>
     <t xml:space="preserve">6.73512935638428</t>
@@ -4487,10 +4487,10 @@
     <t xml:space="preserve">6.62561511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62105226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43852758407593</t>
+    <t xml:space="preserve">6.62105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43852806091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50606966018677</t>
+    <t xml:space="preserve">6.50607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4532,28 +4532,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.677659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812562942505</t>
+    <t xml:space="preserve">6.67765855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86354637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924697875977</t>
+    <t xml:space="preserve">6.92550897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8635458946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924745559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6156964302063</t>
+    <t xml:space="preserve">6.61569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4568,19 +4568,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887351989746</t>
+    <t xml:space="preserve">6.44887399673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279872894287</t>
+    <t xml:space="preserve">6.57279920578003</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541585922241</t>
+    <t xml:space="preserve">6.31541538238525</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214492797852</t>
+    <t xml:space="preserve">6.38214445114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4613,7 +4613,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915433883667</t>
+    <t xml:space="preserve">6.23915386199951</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4634,22 +4634,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999631881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7863507270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167762756348</t>
+    <t xml:space="preserve">5.60999584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74821996688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78635120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167810440063</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803298950195</t>
+    <t xml:space="preserve">6.05803251266479</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4658,13 +4658,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878087997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401393890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597654342651</t>
+    <t xml:space="preserve">5.83878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653745651245</t>
+    <t xml:space="preserve">5.98653793334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4682,13 +4682,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26298570632935</t>
+    <t xml:space="preserve">6.2629861831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728509902954</t>
+    <t xml:space="preserve">6.27728462219238</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4709,10 +4709,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532321929932</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532274246216</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4730,7 +4730,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859367370605</t>
+    <t xml:space="preserve">5.63859415054321</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7720513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78158473968506</t>
+    <t xml:space="preserve">5.68625736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77205181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476182937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7815842628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4760,10 +4760,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541635513306</t>
+    <t xml:space="preserve">5.42887449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541683197021</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4775,16 +4775,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18102407455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943565368652</t>
+    <t xml:space="preserve">5.1810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943517684937</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812732696533</t>
+    <t xml:space="preserve">5.13812685012817</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4799,19 +4799,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336061477661</t>
+    <t xml:space="preserve">5.64336013793945</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71962213516235</t>
+    <t xml:space="preserve">5.7196216583252</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027618408203</t>
+    <t xml:space="preserve">5.40027666091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4826,13 +4826,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569692611694</t>
+    <t xml:space="preserve">5.59569644927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775241851807</t>
+    <t xml:space="preserve">5.75775289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4841,7 +4841,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569667816162</t>
+    <t xml:space="preserve">6.10569620132446</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4850,7 +4850,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382743835449</t>
+    <t xml:space="preserve">6.14382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4862,61 +4862,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635047912598</t>
+    <t xml:space="preserve">6.24868679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4679388999939</t>
+    <t xml:space="preserve">6.41074323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46793937683105</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896760940552</t>
+    <t xml:space="preserve">6.03896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177146911621</t>
+    <t xml:space="preserve">5.98177099227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644456863403</t>
+    <t xml:space="preserve">5.8530797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420066833496</t>
+    <t xml:space="preserve">6.03420114517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79111671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7768177986145</t>
+    <t xml:space="preserve">5.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7911171913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77681827545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4928,28 +4928,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186460494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69578981399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5194354057312</t>
+    <t xml:space="preserve">5.53850030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51943492889404</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560308456421</t>
+    <t xml:space="preserve">5.49560356140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410875320435</t>
+    <t xml:space="preserve">4.91410827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4973,22 +4973,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354711532593</t>
+    <t xml:space="preserve">5.33354759216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691236495972</t>
+    <t xml:space="preserve">5.36691188812256</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457557678223</t>
+    <t xml:space="preserve">5.67195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457509994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5012,7 +5012,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438884735107</t>
+    <t xml:space="preserve">5.21438837051392</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44317388534546</t>
+    <t xml:space="preserve">5.4431734085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5039,16 +5039,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709909439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027545928955</t>
+    <t xml:space="preserve">5.56709861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027593612671</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86261224746704</t>
+    <t xml:space="preserve">5.8626127243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -5757,6 +5757,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.40000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34000015258789</t>
   </si>
 </sst>
 </file>
@@ -71459,7 +71462,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6912615741</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>65331</v>
@@ -71480,6 +71483,32 @@
         <v>1914</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6910185185</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>64604</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>4.46000003814697</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>4.32999992370605</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>4.40999984741211</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1915</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -47,49 +47,49 @@
     <t xml:space="preserve">12.784628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7767143249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758968353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930105209351</t>
+    <t xml:space="preserve">12.7767133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758987426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930114746094</t>
   </si>
   <si>
     <t xml:space="preserve">11.874267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2700777053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233945846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746189117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125690460205</t>
+    <t xml:space="preserve">12.2700786590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233964920044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746170043945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075616836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125699996948</t>
   </si>
   <si>
     <t xml:space="preserve">12.6738033294678</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0563402175903</t>
+    <t xml:space="preserve">12.0563411712646</t>
   </si>
   <si>
     <t xml:space="preserve">12.3729887008667</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1750831604004</t>
+    <t xml:space="preserve">12.1750822067261</t>
   </si>
   <si>
     <t xml:space="preserve">12.3413238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1909151077271</t>
+    <t xml:space="preserve">12.1909160614014</t>
   </si>
   <si>
     <t xml:space="preserve">11.7713575363159</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">11.9850959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1380634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4626264572144</t>
+    <t xml:space="preserve">11.1380643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.462628364563</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063985824585</t>
@@ -119,133 +119,133 @@
     <t xml:space="preserve">11.5417890548706</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3597164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584356307983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180406570435</t>
+    <t xml:space="preserve">11.3597173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.858437538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180416107178</t>
   </si>
   <si>
     <t xml:space="preserve">11.7159452438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8346872329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763620376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3992967605591</t>
+    <t xml:space="preserve">11.8346891403198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6763639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684474945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3992986679077</t>
   </si>
   <si>
     <t xml:space="preserve">11.1855611801147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9692621231079</t>
+    <t xml:space="preserve">11.9692630767822</t>
   </si>
   <si>
     <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284009933472</t>
+    <t xml:space="preserve">12.4284019470215</t>
   </si>
   <si>
     <t xml:space="preserve">12.2304964065552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1117525100708</t>
+    <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
     <t xml:space="preserve">12.1513357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196708679199</t>
+    <t xml:space="preserve">12.1196718215942</t>
   </si>
   <si>
     <t xml:space="preserve">12.8242092132568</t>
   </si>
   <si>
-    <t xml:space="preserve">12.982533454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.950870513916</t>
+    <t xml:space="preserve">12.9825344085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508695602417</t>
   </si>
   <si>
     <t xml:space="preserve">13.1408567428589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2754335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704252243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387632369995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575061798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5762453079224</t>
+    <t xml:space="preserve">13.2754316329956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704271316528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762481689453</t>
   </si>
   <si>
     <t xml:space="preserve">13.5999956130981</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3625106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7529649734497</t>
+    <t xml:space="preserve">13.3625087738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752965927124</t>
   </si>
   <si>
     <t xml:space="preserve">13.1171092987061</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1091928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1962718963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9904489517212</t>
+    <t xml:space="preserve">13.1091918945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.196270942688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9904508590698</t>
   </si>
   <si>
     <t xml:space="preserve">13.0221147537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933618545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975507736206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6025562286377</t>
+    <t xml:space="preserve">13.0933609008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975526809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.602557182312</t>
   </si>
   <si>
     <t xml:space="preserve">12.6500539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8637924194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.467981338501</t>
+    <t xml:space="preserve">12.8637914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
   </si>
   <si>
     <t xml:space="preserve">12.3650722503662</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">12.5788087844849</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7286968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493883132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091566085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9884691238403</t>
+    <t xml:space="preserve">12.7286977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.988468170166</t>
   </si>
   <si>
     <t xml:space="preserve">11.9241018295288</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2217998504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.22984790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942152023315</t>
+    <t xml:space="preserve">12.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942161560059</t>
   </si>
   <si>
     <t xml:space="preserve">12.2620306015015</t>
@@ -284,16 +284,16 @@
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126045227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8091564178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735237121582</t>
+    <t xml:space="preserve">12.4953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126035690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091554641724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735246658325</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263977050781</t>
@@ -302,25 +302,25 @@
     <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654766082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172035217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103065490723</t>
+    <t xml:space="preserve">12.865478515625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666286468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103084564209</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390451431274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4011144638062</t>
+    <t xml:space="preserve">11.4011154174805</t>
   </si>
   <si>
     <t xml:space="preserve">11.2884712219238</t>
@@ -329,34 +329,34 @@
     <t xml:space="preserve">10.8781280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0792760848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022644042969</t>
+    <t xml:space="preserve">11.0792770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689277648926</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6103096008301</t>
+    <t xml:space="preserve">11.6103105545044</t>
   </si>
   <si>
     <t xml:space="preserve">11.3689308166504</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4896192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7574377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735321044922</t>
+    <t xml:space="preserve">11.4896202087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.757438659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735330581665</t>
   </si>
   <si>
     <t xml:space="preserve">10.45973777771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0229530334473</t>
+    <t xml:space="preserve">11.0229539871216</t>
   </si>
   <si>
     <t xml:space="preserve">11.6424932479858</t>
@@ -365,139 +365,139 @@
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321472167969</t>
+    <t xml:space="preserve">11.2321500778198</t>
   </si>
   <si>
     <t xml:space="preserve">10.9827241897583</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9264030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229518890381</t>
+    <t xml:space="preserve">10.92640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229528427124</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700807571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8919172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.875825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1896190643311</t>
+    <t xml:space="preserve">11.5700788497925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.891918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8758249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1896171569824</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309968948364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896160125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0505361557007</t>
+    <t xml:space="preserve">12.8896169662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
     <t xml:space="preserve">12.994213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1229486465454</t>
+    <t xml:space="preserve">13.1229476928711</t>
   </si>
   <si>
     <t xml:space="preserve">13.1551322937012</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746736526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482370376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.249382019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194955825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459320068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8551292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643203735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206424713135</t>
+    <t xml:space="preserve">12.9861669540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0746726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482351303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459329605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919116973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643232345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206443786621</t>
   </si>
   <si>
     <t xml:space="preserve">14.6034030914307</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4022541046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137493133545</t>
+    <t xml:space="preserve">14.4022560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137521743774</t>
   </si>
   <si>
     <t xml:space="preserve">14.6516780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7562780380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183462142944</t>
+    <t xml:space="preserve">14.756275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183452606201</t>
   </si>
   <si>
     <t xml:space="preserve">15.1505298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">15.126389503479</t>
+    <t xml:space="preserve">15.1263904571533</t>
   </si>
   <si>
     <t xml:space="preserve">15.08616065979</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0459337234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562740325928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597202301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873086929321</t>
+    <t xml:space="preserve">15.0459308624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.424090385437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562749862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873106002808</t>
   </si>
   <si>
     <t xml:space="preserve">14.8689203262329</t>
@@ -506,112 +506,112 @@
     <t xml:space="preserve">14.7240934371948</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
+    <t xml:space="preserve">14.8367357254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884607315063</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930578231812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4884567260742</t>
+    <t xml:space="preserve">15.4884586334229</t>
   </si>
   <si>
     <t xml:space="preserve">15.4401845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045511245728</t>
+    <t xml:space="preserve">15.2148952484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045530319214</t>
   </si>
   <si>
     <t xml:space="preserve">15.3919048309326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2551259994507</t>
+    <t xml:space="preserve">15.2551250457764</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666193008423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0137462615967</t>
+    <t xml:space="preserve">15.5286865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.013747215271</t>
   </si>
   <si>
     <t xml:space="preserve">14.8850116729736</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1988019943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.367769241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034000396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654750823975</t>
+    <t xml:space="preserve">15.198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275384902954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677701950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3033990859985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654731750488</t>
   </si>
   <si>
     <t xml:space="preserve">15.2470808029175</t>
   </si>
   <si>
-    <t xml:space="preserve">14.828688621521</t>
+    <t xml:space="preserve">14.8286905288696</t>
   </si>
   <si>
     <t xml:space="preserve">14.5390357971191</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5551271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.112603187561</t>
+    <t xml:space="preserve">14.5551300048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1125993728638</t>
   </si>
   <si>
     <t xml:space="preserve">14.4263925552368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2815647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827156066895</t>
+    <t xml:space="preserve">14.2815656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827127456665</t>
   </si>
   <si>
     <t xml:space="preserve">14.2171974182129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4102993011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631761550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585742950439</t>
+    <t xml:space="preserve">14.4103012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5631742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585771560669</t>
   </si>
   <si>
     <t xml:space="preserve">14.3057041168213</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1045551300049</t>
+    <t xml:space="preserve">14.1045532226562</t>
   </si>
   <si>
     <t xml:space="preserve">14.321795463562</t>
@@ -620,10 +620,10 @@
     <t xml:space="preserve">13.951681137085</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045572280884</t>
+    <t xml:space="preserve">13.6781196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045562744141</t>
   </si>
   <si>
     <t xml:space="preserve">13.3643283843994</t>
@@ -632,106 +632,106 @@
     <t xml:space="preserve">13.1873159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9539833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3160524368286</t>
+    <t xml:space="preserve">12.9539842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3160514831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.5896139144897</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7746715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9114513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011060714722</t>
+    <t xml:space="preserve">13.7746725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9114532470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011051177979</t>
   </si>
   <si>
     <t xml:space="preserve">13.9999580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9815654754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378847122192</t>
+    <t xml:space="preserve">14.9815626144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378856658936</t>
   </si>
   <si>
     <t xml:space="preserve">14.7160472869873</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8447818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9171943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631683349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5367336273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3838663101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091480255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045518875122</t>
+    <t xml:space="preserve">14.8447847366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.917197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631711959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528268814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.536732673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.464319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045528411865</t>
   </si>
   <si>
     <t xml:space="preserve">15.4079990386963</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068500518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263883590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.890754699707</t>
+    <t xml:space="preserve">15.110297203064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068490982056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907566070557</t>
   </si>
   <si>
     <t xml:space="preserve">15.8988018035889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.947078704834</t>
+    <t xml:space="preserve">15.9470767974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.0114440917969</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5344333648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.582706451416</t>
+    <t xml:space="preserve">16.3493747711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.301097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5344314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3332824707031</t>
   </si>
   <si>
-    <t xml:space="preserve">16.453971862793</t>
+    <t xml:space="preserve">16.4539737701416</t>
   </si>
   <si>
     <t xml:space="preserve">16.1723651885986</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">16.1562728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9792633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700662612915</t>
+    <t xml:space="preserve">15.9792613983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700691223145</t>
   </si>
   <si>
     <t xml:space="preserve">16.0919075012207</t>
   </si>
   <si>
-    <t xml:space="preserve">16.003396987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436267852783</t>
+    <t xml:space="preserve">16.0034008026123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0436305999756</t>
   </si>
   <si>
     <t xml:space="preserve">16.4781093597412</t>
@@ -776,34 +776,34 @@
     <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470703125</t>
+    <t xml:space="preserve">18.3850040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470664978027</t>
   </si>
   <si>
     <t xml:space="preserve">18.7229309082031</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0206336975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2700595855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3907451629639</t>
+    <t xml:space="preserve">19.0206317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.270055770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3907432556152</t>
   </si>
   <si>
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.752815246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033912658691</t>
+    <t xml:space="preserve">19.4470653533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033855438232</t>
   </si>
   <si>
     <t xml:space="preserve">19.6079864501953</t>
@@ -812,28 +812,28 @@
     <t xml:space="preserve">19.6321220397949</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7125835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.382698059082</t>
+    <t xml:space="preserve">19.7125854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3827018737793</t>
   </si>
   <si>
     <t xml:space="preserve">19.5838470458984</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3102855682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5436229705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631614685059</t>
+    <t xml:space="preserve">19.3102874755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5436191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631576538086</t>
   </si>
   <si>
     <t xml:space="preserve">19.0689086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0769519805908</t>
+    <t xml:space="preserve">19.0769538879395</t>
   </si>
   <si>
     <t xml:space="preserve">18.8355751037598</t>
@@ -842,25 +842,25 @@
     <t xml:space="preserve">19.0286769866943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5620136260986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5056915283203</t>
+    <t xml:space="preserve">18.972354888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.56201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056896209717</t>
   </si>
   <si>
     <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1654567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171806335449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2597064971924</t>
+    <t xml:space="preserve">19.1654586791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171768188477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585582733154</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">21.1818714141846</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9213676452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841827392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666988372803</t>
+    <t xml:space="preserve">20.9213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841846466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7667007446289</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5726203918457</t>
+    <t xml:space="preserve">21.5726165771484</t>
   </si>
   <si>
     <t xml:space="preserve">20.5387630462646</t>
@@ -896,28 +896,28 @@
     <t xml:space="preserve">20.5550403594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4899158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922309875488</t>
+    <t xml:space="preserve">20.4899196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922271728516</t>
   </si>
   <si>
     <t xml:space="preserve">20.3271045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3515243530273</t>
+    <t xml:space="preserve">20.3515281677246</t>
   </si>
   <si>
     <t xml:space="preserve">20.5143394470215</t>
   </si>
   <si>
-    <t xml:space="preserve">20.986499786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9376487731934</t>
+    <t xml:space="preserve">20.9864959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.937650680542</t>
   </si>
   <si>
     <t xml:space="preserve">21.1248874664307</t>
@@ -932,124 +932,124 @@
     <t xml:space="preserve">20.815544128418</t>
   </si>
   <si>
-    <t xml:space="preserve">21.15744972229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3189640045166</t>
+    <t xml:space="preserve">21.1574459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2945423126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957431793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.318962097168</t>
   </si>
   <si>
     <t xml:space="preserve">19.8386688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828895568848</t>
+    <t xml:space="preserve">20.0828857421875</t>
   </si>
   <si>
     <t xml:space="preserve">20.1480102539062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9851989746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317310333252</t>
+    <t xml:space="preserve">19.985200881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317329406738</t>
   </si>
   <si>
     <t xml:space="preserve">20.3678112030029</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7259922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770603179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3583717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1874217987061</t>
+    <t xml:space="preserve">20.7259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.310827255249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770584106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3583736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1874198913574</t>
   </si>
   <si>
     <t xml:space="preserve">18.9757633209229</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8048133850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.633861541748</t>
+    <t xml:space="preserve">18.8048114776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7071228027344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338577270508</t>
   </si>
   <si>
     <t xml:space="preserve">19.1304340362549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4804801940918</t>
+    <t xml:space="preserve">19.4804840087891</t>
   </si>
   <si>
     <t xml:space="preserve">19.5293254852295</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2049961090088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7816867828369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805763244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7829818725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.677152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1655883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2795562744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597629547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0434799194336</t>
+    <t xml:space="preserve">20.2049942016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7816829681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805725097656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050903320312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6771507263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1655864715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2795543670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597591400146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.043478012085</t>
   </si>
   <si>
     <t xml:space="preserve">20.6852893829346</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1004638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319156646729</t>
+    <t xml:space="preserve">21.1004619598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319194793701</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202610015869</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">21.922664642334</t>
   </si>
   <si>
-    <t xml:space="preserve">21.784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4993534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935260772705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7761344909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6214618682861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169277191162</t>
+    <t xml:space="preserve">21.7842750549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4993553161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935241699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7761325836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6214599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7110118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169296264648</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.630895614624</t>
+    <t xml:space="preserve">22.6308975219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.0542106628418</t>
@@ -1094,85 +1094,85 @@
     <t xml:space="preserve">22.9890842437744</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2007389068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1681785583496</t>
+    <t xml:space="preserve">23.2007427215576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.168176651001</t>
   </si>
   <si>
     <t xml:space="preserve">23.4693813323975</t>
   </si>
   <si>
-    <t xml:space="preserve">23.86012840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659576416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648509979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008331298828</t>
+    <t xml:space="preserve">23.8601303100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298831939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310802459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5996284484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159133911133</t>
+    <t xml:space="preserve">23.599630355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159114837646</t>
   </si>
   <si>
     <t xml:space="preserve">23.9822368621826</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2346000671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4394092559814</t>
+    <t xml:space="preserve">24.23459815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4394111633301</t>
   </si>
   <si>
     <t xml:space="preserve">24.9916763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0567989349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0079517364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8777046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6660499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6497707366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999053955078</t>
+    <t xml:space="preserve">25.0568008422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0079555511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.87770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.666051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999092102051</t>
   </si>
   <si>
     <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4801120758057</t>
+    <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789093017578</t>
@@ -1181,16 +1181,16 @@
     <t xml:space="preserve">24.1613330841064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5602207183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7474575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5765056610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4556884765625</t>
+    <t xml:space="preserve">24.5602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7474555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5765075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4556903839111</t>
   </si>
   <si>
     <t xml:space="preserve">26.2778911590576</t>
@@ -1199,16 +1199,16 @@
     <t xml:space="preserve">25.9848308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1082305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7676258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3850135803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9210033416748</t>
+    <t xml:space="preserve">27.1082324981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7676239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3850116729736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9209995269775</t>
   </si>
   <si>
     <t xml:space="preserve">27.5071258544922</t>
@@ -1220,34 +1220,34 @@
     <t xml:space="preserve">26.6930618286133</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2765960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032348632812</t>
+    <t xml:space="preserve">25.2765979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032386779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.6172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2440357208252</t>
+    <t xml:space="preserve">24.584644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2440319061279</t>
   </si>
   <si>
     <t xml:space="preserve">24.8451442718506</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7393188476562</t>
+    <t xml:space="preserve">24.739315032959</t>
   </si>
   <si>
     <t xml:space="preserve">25.1951904296875</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6429233551025</t>
+    <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
     <t xml:space="preserve">25.5859394073486</t>
@@ -1256,22 +1256,22 @@
     <t xml:space="preserve">25.7243309020996</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6917686462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5452346801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7568893432617</t>
+    <t xml:space="preserve">25.6917667388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5452365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3172969818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3987045288086</t>
+    <t xml:space="preserve">25.3172988891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987083435059</t>
   </si>
   <si>
     <t xml:space="preserve">25.512674331665</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">25.3661422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0242385864258</t>
+    <t xml:space="preserve">25.0242366790771</t>
   </si>
   <si>
     <t xml:space="preserve">25.3824253082275</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">25.0893611907959</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7148933410645</t>
+    <t xml:space="preserve">24.7148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
@@ -1313,28 +1313,28 @@
     <t xml:space="preserve">26.7419052124023</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5790958404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6604995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4976863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127647399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941703796387</t>
+    <t xml:space="preserve">26.5790939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.393159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6605014801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022186279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2941741943359</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826099395752</t>
@@ -1343,43 +1343,43 @@
     <t xml:space="preserve">27.3117485046387</t>
   </si>
   <si>
-    <t xml:space="preserve">27.8815937042236</t>
+    <t xml:space="preserve">27.881591796875</t>
   </si>
   <si>
     <t xml:space="preserve">27.2303428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8233108520508</t>
+    <t xml:space="preserve">26.8233127593994</t>
   </si>
   <si>
     <t xml:space="preserve">26.6197986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1720638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730819702148</t>
+    <t xml:space="preserve">26.1720676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730838775635</t>
   </si>
   <si>
     <t xml:space="preserve">24.6253490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8519878387451</t>
+    <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.974100112915</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615196228027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.358003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137847900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358913421631</t>
+    <t xml:space="preserve">25.5615177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3579978942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137866973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358932495117</t>
   </si>
   <si>
     <t xml:space="preserve">23.3635540008545</t>
@@ -1391,7 +1391,7 @@
     <t xml:space="preserve">26.2534694671631</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6891784667969</t>
+    <t xml:space="preserve">23.6891803741455</t>
   </si>
   <si>
     <t xml:space="preserve">23.5670700073242</t>
@@ -1400,25 +1400,25 @@
     <t xml:space="preserve">20.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6364498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7178554534912</t>
+    <t xml:space="preserve">20.6364517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7178573608398</t>
   </si>
   <si>
     <t xml:space="preserve">19.7002792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062911987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354297637939</t>
+    <t xml:space="preserve">20.4736366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062892913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354335784912</t>
   </si>
   <si>
     <t xml:space="preserve">22.4273834228516</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505100250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
+    <t xml:space="preserve">20.8806686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3283977508545</t>
   </si>
   <si>
     <t xml:space="preserve">21.6947269439697</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">22.4680881500244</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1831665039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5901966094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0203533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.3459758758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1600379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7123012542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077690124512</t>
+    <t xml:space="preserve">22.1831645965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5901947021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0203514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3459777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1600360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7123031616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077709197998</t>
   </si>
   <si>
     <t xml:space="preserve">25.805736541748</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">24.7067546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3811302185059</t>
+    <t xml:space="preserve">24.3811283111572</t>
   </si>
   <si>
     <t xml:space="preserve">24.2183170318604</t>
@@ -1478,22 +1478,22 @@
     <t xml:space="preserve">24.1776161193848</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2997226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7881622314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7053966522217</t>
+    <t xml:space="preserve">24.2997264862061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7881603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
     <t xml:space="preserve">24.1260395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6640090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123058319092</t>
+    <t xml:space="preserve">24.6640129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123077392578</t>
   </si>
   <si>
     <t xml:space="preserve">25.2019863128662</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">25.4088973999023</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7813415527344</t>
+    <t xml:space="preserve">25.7813377380371</t>
   </si>
   <si>
     <t xml:space="preserve">25.7399597167969</t>
@@ -1511,49 +1511,49 @@
     <t xml:space="preserve">25.3261318206787</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2779369354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1469688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951656341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4916667938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5330486297607</t>
+    <t xml:space="preserve">26.2779331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1469669342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.940055847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951694488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.491662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5330467224121</t>
   </si>
   <si>
     <t xml:space="preserve">25.0778369903564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3675155639648</t>
+    <t xml:space="preserve">25.3675136566162</t>
   </si>
   <si>
     <t xml:space="preserve">25.6985740661621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2847499847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6571922302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227233886719</t>
+    <t xml:space="preserve">25.2847480773926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6571941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1537818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227252960205</t>
   </si>
   <si>
     <t xml:space="preserve">25.9468727111816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0710182189941</t>
+    <t xml:space="preserve">26.0710201263428</t>
   </si>
   <si>
     <t xml:space="preserve">25.9054889678955</t>
@@ -1562,16 +1562,16 @@
     <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0642051696777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.022819519043</t>
+    <t xml:space="preserve">27.0642013549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0228214263916</t>
   </si>
   <si>
     <t xml:space="preserve">24.2501850128174</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6294498443604</t>
+    <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
     <t xml:space="preserve">23.7535972595215</t>
@@ -1580,37 +1580,37 @@
     <t xml:space="preserve">24.0432720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8363571166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3811550140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.794979095459</t>
+    <t xml:space="preserve">23.8363628387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3811531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7949771881104</t>
   </si>
   <si>
     <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9191265106201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2088031768799</t>
+    <t xml:space="preserve">23.9191246032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2088050842285</t>
   </si>
   <si>
     <t xml:space="preserve">24.332950592041</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262279510498</t>
+    <t xml:space="preserve">25.4502830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262260437012</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0296382904053</t>
+    <t xml:space="preserve">26.0296363830566</t>
   </si>
   <si>
     <t xml:space="preserve">26.5676097869873</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">26.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503753662109</t>
+    <t xml:space="preserve">26.6503772735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.3606986999512</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">21.7258491516113</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4361705780029</t>
+    <t xml:space="preserve">21.4361724853516</t>
   </si>
   <si>
     <t xml:space="preserve">21.8913822174072</t>
@@ -1655,130 +1655,130 @@
     <t xml:space="preserve">20.7740516662598</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6430854797363</t>
+    <t xml:space="preserve">21.6430835723877</t>
   </si>
   <si>
     <t xml:space="preserve">21.4775562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1051120758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8154315948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6981048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636341094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360801696777</t>
+    <t xml:space="preserve">21.105110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8154335021973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6981029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636360168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360782623291</t>
   </si>
   <si>
     <t xml:space="preserve">21.808614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9395771026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9327602386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0569114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9259433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2638206481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0014190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4634475708008</t>
+    <t xml:space="preserve">20.9395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9327621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0569076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9259471893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.263822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0014171600342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4634456634521</t>
   </si>
   <si>
     <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2083339691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.498010635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7049236297607</t>
+    <t xml:space="preserve">17.6703586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2083320617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4980087280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
     <t xml:space="preserve">18.8290710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6221580505371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8704528808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3670425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5325717926025</t>
+    <t xml:space="preserve">18.6221561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8704509735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3670444488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5325756072998</t>
   </si>
   <si>
     <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0773658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.118745803833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0427989959717</t>
+    <t xml:space="preserve">19.0773639678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187496185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0428009033203</t>
   </si>
   <si>
     <t xml:space="preserve">17.7945041656494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8427066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531204223633</t>
+    <t xml:space="preserve">16.8427085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531242370605</t>
   </si>
   <si>
     <t xml:space="preserve">17.1737651824951</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3806781768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9668521881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8840885162354</t>
+    <t xml:space="preserve">17.3806800842285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.966854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5530300140381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2497138977051</t>
+    <t xml:space="preserve">18.2497100830078</t>
   </si>
   <si>
     <t xml:space="preserve">18.4152450561523</t>
@@ -1787,13 +1787,13 @@
     <t xml:space="preserve">19.1601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4084281921387</t>
+    <t xml:space="preserve">19.40842628479</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4498100280762</t>
+    <t xml:space="preserve">19.4498062133789</t>
   </si>
   <si>
     <t xml:space="preserve">19.9050159454346</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">20.5257549285889</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6499042510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1119289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2842769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0291633605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567211151123</t>
+    <t xml:space="preserve">20.6499061584473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3188419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2842788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0291652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567230224609</t>
   </si>
   <si>
     <t xml:space="preserve">19.9463996887207</t>
@@ -1841,25 +1841,25 @@
     <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.594409942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4868183135986</t>
+    <t xml:space="preserve">16.5364761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5944118499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.48681640625</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910034179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2151470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3310203552246</t>
+    <t xml:space="preserve">17.0910015106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2151489257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3310241699219</t>
   </si>
   <si>
     <t xml:space="preserve">17.3641262054443</t>
@@ -1874,13 +1874,13 @@
     <t xml:space="preserve">18.3407554626465</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0593547821045</t>
+    <t xml:space="preserve">18.0593528747559</t>
   </si>
   <si>
     <t xml:space="preserve">17.645528793335</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2482585906982</t>
+    <t xml:space="preserve">17.2482566833496</t>
   </si>
   <si>
     <t xml:space="preserve">17.6289749145508</t>
@@ -1904,10 +1904,10 @@
     <t xml:space="preserve">18.2248859405518</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861320495605</t>
+    <t xml:space="preserve">17.7614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861358642578</t>
   </si>
   <si>
     <t xml:space="preserve">16.6192398071289</t>
@@ -1919,58 +1919,58 @@
     <t xml:space="preserve">15.5101890563965</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701711654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8397884368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.674259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177816390991</t>
+    <t xml:space="preserve">15.4274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.270170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6742601394653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177835464478</t>
   </si>
   <si>
     <t xml:space="preserve">16.0233325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9322900772095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549783706665</t>
+    <t xml:space="preserve">15.9322910308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0632572174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549802780151</t>
   </si>
   <si>
     <t xml:space="preserve">15.0467014312744</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6659851074219</t>
+    <t xml:space="preserve">14.6659822463989</t>
   </si>
   <si>
     <t xml:space="preserve">14.8232364654541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3255777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426065444946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7125539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614675521851</t>
+    <t xml:space="preserve">15.3255767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3426036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7125549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614665985107</t>
   </si>
   <si>
     <t xml:space="preserve">14.6444396972656</t>
@@ -1979,16 +1979,16 @@
     <t xml:space="preserve">14.806206703186</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5422687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.666145324707</t>
+    <t xml:space="preserve">14.5422677993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661443710327</t>
   </si>
   <si>
     <t xml:space="preserve">14.9083786010742</t>
@@ -1997,49 +1997,49 @@
     <t xml:space="preserve">14.5252389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741544723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2017002105713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3890132904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6018657684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315843582153</t>
+    <t xml:space="preserve">14.4741554260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2016983032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.389012336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6018686294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315853118896</t>
   </si>
   <si>
     <t xml:space="preserve">14.2357559204102</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317499160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507831573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3208990097046</t>
+    <t xml:space="preserve">14.0484457015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.831750869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5507822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.320897102356</t>
   </si>
   <si>
     <t xml:space="preserve">14.7295799255371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0020380020142</t>
+    <t xml:space="preserve">15.0020360946655</t>
   </si>
   <si>
     <t xml:space="preserve">14.4230699539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3379278182983</t>
+    <t xml:space="preserve">14.337926864624</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549566268921</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">13.9462738037109</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6908464431763</t>
+    <t xml:space="preserve">13.6908483505249</t>
   </si>
   <si>
     <t xml:space="preserve">13.7419328689575</t>
@@ -2057,55 +2057,55 @@
     <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821645736694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975257873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0995302200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8866748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8185606002808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225656509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801620483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6227331161499</t>
+    <t xml:space="preserve">13.6312503814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948534011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821655273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0995292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8866729736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8185586929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225666046143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
     <t xml:space="preserve">13.5205631256104</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1799926757812</t>
+    <t xml:space="preserve">13.1799955368042</t>
   </si>
   <si>
     <t xml:space="preserve">13.1544523239136</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2140522003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.166805267334</t>
+    <t xml:space="preserve">13.2140512466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1668033599854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9748163223267</t>
+    <t xml:space="preserve">10.9748153686523</t>
   </si>
   <si>
     <t xml:space="preserve">10.9492721557617</t>
@@ -2120,52 +2120,52 @@
     <t xml:space="preserve">11.1706418991089</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7534446716309</t>
+    <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
     <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.162127494812</t>
+    <t xml:space="preserve">11.1621265411377</t>
   </si>
   <si>
     <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7875022888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7619600296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599575042725</t>
+    <t xml:space="preserve">10.787501335144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7619609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2511072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599555969238</t>
   </si>
   <si>
     <t xml:space="preserve">10.8471012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6683034896851</t>
+    <t xml:space="preserve">10.6683025360107</t>
   </si>
   <si>
     <t xml:space="preserve">10.7279033660889</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5367527008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6644649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6900081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410926818848</t>
+    <t xml:space="preserve">11.3664684295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.53675365448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6644659042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6900091171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410936355591</t>
   </si>
   <si>
     <t xml:space="preserve">11.749608039856</t>
@@ -2174,31 +2174,31 @@
     <t xml:space="preserve">12.1838321685791</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9028625488281</t>
+    <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
     <t xml:space="preserve">11.8177213668823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751512527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476045608521</t>
+    <t xml:space="preserve">11.7751493453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476055145264</t>
   </si>
   <si>
     <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981866836548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898406982422</t>
+    <t xml:space="preserve">11.5026960372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981885910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898416519165</t>
   </si>
   <si>
     <t xml:space="preserve">11.2132129669189</t>
@@ -2213,13 +2213,13 @@
     <t xml:space="preserve">10.6597900390625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0173864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0854988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0514430999756</t>
+    <t xml:space="preserve">11.0173854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0854997634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514421463013</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280698776245</t>
@@ -2234,22 +2234,22 @@
     <t xml:space="preserve">11.2642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6985216140747</t>
+    <t xml:space="preserve">11.6985235214233</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814937591553</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8092079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3247356414795</t>
+    <t xml:space="preserve">11.8092069625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
     <t xml:space="preserve">13.1970233917236</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2395935058594</t>
+    <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
     <t xml:space="preserve">13.5120487213135</t>
@@ -2258,112 +2258,112 @@
     <t xml:space="preserve">13.6738185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.546106338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4145555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8526182174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2187299728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8781595230103</t>
+    <t xml:space="preserve">13.5461053848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4145565032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8526172637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2187280654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8781604766846</t>
   </si>
   <si>
     <t xml:space="preserve">13.7759895324707</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4439344406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8441028594971</t>
+    <t xml:space="preserve">13.4439353942871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8441038131714</t>
   </si>
   <si>
     <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274099349976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254064559937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933542251587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592966079712</t>
+    <t xml:space="preserve">14.6274089813232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.925407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.504373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592956542969</t>
   </si>
   <si>
     <t xml:space="preserve">14.9424352645874</t>
   </si>
   <si>
-    <t xml:space="preserve">14.967978477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870098114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0190658569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467761993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170595169067</t>
+    <t xml:space="preserve">14.9679794311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870088577271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190649032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170623779297</t>
   </si>
   <si>
     <t xml:space="preserve">15.6406021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4618015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656400680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.363471031189</t>
+    <t xml:space="preserve">15.461802482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3634700775146</t>
   </si>
   <si>
     <t xml:space="preserve">14.3294143676758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4826679229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.150616645813</t>
+    <t xml:space="preserve">14.4826698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1506156921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335868835449</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5763263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1165571212769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996967315674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721538543701</t>
+    <t xml:space="preserve">14.5763254165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1165590286255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4911832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721529006958</t>
   </si>
   <si>
     <t xml:space="preserve">13.7078762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292469024658</t>
+    <t xml:space="preserve">13.9292459487915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5035343170166</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">13.3162231445312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5631341934204</t>
+    <t xml:space="preserve">13.563136100769</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375919342041</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">14.406042098999</t>
   </si>
   <si>
-    <t xml:space="preserve">14.269814491272</t>
+    <t xml:space="preserve">14.2698135375977</t>
   </si>
   <si>
     <t xml:space="preserve">14.2953577041626</t>
@@ -2390,37 +2390,37 @@
     <t xml:space="preserve">14.5082130432129</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931858062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.758960723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4183931350708</t>
+    <t xml:space="preserve">14.5167255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761560440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931848526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7589597702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4183921813965</t>
   </si>
   <si>
     <t xml:space="preserve">12.5584573745728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3370866775513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010293960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9880046844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6218929290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.443097114563</t>
+    <t xml:space="preserve">12.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6010284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9880065917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6218948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430952072144</t>
   </si>
   <si>
     <t xml:space="preserve">10.3277349472046</t>
@@ -2444,40 +2444,40 @@
     <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412506103516</t>
+    <t xml:space="preserve">8.31412601470947</t>
   </si>
   <si>
     <t xml:space="preserve">7.96078491210938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66278886795044</t>
+    <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.11020278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00803184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41671466827393</t>
+    <t xml:space="preserve">9.00803279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41671371459961</t>
   </si>
   <si>
     <t xml:space="preserve">9.47631454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57848453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225692749023</t>
+    <t xml:space="preserve">9.5784854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225883483887</t>
   </si>
   <si>
     <t xml:space="preserve">9.46779918670654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16980361938477</t>
+    <t xml:space="preserve">9.09317588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16980266571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.53591346740723</t>
@@ -2492,13 +2492,13 @@
     <t xml:space="preserve">10.089337348938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.131908416748</t>
+    <t xml:space="preserve">10.1319093704224</t>
   </si>
   <si>
     <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75728416442871</t>
+    <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.8764820098877</t>
@@ -2513,13 +2513,13 @@
     <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3192205429077</t>
+    <t xml:space="preserve">10.3192195892334</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299058914185</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9322443008423</t>
+    <t xml:space="preserve">10.9322452545166</t>
   </si>
   <si>
     <t xml:space="preserve">11.1961832046509</t>
@@ -2528,31 +2528,31 @@
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9616231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85945320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78282642364502</t>
+    <t xml:space="preserve">9.96162509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85945415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7828254699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.3060302734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5103702545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51888561248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22940349578857</t>
+    <t xml:space="preserve">9.51037120819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51888465881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
     <t xml:space="preserve">9.26345920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25494384765625</t>
+    <t xml:space="preserve">9.25494480133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.36562919616699</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">8.93140506744385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85477638244629</t>
+    <t xml:space="preserve">8.85477733612061</t>
   </si>
   <si>
     <t xml:space="preserve">9.28048801422119</t>
@@ -2573,46 +2573,46 @@
     <t xml:space="preserve">9.70619773864746</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62957000732422</t>
+    <t xml:space="preserve">9.62957096099854</t>
   </si>
   <si>
     <t xml:space="preserve">9.85093784332275</t>
   </si>
   <si>
-    <t xml:space="preserve">11.187668800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8300733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5405912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254215240479</t>
+    <t xml:space="preserve">11.1876707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8300743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5405902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340793609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6125431060791</t>
   </si>
   <si>
     <t xml:space="preserve">9.9638843536377</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.182391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1998720169067</t>
+    <t xml:space="preserve">10.2435731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1823902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1998710632324</t>
   </si>
   <si>
     <t xml:space="preserve">10.1649103164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0600280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.444598197937</t>
+    <t xml:space="preserve">10.0600271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445991516113</t>
   </si>
   <si>
     <t xml:space="preserve">10.0163269042969</t>
@@ -2624,52 +2624,52 @@
     <t xml:space="preserve">9.72789859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64049625396729</t>
+    <t xml:space="preserve">9.64049530029297</t>
   </si>
   <si>
     <t xml:space="preserve">9.28214454650879</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56183338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41324996948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52687168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49191093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40450859069824</t>
+    <t xml:space="preserve">9.56183242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41324901580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5268726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49191188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40450954437256</t>
   </si>
   <si>
     <t xml:space="preserve">9.15978145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99371719360352</t>
+    <t xml:space="preserve">8.99371814727783</t>
   </si>
   <si>
     <t xml:space="preserve">9.01993751525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90631484985352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57931423187256</t>
+    <t xml:space="preserve">8.9063138961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57931327819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.20348262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36080837249756</t>
+    <t xml:space="preserve">9.36080741882324</t>
   </si>
   <si>
     <t xml:space="preserve">9.18600273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33458709716797</t>
+    <t xml:space="preserve">9.33458805084229</t>
   </si>
   <si>
     <t xml:space="preserve">9.22096347808838</t>
@@ -2678,7 +2678,7 @@
     <t xml:space="preserve">9.44820976257324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29088592529297</t>
+    <t xml:space="preserve">9.29088497161865</t>
   </si>
   <si>
     <t xml:space="preserve">9.01119804382324</t>
@@ -2687,58 +2687,58 @@
     <t xml:space="preserve">10.3484563827515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4358577728271</t>
+    <t xml:space="preserve">10.4358587265015</t>
   </si>
   <si>
     <t xml:space="preserve">10.4271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9777536392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001176834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3186225891113</t>
+    <t xml:space="preserve">10.9777545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001167297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3186235427856</t>
   </si>
   <si>
     <t xml:space="preserve">11.4672079086304</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0826368331909</t>
+    <t xml:space="preserve">11.0826377868652</t>
   </si>
   <si>
     <t xml:space="preserve">10.8903512954712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7942085266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6281433105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5494813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872753143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.226092338562</t>
+    <t xml:space="preserve">10.7942094802856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6281423568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5494823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872743606567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2260932922363</t>
   </si>
   <si>
     <t xml:space="preserve">10.1299495697021</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98136520385742</t>
+    <t xml:space="preserve">9.98136615753174</t>
   </si>
   <si>
     <t xml:space="preserve">9.93766403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.094988822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1124687194824</t>
+    <t xml:space="preserve">10.0949878692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1124677658081</t>
   </si>
   <si>
     <t xml:space="preserve">10.0250673294067</t>
@@ -2747,13 +2747,13 @@
     <t xml:space="preserve">9.95514488220215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78033828735352</t>
+    <t xml:space="preserve">9.78033924102783</t>
   </si>
   <si>
     <t xml:space="preserve">9.75411891937256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65797519683838</t>
+    <t xml:space="preserve">9.65797710418701</t>
   </si>
   <si>
     <t xml:space="preserve">9.7453784942627</t>
@@ -2762,13 +2762,13 @@
     <t xml:space="preserve">9.99884510040283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3222360610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7330255508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7505073547363</t>
+    <t xml:space="preserve">10.3222351074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.750506401062</t>
   </si>
   <si>
     <t xml:space="preserve">10.4620780944824</t>
@@ -2783,25 +2783,25 @@
     <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4970407485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6893243789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106643676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4795589447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5757026672363</t>
+    <t xml:space="preserve">10.4970397949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6893253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4795598983765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.575701713562</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232601165771</t>
+    <t xml:space="preserve">10.5232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.5582208633423</t>
@@ -2822,34 +2822,34 @@
     <t xml:space="preserve">9.82403945922852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86774253845215</t>
+    <t xml:space="preserve">9.86774349212646</t>
   </si>
   <si>
     <t xml:space="preserve">9.61427402496338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0024585723877</t>
+    <t xml:space="preserve">9.00245761871338</t>
   </si>
   <si>
     <t xml:space="preserve">8.82765293121338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5348539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6441068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12482070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16852283477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883399963379</t>
+    <t xml:space="preserve">8.36878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53485488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64410781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1248197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883495330811</t>
   </si>
   <si>
     <t xml:space="preserve">8.98497676849365</t>
@@ -2858,37 +2858,37 @@
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078302383423</t>
+    <t xml:space="preserve">9.69293880462646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078311920166</t>
   </si>
   <si>
     <t xml:space="preserve">11.1350774765015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6070508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324918746948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3587131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5597372055054</t>
+    <t xml:space="preserve">11.6070499420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324928283691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3587141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.559739112854</t>
   </si>
   <si>
     <t xml:space="preserve">11.886739730835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4810762405396</t>
+    <t xml:space="preserve">12.4810771942139</t>
   </si>
   <si>
     <t xml:space="preserve">12.19264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139860153198</t>
+    <t xml:space="preserve">12.1139869689941</t>
   </si>
   <si>
     <t xml:space="preserve">12.2101287841797</t>
@@ -2897,31 +2897,31 @@
     <t xml:space="preserve">11.6857147216797</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0702857971191</t>
+    <t xml:space="preserve">12.0702848434448</t>
   </si>
   <si>
     <t xml:space="preserve">11.974142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916229248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9479217529297</t>
+    <t xml:space="preserve">11.9916219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.947922706604</t>
   </si>
   <si>
     <t xml:space="preserve">12.061544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314659118652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8954792022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0091028213501</t>
+    <t xml:space="preserve">12.1314668655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440645217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8954801559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0091037750244</t>
   </si>
   <si>
     <t xml:space="preserve">12.0178442001343</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">12.6558818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6733617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4898176193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4198951721191</t>
+    <t xml:space="preserve">12.673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4898166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4198942184448</t>
   </si>
   <si>
     <t xml:space="preserve">12.5684785842896</t>
@@ -2948,34 +2948,34 @@
     <t xml:space="preserve">12.7782440185547</t>
   </si>
   <si>
-    <t xml:space="preserve">12.236349105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4461154937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5160369873047</t>
+    <t xml:space="preserve">12.2363500595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4461164474487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.516037940979</t>
   </si>
   <si>
     <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2713098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132066726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8394260406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.909348487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.821946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9880104064941</t>
+    <t xml:space="preserve">12.2713117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8394269943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9093503952026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8219470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9880113601685</t>
   </si>
   <si>
     <t xml:space="preserve">13.0229721069336</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">13.3114004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.215256690979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2502183914185</t>
+    <t xml:space="preserve">13.2152576446533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2502193450928</t>
   </si>
   <si>
     <t xml:space="preserve">12.7607650756836</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9530487060547</t>
+    <t xml:space="preserve">12.953049659729</t>
   </si>
   <si>
     <t xml:space="preserve">12.9792718887329</t>
@@ -3005,10 +3005,10 @@
     <t xml:space="preserve">12.9355697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3026599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407543182373</t>
+    <t xml:space="preserve">13.3026609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075441360474</t>
   </si>
   <si>
     <t xml:space="preserve">13.189037322998</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">13.2239980697632</t>
   </si>
   <si>
-    <t xml:space="preserve">13.800853729248</t>
+    <t xml:space="preserve">13.8008546829224</t>
   </si>
   <si>
     <t xml:space="preserve">14.0281009674072</t>
@@ -3026,7 +3026,7 @@
     <t xml:space="preserve">14.1067628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.395191192627</t>
+    <t xml:space="preserve">14.3951902389526</t>
   </si>
   <si>
     <t xml:space="preserve">14.500075340271</t>
@@ -3035,16 +3035,16 @@
     <t xml:space="preserve">14.4039316177368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5612573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2116460800171</t>
+    <t xml:space="preserve">14.5612564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2116470336914</t>
   </si>
   <si>
     <t xml:space="preserve">13.7484121322632</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0980234146118</t>
+    <t xml:space="preserve">14.0980224609375</t>
   </si>
   <si>
     <t xml:space="preserve">13.7221918106079</t>
@@ -3059,40 +3059,40 @@
     <t xml:space="preserve">14.7098417282104</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6224384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157489776611</t>
+    <t xml:space="preserve">14.6224374771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157480239868</t>
   </si>
   <si>
     <t xml:space="preserve">15.1818141937256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3653593063354</t>
+    <t xml:space="preserve">15.3653602600098</t>
   </si>
   <si>
     <t xml:space="preserve">15.1206312179565</t>
   </si>
   <si>
-    <t xml:space="preserve">14.456374168396</t>
+    <t xml:space="preserve">14.4563751220703</t>
   </si>
   <si>
     <t xml:space="preserve">14.613697052002</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7622814178467</t>
+    <t xml:space="preserve">14.7622804641724</t>
   </si>
   <si>
     <t xml:space="preserve">16.3442668914795</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7550601959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373346328735</t>
+    <t xml:space="preserve">16.7550582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946565628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373336791992</t>
   </si>
   <si>
     <t xml:space="preserve">15.915994644165</t>
@@ -3104,25 +3104,25 @@
     <t xml:space="preserve">15.9422168731689</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1344985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.43528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5663833618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566179275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440202713013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2429962158203</t>
+    <t xml:space="preserve">16.13450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4352836608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5663862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3566198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440212249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.330397605896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2429971694946</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255144119263</t>
@@ -3134,52 +3134,52 @@
     <t xml:space="preserve">15.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2517366409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0681915283203</t>
+    <t xml:space="preserve">15.2517356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.068190574646</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4265394210815</t>
+    <t xml:space="preserve">15.4265413284302</t>
   </si>
   <si>
     <t xml:space="preserve">15.0244903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8933877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234634399414</t>
+    <t xml:space="preserve">14.8933868408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234615325928</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196062088013</t>
+    <t xml:space="preserve">14.9196081161499</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9370880126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1468534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8496837615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031532287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604751586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041772842407</t>
+    <t xml:space="preserve">14.937087059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1468524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.849684715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031541824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2604742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3041763305664</t>
   </si>
   <si>
     <t xml:space="preserve">14.8409433364868</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">14.4214134216309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5962181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7812824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4367980957031</t>
+    <t xml:space="preserve">14.5962171554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7812805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4368000030518</t>
   </si>
   <si>
     <t xml:space="preserve">17.463020324707</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">18.074836730957</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2846012115479</t>
+    <t xml:space="preserve">18.2846031188965</t>
   </si>
   <si>
     <t xml:space="preserve">18.8397483825684</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">18.4696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573722839355</t>
+    <t xml:space="preserve">18.8573741912842</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221244812012</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">19.0688571929932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9807415008545</t>
+    <t xml:space="preserve">18.9807395935059</t>
   </si>
   <si>
     <t xml:space="preserve">18.8749961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5753936767578</t>
+    <t xml:space="preserve">18.5753955841064</t>
   </si>
   <si>
     <t xml:space="preserve">18.2052955627441</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2405452728271</t>
+    <t xml:space="preserve">18.2405433654785</t>
   </si>
   <si>
     <t xml:space="preserve">18.7163829803467</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">18.2934150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581672668457</t>
+    <t xml:space="preserve">18.2581691741943</t>
   </si>
   <si>
     <t xml:space="preserve">18.1524257659912</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8175754547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9056930541992</t>
+    <t xml:space="preserve">17.8175735473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9056949615479</t>
   </si>
   <si>
     <t xml:space="preserve">17.8880672454834</t>
@@ -3287,7 +3287,7 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708446502686</t>
+    <t xml:space="preserve">17.5708427429199</t>
   </si>
   <si>
     <t xml:space="preserve">17.6589603424072</t>
@@ -3299,19 +3299,19 @@
     <t xml:space="preserve">17.3681678771973</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478710174561</t>
+    <t xml:space="preserve">17.1478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">17.4650993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9761867523193</t>
+    <t xml:space="preserve">17.976188659668</t>
   </si>
   <si>
     <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4827251434326</t>
+    <t xml:space="preserve">17.482723236084</t>
   </si>
   <si>
     <t xml:space="preserve">17.2007446289062</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">16.1256980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5222320556641</t>
+    <t xml:space="preserve">16.5222301483154</t>
   </si>
   <si>
     <t xml:space="preserve">16.6367855072021</t>
@@ -3347,22 +3347,22 @@
     <t xml:space="preserve">17.7470779418945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5355949401855</t>
+    <t xml:space="preserve">17.5355930328369</t>
   </si>
   <si>
     <t xml:space="preserve">17.6237144470215</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1743087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417358398438</t>
+    <t xml:space="preserve">16.8747062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1743068695068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417339324951</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3374,10 +3374,10 @@
     <t xml:space="preserve">17.3593597412109</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9716377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249031066895</t>
+    <t xml:space="preserve">16.9716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249050140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3389,19 +3389,19 @@
     <t xml:space="preserve">16.4869823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8042106628418</t>
+    <t xml:space="preserve">16.8042125701904</t>
   </si>
   <si>
     <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8704452514648</t>
+    <t xml:space="preserve">17.8704471588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765842437744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5796527862549</t>
+    <t xml:space="preserve">17.5796546936035</t>
   </si>
   <si>
     <t xml:space="preserve">17.5972766876221</t>
@@ -3413,37 +3413,37 @@
     <t xml:space="preserve">17.0421314239502</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425289154053</t>
+    <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957942962646</t>
+    <t xml:space="preserve">16.4957962036133</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3900547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3019351959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9935188293457</t>
+    <t xml:space="preserve">16.3900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3019371032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.99351978302</t>
   </si>
   <si>
     <t xml:space="preserve">15.8613433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2402534484863</t>
+    <t xml:space="preserve">16.2402515411377</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195610046387</t>
+    <t xml:space="preserve">16.31955909729</t>
   </si>
   <si>
     <t xml:space="preserve">15.7732248306274</t>
@@ -3455,10 +3455,10 @@
     <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3590660095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0330266952515</t>
+    <t xml:space="preserve">15.3590669631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0330276489258</t>
   </si>
   <si>
     <t xml:space="preserve">15.3150062561035</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">15.0154056549072</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2180757522583</t>
+    <t xml:space="preserve">15.2180767059326</t>
   </si>
   <si>
     <t xml:space="preserve">15.1828298568726</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123332977295</t>
+    <t xml:space="preserve">15.1123342514038</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035223007202</t>
@@ -3485,10 +3485,10 @@
     <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1475820541382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0858993530273</t>
+    <t xml:space="preserve">15.1475830078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0859003067017</t>
   </si>
   <si>
     <t xml:space="preserve">14.9801568984985</t>
@@ -3497,7 +3497,7 @@
     <t xml:space="preserve">14.8215427398682</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6188707351685</t>
+    <t xml:space="preserve">14.6188716888428</t>
   </si>
   <si>
     <t xml:space="preserve">14.3985738754272</t>
@@ -3509,40 +3509,40 @@
     <t xml:space="preserve">14.0725345611572</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8434267044067</t>
+    <t xml:space="preserve">13.8434276580811</t>
   </si>
   <si>
     <t xml:space="preserve">13.8962984085083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1959009170532</t>
+    <t xml:space="preserve">14.1959018707275</t>
   </si>
   <si>
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3457040786743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9491691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1080741882324</t>
+    <t xml:space="preserve">14.3104543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9491701126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1080722808838</t>
   </si>
   <si>
     <t xml:space="preserve">14.548376083374</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4778804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254053115845</t>
+    <t xml:space="preserve">14.4778814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254072189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3554,16 +3554,16 @@
     <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.772931098938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0856075286865</t>
+    <t xml:space="preserve">13.7729320526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0856084823608</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0327367782593</t>
+    <t xml:space="preserve">13.032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">13.1296663284302</t>
   </si>
   <si>
-    <t xml:space="preserve">12.944616317749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583766937256</t>
+    <t xml:space="preserve">12.9446172714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852090835571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583776473999</t>
   </si>
   <si>
     <t xml:space="preserve">13.5350112915039</t>
@@ -3587,7 +3587,7 @@
     <t xml:space="preserve">13.5614471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.191349029541</t>
+    <t xml:space="preserve">13.1913499832153</t>
   </si>
   <si>
     <t xml:space="preserve">13.2265968322754</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">13.3147144317627</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2618436813354</t>
+    <t xml:space="preserve">13.2618446350098</t>
   </si>
   <si>
     <t xml:space="preserve">13.4557056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4380807876587</t>
+    <t xml:space="preserve">13.438081741333</t>
   </si>
   <si>
     <t xml:space="preserve">13.4645166397095</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">13.4821405410767</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878820419312</t>
+    <t xml:space="preserve">13.5878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.5702590942383</t>
@@ -3626,13 +3626,13 @@
     <t xml:space="preserve">13.7112493515015</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4468927383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388738632202</t>
+    <t xml:space="preserve">13.4468936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388748168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710531234741</t>
@@ -3647,34 +3647,34 @@
     <t xml:space="preserve">12.6890735626221</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5128355026245</t>
+    <t xml:space="preserve">12.5128364562988</t>
   </si>
   <si>
     <t xml:space="preserve">12.5568952560425</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273899078369</t>
+    <t xml:space="preserve">12.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492738723755</t>
+    <t xml:space="preserve">11.6492748260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078870773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9048175811768</t>
+    <t xml:space="preserve">11.8078880310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9048194885254</t>
   </si>
   <si>
     <t xml:space="preserve">11.8431358337402</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1427373886108</t>
+    <t xml:space="preserve">12.1427383422852</t>
   </si>
   <si>
     <t xml:space="preserve">11.9841260910034</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">11.0412559509277</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8209590911865</t>
+    <t xml:space="preserve">10.8209600448608</t>
   </si>
   <si>
     <t xml:space="preserve">10.803337097168</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">11.1822452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619493484497</t>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.961950302124</t>
   </si>
   <si>
     <t xml:space="preserve">10.9355134963989</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6975936889648</t>
+    <t xml:space="preserve">10.6975946426392</t>
   </si>
   <si>
     <t xml:space="preserve">11.0500688552856</t>
@@ -3749,19 +3749,19 @@
     <t xml:space="preserve">9.56967639923096</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0455169677734</t>
+    <t xml:space="preserve">10.0455160140991</t>
   </si>
   <si>
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373615264893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64883613586426</t>
+    <t xml:space="preserve">9.42868709564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373519897461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64883708953857</t>
   </si>
   <si>
     <t xml:space="preserve">9.01452922821045</t>
@@ -3794,19 +3794,19 @@
     <t xml:space="preserve">8.68848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62680816650391</t>
+    <t xml:space="preserve">8.62680721282959</t>
   </si>
   <si>
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2787389755249</t>
+    <t xml:space="preserve">8.27873992919922</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349117279053</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43735218048096</t>
+    <t xml:space="preserve">8.43735313415527</t>
   </si>
   <si>
     <t xml:space="preserve">8.35363960266113</t>
@@ -3821,7 +3821,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245155334473</t>
+    <t xml:space="preserve">8.36245250701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">8.08487796783447</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01879024505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20824337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01438426971436</t>
+    <t xml:space="preserve">8.01878929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20824432373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01438331604004</t>
   </si>
   <si>
     <t xml:space="preserve">7.88661241531372</t>
@@ -3851,19 +3851,19 @@
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89542293548584</t>
+    <t xml:space="preserve">8.02760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89542388916016</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80730485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819747924805</t>
+    <t xml:space="preserve">7.80730438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819700241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
@@ -3872,19 +3872,19 @@
     <t xml:space="preserve">7.6619086265564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78527498245239</t>
+    <t xml:space="preserve">7.78527545928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.67512702941895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62037038803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03561210632324</t>
+    <t xml:space="preserve">7.95803880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62036991119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03561115264893</t>
   </si>
   <si>
     <t xml:space="preserve">8.06299114227295</t>
@@ -3893,19 +3893,19 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124256134033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92609739303589</t>
+    <t xml:space="preserve">8.08124160766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92609786987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.89871835708618</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64774894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82570934295654</t>
+    <t xml:space="preserve">7.6477484703064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8257098197937</t>
   </si>
   <si>
     <t xml:space="preserve">7.67969036102295</t>
@@ -3914,13 +3914,13 @@
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736042022705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20056486129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96784734725952</t>
+    <t xml:space="preserve">7.54736089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20056438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96784687042236</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
@@ -3929,43 +3929,43 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03629398345947</t>
+    <t xml:space="preserve">7.03629350662231</t>
   </si>
   <si>
     <t xml:space="preserve">6.98153686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76250791549683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90396404266357</t>
+    <t xml:space="preserve">6.76250743865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90396356582642</t>
   </si>
   <si>
     <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80357599258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69406175613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46590709686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48872232437134</t>
+    <t xml:space="preserve">6.80357551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69406127929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46590662002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48872184753418</t>
   </si>
   <si>
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212102890015</t>
+    <t xml:space="preserve">6.19212055206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3974,16 +3974,16 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260562896729</t>
+    <t xml:space="preserve">6.53891658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260515213013</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2605676651001</t>
+    <t xml:space="preserve">6.26056718826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -4001,7 +4001,7 @@
     <t xml:space="preserve">6.46134376525879</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63474130630493</t>
+    <t xml:space="preserve">6.63474082946777</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
@@ -4010,7 +4010,7 @@
     <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49328517913818</t>
+    <t xml:space="preserve">6.49328470230103</t>
   </si>
   <si>
     <t xml:space="preserve">6.64843034744263</t>
@@ -4037,16 +4037,16 @@
     <t xml:space="preserve">7.17318677902222</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19143867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94046831130981</t>
+    <t xml:space="preserve">7.19143915176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94046878814697</t>
   </si>
   <si>
     <t xml:space="preserve">7.02260446548462</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01347780227661</t>
+    <t xml:space="preserve">7.01347827911377</t>
   </si>
   <si>
     <t xml:space="preserve">6.99978876113892</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4067,73 +4067,73 @@
     <t xml:space="preserve">7.18687582015991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5747389793396</t>
+    <t xml:space="preserve">7.57473945617676</t>
   </si>
   <si>
     <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35046482086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21357250213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90784454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81658220291138</t>
+    <t xml:space="preserve">8.3504638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21357345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90784502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81658315658569</t>
   </si>
   <si>
     <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89415502548218</t>
+    <t xml:space="preserve">7.89415550231934</t>
   </si>
   <si>
     <t xml:space="preserve">7.49260330200195</t>
   </si>
   <si>
-    <t xml:space="preserve">7.37396240234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25532197952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34658432006836</t>
+    <t xml:space="preserve">7.37396287918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25532245635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3465838432312</t>
   </si>
   <si>
     <t xml:space="preserve">7.52910804748535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5929913520813</t>
+    <t xml:space="preserve">7.59299087524414</t>
   </si>
   <si>
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415851593018</t>
+    <t xml:space="preserve">6.48415899276733</t>
   </si>
   <si>
     <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21037292480469</t>
+    <t xml:space="preserve">6.21037340164185</t>
   </si>
   <si>
     <t xml:space="preserve">6.27425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05066537857056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04610204696655</t>
+    <t xml:space="preserve">6.0506649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.73581123352051</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95940351486206</t>
+    <t xml:space="preserve">5.9594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">6.25144100189209</t>
@@ -4154,22 +4154,22 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.27881956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
   </si>
   <si>
-    <t xml:space="preserve">6.54347896575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57085800170898</t>
+    <t xml:space="preserve">6.54347991943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57085752487183</t>
   </si>
   <si>
     <t xml:space="preserve">6.47959613800049</t>
@@ -4181,28 +4181,28 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901218414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09105062484741</t>
+    <t xml:space="preserve">6.79901266098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09105110168457</t>
   </si>
   <si>
     <t xml:space="preserve">7.02716732025146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84008026123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57542085647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68949794769287</t>
+    <t xml:space="preserve">6.84008073806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57542037963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68949842453003</t>
   </si>
   <si>
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4214,25 +4214,25 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978691101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17706775665283</t>
+    <t xml:space="preserve">7.93978595733643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17706680297852</t>
   </si>
   <si>
     <t xml:space="preserve">8.12230968475342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78920412063599</t>
+    <t xml:space="preserve">7.78920364379883</t>
   </si>
   <si>
     <t xml:space="preserve">7.69794321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7663893699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72988414764404</t>
+    <t xml:space="preserve">7.76638889312744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7298846244812</t>
   </si>
   <si>
     <t xml:space="preserve">7.66600036621094</t>
@@ -4241,19 +4241,19 @@
     <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7116322517395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9169716835022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86677694320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72075796127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57017517089844</t>
+    <t xml:space="preserve">7.71163129806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91697120666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86677646636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72075843811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57017612457275</t>
   </si>
   <si>
     <t xml:space="preserve">7.62949514389038</t>
@@ -4265,10 +4265,10 @@
     <t xml:space="preserve">7.5519232749939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31464242935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28270101547241</t>
+    <t xml:space="preserve">7.31464290618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28270053863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.1777491569519</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">7.27813768386841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51998138427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4560980796814</t>
+    <t xml:space="preserve">7.5199818611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.46978807449341</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959360122681</t>
+    <t xml:space="preserve">7.79376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959312438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.38696956634521</t>
@@ -4307,22 +4307,22 @@
     <t xml:space="preserve">8.34590244293213</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36871719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8159008026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94366836547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68813419342041</t>
+    <t xml:space="preserve">8.36871814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81589984893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9436674118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68813514709473</t>
   </si>
   <si>
     <t xml:space="preserve">8.66531848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82959079742432</t>
+    <t xml:space="preserve">8.82958984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.8067741394043</t>
@@ -4334,10 +4334,10 @@
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347457885742</t>
+    <t xml:space="preserve">8.84327983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347362518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4367,28 +4367,28 @@
     <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21813488006592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25007629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949398040771</t>
+    <t xml:space="preserve">8.21813583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99910688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83483457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68881607055664</t>
+    <t xml:space="preserve">7.99910736083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83483600616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6888165473938</t>
   </si>
   <si>
     <t xml:space="preserve">7.51085519790649</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">8.00823307037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05386352539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97172784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92153406143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017448425293</t>
+    <t xml:space="preserve">8.05386447906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97172832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9215350151062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04017543792725</t>
   </si>
   <si>
     <t xml:space="preserve">8.09493160247803</t>
@@ -4415,25 +4415,25 @@
     <t xml:space="preserve">8.08580589294434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.15425300598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96716499328613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12755537033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96328449249268</t>
+    <t xml:space="preserve">8.15425205230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96716451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12755584716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96328401565552</t>
   </si>
   <si>
     <t xml:space="preserve">7.3283314704895</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21425437927246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35114765167236</t>
+    <t xml:space="preserve">7.21425485610962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35114717483521</t>
   </si>
   <si>
     <t xml:space="preserve">7.24163246154785</t>
@@ -4442,19 +4442,19 @@
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804113388062</t>
+    <t xml:space="preserve">7.01804161071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73969221115112</t>
+    <t xml:space="preserve">6.73969268798828</t>
   </si>
   <si>
     <t xml:space="preserve">6.86745929718018</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13211822509766</t>
+    <t xml:space="preserve">7.13211917877197</t>
   </si>
   <si>
     <t xml:space="preserve">6.88114833831787</t>
@@ -4469,31 +4469,31 @@
     <t xml:space="preserve">6.95415782928467</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74881839752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73512935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90852737426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561511993408</t>
+    <t xml:space="preserve">6.74881887435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73512983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90852689743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76707077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561559677124</t>
   </si>
   <si>
     <t xml:space="preserve">6.62105226516724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43852758407593</t>
+    <t xml:space="preserve">6.43852806091309</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30619812011719</t>
+    <t xml:space="preserve">6.30619859695435</t>
   </si>
   <si>
     <t xml:space="preserve">6.42027568817139</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50606966018677</t>
+    <t xml:space="preserve">6.50607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4529,28 +4529,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.677659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812562942505</t>
+    <t xml:space="preserve">6.67765855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86354637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924697875977</t>
+    <t xml:space="preserve">6.92550897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8635458946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924745559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6156964302063</t>
+    <t xml:space="preserve">6.61569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4565,19 +4565,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887351989746</t>
+    <t xml:space="preserve">6.44887399673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279872894287</t>
+    <t xml:space="preserve">6.57279920578003</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541585922241</t>
+    <t xml:space="preserve">6.31541538238525</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214492797852</t>
+    <t xml:space="preserve">6.38214445114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915433883667</t>
+    <t xml:space="preserve">6.23915386199951</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4631,22 +4631,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999631881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7863507270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167762756348</t>
+    <t xml:space="preserve">5.60999584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74821996688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78635120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167810440063</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803298950195</t>
+    <t xml:space="preserve">6.05803251266479</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4655,13 +4655,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878087997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401393890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597654342651</t>
+    <t xml:space="preserve">5.83878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653745651245</t>
+    <t xml:space="preserve">5.98653793334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4679,13 +4679,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26298570632935</t>
+    <t xml:space="preserve">6.2629861831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728509902954</t>
+    <t xml:space="preserve">6.27728462219238</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4706,10 +4706,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532321929932</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532274246216</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4727,7 +4727,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859367370605</t>
+    <t xml:space="preserve">5.63859415054321</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4736,16 +4736,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7720513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78158473968506</t>
+    <t xml:space="preserve">5.68625736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77205181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476182937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7815842628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541635513306</t>
+    <t xml:space="preserve">5.42887449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541683197021</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4772,16 +4772,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18102407455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943565368652</t>
+    <t xml:space="preserve">5.1810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943517684937</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812732696533</t>
+    <t xml:space="preserve">5.13812685012817</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4796,19 +4796,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336061477661</t>
+    <t xml:space="preserve">5.64336013793945</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71962213516235</t>
+    <t xml:space="preserve">5.7196216583252</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027618408203</t>
+    <t xml:space="preserve">5.40027666091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4823,13 +4823,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569692611694</t>
+    <t xml:space="preserve">5.59569644927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775241851807</t>
+    <t xml:space="preserve">5.75775289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569667816162</t>
+    <t xml:space="preserve">6.10569620132446</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382743835449</t>
+    <t xml:space="preserve">6.14382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4859,61 +4859,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635047912598</t>
+    <t xml:space="preserve">6.24868679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4679388999939</t>
+    <t xml:space="preserve">6.41074323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46793937683105</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896760940552</t>
+    <t xml:space="preserve">6.03896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177146911621</t>
+    <t xml:space="preserve">5.98177099227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644456863403</t>
+    <t xml:space="preserve">5.8530797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420066833496</t>
+    <t xml:space="preserve">6.03420114517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79111671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7768177986145</t>
+    <t xml:space="preserve">5.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7911171913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77681827545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4925,28 +4925,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186460494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69578981399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5194354057312</t>
+    <t xml:space="preserve">5.53850030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51943492889404</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560308456421</t>
+    <t xml:space="preserve">5.49560356140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410875320435</t>
+    <t xml:space="preserve">4.91410827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4970,22 +4970,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354711532593</t>
+    <t xml:space="preserve">5.33354759216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691236495972</t>
+    <t xml:space="preserve">5.36691188812256</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457557678223</t>
+    <t xml:space="preserve">5.67195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457509994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5009,7 +5009,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438884735107</t>
+    <t xml:space="preserve">5.21438837051392</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44317388534546</t>
+    <t xml:space="preserve">5.4431734085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5036,16 +5036,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709909439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027545928955</t>
+    <t xml:space="preserve">5.56709861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027593612671</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86261224746704</t>
+    <t xml:space="preserve">5.8626127243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -71959,7 +71959,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6911226852</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>42201</v>
@@ -71980,6 +71980,32 @@
         <v>1886</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6937037037</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>51588</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>4.55499982833862</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>4.46999979019165</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>4.55499982833862</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>4.48999977111816</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>1908</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -53,91 +53,91 @@
     <t xml:space="preserve">12.4758977890015</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9930124282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.270076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5233945846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9746170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075635910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125680923462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6738042831421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563411712646</t>
+    <t xml:space="preserve">11.9930105209351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742685317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700786590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5233955383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9746179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6738033294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0563402175903</t>
   </si>
   <si>
     <t xml:space="preserve">12.3729877471924</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1750841140747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413228988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367845535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9850950241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4626264572144</t>
+    <t xml:space="preserve">12.1750831604004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9850959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380624771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955739974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4626274108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.1063985824585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942932128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5417900085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3597164154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
+    <t xml:space="preserve">11.4942922592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5417890548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3597173690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8584356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159442901611</t>
   </si>
   <si>
     <t xml:space="preserve">11.8346862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">11.676365852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684494018555</t>
+    <t xml:space="preserve">11.6763639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684474945068</t>
   </si>
   <si>
     <t xml:space="preserve">11.3992986679077</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">11.9692630767822</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3888206481934</t>
+    <t xml:space="preserve">12.388819694519</t>
   </si>
   <si>
     <t xml:space="preserve">12.4284009933472</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">12.2304964065552</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1117534637451</t>
+    <t xml:space="preserve">12.1117525100708</t>
   </si>
   <si>
     <t xml:space="preserve">12.1513347625732</t>
@@ -167,61 +167,61 @@
     <t xml:space="preserve">12.1196708679199</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8242111206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9508686065674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408586502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754316329956</t>
+    <t xml:space="preserve">12.8242101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9508676528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754325866699</t>
   </si>
   <si>
     <t xml:space="preserve">13.3704252243042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3387613296509</t>
+    <t xml:space="preserve">13.3387622833252</t>
   </si>
   <si>
     <t xml:space="preserve">13.4575061798096</t>
   </si>
   <si>
-    <t xml:space="preserve">13.576247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999946594238</t>
+    <t xml:space="preserve">13.5762462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999956130981</t>
   </si>
   <si>
     <t xml:space="preserve">13.362509727478</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379476547241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7529649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171092987061</t>
+    <t xml:space="preserve">13.0379467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7529640197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171083450317</t>
   </si>
   <si>
     <t xml:space="preserve">13.1091928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.196270942688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9904479980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221147537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933609008789</t>
+    <t xml:space="preserve">13.1962690353394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9904489517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933628082275</t>
   </si>
   <si>
     <t xml:space="preserve">13.0775289535522</t>
@@ -230,49 +230,49 @@
     <t xml:space="preserve">13.0300312042236</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6975517272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6025562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.650053024292</t>
+    <t xml:space="preserve">12.6975526809692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6025581359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6500549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.8637924194336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5867252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788087844849</t>
+    <t xml:space="preserve">12.586724281311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.467981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788097381592</t>
   </si>
   <si>
     <t xml:space="preserve">12.7286968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1493883132935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.988468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241008758545</t>
+    <t xml:space="preserve">12.1493873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091575622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884691238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241018295288</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218008041382</t>
   </si>
   <si>
-    <t xml:space="preserve">12.22984790802</t>
+    <t xml:space="preserve">12.2298469543457</t>
   </si>
   <si>
     <t xml:space="preserve">12.2942152023315</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">12.2620306015015</t>
   </si>
   <si>
-    <t xml:space="preserve">12.286169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953632354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126045227051</t>
+    <t xml:space="preserve">12.2861700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953651428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126054763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091564178467</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0263986587524</t>
+    <t xml:space="preserve">13.0263977050781</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252477645874</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">12.8172016143799</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5999631881714</t>
+    <t xml:space="preserve">12.5999612808228</t>
   </si>
   <si>
     <t xml:space="preserve">12.3666296005249</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3103084564209</t>
+    <t xml:space="preserve">12.3103075027466</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390451431274</t>
@@ -323,19 +323,19 @@
     <t xml:space="preserve">11.4011144638062</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2884712219238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8781290054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792779922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689296722412</t>
+    <t xml:space="preserve">11.2884702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8781280517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792751312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689287185669</t>
   </si>
   <si>
     <t xml:space="preserve">11.6103096008301</t>
@@ -356,61 +356,61 @@
     <t xml:space="preserve">10.45973777771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0229539871216</t>
+    <t xml:space="preserve">11.0229549407959</t>
   </si>
   <si>
     <t xml:space="preserve">11.6424932479858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6344480514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321500778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827251434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264011383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229537963867</t>
+    <t xml:space="preserve">11.6344470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321481704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827241897583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229518890381</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700807571411</t>
+    <t xml:space="preserve">11.5700798034668</t>
   </si>
   <si>
     <t xml:space="preserve">11.8919172286987</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5861721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8758268356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953643798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1896190643311</t>
+    <t xml:space="preserve">11.5861711502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.875825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953662872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1896181106567</t>
   </si>
   <si>
     <t xml:space="preserve">12.4309968948364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896169662476</t>
+    <t xml:space="preserve">12.8896150588989</t>
   </si>
   <si>
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.994213104248</t>
+    <t xml:space="preserve">12.9942140579224</t>
   </si>
   <si>
     <t xml:space="preserve">13.1229476928711</t>
@@ -422,103 +422,103 @@
     <t xml:space="preserve">12.9861669540405</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0746736526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482341766357</t>
+    <t xml:space="preserve">13.0746726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482351303101</t>
   </si>
   <si>
     <t xml:space="preserve">14.2493810653687</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9194974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459348678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643241882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034049987793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022531509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137502670288</t>
+    <t xml:space="preserve">13.9194984436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459329605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919088363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643232345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275405883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206453323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034021377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137493133545</t>
   </si>
   <si>
     <t xml:space="preserve">14.6516780853271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7562770843506</t>
+    <t xml:space="preserve">14.7562780380249</t>
   </si>
   <si>
     <t xml:space="preserve">15.1183443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1505279541016</t>
+    <t xml:space="preserve">15.1505289077759</t>
   </si>
   <si>
     <t xml:space="preserve">15.126389503479</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0861597061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0459327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.424090385437</t>
+    <t xml:space="preserve">15.0861587524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0459337234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4240894317627</t>
   </si>
   <si>
     <t xml:space="preserve">15.4562740325928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3597249984741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873086929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240953445435</t>
+    <t xml:space="preserve">15.3597240447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689222335815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240934371948</t>
   </si>
   <si>
     <t xml:space="preserve">14.8367366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">14.788459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930587768555</t>
+    <t xml:space="preserve">14.7884607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930578231812</t>
   </si>
   <si>
     <t xml:space="preserve">15.4884586334229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4401826858521</t>
+    <t xml:space="preserve">15.4401845932007</t>
   </si>
   <si>
     <t xml:space="preserve">15.2148971557617</t>
@@ -527,67 +527,67 @@
     <t xml:space="preserve">14.8045530319214</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3919086456299</t>
+    <t xml:space="preserve">15.3919067382812</t>
   </si>
   <si>
     <t xml:space="preserve">15.2551259994507</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1666202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286912918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229423522949</t>
+    <t xml:space="preserve">15.1666193008423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286893844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229452133179</t>
   </si>
   <si>
     <t xml:space="preserve">15.0137481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8850107192993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.198805809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827116012573</t>
+    <t xml:space="preserve">14.8850145339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1988039016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275375366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114452362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677711486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034000396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.182710647583</t>
   </si>
   <si>
     <t xml:space="preserve">14.6436338424683</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9654712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470798492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.828688621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5390367507935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551280975342</t>
+    <t xml:space="preserve">14.9654703140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470827102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286905288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5390357971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551261901855</t>
   </si>
   <si>
     <t xml:space="preserve">14.1126012802124</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4263906478882</t>
+    <t xml:space="preserve">14.4263944625854</t>
   </si>
   <si>
     <t xml:space="preserve">14.2815656661987</t>
@@ -596,34 +596,34 @@
     <t xml:space="preserve">14.4827146530151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2171983718872</t>
+    <t xml:space="preserve">14.2171974182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4103012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5631761550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585742950439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045560836792</t>
+    <t xml:space="preserve">14.5631742477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045541763306</t>
   </si>
   <si>
     <t xml:space="preserve">14.3217964172363</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9516830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781215667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045562744141</t>
+    <t xml:space="preserve">13.9516839981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781206130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045572280884</t>
   </si>
   <si>
     <t xml:space="preserve">13.3643264770508</t>
@@ -632,91 +632,91 @@
     <t xml:space="preserve">13.1873149871826</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9539833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.31605052948</t>
+    <t xml:space="preserve">12.9539842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3160514831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.5896129608154</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7746696472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9114542007446</t>
+    <t xml:space="preserve">13.7746706008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9114532470703</t>
   </si>
   <si>
     <t xml:space="preserve">14.2011060714722</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9999570846558</t>
+    <t xml:space="preserve">13.9999580383301</t>
   </si>
   <si>
     <t xml:space="preserve">14.9815645217896</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0378856658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9171953201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631711959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528240203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536732673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643230438232</t>
+    <t xml:space="preserve">15.0378885269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447847366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.917197227478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367345809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643211364746</t>
   </si>
   <si>
     <t xml:space="preserve">15.383861541748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6091470718384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068490982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263883590698</t>
+    <t xml:space="preserve">15.6091461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045499801636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.407998085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1103000640869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263864517212</t>
   </si>
   <si>
     <t xml:space="preserve">15.8907566070557</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8988056182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470777511597</t>
+    <t xml:space="preserve">15.8988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.947078704834</t>
   </si>
   <si>
     <t xml:space="preserve">16.0114459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493785858154</t>
+    <t xml:space="preserve">16.3493747711182</t>
   </si>
   <si>
     <t xml:space="preserve">16.3010997772217</t>
@@ -731,19 +731,19 @@
     <t xml:space="preserve">16.3332843780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4539737701416</t>
+    <t xml:space="preserve">16.4539756774902</t>
   </si>
   <si>
     <t xml:space="preserve">16.17236328125</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1562690734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700662612915</t>
+    <t xml:space="preserve">16.156270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792613983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700643539429</t>
   </si>
   <si>
     <t xml:space="preserve">16.0919036865234</t>
@@ -758,7 +758,7 @@
     <t xml:space="preserve">16.4781112670898</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8964958190918</t>
+    <t xml:space="preserve">16.8964996337891</t>
   </si>
   <si>
     <t xml:space="preserve">16.9769592285156</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">17.5160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.773509979248</t>
+    <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
     <t xml:space="preserve">18.3850021362305</t>
@@ -788,67 +788,67 @@
     <t xml:space="preserve">19.0206336975098</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2700538635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3907470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4068393707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4470710754395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321220397949</t>
+    <t xml:space="preserve">19.2700576782227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3907451629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4068374633789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4470672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079883575439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321239471436</t>
   </si>
   <si>
     <t xml:space="preserve">19.7125854492188</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3827018737793</t>
+    <t xml:space="preserve">19.3826999664307</t>
   </si>
   <si>
     <t xml:space="preserve">19.5838489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3102874755859</t>
+    <t xml:space="preserve">19.3102836608887</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436210632324</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4631614685059</t>
+    <t xml:space="preserve">19.4631595611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.0689086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0769557952881</t>
+    <t xml:space="preserve">19.0769519805908</t>
   </si>
   <si>
     <t xml:space="preserve">18.8355731964111</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0286769866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9723567962646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5620155334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5056915283203</t>
+    <t xml:space="preserve">19.028678894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9723529815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.56201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056896209717</t>
   </si>
   <si>
     <t xml:space="preserve">18.6183338165283</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">19.1654567718506</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8171825408936</t>
+    <t xml:space="preserve">19.8171806335449</t>
   </si>
   <si>
     <t xml:space="preserve">20.259708404541</t>
@@ -866,31 +866,31 @@
     <t xml:space="preserve">20.7585582733154</t>
   </si>
   <si>
-    <t xml:space="preserve">20.557409286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9539318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818675994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213714599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841789245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.766695022583</t>
+    <t xml:space="preserve">20.5574073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539337158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818714141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666988372803</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5726184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5387592315674</t>
+    <t xml:space="preserve">21.5726203918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.538761138916</t>
   </si>
   <si>
     <t xml:space="preserve">20.5550403594971</t>
@@ -899,64 +899,64 @@
     <t xml:space="preserve">20.489917755127</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3922309875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.351526260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5143394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9864959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9376525878906</t>
+    <t xml:space="preserve">20.3922271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3515243530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5143375396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9864978790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946365356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.937650680542</t>
   </si>
   <si>
     <t xml:space="preserve">21.1248874664307</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0353393554688</t>
+    <t xml:space="preserve">21.0353412628174</t>
   </si>
   <si>
     <t xml:space="preserve">20.8399658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8155422210693</t>
+    <t xml:space="preserve">20.815544128418</t>
   </si>
   <si>
     <t xml:space="preserve">21.1574478149414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2945442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957469940186</t>
+    <t xml:space="preserve">20.2945384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3189659118652</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8386688232422</t>
+    <t xml:space="preserve">19.8386707305908</t>
   </si>
   <si>
     <t xml:space="preserve">20.0828857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1480121612549</t>
+    <t xml:space="preserve">20.1480102539062</t>
   </si>
   <si>
     <t xml:space="preserve">19.9851989746094</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1317291259766</t>
+    <t xml:space="preserve">20.1317272186279</t>
   </si>
   <si>
     <t xml:space="preserve">20.3678092956543</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">20.7259941101074</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3108234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770584106445</t>
+    <t xml:space="preserve">20.3108253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770603179932</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
@@ -986,16 +986,16 @@
     <t xml:space="preserve">18.707124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0978698730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1304340362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804821014404</t>
+    <t xml:space="preserve">19.0978717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338577270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1304359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804801940918</t>
   </si>
   <si>
     <t xml:space="preserve">19.5293235778809</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">20.2049961090088</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7816829681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1805763244629</t>
+    <t xml:space="preserve">19.7816848754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1805744171143</t>
   </si>
   <si>
     <t xml:space="preserve">20.2375602722168</t>
@@ -1016,43 +1016,43 @@
     <t xml:space="preserve">20.78297996521</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7748374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6771507263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1655883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2795543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0434799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6852912902832</t>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050922393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.677152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1655902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2795581817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.043478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6852893829346</t>
   </si>
   <si>
     <t xml:space="preserve">21.1004638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5400562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3202629089355</t>
+    <t xml:space="preserve">21.5400543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319156646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3202610015869</t>
   </si>
   <si>
     <t xml:space="preserve">21.922664642334</t>
@@ -1061,31 +1061,31 @@
     <t xml:space="preserve">21.784273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4993515014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3935260772705</t>
+    <t xml:space="preserve">21.4993534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3935279846191</t>
   </si>
   <si>
     <t xml:space="preserve">21.7761344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6214637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0691967010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110061645508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9809417724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.6308975219727</t>
+    <t xml:space="preserve">21.6214618682861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0691947937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.711009979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9809436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6308994293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.0542106628418</t>
@@ -1094,52 +1094,52 @@
     <t xml:space="preserve">22.989086151123</t>
   </si>
   <si>
-    <t xml:space="preserve">23.200740814209</t>
+    <t xml:space="preserve">23.2007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">23.1681785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4693832397461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8601322174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298793792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310802459717</t>
+    <t xml:space="preserve">23.4693813323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601264953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310859680176</t>
   </si>
   <si>
     <t xml:space="preserve">23.9659595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0229434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648471832275</t>
+    <t xml:space="preserve">24.0229415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648490905762</t>
   </si>
   <si>
     <t xml:space="preserve">23.9008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9903812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159114837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9822368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.23459815979</t>
+    <t xml:space="preserve">23.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159133911133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9822387695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2346000671387</t>
   </si>
   <si>
     <t xml:space="preserve">25.4394111633301</t>
@@ -1148,7 +1148,7 @@
     <t xml:space="preserve">24.9916763305664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0568008422852</t>
+    <t xml:space="preserve">25.0567989349365</t>
   </si>
   <si>
     <t xml:space="preserve">25.0079555511475</t>
@@ -1160,79 +1160,79 @@
     <t xml:space="preserve">24.8288631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">24.666051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.649772644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999092102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9604072570801</t>
+    <t xml:space="preserve">24.6660480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6497707366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9604053497314</t>
   </si>
   <si>
     <t xml:space="preserve">25.480110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1789073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7474555969238</t>
+    <t xml:space="preserve">25.1789093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613349914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602207183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7474575042725</t>
   </si>
   <si>
     <t xml:space="preserve">24.5765037536621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4556884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2778911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9848289489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1082344055176</t>
+    <t xml:space="preserve">25.4556903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.277889251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9848308563232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1082363128662</t>
   </si>
   <si>
     <t xml:space="preserve">27.7676258087158</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3850154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209995269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0105457305908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6930656433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2765941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032405853271</t>
+    <t xml:space="preserve">27.3850135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9210014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071277618408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0105476379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6930637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2765979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032367706299</t>
   </si>
   <si>
     <t xml:space="preserve">24.6172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5846500396729</t>
+    <t xml:space="preserve">24.5846462249756</t>
   </si>
   <si>
     <t xml:space="preserve">25.2440357208252</t>
@@ -1241,7 +1241,7 @@
     <t xml:space="preserve">24.8451442718506</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7393169403076</t>
+    <t xml:space="preserve">24.739315032959</t>
   </si>
   <si>
     <t xml:space="preserve">25.1951904296875</t>
@@ -1250,25 +1250,25 @@
     <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5859413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7243309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6917686462402</t>
+    <t xml:space="preserve">25.5859394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7243328094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6917667388916</t>
   </si>
   <si>
     <t xml:space="preserve">25.5452365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7568912506104</t>
+    <t xml:space="preserve">25.7568893432617</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3173007965088</t>
+    <t xml:space="preserve">25.3172988891602</t>
   </si>
   <si>
     <t xml:space="preserve">25.3987064361572</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">25.512674331665</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7650318145752</t>
+    <t xml:space="preserve">25.7650356292725</t>
   </si>
   <si>
     <t xml:space="preserve">26.049955368042</t>
@@ -1286,28 +1286,28 @@
     <t xml:space="preserve">25.2033290863037</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486583709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4625339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661441802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824272155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
+    <t xml:space="preserve">25.0486602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4625358581543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">24.7148952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6836261749268</t>
+    <t xml:space="preserve">25.683629989624</t>
   </si>
   <si>
     <t xml:space="preserve">26.7419033050537</t>
@@ -1322,16 +1322,16 @@
     <t xml:space="preserve">26.6604995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.497688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313571929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6022205352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127647399902</t>
+    <t xml:space="preserve">26.4976844787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022243499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.2941703796387</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">26.7826118469238</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117485046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815937042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6197967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1720676422119</t>
+    <t xml:space="preserve">27.3117504119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.881591796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2303428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233089447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.619800567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1720638275146</t>
   </si>
   <si>
     <t xml:space="preserve">25.0730800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6253471374512</t>
+    <t xml:space="preserve">24.6253490447998</t>
   </si>
   <si>
     <t xml:space="preserve">23.8519897460938</t>
@@ -1373,22 +1373,22 @@
     <t xml:space="preserve">25.5615177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3580017089844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137847900391</t>
+    <t xml:space="preserve">25.3580055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137828826904</t>
   </si>
   <si>
     <t xml:space="preserve">25.2358932495117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.3635540008545</t>
+    <t xml:space="preserve">23.3635559082031</t>
   </si>
   <si>
     <t xml:space="preserve">24.4218330383301</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2534713745117</t>
+    <t xml:space="preserve">26.2534694671631</t>
   </si>
   <si>
     <t xml:space="preserve">23.6891784667969</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">20.1887130737305</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6364479064941</t>
+    <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
     <t xml:space="preserve">20.7178535461426</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">19.7002792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4736328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540241241455</t>
+    <t xml:space="preserve">20.4736347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540260314941</t>
   </si>
   <si>
     <t xml:space="preserve">21.7354316711426</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">21.8168354034424</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8806667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505100250244</t>
+    <t xml:space="preserve">20.8806648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505081176758</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284015655518</t>
@@ -1439,31 +1439,31 @@
     <t xml:space="preserve">21.6947288513184</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4680862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.183162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5901927947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0203514099121</t>
+    <t xml:space="preserve">22.4680881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1831665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5901966094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0203533172607</t>
   </si>
   <si>
     <t xml:space="preserve">22.3459777832031</t>
   </si>
   <si>
-    <t xml:space="preserve">23.1600379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.7123031616211</t>
+    <t xml:space="preserve">23.1600360870361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.7123050689697</t>
   </si>
   <si>
     <t xml:space="preserve">23.6077709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.805736541748</t>
+    <t xml:space="preserve">25.8057384490967</t>
   </si>
   <si>
     <t xml:space="preserve">24.7067546844482</t>
@@ -1472,7 +1472,7 @@
     <t xml:space="preserve">24.3811302185059</t>
   </si>
   <si>
-    <t xml:space="preserve">24.218318939209</t>
+    <t xml:space="preserve">24.2183151245117</t>
   </si>
   <si>
     <t xml:space="preserve">24.1776142120361</t>
@@ -1484,22 +1484,22 @@
     <t xml:space="preserve">24.7881622314453</t>
   </si>
   <si>
-    <t xml:space="preserve">24.705394744873</t>
+    <t xml:space="preserve">24.7053966522217</t>
   </si>
   <si>
     <t xml:space="preserve">24.1260395050049</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6640110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123096466064</t>
+    <t xml:space="preserve">24.6640129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123058319092</t>
   </si>
   <si>
     <t xml:space="preserve">25.2019863128662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.408899307251</t>
+    <t xml:space="preserve">25.4088973999023</t>
   </si>
   <si>
     <t xml:space="preserve">25.7813415527344</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3261337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2779331207275</t>
+    <t xml:space="preserve">25.3261318206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2779350280762</t>
   </si>
   <si>
     <t xml:space="preserve">27.1469688415527</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9400539398193</t>
+    <t xml:space="preserve">26.9400501251221</t>
   </si>
   <si>
     <t xml:space="preserve">26.1951675415039</t>
@@ -1526,19 +1526,19 @@
     <t xml:space="preserve">25.4916648864746</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5330486297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778388977051</t>
+    <t xml:space="preserve">25.5330467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778369903564</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675155639648</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6985740661621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2847518920898</t>
+    <t xml:space="preserve">25.6985759735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2847499847412</t>
   </si>
   <si>
     <t xml:space="preserve">25.6571941375732</t>
@@ -1547,61 +1547,61 @@
     <t xml:space="preserve">26.1537857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8227252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9468746185303</t>
+    <t xml:space="preserve">25.8227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.946870803833</t>
   </si>
   <si>
     <t xml:space="preserve">26.0710201263428</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9054889678955</t>
+    <t xml:space="preserve">25.9054870605469</t>
   </si>
   <si>
     <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0641994476318</t>
+    <t xml:space="preserve">27.0642032623291</t>
   </si>
   <si>
     <t xml:space="preserve">27.0228214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2501850128174</t>
+    <t xml:space="preserve">24.250186920166</t>
   </si>
   <si>
     <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7535972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0432758331299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363609313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3811511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.794979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8777446746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9191284179688</t>
+    <t xml:space="preserve">23.7535953521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0432739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363590240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3811531066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7949752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.877742767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
     <t xml:space="preserve">24.2088050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4502792358398</t>
+    <t xml:space="preserve">24.332950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4502811431885</t>
   </si>
   <si>
     <t xml:space="preserve">26.5262279510498</t>
@@ -1610,46 +1610,46 @@
     <t xml:space="preserve">25.864107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0296382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.56760597229</t>
+    <t xml:space="preserve">26.0296401977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">25.5744285583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6089954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9814338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9882526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6503753662109</t>
+    <t xml:space="preserve">26.6089935302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9814357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9882545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4434623718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6503772735596</t>
   </si>
   <si>
     <t xml:space="preserve">26.3606967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4984798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0914745330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.72585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4361705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8913822174072</t>
+    <t xml:space="preserve">24.4984836578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0914764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7258491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4361686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8913803100586</t>
   </si>
   <si>
     <t xml:space="preserve">20.7740516662598</t>
@@ -1658,10 +1658,10 @@
     <t xml:space="preserve">21.6430854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4775562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1051120758057</t>
+    <t xml:space="preserve">21.4775524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1051139831543</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154315948486</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">19.8636341094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.939582824707</t>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9395790100098</t>
   </si>
   <si>
     <t xml:space="preserve">21.9327621459961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0569095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9259452819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.263822555542</t>
+    <t xml:space="preserve">22.0569114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9259433746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2638206481934</t>
   </si>
   <si>
     <t xml:space="preserve">18.0014190673828</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6703605651855</t>
+    <t xml:space="preserve">17.6703567504883</t>
   </si>
   <si>
     <t xml:space="preserve">17.8772716522217</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">18.2083320617676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4980068206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7049217224121</t>
+    <t xml:space="preserve">18.498010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">18.8290691375732</t>
@@ -1727,31 +1727,31 @@
     <t xml:space="preserve">18.6221580505371</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704509735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3670406341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5325756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.491189956665</t>
+    <t xml:space="preserve">18.8704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3670425415039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773658752441</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187477111816</t>
+    <t xml:space="preserve">19.118745803833</t>
   </si>
   <si>
     <t xml:space="preserve">18.0428009033203</t>
   </si>
   <si>
-    <t xml:space="preserve">17.794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8427066802979</t>
+    <t xml:space="preserve">17.7945041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8427085876465</t>
   </si>
   <si>
     <t xml:space="preserve">17.7531223297119</t>
@@ -1763,19 +1763,19 @@
     <t xml:space="preserve">17.3806781768799</t>
   </si>
   <si>
-    <t xml:space="preserve">16.966854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357936859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599430084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8840866088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5530300140381</t>
+    <t xml:space="preserve">16.9668560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357917785645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599411010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8840885162354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497119903564</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">19.1601314544678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4084281921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5739555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4498062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6499042510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3188400268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1119289398193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2842788696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0291633605957</t>
+    <t xml:space="preserve">19.40842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5739574432373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4498081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222503662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.64990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3188419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2842769622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.029167175293</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567211151123</t>
@@ -1829,64 +1829,64 @@
     <t xml:space="preserve">19.9463996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2428951263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3256645202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0359840393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2979164123535</t>
+    <t xml:space="preserve">19.2428970336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.325662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.035982131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
     <t xml:space="preserve">16.5364742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5944118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4868144989014</t>
+    <t xml:space="preserve">16.594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4868183135986</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910015106201</t>
+    <t xml:space="preserve">17.0910034179688</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310222625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.364128112793</t>
+    <t xml:space="preserve">17.3310203552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3641242980957</t>
   </si>
   <si>
     <t xml:space="preserve">18.2910957336426</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6056041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3407573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0593547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.645528793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2482566833496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289710998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.07590675354</t>
+    <t xml:space="preserve">18.6056022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3407554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0593566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6455268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2482585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0759086608887</t>
   </si>
   <si>
     <t xml:space="preserve">18.1255664825439</t>
@@ -1898,154 +1898,157 @@
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2248840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7613983154297</t>
+    <t xml:space="preserve">17.9765892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2248859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7614002227783</t>
   </si>
   <si>
     <t xml:space="preserve">16.5861339569092</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6192378997803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5033702850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101881027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274244308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701711654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8397922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328792572021</t>
+    <t xml:space="preserve">16.6192398071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5033721923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101890563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274215698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2701692581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397884368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328783035278</t>
   </si>
   <si>
     <t xml:space="preserve">14.6742601394653</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177825927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233345031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322891235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632524490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467014312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659822463989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3255748748779</t>
+    <t xml:space="preserve">15.6177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322900772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0632562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549783706665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.046703338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659841537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232345581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3255758285522</t>
   </si>
   <si>
     <t xml:space="preserve">15.3426027297974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7125539779663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402652740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614675521851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6444396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5422687530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811697006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5252389907837</t>
+    <t xml:space="preserve">14.7125520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6444387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.806209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5422677993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083805084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5252380371094</t>
   </si>
   <si>
     <t xml:space="preserve">14.4741544723511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2017002105713</t>
+    <t xml:space="preserve">14.2017011642456</t>
   </si>
   <si>
     <t xml:space="preserve">14.389012336731</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6018695831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315853118896</t>
+    <t xml:space="preserve">14.6018676757812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315843582153</t>
   </si>
   <si>
     <t xml:space="preserve">14.2357549667358</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846704483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317518234253</t>
+    <t xml:space="preserve">14.0484437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.831750869751</t>
   </si>
   <si>
     <t xml:space="preserve">14.5507831573486</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3208990097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7295789718628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4230699539185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3379278182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462728500366</t>
+    <t xml:space="preserve">14.320897102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7295799255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020360946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232393264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4230690002441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.337926864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3549547195435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462738037109</t>
   </si>
   <si>
     <t xml:space="preserve">13.6908473968506</t>
@@ -2063,22 +2066,22 @@
     <t xml:space="preserve">13.0948524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821664810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3975276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0995283126831</t>
+    <t xml:space="preserve">13.2821645736694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3975267410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0995292663574</t>
   </si>
   <si>
     <t xml:space="preserve">13.8866729736328</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8185596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225666046143</t>
+    <t xml:space="preserve">13.8185606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225656509399</t>
   </si>
   <si>
     <t xml:space="preserve">13.5801630020142</t>
@@ -2093,19 +2096,19 @@
     <t xml:space="preserve">13.1799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544513702393</t>
+    <t xml:space="preserve">13.1544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">13.2140522003174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1668033599854</t>
+    <t xml:space="preserve">12.1668043136597</t>
   </si>
   <si>
     <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9748163223267</t>
+    <t xml:space="preserve">10.9748153686523</t>
   </si>
   <si>
     <t xml:space="preserve">10.9492721557617</t>
@@ -2114,22 +2117,22 @@
     <t xml:space="preserve">10.5491046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7449321746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1706409454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7534456253052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0344133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811588287354</t>
+    <t xml:space="preserve">10.7449312210083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1706418991089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7534446716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0344142913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1621284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.881157875061</t>
   </si>
   <si>
     <t xml:space="preserve">10.7875022888184</t>
@@ -2138,19 +2141,19 @@
     <t xml:space="preserve">10.7619600296021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2511081695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0599565505981</t>
+    <t xml:space="preserve">10.2511072158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0599575042725</t>
   </si>
   <si>
     <t xml:space="preserve">10.8471021652222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6683025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7279024124146</t>
+    <t xml:space="preserve">10.6683034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7279033660889</t>
   </si>
   <si>
     <t xml:space="preserve">11.3664693832397</t>
@@ -2159,7 +2162,7 @@
     <t xml:space="preserve">11.5367527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6644659042358</t>
+    <t xml:space="preserve">11.6644649505615</t>
   </si>
   <si>
     <t xml:space="preserve">11.6900081634521</t>
@@ -2168,7 +2171,7 @@
     <t xml:space="preserve">11.7410926818848</t>
   </si>
   <si>
-    <t xml:space="preserve">11.749608039856</t>
+    <t xml:space="preserve">11.7496070861816</t>
   </si>
   <si>
     <t xml:space="preserve">12.1838331222534</t>
@@ -2177,28 +2180,28 @@
     <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8177223205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7751502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0476055145264</t>
+    <t xml:space="preserve">11.8177213668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7751512527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0476045608521</t>
   </si>
   <si>
     <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026960372925</t>
+    <t xml:space="preserve">11.5026950836182</t>
   </si>
   <si>
     <t xml:space="preserve">11.1450986862183</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8981885910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898406982422</t>
+    <t xml:space="preserve">10.8981876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898397445679</t>
   </si>
   <si>
     <t xml:space="preserve">11.2132129669189</t>
@@ -2210,16 +2213,16 @@
     <t xml:space="preserve">10.4724760055542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597909927368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0173854827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0854997634888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.051441192627</t>
+    <t xml:space="preserve">10.6597900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0173864364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0855007171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514430999756</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280708312988</t>
@@ -2228,10 +2231,10 @@
     <t xml:space="preserve">11.0003576278687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0088710784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2642974853516</t>
+    <t xml:space="preserve">11.0088720321655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2642965316772</t>
   </si>
   <si>
     <t xml:space="preserve">11.6985216140747</t>
@@ -2240,28 +2243,28 @@
     <t xml:space="preserve">11.6814947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8092079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3247375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1970224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2395935058594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5120496749878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6738176345825</t>
+    <t xml:space="preserve">11.8092069625854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3247346878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1970243453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2395944595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5120487213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6738195419312</t>
   </si>
   <si>
     <t xml:space="preserve">13.546106338501</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4145565032959</t>
+    <t xml:space="preserve">14.4145555496216</t>
   </si>
   <si>
     <t xml:space="preserve">13.8526182174683</t>
@@ -2273,16 +2276,16 @@
     <t xml:space="preserve">13.8781595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7759895324707</t>
+    <t xml:space="preserve">13.775990486145</t>
   </si>
   <si>
     <t xml:space="preserve">13.4439353942871</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8441019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4486122131348</t>
+    <t xml:space="preserve">13.8441028594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4486131668091</t>
   </si>
   <si>
     <t xml:space="preserve">14.6274099349976</t>
@@ -2294,82 +2297,82 @@
     <t xml:space="preserve">15.5043725967407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5933523178101</t>
+    <t xml:space="preserve">14.5933542251587</t>
   </si>
   <si>
     <t xml:space="preserve">14.5592966079712</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9424362182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9679794311523</t>
+    <t xml:space="preserve">14.942437171936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.967978477478</t>
   </si>
   <si>
     <t xml:space="preserve">14.6870098114014</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0190620422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.640604019165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4618005752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656400680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.363471031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3294143676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4826707839966</t>
+    <t xml:space="preserve">15.019063949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467761993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170595169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406021118164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3634700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3294134140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4826688766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.1506147384644</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1335859298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5763254165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1165590286255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4911832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804988861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996995925903</t>
+    <t xml:space="preserve">14.1335849761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5763263702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1165580749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4911842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.499698638916</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721529006958</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7078762054443</t>
+    <t xml:space="preserve">13.7078771591187</t>
   </si>
   <si>
     <t xml:space="preserve">13.9292459487915</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3162221908569</t>
+    <t xml:space="preserve">13.5035352706909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3162231445312</t>
   </si>
   <si>
     <t xml:space="preserve">13.5631341934204</t>
@@ -2378,61 +2381,61 @@
     <t xml:space="preserve">13.5375919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.269814491272</t>
+    <t xml:space="preserve">14.4060411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2698135375977</t>
   </si>
   <si>
     <t xml:space="preserve">14.2953577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5082111358643</t>
+    <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
     <t xml:space="preserve">14.5167255401611</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1761569976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931867599487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7589597702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4183921813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5584573745728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3370885848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9880056381226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6218948364258</t>
+    <t xml:space="preserve">14.176157951355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931858062744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.758960723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4183931350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5584583282471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3370876312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6010293960571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9880046844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6218938827515</t>
   </si>
   <si>
     <t xml:space="preserve">11.4430961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3277359008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82539653778076</t>
+    <t xml:space="preserve">10.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82539749145508</t>
   </si>
   <si>
     <t xml:space="preserve">9.4252290725708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74025344848633</t>
+    <t xml:space="preserve">9.74025440216064</t>
   </si>
   <si>
     <t xml:space="preserve">8.08424091339111</t>
@@ -2441,34 +2444,34 @@
     <t xml:space="preserve">8.7355785369873</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27155303955078</t>
+    <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
     <t xml:space="preserve">8.31412506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278743743896</t>
+    <t xml:space="preserve">7.96078586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278791427612</t>
   </si>
   <si>
     <t xml:space="preserve">9.11020278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00803184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41671466827393</t>
+    <t xml:space="preserve">9.00803279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41671562194824</t>
   </si>
   <si>
     <t xml:space="preserve">9.47631454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57848453521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225788116455</t>
+    <t xml:space="preserve">9.5784854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225692749023</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
@@ -2477,13 +2480,13 @@
     <t xml:space="preserve">9.09317493438721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16980361938477</t>
+    <t xml:space="preserve">9.16980266571045</t>
   </si>
   <si>
     <t xml:space="preserve">9.53591442108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48482894897461</t>
+    <t xml:space="preserve">9.48482799530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.62105655670166</t>
@@ -2498,7 +2501,7 @@
     <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75728225708008</t>
+    <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
     <t xml:space="preserve">9.8764820098877</t>
@@ -2513,7 +2516,7 @@
     <t xml:space="preserve">10.2936792373657</t>
   </si>
   <si>
-    <t xml:space="preserve">10.319221496582</t>
+    <t xml:space="preserve">10.3192205429077</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299058914185</t>
@@ -2522,7 +2525,7 @@
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961832046509</t>
+    <t xml:space="preserve">11.1961841583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
@@ -2534,13 +2537,13 @@
     <t xml:space="preserve">9.85945320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7828254699707</t>
+    <t xml:space="preserve">9.78282642364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.30603122711182</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51037120819092</t>
+    <t xml:space="preserve">9.51037216186523</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888656616211</t>
@@ -2555,37 +2558,37 @@
     <t xml:space="preserve">9.25494480133057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36563014984131</t>
+    <t xml:space="preserve">9.36562919616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.86329078674316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93140506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85477733612061</t>
+    <t xml:space="preserve">8.93140316009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85477638244629</t>
   </si>
   <si>
     <t xml:space="preserve">9.28048801422119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70619678497314</t>
+    <t xml:space="preserve">9.70619773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.62957096099854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85093879699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876697540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8300733566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5405902862549</t>
+    <t xml:space="preserve">9.85093784332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1876707077026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8300743103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5405912399292</t>
   </si>
   <si>
     <t xml:space="preserve">10.2340784072876</t>
@@ -2597,13 +2600,13 @@
     <t xml:space="preserve">9.96388339996338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2435722351074</t>
+    <t xml:space="preserve">10.2435741424561</t>
   </si>
   <si>
     <t xml:space="preserve">10.182391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1998710632324</t>
+    <t xml:space="preserve">10.1998720169067</t>
   </si>
   <si>
     <t xml:space="preserve">10.1649103164673</t>
@@ -2615,13 +2618,13 @@
     <t xml:space="preserve">10.444598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0163259506226</t>
+    <t xml:space="preserve">10.0163269042969</t>
   </si>
   <si>
     <t xml:space="preserve">9.90270328521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7278995513916</t>
+    <t xml:space="preserve">9.72789859771729</t>
   </si>
   <si>
     <t xml:space="preserve">9.64049625396729</t>
@@ -2636,16 +2639,16 @@
     <t xml:space="preserve">9.41324996948242</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5268726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49191093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40450859069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15978240966797</t>
+    <t xml:space="preserve">9.52687168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49191188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40450954437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15978145599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.99371719360352</t>
@@ -2654,25 +2657,25 @@
     <t xml:space="preserve">9.01993751525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9063138961792</t>
+    <t xml:space="preserve">8.90631484985352</t>
   </si>
   <si>
     <t xml:space="preserve">9.57931423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18600273132324</t>
+    <t xml:space="preserve">9.20348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36080837249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18600177764893</t>
   </si>
   <si>
     <t xml:space="preserve">9.33458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2209644317627</t>
+    <t xml:space="preserve">9.22096252441406</t>
   </si>
   <si>
     <t xml:space="preserve">9.44821071624756</t>
@@ -2684,19 +2687,19 @@
     <t xml:space="preserve">9.01119804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3484563827515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358587265015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271183013916</t>
+    <t xml:space="preserve">10.3484554290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358568191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271173477173</t>
   </si>
   <si>
     <t xml:space="preserve">10.9777536392212</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1001167297363</t>
+    <t xml:space="preserve">11.1001176834106</t>
   </si>
   <si>
     <t xml:space="preserve">11.3186225891113</t>
@@ -2708,52 +2711,49 @@
     <t xml:space="preserve">11.0826377868652</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8903522491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7942085266113</t>
+    <t xml:space="preserve">10.8903503417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7942094802856</t>
   </si>
   <si>
     <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5494813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872743606567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299495697021</t>
+    <t xml:space="preserve">10.5494804382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872753143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.226092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299486160278</t>
   </si>
   <si>
     <t xml:space="preserve">9.98136520385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93766307830811</t>
+    <t xml:space="preserve">9.93766498565674</t>
   </si>
   <si>
     <t xml:space="preserve">10.094988822937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1124677658081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250663757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87648296356201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95514488220215</t>
+    <t xml:space="preserve">10.1124696731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250673294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95514583587646</t>
   </si>
   <si>
     <t xml:space="preserve">9.78033924102783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75411987304688</t>
+    <t xml:space="preserve">9.75411796569824</t>
   </si>
   <si>
     <t xml:space="preserve">9.6579761505127</t>
@@ -2762,19 +2762,19 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884414672852</t>
+    <t xml:space="preserve">9.99884510040283</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222360610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7330265045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.750506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620790481567</t>
+    <t xml:space="preserve">10.7330274581909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7505073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620780944824</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
@@ -2786,34 +2786,34 @@
     <t xml:space="preserve">10.3659362792969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4970397949219</t>
+    <t xml:space="preserve">10.4970407485962</t>
   </si>
   <si>
     <t xml:space="preserve">10.6893253326416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6106634140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4795598983765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5757026672363</t>
+    <t xml:space="preserve">10.6106643676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4795589447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5757036209106</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5582218170166</t>
+    <t xml:space="preserve">10.5232601165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5582208633423</t>
   </si>
   <si>
     <t xml:space="preserve">10.4708185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81530094146729</t>
+    <t xml:space="preserve">9.81529998779297</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
@@ -2828,7 +2828,7 @@
     <t xml:space="preserve">9.86774253845215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61427593231201</t>
+    <t xml:space="preserve">9.6142749786377</t>
   </si>
   <si>
     <t xml:space="preserve">9.00245761871338</t>
@@ -2846,34 +2846,34 @@
     <t xml:space="preserve">8.6441068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12482070922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1685209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98497581481934</t>
+    <t xml:space="preserve">9.1248197555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98497676849365</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293785095215</t>
+    <t xml:space="preserve">9.69293689727783</t>
   </si>
   <si>
     <t xml:space="preserve">10.9078311920166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1350784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070518493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324918746948</t>
+    <t xml:space="preserve">11.1350774765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070508956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324928283691</t>
   </si>
   <si>
     <t xml:space="preserve">12.3587141036987</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">12.4810762405396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.19264793396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139860153198</t>
+    <t xml:space="preserve">12.1926488876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139869689941</t>
   </si>
   <si>
     <t xml:space="preserve">12.210129737854</t>
@@ -2900,25 +2900,25 @@
     <t xml:space="preserve">11.6857137680054</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0702848434448</t>
+    <t xml:space="preserve">12.0702857971191</t>
   </si>
   <si>
     <t xml:space="preserve">11.974142074585</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9916229248047</t>
+    <t xml:space="preserve">11.991623878479</t>
   </si>
   <si>
     <t xml:space="preserve">11.947922706604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0615453720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314678192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440645217896</t>
+    <t xml:space="preserve">12.061544418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314659118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440635681152</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954801559448</t>
@@ -2930,13 +2930,13 @@
     <t xml:space="preserve">12.0178442001343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6558809280396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.673360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4898166656494</t>
+    <t xml:space="preserve">12.6558818817139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6733617782593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4898176193237</t>
   </si>
   <si>
     <t xml:space="preserve">12.4198951721191</t>
@@ -2954,40 +2954,40 @@
     <t xml:space="preserve">12.2363500595093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4461145401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.516037940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5509996414185</t>
+    <t xml:space="preserve">12.4461154937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5160369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8132057189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8394269943237</t>
+    <t xml:space="preserve">12.8132066726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8394260406494</t>
   </si>
   <si>
     <t xml:space="preserve">12.909348487854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8219451904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9880104064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0229711532593</t>
+    <t xml:space="preserve">12.821946144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9880094528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0229721069336</t>
   </si>
   <si>
     <t xml:space="preserve">13.3114004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2152585983276</t>
+    <t xml:space="preserve">13.215256690979</t>
   </si>
   <si>
     <t xml:space="preserve">13.2502193450928</t>
@@ -2996,34 +2996,34 @@
     <t xml:space="preserve">12.7607641220093</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6296615600586</t>
+    <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
     <t xml:space="preserve">12.953049659729</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9792709350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9355688095093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.302661895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.407543182373</t>
+    <t xml:space="preserve">12.9792718887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9355697631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3026599884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4075441360474</t>
   </si>
   <si>
     <t xml:space="preserve">13.1890382766724</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2239990234375</t>
+    <t xml:space="preserve">13.2239980697632</t>
   </si>
   <si>
     <t xml:space="preserve">13.800853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0280990600586</t>
+    <t xml:space="preserve">14.0281000137329</t>
   </si>
   <si>
     <t xml:space="preserve">14.106761932373</t>
@@ -3035,52 +3035,52 @@
     <t xml:space="preserve">14.5000743865967</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4039316177368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5612554550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2116460800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7484121322632</t>
+    <t xml:space="preserve">14.4039306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5612573623657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2116470336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7484140396118</t>
   </si>
   <si>
     <t xml:space="preserve">14.0980224609375</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7221927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3864498138428</t>
+    <t xml:space="preserve">13.7221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3864517211914</t>
   </si>
   <si>
     <t xml:space="preserve">14.6661386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7098417282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6224384307861</t>
+    <t xml:space="preserve">14.7098398208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6224374771118</t>
   </si>
   <si>
     <t xml:space="preserve">15.0157489776611</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818141937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653602600098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1206302642822</t>
+    <t xml:space="preserve">15.1818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653593063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1206312179565</t>
   </si>
   <si>
     <t xml:space="preserve">14.456374168396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6136960983276</t>
+    <t xml:space="preserve">14.6136980056763</t>
   </si>
   <si>
     <t xml:space="preserve">14.762282371521</t>
@@ -3089,40 +3089,40 @@
     <t xml:space="preserve">16.3442687988281</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7550582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946546554565</t>
+    <t xml:space="preserve">16.7550601959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946556091309</t>
   </si>
   <si>
     <t xml:space="preserve">15.8373327255249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9159936904907</t>
+    <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.9247331619263</t>
   </si>
   <si>
-    <t xml:space="preserve">15.942214012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.13450050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.43528175354</t>
+    <t xml:space="preserve">15.9422149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1344985961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4352798461914</t>
   </si>
   <si>
     <t xml:space="preserve">15.566385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3566188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303995132446</t>
+    <t xml:space="preserve">15.3566198348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440221786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303985595703</t>
   </si>
   <si>
     <t xml:space="preserve">15.2429962158203</t>
@@ -3134,13 +3134,13 @@
     <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779569625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517366409302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.068190574646</t>
+    <t xml:space="preserve">15.2779550552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517375946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0681915283203</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381120681763</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">15.4265403747559</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0244913101196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8933849334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234634399414</t>
+    <t xml:space="preserve">15.0244922637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8933877944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234615325928</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
@@ -3164,10 +3164,10 @@
     <t xml:space="preserve">14.9196071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">14.99827003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9370880126953</t>
+    <t xml:space="preserve">14.9982671737671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9370889663696</t>
   </si>
   <si>
     <t xml:space="preserve">15.1468534469604</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">15.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2604761123657</t>
+    <t xml:space="preserve">15.2604751586914</t>
   </si>
   <si>
     <t xml:space="preserve">15.3041772842407</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">14.8409433364868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4214134216309</t>
+    <t xml:space="preserve">14.4214124679565</t>
   </si>
   <si>
     <t xml:space="preserve">14.5962181091309</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7812805175781</t>
+    <t xml:space="preserve">16.7812824249268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4367980957031</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048980712891</t>
+    <t xml:space="preserve">18.5048999786377</t>
   </si>
   <si>
     <t xml:space="preserve">18.7340068817139</t>
@@ -3224,7 +3224,7 @@
     <t xml:space="preserve">18.8573722839355</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8221282958984</t>
+    <t xml:space="preserve">18.8221263885498</t>
   </si>
   <si>
     <t xml:space="preserve">19.3684597015381</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">18.2052955627441</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6987590789795</t>
+    <t xml:space="preserve">18.6987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">18.7163829803467</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2934131622314</t>
+    <t xml:space="preserve">18.2934150695801</t>
   </si>
   <si>
     <t xml:space="preserve">18.2581653594971</t>
@@ -3281,19 +3281,19 @@
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.888069152832</t>
+    <t xml:space="preserve">17.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6413383483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5708427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589622497559</t>
+    <t xml:space="preserve">17.64133644104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5708446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589603424072</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">17.3681697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4650993347168</t>
+    <t xml:space="preserve">17.1478710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4650974273682</t>
   </si>
   <si>
     <t xml:space="preserve">17.9761867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8351974487305</t>
+    <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
@@ -3320,22 +3320,22 @@
     <t xml:space="preserve">17.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.125696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5222320556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6367874145508</t>
+    <t xml:space="preserve">16.3724308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1256980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5222339630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6367855072021</t>
   </si>
   <si>
     <t xml:space="preserve">17.3857936859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2448024749756</t>
+    <t xml:space="preserve">17.2448043823242</t>
   </si>
   <si>
     <t xml:space="preserve">17.3769798278809</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">17.7470779418945</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5355930328369</t>
+    <t xml:space="preserve">17.5355949401855</t>
   </si>
   <si>
     <t xml:space="preserve">17.6237144470215</t>
@@ -3359,13 +3359,13 @@
     <t xml:space="preserve">16.8747062683105</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0861873626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1743087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417339324951</t>
+    <t xml:space="preserve">17.0861892700195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1743106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417358398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">16.9716358184814</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7249031066895</t>
+    <t xml:space="preserve">16.7249011993408</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">16.8042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2183704376221</t>
+    <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
@@ -3419,7 +3419,7 @@
     <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927276611328</t>
+    <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
     <t xml:space="preserve">16.4957942962646</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">16.3900527954102</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3019371032715</t>
+    <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
     <t xml:space="preserve">15.9935188293457</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">15.8613433837891</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2402515411377</t>
+    <t xml:space="preserve">16.2402534484863</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">16.3195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7732219696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176801681519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119358062744</t>
+    <t xml:space="preserve">15.7732229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590660095215</t>
@@ -3464,16 +3464,16 @@
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154037475586</t>
+    <t xml:space="preserve">15.3150043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
     <t xml:space="preserve">15.2180776596069</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1828269958496</t>
+    <t xml:space="preserve">15.1828279495239</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242147445679</t>
@@ -3485,16 +3485,16 @@
     <t xml:space="preserve">15.1035223007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4912433624268</t>
+    <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.1475820541382</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0859003067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9801568984985</t>
+    <t xml:space="preserve">15.0858993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9801559448242</t>
   </si>
   <si>
     <t xml:space="preserve">14.8215436935425</t>
@@ -3503,7 +3503,7 @@
     <t xml:space="preserve">14.6188697814941</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3985748291016</t>
+    <t xml:space="preserve">14.3985738754272</t>
   </si>
   <si>
     <t xml:space="preserve">14.0020408630371</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">14.3104553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.345703125</t>
+    <t xml:space="preserve">14.3457040786743</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3536,37 +3536,37 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483770370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4778814315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254072189331</t>
+    <t xml:space="preserve">14.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4778804779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254062652588</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8169927597046</t>
+    <t xml:space="preserve">13.8169918060303</t>
   </si>
   <si>
     <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0856084823608</t>
+    <t xml:space="preserve">13.772931098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.032735824585</t>
+    <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
@@ -3578,10 +3578,10 @@
     <t xml:space="preserve">12.9446172714233</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583776473999</t>
+    <t xml:space="preserve">13.3852109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583766937256</t>
   </si>
   <si>
     <t xml:space="preserve">13.5350112915039</t>
@@ -3590,13 +3590,13 @@
     <t xml:space="preserve">13.5614471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1913499832153</t>
+    <t xml:space="preserve">13.191349029541</t>
   </si>
   <si>
     <t xml:space="preserve">13.2265977859497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6231298446655</t>
+    <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
     <t xml:space="preserve">13.314715385437</t>
@@ -3605,22 +3605,22 @@
     <t xml:space="preserve">13.2618436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.438081741333</t>
+    <t xml:space="preserve">13.4557065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4380807876587</t>
   </si>
   <si>
     <t xml:space="preserve">13.4645166397095</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4997634887695</t>
+    <t xml:space="preserve">13.4997644424438</t>
   </si>
   <si>
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878839492798</t>
+    <t xml:space="preserve">13.5878829956055</t>
   </si>
   <si>
     <t xml:space="preserve">13.5702600479126</t>
@@ -3629,13 +3629,13 @@
     <t xml:space="preserve">13.7112503051758</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4468946456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388748168945</t>
+    <t xml:space="preserve">13.4468936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710540771484</t>
@@ -3656,13 +3656,13 @@
     <t xml:space="preserve">12.5568962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273918151855</t>
+    <t xml:space="preserve">12.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492748260498</t>
+    <t xml:space="preserve">11.6492738723755</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
@@ -3671,10 +3671,10 @@
     <t xml:space="preserve">11.8078870773315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9048194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8431348800659</t>
+    <t xml:space="preserve">11.9048185348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8431358337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3683,16 +3683,16 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.464225769043</t>
+    <t xml:space="preserve">11.5347194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4642248153687</t>
   </si>
   <si>
     <t xml:space="preserve">11.1117506027222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9090785980225</t>
+    <t xml:space="preserve">10.9090795516968</t>
   </si>
   <si>
     <t xml:space="preserve">11.2263050079346</t>
@@ -3701,7 +3701,7 @@
     <t xml:space="preserve">11.1293754577637</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0412549972534</t>
+    <t xml:space="preserve">11.0412559509277</t>
   </si>
   <si>
     <t xml:space="preserve">10.8209600448608</t>
@@ -3731,7 +3731,7 @@
     <t xml:space="preserve">10.6975936889648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0500679016113</t>
+    <t xml:space="preserve">11.0500688552856</t>
   </si>
   <si>
     <t xml:space="preserve">10.4772977828979</t>
@@ -3776,10 +3776,10 @@
     <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977798461914</t>
+    <t xml:space="preserve">9.25244998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977703094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.83829212188721</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">9.24363708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74576854705811</t>
+    <t xml:space="preserve">8.74576759338379</t>
   </si>
   <si>
     <t xml:space="preserve">8.68848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62680721282959</t>
+    <t xml:space="preserve">8.62680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27873992919922</t>
+    <t xml:space="preserve">8.2787389755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349212646484</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433300018311</t>
+    <t xml:space="preserve">8.27433395385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245155334473</t>
+    <t xml:space="preserve">8.36245059967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3848,43 +3848,43 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88661098480225</t>
+    <t xml:space="preserve">7.8866114616394</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760219573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.895423412323</t>
+    <t xml:space="preserve">8.02760124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80730533599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819700241089</t>
+    <t xml:space="preserve">7.80730485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527641296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6751275062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95803880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512655258179</t>
+    <t xml:space="preserve">7.66190958023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512702941895</t>
   </si>
   <si>
     <t xml:space="preserve">7.62037038803101</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124160766602</t>
+    <t xml:space="preserve">8.08124256134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.92609739303589</t>
@@ -3911,16 +3911,16 @@
     <t xml:space="preserve">7.64774894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570886611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67968988418579</t>
+    <t xml:space="preserve">7.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736089706421</t>
+    <t xml:space="preserve">7.54736042022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833311080933</t>
+    <t xml:space="preserve">6.85833263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">6.90396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444932937622</t>
+    <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406127929688</t>
+    <t xml:space="preserve">6.69406175613403</t>
   </si>
   <si>
     <t xml:space="preserve">6.46590709686279</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212055206299</t>
+    <t xml:space="preserve">6.19212102890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891658782959</t>
+    <t xml:space="preserve">6.53891611099243</t>
   </si>
   <si>
     <t xml:space="preserve">6.55260562896729</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474082946777</t>
+    <t xml:space="preserve">6.46134376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474130630493</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173133850098</t>
+    <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813837051392</t>
+    <t xml:space="preserve">6.80813884735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231248855591</t>
+    <t xml:space="preserve">7.18231296539307</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12687397003174</t>
+    <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
     <t xml:space="preserve">8.35046482086182</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">7.81658220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03104972839355</t>
+    <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
     <t xml:space="preserve">7.89415502548218</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910852432251</t>
+    <t xml:space="preserve">7.52910804748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775032043457</t>
+    <t xml:space="preserve">6.48415851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
     <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27425718307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0506649017334</t>
+    <t xml:space="preserve">6.27425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05066537857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610204696655</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27881956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445049285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746046066284</t>
+    <t xml:space="preserve">6.2788200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39745998382568</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901266098022</t>
+    <t xml:space="preserve">6.79901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959449768066</t>
+    <t xml:space="preserve">6.94959497451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978595733643</t>
+    <t xml:space="preserve">7.93978691101074</t>
   </si>
   <si>
     <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12231063842773</t>
+    <t xml:space="preserve">8.12230968475342</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76638889312744</t>
+    <t xml:space="preserve">7.69794321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7663893699646</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77095317840576</t>
+    <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91697216033936</t>
+    <t xml:space="preserve">7.9169716835022</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4262,22 +4262,22 @@
     <t xml:space="preserve">7.57017517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62949562072754</t>
+    <t xml:space="preserve">7.62949514389038</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55192279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31464290618896</t>
+    <t xml:space="preserve">7.5519232749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17774963378906</t>
+    <t xml:space="preserve">7.1777491569519</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45609855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46978855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59755373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79376745223999</t>
+    <t xml:space="preserve">7.4560980796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46978807449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79376792907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38697052001953</t>
+    <t xml:space="preserve">8.38696956634521</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">8.36871719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81589984893799</t>
+    <t xml:space="preserve">8.8159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.94366836547852</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98017311096191</t>
+    <t xml:space="preserve">8.9801721572876</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">8.8432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89347362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77939510345459</t>
+    <t xml:space="preserve">8.89347457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77939605712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.7292013168335</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41891288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40978622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44172763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22726154327393</t>
+    <t xml:space="preserve">8.41891193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40978527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44172668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.21813488006592</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949493408203</t>
+    <t xml:space="preserve">8.24551296234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949398040771</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085472106934</t>
+    <t xml:space="preserve">7.83483457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68881607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085519790649</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580493927002</t>
+    <t xml:space="preserve">8.09493160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580589294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716451644897</t>
+    <t xml:space="preserve">7.96716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24163293838501</t>
+    <t xml:space="preserve">7.24163246154785</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804161071777</t>
+    <t xml:space="preserve">7.01804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745882034302</t>
+    <t xml:space="preserve">6.86745929718018</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88114786148071</t>
+    <t xml:space="preserve">6.88114833831787</t>
   </si>
   <si>
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78075981140137</t>
+    <t xml:space="preserve">6.78076028823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">6.90852737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76707077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561559677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62105178833008</t>
+    <t xml:space="preserve">6.76707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62105226516724</t>
   </si>
   <si>
     <t xml:space="preserve">6.43852758407593</t>
@@ -29373,7 +29373,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G894" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G895" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G896" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G897" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G898" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G899" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G900" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G903" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G904" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G906" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G907" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G908" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G909" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G910" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>16</v>
       </c>
       <c r="G912" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G913" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G914" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G915" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G916" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G917" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G918" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G919" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G920" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G921" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G922" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G923" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G924" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G925" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G926" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G927" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G928" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G929" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G930" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G931" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G932" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G933" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G934" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G936" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G937" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G938" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G939" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G940" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G941" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G942" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G943" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G944" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G945" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G947" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G948" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G949" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G950" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G951" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G952" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G953" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G954" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G955" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G956" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G957" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G958" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G959" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G960" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G961" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G962" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G963" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G964" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G965" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G966" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G967" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G968" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G969" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G970" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G971" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G972" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G974" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G975" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G976" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>15.5</v>
       </c>
       <c r="G979" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31609,7 +31609,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G980" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G981" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G982" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G983" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G984" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G986" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G988" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G990" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G991" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G992" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G994" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G995" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G996" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G997" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G998" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1002" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>17.25</v>
       </c>
       <c r="G1003" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G1006" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1007" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1008" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1009" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1011" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1012" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1013" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32493,7 +32493,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1014" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1015" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32597,7 +32597,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1018" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32623,7 +32623,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32675,7 +32675,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1021" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32701,7 +32701,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1022" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32727,7 +32727,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1023" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1025" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1028" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1029" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1030" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1031" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1032" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1033" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1034" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1035" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1036" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1037" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G1038" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1039" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G1040" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1042" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1043" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1045" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -33325,7 +33325,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1046" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1047" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33377,7 +33377,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33403,7 +33403,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G1050" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33455,7 +33455,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1051" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1052" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>14.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1054" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1055" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1056" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1058" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1059" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1060" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1061" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1062" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1063" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1065" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>9.49499988555908</v>
       </c>
       <c r="G1066" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1067" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1068" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1069" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1070" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>9</v>
       </c>
       <c r="G1071" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1073" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1074" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1075" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>11.25</v>
       </c>
       <c r="G1076" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1077" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1078" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1079" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1080" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -34235,7 +34235,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1082" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -34313,7 +34313,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1084" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1086" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1087" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1088" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1089" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1090" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1091" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1093" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1094" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>12.25</v>
       </c>
       <c r="G1095" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1096" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1097" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1099" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1101" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1103" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1104" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G1105" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1106" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1107" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1108" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G1109" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>11</v>
       </c>
       <c r="G1110" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>11</v>
       </c>
       <c r="G1111" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1112" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1113" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1115" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1117" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1119" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1122" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1123" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1124" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1125" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1126" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1127" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1128" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1130" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1131" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1132" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1133" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1134" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G1135" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1136" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1137" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1138" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1139" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1140" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1141" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1142" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1143" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1144" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1146" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1147" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1148" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1149" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1150" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -36055,7 +36055,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1151" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -36081,7 +36081,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1152" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1153" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1154" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1155" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1156" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -36211,7 +36211,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1158" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G1159" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1160" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1161" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -36341,7 +36341,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1162" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -36367,7 +36367,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1163" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -36393,7 +36393,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1164" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -36419,7 +36419,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1165" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -36445,7 +36445,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1166" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -36471,7 +36471,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1167" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -36497,7 +36497,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1168" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -36523,7 +36523,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1169" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -36549,7 +36549,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1170" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -36575,7 +36575,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1171" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -36601,7 +36601,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1172" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -36627,7 +36627,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1173" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -36653,7 +36653,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1174" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -36679,7 +36679,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1175" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -36705,7 +36705,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1176" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -36731,7 +36731,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1177" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -36757,7 +36757,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1178" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -36783,7 +36783,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1179" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36809,7 +36809,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1180" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36835,7 +36835,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1181" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36861,7 +36861,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1182" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36887,7 +36887,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1183" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36913,7 +36913,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G1184" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36939,7 +36939,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>910</v>
+        <v>830</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -37095,7 +37095,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1191" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37173,7 +37173,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1194" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -37199,7 +37199,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1195" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -37355,7 +37355,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1201" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -37511,7 +37511,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1207" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -37745,7 +37745,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -37771,7 +37771,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1217" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -37953,7 +37953,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1224" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -38291,7 +38291,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1237" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -72645,7 +72645,7 @@
     </row>
     <row r="2559">
       <c r="A2559" s="1" t="n">
-        <v>46049.6912847222</v>
+        <v>46049.3333333333</v>
       </c>
       <c r="B2559" t="n">
         <v>191986</v>
@@ -72666,6 +72666,32 @@
         <v>1882</v>
       </c>
       <c r="H2559" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2560">
+      <c r="A2560" s="1" t="n">
+        <v>46050.6910763889</v>
+      </c>
+      <c r="B2560" t="n">
+        <v>98498</v>
+      </c>
+      <c r="C2560" t="n">
+        <v>4.38000011444092</v>
+      </c>
+      <c r="D2560" t="n">
+        <v>4.23999977111816</v>
+      </c>
+      <c r="E2560" t="n">
+        <v>4.26000022888184</v>
+      </c>
+      <c r="F2560" t="n">
+        <v>4.27500009536743</v>
+      </c>
+      <c r="G2560" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H2560" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1929" uniqueCount="1929">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1930" uniqueCount="1930">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608814239502</t>
+    <t xml:space="preserve">12.7608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846279144287</t>
+    <t xml:space="preserve">12.784628868103</t>
   </si>
   <si>
     <t xml:space="preserve">12.7767133712769</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4758977890015</t>
+    <t xml:space="preserve">12.4759006500244</t>
   </si>
   <si>
     <t xml:space="preserve">11.9930114746094</t>
@@ -59,28 +59,28 @@
     <t xml:space="preserve">11.8742685317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2700786590576</t>
+    <t xml:space="preserve">12.270076751709</t>
   </si>
   <si>
     <t xml:space="preserve">12.5233955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9746179580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075626373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4125699996948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6738033294678</t>
+    <t xml:space="preserve">12.9746160507202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075645446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4125690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6738042831421</t>
   </si>
   <si>
     <t xml:space="preserve">12.0563411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3729877471924</t>
+    <t xml:space="preserve">12.3729887008667</t>
   </si>
   <si>
     <t xml:space="preserve">12.1750831604004</t>
@@ -92,25 +92,25 @@
     <t xml:space="preserve">12.1909160614014</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7713565826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367816925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9850969314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955720901489</t>
+    <t xml:space="preserve">11.7713575363159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9850950241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955730438232</t>
   </si>
   <si>
     <t xml:space="preserve">11.4626274108887</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1063976287842</t>
+    <t xml:space="preserve">11.1063995361328</t>
   </si>
   <si>
     <t xml:space="preserve">11.4942922592163</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">11.7159452438354</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8346881866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763639450073</t>
+    <t xml:space="preserve">11.8346872329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6763648986816</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684484481812</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">11.3992977142334</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1855611801147</t>
+    <t xml:space="preserve">11.1855621337891</t>
   </si>
   <si>
     <t xml:space="preserve">11.9692630767822</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">12.3888206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284009933472</t>
+    <t xml:space="preserve">12.4284019470215</t>
   </si>
   <si>
     <t xml:space="preserve">12.2304973602295</t>
@@ -164,34 +164,34 @@
     <t xml:space="preserve">12.1513357162476</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1196708679199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242101669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9825325012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9508714675903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704271316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387613296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575052261353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5762500762939</t>
+    <t xml:space="preserve">12.1196727752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242092132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.982533454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.950870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408576965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704261779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575023651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762481689453</t>
   </si>
   <si>
     <t xml:space="preserve">13.5999975204468</t>
@@ -200,37 +200,37 @@
     <t xml:space="preserve">13.3625087738037</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0379457473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7529649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091928482056</t>
+    <t xml:space="preserve">13.0379467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.752965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171083450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091938018799</t>
   </si>
   <si>
     <t xml:space="preserve">13.1962699890137</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9904508590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0221147537231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933618545532</t>
+    <t xml:space="preserve">12.9904489517212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0221138000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933609008789</t>
   </si>
   <si>
     <t xml:space="preserve">13.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0300312042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975526809692</t>
+    <t xml:space="preserve">13.030029296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975517272949</t>
   </si>
   <si>
     <t xml:space="preserve">12.602557182312</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">12.650053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8637895584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867261886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788068771362</t>
+    <t xml:space="preserve">12.8637914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788087844849</t>
   </si>
   <si>
     <t xml:space="preserve">12.7286968231201</t>
@@ -263,85 +263,85 @@
     <t xml:space="preserve">12.1091585159302</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9884691238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241018295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2218008041382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.22984790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942142486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620306015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2861680984497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4953651428223</t>
+    <t xml:space="preserve">11.988468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241008758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2218017578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2298469543457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620296478271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2861700057983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4953641891479</t>
   </si>
   <si>
     <t xml:space="preserve">12.7126045227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.809157371521</t>
+    <t xml:space="preserve">12.8091564178467</t>
   </si>
   <si>
     <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0263967514038</t>
+    <t xml:space="preserve">13.0263986587524</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654766082764</t>
+    <t xml:space="preserve">12.8654775619507</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666296005249</t>
+    <t xml:space="preserve">12.5999622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666286468506</t>
   </si>
   <si>
     <t xml:space="preserve">12.3103065490723</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7390441894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011135101318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884702682495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8781261444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792798995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689277648926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103086471558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3689308166504</t>
+    <t xml:space="preserve">11.7390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884712219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8781270980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792779922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689287185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3689298629761</t>
   </si>
   <si>
     <t xml:space="preserve">11.4896202087402</t>
@@ -350,40 +350,40 @@
     <t xml:space="preserve">10.757438659668</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0735330581665</t>
+    <t xml:space="preserve">10.0735349655151</t>
   </si>
   <si>
     <t xml:space="preserve">10.4597387313843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0229549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424942016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6344480514526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321500778198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827260971069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160577774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229518890381</t>
+    <t xml:space="preserve">11.0229539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.634446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321491241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.92640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160587310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229528427124</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700798034668</t>
+    <t xml:space="preserve">11.5700778961182</t>
   </si>
   <si>
     <t xml:space="preserve">11.891918182373</t>
@@ -392,127 +392,127 @@
     <t xml:space="preserve">11.5861711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">11.875825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953662872314</t>
+    <t xml:space="preserve">11.8758268356323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953653335571</t>
   </si>
   <si>
     <t xml:space="preserve">12.1896181106567</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896150588989</t>
+    <t xml:space="preserve">12.4309959411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896160125732</t>
   </si>
   <si>
     <t xml:space="preserve">13.0505342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9942111968994</t>
+    <t xml:space="preserve">12.9942140579224</t>
   </si>
   <si>
     <t xml:space="preserve">13.1229486465454</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1551332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861669540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746717453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482360839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.249382019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194984436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459329605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643213272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206462860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034030914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022531509399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137502670288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516771316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562770843506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183462142944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505289077759</t>
+    <t xml:space="preserve">13.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0746726989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482351303101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493801116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194974899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459348678589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919088363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643232345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6275415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206453323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022550582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137493133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516790390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7562761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505279541016</t>
   </si>
   <si>
     <t xml:space="preserve">15.1263904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.08616065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0459299087524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2953538894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240913391113</t>
+    <t xml:space="preserve">15.086163520813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0459327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.295352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.424090385437</t>
   </si>
   <si>
     <t xml:space="preserve">15.4562740325928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3597240447998</t>
+    <t xml:space="preserve">15.3597230911255</t>
   </si>
   <si>
     <t xml:space="preserve">15.2873096466064</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240934371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7884616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930568695068</t>
+    <t xml:space="preserve">14.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.788459777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930578231812</t>
   </si>
   <si>
     <t xml:space="preserve">15.4884605407715</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">15.4401845932007</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2148962020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8045501708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3919048309326</t>
+    <t xml:space="preserve">15.214898109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8045511245728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3919076919556</t>
   </si>
   <si>
     <t xml:space="preserve">15.2551250457764</t>
@@ -536,91 +536,91 @@
     <t xml:space="preserve">15.1666202545166</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286874771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229413986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.013747215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850126266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.311448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436319351196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286905288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5390357971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5551261901855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126003265381</t>
+    <t xml:space="preserve">15.5286884307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229433059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0137491226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198802947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114461898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.367769241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034019470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.182713508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654703140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470817565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.828688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5390377044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5551300048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1126022338867</t>
   </si>
   <si>
     <t xml:space="preserve">14.4263925552368</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2815675735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827146530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171983718872</t>
+    <t xml:space="preserve">14.2815656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827136993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2172002792358</t>
   </si>
   <si>
     <t xml:space="preserve">14.4103012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5631761550903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585752487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057041168213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045570373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217964172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781196594238</t>
+    <t xml:space="preserve">14.563175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045579910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9516830444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781215667725</t>
   </si>
   <si>
     <t xml:space="preserve">13.4045572280884</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">13.3643274307251</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1873159408569</t>
+    <t xml:space="preserve">13.1873149871826</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539842605591</t>
@@ -638,85 +638,85 @@
     <t xml:space="preserve">13.3160514831543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5896139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746725082397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.911452293396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9999570846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9815635681152</t>
+    <t xml:space="preserve">13.5896129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746715545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9114542007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011079788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9999561309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9815626144409</t>
   </si>
   <si>
     <t xml:space="preserve">15.0378847122192</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447828292847</t>
+    <t xml:space="preserve">14.716046333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447818756104</t>
   </si>
   <si>
     <t xml:space="preserve">14.917197227478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2631721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528259277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536732673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643220901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.383861541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.609148979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045518875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.407998085022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1103000640869</t>
+    <t xml:space="preserve">15.2631731033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6011009216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528249740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367317199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4643201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838605880737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091480255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045490264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4079971313477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1102991104126</t>
   </si>
   <si>
     <t xml:space="preserve">15.2068500518799</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8263921737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.89075756073</t>
+    <t xml:space="preserve">15.8263874053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907556533813</t>
   </si>
   <si>
     <t xml:space="preserve">15.8988027572632</t>
   </si>
   <si>
-    <t xml:space="preserve">15.947078704834</t>
+    <t xml:space="preserve">15.9470777511597</t>
   </si>
   <si>
     <t xml:space="preserve">16.0114459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493728637695</t>
+    <t xml:space="preserve">16.3493766784668</t>
   </si>
   <si>
     <t xml:space="preserve">16.3010997772217</t>
@@ -725,37 +725,37 @@
     <t xml:space="preserve">16.5344295501709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5827102661133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3332843780518</t>
+    <t xml:space="preserve">16.5827083587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3332805633545</t>
   </si>
   <si>
     <t xml:space="preserve">16.453971862793</t>
   </si>
   <si>
-    <t xml:space="preserve">16.17236328125</t>
+    <t xml:space="preserve">16.1723670959473</t>
   </si>
   <si>
     <t xml:space="preserve">16.1562728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9792642593384</t>
+    <t xml:space="preserve">15.9792633056641</t>
   </si>
   <si>
     <t xml:space="preserve">15.7700662612915</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0919075012207</t>
+    <t xml:space="preserve">16.0919017791748</t>
   </si>
   <si>
     <t xml:space="preserve">16.0033988952637</t>
   </si>
   <si>
-    <t xml:space="preserve">16.043628692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4781093597412</t>
+    <t xml:space="preserve">16.0436305999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4781131744385</t>
   </si>
   <si>
     <t xml:space="preserve">16.8964996337891</t>
@@ -764,70 +764,70 @@
     <t xml:space="preserve">16.9769592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792591094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5160369873047</t>
+    <t xml:space="preserve">17.0413284301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.516040802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.773509979248</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850021362305</t>
+    <t xml:space="preserve">18.3850040435791</t>
   </si>
   <si>
     <t xml:space="preserve">18.7470684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7229328155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206317901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2700538635254</t>
+    <t xml:space="preserve">18.7229309082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206336975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2700576782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907470703125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4068374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4470672607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033855438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079883575439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3826999664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5838508605957</t>
+    <t xml:space="preserve">19.4068393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4470691680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033893585205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079845428467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125835418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5838489532471</t>
   </si>
   <si>
     <t xml:space="preserve">19.3102874755859</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5436210632324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631576538086</t>
+    <t xml:space="preserve">19.5436229705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631595611572</t>
   </si>
   <si>
     <t xml:space="preserve">19.0689086914062</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">19.0769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355731964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.028678894043</t>
+    <t xml:space="preserve">18.8355751037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286808013916</t>
   </si>
   <si>
     <t xml:space="preserve">18.9723567962646</t>
@@ -848,16 +848,16 @@
     <t xml:space="preserve">18.5620136260986</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5056896209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.618335723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654605865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171806335449</t>
+    <t xml:space="preserve">18.5056915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183319091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654567718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171825408936</t>
   </si>
   <si>
     <t xml:space="preserve">20.259708404541</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">20.5574073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9539337158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818714141846</t>
+    <t xml:space="preserve">20.9539318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818695068359</t>
   </si>
   <si>
     <t xml:space="preserve">20.9213714599609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0841808319092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666988372803</t>
+    <t xml:space="preserve">21.0841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027770996094</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">21.5726184844971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.538761138916</t>
+    <t xml:space="preserve">20.5387592315674</t>
   </si>
   <si>
     <t xml:space="preserve">20.5550403594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.4899158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271026611328</t>
+    <t xml:space="preserve">20.489917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922309875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271045684814</t>
   </si>
   <si>
     <t xml:space="preserve">20.351526260376</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5143413543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9864978790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946365356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9376525878906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.124885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8399620056152</t>
+    <t xml:space="preserve">20.5143394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9864940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946346282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9376487731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1248874664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8399639129639</t>
   </si>
   <si>
     <t xml:space="preserve">20.8155403137207</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">21.1574478149414</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2945423126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957431793213</t>
+    <t xml:space="preserve">20.2945404052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
     <t xml:space="preserve">20.3189659118652</t>
@@ -947,58 +947,58 @@
     <t xml:space="preserve">19.8386707305908</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828876495361</t>
+    <t xml:space="preserve">20.0828857421875</t>
   </si>
   <si>
     <t xml:space="preserve">20.1480121612549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9851970672607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3678073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770584106445</t>
+    <t xml:space="preserve">19.9851989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3678112030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108234405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770603179932</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9757614135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8048114776611</t>
+    <t xml:space="preserve">19.1874179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9757633209229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8048095703125</t>
   </si>
   <si>
     <t xml:space="preserve">18.707124710083</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0978736877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338577270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1304359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293254852295</t>
+    <t xml:space="preserve">19.0978717803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338596343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1304340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293235778809</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049961090088</t>
@@ -1007,22 +1007,22 @@
     <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805782318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7829780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748413085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050903320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.677152633667</t>
+    <t xml:space="preserve">20.1805744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6771507263184</t>
   </si>
   <si>
     <t xml:space="preserve">21.1655883789062</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">21.0597610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0434799194336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6852893829346</t>
+    <t xml:space="preserve">21.043478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6852931976318</t>
   </si>
   <si>
     <t xml:space="preserve">21.1004619598389</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5400543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260864257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5319175720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3202629089355</t>
+    <t xml:space="preserve">21.5400524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260883331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5319156646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3202610015869</t>
   </si>
   <si>
     <t xml:space="preserve">21.922664642334</t>
@@ -1070,7 +1070,7 @@
     <t xml:space="preserve">21.7761344909668</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6214599609375</t>
+    <t xml:space="preserve">21.6214618682861</t>
   </si>
   <si>
     <t xml:space="preserve">22.0691986083984</t>
@@ -1079,22 +1079,22 @@
     <t xml:space="preserve">21.711009979248</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5169277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9809436798096</t>
+    <t xml:space="preserve">22.5169296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9809417724609</t>
   </si>
   <si>
     <t xml:space="preserve">22.6308975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0542106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9890842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007389068604</t>
+    <t xml:space="preserve">23.0542125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9890823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
     <t xml:space="preserve">23.1681785583496</t>
@@ -1112,10 +1112,10 @@
     <t xml:space="preserve">24.0310840606689</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9659614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229434967041</t>
+    <t xml:space="preserve">23.9659595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229415893555</t>
   </si>
   <si>
     <t xml:space="preserve">24.3648490905762</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">23.9008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9903812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599630355835</t>
+    <t xml:space="preserve">23.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996341705322</t>
   </si>
   <si>
     <t xml:space="preserve">23.5263652801514</t>
@@ -1136,10 +1136,10 @@
     <t xml:space="preserve">23.6159114837646</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9822387695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2346000671387</t>
+    <t xml:space="preserve">23.982234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.23459815979</t>
   </si>
   <si>
     <t xml:space="preserve">25.4394092559814</t>
@@ -1148,67 +1148,67 @@
     <t xml:space="preserve">24.9916744232178</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0568027496338</t>
+    <t xml:space="preserve">25.0568046569824</t>
   </si>
   <si>
     <t xml:space="preserve">25.0079555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8777046203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288669586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6660499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6497688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999073028564</t>
+    <t xml:space="preserve">24.87770652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6660480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.649772644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999092102051</t>
   </si>
   <si>
     <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1789112091064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613311767578</t>
+    <t xml:space="preserve">25.480110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1789093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613330841064</t>
   </si>
   <si>
     <t xml:space="preserve">24.5602226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7474575042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5765018463135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4556884765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2778911590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9848308563232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1082305908203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.7676296234131</t>
+    <t xml:space="preserve">24.7474555969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5765056610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4556903839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2778930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9848289489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1082324981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.7676239013672</t>
   </si>
   <si>
     <t xml:space="preserve">27.3850154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9209995269775</t>
+    <t xml:space="preserve">26.9210014343262</t>
   </si>
   <si>
     <t xml:space="preserve">27.5071239471436</t>
@@ -1220,49 +1220,49 @@
     <t xml:space="preserve">26.6930656433105</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2765922546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102668762207</t>
+    <t xml:space="preserve">25.2765960693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9102687835693</t>
   </si>
   <si>
     <t xml:space="preserve">24.5032386779785</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6172046661377</t>
+    <t xml:space="preserve">24.617208480835</t>
   </si>
   <si>
     <t xml:space="preserve">24.584644317627</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2440357208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8451442718506</t>
+    <t xml:space="preserve">25.2440338134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8451461791992</t>
   </si>
   <si>
     <t xml:space="preserve">24.7393169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6429233551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5859375</t>
+    <t xml:space="preserve">25.1951923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6429252624512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5859413146973</t>
   </si>
   <si>
     <t xml:space="preserve">25.724328994751</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6917686462402</t>
+    <t xml:space="preserve">25.6917667388916</t>
   </si>
   <si>
     <t xml:space="preserve">25.5452365875244</t>
   </si>
   <si>
-    <t xml:space="preserve">25.756893157959</t>
+    <t xml:space="preserve">25.7568950653076</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208148956299</t>
@@ -1271,16 +1271,16 @@
     <t xml:space="preserve">25.3173007965088</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3987045288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5126762390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7650318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499534606934</t>
+    <t xml:space="preserve">25.3987064361572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.512674331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7650337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.049955368042</t>
   </si>
   <si>
     <t xml:space="preserve">25.2033309936523</t>
@@ -1289,22 +1289,22 @@
     <t xml:space="preserve">25.0486602783203</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4625358581543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661403656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242385864258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148952484131</t>
+    <t xml:space="preserve">24.4625339508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824272155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148933410645</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
@@ -1313,13 +1313,13 @@
     <t xml:space="preserve">26.741907119751</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5790977478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3931579589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6605014801025</t>
+    <t xml:space="preserve">26.5790958404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3931560516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6604995727539</t>
   </si>
   <si>
     <t xml:space="preserve">26.4976863861084</t>
@@ -1331,64 +1331,64 @@
     <t xml:space="preserve">25.602222442627</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2127685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.29416847229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7826080322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3117523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.8815879821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.2303447723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
+    <t xml:space="preserve">26.2127647399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2941722869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7826137542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.3117485046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8815937042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.2303428649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
   </si>
   <si>
     <t xml:space="preserve">26.6197986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1720657348633</t>
+    <t xml:space="preserve">26.1720638275146</t>
   </si>
   <si>
     <t xml:space="preserve">25.0730819702148</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6253452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8519878387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.974100112915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5615177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3579998016357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137886047363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358932495117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3635540008545</t>
+    <t xml:space="preserve">24.6253471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8519916534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9740982055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5615196228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.358003616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137828826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358951568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3635520935059</t>
   </si>
   <si>
     <t xml:space="preserve">24.4218311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2534713745117</t>
+    <t xml:space="preserve">26.2534694671631</t>
   </si>
   <si>
     <t xml:space="preserve">23.6891765594482</t>
@@ -1397,58 +1397,58 @@
     <t xml:space="preserve">23.5670680999756</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1887149810791</t>
+    <t xml:space="preserve">20.1887130737305</t>
   </si>
   <si>
     <t xml:space="preserve">20.6364498138428</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7178535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7002773284912</t>
+    <t xml:space="preserve">20.7178554534912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540241241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8168354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6947269439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1831645965576</t>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.816837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284015655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6947288513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680881500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.183162689209</t>
   </si>
   <si>
     <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0203514099121</t>
+    <t xml:space="preserve">22.0203495025635</t>
   </si>
   <si>
     <t xml:space="preserve">22.3459758758545</t>
@@ -1457,10 +1457,10 @@
     <t xml:space="preserve">23.1600399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123031616211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077728271484</t>
+    <t xml:space="preserve">22.7123012542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077709197998</t>
   </si>
   <si>
     <t xml:space="preserve">25.805736541748</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">24.7067546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3811321258545</t>
+    <t xml:space="preserve">24.3811302185059</t>
   </si>
   <si>
     <t xml:space="preserve">24.2183170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1776142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2997226715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7881603240967</t>
+    <t xml:space="preserve">24.1776161193848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2997245788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7881622314453</t>
   </si>
   <si>
     <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1260375976562</t>
+    <t xml:space="preserve">24.1260395050049</t>
   </si>
   <si>
     <t xml:space="preserve">24.6640110015869</t>
@@ -1502,61 +1502,61 @@
     <t xml:space="preserve">25.4088973999023</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7813396453857</t>
+    <t xml:space="preserve">25.7813415527344</t>
   </si>
   <si>
     <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3261318206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2779350280762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1469650268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951656341553</t>
+    <t xml:space="preserve">25.3261337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2779312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1469688415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9400501251221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951675415039</t>
   </si>
   <si>
     <t xml:space="preserve">25.4916648864746</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5330505371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778369903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3675155639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6985721588135</t>
+    <t xml:space="preserve">25.5330448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778350830078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3675136566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6985759735107</t>
   </si>
   <si>
     <t xml:space="preserve">25.2847518920898</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6571941375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1537837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227233886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9468727111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0710182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9054908752441</t>
+    <t xml:space="preserve">25.6571960449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1537857055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.946870803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0710201263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
     <t xml:space="preserve">26.319314956665</t>
@@ -1565,46 +1565,46 @@
     <t xml:space="preserve">27.0642032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0228214263916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2501850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.629451751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7535972595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0432720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363590240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3811531066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.794979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.877742767334</t>
+    <t xml:space="preserve">27.022819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.250186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6294479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7535934448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0432739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363609313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3811511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7949752807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8777446746826</t>
   </si>
   <si>
     <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2088031768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.332950592041</t>
+    <t xml:space="preserve">24.2088069915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3329524993896</t>
   </si>
   <si>
     <t xml:space="preserve">25.4502811431885</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5262279510498</t>
+    <t xml:space="preserve">26.5262260437012</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
@@ -1613,52 +1613,52 @@
     <t xml:space="preserve">26.0296382904053</t>
   </si>
   <si>
-    <t xml:space="preserve">26.5676078796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5744304656982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6089954376221</t>
+    <t xml:space="preserve">26.56760597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5744285583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6089935302734</t>
   </si>
   <si>
     <t xml:space="preserve">26.9814338684082</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9882545471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4434623718262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6503772735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606967926025</t>
+    <t xml:space="preserve">25.9882564544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4434642791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3606986999512</t>
   </si>
   <si>
     <t xml:space="preserve">24.4984836578369</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0914745330811</t>
+    <t xml:space="preserve">23.0914707183838</t>
   </si>
   <si>
     <t xml:space="preserve">21.72585105896</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4361705780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8913822174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7740497589111</t>
+    <t xml:space="preserve">21.4361724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8913803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7740516662598</t>
   </si>
   <si>
     <t xml:space="preserve">21.6430854797363</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4775543212891</t>
+    <t xml:space="preserve">21.4775562286377</t>
   </si>
   <si>
     <t xml:space="preserve">21.1051120758057</t>
@@ -1667,37 +1667,37 @@
     <t xml:space="preserve">20.8154315948486</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6981048583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636360168457</t>
+    <t xml:space="preserve">19.6981029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636341094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.3602237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2360820770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9395790100098</t>
+    <t xml:space="preserve">20.2360763549805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9395809173584</t>
   </si>
   <si>
     <t xml:space="preserve">21.9327621459961</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0569095611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9259471893311</t>
+    <t xml:space="preserve">22.0569114685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9259452819824</t>
   </si>
   <si>
     <t xml:space="preserve">22.263822555542</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0014190673828</t>
+    <t xml:space="preserve">18.0014171600342</t>
   </si>
   <si>
     <t xml:space="preserve">17.4634456634521</t>
@@ -1706,25 +1706,25 @@
     <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6703586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8772716522217</t>
+    <t xml:space="preserve">17.6703567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.877269744873</t>
   </si>
   <si>
     <t xml:space="preserve">18.2083320617676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4980087280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7049236297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8290691375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6221580505371</t>
+    <t xml:space="preserve">18.498010635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7049198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8290710449219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6221599578857</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
@@ -1733,10 +1733,10 @@
     <t xml:space="preserve">19.3670425415039</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5325736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4911918640137</t>
+    <t xml:space="preserve">19.5325717926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.491189956665</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773639678955</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">16.8427066802979</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7531223297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737651824951</t>
+    <t xml:space="preserve">17.7531261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737670898438</t>
   </si>
   <si>
     <t xml:space="preserve">17.3806781768799</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">16.7599411010742</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8840885162354</t>
+    <t xml:space="preserve">16.884090423584</t>
   </si>
   <si>
     <t xml:space="preserve">16.5530300140381</t>
@@ -1790,49 +1790,49 @@
     <t xml:space="preserve">19.40842628479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5739574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4498081207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222503662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257549285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6499042510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3188400268555</t>
+    <t xml:space="preserve">19.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4498062133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050178527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222522735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.64990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3188419342041</t>
   </si>
   <si>
     <t xml:space="preserve">20.1119289398193</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7808685302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2842769622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0291633605957</t>
+    <t xml:space="preserve">19.7808704376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2842788696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.029167175293</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567211151123</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9464015960693</t>
+    <t xml:space="preserve">19.9463996887207</t>
   </si>
   <si>
     <t xml:space="preserve">19.2428951263428</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3256607055664</t>
+    <t xml:space="preserve">19.325662612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.035982131958</t>
@@ -1841,16 +1841,16 @@
     <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5944118499756</t>
+    <t xml:space="preserve">16.5364761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.594409942627</t>
   </si>
   <si>
     <t xml:space="preserve">16.48681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4537105560303</t>
+    <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0910015106201</t>
@@ -1859,28 +1859,28 @@
     <t xml:space="preserve">17.2151489257812</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310203552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3641242980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910957336426</t>
+    <t xml:space="preserve">17.3310222625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910976409912</t>
   </si>
   <si>
     <t xml:space="preserve">18.6056041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3407535552979</t>
+    <t xml:space="preserve">18.3407554626465</t>
   </si>
   <si>
     <t xml:space="preserve">18.0593528747559</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6455268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2482566833496</t>
+    <t xml:space="preserve">17.645528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.248254776001</t>
   </si>
   <si>
     <t xml:space="preserve">17.6289749145508</t>
@@ -1892,22 +1892,22 @@
     <t xml:space="preserve">18.1255664825439</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620807647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7779502868652</t>
+    <t xml:space="preserve">17.6620826721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
     <t xml:space="preserve">17.9765892028809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2248859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861320495605</t>
+    <t xml:space="preserve">18.2248821258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861339569092</t>
   </si>
   <si>
     <t xml:space="preserve">16.6192398071289</t>
@@ -1916,13 +1916,13 @@
     <t xml:space="preserve">16.5033702850342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274215698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701692581177</t>
+    <t xml:space="preserve">15.5101861953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.270170211792</t>
   </si>
   <si>
     <t xml:space="preserve">14.8397903442383</t>
@@ -1934,61 +1934,61 @@
     <t xml:space="preserve">14.674259185791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6177854537964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0233306884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322919845581</t>
+    <t xml:space="preserve">15.6177835464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0233325958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322891235352</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632543563843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.046703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232374191284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3255758285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3426027297974</t>
+    <t xml:space="preserve">15.0549812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659822463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232383728027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3255777359009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.342604637146</t>
   </si>
   <si>
     <t xml:space="preserve">14.7125539779663</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8402662277222</t>
+    <t xml:space="preserve">14.8402643203735</t>
   </si>
   <si>
     <t xml:space="preserve">14.6614675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6444396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8062086105347</t>
+    <t xml:space="preserve">14.6444387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8062076568604</t>
   </si>
   <si>
     <t xml:space="preserve">14.5422687530518</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661415100098</t>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811706542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661434173584</t>
   </si>
   <si>
     <t xml:space="preserve">14.9083786010742</t>
@@ -1997,31 +1997,31 @@
     <t xml:space="preserve">14.5252389907837</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741535186768</t>
+    <t xml:space="preserve">14.4741544723511</t>
   </si>
   <si>
     <t xml:space="preserve">14.2017002105713</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3890132904053</t>
+    <t xml:space="preserve">14.3890142440796</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315824508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2357568740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0484437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1846723556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317518234253</t>
+    <t xml:space="preserve">14.4315843582153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2357559204102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1846704483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8317527770996</t>
   </si>
   <si>
     <t xml:space="preserve">14.5507841110229</t>
@@ -2033,7 +2033,7 @@
     <t xml:space="preserve">14.7295799255371</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0020380020142</t>
+    <t xml:space="preserve">15.0020351409912</t>
   </si>
   <si>
     <t xml:space="preserve">14.4230699539185</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">14.3379287719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549556732178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462747573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6908464431763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419319152832</t>
+    <t xml:space="preserve">14.3549566268921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462728500366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6908473968506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419338226318</t>
   </si>
   <si>
     <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948534011841</t>
+    <t xml:space="preserve">13.6312484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948524475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821645736694</t>
@@ -2069,13 +2069,13 @@
     <t xml:space="preserve">14.3975257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0995311737061</t>
+    <t xml:space="preserve">14.0995292663574</t>
   </si>
   <si>
     <t xml:space="preserve">13.8866739273071</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8185606002808</t>
+    <t xml:space="preserve">13.8185596466064</t>
   </si>
   <si>
     <t xml:space="preserve">13.2225656509399</t>
@@ -2084,46 +2084,46 @@
     <t xml:space="preserve">13.5801620483398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6227340698242</t>
+    <t xml:space="preserve">13.6227350234985</t>
   </si>
   <si>
     <t xml:space="preserve">13.5205640792847</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1799936294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544532775879</t>
+    <t xml:space="preserve">13.1799945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544523239136</t>
   </si>
   <si>
     <t xml:space="preserve">13.2140522003174</t>
   </si>
   <si>
-    <t xml:space="preserve">12.166805267334</t>
+    <t xml:space="preserve">12.1668033599854</t>
   </si>
   <si>
     <t xml:space="preserve">10.9663009643555</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9748163223267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492721557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5491056442261</t>
+    <t xml:space="preserve">10.9748153686523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.949273109436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5491037368774</t>
   </si>
   <si>
     <t xml:space="preserve">10.7449321746826</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1706409454346</t>
+    <t xml:space="preserve">11.1706418991089</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0344152450562</t>
+    <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
     <t xml:space="preserve">11.162127494812</t>
@@ -2135,10 +2135,10 @@
     <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7619590759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.251106262207</t>
+    <t xml:space="preserve">10.7619609832764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2511072158813</t>
   </si>
   <si>
     <t xml:space="preserve">11.0599575042725</t>
@@ -2147,103 +2147,103 @@
     <t xml:space="preserve">10.8471012115479</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6683034896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7279033660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664684295654</t>
+    <t xml:space="preserve">10.6683015823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7279043197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664693832397</t>
   </si>
   <si>
     <t xml:space="preserve">11.5367527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6644649505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6900091171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410926818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.749608039856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1838331222534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9028625488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8177213668823</t>
+    <t xml:space="preserve">11.6644659042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6900081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410936355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7496070861816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1838321685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9028635025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.817723274231</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751512527466</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0476045608521</t>
+    <t xml:space="preserve">12.0476036071777</t>
   </si>
   <si>
     <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5026950836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1450977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898397445679</t>
+    <t xml:space="preserve">11.5026960372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1450996398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981866836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
     <t xml:space="preserve">11.2132120132446</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7108745574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4724760055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6597900390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0173864364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0854988098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0514430999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1280698776245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088720321655</t>
+    <t xml:space="preserve">10.7108755111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4724769592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6597890853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0173854827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0854997634888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0514421463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1280717849731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0003576278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088729858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.2642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6985216140747</t>
+    <t xml:space="preserve">11.698522567749</t>
   </si>
   <si>
     <t xml:space="preserve">11.6814947128296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8092088699341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3247356414795</t>
+    <t xml:space="preserve">11.8092079162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3247365951538</t>
   </si>
   <si>
     <t xml:space="preserve">13.1970233917236</t>
@@ -2252,28 +2252,28 @@
     <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5120496749878</t>
+    <t xml:space="preserve">13.5120487213135</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738185882568</t>
   </si>
   <si>
-    <t xml:space="preserve">13.546106338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4145555496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8526172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2187299728394</t>
+    <t xml:space="preserve">13.5461053848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4145545959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8526191711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.218729019165</t>
   </si>
   <si>
     <t xml:space="preserve">13.8781585693359</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7759895324707</t>
+    <t xml:space="preserve">13.775990486145</t>
   </si>
   <si>
     <t xml:space="preserve">13.4439344406128</t>
@@ -2282,7 +2282,7 @@
     <t xml:space="preserve">13.8441038131714</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4486112594604</t>
+    <t xml:space="preserve">14.4486131668091</t>
   </si>
   <si>
     <t xml:space="preserve">14.6274099349976</t>
@@ -2291,55 +2291,55 @@
     <t xml:space="preserve">14.9254083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933532714844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942437171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.967978477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.68701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.019063949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6406021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4618015289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656410217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3634719848633</t>
+    <t xml:space="preserve">15.5043716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933523178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592966079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9679775238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870107650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0190629959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1467771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3634700775146</t>
   </si>
   <si>
     <t xml:space="preserve">14.3294124603271</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4826679229736</t>
+    <t xml:space="preserve">14.4826688766479</t>
   </si>
   <si>
     <t xml:space="preserve">14.1506156921387</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1335859298706</t>
+    <t xml:space="preserve">14.1335868835449</t>
   </si>
   <si>
     <t xml:space="preserve">14.5763254165649</t>
@@ -2348,55 +2348,55 @@
     <t xml:space="preserve">14.1165580749512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4911832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3804998397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4996976852417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721538543701</t>
+    <t xml:space="preserve">14.4911842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3804979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4996995925903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721529006958</t>
   </si>
   <si>
     <t xml:space="preserve">13.7078762054443</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9292459487915</t>
+    <t xml:space="preserve">13.9292449951172</t>
   </si>
   <si>
     <t xml:space="preserve">13.5035352706909</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3162240982056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5631341934204</t>
+    <t xml:space="preserve">13.3162231445312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631351470947</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">14.406042098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.269814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2953577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5167245864868</t>
+    <t xml:space="preserve">14.4060401916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2698154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.295355796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5167236328125</t>
   </si>
   <si>
     <t xml:space="preserve">14.1761569976807</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1931858062744</t>
+    <t xml:space="preserve">14.1931848526001</t>
   </si>
   <si>
     <t xml:space="preserve">13.758960723877</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">12.5584583282471</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3370876312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6010293960571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9880046844482</t>
+    <t xml:space="preserve">12.3370885848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6010284423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9880056381226</t>
   </si>
   <si>
     <t xml:space="preserve">11.6218938827515</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">11.4430961608887</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3277349472046</t>
+    <t xml:space="preserve">10.3277359008789</t>
   </si>
   <si>
     <t xml:space="preserve">9.82539653778076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42522811889648</t>
+    <t xml:space="preserve">9.4252290725708</t>
   </si>
   <si>
     <t xml:space="preserve">9.74025440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08424091339111</t>
+    <t xml:space="preserve">8.0842399597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.73557758331299</t>
@@ -2444,106 +2444,106 @@
     <t xml:space="preserve">8.27155303955078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412506103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11020278930664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00803089141846</t>
+    <t xml:space="preserve">8.31412601470947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078681945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278886795044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11020374298096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00803279876709</t>
   </si>
   <si>
     <t xml:space="preserve">9.41671466827393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47631454467773</t>
+    <t xml:space="preserve">9.47631359100342</t>
   </si>
   <si>
     <t xml:space="preserve">9.57848453521729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44225692749023</t>
+    <t xml:space="preserve">9.44225788116455</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317398071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16980361938477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53591442108154</t>
+    <t xml:space="preserve">9.09317588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16980266571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53591346740723</t>
   </si>
   <si>
     <t xml:space="preserve">9.48482799530029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62105655670166</t>
+    <t xml:space="preserve">9.62105560302734</t>
   </si>
   <si>
     <t xml:space="preserve">10.089337348938</t>
   </si>
   <si>
-    <t xml:space="preserve">10.131908416748</t>
+    <t xml:space="preserve">10.1319074630737</t>
   </si>
   <si>
     <t xml:space="preserve">10.0467662811279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75728416442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8764820098877</t>
+    <t xml:space="preserve">9.75728321075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87648296356201</t>
   </si>
   <si>
     <t xml:space="preserve">9.97013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0552806854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2936782836914</t>
+    <t xml:space="preserve">10.0552816390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2936792373657</t>
   </si>
   <si>
     <t xml:space="preserve">10.3192205429077</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4299068450928</t>
+    <t xml:space="preserve">10.4299058914185</t>
   </si>
   <si>
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961841583252</t>
+    <t xml:space="preserve">11.1961832046509</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9616231918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85945320129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7828254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30603122711182</t>
+    <t xml:space="preserve">9.96162414550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85945415496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78282642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3060302734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.51037120819092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51888656616211</t>
+    <t xml:space="preserve">9.51888561248779</t>
   </si>
   <si>
     <t xml:space="preserve">9.22940349578857</t>
@@ -2552,28 +2552,28 @@
     <t xml:space="preserve">9.26345920562744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25494384765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36563014984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86329078674316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93140411376953</t>
+    <t xml:space="preserve">9.25494480133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36562824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86329174041748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93140506744385</t>
   </si>
   <si>
     <t xml:space="preserve">8.85477638244629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28048801422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70619678497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62957000732422</t>
+    <t xml:space="preserve">9.28048706054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70619773864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62957096099854</t>
   </si>
   <si>
     <t xml:space="preserve">9.85093879699707</t>
@@ -2582,28 +2582,28 @@
     <t xml:space="preserve">11.1876697540283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8300743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5405912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340774536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61254215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96388339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435741424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.182391166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1998720169067</t>
+    <t xml:space="preserve">10.8300733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5405902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61254119873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9638843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435722351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1823921203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1998701095581</t>
   </si>
   <si>
     <t xml:space="preserve">10.1649103164673</t>
@@ -2612,22 +2612,22 @@
     <t xml:space="preserve">10.0600280761719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.444598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0163269042969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90270328521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72789859771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64049625396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28214454650879</t>
+    <t xml:space="preserve">10.4445972442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0163259506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90270233154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72789764404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64049530029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28214550018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.56183338165283</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">9.52687168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49191188812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40450954437256</t>
+    <t xml:space="preserve">9.49190998077393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40450859069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.15978145599365</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">9.20348262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36080837249756</t>
+    <t xml:space="preserve">9.36080741882324</t>
   </si>
   <si>
     <t xml:space="preserve">9.18600177764893</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">9.33458709716797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22096252441406</t>
+    <t xml:space="preserve">9.22096347808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.44821071624756</t>
@@ -2684,13 +2684,13 @@
     <t xml:space="preserve">9.01119804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3484554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358568191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271173477173</t>
+    <t xml:space="preserve">10.3484563827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358577728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271192550659</t>
   </si>
   <si>
     <t xml:space="preserve">10.9777536392212</t>
@@ -2702,13 +2702,13 @@
     <t xml:space="preserve">11.3186225891113</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4672069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0826377868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8903503417969</t>
+    <t xml:space="preserve">11.4672079086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0826368331909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8903522491455</t>
   </si>
   <si>
     <t xml:space="preserve">10.7942094802856</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5494804382324</t>
+    <t xml:space="preserve">10.5494813919067</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872753143311</t>
@@ -2726,22 +2726,22 @@
     <t xml:space="preserve">10.226092338562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1299486160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98136520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93766498565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.094988822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1124696731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0250673294067</t>
+    <t xml:space="preserve">10.1299495697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98136615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93766307830811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0949897766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1124677658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0250663757324</t>
   </si>
   <si>
     <t xml:space="preserve">9.95514583587646</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">9.78033924102783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75411796569824</t>
+    <t xml:space="preserve">9.75411891937256</t>
   </si>
   <si>
     <t xml:space="preserve">9.6579761505127</t>
@@ -2759,25 +2759,25 @@
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884510040283</t>
+    <t xml:space="preserve">9.99884414672852</t>
   </si>
   <si>
     <t xml:space="preserve">10.3222360610962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7330274581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7505073547363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620780944824</t>
+    <t xml:space="preserve">10.7330265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.750506401062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620800018311</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3834161758423</t>
+    <t xml:space="preserve">10.3834171295166</t>
   </si>
   <si>
     <t xml:space="preserve">10.3659362792969</t>
@@ -2786,64 +2786,64 @@
     <t xml:space="preserve">10.4970407485962</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6893253326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106643676758</t>
+    <t xml:space="preserve">10.6893262863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106624603271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4795589447021</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5757036209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5669622421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5232601165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5582208633423</t>
+    <t xml:space="preserve">10.5757026672363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5669631958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5232610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5582218170166</t>
   </si>
   <si>
     <t xml:space="preserve">10.4708185195923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81529998779297</t>
+    <t xml:space="preserve">9.81530094146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99010562896729</t>
+    <t xml:space="preserve">9.9901065826416</t>
   </si>
   <si>
     <t xml:space="preserve">9.82404041290283</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86774253845215</t>
+    <t xml:space="preserve">9.86774158477783</t>
   </si>
   <si>
     <t xml:space="preserve">9.6142749786377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00245761871338</t>
+    <t xml:space="preserve">9.00245666503906</t>
   </si>
   <si>
     <t xml:space="preserve">8.82765293121338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36878871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5348539352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6441068649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1248197555542</t>
+    <t xml:space="preserve">8.36878967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53485488891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64410781860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12482070922852</t>
   </si>
   <si>
     <t xml:space="preserve">9.16852188110352</t>
@@ -2852,25 +2852,25 @@
     <t xml:space="preserve">8.88883304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98497676849365</t>
+    <t xml:space="preserve">8.98497581481934</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350774765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070508956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3324928283691</t>
+    <t xml:space="preserve">9.69293594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078321456909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070518493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3324918746948</t>
   </si>
   <si>
     <t xml:space="preserve">12.3587141036987</t>
@@ -2888,16 +2888,16 @@
     <t xml:space="preserve">12.1926488876343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857137680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0702857971191</t>
+    <t xml:space="preserve">12.1139860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2101287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0702848434448</t>
   </si>
   <si>
     <t xml:space="preserve">11.974142074585</t>
@@ -2906,40 +2906,40 @@
     <t xml:space="preserve">11.991623878479</t>
   </si>
   <si>
-    <t xml:space="preserve">11.947922706604</t>
+    <t xml:space="preserve">11.9479217529297</t>
   </si>
   <si>
     <t xml:space="preserve">12.061544418335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1314659118652</t>
+    <t xml:space="preserve">12.1314678192139</t>
   </si>
   <si>
     <t xml:space="preserve">12.0440635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8954801559448</t>
+    <t xml:space="preserve">11.8954792022705</t>
   </si>
   <si>
     <t xml:space="preserve">12.0091028213501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0178442001343</t>
+    <t xml:space="preserve">12.0178451538086</t>
   </si>
   <si>
     <t xml:space="preserve">12.6558818817139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6733617782593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4898176193237</t>
+    <t xml:space="preserve">12.673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4898166656494</t>
   </si>
   <si>
     <t xml:space="preserve">12.4198951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684795379639</t>
+    <t xml:space="preserve">12.5684785842896</t>
   </si>
   <si>
     <t xml:space="preserve">12.5422592163086</t>
@@ -2957,16 +2957,16 @@
     <t xml:space="preserve">12.5160369873047</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5509986877441</t>
+    <t xml:space="preserve">12.5509996414185</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8132066726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8394260406494</t>
+    <t xml:space="preserve">12.8132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8394269943237</t>
   </si>
   <si>
     <t xml:space="preserve">12.909348487854</t>
@@ -2975,13 +2975,13 @@
     <t xml:space="preserve">12.821946144104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9880094528198</t>
+    <t xml:space="preserve">12.9880104064941</t>
   </si>
   <si>
     <t xml:space="preserve">13.0229721069336</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3114004135132</t>
+    <t xml:space="preserve">13.3113994598389</t>
   </si>
   <si>
     <t xml:space="preserve">13.215256690979</t>
@@ -2996,22 +2996,22 @@
     <t xml:space="preserve">12.6296606063843</t>
   </si>
   <si>
-    <t xml:space="preserve">12.953049659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9792718887329</t>
+    <t xml:space="preserve">12.9530506134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9792709350586</t>
   </si>
   <si>
     <t xml:space="preserve">12.9355697631836</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3026599884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4075441360474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1890382766724</t>
+    <t xml:space="preserve">13.3026609420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.407543182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1890363693237</t>
   </si>
   <si>
     <t xml:space="preserve">13.2239980697632</t>
@@ -3029,28 +3029,28 @@
     <t xml:space="preserve">14.395191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5000743865967</t>
+    <t xml:space="preserve">14.5000734329224</t>
   </si>
   <si>
     <t xml:space="preserve">14.4039306640625</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5612573623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2116470336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7484140396118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980224609375</t>
+    <t xml:space="preserve">14.5612564086914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2116460800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7484130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980215072632</t>
   </si>
   <si>
     <t xml:space="preserve">13.7221918106079</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3864517211914</t>
+    <t xml:space="preserve">14.3864498138428</t>
   </si>
   <si>
     <t xml:space="preserve">14.6661386489868</t>
@@ -3065,64 +3065,64 @@
     <t xml:space="preserve">15.0157489776611</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1818161010742</t>
+    <t xml:space="preserve">15.1818141937256</t>
   </si>
   <si>
     <t xml:space="preserve">15.3653593063354</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1206312179565</t>
+    <t xml:space="preserve">15.1206302642822</t>
   </si>
   <si>
     <t xml:space="preserve">14.456374168396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6136980056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3442687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7550601959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373327255249</t>
+    <t xml:space="preserve">14.6136960983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7622814178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3442668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7550582885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373346328735</t>
   </si>
   <si>
     <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9247331619263</t>
+    <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
     <t xml:space="preserve">15.9422149658203</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1344985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4352798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.566385269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3566198348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440221786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303985595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2429962158203</t>
+    <t xml:space="preserve">16.13450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4352807998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5663862228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3566179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440231323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.242995262146</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255163192749</t>
@@ -3131,82 +3131,82 @@
     <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2779550552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2517375946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0681915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1381120681763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4265403747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0244922637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8933877944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234615325928</t>
+    <t xml:space="preserve">15.2779579162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2517356872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.068190574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.138111114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4265394210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.024489402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8933868408203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234643936157</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196071624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9982671737671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9370889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1468534469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.849684715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1031532287598</t>
+    <t xml:space="preserve">14.919605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9982709884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9370880126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1468524932861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8496837615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1031541824341</t>
   </si>
   <si>
     <t xml:space="preserve">15.2604751586914</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3041772842407</t>
+    <t xml:space="preserve">15.304178237915</t>
   </si>
   <si>
     <t xml:space="preserve">14.8409433364868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4214124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5962181091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7812824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4367980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4630184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.074836730957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2846012115479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8397483825684</t>
+    <t xml:space="preserve">14.4214134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5962190628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7812805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4367961883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.463020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0748386383057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2846031188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.839750289917</t>
   </si>
   <si>
     <t xml:space="preserve">18.5048999786377</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">18.7340068817139</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4696521759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8573722839355</t>
+    <t xml:space="preserve">18.4696502685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8573741912842</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
@@ -3230,7 +3230,7 @@
     <t xml:space="preserve">18.9631156921387</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1217288970947</t>
+    <t xml:space="preserve">19.1217308044434</t>
   </si>
   <si>
     <t xml:space="preserve">19.0688571929932</t>
@@ -3242,13 +3242,13 @@
     <t xml:space="preserve">18.8749961853027</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5753936767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2052955627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987609863281</t>
+    <t xml:space="preserve">18.5753955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2052936553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987590789795</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">18.2405452728271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7163829803467</t>
+    <t xml:space="preserve">18.7163848876953</t>
   </si>
   <si>
     <t xml:space="preserve">18.2934150695801</t>
@@ -3272,13 +3272,13 @@
     <t xml:space="preserve">18.0290584564209</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8175735473633</t>
+    <t xml:space="preserve">17.8175754547119</t>
   </si>
   <si>
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8880672454834</t>
+    <t xml:space="preserve">17.888069152832</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
@@ -3287,34 +3287,34 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589603424072</t>
+    <t xml:space="preserve">17.5708427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589622497559</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3681697845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1478710174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4650974273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9761867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8351993560791</t>
+    <t xml:space="preserve">17.3681678771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1478729248047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4650993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9761848449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8351974487305</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2007446289062</t>
+    <t xml:space="preserve">17.2007465362549</t>
   </si>
   <si>
     <t xml:space="preserve">16.3724308013916</t>
@@ -3323,7 +3323,7 @@
     <t xml:space="preserve">16.1256980895996</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5222339630127</t>
+    <t xml:space="preserve">16.5222320556641</t>
   </si>
   <si>
     <t xml:space="preserve">16.6367855072021</t>
@@ -3332,10 +3332,10 @@
     <t xml:space="preserve">17.3857936859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2448043823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3769798278809</t>
+    <t xml:space="preserve">17.2448024749756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3769817352295</t>
   </si>
   <si>
     <t xml:space="preserve">17.4122276306152</t>
@@ -3359,7 +3359,7 @@
     <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1743106842041</t>
+    <t xml:space="preserve">17.1743087768555</t>
   </si>
   <si>
     <t xml:space="preserve">17.3417358398438</t>
@@ -3371,28 +3371,28 @@
     <t xml:space="preserve">16.9540100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3593597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9716358184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249011993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6896572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6720314025879</t>
+    <t xml:space="preserve">17.3593559265137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9716377258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249031066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6896553039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
     <t xml:space="preserve">16.4869842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8042106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2183685302734</t>
+    <t xml:space="preserve">16.8042125701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2183704376221</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
@@ -3407,7 +3407,7 @@
     <t xml:space="preserve">17.5972785949707</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2888622283936</t>
+    <t xml:space="preserve">17.2888641357422</t>
   </si>
   <si>
     <t xml:space="preserve">17.0421314239502</t>
@@ -3416,7 +3416,7 @@
     <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927257537842</t>
+    <t xml:space="preserve">16.5927276611328</t>
   </si>
   <si>
     <t xml:space="preserve">16.4957942962646</t>
@@ -3431,16 +3431,16 @@
     <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9935188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8613433837891</t>
+    <t xml:space="preserve">15.99351978302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8613424301147</t>
   </si>
   <si>
     <t xml:space="preserve">16.2402534484863</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5134201049805</t>
+    <t xml:space="preserve">16.5134181976318</t>
   </si>
   <si>
     <t xml:space="preserve">16.3195610046387</t>
@@ -3455,31 +3455,31 @@
     <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3590660095215</t>
+    <t xml:space="preserve">15.3590669631958</t>
   </si>
   <si>
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150043487549</t>
+    <t xml:space="preserve">15.3150062561035</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2180776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1828279495239</t>
+    <t xml:space="preserve">15.2180767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1828289031982</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123352050781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035223007202</t>
+    <t xml:space="preserve">15.1123332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035213470459</t>
   </si>
   <si>
     <t xml:space="preserve">15.4912443161011</t>
@@ -3491,13 +3491,13 @@
     <t xml:space="preserve">15.0858993530273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9801559448242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8215436935425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6188697814941</t>
+    <t xml:space="preserve">14.9801568984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8215417861938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6188688278198</t>
   </si>
   <si>
     <t xml:space="preserve">14.3985738754272</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3457040786743</t>
+    <t xml:space="preserve">14.3104543685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.345703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">14.1870899200439</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1254062652588</t>
+    <t xml:space="preserve">14.1254072189331</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1384782791138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0327367782593</t>
+    <t xml:space="preserve">13.1384792327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.032735824585</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
@@ -3578,16 +3578,16 @@
     <t xml:space="preserve">13.3852109909058</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6583766937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5350112915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5614471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.191349029541</t>
+    <t xml:space="preserve">13.6583776473999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5350122451782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.561448097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1913499832153</t>
   </si>
   <si>
     <t xml:space="preserve">13.2265977859497</t>
@@ -3596,19 +3596,19 @@
     <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.314715385437</t>
+    <t xml:space="preserve">13.3147163391113</t>
   </si>
   <si>
     <t xml:space="preserve">13.2618436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557065963745</t>
+    <t xml:space="preserve">13.4557056427002</t>
   </si>
   <si>
     <t xml:space="preserve">13.4380807876587</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4645166397095</t>
+    <t xml:space="preserve">13.4645156860352</t>
   </si>
   <si>
     <t xml:space="preserve">13.4997644424438</t>
@@ -3617,22 +3617,22 @@
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5702600479126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7112503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468936920166</t>
+    <t xml:space="preserve">13.5878839492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5702590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7112493515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468946456909</t>
   </si>
   <si>
     <t xml:space="preserve">13.1649141311646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8388738632202</t>
+    <t xml:space="preserve">12.8388748168945</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710540771484</t>
@@ -3644,34 +3644,34 @@
     <t xml:space="preserve">12.6978855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6890745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5128364562988</t>
+    <t xml:space="preserve">12.6890735626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5128374099731</t>
   </si>
   <si>
     <t xml:space="preserve">12.5568962097168</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6273908615112</t>
+    <t xml:space="preserve">12.6273918151855</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492738723755</t>
+    <t xml:space="preserve">11.6492748260498</t>
   </si>
   <si>
     <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8078870773315</t>
+    <t xml:space="preserve">11.8078880310059</t>
   </si>
   <si>
     <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431358337402</t>
+    <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3680,25 +3680,25 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347194671631</t>
+    <t xml:space="preserve">11.5347213745117</t>
   </si>
   <si>
     <t xml:space="preserve">11.4642248153687</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1117506027222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9090795516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2263050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1293754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0412559509277</t>
+    <t xml:space="preserve">11.1117515563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9090785980225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2263059616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0412549972534</t>
   </si>
   <si>
     <t xml:space="preserve">10.8209600448608</t>
@@ -3716,13 +3716,13 @@
     <t xml:space="preserve">11.1822452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355134963989</t>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.961950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355144500732</t>
   </si>
   <si>
     <t xml:space="preserve">10.6975936889648</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">10.4772977828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7592763900757</t>
+    <t xml:space="preserve">10.75927734375</t>
   </si>
   <si>
     <t xml:space="preserve">10.2393779754639</t>
@@ -3746,16 +3746,16 @@
     <t xml:space="preserve">9.54324054718018</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56967639923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0455169677734</t>
+    <t xml:space="preserve">9.56967544555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0455160140991</t>
   </si>
   <si>
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
+    <t xml:space="preserve">9.42868709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.61373519897461</t>
@@ -3776,7 +3776,7 @@
     <t xml:space="preserve">9.25244998931885</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04977703094482</t>
+    <t xml:space="preserve">9.04977798461914</t>
   </si>
   <si>
     <t xml:space="preserve">8.83829212188721</t>
@@ -3788,16 +3788,16 @@
     <t xml:space="preserve">9.24363708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74576759338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68848991394043</t>
+    <t xml:space="preserve">8.74576854705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68849086761475</t>
   </si>
   <si>
     <t xml:space="preserve">8.62680816650391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61359024047852</t>
+    <t xml:space="preserve">8.6135892868042</t>
   </si>
   <si>
     <t xml:space="preserve">8.2787389755249</t>
@@ -3809,19 +3809,19 @@
     <t xml:space="preserve">8.43735313415527</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35363960266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27433395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26552200317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25671005249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36245059967041</t>
+    <t xml:space="preserve">8.35364055633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27433300018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26552295684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25670909881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36245155334473</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">8.42413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13334274291992</t>
+    <t xml:space="preserve">8.13334369659424</t>
   </si>
   <si>
     <t xml:space="preserve">8.08487892150879</t>
@@ -3848,40 +3848,40 @@
     <t xml:space="preserve">7.8866114616394</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12453174591064</t>
+    <t xml:space="preserve">8.12453269958496</t>
   </si>
   <si>
     <t xml:space="preserve">8.02760124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89542293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93067169189453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80730485916138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819747924805</t>
+    <t xml:space="preserve">7.89542388916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93067121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80730438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819700241089</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190958023071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527593612671</t>
+    <t xml:space="preserve">7.66190910339355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527641296387</t>
   </si>
   <si>
     <t xml:space="preserve">7.67512798309326</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512702941895</t>
+    <t xml:space="preserve">7.95803880691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512655258179</t>
   </si>
   <si>
     <t xml:space="preserve">7.62037038803101</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124256134033</t>
+    <t xml:space="preserve">8.08124160766602</t>
   </si>
   <si>
     <t xml:space="preserve">7.92609739303589</t>
@@ -3908,16 +3908,16 @@
     <t xml:space="preserve">7.64774894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67969036102295</t>
+    <t xml:space="preserve">7.82570886611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67968988418579</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736042022705</t>
+    <t xml:space="preserve">7.54736089706421</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
@@ -3932,7 +3932,7 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3950,13 +3950,13 @@
     <t xml:space="preserve">6.90396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444980621338</t>
+    <t xml:space="preserve">6.79444932937622</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406175613403</t>
+    <t xml:space="preserve">6.69406127929688</t>
   </si>
   <si>
     <t xml:space="preserve">6.46590709686279</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212102890015</t>
+    <t xml:space="preserve">6.19212055206299</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891611099243</t>
+    <t xml:space="preserve">6.53891658782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.55260562896729</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134376525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474130630493</t>
+    <t xml:space="preserve">6.46134328842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474082946777</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173181533813</t>
+    <t xml:space="preserve">6.56173133850098</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
@@ -4019,7 +4019,7 @@
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813884735107</t>
+    <t xml:space="preserve">6.80813837051392</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12687301635742</t>
+    <t xml:space="preserve">8.12687397003174</t>
   </si>
   <si>
     <t xml:space="preserve">8.35046482086182</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">7.81658220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03104877471924</t>
+    <t xml:space="preserve">8.03104972839355</t>
   </si>
   <si>
     <t xml:space="preserve">7.89415502548218</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910804748535</t>
+    <t xml:space="preserve">7.52910852432251</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4115,19 +4115,19 @@
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415851593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775079727173</t>
+    <t xml:space="preserve">6.48415899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775032043457</t>
   </si>
   <si>
     <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27425670623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05066537857056</t>
+    <t xml:space="preserve">6.27425718307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0506649017334</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610204696655</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445001602173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.27881956100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445049285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901218414307</t>
+    <t xml:space="preserve">6.79901266098022</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4217,22 +4217,22 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978691101074</t>
+    <t xml:space="preserve">7.93978595733643</t>
   </si>
   <si>
     <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12230968475342</t>
+    <t xml:space="preserve">8.12231063842773</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794321060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7663893699646</t>
+    <t xml:space="preserve">7.69794273376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76638889312744</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4241,13 +4241,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7709527015686</t>
+    <t xml:space="preserve">7.77095317840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9169716835022</t>
+    <t xml:space="preserve">7.91697216033936</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4259,22 +4259,22 @@
     <t xml:space="preserve">7.57017517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62949514389038</t>
+    <t xml:space="preserve">7.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5519232749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31464242935181</t>
+    <t xml:space="preserve">7.55192279815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31464290618896</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1777491569519</t>
+    <t xml:space="preserve">7.17774963378906</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4289,22 +4289,22 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4560980796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46978807449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59755420684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79376792907715</t>
+    <t xml:space="preserve">7.45609855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46978855133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59755373001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79376745223999</t>
   </si>
   <si>
     <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38696956634521</t>
+    <t xml:space="preserve">8.38697052001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">8.36871719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8159008026123</t>
+    <t xml:space="preserve">8.81589984893799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94366836547852</t>
@@ -4331,7 +4331,7 @@
     <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9801721572876</t>
+    <t xml:space="preserve">8.98017311096191</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
@@ -4340,10 +4340,10 @@
     <t xml:space="preserve">8.8432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89347457885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77939605712891</t>
+    <t xml:space="preserve">8.89347362518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77939510345459</t>
   </si>
   <si>
     <t xml:space="preserve">8.7292013168335</t>
@@ -4358,16 +4358,16 @@
     <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41891193389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40978527069092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44172668457031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22726249694824</t>
+    <t xml:space="preserve">8.41891288757324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40978622436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44172763824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22726154327393</t>
   </si>
   <si>
     <t xml:space="preserve">8.21813488006592</t>
@@ -4376,10 +4376,10 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551296234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949398040771</t>
+    <t xml:space="preserve">8.24551391601562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949493408203</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68881607055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085519790649</t>
+    <t xml:space="preserve">7.83483505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6888165473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085472106934</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4412,16 +4412,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580589294434</t>
+    <t xml:space="preserve">8.09493255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580493927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716499328613</t>
+    <t xml:space="preserve">7.96716451644897</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4439,13 +4439,13 @@
     <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24163246154785</t>
+    <t xml:space="preserve">7.24163293838501</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804113388062</t>
+    <t xml:space="preserve">7.01804161071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4454,19 +4454,19 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745929718018</t>
+    <t xml:space="preserve">6.86745882034302</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88114833831787</t>
+    <t xml:space="preserve">6.88114786148071</t>
   </si>
   <si>
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78076028823853</t>
+    <t xml:space="preserve">6.78075981140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4481,13 +4481,13 @@
     <t xml:space="preserve">6.90852737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76707124710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62105226516724</t>
+    <t xml:space="preserve">6.76707077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561559677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62105178833008</t>
   </si>
   <si>
     <t xml:space="preserve">6.43852758407593</t>
@@ -5799,6 +5799,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.13000011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11999988555908</t>
   </si>
 </sst>
 </file>
@@ -72749,7 +72752,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6909837963</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>112088</v>
@@ -72770,6 +72773,32 @@
         <v>1928</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6910069444</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>83780</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>4.15000009536743</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>4.05000019073486</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>4.11499977111816</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -38,67 +38,67 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608804702759</t>
+    <t xml:space="preserve">12.7608814239502</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.784628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767124176025</t>
+    <t xml:space="preserve">12.7846298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767133712769</t>
   </si>
   <si>
     <t xml:space="preserve">12.4758987426758</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9930095672607</t>
+    <t xml:space="preserve">11.9930114746094</t>
   </si>
   <si>
     <t xml:space="preserve">11.8742685317993</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2700786590576</t>
+    <t xml:space="preserve">12.2700777053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.5233955383301</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9746170043945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5075616836548</t>
+    <t xml:space="preserve">12.9746179580688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5075626373291</t>
   </si>
   <si>
     <t xml:space="preserve">12.4125699996948</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6738033294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3729887008667</t>
+    <t xml:space="preserve">12.6738014221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0563402175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3729877471924</t>
   </si>
   <si>
     <t xml:space="preserve">12.1750841140747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909160614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367826461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9850950241089</t>
+    <t xml:space="preserve">12.3413228988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909151077271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713594436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367835998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9850959777832</t>
   </si>
   <si>
     <t xml:space="preserve">11.1380643844604</t>
@@ -107,19 +107,19 @@
     <t xml:space="preserve">10.9955730438232</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4626274108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1063985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942922592163</t>
+    <t xml:space="preserve">11.4626293182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1063976287842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4942932128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417900085449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3597202301025</t>
+    <t xml:space="preserve">11.3597164154053</t>
   </si>
   <si>
     <t xml:space="preserve">11.8584356307983</t>
@@ -128,28 +128,28 @@
     <t xml:space="preserve">11.5180406570435</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7159442901611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346872329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763648986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6684465408325</t>
+    <t xml:space="preserve">11.7159461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6763639450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6684484481812</t>
   </si>
   <si>
     <t xml:space="preserve">11.3992986679077</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1855611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692621231079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3888206481934</t>
+    <t xml:space="preserve">11.1855621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3888216018677</t>
   </si>
   <si>
     <t xml:space="preserve">12.4284019470215</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">12.2304973602295</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1117544174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1513357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242092132568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.982533454895</t>
+    <t xml:space="preserve">12.1117553710938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1513338088989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196708679199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242101669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9825325012207</t>
   </si>
   <si>
     <t xml:space="preserve">12.9508695602417</t>
@@ -179,40 +179,40 @@
     <t xml:space="preserve">13.1408567428589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2754335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704271316528</t>
+    <t xml:space="preserve">13.2754306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704261779785</t>
   </si>
   <si>
     <t xml:space="preserve">13.3387613296509</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4575061798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.576247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999965667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625116348267</t>
+    <t xml:space="preserve">13.4575042724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999946594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379467010498</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7529649734497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1171083450317</t>
+    <t xml:space="preserve">12.752965927124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1171073913574</t>
   </si>
   <si>
     <t xml:space="preserve">13.1091928482056</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1962699890137</t>
+    <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9904508590698</t>
@@ -221,49 +221,49 @@
     <t xml:space="preserve">13.0221147537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775289535522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300302505493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6975517272949</t>
+    <t xml:space="preserve">13.0933618545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775279998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0300312042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6975526809692</t>
   </si>
   <si>
     <t xml:space="preserve">12.602557182312</t>
   </si>
   <si>
-    <t xml:space="preserve">12.650053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.863790512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5867252349854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4679832458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650732040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493892669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.988468170166</t>
+    <t xml:space="preserve">12.6500549316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8637914657593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5867261886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788078308105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884691238403</t>
   </si>
   <si>
     <t xml:space="preserve">11.9241018295288</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">12.2298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620325088501</t>
+    <t xml:space="preserve">12.2942142486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620306015015</t>
   </si>
   <si>
     <t xml:space="preserve">12.286169052124</t>
@@ -287,88 +287,88 @@
     <t xml:space="preserve">12.4953641891479</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7126054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.809157371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735227584839</t>
+    <t xml:space="preserve">12.7126045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
     <t xml:space="preserve">13.0263977050781</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8252487182617</t>
+    <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
     <t xml:space="preserve">12.8654775619507</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8172035217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999612808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3666296005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103065490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7390460968018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4011154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884712219238</t>
+    <t xml:space="preserve">12.8172016143799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999622344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3666305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103084564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7390451431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884702682495</t>
   </si>
   <si>
     <t xml:space="preserve">10.8781280517578</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0792779922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022634506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689306259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6103096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3689317703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4896202087402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.757438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735330581665</t>
+    <t xml:space="preserve">11.0792760848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022624969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689287185669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6103086471558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3689308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4896211624146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7574396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735340118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.45973777771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0229558944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424932479858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.634446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.982723236084</t>
+    <t xml:space="preserve">11.0229549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6344470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827251434326</t>
   </si>
   <si>
     <t xml:space="preserve">10.92640209198</t>
@@ -377,22 +377,22 @@
     <t xml:space="preserve">11.2160577774048</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7229528427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7470932006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5700788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8919172286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861701965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.875825881958</t>
+    <t xml:space="preserve">11.7229537963867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7470922470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5700798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.891918182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8758249282837</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953672409058</t>
@@ -401,121 +401,121 @@
     <t xml:space="preserve">12.1896171569824</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4309949874878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896160125732</t>
+    <t xml:space="preserve">12.4309978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896179199219</t>
   </si>
   <si>
     <t xml:space="preserve">13.0505352020264</t>
   </si>
   <si>
-    <t xml:space="preserve">12.994213104248</t>
+    <t xml:space="preserve">12.9942140579224</t>
   </si>
   <si>
     <t xml:space="preserve">13.1229476928711</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1551332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746736526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482351303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.24937915802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194974899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459348678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608781814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919107437134</t>
+    <t xml:space="preserve">13.1551322937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861669540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0746717453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493810653687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194965362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459339141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919097900391</t>
   </si>
   <si>
     <t xml:space="preserve">14.7643232345581</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6275424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8206424713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137493133545</t>
+    <t xml:space="preserve">14.6275415420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8206443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034059524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137521743774</t>
   </si>
   <si>
     <t xml:space="preserve">14.6516799926758</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7562789916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505289077759</t>
+    <t xml:space="preserve">14.7562761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183471679688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505298614502</t>
   </si>
   <si>
     <t xml:space="preserve">15.1263904571533</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0861616134644</t>
+    <t xml:space="preserve">15.0861625671387</t>
   </si>
   <si>
     <t xml:space="preserve">15.0459318161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2953538894653</t>
+    <t xml:space="preserve">15.295355796814</t>
   </si>
   <si>
     <t xml:space="preserve">15.4240922927856</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4562768936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597230911255</t>
+    <t xml:space="preserve">15.4562721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597249984741</t>
   </si>
   <si>
     <t xml:space="preserve">15.2873115539551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8689193725586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240905761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
+    <t xml:space="preserve">14.8689203262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930578231812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4884614944458</t>
+    <t xml:space="preserve">15.4884576797485</t>
   </si>
   <si>
     <t xml:space="preserve">15.4401836395264</t>
@@ -530,280 +530,280 @@
     <t xml:space="preserve">15.3919067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2551221847534</t>
+    <t xml:space="preserve">15.2551259994507</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666212081909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229433059692</t>
+    <t xml:space="preserve">15.5286865234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229452133179</t>
   </si>
   <si>
     <t xml:space="preserve">15.0137481689453</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8850126266479</t>
+    <t xml:space="preserve">14.8850135803223</t>
   </si>
   <si>
     <t xml:space="preserve">15.1988048553467</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3275394439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114490509033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677682876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436338424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470817565918</t>
+    <t xml:space="preserve">15.3275375366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677673339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034038543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827154159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436347961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470808029175</t>
   </si>
   <si>
     <t xml:space="preserve">14.8286905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5390367507935</t>
+    <t xml:space="preserve">14.5390357971191</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551271438599</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1126022338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263944625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2815647125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827165603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171993255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103002548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631732940674</t>
+    <t xml:space="preserve">14.1125993728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263925552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815637588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171974182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103012084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5631742477417</t>
   </si>
   <si>
     <t xml:space="preserve">14.4585752487183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.305703163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045551300049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9516830444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781196594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045581817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3643283843994</t>
+    <t xml:space="preserve">14.3057041168213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045560836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9516801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781187057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">13.1873159408569</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9539833068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.31605052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5896139144897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746715545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9114551544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011070251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9999551773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9815645217896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378866195679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447818756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9171953201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011018753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5528268814087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5367345809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4643211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3838605880737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.609148979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4080009460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1103000640869</t>
+    <t xml:space="preserve">12.9539842605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3160514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5896129608154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746725082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9114513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011051177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9999580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9815635681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378847122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447828292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9171981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631702423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010980606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.552827835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.536732673645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.464319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091470718384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.407998085022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1103010177612</t>
   </si>
   <si>
     <t xml:space="preserve">15.2068510055542</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8263893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.89075756073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988008499146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9470796585083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114479064941</t>
+    <t xml:space="preserve">15.8263912200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8988037109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.947078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114459991455</t>
   </si>
   <si>
     <t xml:space="preserve">16.3493747711182</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3011016845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5344314575195</t>
+    <t xml:space="preserve">16.301097869873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5344333648682</t>
   </si>
   <si>
     <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3332805633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4539737701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1723670959473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1562767028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792633056641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436325073242</t>
+    <t xml:space="preserve">16.3332843780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.453971862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.17236328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1562728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700634002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.003396987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0436267852783</t>
   </si>
   <si>
     <t xml:space="preserve">16.4781093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8965034484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769611358643</t>
+    <t xml:space="preserve">16.8965015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769630432129</t>
   </si>
   <si>
     <t xml:space="preserve">17.0413284301758</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3792591094971</t>
+    <t xml:space="preserve">17.3792572021484</t>
   </si>
   <si>
     <t xml:space="preserve">17.5160388946533</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7735080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3850021362305</t>
+    <t xml:space="preserve">17.773509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3850002288818</t>
   </si>
   <si>
     <t xml:space="preserve">18.7470684051514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7229347229004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0206298828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.270055770874</t>
+    <t xml:space="preserve">18.7229290008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0206317901611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2700595855713</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4068374633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4470691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528133392334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033912658691</t>
+    <t xml:space="preserve">19.4068393707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4470672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033874511719</t>
   </si>
   <si>
     <t xml:space="preserve">19.6079864501953</t>
@@ -812,136 +812,136 @@
     <t xml:space="preserve">19.6321239471436</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7125854492188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3827018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5838470458984</t>
+    <t xml:space="preserve">19.7125835418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.382698059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5838451385498</t>
   </si>
   <si>
     <t xml:space="preserve">19.3102855682373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5436191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4631595611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0689086914062</t>
+    <t xml:space="preserve">19.5436153411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4631614685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0689105987549</t>
   </si>
   <si>
     <t xml:space="preserve">19.0769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0286769866943</t>
+    <t xml:space="preserve">18.8355731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.028678894043</t>
   </si>
   <si>
     <t xml:space="preserve">18.9723567962646</t>
   </si>
   <si>
-    <t xml:space="preserve">18.56201171875</t>
+    <t xml:space="preserve">18.5620136260986</t>
   </si>
   <si>
     <t xml:space="preserve">18.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6183319091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1654567718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8171825408936</t>
+    <t xml:space="preserve">18.6183338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1654605865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8171787261963</t>
   </si>
   <si>
     <t xml:space="preserve">20.259708404541</t>
   </si>
   <si>
+    <t xml:space="preserve">20.7585563659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5574073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539318084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1818695068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9213695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841827392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7666969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0027751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5726165771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.538761138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5550422668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4899139404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922271728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3271045684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.351526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5143394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9864940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946384429932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9376487731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1248874664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0353412628174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8155422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1574478149414</t>
+  </si>
+  <si>
     <t xml:space="preserve">20.7585601806641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5574073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9539318084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1818695068359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9213695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841846466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7666969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0027751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5726165771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.538761138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5550403594971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4899158477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3271045684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5143394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9864959716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946346282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9376487731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1248874664307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0353374481201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8399639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8155422210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1574478149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7585582733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945423126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957469940186</t>
+    <t xml:space="preserve">20.2945442199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
     <t xml:space="preserve">20.318962097168</t>
@@ -950,28 +950,28 @@
     <t xml:space="preserve">19.8386688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828876495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.985200881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1317310333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3678092956543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7259922027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108234405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9770584106445</t>
+    <t xml:space="preserve">20.0828857421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9851989746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1317291259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3678073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7259941101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9770603179932</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">18.9757633209229</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8048095703125</t>
+    <t xml:space="preserve">18.8048133850098</t>
   </si>
   <si>
     <t xml:space="preserve">18.7071228027344</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0978717803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6338596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1304378509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293254852295</t>
+    <t xml:space="preserve">19.0978736877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6338558197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1304340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293273925781</t>
   </si>
   <si>
     <t xml:space="preserve">20.2049942016602</t>
@@ -1013,16 +1013,16 @@
     <t xml:space="preserve">20.1805744171143</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2375583648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7829780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748374938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9050884246826</t>
+    <t xml:space="preserve">20.2375564575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829818725586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748394012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050903320312</t>
   </si>
   <si>
     <t xml:space="preserve">20.6771507263184</t>
@@ -1034,25 +1034,25 @@
     <t xml:space="preserve">21.2795562744141</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0597591400146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0434799194336</t>
+    <t xml:space="preserve">21.0597610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0434761047363</t>
   </si>
   <si>
     <t xml:space="preserve">20.6852931976318</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1004657745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400562286377</t>
+    <t xml:space="preserve">21.1004638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400581359863</t>
   </si>
   <si>
     <t xml:space="preserve">21.4260883331299</t>
   </si>
   <si>
-    <t xml:space="preserve">21.5319137573242</t>
+    <t xml:space="preserve">21.5319175720215</t>
   </si>
   <si>
     <t xml:space="preserve">21.3202610015869</t>
@@ -1064,25 +1064,25 @@
     <t xml:space="preserve">21.784273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">21.4993534088135</t>
+    <t xml:space="preserve">21.4993553161621</t>
   </si>
   <si>
     <t xml:space="preserve">21.3935260772705</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7761325836182</t>
+    <t xml:space="preserve">21.7761344909668</t>
   </si>
   <si>
     <t xml:space="preserve">21.6214618682861</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0692005157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169277191162</t>
+    <t xml:space="preserve">22.0691967010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7110118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169315338135</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
@@ -1091,40 +1091,40 @@
     <t xml:space="preserve">22.6308975219727</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0542106628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9890842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007389068604</t>
+    <t xml:space="preserve">23.0542087554932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9890823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
     <t xml:space="preserve">23.1681785583496</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4693794250488</t>
+    <t xml:space="preserve">23.4693832397461</t>
   </si>
   <si>
     <t xml:space="preserve">23.8601303100586</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7298774719238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310840606689</t>
+    <t xml:space="preserve">23.7298812866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310821533203</t>
   </si>
   <si>
     <t xml:space="preserve">23.9659595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0229454040527</t>
+    <t xml:space="preserve">24.0229434967041</t>
   </si>
   <si>
     <t xml:space="preserve">24.3648490905762</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9008350372314</t>
+    <t xml:space="preserve">23.9008312225342</t>
   </si>
   <si>
     <t xml:space="preserve">23.9903793334961</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">23.5996322631836</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5263633728027</t>
+    <t xml:space="preserve">23.5263652801514</t>
   </si>
   <si>
     <t xml:space="preserve">23.6159114837646</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">23.9822387695312</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2346000671387</t>
+    <t xml:space="preserve">24.23459815979</t>
   </si>
   <si>
     <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.9916763305664</t>
+    <t xml:space="preserve">24.9916744232178</t>
   </si>
   <si>
     <t xml:space="preserve">25.0568008422852</t>
@@ -1157,13 +1157,13 @@
     <t xml:space="preserve">25.0079555511475</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288650512695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6660480499268</t>
+    <t xml:space="preserve">24.8777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6660499572754</t>
   </si>
   <si>
     <t xml:space="preserve">24.6497707366943</t>
@@ -1175,34 +1175,34 @@
     <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.480110168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1789073944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1613330841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5602245330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7474555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5765037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4556903839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.277889251709</t>
+    <t xml:space="preserve">25.4801139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1789093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1613311767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5602207183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7474575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5765075683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4556922912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2778911590576</t>
   </si>
   <si>
     <t xml:space="preserve">25.9848289489746</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1082344055176</t>
+    <t xml:space="preserve">27.1082324981689</t>
   </si>
   <si>
     <t xml:space="preserve">27.7676258087158</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">27.3850154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9209976196289</t>
+    <t xml:space="preserve">26.9209995269775</t>
   </si>
   <si>
     <t xml:space="preserve">27.5071239471436</t>
@@ -1223,19 +1223,19 @@
     <t xml:space="preserve">26.6930637359619</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2765960693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9102687835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.617208480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5846462249756</t>
+    <t xml:space="preserve">25.2765941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.910270690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.584644317627</t>
   </si>
   <si>
     <t xml:space="preserve">25.2440338134766</t>
@@ -1247,10 +1247,10 @@
     <t xml:space="preserve">24.7393169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951904296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6429233551025</t>
+    <t xml:space="preserve">25.1951923370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
     <t xml:space="preserve">25.5859413146973</t>
@@ -1262,58 +1262,58 @@
     <t xml:space="preserve">25.6917686462402</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5452365875244</t>
+    <t xml:space="preserve">25.545238494873</t>
   </si>
   <si>
     <t xml:space="preserve">25.7568950653076</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5208148956299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3173007965088</t>
+    <t xml:space="preserve">25.5208168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3172988891602</t>
   </si>
   <si>
     <t xml:space="preserve">25.3987064361572</t>
   </si>
   <si>
-    <t xml:space="preserve">25.512674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7650318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499534606934</t>
+    <t xml:space="preserve">25.5126724243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7650356292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499515533447</t>
   </si>
   <si>
     <t xml:space="preserve">25.2033309936523</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0486602783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4625377655029</t>
+    <t xml:space="preserve">25.0486621856689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4625339508057</t>
   </si>
   <si>
     <t xml:space="preserve">25.3661422729492</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0242404937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148952484131</t>
+    <t xml:space="preserve">25.0242385864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824253082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893611907959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148971557617</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.741907119751</t>
+    <t xml:space="preserve">26.7419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">26.5790939331055</t>
@@ -1325,16 +1325,16 @@
     <t xml:space="preserve">26.6605014801025</t>
   </si>
   <si>
-    <t xml:space="preserve">26.497688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6022243499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127647399902</t>
+    <t xml:space="preserve">26.4976863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
     <t xml:space="preserve">26.2941722869873</t>
@@ -1361,25 +1361,25 @@
     <t xml:space="preserve">26.1720638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">25.0730819702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6253452301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8519916534424</t>
+    <t xml:space="preserve">25.0730800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6253471374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.974100112915</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615196228027</t>
+    <t xml:space="preserve">25.5615177154541</t>
   </si>
   <si>
     <t xml:space="preserve">25.3580055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1137809753418</t>
+    <t xml:space="preserve">25.1137847900391</t>
   </si>
   <si>
     <t xml:space="preserve">25.2358932495117</t>
@@ -1388,13 +1388,13 @@
     <t xml:space="preserve">23.3635540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218349456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2534713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6891784667969</t>
+    <t xml:space="preserve">24.4218311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2534694671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6891765594482</t>
   </si>
   <si>
     <t xml:space="preserve">23.5670700073242</t>
@@ -1403,19 +1403,19 @@
     <t xml:space="preserve">20.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6364498138428</t>
+    <t xml:space="preserve">20.6364479064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.7178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7002792358398</t>
+    <t xml:space="preserve">19.7002811431885</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736366271973</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2062892913818</t>
+    <t xml:space="preserve">21.2062911987305</t>
   </si>
   <si>
     <t xml:space="preserve">21.6540260314941</t>
@@ -1424,25 +1424,25 @@
     <t xml:space="preserve">21.7354335784912</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4273815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.816837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8806667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505100250244</t>
+    <t xml:space="preserve">22.4273834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8168354034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8806686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.450511932373</t>
   </si>
   <si>
     <t xml:space="preserve">21.3284015655518</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6947288513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4680862426758</t>
+    <t xml:space="preserve">21.6947269439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4680843353271</t>
   </si>
   <si>
     <t xml:space="preserve">22.1831645965576</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
-    <t xml:space="preserve">22.0203533172607</t>
+    <t xml:space="preserve">22.0203514099121</t>
   </si>
   <si>
     <t xml:space="preserve">22.3459777832031</t>
@@ -1460,55 +1460,55 @@
     <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123031616211</t>
+    <t xml:space="preserve">22.7123050689697</t>
   </si>
   <si>
     <t xml:space="preserve">23.6077709197998</t>
   </si>
   <si>
-    <t xml:space="preserve">25.805736541748</t>
+    <t xml:space="preserve">25.8057384490967</t>
   </si>
   <si>
     <t xml:space="preserve">24.7067546844482</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3811283111572</t>
+    <t xml:space="preserve">24.3811302185059</t>
   </si>
   <si>
     <t xml:space="preserve">24.2183170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1776142120361</t>
+    <t xml:space="preserve">24.1776123046875</t>
   </si>
   <si>
     <t xml:space="preserve">24.2997245788574</t>
   </si>
   <si>
-    <t xml:space="preserve">24.7881622314453</t>
+    <t xml:space="preserve">24.788158416748</t>
   </si>
   <si>
     <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1260375976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640110015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019863128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.408899307251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.781343460083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7399597167969</t>
+    <t xml:space="preserve">24.1260395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640129089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4088954925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7813415527344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7399578094482</t>
   </si>
   <si>
     <t xml:space="preserve">25.3261337280273</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">27.1469669342041</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9400520324707</t>
+    <t xml:space="preserve">26.940055847168</t>
   </si>
   <si>
     <t xml:space="preserve">26.1951656341553</t>
@@ -1529,31 +1529,31 @@
     <t xml:space="preserve">25.491662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5330429077148</t>
+    <t xml:space="preserve">25.5330448150635</t>
   </si>
   <si>
     <t xml:space="preserve">25.0778369903564</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3675155639648</t>
+    <t xml:space="preserve">25.3675136566162</t>
   </si>
   <si>
     <t xml:space="preserve">25.6985740661621</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2847518920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6571960449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.153787612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8227252960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.946870803833</t>
+    <t xml:space="preserve">25.2847499847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6571941375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1537837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.8227233886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9468746185303</t>
   </si>
   <si>
     <t xml:space="preserve">26.0710201263428</t>
@@ -1562,34 +1562,34 @@
     <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
-    <t xml:space="preserve">26.319314956665</t>
+    <t xml:space="preserve">26.3193130493164</t>
   </si>
   <si>
     <t xml:space="preserve">27.0642032623291</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0228176116943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.250186920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6294460296631</t>
+    <t xml:space="preserve">27.022819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2501888275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6294479370117</t>
   </si>
   <si>
     <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0432720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8363590240479</t>
+    <t xml:space="preserve">24.0432739257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8363609313965</t>
   </si>
   <si>
     <t xml:space="preserve">23.3811511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">23.794979095459</t>
+    <t xml:space="preserve">23.7949810028076</t>
   </si>
   <si>
     <t xml:space="preserve">23.877742767334</t>
@@ -1598,16 +1598,16 @@
     <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2088050842285</t>
+    <t xml:space="preserve">24.2088031768799</t>
   </si>
   <si>
     <t xml:space="preserve">24.3329524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262260437012</t>
+    <t xml:space="preserve">25.4502830505371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262279510498</t>
   </si>
   <si>
     <t xml:space="preserve">25.864107131958</t>
@@ -1619,37 +1619,37 @@
     <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
-    <t xml:space="preserve">25.574426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6089935302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9814338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9882545471191</t>
+    <t xml:space="preserve">25.5744304656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6089954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9814357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9882526397705</t>
   </si>
   <si>
     <t xml:space="preserve">26.4434623718262</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503753662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4984798431396</t>
+    <t xml:space="preserve">26.6503772735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3606986999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4984836578369</t>
   </si>
   <si>
     <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.72585105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4361743927002</t>
+    <t xml:space="preserve">21.7258491516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4361724853516</t>
   </si>
   <si>
     <t xml:space="preserve">21.89137840271</t>
@@ -1658,37 +1658,37 @@
     <t xml:space="preserve">20.7740535736084</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6430835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4775562286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1051120758057</t>
+    <t xml:space="preserve">21.6430854797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4775543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1051082611084</t>
   </si>
   <si>
     <t xml:space="preserve">20.8154335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6981010437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636341094971</t>
+    <t xml:space="preserve">19.6981029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636360168457</t>
   </si>
   <si>
     <t xml:space="preserve">20.3602256774902</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2360763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.939582824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9327621459961</t>
+    <t xml:space="preserve">20.2360801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9395809173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9327640533447</t>
   </si>
   <si>
     <t xml:space="preserve">22.0569095611572</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">22.9259433746338</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2638263702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0014171600342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4634475708008</t>
+    <t xml:space="preserve">22.263822555542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0014190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4634418487549</t>
   </si>
   <si>
     <t xml:space="preserve">17.5462112426758</t>
@@ -1712,7 +1712,7 @@
     <t xml:space="preserve">17.6703586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877269744873</t>
+    <t xml:space="preserve">17.8772716522217</t>
   </si>
   <si>
     <t xml:space="preserve">18.2083301544189</t>
@@ -1724,55 +1724,55 @@
     <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8290710449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6221580505371</t>
+    <t xml:space="preserve">18.8290691375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6221561431885</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3670444488525</t>
+    <t xml:space="preserve">19.3670425415039</t>
   </si>
   <si>
     <t xml:space="preserve">19.5325736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">19.491189956665</t>
+    <t xml:space="preserve">19.4911918640137</t>
   </si>
   <si>
     <t xml:space="preserve">19.0773639678955</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1187477111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0427989959717</t>
+    <t xml:space="preserve">19.118745803833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0428009033203</t>
   </si>
   <si>
     <t xml:space="preserve">17.794506072998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8427066802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806819915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.966854095459</t>
+    <t xml:space="preserve">16.8427085876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9668560028076</t>
   </si>
   <si>
     <t xml:space="preserve">16.6357955932617</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7599411010742</t>
+    <t xml:space="preserve">16.7599430084229</t>
   </si>
   <si>
     <t xml:space="preserve">16.884090423584</t>
@@ -1781,16 +1781,16 @@
     <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2497119903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4152450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.40842628479</t>
+    <t xml:space="preserve">18.2497138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4152412414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4084281921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739555358887</t>
@@ -1799,7 +1799,7 @@
     <t xml:space="preserve">19.4498100280762</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9050178527832</t>
+    <t xml:space="preserve">19.9050140380859</t>
   </si>
   <si>
     <t xml:space="preserve">19.8222522735596</t>
@@ -1814,7 +1814,7 @@
     <t xml:space="preserve">20.3188438415527</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1119289398193</t>
+    <t xml:space="preserve">20.111930847168</t>
   </si>
   <si>
     <t xml:space="preserve">19.7808704376221</t>
@@ -1823,37 +1823,37 @@
     <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0291652679443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567211151123</t>
+    <t xml:space="preserve">20.0291633605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567230224609</t>
   </si>
   <si>
     <t xml:space="preserve">19.9463996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.325662612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0359802246094</t>
+    <t xml:space="preserve">19.2428951263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3256587982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0359840393066</t>
   </si>
   <si>
     <t xml:space="preserve">17.2979145050049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364723205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.594409942627</t>
+    <t xml:space="preserve">16.5364761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5944118499756</t>
   </si>
   <si>
     <t xml:space="preserve">16.48681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4537086486816</t>
+    <t xml:space="preserve">16.453706741333</t>
   </si>
   <si>
     <t xml:space="preserve">17.0910015106201</t>
@@ -1862,37 +1862,37 @@
     <t xml:space="preserve">17.2151470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310241699219</t>
+    <t xml:space="preserve">17.3310203552246</t>
   </si>
   <si>
     <t xml:space="preserve">17.364128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2910976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6056041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3407573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0593528747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6455268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2482528686523</t>
+    <t xml:space="preserve">18.2910957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6056022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3407554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0593566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.645528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.248254776001</t>
   </si>
   <si>
     <t xml:space="preserve">17.6289749145508</t>
   </si>
   <si>
-    <t xml:space="preserve">18.07590675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1255664825439</t>
+    <t xml:space="preserve">18.0759048461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1255645751953</t>
   </si>
   <si>
     <t xml:space="preserve">17.6620807647705</t>
@@ -1901,121 +1901,121 @@
     <t xml:space="preserve">17.7779521942139</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765892028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2248859405518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861339569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6192436218262</t>
+    <t xml:space="preserve">17.9765911102295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2248840332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861358642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6192417144775</t>
   </si>
   <si>
     <t xml:space="preserve">16.5033702850342</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5101890563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274234771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701692581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8397912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328773498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6742563247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177845001221</t>
+    <t xml:space="preserve">15.5101881027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274225234985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.270170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328783035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6742582321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177835464478</t>
   </si>
   <si>
     <t xml:space="preserve">16.0233345031738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9322910308838</t>
+    <t xml:space="preserve">15.9322891235352</t>
   </si>
   <si>
     <t xml:space="preserve">15.0632562637329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0549783706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0467042922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232364654541</t>
+    <t xml:space="preserve">15.0549812316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6659822463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232383728027</t>
   </si>
   <si>
     <t xml:space="preserve">15.3255767822266</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3426036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.712553024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8402662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6614656448364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6444396972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8062086105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5422687530518</t>
+    <t xml:space="preserve">15.3426027297974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7125520706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8402652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6614665985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6444406509399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.806209564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5422677993774</t>
   </si>
   <si>
     <t xml:space="preserve">14.8913507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9811687469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083795547485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.525239944458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4741544723511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2017011642456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3890132904053</t>
+    <t xml:space="preserve">15.9811697006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661424636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083805084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5252389907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4741554260254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2017002105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3890142440796</t>
   </si>
   <si>
     <t xml:space="preserve">14.6018676757812</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315843582153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2357549667358</t>
+    <t xml:space="preserve">14.4315853118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2357559204102</t>
   </si>
   <si>
     <t xml:space="preserve">14.0484437942505</t>
@@ -2024,49 +2024,49 @@
     <t xml:space="preserve">14.1846714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8317527770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5507822036743</t>
+    <t xml:space="preserve">14.8317518234253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.55078125</t>
   </si>
   <si>
     <t xml:space="preserve">14.3208990097046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7295799255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0020370483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232374191284</t>
+    <t xml:space="preserve">14.7295818328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0020360946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8232355117798</t>
   </si>
   <si>
     <t xml:space="preserve">14.4230699539185</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3379287719727</t>
+    <t xml:space="preserve">14.3379278182983</t>
   </si>
   <si>
     <t xml:space="preserve">14.3549547195435</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9462738037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6908473968506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7419319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7930192947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6312475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0948534011841</t>
+    <t xml:space="preserve">13.9462747573853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6908483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7419328689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7930173873901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6312484741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0948524475098</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821655273438</t>
@@ -2075,31 +2075,31 @@
     <t xml:space="preserve">14.3975276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0995283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8866729736328</t>
+    <t xml:space="preserve">14.0995302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8866739273071</t>
   </si>
   <si>
     <t xml:space="preserve">13.8185596466064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2225646972656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801630020142</t>
+    <t xml:space="preserve">13.2225675582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801639556885</t>
   </si>
   <si>
     <t xml:space="preserve">13.6227340698242</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5205640792847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1799945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1544513702393</t>
+    <t xml:space="preserve">13.5205631256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1799955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1544532775879</t>
   </si>
   <si>
     <t xml:space="preserve">13.2140522003174</t>
@@ -2108,10 +2108,10 @@
     <t xml:space="preserve">12.1668033599854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9663000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748153686523</t>
+    <t xml:space="preserve">10.9663009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.974814414978</t>
   </si>
   <si>
     <t xml:space="preserve">10.9492721557617</t>
@@ -2132,13 +2132,13 @@
     <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1621265411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7875022888184</t>
+    <t xml:space="preserve">11.162127494812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8811588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.787501335144</t>
   </si>
   <si>
     <t xml:space="preserve">10.7619609832764</t>
@@ -2150,67 +2150,67 @@
     <t xml:space="preserve">11.0599565505981</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8471002578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6683025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7279024124146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664703369141</t>
+    <t xml:space="preserve">10.8471021652222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6683044433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7279033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664684295654</t>
   </si>
   <si>
     <t xml:space="preserve">11.5367527008057</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6644649505615</t>
+    <t xml:space="preserve">11.6644659042358</t>
   </si>
   <si>
     <t xml:space="preserve">11.6900091171265</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7410936355591</t>
+    <t xml:space="preserve">11.7410945892334</t>
   </si>
   <si>
     <t xml:space="preserve">11.749608039856</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1838331222534</t>
+    <t xml:space="preserve">12.1838321685791</t>
   </si>
   <si>
     <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8177223205566</t>
+    <t xml:space="preserve">11.8177213668823</t>
   </si>
   <si>
     <t xml:space="preserve">11.7751502990723</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0476045608521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4601259231567</t>
+    <t xml:space="preserve">12.0476055145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4601249694824</t>
   </si>
   <si>
     <t xml:space="preserve">11.5026960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1450996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2898406982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2132139205933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7108755111694</t>
+    <t xml:space="preserve">11.1450986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981885910034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2898397445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2132129669189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7108745574951</t>
   </si>
   <si>
     <t xml:space="preserve">10.4724769592285</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">10.6597890853882</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0173864364624</t>
+    <t xml:space="preserve">11.0173854827881</t>
   </si>
   <si>
     <t xml:space="preserve">11.0854997634888</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">11.0514421463013</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1280717849731</t>
+    <t xml:space="preserve">11.1280698776245</t>
   </si>
   <si>
     <t xml:space="preserve">11.0003576278687</t>
@@ -2240,46 +2240,46 @@
     <t xml:space="preserve">11.2642984390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6985235214233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814937591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8092079162598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3247375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1970243453979</t>
+    <t xml:space="preserve">11.698522567749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814947128296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8092060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3247365951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1970233917236</t>
   </si>
   <si>
     <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5120487213135</t>
+    <t xml:space="preserve">13.5120496749878</t>
   </si>
   <si>
     <t xml:space="preserve">13.6738195419312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5461053848267</t>
+    <t xml:space="preserve">13.546106338501</t>
   </si>
   <si>
     <t xml:space="preserve">14.4145545959473</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8526182174683</t>
+    <t xml:space="preserve">13.8526172637939</t>
   </si>
   <si>
     <t xml:space="preserve">14.2187271118164</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8781585693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.775990486145</t>
+    <t xml:space="preserve">13.8781595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7759885787964</t>
   </si>
   <si>
     <t xml:space="preserve">13.4439363479614</t>
@@ -2288,61 +2288,61 @@
     <t xml:space="preserve">13.8441028594971</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4486112594604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6274118423462</t>
+    <t xml:space="preserve">14.4486122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6274089813232</t>
   </si>
   <si>
     <t xml:space="preserve">14.9254083633423</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5043745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933523178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5592975616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.942437171936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.967978477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6870098114014</t>
+    <t xml:space="preserve">15.5043716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933532714844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5592956542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9424362182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.967981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6870088577271</t>
   </si>
   <si>
     <t xml:space="preserve">15.019063949585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1467790603638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170595169067</t>
+    <t xml:space="preserve">15.1467781066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170623779297</t>
   </si>
   <si>
     <t xml:space="preserve">15.6406021118164</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4618043899536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656400680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.363471031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3294134140015</t>
+    <t xml:space="preserve">15.461802482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656410217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3634719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3294124603271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4826698303223</t>
   </si>
   <si>
-    <t xml:space="preserve">14.150616645813</t>
+    <t xml:space="preserve">14.1506147384644</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335868835449</t>
@@ -2351,70 +2351,70 @@
     <t xml:space="preserve">14.5763254165649</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1165571212769</t>
+    <t xml:space="preserve">14.1165599822998</t>
   </si>
   <si>
     <t xml:space="preserve">14.4911832809448</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3804998397827</t>
+    <t xml:space="preserve">14.3804969787598</t>
   </si>
   <si>
     <t xml:space="preserve">14.4996995925903</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7721519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7078762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292449951172</t>
+    <t xml:space="preserve">14.7721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7078771591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292459487915</t>
   </si>
   <si>
     <t xml:space="preserve">13.5035343170166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3162231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.563136100769</t>
+    <t xml:space="preserve">13.3162221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631351470947</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375909805298</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4060401916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.269814491272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5082130432129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5167236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1761560440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1931867599487</t>
+    <t xml:space="preserve">14.4060411453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2698125839233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2953567504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5082120895386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5167255401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1761569976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1931858062744</t>
   </si>
   <si>
     <t xml:space="preserve">13.7589616775513</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4183931350708</t>
+    <t xml:space="preserve">13.4183921813965</t>
   </si>
   <si>
     <t xml:space="preserve">12.5584573745728</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3370876312256</t>
+    <t xml:space="preserve">12.3370885848999</t>
   </si>
   <si>
     <t xml:space="preserve">12.6010284423828</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">11.9880056381226</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6218938827515</t>
+    <t xml:space="preserve">11.6218957901001</t>
   </si>
   <si>
     <t xml:space="preserve">11.4430952072144</t>
@@ -2432,34 +2432,34 @@
     <t xml:space="preserve">10.3277349472046</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82539749145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42522811889648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74025440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08424091339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73557758331299</t>
+    <t xml:space="preserve">9.82539653778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4252290725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74025535583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08424186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7355785369873</t>
   </si>
   <si>
     <t xml:space="preserve">8.2715539932251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31412410736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96078586578369</t>
+    <t xml:space="preserve">8.31412506103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96078491210938</t>
   </si>
   <si>
     <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11020278930664</t>
+    <t xml:space="preserve">9.11020374298096</t>
   </si>
   <si>
     <t xml:space="preserve">9.00803279876709</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">9.47631359100342</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5784854888916</t>
+    <t xml:space="preserve">9.57848453521729</t>
   </si>
   <si>
     <t xml:space="preserve">9.44225692749023</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317398071289</t>
+    <t xml:space="preserve">9.09317493438721</t>
   </si>
   <si>
     <t xml:space="preserve">9.16980266571045</t>
@@ -2489,16 +2489,16 @@
     <t xml:space="preserve">9.53591346740723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48482894897461</t>
+    <t xml:space="preserve">9.48482799530029</t>
   </si>
   <si>
     <t xml:space="preserve">9.62105560302734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319074630737</t>
+    <t xml:space="preserve">10.0893363952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.131908416748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0467662811279</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">9.75728321075439</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87648296356201</t>
+    <t xml:space="preserve">9.8764820098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.97013854980469</t>
@@ -2519,28 +2519,28 @@
     <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.319221496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4299058914185</t>
+    <t xml:space="preserve">10.3192195892334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4299049377441</t>
   </si>
   <si>
     <t xml:space="preserve">10.9322443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961832046509</t>
+    <t xml:space="preserve">11.1961841583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96162509918213</t>
+    <t xml:space="preserve">9.96162414550781</t>
   </si>
   <si>
     <t xml:space="preserve">9.85945320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78282451629639</t>
+    <t xml:space="preserve">9.7828254699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.3060302734375</t>
@@ -2552,7 +2552,7 @@
     <t xml:space="preserve">9.51888561248779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22940158843994</t>
+    <t xml:space="preserve">9.22940254211426</t>
   </si>
   <si>
     <t xml:space="preserve">9.26346015930176</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">8.86329174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93140506744385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85477542877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28048706054688</t>
+    <t xml:space="preserve">8.93140602111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85477638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28048801422119</t>
   </si>
   <si>
     <t xml:space="preserve">9.70619773864746</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">9.85093879699707</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876707077026</t>
+    <t xml:space="preserve">11.187671661377</t>
   </si>
   <si>
     <t xml:space="preserve">10.8300743103027</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">10.2340793609619</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61254119873047</t>
+    <t xml:space="preserve">9.61254215240479</t>
   </si>
   <si>
     <t xml:space="preserve">9.9638843536377</t>
@@ -2609,22 +2609,22 @@
     <t xml:space="preserve">10.182391166687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1998720169067</t>
+    <t xml:space="preserve">10.1998710632324</t>
   </si>
   <si>
     <t xml:space="preserve">10.1649103164673</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0600280761719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.444598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0163259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90270328521729</t>
+    <t xml:space="preserve">10.0600271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4445991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0163269042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9027042388916</t>
   </si>
   <si>
     <t xml:space="preserve">9.72789764404297</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">9.64049530029297</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28214550018311</t>
+    <t xml:space="preserve">9.28214645385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.56183242797852</t>
@@ -2642,70 +2642,70 @@
     <t xml:space="preserve">9.41324901580811</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52687168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49190998077393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40450954437256</t>
+    <t xml:space="preserve">9.5268726348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49191188812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40450859069824</t>
   </si>
   <si>
     <t xml:space="preserve">9.15978145599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99371719360352</t>
+    <t xml:space="preserve">8.99371814727783</t>
   </si>
   <si>
     <t xml:space="preserve">9.01993751525879</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9063138961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57931423187256</t>
+    <t xml:space="preserve">8.90631484985352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57931327819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.20348262786865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36080741882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18600273132324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33458614349365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22096347808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44820976257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29088592529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01119709014893</t>
+    <t xml:space="preserve">9.36080646514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18600177764893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33458709716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22096252441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44821071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29088497161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01119804382324</t>
   </si>
   <si>
     <t xml:space="preserve">10.3484563827515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4358577728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4271183013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9777536392212</t>
+    <t xml:space="preserve">10.4358587265015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4271173477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9777545928955</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001167297363</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3186235427856</t>
+    <t xml:space="preserve">11.31862449646</t>
   </si>
   <si>
     <t xml:space="preserve">11.4672079086304</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">11.0826368331909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8903512954712</t>
+    <t xml:space="preserve">10.8903503417969</t>
   </si>
   <si>
     <t xml:space="preserve">10.7942094802856</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">10.6281433105469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5494813919067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872743606567</t>
+    <t xml:space="preserve">10.5494823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872734069824</t>
   </si>
   <si>
     <t xml:space="preserve">10.226092338562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1299495697021</t>
+    <t xml:space="preserve">10.1299486160278</t>
   </si>
   <si>
     <t xml:space="preserve">9.98136615753174</t>
@@ -2741,13 +2741,13 @@
     <t xml:space="preserve">9.93766403198242</t>
   </si>
   <si>
-    <t xml:space="preserve">10.094988822937</t>
+    <t xml:space="preserve">10.0949878692627</t>
   </si>
   <si>
     <t xml:space="preserve">10.1124687194824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0250663757324</t>
+    <t xml:space="preserve">10.0250673294067</t>
   </si>
   <si>
     <t xml:space="preserve">9.95514488220215</t>
@@ -2756,31 +2756,31 @@
     <t xml:space="preserve">9.78034019470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75411891937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65797710418701</t>
+    <t xml:space="preserve">9.75411796569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6579761505127</t>
   </si>
   <si>
     <t xml:space="preserve">9.74537944793701</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884510040283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3222351074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7330255508423</t>
+    <t xml:space="preserve">9.99884605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3222341537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7330265045166</t>
   </si>
   <si>
     <t xml:space="preserve">10.7505073547363</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4620800018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2785339355469</t>
+    <t xml:space="preserve">10.4620790481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2785348892212</t>
   </si>
   <si>
     <t xml:space="preserve">10.3834171295166</t>
@@ -2801,13 +2801,13 @@
     <t xml:space="preserve">10.4795598983765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5757026672363</t>
+    <t xml:space="preserve">10.575701713562</t>
   </si>
   <si>
     <t xml:space="preserve">10.5669622421265</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5232601165771</t>
+    <t xml:space="preserve">10.5232610702515</t>
   </si>
   <si>
     <t xml:space="preserve">10.5582218170166</t>
@@ -2816,16 +2816,16 @@
     <t xml:space="preserve">10.4708194732666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81529903411865</t>
+    <t xml:space="preserve">9.81530094146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9901065826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82404041290283</t>
+    <t xml:space="preserve">9.99010562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82403945922852</t>
   </si>
   <si>
     <t xml:space="preserve">9.86774253845215</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">9.00245761871338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8276538848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36878871917725</t>
+    <t xml:space="preserve">8.82765197753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5348539352417</t>
@@ -2858,91 +2858,91 @@
     <t xml:space="preserve">8.88883399963379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98497581481934</t>
+    <t xml:space="preserve">8.98497772216797</t>
   </si>
   <si>
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078321456909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350774765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070518493652</t>
+    <t xml:space="preserve">9.69293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078311920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350784301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070499420166</t>
   </si>
   <si>
     <t xml:space="preserve">12.3324928283691</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3587141036987</t>
+    <t xml:space="preserve">12.3587131500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.559739112854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8867406845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4810762405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1926488876343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857128143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0702857971191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9741411209106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.991623878479</t>
+    <t xml:space="preserve">11.886739730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4810771942139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.19264793396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2101278305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0702848434448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.974142074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9916229248047</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.061544418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1314678192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0440635681152</t>
+    <t xml:space="preserve">12.0615453720093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1314668655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0440645217896</t>
   </si>
   <si>
     <t xml:space="preserve">11.8954801559448</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0091037750244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.01784324646</t>
+    <t xml:space="preserve">12.0091028213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0178442001343</t>
   </si>
   <si>
     <t xml:space="preserve">12.6558809280396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6733627319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4898157119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4198951721191</t>
+    <t xml:space="preserve">12.673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4898166656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4198942184448</t>
   </si>
   <si>
     <t xml:space="preserve">12.5684795379639</t>
@@ -2951,37 +2951,37 @@
     <t xml:space="preserve">12.5422582626343</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7782440185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2363510131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4461164474487</t>
+    <t xml:space="preserve">12.778244972229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2363500595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4461154937744</t>
   </si>
   <si>
     <t xml:space="preserve">12.516037940979</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5509996414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2713108062744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8132066726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8394269943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9093494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.821946144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9880104064941</t>
+    <t xml:space="preserve">12.5509986877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2713117599487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8132057189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.839427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.909348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8219470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9880113601685</t>
   </si>
   <si>
     <t xml:space="preserve">13.0229721069336</t>
@@ -2999,10 +2999,10 @@
     <t xml:space="preserve">12.7607650756836</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6296615600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9530506134033</t>
+    <t xml:space="preserve">12.6296606063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.953049659729</t>
   </si>
   <si>
     <t xml:space="preserve">12.9792709350586</t>
@@ -3023,19 +3023,19 @@
     <t xml:space="preserve">13.2239971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">13.800853729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0280990600586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1067628860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3951921463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5000743865967</t>
+    <t xml:space="preserve">13.8008556365967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0281009674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1067638397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3951902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.500075340271</t>
   </si>
   <si>
     <t xml:space="preserve">14.4039316177368</t>
@@ -3047,19 +3047,19 @@
     <t xml:space="preserve">14.2116460800171</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7484121322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0980215072632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7221927642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3864498138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6661396026611</t>
+    <t xml:space="preserve">13.7484130859375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0980224609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7221918106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3864517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6661386489868</t>
   </si>
   <si>
     <t xml:space="preserve">14.7098398208618</t>
@@ -3068,25 +3068,25 @@
     <t xml:space="preserve">14.6224374771118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0157489776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653593063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1206302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4563751220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6136951446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762282371521</t>
+    <t xml:space="preserve">15.0157480239868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818132400513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1206331253052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4563732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.613697052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7622804641724</t>
   </si>
   <si>
     <t xml:space="preserve">16.3442668914795</t>
@@ -3095,52 +3095,52 @@
     <t xml:space="preserve">16.7550582885742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946556091309</t>
+    <t xml:space="preserve">15.9946584701538</t>
   </si>
   <si>
     <t xml:space="preserve">15.8373336791992</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9159965515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9247350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9422168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1344985961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4352798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5663843154907</t>
+    <t xml:space="preserve">15.9159927368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9247369766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9422149658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.13450050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4352807998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.566385269165</t>
   </si>
   <si>
     <t xml:space="preserve">15.3566179275513</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4440221786499</t>
+    <t xml:space="preserve">15.4440202713013</t>
   </si>
   <si>
     <t xml:space="preserve">15.3303985595703</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2429962158203</t>
+    <t xml:space="preserve">15.242995262146</t>
   </si>
   <si>
     <t xml:space="preserve">15.2255153656006</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2866973876953</t>
+    <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779569625854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2517356872559</t>
+    <t xml:space="preserve">15.2517366409302</t>
   </si>
   <si>
     <t xml:space="preserve">15.0681896209717</t>
@@ -3149,28 +3149,28 @@
     <t xml:space="preserve">15.1381130218506</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4265413284302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8933868408203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8234634399414</t>
+    <t xml:space="preserve">15.4265403747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0244913101196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.893385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8234624862671</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196062088013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9982690811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.937087059021</t>
+    <t xml:space="preserve">14.9196071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.99827003479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9370851516724</t>
   </si>
   <si>
     <t xml:space="preserve">15.1468524932861</t>
@@ -3179,31 +3179,31 @@
     <t xml:space="preserve">14.849684715271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1031522750854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2604761123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3041772842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8409423828125</t>
+    <t xml:space="preserve">15.1031513214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.26047706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.304178237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8409452438354</t>
   </si>
   <si>
     <t xml:space="preserve">14.4214115142822</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5962171554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7812786102295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4367980957031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4630184173584</t>
+    <t xml:space="preserve">14.5962162017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7812805175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4368000030518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.463020324707</t>
   </si>
   <si>
     <t xml:space="preserve">18.074836730957</t>
@@ -3212,43 +3212,43 @@
     <t xml:space="preserve">18.2846031188965</t>
   </si>
   <si>
-    <t xml:space="preserve">18.839750289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5049018859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7340087890625</t>
+    <t xml:space="preserve">18.8397483825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340068817139</t>
   </si>
   <si>
     <t xml:space="preserve">18.4696502685547</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573722839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8221244812012</t>
+    <t xml:space="preserve">18.8573741912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8221282958984</t>
   </si>
   <si>
     <t xml:space="preserve">19.3684597015381</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9631175994873</t>
+    <t xml:space="preserve">18.9631156921387</t>
   </si>
   <si>
     <t xml:space="preserve">19.1217288970947</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0688591003418</t>
+    <t xml:space="preserve">19.0688571929932</t>
   </si>
   <si>
     <t xml:space="preserve">18.9807395935059</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8749961853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5753917694092</t>
+    <t xml:space="preserve">18.8749942779541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
     <t xml:space="preserve">18.2052955627441</t>
@@ -3269,52 +3269,52 @@
     <t xml:space="preserve">18.2934150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2581691741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1524257659912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0290603637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8175754547119</t>
+    <t xml:space="preserve">18.2581672668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1524276733398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0290584564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8175735473633</t>
   </si>
   <si>
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8880672454834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7647018432617</t>
+    <t xml:space="preserve">17.888069152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7647037506104</t>
   </si>
   <si>
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708446502686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589603424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.526782989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3681678771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1478710174561</t>
+    <t xml:space="preserve">17.5708427429199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5267810821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3681697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1478729248047</t>
   </si>
   <si>
     <t xml:space="preserve">17.4651012420654</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9761867523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8351974487305</t>
+    <t xml:space="preserve">17.976188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
     <t xml:space="preserve">17.482723236084</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">17.2007446289062</t>
   </si>
   <si>
-    <t xml:space="preserve">16.372428894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.125696182251</t>
+    <t xml:space="preserve">16.3724308013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1256980895996</t>
   </si>
   <si>
     <t xml:space="preserve">16.5222320556641</t>
@@ -3335,7 +3335,7 @@
     <t xml:space="preserve">16.6367855072021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3857936859131</t>
+    <t xml:space="preserve">17.3857917785645</t>
   </si>
   <si>
     <t xml:space="preserve">17.2448024749756</t>
@@ -3347,10 +3347,10 @@
     <t xml:space="preserve">17.4122276306152</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7823295593262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7470779418945</t>
+    <t xml:space="preserve">17.7823257446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7470798492432</t>
   </si>
   <si>
     <t xml:space="preserve">17.5355949401855</t>
@@ -3359,31 +3359,31 @@
     <t xml:space="preserve">17.6237125396729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8747043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0861892700195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1743106842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417358398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1654949188232</t>
+    <t xml:space="preserve">16.8747062683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0861911773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1743087768555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417339324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1654968261719</t>
   </si>
   <si>
     <t xml:space="preserve">16.9540100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3593597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9716377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249031066895</t>
+    <t xml:space="preserve">17.3593578338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249050140381</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896553039551</t>
@@ -3392,70 +3392,70 @@
     <t xml:space="preserve">16.6720333099365</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4869842529297</t>
+    <t xml:space="preserve">16.4869823455811</t>
   </si>
   <si>
     <t xml:space="preserve">16.8042106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2183704376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8704452514648</t>
+    <t xml:space="preserve">17.2183685302734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8704471588135</t>
   </si>
   <si>
     <t xml:space="preserve">17.6765842437744</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5796546936035</t>
+    <t xml:space="preserve">17.5796566009521</t>
   </si>
   <si>
     <t xml:space="preserve">17.5972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2888641357422</t>
+    <t xml:space="preserve">17.2888622283936</t>
   </si>
   <si>
     <t xml:space="preserve">17.0421295166016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7425289154053</t>
+    <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
     <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4957942962646</t>
+    <t xml:space="preserve">16.4957962036133</t>
   </si>
   <si>
     <t xml:space="preserve">16.3988647460938</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3900547027588</t>
+    <t xml:space="preserve">16.3900527954102</t>
   </si>
   <si>
     <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9935207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8613433837891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2402534484863</t>
+    <t xml:space="preserve">15.9935216903687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8613414764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2402515411377</t>
   </si>
   <si>
     <t xml:space="preserve">16.5134201049805</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3195610046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7732229232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176801681519</t>
+    <t xml:space="preserve">16.31955909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7732248306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176792144775</t>
   </si>
   <si>
     <t xml:space="preserve">15.411937713623</t>
@@ -3464,58 +3464,58 @@
     <t xml:space="preserve">15.3590669631958</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0330276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3150053024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0154047012329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2180767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1828289031982</t>
+    <t xml:space="preserve">15.0330295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3150072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0154056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2180776596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1828298568726</t>
   </si>
   <si>
     <t xml:space="preserve">15.0242137908936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123342514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1035213470459</t>
+    <t xml:space="preserve">15.1123332977295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1035232543945</t>
   </si>
   <si>
     <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1475830078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.085898399353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9801559448242</t>
+    <t xml:space="preserve">15.1475820541382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0858993530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9801568984985</t>
   </si>
   <si>
     <t xml:space="preserve">14.8215436935425</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6188697814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3985748291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0020418167114</t>
+    <t xml:space="preserve">14.6188716888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3985738754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0020399093628</t>
   </si>
   <si>
     <t xml:space="preserve">14.0725355148315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8434267044067</t>
+    <t xml:space="preserve">13.8434276580811</t>
   </si>
   <si>
     <t xml:space="preserve">13.8962984085083</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">14.3104553222656</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3457040786743</t>
+    <t xml:space="preserve">14.345703125</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491701126099</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483751296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4778804779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1870889663696</t>
+    <t xml:space="preserve">14.548376083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4778814315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1870899200439</t>
   </si>
   <si>
     <t xml:space="preserve">14.1254072189331</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">13.8169918060303</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6055068969727</t>
+    <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
     <t xml:space="preserve">13.7729320526123</t>
@@ -3566,16 +3566,16 @@
     <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1384792327881</t>
+    <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
     <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4028339385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1296663284302</t>
+    <t xml:space="preserve">13.4028329849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1296672821045</t>
   </si>
   <si>
     <t xml:space="preserve">12.9446172714233</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">13.3852100372314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6583776473999</t>
+    <t xml:space="preserve">13.6583786010742</t>
   </si>
   <si>
     <t xml:space="preserve">13.5350112915039</t>
@@ -3593,70 +3593,70 @@
     <t xml:space="preserve">13.5614471435547</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1913499832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2265968322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6231307983398</t>
+    <t xml:space="preserve">13.191349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2265958786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6231298446655</t>
   </si>
   <si>
     <t xml:space="preserve">13.314715385437</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2618455886841</t>
+    <t xml:space="preserve">13.2618446350098</t>
   </si>
   <si>
     <t xml:space="preserve">13.4557046890259</t>
   </si>
   <si>
-    <t xml:space="preserve">13.438081741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4645166397095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4997634887695</t>
+    <t xml:space="preserve">13.4380807876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4645175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4997644424438</t>
   </si>
   <si>
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878839492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.570258140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7112503051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4468927383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1649131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9710531234741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7948169708252</t>
+    <t xml:space="preserve">13.5878829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5702590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7112493515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4468936920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1649141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388757705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9710540771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7948160171509</t>
   </si>
   <si>
     <t xml:space="preserve">12.6978855133057</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6890735626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5128364562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568962097168</t>
+    <t xml:space="preserve">12.6890726089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5128355026245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568952560425</t>
   </si>
   <si>
     <t xml:space="preserve">12.6273908615112</t>
@@ -3674,64 +3674,64 @@
     <t xml:space="preserve">11.8078880310059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9048185348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8431358337402</t>
+    <t xml:space="preserve">11.9048194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8431348800659</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9841260910034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5347204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.464225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1117506027222</t>
+    <t xml:space="preserve">11.9841251373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5347194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4642248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1117515563965</t>
   </si>
   <si>
     <t xml:space="preserve">10.9090785980225</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2263050079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1293754577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0412569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.803337097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1910572052002</t>
+    <t xml:space="preserve">11.2263059616089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1293745040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209600448608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8033361434937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1910581588745</t>
   </si>
   <si>
     <t xml:space="preserve">11.3937311172485</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1822452545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7416524887085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9619493484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355134963989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6975936889648</t>
+    <t xml:space="preserve">11.1822462081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7416534423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.961950302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355144500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6975946426392</t>
   </si>
   <si>
     <t xml:space="preserve">11.0500688552856</t>
@@ -3740,16 +3740,16 @@
     <t xml:space="preserve">10.4772977828979</t>
   </si>
   <si>
-    <t xml:space="preserve">10.75927734375</t>
+    <t xml:space="preserve">10.7592763900757</t>
   </si>
   <si>
     <t xml:space="preserve">10.2393770217896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710250854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54324054718018</t>
+    <t xml:space="preserve">9.73710155487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54324150085449</t>
   </si>
   <si>
     <t xml:space="preserve">9.56967544555664</t>
@@ -3761,7 +3761,7 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868614196777</t>
+    <t xml:space="preserve">9.42868709564209</t>
   </si>
   <si>
     <t xml:space="preserve">9.61373519897461</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">8.64883708953857</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01453018188477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89116477966309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87353897094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25245094299316</t>
+    <t xml:space="preserve">9.01452922821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89116287231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87353992462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25244998931885</t>
   </si>
   <si>
     <t xml:space="preserve">9.04977703094482</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">8.68848991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.62680721282959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6135892868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2787389755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24349212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43735218048096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35363864898682</t>
+    <t xml:space="preserve">8.62680816650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61359024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27873992919922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24349117279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43735313415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
     <t xml:space="preserve">8.27433395385742</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245155334473</t>
+    <t xml:space="preserve">8.36245250701904</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3836,34 +3836,34 @@
     <t xml:space="preserve">8.42413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13334274291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08487796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01878929138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20824337005615</t>
+    <t xml:space="preserve">8.13334465026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08487892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01879024505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20824432373047</t>
   </si>
   <si>
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8866114616394</t>
+    <t xml:space="preserve">7.88661241531372</t>
   </si>
   <si>
     <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02760124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89542293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93067169189453</t>
+    <t xml:space="preserve">8.02760219573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89542388916016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93067073822021</t>
   </si>
   <si>
     <t xml:space="preserve">7.80730533599854</t>
@@ -3872,25 +3872,25 @@
     <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69275093078613</t>
+    <t xml:space="preserve">7.69275140762329</t>
   </si>
   <si>
     <t xml:space="preserve">7.66190958023071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78527593612671</t>
+    <t xml:space="preserve">7.78527545928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512655258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803880691528</t>
   </si>
   <si>
     <t xml:space="preserve">7.6751275062561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95803928375244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512702941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62036991119385</t>
+    <t xml:space="preserve">7.62036943435669</t>
   </si>
   <si>
     <t xml:space="preserve">8.03561115264893</t>
@@ -3899,13 +3899,13 @@
     <t xml:space="preserve">8.06299114227295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34133911132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08124160766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92609834671021</t>
+    <t xml:space="preserve">8.34134006500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08124256134033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92609786987305</t>
   </si>
   <si>
     <t xml:space="preserve">7.89871835708618</t>
@@ -3914,22 +3914,22 @@
     <t xml:space="preserve">7.6477484703064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67968988418579</t>
+    <t xml:space="preserve">7.8257098197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736089706421</t>
+    <t xml:space="preserve">7.54736042022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96784734725952</t>
+    <t xml:space="preserve">6.96784687042236</t>
   </si>
   <si>
     <t xml:space="preserve">6.88571119308472</t>
@@ -3938,19 +3938,19 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833263397217</t>
+    <t xml:space="preserve">6.85833311080933</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03629398345947</t>
+    <t xml:space="preserve">7.03629350662231</t>
   </si>
   <si>
     <t xml:space="preserve">6.98153686523438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76250791549683</t>
+    <t xml:space="preserve">6.76250743865967</t>
   </si>
   <si>
     <t xml:space="preserve">6.90396356582642</t>
@@ -3959,13 +3959,13 @@
     <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80357599258423</t>
+    <t xml:space="preserve">6.80357551574707</t>
   </si>
   <si>
     <t xml:space="preserve">6.69406127929688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46590662002563</t>
+    <t xml:space="preserve">6.46590614318848</t>
   </si>
   <si>
     <t xml:space="preserve">6.48872232437134</t>
@@ -3974,25 +3974,25 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212055206299</t>
+    <t xml:space="preserve">6.19212102890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50697469711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53891611099243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.55260562896729</t>
+    <t xml:space="preserve">6.50697422027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53891658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.55260515213013</t>
   </si>
   <si>
     <t xml:space="preserve">6.42940187454224</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2605676651001</t>
+    <t xml:space="preserve">6.26056718826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.1054220199585</t>
@@ -4001,16 +4001,16 @@
     <t xml:space="preserve">6.205810546875</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29250907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51153802871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46134328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474130630493</t>
+    <t xml:space="preserve">6.29250955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51153755187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46134376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474082946777</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454704284668</t>
@@ -4022,10 +4022,10 @@
     <t xml:space="preserve">6.49328517913818</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64843034744263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80813932418823</t>
+    <t xml:space="preserve">6.64843082427979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80813884735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4034,16 +4034,16 @@
     <t xml:space="preserve">6.83551740646362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.81726455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.40590381622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3602728843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17318630218506</t>
+    <t xml:space="preserve">6.81726503372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.40590476989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36027336120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17318677902222</t>
   </si>
   <si>
     <t xml:space="preserve">7.19143915176392</t>
@@ -4064,19 +4064,19 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231296539307</t>
+    <t xml:space="preserve">7.18231248855591</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13668203353882</t>
+    <t xml:space="preserve">7.13668155670166</t>
   </si>
   <si>
     <t xml:space="preserve">7.18687582015991</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5747389793396</t>
+    <t xml:space="preserve">7.57473945617676</t>
   </si>
   <si>
     <t xml:space="preserve">8.12687301635742</t>
@@ -4088,73 +4088,73 @@
     <t xml:space="preserve">8.21357250213623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90784454345703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81658267974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03104972839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89415502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49260330200195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.37396287918091</t>
+    <t xml:space="preserve">7.90784502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81658220291138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03104877471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89415550231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49260282516479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.37396240234375</t>
   </si>
   <si>
     <t xml:space="preserve">7.25532197952271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3465838432312</t>
+    <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
     <t xml:space="preserve">7.52910757064819</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59299087524414</t>
+    <t xml:space="preserve">7.5929913520813</t>
   </si>
   <si>
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415899276733</t>
+    <t xml:space="preserve">6.48415851593018</t>
   </si>
   <si>
     <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21037292480469</t>
+    <t xml:space="preserve">6.21037340164185</t>
   </si>
   <si>
     <t xml:space="preserve">6.27425670623779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05066537857056</t>
+    <t xml:space="preserve">6.0506649017334</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610157012939</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73581171035767</t>
+    <t xml:space="preserve">5.73581123352051</t>
   </si>
   <si>
     <t xml:space="preserve">5.9594030380249</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25144100189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37008142471313</t>
+    <t xml:space="preserve">6.25144147872925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37008190155029</t>
   </si>
   <si>
     <t xml:space="preserve">6.34270286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.392897605896</t>
+    <t xml:space="preserve">6.39289712905884</t>
   </si>
   <si>
     <t xml:space="preserve">6.28794574737549</t>
@@ -4163,13 +4163,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2788200378418</t>
+    <t xml:space="preserve">6.27881956100464</t>
   </si>
   <si>
     <t xml:space="preserve">6.32445049285889</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39745998382568</t>
+    <t xml:space="preserve">6.39746046066284</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4187,19 +4187,19 @@
     <t xml:space="preserve">6.51610040664673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65755701065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79901218414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09105062484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02716684341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84008026123047</t>
+    <t xml:space="preserve">6.65755653381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79901266098022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09105110168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02716732025146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84008073806763</t>
   </si>
   <si>
     <t xml:space="preserve">6.57542085647583</t>
@@ -4208,10 +4208,10 @@
     <t xml:space="preserve">6.68949842453003</t>
   </si>
   <si>
-    <t xml:space="preserve">6.83095455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94959497451782</t>
+    <t xml:space="preserve">6.83095407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94959449768066</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4226,10 +4226,10 @@
     <t xml:space="preserve">7.93978595733643</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17706775665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12230968475342</t>
+    <t xml:space="preserve">8.17706680297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12231063842773</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
@@ -4238,34 +4238,34 @@
     <t xml:space="preserve">7.69794321060181</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76638889312744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7298846244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6660008430481</t>
+    <t xml:space="preserve">7.76638841629028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72988367080688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
     <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71163177490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91697072982788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86677694320679</t>
+    <t xml:space="preserve">7.7116322517395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91697120666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86677742004395</t>
   </si>
   <si>
     <t xml:space="preserve">7.72075796127319</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5701756477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62949514389038</t>
+    <t xml:space="preserve">7.57017612457275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62949562072754</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
@@ -4274,67 +4274,67 @@
     <t xml:space="preserve">7.5519232749939</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31464290618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28270101547241</t>
+    <t xml:space="preserve">7.31464242935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28270053863525</t>
   </si>
   <si>
     <t xml:space="preserve">7.1777491569519</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04998254776001</t>
+    <t xml:space="preserve">7.04998302459717</t>
   </si>
   <si>
     <t xml:space="preserve">7.35571050643921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27813768386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5199818611145</t>
+    <t xml:space="preserve">7.27813816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
     <t xml:space="preserve">7.45609855651855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46978759765625</t>
+    <t xml:space="preserve">7.46978807449341</t>
   </si>
   <si>
     <t xml:space="preserve">7.59755420684814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79376792907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88959360122681</t>
+    <t xml:space="preserve">7.79376745223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88959312438965</t>
   </si>
   <si>
     <t xml:space="preserve">8.38696956634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34590339660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36871814727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81589984893799</t>
+    <t xml:space="preserve">8.34590244293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36871719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.9436674118042</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68813514709473</t>
+    <t xml:space="preserve">8.68813419342041</t>
   </si>
   <si>
     <t xml:space="preserve">8.66531848907471</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82959079742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80677509307861</t>
+    <t xml:space="preserve">8.82958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
     <t xml:space="preserve">8.9801721572876</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">8.62425136566162</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8432788848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89347457885742</t>
+    <t xml:space="preserve">8.84327983856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89347362518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.77939605712891</t>
@@ -4355,13 +4355,13 @@
     <t xml:space="preserve">8.7292013168335</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71094989776611</t>
+    <t xml:space="preserve">8.7109489440918</t>
   </si>
   <si>
     <t xml:space="preserve">8.72463893890381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51473712921143</t>
+    <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
     <t xml:space="preserve">8.41891193389893</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21813583374023</t>
+    <t xml:space="preserve">8.21813488006592</t>
   </si>
   <si>
     <t xml:space="preserve">8.25007724761963</t>
@@ -4391,31 +4391,31 @@
     <t xml:space="preserve">8.00367069244385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99910688400269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83483552932739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085519790649</t>
+    <t xml:space="preserve">7.99910640716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83483505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68881607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085567474365</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05386447906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97172784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9215350151062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04017543792725</t>
+    <t xml:space="preserve">8.05386352539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97172832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92153406143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
     <t xml:space="preserve">8.09493160247803</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">8.15425205230713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716499328613</t>
+    <t xml:space="preserve">7.96716547012329</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96328401565552</t>
+    <t xml:space="preserve">6.96328449249268</t>
   </si>
   <si>
     <t xml:space="preserve">7.3283314704895</t>
@@ -4442,16 +4442,16 @@
     <t xml:space="preserve">7.21425437927246</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35114765167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24163246154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11842966079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01804161071777</t>
+    <t xml:space="preserve">7.35114717483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24163293838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11842918395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745929718018</t>
+    <t xml:space="preserve">6.86745882034302</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211870193481</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78076028823853</t>
+    <t xml:space="preserve">6.78075981140137</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4481,10 +4481,10 @@
     <t xml:space="preserve">6.74881887435913</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73512935638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90852737426758</t>
+    <t xml:space="preserve">6.73512983322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90852689743042</t>
   </si>
   <si>
     <t xml:space="preserve">6.76707124710083</t>
@@ -4493,16 +4493,16 @@
     <t xml:space="preserve">6.62561511993408</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62105226516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43852758407593</t>
+    <t xml:space="preserve">6.62105178833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43852853775024</t>
   </si>
   <si>
     <t xml:space="preserve">6.28338289260864</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30619859695435</t>
+    <t xml:space="preserve">6.30619812011719</t>
   </si>
   <si>
     <t xml:space="preserve">6.42027568817139</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">6.52036905288696</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50606966018677</t>
+    <t xml:space="preserve">6.50607013702393</t>
   </si>
   <si>
     <t xml:space="preserve">6.64429378509521</t>
@@ -4538,28 +4538,28 @@
     <t xml:space="preserve">6.62046241760254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.677659034729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66812562942505</t>
+    <t xml:space="preserve">6.67765855789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66812610626221</t>
   </si>
   <si>
     <t xml:space="preserve">6.73008823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92550849914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86354637145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84924697875977</t>
+    <t xml:space="preserve">6.92550897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8635458946228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84924745559692</t>
   </si>
   <si>
     <t xml:space="preserve">6.74915361404419</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6156964302063</t>
+    <t xml:space="preserve">6.61569595336914</t>
   </si>
   <si>
     <t xml:space="preserve">6.5299015045166</t>
@@ -4574,19 +4574,19 @@
     <t xml:space="preserve">6.49653720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44887351989746</t>
+    <t xml:space="preserve">6.44887399673462</t>
   </si>
   <si>
     <t xml:space="preserve">6.43457460403442</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57279872894287</t>
+    <t xml:space="preserve">6.57279920578003</t>
   </si>
   <si>
     <t xml:space="preserve">6.35354661941528</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31541585922241</t>
+    <t xml:space="preserve">6.31541538238525</t>
   </si>
   <si>
     <t xml:space="preserve">6.37737846374512</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">6.40597629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38214492797852</t>
+    <t xml:space="preserve">6.38214445114136</t>
   </si>
   <si>
     <t xml:space="preserve">6.48223829269409</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">6.36784553527832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23915433883667</t>
+    <t xml:space="preserve">6.23915386199951</t>
   </si>
   <si>
     <t xml:space="preserve">6.33448123931885</t>
@@ -4640,22 +4640,22 @@
     <t xml:space="preserve">5.64812660217285</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60999631881714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74822044372559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7863507270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88167762756348</t>
+    <t xml:space="preserve">5.60999584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74821996688843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78635120391846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88167810440063</t>
   </si>
   <si>
     <t xml:space="preserve">5.94364023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05803298950195</t>
+    <t xml:space="preserve">6.05803251266479</t>
   </si>
   <si>
     <t xml:space="preserve">5.95317316055298</t>
@@ -4664,13 +4664,13 @@
     <t xml:space="preserve">5.91504240036011</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83878087997437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83401393890381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89597654342651</t>
+    <t xml:space="preserve">5.83878040313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83401441574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89597702026367</t>
   </si>
   <si>
     <t xml:space="preserve">5.80064964294434</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">5.81494903564453</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98653745651245</t>
+    <t xml:space="preserve">5.98653793334961</t>
   </si>
   <si>
     <t xml:space="preserve">6.1295280456543</t>
@@ -4688,13 +4688,13 @@
     <t xml:space="preserve">6.07233190536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26298570632935</t>
+    <t xml:space="preserve">6.2629861831665</t>
   </si>
   <si>
     <t xml:space="preserve">6.22962141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27728509902954</t>
+    <t xml:space="preserve">6.27728462219238</t>
   </si>
   <si>
     <t xml:space="preserve">6.33924770355225</t>
@@ -4715,10 +4715,10 @@
     <t xml:space="preserve">5.82448196411133</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7148551940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70532321929932</t>
+    <t xml:space="preserve">5.71485567092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70532274246216</t>
   </si>
   <si>
     <t xml:space="preserve">5.73392105102539</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">5.55756568908691</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63859367370605</t>
+    <t xml:space="preserve">5.63859415054321</t>
   </si>
   <si>
     <t xml:space="preserve">5.848313331604</t>
@@ -4745,16 +4745,16 @@
     <t xml:space="preserve">5.7100887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68625783920288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7720513343811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61476230621338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78158473968506</t>
+    <t xml:space="preserve">5.68625736236572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77205181121826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61476182937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7815842628479</t>
   </si>
   <si>
     <t xml:space="preserve">5.52420139312744</t>
@@ -4766,10 +4766,10 @@
     <t xml:space="preserve">5.37167835235596</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42887496948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.29541635513306</t>
+    <t xml:space="preserve">5.42887449264526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.29541683197021</t>
   </si>
   <si>
     <t xml:space="preserve">5.28588390350342</t>
@@ -4781,16 +4781,16 @@
     <t xml:space="preserve">5.19055700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18102407455444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00943565368652</t>
+    <t xml:space="preserve">5.1810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00943517684937</t>
   </si>
   <si>
     <t xml:space="preserve">5.07616424560547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.13812732696533</t>
+    <t xml:space="preserve">5.13812685012817</t>
   </si>
   <si>
     <t xml:space="preserve">5.20962238311768</t>
@@ -4805,19 +4805,19 @@
     <t xml:space="preserve">5.47653818130493</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64336061477661</t>
+    <t xml:space="preserve">5.64336013793945</t>
   </si>
   <si>
     <t xml:space="preserve">5.57663106918335</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71962213516235</t>
+    <t xml:space="preserve">5.7196216583252</t>
   </si>
   <si>
     <t xml:space="preserve">5.05233287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">5.40027618408203</t>
+    <t xml:space="preserve">5.40027666091919</t>
   </si>
   <si>
     <t xml:space="preserve">5.19532299041748</t>
@@ -4832,13 +4832,13 @@
     <t xml:space="preserve">5.24775314331055</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59569692611694</t>
+    <t xml:space="preserve">5.59569644927979</t>
   </si>
   <si>
     <t xml:space="preserve">5.74345350265503</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75775241851807</t>
+    <t xml:space="preserve">5.75775289535522</t>
   </si>
   <si>
     <t xml:space="preserve">5.81018257141113</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">5.97700500488281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10569667816162</t>
+    <t xml:space="preserve">6.10569620132446</t>
   </si>
   <si>
     <t xml:space="preserve">6.00083637237549</t>
@@ -4856,7 +4856,7 @@
     <t xml:space="preserve">6.09139728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14382743835449</t>
+    <t xml:space="preserve">6.14382696151733</t>
   </si>
   <si>
     <t xml:space="preserve">6.08186483383179</t>
@@ -4868,61 +4868,61 @@
     <t xml:space="preserve">6.24392080307007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24868631362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29635047912598</t>
+    <t xml:space="preserve">6.24868679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29635000228882</t>
   </si>
   <si>
     <t xml:space="preserve">6.28205156326294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41074275970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4679388999939</t>
+    <t xml:space="preserve">6.41074323654175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46793937683105</t>
   </si>
   <si>
     <t xml:space="preserve">6.02943468093872</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03896760940552</t>
+    <t xml:space="preserve">6.03896713256836</t>
   </si>
   <si>
     <t xml:space="preserve">6.13906097412109</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98177146911621</t>
+    <t xml:space="preserve">5.98177099227905</t>
   </si>
   <si>
     <t xml:space="preserve">5.90074348449707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85307931900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88644456863403</t>
+    <t xml:space="preserve">5.8530797958374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88644409179688</t>
   </si>
   <si>
     <t xml:space="preserve">5.7958836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03420066833496</t>
+    <t xml:space="preserve">6.03420114517212</t>
   </si>
   <si>
     <t xml:space="preserve">5.86737871170044</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80541610717773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79111671447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76728582382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7768177986145</t>
+    <t xml:space="preserve">5.80541658401489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7911171913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76728534698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77681827545166</t>
   </si>
   <si>
     <t xml:space="preserve">5.70055627822876</t>
@@ -4934,28 +4934,28 @@
     <t xml:space="preserve">5.54803323745728</t>
   </si>
   <si>
-    <t xml:space="preserve">5.53850078582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61952829360962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57186460494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69578981399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73868751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5194354057312</t>
+    <t xml:space="preserve">5.53850030899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61952877044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57186508178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69579029083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73868703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.51943492889404</t>
   </si>
   <si>
     <t xml:space="preserve">5.4336404800415</t>
   </si>
   <si>
-    <t xml:space="preserve">5.49560308456421</t>
+    <t xml:space="preserve">5.49560356140137</t>
   </si>
   <si>
     <t xml:space="preserve">5.53373432159424</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">4.96653842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91410875320435</t>
+    <t xml:space="preserve">4.91410827636719</t>
   </si>
   <si>
     <t xml:space="preserve">4.84261322021484</t>
@@ -4979,22 +4979,22 @@
     <t xml:space="preserve">5.0952296257019</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33354711532593</t>
+    <t xml:space="preserve">5.33354759216309</t>
   </si>
   <si>
     <t xml:space="preserve">5.47177124023438</t>
   </si>
   <si>
-    <t xml:space="preserve">5.36691236495972</t>
+    <t xml:space="preserve">5.36691188812256</t>
   </si>
   <si>
     <t xml:space="preserve">5.65289258956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67195844650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41457557678223</t>
+    <t xml:space="preserve">5.67195796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41457509994507</t>
   </si>
   <si>
     <t xml:space="preserve">5.3764443397522</t>
@@ -5018,7 +5018,7 @@
     <t xml:space="preserve">5.20485591888428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21438884735107</t>
+    <t xml:space="preserve">5.21438837051392</t>
   </si>
   <si>
     <t xml:space="preserve">5.15719223022461</t>
@@ -5030,7 +5030,7 @@
     <t xml:space="preserve">5.42410802841187</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44317388534546</t>
+    <t xml:space="preserve">5.4431734085083</t>
   </si>
   <si>
     <t xml:space="preserve">5.31924819946289</t>
@@ -5045,16 +5045,16 @@
     <t xml:space="preserve">5.96747255325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.56709909439087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91027545928955</t>
+    <t xml:space="preserve">5.56709861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91027593612671</t>
   </si>
   <si>
     <t xml:space="preserve">5.89121055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86261224746704</t>
+    <t xml:space="preserve">5.8626127243042</t>
   </si>
   <si>
     <t xml:space="preserve">5.66242551803589</t>
@@ -73059,7 +73059,7 @@
     </row>
     <row r="2574">
       <c r="A2574" s="1" t="n">
-        <v>46070.6912152778</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2574" t="n">
         <v>55841</v>
@@ -73080,6 +73080,32 @@
         <v>1914</v>
       </c>
       <c r="H2574" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2575">
+      <c r="A2575" s="1" t="n">
+        <v>46071.6910185185</v>
+      </c>
+      <c r="B2575" t="n">
+        <v>44126</v>
+      </c>
+      <c r="C2575" t="n">
+        <v>4.3600001335144</v>
+      </c>
+      <c r="D2575" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="E2575" t="n">
+        <v>4.28999996185303</v>
+      </c>
+      <c r="F2575" t="n">
+        <v>4.33500003814697</v>
+      </c>
+      <c r="G2575" t="s">
+        <v>1913</v>
+      </c>
+      <c r="H2575" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767133712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758996963501</t>
+    <t xml:space="preserve">12.7846279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767143249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758987426758</t>
   </si>
   <si>
     <t xml:space="preserve">11.9930105209351</t>
@@ -71,10 +71,10 @@
     <t xml:space="preserve">12.5075635910034</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4125709533691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6738014221191</t>
+    <t xml:space="preserve">12.4125690460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6738033294678</t>
   </si>
   <si>
     <t xml:space="preserve">12.0563411712646</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">12.1750841140747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3413228988647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713575363159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6367835998535</t>
+    <t xml:space="preserve">12.3413238525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713584899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6367826461792</t>
   </si>
   <si>
     <t xml:space="preserve">11.9850959777832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1380643844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955730438232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4626274108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1063985824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4942932128906</t>
+    <t xml:space="preserve">11.1380634307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955720901489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.462628364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1063995361328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.494291305542</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417881011963</t>
@@ -122,37 +122,37 @@
     <t xml:space="preserve">11.3597173690796</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8584365844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5180416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159461975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346872329712</t>
+    <t xml:space="preserve">11.8584356307983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5180406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346862792969</t>
   </si>
   <si>
     <t xml:space="preserve">11.6763639450073</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6684474945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3992977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1855611801147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9692640304565</t>
+    <t xml:space="preserve">11.6684484481812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3992986679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1855621337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9692630767822</t>
   </si>
   <si>
     <t xml:space="preserve">12.3888206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284000396729</t>
+    <t xml:space="preserve">12.4284009933472</t>
   </si>
   <si>
     <t xml:space="preserve">12.2304964065552</t>
@@ -161,106 +161,106 @@
     <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1513357162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196718215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242092132568</t>
+    <t xml:space="preserve">12.1513347625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196699142456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242111206055</t>
   </si>
   <si>
     <t xml:space="preserve">12.982533454895</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9508695602417</t>
+    <t xml:space="preserve">12.9508714675903</t>
   </si>
   <si>
     <t xml:space="preserve">13.1408567428589</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2754335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.576247215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999975204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3625106811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0379467010498</t>
+    <t xml:space="preserve">13.2754344940186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704290390015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387603759766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575052261353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762481689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999946594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.362509727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0379457473755</t>
   </si>
   <si>
     <t xml:space="preserve">12.752965927124</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1171083450317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091909408569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1962690353394</t>
+    <t xml:space="preserve">13.1171102523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091928482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
     <t xml:space="preserve">12.9904508590698</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0221166610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0933628082275</t>
+    <t xml:space="preserve">13.0221157073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0933609008789</t>
   </si>
   <si>
     <t xml:space="preserve">13.0775279998779</t>
   </si>
   <si>
-    <t xml:space="preserve">13.030029296875</t>
+    <t xml:space="preserve">13.0300302505493</t>
   </si>
   <si>
     <t xml:space="preserve">12.6975526809692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6025581359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6500549316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8637914657593</t>
+    <t xml:space="preserve">12.6025562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6500539779663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8637895584106</t>
   </si>
   <si>
     <t xml:space="preserve">12.5867252349854</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4679822921753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650712966919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5788097381592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7286958694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1493873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091585159302</t>
+    <t xml:space="preserve">12.4679832458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650722503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5788087844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7286968231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091575622559</t>
   </si>
   <si>
     <t xml:space="preserve">11.988468170166</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">12.2298469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2942161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2620306015015</t>
+    <t xml:space="preserve">12.2942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2620325088501</t>
   </si>
   <si>
     <t xml:space="preserve">12.2861700057983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4953641891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7126045227051</t>
+    <t xml:space="preserve">12.4953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7126054763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.8091564178467</t>
@@ -296,103 +296,103 @@
     <t xml:space="preserve">12.8735237121582</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0263977050781</t>
+    <t xml:space="preserve">13.0263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654794692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8172016143799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5999612808228</t>
+    <t xml:space="preserve">12.8654766082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8172025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5999622344971</t>
   </si>
   <si>
     <t xml:space="preserve">12.3666286468506</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3103084564209</t>
+    <t xml:space="preserve">12.3103075027466</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390460968018</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4011154174805</t>
+    <t xml:space="preserve">11.4011144638062</t>
   </si>
   <si>
     <t xml:space="preserve">11.2884712219238</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8781270980835</t>
+    <t xml:space="preserve">10.8781280517578</t>
   </si>
   <si>
     <t xml:space="preserve">11.0792770385742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6022624969482</t>
+    <t xml:space="preserve">11.6022634506226</t>
   </si>
   <si>
     <t xml:space="preserve">12.0689287185669</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6103096008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3689308166504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4896173477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.757438659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4597368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6344470977783</t>
+    <t xml:space="preserve">11.6103105545044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3689317703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4896202087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7574396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735330581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229558944702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424932479858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6344480514526</t>
   </si>
   <si>
     <t xml:space="preserve">11.2321491241455</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9827241897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264030456543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160568237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229528427124</t>
+    <t xml:space="preserve">10.9827251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264039993286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229509353638</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700788497925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.891918182373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5861711502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8758268356323</t>
+    <t xml:space="preserve">11.5700807571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8919172286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5861721038818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.875825881958</t>
   </si>
   <si>
     <t xml:space="preserve">11.7953662872314</t>
@@ -404,67 +404,67 @@
     <t xml:space="preserve">12.4309968948364</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8896179199219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0505352020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.994213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1229467391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746736526489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482332229614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2493810653687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9194965362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3459358215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8551292419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6919097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7643222808838</t>
+    <t xml:space="preserve">12.8896150588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0505332946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9942121505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1229486465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1551332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861679077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.074670791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482341766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2493801116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9194955825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3459339141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551301956177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608781814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6919116973877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7643241882324</t>
   </si>
   <si>
     <t xml:space="preserve">14.6275405883789</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8206453323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6034069061279</t>
+    <t xml:space="preserve">14.8206443786621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034030914307</t>
   </si>
   <si>
     <t xml:space="preserve">14.4022550582886</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3137483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516790390015</t>
+    <t xml:space="preserve">14.3137502670288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516780853271</t>
   </si>
   <si>
     <t xml:space="preserve">14.7562770843506</t>
@@ -473,289 +473,289 @@
     <t xml:space="preserve">15.1183443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1505298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1263904571533</t>
+    <t xml:space="preserve">15.1505270004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1263914108276</t>
   </si>
   <si>
     <t xml:space="preserve">15.0861616134644</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0459337234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.295355796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4240922927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4562730789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3597240447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873086929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689212799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240934371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7884607315063</t>
+    <t xml:space="preserve">15.0459299087524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2953538894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4240913391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4562749862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3597230911255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873096466064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240896224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367366790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884616851807</t>
   </si>
   <si>
     <t xml:space="preserve">14.8930606842041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4884586334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4401817321777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2148971557617</t>
+    <t xml:space="preserve">15.4884576797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4401836395264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2148962020874</t>
   </si>
   <si>
     <t xml:space="preserve">14.8045520782471</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3919076919556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2551250457764</t>
+    <t xml:space="preserve">15.3919038772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2551240921021</t>
   </si>
   <si>
     <t xml:space="preserve">15.1666212081909</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5286893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229442596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0137462615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1988048553467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275384902954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3114471435547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677701950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034019470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6436357498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9654703140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286924362183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5390357971191</t>
+    <t xml:space="preserve">15.5286874771118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229423522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.013747215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850135803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.198805809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114490509033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034038543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6436338424683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9654712677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.828688621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5390367507935</t>
   </si>
   <si>
     <t xml:space="preserve">14.5551280975342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1126003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263944625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.281566619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171983718872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4103012084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5631732940674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585752487183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057060241699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.321795463562</t>
+    <t xml:space="preserve">14.1126022338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827146530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171993255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4103002548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.563175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585762023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3057022094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045551300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217973709106</t>
   </si>
   <si>
     <t xml:space="preserve">13.9516820907593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6781187057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4045581817627</t>
+    <t xml:space="preserve">13.6781196594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4045572280884</t>
   </si>
   <si>
     <t xml:space="preserve">13.3643283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1873140335083</t>
+    <t xml:space="preserve">13.1873149871826</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539833068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.31605052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5896129608154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7746715545654</t>
+    <t xml:space="preserve">13.3160514831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5896158218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7746725082397</t>
   </si>
   <si>
     <t xml:space="preserve">13.9114532470703</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2011041641235</t>
+    <t xml:space="preserve">14.2011032104492</t>
   </si>
   <si>
     <t xml:space="preserve">13.9999580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9815635681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0378847122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160472869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.844783782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9171953201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2631721496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6011037826538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.552827835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.536732673645</t>
+    <t xml:space="preserve">14.9815654754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0378866195679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447818756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9171981811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2631740570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6010999679565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5528259277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5367374420166</t>
   </si>
   <si>
     <t xml:space="preserve">15.4643211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">15.383861541748</t>
+    <t xml:space="preserve">15.3838624954224</t>
   </si>
   <si>
     <t xml:space="preserve">15.6091470718384</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5045499801636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4079971313477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.110297203064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068510055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263893127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8907566070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8988037109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.947078704834</t>
+    <t xml:space="preserve">15.5045509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4079999923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1102991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263883590698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907556533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8988027572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9470767974854</t>
   </si>
   <si>
     <t xml:space="preserve">16.0114459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493728637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.301097869873</t>
+    <t xml:space="preserve">16.3493766784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3010997772217</t>
   </si>
   <si>
     <t xml:space="preserve">16.5344314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5827102661133</t>
+    <t xml:space="preserve">16.5827083587646</t>
   </si>
   <si>
     <t xml:space="preserve">16.3332843780518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.453971862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.17236328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.156270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9792613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700672149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919075012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
+    <t xml:space="preserve">16.4539737701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1723670959473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1562728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9792642593384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.003396987915</t>
   </si>
   <si>
     <t xml:space="preserve">16.043628692627</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4781112670898</t>
+    <t xml:space="preserve">16.4781093597412</t>
   </si>
   <si>
     <t xml:space="preserve">16.8964996337891</t>
@@ -764,85 +764,85 @@
     <t xml:space="preserve">16.9769592285156</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0413284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5160388946533</t>
+    <t xml:space="preserve">17.0413265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.516040802002</t>
   </si>
   <si>
     <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850002288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7470703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7229328155518</t>
+    <t xml:space="preserve">18.3850040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7470684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7229309082031</t>
   </si>
   <si>
     <t xml:space="preserve">19.0206317901611</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2700576782227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3907470703125</t>
+    <t xml:space="preserve">19.270055770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3907451629639</t>
   </si>
   <si>
     <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4470691680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7528114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5033893585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125835418701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3827018737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5838470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3102855682373</t>
+    <t xml:space="preserve">19.4470672607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7528133392334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5033874511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125854492188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3826999664307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5838489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3102874755859</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4631614685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0689086914062</t>
+    <t xml:space="preserve">19.4631595611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0689067840576</t>
   </si>
   <si>
     <t xml:space="preserve">19.0769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8355751037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.028678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9723567962646</t>
+    <t xml:space="preserve">18.8355731964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.972354888916</t>
   </si>
   <si>
     <t xml:space="preserve">18.56201171875</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">18.5056896209717</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6183319091797</t>
+    <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
     <t xml:space="preserve">19.1654605865479</t>
@@ -860,25 +860,25 @@
     <t xml:space="preserve">19.8171806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2597103118896</t>
+    <t xml:space="preserve">20.259708404541</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585563659668</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5574073791504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9539337158203</t>
+    <t xml:space="preserve">20.557409286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9539318084717</t>
   </si>
   <si>
     <t xml:space="preserve">21.1818675994873</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9213695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0841827392578</t>
+    <t xml:space="preserve">20.9213714599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0841789245605</t>
   </si>
   <si>
     <t xml:space="preserve">20.7666988372803</t>
@@ -890,55 +890,55 @@
     <t xml:space="preserve">21.5726203918457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.538761138916</t>
+    <t xml:space="preserve">20.5387592315674</t>
   </si>
   <si>
     <t xml:space="preserve">20.5550422668457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922271728516</t>
+    <t xml:space="preserve">20.4899196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922309875488</t>
   </si>
   <si>
     <t xml:space="preserve">20.3271045684814</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3515281677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5143413543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9864940643311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9946346282959</t>
+    <t xml:space="preserve">20.351526260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5143394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9864959716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9946384429932</t>
   </si>
   <si>
     <t xml:space="preserve">20.937650680542</t>
   </si>
   <si>
-    <t xml:space="preserve">21.124885559082</t>
+    <t xml:space="preserve">21.1248874664307</t>
   </si>
   <si>
     <t xml:space="preserve">21.0353393554688</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8399639129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8155384063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1574440002441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2945442199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5957431793213</t>
+    <t xml:space="preserve">20.8399620056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8155422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1574459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2945423126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5957469940186</t>
   </si>
   <si>
     <t xml:space="preserve">20.3189640045166</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">20.0828857421875</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1480121612549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.985200881958</t>
+    <t xml:space="preserve">20.1480102539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9851989746094</t>
   </si>
   <si>
     <t xml:space="preserve">20.1317291259766</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3678073883057</t>
+    <t xml:space="preserve">20.3678112030029</t>
   </si>
   <si>
     <t xml:space="preserve">20.7259941101074</t>
@@ -968,31 +968,31 @@
     <t xml:space="preserve">20.3108234405518</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9770603179932</t>
+    <t xml:space="preserve">19.9770584106445</t>
   </si>
   <si>
     <t xml:space="preserve">19.3583736419678</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1874198913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9757633209229</t>
+    <t xml:space="preserve">19.1874179840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9757614135742</t>
   </si>
   <si>
     <t xml:space="preserve">18.8048133850098</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7071228027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0978736877441</t>
+    <t xml:space="preserve">18.7071266174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0978698730469</t>
   </si>
   <si>
     <t xml:space="preserve">18.6338577270508</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1304321289062</t>
+    <t xml:space="preserve">19.1304359436035</t>
   </si>
   <si>
     <t xml:space="preserve">19.4804821014404</t>
@@ -1004,13 +1004,13 @@
     <t xml:space="preserve">20.2049942016602</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7816848754883</t>
+    <t xml:space="preserve">19.7816829681396</t>
   </si>
   <si>
     <t xml:space="preserve">20.1805763244629</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2375621795654</t>
+    <t xml:space="preserve">20.2375583648682</t>
   </si>
   <si>
     <t xml:space="preserve">20.78297996521</t>
@@ -1022,31 +1022,31 @@
     <t xml:space="preserve">20.9050884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">20.677152633667</t>
+    <t xml:space="preserve">20.6771507263184</t>
   </si>
   <si>
     <t xml:space="preserve">21.1655864715576</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2795543670654</t>
+    <t xml:space="preserve">21.2795562744141</t>
   </si>
   <si>
     <t xml:space="preserve">21.0597610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">21.043478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6852951049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1004600524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4260902404785</t>
+    <t xml:space="preserve">21.0434799194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1004657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400562286377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4260883331299</t>
   </si>
   <si>
     <t xml:space="preserve">21.5319156646729</t>
@@ -1055,7 +1055,7 @@
     <t xml:space="preserve">21.3202629089355</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9226665496826</t>
+    <t xml:space="preserve">21.9226627349854</t>
   </si>
   <si>
     <t xml:space="preserve">21.7842750549316</t>
@@ -1067,55 +1067,55 @@
     <t xml:space="preserve">21.3935241699219</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7761325836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6214637756348</t>
+    <t xml:space="preserve">21.7761363983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6214599609375</t>
   </si>
   <si>
     <t xml:space="preserve">22.0691986083984</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169277191162</t>
+    <t xml:space="preserve">21.7110061645508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169296264648</t>
   </si>
   <si>
     <t xml:space="preserve">22.9809436798096</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6308975219727</t>
+    <t xml:space="preserve">22.6308994293213</t>
   </si>
   <si>
     <t xml:space="preserve">23.0542106628418</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9890842437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.2007427215576</t>
+    <t xml:space="preserve">22.9890823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.200740814209</t>
   </si>
   <si>
     <t xml:space="preserve">23.168176651001</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4693813323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8601303100586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7298831939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0310821533203</t>
+    <t xml:space="preserve">23.4693794250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601322174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7298793792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0310840606689</t>
   </si>
   <si>
     <t xml:space="preserve">23.9659595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0229434967041</t>
+    <t xml:space="preserve">24.0229415893555</t>
   </si>
   <si>
     <t xml:space="preserve">24.3648490905762</t>
@@ -1124,31 +1124,31 @@
     <t xml:space="preserve">23.9008350372314</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9903793334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263633728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.615909576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9822368621826</t>
+    <t xml:space="preserve">23.9903812408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996284484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159114837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9822387695312</t>
   </si>
   <si>
     <t xml:space="preserve">24.2346000671387</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4394111633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.991678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0567989349365</t>
+    <t xml:space="preserve">25.4394092559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9916744232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0568008422852</t>
   </si>
   <si>
     <t xml:space="preserve">25.0079555511475</t>
@@ -1157,28 +1157,28 @@
     <t xml:space="preserve">24.87770652771</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8288631439209</t>
+    <t xml:space="preserve">24.8288612365723</t>
   </si>
   <si>
     <t xml:space="preserve">24.6660480499268</t>
   </si>
   <si>
-    <t xml:space="preserve">24.6497688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.6999092102051</t>
+    <t xml:space="preserve">24.6497707366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6999111175537</t>
   </si>
   <si>
     <t xml:space="preserve">25.9604072570801</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4801139831543</t>
+    <t xml:space="preserve">25.4801120758057</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789112091064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1613311767578</t>
+    <t xml:space="preserve">24.1613330841064</t>
   </si>
   <si>
     <t xml:space="preserve">24.5602226257324</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">24.7474555969238</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5765056610107</t>
+    <t xml:space="preserve">24.5765037536621</t>
   </si>
   <si>
     <t xml:space="preserve">25.4556903839111</t>
@@ -1199,79 +1199,79 @@
     <t xml:space="preserve">25.9848308563232</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1082324981689</t>
+    <t xml:space="preserve">27.1082305908203</t>
   </si>
   <si>
     <t xml:space="preserve">27.7676239013672</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3850154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9209976196289</t>
+    <t xml:space="preserve">27.3850173950195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9210014343262</t>
   </si>
   <si>
     <t xml:space="preserve">27.5071258544922</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0105476379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6930637359619</t>
+    <t xml:space="preserve">27.0105438232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6930618286133</t>
   </si>
   <si>
     <t xml:space="preserve">25.2765960693359</t>
   </si>
   <si>
-    <t xml:space="preserve">24.910270690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5032405853271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.617208480835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5846462249756</t>
+    <t xml:space="preserve">24.9102687835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5032367706299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6172065734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.584644317627</t>
   </si>
   <si>
     <t xml:space="preserve">25.2440357208252</t>
   </si>
   <si>
-    <t xml:space="preserve">24.8451442718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7393169403076</t>
+    <t xml:space="preserve">24.8451461791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7393188476562</t>
   </si>
   <si>
     <t xml:space="preserve">25.1951923370361</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6429233551025</t>
+    <t xml:space="preserve">25.6429252624512</t>
   </si>
   <si>
     <t xml:space="preserve">25.5859394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">25.724328994751</t>
+    <t xml:space="preserve">25.7243309020996</t>
   </si>
   <si>
     <t xml:space="preserve">25.6917686462402</t>
   </si>
   <si>
-    <t xml:space="preserve">25.545238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7568912506104</t>
+    <t xml:space="preserve">25.5452365875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.756893157959</t>
   </si>
   <si>
     <t xml:space="preserve">25.5208168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3172988891602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3987045288086</t>
+    <t xml:space="preserve">25.3173007965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3987064361572</t>
   </si>
   <si>
     <t xml:space="preserve">25.512674331665</t>
@@ -1283,37 +1283,37 @@
     <t xml:space="preserve">26.0499534606934</t>
   </si>
   <si>
-    <t xml:space="preserve">25.203332901001</t>
+    <t xml:space="preserve">25.2033309936523</t>
   </si>
   <si>
     <t xml:space="preserve">25.0486583709717</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4625377655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661422729492</t>
+    <t xml:space="preserve">24.4625339508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661441802979</t>
   </si>
   <si>
     <t xml:space="preserve">25.0242366790771</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3824234008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
+    <t xml:space="preserve">25.3824253082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893611907959</t>
   </si>
   <si>
     <t xml:space="preserve">24.7148952484131</t>
   </si>
   <si>
-    <t xml:space="preserve">25.6836242675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7419052124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5790939331055</t>
+    <t xml:space="preserve">25.6836261749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7419033050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5790958404541</t>
   </si>
   <si>
     <t xml:space="preserve">27.3931560516357</t>
@@ -1322,40 +1322,40 @@
     <t xml:space="preserve">26.6604995727539</t>
   </si>
   <si>
-    <t xml:space="preserve">26.4976863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313552856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.602222442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2127685546875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2941722869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.7826118469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.3117523193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.881591796875</t>
+    <t xml:space="preserve">26.497688293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313571929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.6022205352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2127666473389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2941703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.7826099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.31174659729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.8815956115723</t>
   </si>
   <si>
     <t xml:space="preserve">27.2303428649902</t>
   </si>
   <si>
-    <t xml:space="preserve">26.8233165740967</t>
+    <t xml:space="preserve">26.8233127593994</t>
   </si>
   <si>
     <t xml:space="preserve">26.6197986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.172061920166</t>
+    <t xml:space="preserve">26.1720638275146</t>
   </si>
   <si>
     <t xml:space="preserve">25.0730819702148</t>
@@ -1364,58 +1364,58 @@
     <t xml:space="preserve">24.6253471374512</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8519878387451</t>
+    <t xml:space="preserve">23.8519897460938</t>
   </si>
   <si>
     <t xml:space="preserve">23.9740982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.358003616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1137828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2358913421631</t>
+    <t xml:space="preserve">25.5615177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3580017089844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1137847900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2358932495117</t>
   </si>
   <si>
     <t xml:space="preserve">23.3635540008545</t>
   </si>
   <si>
-    <t xml:space="preserve">24.4218311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2534732818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6891765594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5670700073242</t>
+    <t xml:space="preserve">24.4218330383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2534675598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6891784667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5670680999756</t>
   </si>
   <si>
     <t xml:space="preserve">20.1887149810791</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6364498138428</t>
+    <t xml:space="preserve">20.6364479064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.7178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7002811431885</t>
+    <t xml:space="preserve">19.7002792358398</t>
   </si>
   <si>
     <t xml:space="preserve">20.4736347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540241241455</t>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540279388428</t>
   </si>
   <si>
     <t xml:space="preserve">21.7354316711426</t>
@@ -1424,16 +1424,16 @@
     <t xml:space="preserve">22.4273834228516</t>
   </si>
   <si>
-    <t xml:space="preserve">21.816837310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8806667327881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4505100250244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
+    <t xml:space="preserve">21.8168354034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8806648254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.450511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284034729004</t>
   </si>
   <si>
     <t xml:space="preserve">21.6947288513184</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">22.4680862426758</t>
   </si>
   <si>
-    <t xml:space="preserve">22.1831645965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5901927947998</t>
+    <t xml:space="preserve">22.183162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5901966094971</t>
   </si>
   <si>
     <t xml:space="preserve">22.0203533172607</t>
@@ -1457,16 +1457,16 @@
     <t xml:space="preserve">23.1600399017334</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123069763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6077709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8057384490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7067546844482</t>
+    <t xml:space="preserve">22.7123050689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6077690124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.805736541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7067527770996</t>
   </si>
   <si>
     <t xml:space="preserve">24.3811283111572</t>
@@ -1475,37 +1475,37 @@
     <t xml:space="preserve">24.2183170318604</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1776161193848</t>
+    <t xml:space="preserve">24.1776142120361</t>
   </si>
   <si>
     <t xml:space="preserve">24.2997226715088</t>
   </si>
   <si>
-    <t xml:space="preserve">24.788158416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.705394744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1260414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640129089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.9123096466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2019844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4089012145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7813415527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.7399578094482</t>
+    <t xml:space="preserve">24.7881603240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7053985595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1260375976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.9123058319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2019863128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4088973999023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7813396453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.7399597167969</t>
   </si>
   <si>
     <t xml:space="preserve">25.3261337280273</t>
@@ -1514,22 +1514,22 @@
     <t xml:space="preserve">26.2779331207275</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1469688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400520324707</t>
+    <t xml:space="preserve">27.1469650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.940055847168</t>
   </si>
   <si>
     <t xml:space="preserve">26.1951656341553</t>
   </si>
   <si>
-    <t xml:space="preserve">25.491662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.5330448150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778350830078</t>
+    <t xml:space="preserve">25.4916648864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5330467224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778369903564</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675155639648</t>
@@ -1547,28 +1547,28 @@
     <t xml:space="preserve">26.1537837982178</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8227233886719</t>
+    <t xml:space="preserve">25.8227252960205</t>
   </si>
   <si>
     <t xml:space="preserve">25.9468727111816</t>
   </si>
   <si>
-    <t xml:space="preserve">26.0710182189941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9054908752441</t>
+    <t xml:space="preserve">26.0710220336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9054870605469</t>
   </si>
   <si>
     <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0642013549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.022819519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2501850128174</t>
+    <t xml:space="preserve">27.0642032623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0228176116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.250186920166</t>
   </si>
   <si>
     <t xml:space="preserve">23.6294479370117</t>
@@ -1586,103 +1586,103 @@
     <t xml:space="preserve">23.3811531066895</t>
   </si>
   <si>
-    <t xml:space="preserve">23.794979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8777446746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9191246032715</t>
+    <t xml:space="preserve">23.7949771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.877742767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
     <t xml:space="preserve">24.2088050842285</t>
   </si>
   <si>
-    <t xml:space="preserve">24.3329524993896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.4502811431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.5262260437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.8641090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0296382904053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.56760597229</t>
+    <t xml:space="preserve">24.332950592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4502792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5262279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.864107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0296363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">25.5744285583496</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6089916229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9814338684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.9882526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4434623718262</t>
+    <t xml:space="preserve">26.6089954376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9814357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.9882545471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4434642791748</t>
   </si>
   <si>
     <t xml:space="preserve">26.6503772735596</t>
   </si>
   <si>
-    <t xml:space="preserve">26.3607006072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4984855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.0914764404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7258491516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4361705780029</t>
+    <t xml:space="preserve">26.3606967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4984836578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.0914745330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7258472442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4361686706543</t>
   </si>
   <si>
     <t xml:space="preserve">21.89137840271</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7740516662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6430835723877</t>
+    <t xml:space="preserve">20.7740497589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6430816650391</t>
   </si>
   <si>
     <t xml:space="preserve">21.4775543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">21.105110168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8154335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6981029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8636360168457</t>
+    <t xml:space="preserve">21.1051120758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8154354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6981048583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8636341094971</t>
   </si>
   <si>
     <t xml:space="preserve">20.3602237701416</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2360782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.808614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9395809173584</t>
+    <t xml:space="preserve">20.2360801696777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8086166381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.939582824707</t>
   </si>
   <si>
     <t xml:space="preserve">21.9327640533447</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">22.0569114685059</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9259433746338</t>
+    <t xml:space="preserve">22.9259471893311</t>
   </si>
   <si>
     <t xml:space="preserve">22.2638206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0014190673828</t>
+    <t xml:space="preserve">18.0014171600342</t>
   </si>
   <si>
     <t xml:space="preserve">17.4634456634521</t>
@@ -1706,76 +1706,76 @@
     <t xml:space="preserve">17.5462093353271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6703567504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.877269744873</t>
+    <t xml:space="preserve">17.6703586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8772716522217</t>
   </si>
   <si>
     <t xml:space="preserve">18.2083320617676</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4980087280273</t>
+    <t xml:space="preserve">18.4980068206787</t>
   </si>
   <si>
     <t xml:space="preserve">18.7049217224121</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8290710449219</t>
+    <t xml:space="preserve">18.8290672302246</t>
   </si>
   <si>
     <t xml:space="preserve">18.6221561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8704509735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3670425415039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5325756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4911918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0773658752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1187496185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0427989959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.794506072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8427085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599411010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.884090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5530319213867</t>
+    <t xml:space="preserve">18.8704528808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3670406341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5325736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0773620605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1187477111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0428009033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7945041656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8427066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531223297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737689971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.966854095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357955932617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599430084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5530300140381</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497119903564</t>
@@ -1784,76 +1784,76 @@
     <t xml:space="preserve">18.4152431488037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1601295471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.40842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5739574432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4498062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050140380859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257568359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6499042510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3188438415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7808704376221</t>
+    <t xml:space="preserve">19.1601314544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4084281921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5739555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4498100280762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050159454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257549285889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.64990234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3188419342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1119289398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7808685302734</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.029167175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6567211151123</t>
+    <t xml:space="preserve">20.0291652679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6567230224609</t>
   </si>
   <si>
     <t xml:space="preserve">19.9463996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2428970336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3256607055664</t>
+    <t xml:space="preserve">19.2428932189941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.325662612915</t>
   </si>
   <si>
     <t xml:space="preserve">19.035982131958</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2979145050049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5364742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5944118499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.48681640625</t>
+    <t xml:space="preserve">17.2979164123535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5364761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.594409942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4868183135986</t>
   </si>
   <si>
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0910015106201</t>
+    <t xml:space="preserve">17.0910034179688</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151489257812</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">17.3310203552246</t>
   </si>
   <si>
-    <t xml:space="preserve">17.364128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2910976409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6056041717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3407573699951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0593547821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.645528793335</t>
+    <t xml:space="preserve">17.3641262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2910957336426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6056003570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3407554626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.0593509674072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6455268859863</t>
   </si>
   <si>
     <t xml:space="preserve">17.2482566833496</t>
@@ -1892,7 +1892,7 @@
     <t xml:space="preserve">18.1255645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620845794678</t>
+    <t xml:space="preserve">17.6620807647705</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779521942139</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">18.2248840332031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7613983154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5861358642578</t>
+    <t xml:space="preserve">17.7614002227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5861339569092</t>
   </si>
   <si>
     <t xml:space="preserve">16.6192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5033702850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5101871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4274225234985</t>
+    <t xml:space="preserve">16.5033683776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5101881027222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4274244308472</t>
   </si>
   <si>
     <t xml:space="preserve">15.2701692581177</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8397912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328763961792</t>
+    <t xml:space="preserve">14.839789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328783035278</t>
   </si>
   <si>
     <t xml:space="preserve">14.6742601394653</t>
@@ -1937,34 +1937,34 @@
     <t xml:space="preserve">15.6177835464478</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0233325958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9322929382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632572174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549812316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.046703338623</t>
+    <t xml:space="preserve">16.0233306884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9322900772095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0632562637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0549793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0467023849487</t>
   </si>
   <si>
     <t xml:space="preserve">14.6659832000732</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3255748748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.342604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7125539779663</t>
+    <t xml:space="preserve">14.8232364654541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3255767822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3426036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.712553024292</t>
   </si>
   <si>
     <t xml:space="preserve">14.8402652740479</t>
@@ -1973,34 +1973,34 @@
     <t xml:space="preserve">14.6614675521851</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6444406509399</t>
+    <t xml:space="preserve">14.6444396972656</t>
   </si>
   <si>
     <t xml:space="preserve">14.8062086105347</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5422677993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8913497924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9811697006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6661405563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9083795547485</t>
+    <t xml:space="preserve">14.5422687530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8913507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9811725616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6661434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9083786010742</t>
   </si>
   <si>
     <t xml:space="preserve">14.525239944458</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4741554260254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.201699256897</t>
+    <t xml:space="preserve">14.4741544723511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2017002105713</t>
   </si>
   <si>
     <t xml:space="preserve">14.3890132904053</t>
@@ -2018,10 +2018,10 @@
     <t xml:space="preserve">14.0484447479248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1846694946289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8317527770996</t>
+    <t xml:space="preserve">14.1846714019775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8317518234253</t>
   </si>
   <si>
     <t xml:space="preserve">14.5507831573486</t>
@@ -2030,25 +2030,28 @@
     <t xml:space="preserve">14.3208990097046</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7295789718628</t>
+    <t xml:space="preserve">14.7295799255371</t>
   </si>
   <si>
     <t xml:space="preserve">15.0020360946655</t>
   </si>
   <si>
+    <t xml:space="preserve">14.8232374191284</t>
+  </si>
+  <si>
     <t xml:space="preserve">14.4230699539185</t>
   </si>
   <si>
     <t xml:space="preserve">14.3379287719727</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3549566268921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9462728500366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6908483505249</t>
+    <t xml:space="preserve">14.3549556732178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9462718963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6908473968506</t>
   </si>
   <si>
     <t xml:space="preserve">13.7419328689575</t>
@@ -2057,82 +2060,82 @@
     <t xml:space="preserve">13.7930183410645</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6312484741211</t>
+    <t xml:space="preserve">13.6312494277954</t>
   </si>
   <si>
     <t xml:space="preserve">13.0948524475098</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821655273438</t>
+    <t xml:space="preserve">13.2821645736694</t>
   </si>
   <si>
     <t xml:space="preserve">14.3975257873535</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0995292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8866729736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8185596466064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2225666046143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5801639556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6227350234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5205631256104</t>
+    <t xml:space="preserve">14.0995302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8866739273071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8185606002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2225675582886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5801630020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6227331161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5205640792847</t>
   </si>
   <si>
     <t xml:space="preserve">13.1799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1544513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2140531539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1668033599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9663019180298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9748153686523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9492721557617</t>
+    <t xml:space="preserve">13.1544523239136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2140522003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1668043136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9663009643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9748163223267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9492712020874</t>
   </si>
   <si>
     <t xml:space="preserve">10.5491056442261</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7449312210083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1706409454346</t>
+    <t xml:space="preserve">10.7449321746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1706418991089</t>
   </si>
   <si>
     <t xml:space="preserve">10.7534456253052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0344133377075</t>
+    <t xml:space="preserve">11.0344142913818</t>
   </si>
   <si>
     <t xml:space="preserve">11.162127494812</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8811597824097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7875032424927</t>
+    <t xml:space="preserve">10.8811588287354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7875022888184</t>
   </si>
   <si>
     <t xml:space="preserve">10.7619600296021</t>
@@ -2141,16 +2144,16 @@
     <t xml:space="preserve">10.2511072158813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0599555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8471021652222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6683025360107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7279024124146</t>
+    <t xml:space="preserve">11.0599575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8471012115479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6683034896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7279033660889</t>
   </si>
   <si>
     <t xml:space="preserve">11.3664684295654</t>
@@ -2162,10 +2165,10 @@
     <t xml:space="preserve">11.6644659042358</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6900072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7410936355591</t>
+    <t xml:space="preserve">11.6900081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7410926818848</t>
   </si>
   <si>
     <t xml:space="preserve">11.749608039856</t>
@@ -2174,13 +2177,13 @@
     <t xml:space="preserve">12.1838331222534</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9028625488281</t>
+    <t xml:space="preserve">11.9028635025024</t>
   </si>
   <si>
     <t xml:space="preserve">11.8177213668823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7751493453979</t>
+    <t xml:space="preserve">11.7751502990723</t>
   </si>
   <si>
     <t xml:space="preserve">12.0476055145264</t>
@@ -2192,16 +2195,16 @@
     <t xml:space="preserve">11.5026960372925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1450996398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8981885910034</t>
+    <t xml:space="preserve">11.1450986862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8981876373291</t>
   </si>
   <si>
     <t xml:space="preserve">11.2898406982422</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2132129669189</t>
+    <t xml:space="preserve">11.2132139205933</t>
   </si>
   <si>
     <t xml:space="preserve">10.7108745574951</t>
@@ -2210,46 +2213,46 @@
     <t xml:space="preserve">10.4724760055542</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6597890853882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0173854827881</t>
+    <t xml:space="preserve">10.6597900390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0173864364624</t>
   </si>
   <si>
     <t xml:space="preserve">11.0854997634888</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0514421463013</t>
+    <t xml:space="preserve">11.0514430999756</t>
   </si>
   <si>
     <t xml:space="preserve">11.1280708312988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0003566741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0088710784912</t>
+    <t xml:space="preserve">11.0003576278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0088720321655</t>
   </si>
   <si>
     <t xml:space="preserve">11.2642984390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.698522567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6814947128296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8092069625854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3247375488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1970224380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.239595413208</t>
+    <t xml:space="preserve">11.6985216140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6814956665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8092079162598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3247356414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1970233917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2395944595337</t>
   </si>
   <si>
     <t xml:space="preserve">13.5120496749878</t>
@@ -2264,16 +2267,16 @@
     <t xml:space="preserve">14.4145555496216</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8526172637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2187280654907</t>
+    <t xml:space="preserve">13.8526182174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2187309265137</t>
   </si>
   <si>
     <t xml:space="preserve">13.8781595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7759885787964</t>
+    <t xml:space="preserve">13.7759895324707</t>
   </si>
   <si>
     <t xml:space="preserve">13.4439344406128</t>
@@ -2285,16 +2288,16 @@
     <t xml:space="preserve">14.4486122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6274089813232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9254083633423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5043725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5933523178101</t>
+    <t xml:space="preserve">14.6274099349976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9254093170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.504373550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5933542251587</t>
   </si>
   <si>
     <t xml:space="preserve">14.5592956542969</t>
@@ -2303,7 +2306,7 @@
     <t xml:space="preserve">14.9424362182617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9679775238037</t>
+    <t xml:space="preserve">14.9679794311523</t>
   </si>
   <si>
     <t xml:space="preserve">14.6870098114014</t>
@@ -2312,67 +2315,67 @@
     <t xml:space="preserve">15.019063949585</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1467781066895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3170614242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6406021118164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4618005752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4656419754028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.363471031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3294134140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4826707839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.15061378479</t>
+    <t xml:space="preserve">15.1467771530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3170623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6406030654907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4618034362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4656400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3634700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3294143676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4826698303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.150616645813</t>
   </si>
   <si>
     <t xml:space="preserve">14.1335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5763254165649</t>
+    <t xml:space="preserve">14.5763263702393</t>
   </si>
   <si>
     <t xml:space="preserve">14.1165580749512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4911851882935</t>
+    <t xml:space="preserve">14.4911842346191</t>
   </si>
   <si>
     <t xml:space="preserve">14.3804988861084</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4997005462646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721519470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7078762054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9292459487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5035343170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3162231445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5631351470947</t>
+    <t xml:space="preserve">14.499698638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721538543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7078771591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9292469024658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5035333633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3162221908569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5631341934204</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375909805298</t>
@@ -2390,19 +2393,19 @@
     <t xml:space="preserve">14.5082120895386</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5167255401611</t>
+    <t xml:space="preserve">14.5167245864868</t>
   </si>
   <si>
     <t xml:space="preserve">14.1761560440063</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1931858062744</t>
+    <t xml:space="preserve">14.1931848526001</t>
   </si>
   <si>
     <t xml:space="preserve">13.758960723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4183921813965</t>
+    <t xml:space="preserve">13.4183931350708</t>
   </si>
   <si>
     <t xml:space="preserve">12.5584583282471</t>
@@ -2411,34 +2414,34 @@
     <t xml:space="preserve">12.3370876312256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6010284423828</t>
+    <t xml:space="preserve">12.6010303497314</t>
   </si>
   <si>
     <t xml:space="preserve">11.9880046844482</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6218948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4430952072144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3277339935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82539558410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4252290725708</t>
+    <t xml:space="preserve">11.6218938827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4430961608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3277349472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82539749145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42523002624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.74025344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0842399597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73557949066162</t>
+    <t xml:space="preserve">8.08424091339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73557758331299</t>
   </si>
   <si>
     <t xml:space="preserve">8.2715539932251</t>
@@ -2447,34 +2450,34 @@
     <t xml:space="preserve">8.31412506103516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96078586578369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66278743743896</t>
+    <t xml:space="preserve">7.96078491210938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66278839111328</t>
   </si>
   <si>
     <t xml:space="preserve">9.11020278930664</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00803184509277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41671562194824</t>
+    <t xml:space="preserve">9.00803279876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41671466827393</t>
   </si>
   <si>
     <t xml:space="preserve">9.47631454467773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5784854888916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44225788116455</t>
+    <t xml:space="preserve">9.57848453521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44225692749023</t>
   </si>
   <si>
     <t xml:space="preserve">9.46780014038086</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09317493438721</t>
+    <t xml:space="preserve">9.09317588806152</t>
   </si>
   <si>
     <t xml:space="preserve">9.16980361938477</t>
@@ -2483,16 +2486,16 @@
     <t xml:space="preserve">9.53591442108154</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48482894897461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62105655670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0893383026123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1319093704224</t>
+    <t xml:space="preserve">9.48482799530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62105464935303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.089337348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.131908416748</t>
   </si>
   <si>
     <t xml:space="preserve">10.0467662811279</t>
@@ -2507,13 +2510,13 @@
     <t xml:space="preserve">9.97013854980469</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0552816390991</t>
+    <t xml:space="preserve">10.0552825927734</t>
   </si>
   <si>
     <t xml:space="preserve">10.2936782836914</t>
   </si>
   <si>
-    <t xml:space="preserve">10.319221496582</t>
+    <t xml:space="preserve">10.3192195892334</t>
   </si>
   <si>
     <t xml:space="preserve">10.4299058914185</t>
@@ -2522,7 +2525,7 @@
     <t xml:space="preserve">10.9322452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1961841583252</t>
+    <t xml:space="preserve">11.1961832046509</t>
   </si>
   <si>
     <t xml:space="preserve">10.9407587051392</t>
@@ -2534,25 +2537,25 @@
     <t xml:space="preserve">9.85945320129395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7828254699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3060302734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51037120819092</t>
+    <t xml:space="preserve">9.78282642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30603122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5103702545166</t>
   </si>
   <si>
     <t xml:space="preserve">9.51888561248779</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22940254211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26345825195312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25494575500488</t>
+    <t xml:space="preserve">9.22940349578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26345920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25494480133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.36562919616699</t>
@@ -2564,13 +2567,13 @@
     <t xml:space="preserve">8.93140411376953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85477733612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28048706054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70619678497314</t>
+    <t xml:space="preserve">8.85477638244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28048801422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70619773864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.62957000732422</t>
@@ -2582,25 +2585,25 @@
     <t xml:space="preserve">11.1876697540283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8300743103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5405912399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2340793609619</t>
+    <t xml:space="preserve">10.8300733566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5405902862549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2340784072876</t>
   </si>
   <si>
     <t xml:space="preserve">9.61254215240479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96388339996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435722351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1823921203613</t>
+    <t xml:space="preserve">9.9638843536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435731887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.182391166687</t>
   </si>
   <si>
     <t xml:space="preserve">10.1998720169067</t>
@@ -2624,7 +2627,7 @@
     <t xml:space="preserve">9.72789859771729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64049530029297</t>
+    <t xml:space="preserve">9.64049625396729</t>
   </si>
   <si>
     <t xml:space="preserve">9.28214454650879</t>
@@ -2645,34 +2648,34 @@
     <t xml:space="preserve">9.40450859069824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15978240966797</t>
+    <t xml:space="preserve">9.15978145599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.99371719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01993751525879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9063138961792</t>
+    <t xml:space="preserve">9.01993846893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90631580352783</t>
   </si>
   <si>
     <t xml:space="preserve">9.57931423187256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20348358154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36080741882324</t>
+    <t xml:space="preserve">9.20348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36080837249756</t>
   </si>
   <si>
     <t xml:space="preserve">9.18600273132324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33458709716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2209644317627</t>
+    <t xml:space="preserve">9.33458805084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22096347808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.44821071624756</t>
@@ -2684,55 +2687,55 @@
     <t xml:space="preserve">9.01119804382324</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3484554290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4358587265015</t>
+    <t xml:space="preserve">10.3484563827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4358577728271</t>
   </si>
   <si>
     <t xml:space="preserve">10.4271183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9777526855469</t>
+    <t xml:space="preserve">10.9777536392212</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001176834106</t>
   </si>
   <si>
-    <t xml:space="preserve">11.318621635437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4672069549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0826377868652</t>
+    <t xml:space="preserve">11.3186225891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4672079086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0826368331909</t>
   </si>
   <si>
     <t xml:space="preserve">10.8903512954712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7942085266113</t>
+    <t xml:space="preserve">10.7942094802856</t>
   </si>
   <si>
     <t xml:space="preserve">10.6281442642212</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5494823455811</t>
+    <t xml:space="preserve">10.5494813919067</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872753143311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2260913848877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1299495697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98136520385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93766307830811</t>
+    <t xml:space="preserve">10.226092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1299486160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98136615753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93766403198242</t>
   </si>
   <si>
     <t xml:space="preserve">10.0949897766113</t>
@@ -2744,37 +2747,34 @@
     <t xml:space="preserve">10.0250673294067</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87648296356201</t>
-  </si>
-  <si>
     <t xml:space="preserve">9.95514488220215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78033924102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75411987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6579761505127</t>
+    <t xml:space="preserve">9.78033828735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75411891937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65797519683838</t>
   </si>
   <si>
     <t xml:space="preserve">9.7453784942627</t>
   </si>
   <si>
-    <t xml:space="preserve">9.99884414672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3222360610962</t>
+    <t xml:space="preserve">9.99884510040283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3222370147705</t>
   </si>
   <si>
     <t xml:space="preserve">10.7330265045166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.750506401062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4620800018311</t>
+    <t xml:space="preserve">10.7505073547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4620790481567</t>
   </si>
   <si>
     <t xml:space="preserve">10.2785339355469</t>
@@ -2783,19 +2783,19 @@
     <t xml:space="preserve">10.3834171295166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3659372329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4970397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6893243789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6106624603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4795598983765</t>
+    <t xml:space="preserve">10.3659362792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4970407485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6893253326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6106634140015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4795589447021</t>
   </si>
   <si>
     <t xml:space="preserve">10.5757036209106</t>
@@ -2807,13 +2807,13 @@
     <t xml:space="preserve">10.5232610702515</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5582227706909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4708194732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81529998779297</t>
+    <t xml:space="preserve">10.5582208633423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4708185195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81530094146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.0687685012817</t>
@@ -2822,7 +2822,7 @@
     <t xml:space="preserve">9.99010562896729</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82404136657715</t>
+    <t xml:space="preserve">9.82403945922852</t>
   </si>
   <si>
     <t xml:space="preserve">9.86774253845215</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">8.82765293121338</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36878871917725</t>
+    <t xml:space="preserve">8.36878967285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.5348539352417</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">8.6441068649292</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12482166290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1685209274292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88883399963379</t>
+    <t xml:space="preserve">9.12482070922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16852188110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88883304595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.98497676849365</t>
@@ -2861,16 +2861,16 @@
     <t xml:space="preserve">9.94640445709229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69293785095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9078311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1350784301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6070518493652</t>
+    <t xml:space="preserve">9.69293689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9078302383423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1350774765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6070508956909</t>
   </si>
   <si>
     <t xml:space="preserve">12.3324918746948</t>
@@ -2879,10 +2879,10 @@
     <t xml:space="preserve">12.3587141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5597381591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8867406845093</t>
+    <t xml:space="preserve">12.5597372055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.886739730835</t>
   </si>
   <si>
     <t xml:space="preserve">12.4810762405396</t>
@@ -2891,28 +2891,28 @@
     <t xml:space="preserve">12.19264793396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139850616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.210129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6857137680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0702848434448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.974142074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9916229248047</t>
+    <t xml:space="preserve">12.1139860153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2101287841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6857147216797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0702857971191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9741430282593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.991623878479</t>
   </si>
   <si>
     <t xml:space="preserve">11.9479217529297</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0615453720093</t>
+    <t xml:space="preserve">12.061544418335</t>
   </si>
   <si>
     <t xml:space="preserve">12.1314668655396</t>
@@ -2921,22 +2921,22 @@
     <t xml:space="preserve">12.0440635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8954801559448</t>
+    <t xml:space="preserve">11.8954792022705</t>
   </si>
   <si>
     <t xml:space="preserve">12.0091028213501</t>
   </si>
   <si>
-    <t xml:space="preserve">12.01784324646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6558809280396</t>
+    <t xml:space="preserve">12.0178442001343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6558818817139</t>
   </si>
   <si>
     <t xml:space="preserve">12.6733617782593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4898166656494</t>
+    <t xml:space="preserve">12.4898176193237</t>
   </si>
   <si>
     <t xml:space="preserve">12.4198951721191</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">12.5422592163086</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7782459259033</t>
+    <t xml:space="preserve">12.778244972229</t>
   </si>
   <si>
     <t xml:space="preserve">12.2363500595093</t>
@@ -2957,25 +2957,25 @@
     <t xml:space="preserve">12.4461145401001</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5160388946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5509996414185</t>
+    <t xml:space="preserve">12.5160369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5509986877441</t>
   </si>
   <si>
     <t xml:space="preserve">12.2713108062744</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8132057189941</t>
+    <t xml:space="preserve">12.8132066726685</t>
   </si>
   <si>
     <t xml:space="preserve">12.8394269943237</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9093494415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8219451904297</t>
+    <t xml:space="preserve">12.909348487854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.821946144104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9880104064941</t>
@@ -2987,10 +2987,10 @@
     <t xml:space="preserve">13.3114004135132</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2152576446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2502193450928</t>
+    <t xml:space="preserve">13.215256690979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2502183914185</t>
   </si>
   <si>
     <t xml:space="preserve">12.7607650756836</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">12.6296615600586</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9530506134033</t>
+    <t xml:space="preserve">12.953049659729</t>
   </si>
   <si>
     <t xml:space="preserve">12.9792718887329</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9355697631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.302661895752</t>
+    <t xml:space="preserve">12.9355707168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3026599884033</t>
   </si>
   <si>
     <t xml:space="preserve">13.407543182373</t>
@@ -3023,22 +3023,22 @@
     <t xml:space="preserve">13.800853729248</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0280990600586</t>
+    <t xml:space="preserve">14.0281000137329</t>
   </si>
   <si>
     <t xml:space="preserve">14.1067628860474</t>
   </si>
   <si>
-    <t xml:space="preserve">14.395191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5000743865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4039306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5612545013428</t>
+    <t xml:space="preserve">14.3951902389526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5000734329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4039316177368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5612554550171</t>
   </si>
   <si>
     <t xml:space="preserve">14.2116460800171</t>
@@ -3059,55 +3059,55 @@
     <t xml:space="preserve">14.6661386489868</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7098407745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6224374771118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0157480239868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1818132400513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3653583526611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1206302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.456374168396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6136960983276</t>
+    <t xml:space="preserve">14.7098417282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6224365234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0157489776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1818141937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3653593063354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1206312179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4563732147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.613697052002</t>
   </si>
   <si>
     <t xml:space="preserve">14.762282371521</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3442687988281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7550582885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9946565628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8373327255249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9159936904907</t>
+    <t xml:space="preserve">16.3442668914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7550601959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8373346328735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.915994644165</t>
   </si>
   <si>
     <t xml:space="preserve">15.9247350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9422159194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.13450050354</t>
+    <t xml:space="preserve">15.9422168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1344985961914</t>
   </si>
   <si>
     <t xml:space="preserve">15.43528175354</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">15.566385269165</t>
   </si>
   <si>
-    <t xml:space="preserve">15.356616973877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4440231323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3303995132446</t>
+    <t xml:space="preserve">15.3566179275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4440221786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3304004669189</t>
   </si>
   <si>
     <t xml:space="preserve">15.2429962158203</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">15.2255163192749</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2866954803467</t>
+    <t xml:space="preserve">15.286696434021</t>
   </si>
   <si>
     <t xml:space="preserve">15.2779569625854</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">15.2517366409302</t>
   </si>
   <si>
-    <t xml:space="preserve">15.068190574646</t>
+    <t xml:space="preserve">15.0681896209717</t>
   </si>
   <si>
     <t xml:space="preserve">15.1381120681763</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4265403747559</t>
+    <t xml:space="preserve">15.4265394210815</t>
   </si>
   <si>
     <t xml:space="preserve">15.0244903564453</t>
@@ -3155,13 +3155,13 @@
     <t xml:space="preserve">14.893385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8234624862671</t>
+    <t xml:space="preserve">14.8234643936157</t>
   </si>
   <si>
     <t xml:space="preserve">15.0856714248657</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9196071624756</t>
+    <t xml:space="preserve">14.9196062088013</t>
   </si>
   <si>
     <t xml:space="preserve">14.9982690811157</t>
@@ -3170,58 +3170,58 @@
     <t xml:space="preserve">14.9370880126953</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1468524932861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8496856689453</t>
+    <t xml:space="preserve">15.1468534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8496837615967</t>
   </si>
   <si>
     <t xml:space="preserve">15.1031532287598</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2604761123657</t>
+    <t xml:space="preserve">15.2604751586914</t>
   </si>
   <si>
     <t xml:space="preserve">15.3041772842407</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8409423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4214124679565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5962171554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7812805175781</t>
+    <t xml:space="preserve">14.8409433364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4214134216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5962190628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7812824249268</t>
   </si>
   <si>
     <t xml:space="preserve">17.4367980957031</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4630184173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.0748386383057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2846031188965</t>
+    <t xml:space="preserve">17.463020324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.074836730957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2846012115479</t>
   </si>
   <si>
     <t xml:space="preserve">18.8397483825684</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5048980712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7340087890625</t>
+    <t xml:space="preserve">18.5048999786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7340068817139</t>
   </si>
   <si>
     <t xml:space="preserve">18.4696521759033</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8573741912842</t>
+    <t xml:space="preserve">18.8573722839355</t>
   </si>
   <si>
     <t xml:space="preserve">18.8221263885498</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">18.5753936767578</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2052936553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6987590789795</t>
+    <t xml:space="preserve">18.2052955627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6987609863281</t>
   </si>
   <si>
     <t xml:space="preserve">18.5401477813721</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2405433654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7163848876953</t>
+    <t xml:space="preserve">18.2405452728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7163829803467</t>
   </si>
   <si>
     <t xml:space="preserve">18.2934150695801</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">17.9056930541992</t>
   </si>
   <si>
-    <t xml:space="preserve">17.888069152832</t>
+    <t xml:space="preserve">17.8880672454834</t>
   </si>
   <si>
     <t xml:space="preserve">17.7647037506104</t>
@@ -3290,10 +3290,10 @@
     <t xml:space="preserve">17.64133644104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5708427429199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6589622497559</t>
+    <t xml:space="preserve">17.5708446502686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6589603424072</t>
   </si>
   <si>
     <t xml:space="preserve">17.5267810821533</t>
@@ -3302,16 +3302,16 @@
     <t xml:space="preserve">17.3681697845459</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1478729248047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4650993347168</t>
+    <t xml:space="preserve">17.1478710174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4650974273682</t>
   </si>
   <si>
     <t xml:space="preserve">17.9761867523193</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8351974487305</t>
+    <t xml:space="preserve">17.8351993560791</t>
   </si>
   <si>
     <t xml:space="preserve">17.4827251434326</t>
@@ -3323,10 +3323,10 @@
     <t xml:space="preserve">16.3724308013916</t>
   </si>
   <si>
-    <t xml:space="preserve">16.125696182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5222320556641</t>
+    <t xml:space="preserve">16.1256980895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5222339630127</t>
   </si>
   <si>
     <t xml:space="preserve">16.6367855072021</t>
@@ -3335,10 +3335,10 @@
     <t xml:space="preserve">17.3857936859131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2448024749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3769817352295</t>
+    <t xml:space="preserve">17.2448043823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3769798278809</t>
   </si>
   <si>
     <t xml:space="preserve">17.4122276306152</t>
@@ -3362,10 +3362,10 @@
     <t xml:space="preserve">17.0861892700195</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1743087768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3417339324951</t>
+    <t xml:space="preserve">17.1743106842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3417358398438</t>
   </si>
   <si>
     <t xml:space="preserve">17.1654968261719</t>
@@ -3374,13 +3374,13 @@
     <t xml:space="preserve">16.9540100097656</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3593578338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9716377258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7249031066895</t>
+    <t xml:space="preserve">17.3593597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9716358184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7249011993408</t>
   </si>
   <si>
     <t xml:space="preserve">16.6896572113037</t>
@@ -3392,16 +3392,16 @@
     <t xml:space="preserve">16.4869842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8042125701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2183704376221</t>
+    <t xml:space="preserve">16.8042106628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2183685302734</t>
   </si>
   <si>
     <t xml:space="preserve">17.8704452514648</t>
   </si>
   <si>
-    <t xml:space="preserve">17.676586151123</t>
+    <t xml:space="preserve">17.6765842437744</t>
   </si>
   <si>
     <t xml:space="preserve">17.5796527862549</t>
@@ -3419,19 +3419,19 @@
     <t xml:space="preserve">16.7425270080566</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5927276611328</t>
+    <t xml:space="preserve">16.5927257537842</t>
   </si>
   <si>
     <t xml:space="preserve">16.4957942962646</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3988647460938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3900547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3019371032715</t>
+    <t xml:space="preserve">16.3988666534424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3900527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3019351959229</t>
   </si>
   <si>
     <t xml:space="preserve">15.9935188293457</t>
@@ -3449,13 +3449,13 @@
     <t xml:space="preserve">16.3195610046387</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7732238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5176820755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4119358062744</t>
+    <t xml:space="preserve">15.7732229232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5176811218262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4119367599487</t>
   </si>
   <si>
     <t xml:space="preserve">15.3590660095215</t>
@@ -3464,13 +3464,13 @@
     <t xml:space="preserve">15.0330266952515</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3150062561035</t>
+    <t xml:space="preserve">15.3150043487549</t>
   </si>
   <si>
     <t xml:space="preserve">15.0154047012329</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2180767059326</t>
+    <t xml:space="preserve">15.2180776596069</t>
   </si>
   <si>
     <t xml:space="preserve">15.1828279495239</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">15.0242147445679</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1123332977295</t>
+    <t xml:space="preserve">15.1123352050781</t>
   </si>
   <si>
     <t xml:space="preserve">15.1035223007202</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4912433624268</t>
+    <t xml:space="preserve">15.4912443161011</t>
   </si>
   <si>
     <t xml:space="preserve">15.1475820541382</t>
@@ -3494,16 +3494,16 @@
     <t xml:space="preserve">15.0858993530273</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9801568984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8215427398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6188688278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3985748291016</t>
+    <t xml:space="preserve">14.9801559448242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8215436935425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6188697814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3985738754272</t>
   </si>
   <si>
     <t xml:space="preserve">14.0020408630371</t>
@@ -3524,10 +3524,10 @@
     <t xml:space="preserve">14.2840194702148</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3104543685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.345703125</t>
+    <t xml:space="preserve">14.3104553222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3457040786743</t>
   </si>
   <si>
     <t xml:space="preserve">13.9491691589355</t>
@@ -3536,16 +3536,16 @@
     <t xml:space="preserve">16.1080741882324</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5483770370483</t>
+    <t xml:space="preserve">14.548376083374</t>
   </si>
   <si>
     <t xml:space="preserve">14.4778804779053</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1870889663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1254072189331</t>
+    <t xml:space="preserve">14.1870899200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1254062652588</t>
   </si>
   <si>
     <t xml:space="preserve">14.0637235641479</t>
@@ -3557,58 +3557,58 @@
     <t xml:space="preserve">13.6055059432983</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7729320526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0856084823608</t>
+    <t xml:space="preserve">13.772931098938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0856075286865</t>
   </si>
   <si>
     <t xml:space="preserve">13.1384782791138</t>
   </si>
   <si>
-    <t xml:space="preserve">13.032735824585</t>
+    <t xml:space="preserve">13.0327367782593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4028339385986</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1296672821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9446182250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3852100372314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6583776473999</t>
+    <t xml:space="preserve">13.1296663284302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9446172714233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3852109909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6583766937256</t>
   </si>
   <si>
     <t xml:space="preserve">13.5350112915039</t>
   </si>
   <si>
-    <t xml:space="preserve">13.561448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1913509368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2265968322754</t>
+    <t xml:space="preserve">13.5614471435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.191349029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2265977859497</t>
   </si>
   <si>
     <t xml:space="preserve">13.6231307983398</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3147163391113</t>
+    <t xml:space="preserve">13.314715385437</t>
   </si>
   <si>
     <t xml:space="preserve">13.2618436813354</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4557056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.438081741333</t>
+    <t xml:space="preserve">13.4557065963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4380807876587</t>
   </si>
   <si>
     <t xml:space="preserve">13.4645166397095</t>
@@ -3620,10 +3620,10 @@
     <t xml:space="preserve">13.482141494751</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5878839492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5702590942383</t>
+    <t xml:space="preserve">13.5878829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5702600479126</t>
   </si>
   <si>
     <t xml:space="preserve">13.7112503051758</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">13.4468936920166</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1649131774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8388748168945</t>
+    <t xml:space="preserve">13.1649141311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8388738632202</t>
   </si>
   <si>
     <t xml:space="preserve">12.9710540771484</t>
@@ -3650,22 +3650,22 @@
     <t xml:space="preserve">12.6890745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5128374099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5568952560425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6273918151855</t>
+    <t xml:space="preserve">12.5128364562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5568962097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6273908615112</t>
   </si>
   <si>
     <t xml:space="preserve">12.40709400177</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6492757797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.587592124939</t>
+    <t xml:space="preserve">11.6492738723755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5875911712646</t>
   </si>
   <si>
     <t xml:space="preserve">11.8078870773315</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">11.9048185348511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8431348800659</t>
+    <t xml:space="preserve">11.8431358337402</t>
   </si>
   <si>
     <t xml:space="preserve">12.1427383422852</t>
@@ -3683,13 +3683,13 @@
     <t xml:space="preserve">11.9841260910034</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5347204208374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.464225769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1117515563965</t>
+    <t xml:space="preserve">11.5347194671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4642248153687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1117506027222</t>
   </si>
   <si>
     <t xml:space="preserve">10.9090795516968</t>
@@ -3698,13 +3698,13 @@
     <t xml:space="preserve">11.2263050079346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1293745040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0412549972534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8209590911865</t>
+    <t xml:space="preserve">11.1293754577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0412559509277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8209600448608</t>
   </si>
   <si>
     <t xml:space="preserve">10.803337097168</t>
@@ -3719,13 +3719,13 @@
     <t xml:space="preserve">11.1822452545166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7416534423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.961950302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9355144500732</t>
+    <t xml:space="preserve">10.7416524887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9619493484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9355134963989</t>
   </si>
   <si>
     <t xml:space="preserve">10.6975936889648</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">10.2393779754639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73710250854492</t>
+    <t xml:space="preserve">9.73710155487061</t>
   </si>
   <si>
     <t xml:space="preserve">9.54324054718018</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">9.85165596008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42868709564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61373615264893</t>
+    <t xml:space="preserve">9.42868614196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61373519897461</t>
   </si>
   <si>
     <t xml:space="preserve">8.64883613586426</t>
@@ -3776,13 +3776,13 @@
     <t xml:space="preserve">8.87353897094727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25244903564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977798461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83829307556152</t>
+    <t xml:space="preserve">9.25244998931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977703094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83829212188721</t>
   </si>
   <si>
     <t xml:space="preserve">8.70611381530762</t>
@@ -3791,19 +3791,19 @@
     <t xml:space="preserve">9.24363708496094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74576854705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68849086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62680721282959</t>
+    <t xml:space="preserve">8.74576759338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68848991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62680816650391</t>
   </si>
   <si>
     <t xml:space="preserve">8.61359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27873992919922</t>
+    <t xml:space="preserve">8.2787389755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.24349212646484</t>
@@ -3815,7 +3815,7 @@
     <t xml:space="preserve">8.35363960266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27433300018311</t>
+    <t xml:space="preserve">8.27433395385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.26552200317383</t>
@@ -3824,7 +3824,7 @@
     <t xml:space="preserve">8.25671005249023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36245155334473</t>
+    <t xml:space="preserve">8.36245059967041</t>
   </si>
   <si>
     <t xml:space="preserve">8.31398677825928</t>
@@ -3833,13 +3833,13 @@
     <t xml:space="preserve">8.42413520812988</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13334369659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08487796783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01878929138184</t>
+    <t xml:space="preserve">8.13334274291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08487892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01879024505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.20824432373047</t>
@@ -3848,43 +3848,43 @@
     <t xml:space="preserve">8.01438426971436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88661193847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12453269958496</t>
+    <t xml:space="preserve">7.8866114616394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12453174591064</t>
   </si>
   <si>
     <t xml:space="preserve">8.02760124206543</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89542388916016</t>
+    <t xml:space="preserve">7.89542293548584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93067169189453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80730438232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57819700241089</t>
+    <t xml:space="preserve">7.80730485916138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57819747924805</t>
   </si>
   <si>
     <t xml:space="preserve">7.69275045394897</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66190910339355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78527641296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6751275062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95803880691528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67512655258179</t>
+    <t xml:space="preserve">7.66190958023071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78527593612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512798309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95803928375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67512702941895</t>
   </si>
   <si>
     <t xml:space="preserve">7.62037038803101</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">8.34133911132812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.08124160766602</t>
+    <t xml:space="preserve">8.08124256134033</t>
   </si>
   <si>
     <t xml:space="preserve">7.92609739303589</t>
@@ -3911,16 +3911,16 @@
     <t xml:space="preserve">7.64774894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82570886611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67968988418579</t>
+    <t xml:space="preserve">7.82570934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67969036102295</t>
   </si>
   <si>
     <t xml:space="preserve">7.69337940216064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54736089706421</t>
+    <t xml:space="preserve">7.54736042022705</t>
   </si>
   <si>
     <t xml:space="preserve">7.20056486129761</t>
@@ -3935,7 +3935,7 @@
     <t xml:space="preserve">7.04085683822632</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85833311080933</t>
+    <t xml:space="preserve">6.85833263397217</t>
   </si>
   <si>
     <t xml:space="preserve">6.93590545654297</t>
@@ -3953,13 +3953,13 @@
     <t xml:space="preserve">6.90396404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79444932937622</t>
+    <t xml:space="preserve">6.79444980621338</t>
   </si>
   <si>
     <t xml:space="preserve">6.80357599258423</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69406127929688</t>
+    <t xml:space="preserve">6.69406175613403</t>
   </si>
   <si>
     <t xml:space="preserve">6.46590709686279</t>
@@ -3971,7 +3971,7 @@
     <t xml:space="preserve">6.41571283340454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19212055206299</t>
+    <t xml:space="preserve">6.19212102890015</t>
   </si>
   <si>
     <t xml:space="preserve">6.36095523834229</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">6.50697469711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53891658782959</t>
+    <t xml:space="preserve">6.53891611099243</t>
   </si>
   <si>
     <t xml:space="preserve">6.55260562896729</t>
@@ -4004,16 +4004,16 @@
     <t xml:space="preserve">6.51153802871704</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46134328842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63474082946777</t>
+    <t xml:space="preserve">6.46134376525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63474130630493</t>
   </si>
   <si>
     <t xml:space="preserve">6.58454751968384</t>
   </si>
   <si>
-    <t xml:space="preserve">6.56173133850098</t>
+    <t xml:space="preserve">6.56173181533813</t>
   </si>
   <si>
     <t xml:space="preserve">6.49328517913818</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">6.64843034744263</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80813837051392</t>
+    <t xml:space="preserve">6.80813884735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.92677927017212</t>
@@ -4061,7 +4061,7 @@
     <t xml:space="preserve">6.82182788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18231248855591</t>
+    <t xml:space="preserve">7.18231296539307</t>
   </si>
   <si>
     <t xml:space="preserve">7.41503047943115</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">7.5747389793396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12687397003174</t>
+    <t xml:space="preserve">8.12687301635742</t>
   </si>
   <si>
     <t xml:space="preserve">8.35046482086182</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">7.81658220291138</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03104972839355</t>
+    <t xml:space="preserve">8.03104877471924</t>
   </si>
   <si>
     <t xml:space="preserve">7.89415502548218</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">7.34658432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52910852432251</t>
+    <t xml:space="preserve">7.52910804748535</t>
   </si>
   <si>
     <t xml:space="preserve">7.5929913520813</t>
@@ -4118,19 +4118,19 @@
     <t xml:space="preserve">7.23706960678101</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48415899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70775032043457</t>
+    <t xml:space="preserve">6.48415851593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70775079727173</t>
   </si>
   <si>
     <t xml:space="preserve">6.21037292480469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27425718307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0506649017334</t>
+    <t xml:space="preserve">6.27425670623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05066537857056</t>
   </si>
   <si>
     <t xml:space="preserve">6.04610204696655</t>
@@ -4160,13 +4160,13 @@
     <t xml:space="preserve">6.43396520614624</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27881956100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32445049285889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39746046066284</t>
+    <t xml:space="preserve">6.2788200378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32445001602173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39745998382568</t>
   </si>
   <si>
     <t xml:space="preserve">6.58910989761353</t>
@@ -4187,7 +4187,7 @@
     <t xml:space="preserve">6.65755701065063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79901266098022</t>
+    <t xml:space="preserve">6.79901218414307</t>
   </si>
   <si>
     <t xml:space="preserve">7.09105062484741</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">6.83095455169678</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94959449768066</t>
+    <t xml:space="preserve">6.94959497451782</t>
   </si>
   <si>
     <t xml:space="preserve">7.07279825210571</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">7.28726387023926</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93978595733643</t>
+    <t xml:space="preserve">7.93978691101074</t>
   </si>
   <si>
     <t xml:space="preserve">8.17706775665283</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12231063842773</t>
+    <t xml:space="preserve">8.12230968475342</t>
   </si>
   <si>
     <t xml:space="preserve">7.78920412063599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69794273376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76638889312744</t>
+    <t xml:space="preserve">7.69794321060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7663893699646</t>
   </si>
   <si>
     <t xml:space="preserve">7.72988414764404</t>
@@ -4244,13 +4244,13 @@
     <t xml:space="preserve">7.66600036621094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77095317840576</t>
+    <t xml:space="preserve">7.7709527015686</t>
   </si>
   <si>
     <t xml:space="preserve">7.7116322517395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91697216033936</t>
+    <t xml:space="preserve">7.9169716835022</t>
   </si>
   <si>
     <t xml:space="preserve">7.86677694320679</t>
@@ -4262,22 +4262,22 @@
     <t xml:space="preserve">7.57017517089844</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62949562072754</t>
+    <t xml:space="preserve">7.62949514389038</t>
   </si>
   <si>
     <t xml:space="preserve">7.63405895233154</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55192279815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31464290618896</t>
+    <t xml:space="preserve">7.5519232749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31464242935181</t>
   </si>
   <si>
     <t xml:space="preserve">7.28270101547241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17774963378906</t>
+    <t xml:space="preserve">7.1777491569519</t>
   </si>
   <si>
     <t xml:space="preserve">7.04998302459717</t>
@@ -4292,22 +4292,22 @@
     <t xml:space="preserve">7.51998138427734</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45609855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46978855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59755373001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79376745223999</t>
+    <t xml:space="preserve">7.4560980796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46978807449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59755420684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79376792907715</t>
   </si>
   <si>
     <t xml:space="preserve">7.88959360122681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38697052001953</t>
+    <t xml:space="preserve">8.38696956634521</t>
   </si>
   <si>
     <t xml:space="preserve">8.34590244293213</t>
@@ -4316,7 +4316,7 @@
     <t xml:space="preserve">8.36871719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81589984893799</t>
+    <t xml:space="preserve">8.8159008026123</t>
   </si>
   <si>
     <t xml:space="preserve">8.94366836547852</t>
@@ -4334,7 +4334,7 @@
     <t xml:space="preserve">8.8067741394043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98017311096191</t>
+    <t xml:space="preserve">8.9801721572876</t>
   </si>
   <si>
     <t xml:space="preserve">8.62425136566162</t>
@@ -4343,10 +4343,10 @@
     <t xml:space="preserve">8.8432788848877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89347362518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77939510345459</t>
+    <t xml:space="preserve">8.89347457885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77939605712891</t>
   </si>
   <si>
     <t xml:space="preserve">8.7292013168335</t>
@@ -4361,16 +4361,16 @@
     <t xml:space="preserve">8.51473617553711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41891288757324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40978622436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44172763824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22726154327393</t>
+    <t xml:space="preserve">8.41891193389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40978527069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44172668457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22726249694824</t>
   </si>
   <si>
     <t xml:space="preserve">8.21813488006592</t>
@@ -4379,10 +4379,10 @@
     <t xml:space="preserve">8.25007629394531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24551391601562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09949493408203</t>
+    <t xml:space="preserve">8.24551296234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09949398040771</t>
   </si>
   <si>
     <t xml:space="preserve">8.00367069244385</t>
@@ -4391,13 +4391,13 @@
     <t xml:space="preserve">7.99910688400269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83483505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6888165473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51085472106934</t>
+    <t xml:space="preserve">7.83483457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68881607055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51085519790649</t>
   </si>
   <si>
     <t xml:space="preserve">8.00823307037354</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">8.04017448425293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09493255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.08580493927002</t>
+    <t xml:space="preserve">8.09493160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.08580589294434</t>
   </si>
   <si>
     <t xml:space="preserve">8.15425300598145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96716451644897</t>
+    <t xml:space="preserve">7.96716499328613</t>
   </si>
   <si>
     <t xml:space="preserve">7.12755537033081</t>
@@ -4442,13 +4442,13 @@
     <t xml:space="preserve">7.35114765167236</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24163293838501</t>
+    <t xml:space="preserve">7.24163246154785</t>
   </si>
   <si>
     <t xml:space="preserve">7.11842918395996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01804161071777</t>
+    <t xml:space="preserve">7.01804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.00435209274292</t>
@@ -4457,19 +4457,19 @@
     <t xml:space="preserve">6.73969221115112</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86745882034302</t>
+    <t xml:space="preserve">6.86745929718018</t>
   </si>
   <si>
     <t xml:space="preserve">7.13211822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88114786148071</t>
+    <t xml:space="preserve">6.88114833831787</t>
   </si>
   <si>
     <t xml:space="preserve">6.89483785629272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78075981140137</t>
+    <t xml:space="preserve">6.78076028823853</t>
   </si>
   <si>
     <t xml:space="preserve">6.95415782928467</t>
@@ -4484,13 +4484,13 @@
     <t xml:space="preserve">6.90852737426758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76707077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62561559677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62105178833008</t>
+    <t xml:space="preserve">6.76707124710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62561511993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62105226516724</t>
   </si>
   <si>
     <t xml:space="preserve">6.43852758407593</t>
@@ -29400,7 +29400,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G894" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -29426,7 +29426,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G895" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -29452,7 +29452,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G896" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -29478,7 +29478,7 @@
         <v>16.8600006103516</v>
       </c>
       <c r="G897" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -29504,7 +29504,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G898" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -29530,7 +29530,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G899" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -29556,7 +29556,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G900" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -29582,7 +29582,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G901" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -29608,7 +29608,7 @@
         <v>16.0100002288818</v>
       </c>
       <c r="G902" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -29634,7 +29634,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G903" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -29660,7 +29660,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G904" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -29712,7 +29712,7 @@
         <v>16.9099998474121</v>
       </c>
       <c r="G906" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -29738,7 +29738,7 @@
         <v>16.5599994659424</v>
       </c>
       <c r="G907" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -29764,7 +29764,7 @@
         <v>16.3099994659424</v>
       </c>
       <c r="G908" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -29790,7 +29790,7 @@
         <v>16.2299995422363</v>
       </c>
       <c r="G909" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -29816,7 +29816,7 @@
         <v>15.5299997329712</v>
       </c>
       <c r="G910" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -29842,7 +29842,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -29868,7 +29868,7 @@
         <v>16</v>
       </c>
       <c r="G912" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -29894,7 +29894,7 @@
         <v>15.8800001144409</v>
       </c>
       <c r="G913" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -29920,7 +29920,7 @@
         <v>15.4799995422363</v>
       </c>
       <c r="G914" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -29946,7 +29946,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G915" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -29972,7 +29972,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G916" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -29998,7 +29998,7 @@
         <v>14.289999961853</v>
       </c>
       <c r="G917" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -30024,7 +30024,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G918" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -30050,7 +30050,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G919" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -30076,7 +30076,7 @@
         <v>12.8599996566772</v>
       </c>
       <c r="G920" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -30102,7 +30102,7 @@
         <v>12.3900003433228</v>
       </c>
       <c r="G921" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -30128,7 +30128,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G922" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -30154,7 +30154,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G923" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -30180,7 +30180,7 @@
         <v>12.6300001144409</v>
       </c>
       <c r="G924" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -30206,7 +30206,7 @@
         <v>12.960000038147</v>
       </c>
       <c r="G925" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -30232,7 +30232,7 @@
         <v>13.1099996566772</v>
       </c>
       <c r="G926" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -30258,7 +30258,7 @@
         <v>12.7799997329712</v>
       </c>
       <c r="G927" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -30284,7 +30284,7 @@
         <v>12.6700000762939</v>
       </c>
       <c r="G928" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -30310,7 +30310,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G929" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -30336,7 +30336,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G930" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -30362,7 +30362,7 @@
         <v>12.6400003433228</v>
       </c>
       <c r="G931" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -30388,7 +30388,7 @@
         <v>12.9899997711182</v>
       </c>
       <c r="G932" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -30414,7 +30414,7 @@
         <v>12.7399997711182</v>
       </c>
       <c r="G933" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -30440,7 +30440,7 @@
         <v>12.5299997329712</v>
       </c>
       <c r="G934" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -30466,7 +30466,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G935" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -30492,7 +30492,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G936" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -30518,7 +30518,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G937" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -30544,7 +30544,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G938" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -30570,7 +30570,7 @@
         <v>13.7299995422363</v>
       </c>
       <c r="G939" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -30596,7 +30596,7 @@
         <v>13.789999961853</v>
       </c>
       <c r="G940" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -30622,7 +30622,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G941" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -30648,7 +30648,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G942" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -30674,7 +30674,7 @@
         <v>13.9799995422363</v>
       </c>
       <c r="G943" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -30700,7 +30700,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G944" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -30726,7 +30726,7 @@
         <v>13.8299999237061</v>
       </c>
       <c r="G945" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -30752,7 +30752,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G946" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -30778,7 +30778,7 @@
         <v>13.8800001144409</v>
       </c>
       <c r="G947" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -30804,7 +30804,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G948" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -30830,7 +30830,7 @@
         <v>13.5100002288818</v>
       </c>
       <c r="G949" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -30856,7 +30856,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G950" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -30882,7 +30882,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G951" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -30908,7 +30908,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G952" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -30934,7 +30934,7 @@
         <v>13.1700000762939</v>
       </c>
       <c r="G953" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -30960,7 +30960,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G954" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -30986,7 +30986,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G955" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -31012,7 +31012,7 @@
         <v>12.5200004577637</v>
       </c>
       <c r="G956" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -31038,7 +31038,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G957" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -31064,7 +31064,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G958" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -31090,7 +31090,7 @@
         <v>12.6199998855591</v>
       </c>
       <c r="G959" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -31116,7 +31116,7 @@
         <v>12.8900003433228</v>
       </c>
       <c r="G960" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -31142,7 +31142,7 @@
         <v>12.9799995422363</v>
       </c>
       <c r="G961" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -31168,7 +31168,7 @@
         <v>13.2600002288818</v>
       </c>
       <c r="G962" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -31194,7 +31194,7 @@
         <v>13.0699996948242</v>
       </c>
       <c r="G963" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -31220,7 +31220,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G964" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -31246,7 +31246,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G965" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -31272,7 +31272,7 @@
         <v>13.0900001525879</v>
       </c>
       <c r="G966" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -31298,7 +31298,7 @@
         <v>12.9200000762939</v>
       </c>
       <c r="G967" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -31324,7 +31324,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G968" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -31350,7 +31350,7 @@
         <v>12.9399995803833</v>
       </c>
       <c r="G969" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -31376,7 +31376,7 @@
         <v>13.0200004577637</v>
       </c>
       <c r="G970" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -31402,7 +31402,7 @@
         <v>12.8800001144409</v>
       </c>
       <c r="G971" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -31428,7 +31428,7 @@
         <v>13.2299995422363</v>
       </c>
       <c r="G972" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -31454,7 +31454,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G973" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -31480,7 +31480,7 @@
         <v>13.7399997711182</v>
       </c>
       <c r="G974" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -31506,7 +31506,7 @@
         <v>13.7200002670288</v>
       </c>
       <c r="G975" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -31532,7 +31532,7 @@
         <v>13.8699998855591</v>
       </c>
       <c r="G976" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -31558,7 +31558,7 @@
         <v>14.1499996185303</v>
       </c>
       <c r="G977" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -31584,7 +31584,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G978" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -31610,7 +31610,7 @@
         <v>15.5</v>
       </c>
       <c r="G979" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -31636,7 +31636,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G980" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -31662,7 +31662,7 @@
         <v>15.8699998855591</v>
       </c>
       <c r="G981" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -31688,7 +31688,7 @@
         <v>16.0599994659424</v>
       </c>
       <c r="G982" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -31714,7 +31714,7 @@
         <v>15.9099998474121</v>
       </c>
       <c r="G983" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -31740,7 +31740,7 @@
         <v>16.9300003051758</v>
       </c>
       <c r="G984" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -31792,7 +31792,7 @@
         <v>16.2700004577637</v>
       </c>
       <c r="G986" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -31844,7 +31844,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G988" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -31870,7 +31870,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -31896,7 +31896,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G990" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -31922,7 +31922,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G991" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -31948,7 +31948,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G992" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -31974,7 +31974,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G993" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -32000,7 +32000,7 @@
         <v>16.9699993133545</v>
       </c>
       <c r="G994" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -32026,7 +32026,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G995" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -32052,7 +32052,7 @@
         <v>17.5300006866455</v>
       </c>
       <c r="G996" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -32078,7 +32078,7 @@
         <v>18.2099990844727</v>
       </c>
       <c r="G997" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -32104,7 +32104,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G998" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -32130,7 +32130,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G999" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -32156,7 +32156,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G1000" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -32208,7 +32208,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1002" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -32234,7 +32234,7 @@
         <v>17.25</v>
       </c>
       <c r="G1003" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -32286,7 +32286,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1005" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -32312,7 +32312,7 @@
         <v>17.7900009155273</v>
       </c>
       <c r="G1006" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -32338,7 +32338,7 @@
         <v>17.9899997711182</v>
       </c>
       <c r="G1007" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -32364,7 +32364,7 @@
         <v>18.3700008392334</v>
       </c>
       <c r="G1008" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -32390,7 +32390,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1009" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -32416,7 +32416,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1010" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -32442,7 +32442,7 @@
         <v>16.9899997711182</v>
       </c>
       <c r="G1011" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -32468,7 +32468,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1012" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -32494,7 +32494,7 @@
         <v>16.8299999237061</v>
       </c>
       <c r="G1013" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -32520,7 +32520,7 @@
         <v>16.9400005340576</v>
       </c>
       <c r="G1014" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -32546,7 +32546,7 @@
         <v>16.8700008392334</v>
       </c>
       <c r="G1015" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -32572,7 +32572,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1016" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -32624,7 +32624,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1018" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -32650,7 +32650,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1019" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -32676,7 +32676,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1020" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -32702,7 +32702,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1021" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -32728,7 +32728,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1022" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -32754,7 +32754,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1023" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -32806,7 +32806,7 @@
         <v>17.0100002288818</v>
       </c>
       <c r="G1025" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -32884,7 +32884,7 @@
         <v>17.4099998474121</v>
       </c>
       <c r="G1028" t="s">
-        <v>647</v>
+        <v>674</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -32910,7 +32910,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1029" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -32936,7 +32936,7 @@
         <v>16.8899993896484</v>
       </c>
       <c r="G1030" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -32962,7 +32962,7 @@
         <v>17.0300006866455</v>
       </c>
       <c r="G1031" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32988,7 +32988,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1032" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -33014,7 +33014,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1033" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -33040,7 +33040,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1034" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -33066,7 +33066,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1035" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -33092,7 +33092,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1036" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -33118,7 +33118,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1037" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -33144,7 +33144,7 @@
         <v>15.789999961853</v>
       </c>
       <c r="G1038" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -33170,7 +33170,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G1039" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -33196,7 +33196,7 @@
         <v>15.9300003051758</v>
       </c>
       <c r="G1040" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -33222,7 +33222,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -33248,7 +33248,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1042" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -33274,7 +33274,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1043" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -33300,7 +33300,7 @@
         <v>16.7900009155273</v>
       </c>
       <c r="G1044" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -33326,7 +33326,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1045" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -33352,7 +33352,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1046" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -33378,7 +33378,7 @@
         <v>16.8400001525879</v>
       </c>
       <c r="G1047" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -33404,7 +33404,7 @@
         <v>17.0499992370605</v>
       </c>
       <c r="G1048" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -33430,7 +33430,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G1049" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -33456,7 +33456,7 @@
         <v>16.6700000762939</v>
       </c>
       <c r="G1050" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -33482,7 +33482,7 @@
         <v>16.1599998474121</v>
       </c>
       <c r="G1051" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -33508,7 +33508,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G1052" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -33534,7 +33534,7 @@
         <v>14.75</v>
       </c>
       <c r="G1053" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -33560,7 +33560,7 @@
         <v>14.4899997711182</v>
       </c>
       <c r="G1054" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -33586,7 +33586,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1055" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -33612,7 +33612,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1056" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -33638,7 +33638,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1057" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -33664,7 +33664,7 @@
         <v>13.460000038147</v>
       </c>
       <c r="G1058" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -33690,7 +33690,7 @@
         <v>13.4399995803833</v>
       </c>
       <c r="G1059" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -33716,7 +33716,7 @@
         <v>12.9300003051758</v>
       </c>
       <c r="G1060" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -33742,7 +33742,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1061" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -33768,7 +33768,7 @@
         <v>12.1300001144409</v>
       </c>
       <c r="G1062" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -33794,7 +33794,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G1063" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -33820,7 +33820,7 @@
         <v>11.0699996948242</v>
       </c>
       <c r="G1064" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -33846,7 +33846,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1065" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -33872,7 +33872,7 @@
         <v>9.49499988555908</v>
       </c>
       <c r="G1066" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -33898,7 +33898,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1067" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -33924,7 +33924,7 @@
         <v>9.71500015258789</v>
       </c>
       <c r="G1068" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -33950,7 +33950,7 @@
         <v>9.76500034332275</v>
       </c>
       <c r="G1069" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -33976,7 +33976,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G1070" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -34002,7 +34002,7 @@
         <v>9</v>
       </c>
       <c r="G1071" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -34028,7 +34028,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G1072" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -34054,7 +34054,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G1073" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -34080,7 +34080,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G1074" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -34106,7 +34106,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1075" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -34132,7 +34132,7 @@
         <v>11.25</v>
       </c>
       <c r="G1076" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -34158,7 +34158,7 @@
         <v>11.0900001525879</v>
       </c>
       <c r="G1077" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -34184,7 +34184,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1078" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -34210,7 +34210,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1079" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -34236,7 +34236,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1080" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -34262,7 +34262,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G1081" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -34288,7 +34288,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G1082" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -34314,7 +34314,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1083" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -34340,7 +34340,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1084" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -34366,7 +34366,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1085" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -34392,7 +34392,7 @@
         <v>11.8000001907349</v>
       </c>
       <c r="G1086" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -34418,7 +34418,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1087" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -34444,7 +34444,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1088" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -34470,7 +34470,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1089" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -34496,7 +34496,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G1090" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -34522,7 +34522,7 @@
         <v>11.8100004196167</v>
       </c>
       <c r="G1091" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -34548,7 +34548,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1092" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -34574,7 +34574,7 @@
         <v>12.0900001525879</v>
       </c>
       <c r="G1093" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -34600,7 +34600,7 @@
         <v>12.1199998855591</v>
       </c>
       <c r="G1094" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -34626,7 +34626,7 @@
         <v>12.25</v>
       </c>
       <c r="G1095" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -34652,7 +34652,7 @@
         <v>12.8400001525879</v>
       </c>
       <c r="G1096" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -34678,7 +34678,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G1097" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -34704,7 +34704,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -34730,7 +34730,7 @@
         <v>12.5799999237061</v>
       </c>
       <c r="G1099" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -34756,7 +34756,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1100" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -34782,7 +34782,7 @@
         <v>11.5799999237061</v>
       </c>
       <c r="G1101" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -34808,7 +34808,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1102" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -34834,7 +34834,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G1103" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -34860,7 +34860,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G1104" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -34886,7 +34886,7 @@
         <v>11.1700000762939</v>
       </c>
       <c r="G1105" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -34912,7 +34912,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G1106" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -34938,7 +34938,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1107" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -34964,7 +34964,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G1108" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -34990,7 +34990,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G1109" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -35016,7 +35016,7 @@
         <v>11</v>
       </c>
       <c r="G1110" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -35042,7 +35042,7 @@
         <v>11</v>
       </c>
       <c r="G1111" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -35068,7 +35068,7 @@
         <v>10.4099998474121</v>
       </c>
       <c r="G1112" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -35094,7 +35094,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G1113" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -35120,7 +35120,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G1114" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -35146,7 +35146,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1115" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -35172,7 +35172,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1116" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -35198,7 +35198,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1117" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -35224,7 +35224,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1118" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -35250,7 +35250,7 @@
         <v>11.3100004196167</v>
       </c>
       <c r="G1119" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -35276,7 +35276,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1120" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -35302,7 +35302,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1121" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -35328,7 +35328,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1122" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -35354,7 +35354,7 @@
         <v>11.4899997711182</v>
       </c>
       <c r="G1123" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -35380,7 +35380,7 @@
         <v>13.1400003433228</v>
       </c>
       <c r="G1124" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -35406,7 +35406,7 @@
         <v>12.7200002670288</v>
       </c>
       <c r="G1125" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -35432,7 +35432,7 @@
         <v>12.3800001144409</v>
       </c>
       <c r="G1126" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -35458,7 +35458,7 @@
         <v>12.0200004577637</v>
       </c>
       <c r="G1127" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -35484,7 +35484,7 @@
         <v>11.289999961853</v>
       </c>
       <c r="G1128" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -35510,7 +35510,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1129" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -35536,7 +35536,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G1130" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -35562,7 +35562,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G1131" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -35588,7 +35588,7 @@
         <v>11.6499996185303</v>
       </c>
       <c r="G1132" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -35614,7 +35614,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1133" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -35640,7 +35640,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1134" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -35666,7 +35666,7 @@
         <v>11.5100002288818</v>
       </c>
       <c r="G1135" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -35692,7 +35692,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1136" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -35718,7 +35718,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1137" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -35744,7 +35744,7 @@
         <v>11.460000038147</v>
       </c>
       <c r="G1138" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -35770,7 +35770,7 @@
         <v>11.3299999237061</v>
       </c>
       <c r="G1139" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -35796,7 +35796,7 @@
         <v>11.1300001144409</v>
       </c>
       <c r="G1140" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -35822,7 +35822,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G1141" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -35848,7 +35848,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G1142" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -35874,7 +35874,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G1143" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -35900,7 +35900,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G1144" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -35926,7 +35926,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1145" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -35952,7 +35952,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1146" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -35978,7 +35978,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G1147" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -36004,7 +36004,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1148" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -36030,7 +36030,7 @@
         <v>10.289999961853</v>
       </c>
       <c r="G1149" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -36056,7 +36056,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1150" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -36082,7 +36082,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G1151" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -36108,7 +36108,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1152" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -36134,7 +36134,7 @@
         <v>10.5299997329712</v>
       </c>
       <c r="G1153" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -36160,7 +36160,7 @@
         <v>10.710000038147</v>
       </c>
       <c r="G1154" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -36186,7 +36186,7 @@
         <v>10.5100002288818</v>
       </c>
       <c r="G1155" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -36212,7 +36212,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G1156" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -36238,7 +36238,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1157" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -36264,7 +36264,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1158" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -36290,7 +36290,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G1159" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -36316,7 +36316,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G1160" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -36342,7 +36342,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="G1161" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -36368,7 +36368,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G1162" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -36394,7 +36394,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1163" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -36420,7 +36420,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1164" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -36446,7 +36446,7 @@
         <v>12.5600004196167</v>
       </c>
       <c r="G1165" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -36472,7 +36472,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G1166" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -36498,7 +36498,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G1167" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -36524,7 +36524,7 @@
         <v>13.1199998855591</v>
       </c>
       <c r="G1168" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -36550,7 +36550,7 @@
         <v>12.6800003051758</v>
       </c>
       <c r="G1169" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -36576,7 +36576,7 @@
         <v>12.460000038147</v>
       </c>
       <c r="G1170" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -36602,7 +36602,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1171" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -36628,7 +36628,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G1172" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -36654,7 +36654,7 @@
         <v>12.0699996948242</v>
       </c>
       <c r="G1173" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -36680,7 +36680,7 @@
         <v>11.6700000762939</v>
       </c>
       <c r="G1174" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -36706,7 +36706,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1175" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -36732,7 +36732,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1176" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -36758,7 +36758,7 @@
         <v>11.5900001525879</v>
       </c>
       <c r="G1177" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -36784,7 +36784,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G1178" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -36810,7 +36810,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1179" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -36836,7 +36836,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1180" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -36862,7 +36862,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1181" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -36888,7 +36888,7 @@
         <v>11.5699996948242</v>
       </c>
       <c r="G1182" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -36914,7 +36914,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1183" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -36940,7 +36940,7 @@
         <v>11.4700002670288</v>
       </c>
       <c r="G1184" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -36966,7 +36966,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>910</v>
+        <v>830</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -37122,7 +37122,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G1191" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -37200,7 +37200,7 @@
         <v>11.7700004577637</v>
       </c>
       <c r="G1194" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -37226,7 +37226,7 @@
         <v>11.9300003051758</v>
       </c>
       <c r="G1195" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -37382,7 +37382,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G1201" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -37538,7 +37538,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G1207" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -37772,7 +37772,7 @@
         <v>11.9499998092651</v>
       </c>
       <c r="G1216" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -37798,7 +37798,7 @@
         <v>11.6300001144409</v>
       </c>
       <c r="G1217" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -37980,7 +37980,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G1224" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -38318,7 +38318,7 @@
         <v>11.3699998855591</v>
       </c>
       <c r="G1237" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -73322,7 +73322,7 @@
     </row>
     <row r="2584">
       <c r="A2584" s="1" t="n">
-        <v>46084.6909953704</v>
+        <v>46084.3333333333</v>
       </c>
       <c r="B2584" t="n">
         <v>100013</v>
@@ -73343,6 +73343,32 @@
         <v>1863</v>
       </c>
       <c r="H2584" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2585">
+      <c r="A2585" s="1" t="n">
+        <v>46085.69125</v>
+      </c>
+      <c r="B2585" t="n">
+        <v>25011</v>
+      </c>
+      <c r="C2585" t="n">
+        <v>4.11999988555908</v>
+      </c>
+      <c r="D2585" t="n">
+        <v>4.03000020980835</v>
+      </c>
+      <c r="E2585" t="n">
+        <v>4.06500005722046</v>
+      </c>
+      <c r="F2585" t="n">
+        <v>4.1100001335144</v>
+      </c>
+      <c r="G2585" t="s">
+        <v>1933</v>
+      </c>
+      <c r="H2585" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/DAL.MI.xlsx
+++ b/data/DAL.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1941" uniqueCount="1941">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1942" uniqueCount="1942">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7608814239502</t>
+    <t xml:space="preserve">12.7608823776245</t>
   </si>
   <si>
     <t xml:space="preserve">DAL.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7846279144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7767114639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4758968353271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9930114746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8742704391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2700786590576</t>
+    <t xml:space="preserve">12.7846298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7767124176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4758977890015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9930124282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8742685317993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2700777053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.5233945846558</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9746160507202</t>
+    <t xml:space="preserve">12.9746189117432</t>
   </si>
   <si>
     <t xml:space="preserve">12.5075616836548</t>
@@ -74,46 +74,46 @@
     <t xml:space="preserve">12.4125690460205</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6738023757935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0563411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3729887008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.175085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3413238525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1909151077271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7713565826416</t>
+    <t xml:space="preserve">12.6738042831421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.056342124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3729867935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1750841140747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3413228988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1909160614014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7713575363159</t>
   </si>
   <si>
     <t xml:space="preserve">11.6367835998535</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9850969314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1380634307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9955720901489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4626264572144</t>
+    <t xml:space="preserve">11.9850959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1380643844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9955730438232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4626274108887</t>
   </si>
   <si>
     <t xml:space="preserve">11.1064004898071</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4942922592163</t>
+    <t xml:space="preserve">11.4942932128906</t>
   </si>
   <si>
     <t xml:space="preserve">11.5417890548706</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">11.8584356307983</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5180406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7159452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8346872329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6763639450073</t>
+    <t xml:space="preserve">11.5180397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7159461975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8346881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.676362991333</t>
   </si>
   <si>
     <t xml:space="preserve">11.6684474945068</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3992986679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1855611801147</t>
+    <t xml:space="preserve">11.3992967605591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1855602264404</t>
   </si>
   <si>
     <t xml:space="preserve">11.9692630767822</t>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">12.3888206481934</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4284009933472</t>
+    <t xml:space="preserve">12.4284019470215</t>
   </si>
   <si>
     <t xml:space="preserve">12.2304964065552</t>
@@ -161,43 +161,43 @@
     <t xml:space="preserve">12.1117544174194</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1513376235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1196727752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8242120742798</t>
+    <t xml:space="preserve">12.1513357162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1196718215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8242111206055</t>
   </si>
   <si>
     <t xml:space="preserve">12.9825344085693</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9508695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1408567428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2754325866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3704261779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3387622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4575042724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5762481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5999984741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.362509727478</t>
+    <t xml:space="preserve">12.950870513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1408586502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2754306793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3704252243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3387613296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4575033187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5762462615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5999946594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3625087738037</t>
   </si>
   <si>
     <t xml:space="preserve">13.0379486083984</t>
@@ -206,28 +206,28 @@
     <t xml:space="preserve">12.7529649734497</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1171092987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1091909408569</t>
+    <t xml:space="preserve">13.1171083450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1091928482056</t>
   </si>
   <si>
     <t xml:space="preserve">13.196270942688</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9904508590698</t>
+    <t xml:space="preserve">12.9904499053955</t>
   </si>
   <si>
     <t xml:space="preserve">13.0221147537231</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0933609008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0775279998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0300302505493</t>
+    <t xml:space="preserve">13.0933599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0775289535522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0300312042236</t>
   </si>
   <si>
     <t xml:space="preserve">12.6975517272949</t>
@@ -236,19 +236,19 @@
     <t xml:space="preserve">12.6025562286377</t>
   </si>
   <si>
-    <t xml:space="preserve">12.650053024292</t>
+    <t xml:space="preserve">12.6500549316406</t>
   </si>
   <si>
     <t xml:space="preserve">12.8637914657593</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5867233276367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.467981338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3650722503662</t>
+    <t xml:space="preserve">12.5867252349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4679822921753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3650712966919</t>
   </si>
   <si>
     <t xml:space="preserve">12.5788097381592</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">12.7286968231201</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1493892669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1091594696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9884691238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9241027832031</t>
+    <t xml:space="preserve">12.1493883132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1091585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9884700775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9241008758545</t>
   </si>
   <si>
     <t xml:space="preserve">12.2218017578125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.22984790802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2942161560059</t>
+    <t xml:space="preserve">12.2298488616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2942152023315</t>
   </si>
   <si>
     <t xml:space="preserve">12.2620306015015</t>
@@ -287,22 +287,22 @@
     <t xml:space="preserve">12.4953651428223</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7126035690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8091554641724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8735237121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0263977050781</t>
+    <t xml:space="preserve">12.7126045227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8091564178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8735227584839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0263967514038</t>
   </si>
   <si>
     <t xml:space="preserve">12.8252477645874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8654775619507</t>
+    <t xml:space="preserve">12.865478515625</t>
   </si>
   <si>
     <t xml:space="preserve">12.8172025680542</t>
@@ -311,136 +311,136 @@
     <t xml:space="preserve">12.5999622344971</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3666276931763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3103075027466</t>
+    <t xml:space="preserve">12.3666296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3103084564209</t>
   </si>
   <si>
     <t xml:space="preserve">11.7390451431274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4011154174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2884721755981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8781280517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0792779922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6022624969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0689306259155</t>
+    <t xml:space="preserve">11.4011144638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2884702682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8781299591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0792770385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6022634506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0689296722412</t>
   </si>
   <si>
     <t xml:space="preserve">11.6103105545044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3689317703247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4896192550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7574377059937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0735340118408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4597368240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0229549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6424932479858</t>
+    <t xml:space="preserve">11.3689308166504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4896202087402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7574396133423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0735321044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.45973777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0229539871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6424922943115</t>
   </si>
   <si>
     <t xml:space="preserve">11.6344470977783</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2321491241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9827241897583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9264039993286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2160577774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7229518890381</t>
+    <t xml:space="preserve">11.2321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9827251434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9264030456543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2160568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7229528427124</t>
   </si>
   <si>
     <t xml:space="preserve">11.747091293335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5700807571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8919162750244</t>
+    <t xml:space="preserve">11.5700798034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8919172286987</t>
   </si>
   <si>
     <t xml:space="preserve">11.5861721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8758268356323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7953662872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1896171569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4309968948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8896169662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0505332946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9942121505737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1229476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1551322937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9861660003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0746726989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3482351303101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2493801116943</t>
+    <t xml:space="preserve">11.875825881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7953672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1896181106567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4309978485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8896160125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0505342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.994213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1229486465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1551313400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9861669540405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0746717453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3482360839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.249382019043</t>
   </si>
   <si>
     <t xml:space="preserve">13.9194974899292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3459348678589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.855128288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1608781814575</t>
+    <t xml:space="preserve">14.3459339141846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8551292419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1608762741089</t>
   </si>
   <si>
     <t xml:space="preserve">14.6919088363647</t>
@@ -452,40 +452,40 @@
     <t xml:space="preserve">14.6275415420532</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8206443786621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.603404045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4022550582886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3137493133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6516790390015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7562742233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1183443069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1505289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1263904571533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.08616065979</t>
+    <t xml:space="preserve">14.8206434249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6034049987793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4022560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3137512207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6516809463501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.756275177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1183452606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1505308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.126389503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0861625671387</t>
   </si>
   <si>
     <t xml:space="preserve">15.0459327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">15.295355796814</t>
+    <t xml:space="preserve">15.2953567504883</t>
   </si>
   <si>
     <t xml:space="preserve">15.4240922927856</t>
@@ -494,25 +494,25 @@
     <t xml:space="preserve">15.4562740325928</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3597211837769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2873086929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8689222335815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7240943908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8367357254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.788459777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8930616378784</t>
+    <t xml:space="preserve">15.3597249984741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2873106002808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8689184188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7240924835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8367376327515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7884588241577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8930587768555</t>
   </si>
   <si>
     <t xml:space="preserve">15.4884586334229</t>
@@ -530,112 +530,112 @@
     <t xml:space="preserve">15.3919067382812</t>
   </si>
   <si>
-    <t xml:space="preserve">15.255126953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1666202545166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5286893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2229423522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0137481689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8850116729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.198802947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3275375366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.311448097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3677701950073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3034009933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.182713508606</t>
+    <t xml:space="preserve">15.2551250457764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1666212081909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5286855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2229413986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0137500762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8850126266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1988039016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3275394439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3114500045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3677682876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3034038543701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827144622803</t>
   </si>
   <si>
     <t xml:space="preserve">14.6436357498169</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9654712677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2470827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8286905288696</t>
+    <t xml:space="preserve">14.9654722213745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2470798492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8286914825439</t>
   </si>
   <si>
     <t xml:space="preserve">14.5390377044678</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5551271438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1126012802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4263935089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2815675735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4827136993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2171993255615</t>
+    <t xml:space="preserve">14.5551280975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1126003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4263906478882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2815656661987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4827156066895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2171974182129</t>
   </si>
   <si>
     <t xml:space="preserve">14.4103012084961</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5631742477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4585733413696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3057050704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1045560836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.951681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6781187057495</t>
+    <t xml:space="preserve">14.563175201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4585752487183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.305703163147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1045551300049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3217935562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9516801834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6781177520752</t>
   </si>
   <si>
     <t xml:space="preserve">13.4045572280884</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3643283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1873140335083</t>
+    <t xml:space="preserve">13.3643264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1873159408569</t>
   </si>
   <si>
     <t xml:space="preserve">12.9539833068848</t>
   </si>
   <si>
-    <t xml:space="preserve">13.31605052948</t>
+    <t xml:space="preserve">13.3160514831543</t>
   </si>
   <si>
     <t xml:space="preserve">13.5896129608154</t>
@@ -644,67 +644,67 @@
     <t xml:space="preserve">13.7746715545654</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9114532470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2011041641235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9999580383301</t>
+    <t xml:space="preserve">13.911452293396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2011051177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9999570846558</t>
   </si>
   <si>
     <t xml:space="preserve">14.9815654754639</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0378837585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447828292847</t>
+    <t xml:space="preserve">15.0378847122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7160491943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447818756104</t>
   </si>
   <si>
     <t xml:space="preserve">14.917197227478</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2631711959839</t>
+    <t xml:space="preserve">15.2631692886353</t>
   </si>
   <si>
     <t xml:space="preserve">15.6010999679565</t>
   </si>
   <si>
-    <t xml:space="preserve">15.552827835083</t>
+    <t xml:space="preserve">15.5528259277344</t>
   </si>
   <si>
     <t xml:space="preserve">15.5367317199707</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4643211364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3838634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6091508865356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5045528411865</t>
+    <t xml:space="preserve">15.464319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3838653564453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6091451644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5045518875122</t>
   </si>
   <si>
     <t xml:space="preserve">15.4079971313477</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1102962493896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2068481445312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8263883590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8907527923584</t>
+    <t xml:space="preserve">15.1102991104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2068500518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8263893127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8907566070557</t>
   </si>
   <si>
     <t xml:space="preserve">15.8988018035889</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">16.0114459991455</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3493766784668</t>
+    <t xml:space="preserve">16.3493747711182</t>
   </si>
   <si>
     <t xml:space="preserve">16.3010997772217</t>
@@ -725,10 +725,10 @@
     <t xml:space="preserve">16.5344333648682</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5827083587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3332843780518</t>
+    <t xml:space="preserve">16.582706451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3332805633545</t>
   </si>
   <si>
     <t xml:space="preserve">16.4539737701416</t>
@@ -740,43 +740,43 @@
     <t xml:space="preserve">16.1562728881836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9792613983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7700681686401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0919036865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0033988952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0436305999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4781093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8964996337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9769592285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0413284301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3792552947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5160388946533</t>
+    <t xml:space="preserve">15.9792594909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7700662612915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0919055938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.003396987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.043628692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4781112670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8965015411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9769611358643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0413265228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3792572021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5160369873047</t>
   </si>
   <si>
     <t xml:space="preserve">17.7735080718994</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3850021362305</t>
+    <t xml:space="preserve">18.3850002288818</t>
   </si>
   <si>
     <t xml:space="preserve">18.7470703125</t>
@@ -788,46 +788,46 @@
     <t xml:space="preserve">19.0206298828125</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2700538635254</t>
+    <t xml:space="preserve">19.2700576782227</t>
   </si>
   <si>
     <t xml:space="preserve">19.3907451629639</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4068393707275</t>
+    <t xml:space="preserve">19.4068374633789</t>
   </si>
   <si>
     <t xml:space="preserve">19.4470672607422</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7528133392334</t>
+    <t xml:space="preserve">19.7528114318848</t>
   </si>
   <si>
     <t xml:space="preserve">19.5033893585205</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6079845428467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6321239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7125835418701</t>
+    <t xml:space="preserve">19.6079864501953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6321258544922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7125797271729</t>
   </si>
   <si>
     <t xml:space="preserve">19.3827018737793</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5838470458984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3102874755859</t>
+    <t xml:space="preserve">19.5838451385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3102855682373</t>
   </si>
   <si>
     <t xml:space="preserve">19.5436191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4631595611572</t>
+    <t xml:space="preserve">19.4631614685059</t>
   </si>
   <si>
     <t xml:space="preserve">19.0689086914062</t>
@@ -839,19 +839,19 @@
     <t xml:space="preserve">18.8355751037598</t>
   </si>
   <si>
-    <t xml:space="preserve">19.028678894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9723529815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.56201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5056915283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6183319091797</t>
+    <t xml:space="preserve">19.0286769866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9723567962646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5620136260986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5056896209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6183338165283</t>
   </si>
   <si>
     <t xml:space="preserve">19.1654586791992</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">19.8171806335449</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2597103118896</t>
+    <t xml:space="preserve">20.2597064971924</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585563659668</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">20.5574073791504</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9539318084717</t>
+    <t xml:space="preserve">20.9539337158203</t>
   </si>
   <si>
     <t xml:space="preserve">21.1818695068359</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9213714599609</t>
+    <t xml:space="preserve">20.9213695526123</t>
   </si>
   <si>
     <t xml:space="preserve">21.0841808319092</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7666988372803</t>
+    <t xml:space="preserve">20.7666969299316</t>
   </si>
   <si>
     <t xml:space="preserve">21.0027751922607</t>
@@ -896,16 +896,16 @@
     <t xml:space="preserve">20.5550403594971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.489917755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3922290802002</t>
+    <t xml:space="preserve">20.4899158477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3922271728516</t>
   </si>
   <si>
     <t xml:space="preserve">20.3271026611328</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3515281677246</t>
+    <t xml:space="preserve">20.3515243530273</t>
   </si>
   <si>
     <t xml:space="preserve">20.5143413543701</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">20.9864959716797</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9946346282959</t>
+    <t xml:space="preserve">20.9946384429932</t>
   </si>
   <si>
     <t xml:space="preserve">20.937650680542</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">21.124885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">21.0353393554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8399620056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8155403137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1574459075928</t>
+    <t xml:space="preserve">21.0353374481201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8399639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8155422210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1574478149414</t>
   </si>
   <si>
     <t xml:space="preserve">20.7585582733154</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">20.5957450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3189659118652</t>
+    <t xml:space="preserve">20.318962097168</t>
   </si>
   <si>
     <t xml:space="preserve">19.8386669158936</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0828857421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1480140686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9851989746094</t>
+    <t xml:space="preserve">20.0828876495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1480121612549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9851970672607</t>
   </si>
   <si>
     <t xml:space="preserve">20.1317291259766</t>
@@ -965,88 +965,88 @@
     <t xml:space="preserve">20.3678073883057</t>
   </si>
   <si>
-    <t xml:space="preserve">20.7259941101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3108234405518</t>
+    <t xml:space="preserve">20.7259960174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3108253479004</t>
   </si>
   <si>
     <t xml:space="preserve">19.9770584106445</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3583717346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1874217987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9757633209229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8048114776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7071228027344</t>
+    <t xml:space="preserve">19.3583736419678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1874198913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9757652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8048095703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.707124710083</t>
   </si>
   <si>
     <t xml:space="preserve">19.0978717803955</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6338596343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1304321289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4804840087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5293254852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2049961090088</t>
+    <t xml:space="preserve">18.6338577270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1304340362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4804821014404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5293273925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2049980163574</t>
   </si>
   <si>
     <t xml:space="preserve">19.7816848754883</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1805725097656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2375602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.78297996521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7748394012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.905086517334</t>
+    <t xml:space="preserve">20.1805744171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2375583648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7829780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7748374938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9050884246826</t>
   </si>
   <si>
     <t xml:space="preserve">20.677152633667</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1655864715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2795543670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.0597610473633</t>
+    <t xml:space="preserve">21.1655883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2795562744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.0597591400146</t>
   </si>
   <si>
     <t xml:space="preserve">21.043478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6852931976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1004619598389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.5400562286377</t>
+    <t xml:space="preserve">20.6852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1004657745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.5400581359863</t>
   </si>
   <si>
     <t xml:space="preserve">21.4260864257812</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">21.5319156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3202629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9226665496826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7842769622803</t>
+    <t xml:space="preserve">21.3202610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9226627349854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.784273147583</t>
   </si>
   <si>
     <t xml:space="preserve">21.4993515014648</t>
   </si>
   <si>
-    <t xml:space="preserve">21.3935241699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7761325836182</t>
+    <t xml:space="preserve">21.3935279846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7761344909668</t>
   </si>
   <si>
     <t xml:space="preserve">21.6214637756348</t>
@@ -1079,64 +1079,64 @@
     <t xml:space="preserve">22.0691967010498</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7110080718994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5169277191162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9809455871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.630895614624</t>
+    <t xml:space="preserve">21.7110118865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5169296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9809436798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.6308975219727</t>
   </si>
   <si>
     <t xml:space="preserve">23.0542087554932</t>
   </si>
   <si>
-    <t xml:space="preserve">22.989086151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.200740814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1681785583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4693794250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.8601303100586</t>
+    <t xml:space="preserve">22.9890842437744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.2007389068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1681804656982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4693813323975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.8601322174072</t>
   </si>
   <si>
     <t xml:space="preserve">23.7298793792725</t>
   </si>
   <si>
-    <t xml:space="preserve">24.0310840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9659595489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.0229415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.3648490905762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9008331298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.9903812408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.599630355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5263614654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6159114837646</t>
+    <t xml:space="preserve">24.0310821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9659576416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.0229434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.3648509979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9008312225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.9903793334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5996322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5263652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6159133911133</t>
   </si>
   <si>
     <t xml:space="preserve">23.9822387695312</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">25.4394092559814</t>
   </si>
   <si>
-    <t xml:space="preserve">24.991678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0568008422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0079555511475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8777084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.8288612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6660499572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.649772644043</t>
+    <t xml:space="preserve">24.9916725158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0568027496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0079574584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8777046203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.8288631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.666051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6497707366943</t>
   </si>
   <si>
     <t xml:space="preserve">25.6999092102051</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9604053497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.480110168457</t>
+    <t xml:space="preserve">25.9604072570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.4801120758057</t>
   </si>
   <si>
     <t xml:space="preserve">25.1789073944092</t>
@@ -1184,25 +1184,25 @@
     <t xml:space="preserve">24.1613330841064</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7474555969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5765037536621</t>
+    <t xml:space="preserve">24.5602207183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7474575042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5765056610107</t>
   </si>
   <si>
     <t xml:space="preserve">25.4556922912598</t>
   </si>
   <si>
-    <t xml:space="preserve">26.277889251709</t>
+    <t xml:space="preserve">26.2778911590576</t>
   </si>
   <si>
     <t xml:space="preserve">25.984827041626</t>
   </si>
   <si>
-    <t xml:space="preserve">27.1082344055176</t>
+    <t xml:space="preserve">27.1082324981689</t>
   </si>
   <si>
     <t xml:space="preserve">27.7676258087158</t>
@@ -1211,13 +1211,13 @@
     <t xml:space="preserve">27.3850154876709</t>
   </si>
   <si>
-    <t xml:space="preserve">26.9209976196289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.5071220397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.0105457305908</t>
+    <t xml:space="preserve">26.9210014343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.5071239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.0105476379395</t>
   </si>
   <si>
     <t xml:space="preserve">26.6930637359619</t>
@@ -1229,16 +1229,16 @@
     <t xml:space="preserve">24.9102687835693</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5032405853271</t>
+    <t xml:space="preserve">24.5032386779785</t>
   </si>
   <si>
     <t xml:space="preserve">24.6172065734863</t>
   </si>
   <si>
-    <t xml:space="preserve">24.5846462249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2440338134766</t>
+    <t xml:space="preserve">24.584644317627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2440357208252</t>
   </si>
   <si>
     <t xml:space="preserve">24.8451461791992</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">24.7393169403076</t>
   </si>
   <si>
-    <t xml:space="preserve">25.1951904296875</t>
+    <t xml:space="preserve">25.1951923370361</t>
   </si>
   <si>
     <t xml:space="preserve">25.6429233551025</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">25.5859413146973</t>
   </si>
   <si>
-    <t xml:space="preserve">25.724328994751</t>
+    <t xml:space="preserve">25.7243309020996</t>
   </si>
   <si>
     <t xml:space="preserve">25.6917667388916</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5452346801758</t>
+    <t xml:space="preserve">25.5452365875244</t>
   </si>
   <si>
     <t xml:space="preserve">25.7568912506104</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">25.5208168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3172988891602</t>
+    <t xml:space="preserve">25.3173007965088</t>
   </si>
   <si>
     <t xml:space="preserve">25.3987064361572</t>
@@ -1280,55 +1280,55 @@
     <t xml:space="preserve">25.512674331665</t>
   </si>
   <si>
-    <t xml:space="preserve">25.7650318145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0499534606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.2033309936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.048656463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4625339508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3661441802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0242366790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3824253082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0893630981445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7148971557617</t>
+    <t xml:space="preserve">25.7650337219238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0499515533447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.2033290863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0486602783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.462532043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3661422729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0242404937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.3824234008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0893650054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7148952484131</t>
   </si>
   <si>
     <t xml:space="preserve">25.6836261749268</t>
   </si>
   <si>
-    <t xml:space="preserve">26.741907119751</t>
+    <t xml:space="preserve">26.7419033050537</t>
   </si>
   <si>
     <t xml:space="preserve">26.5790939331055</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3931560516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.6604995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.497688293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1313591003418</t>
+    <t xml:space="preserve">27.393159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6605014801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4976863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1313571929932</t>
   </si>
   <si>
     <t xml:space="preserve">25.602222442627</t>
@@ -1337,43 +1337,43 @@
     <t xml:space="preserve">26.2127666473389</t>
   </si>
   <si>
-    <t xml:space="preserve">26.2941703796387</t>
+    <t xml:space="preserve">26.2941741943359</t>
   </si>
   <si>
     <t xml:space="preserve">26.7826099395752</t>
   </si>
   <si>
-    <t xml:space="preserve">27.3117504119873</t>
+    <t xml:space="preserve">27.3117523193359</t>
   </si>
   <si>
     <t xml:space="preserve">27.8815937042236</t>
   </si>
   <si>
-    <t xml:space="preserve">27.2303428649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.823314666748</t>
+    <t xml:space="preserve">27.2303447723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.8233127593994</t>
   </si>
   <si>
     <t xml:space="preserve">26.6197986602783</t>
   </si>
   <si>
-    <t xml:space="preserve">26.1720638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0730800628662</t>
+    <t xml:space="preserve">26.1720657348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0730819702148</t>
   </si>
   <si>
     <t xml:space="preserve">24.6253452301025</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8519859313965</t>
+    <t xml:space="preserve">23.8519916534424</t>
   </si>
   <si>
     <t xml:space="preserve">23.9740982055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5615177154541</t>
+    <t xml:space="preserve">25.5615196228027</t>
   </si>
   <si>
     <t xml:space="preserve">25.358003616333</t>
@@ -1382,91 +1382,91 @@
     <t xml:space="preserve">25.1137828826904</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2358951568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3635520935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4218349456787</t>
+    <t xml:space="preserve">25.2358932495117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3635540008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4218311309814</t>
   </si>
   <si>
     <t xml:space="preserve">26.2534713745117</t>
   </si>
   <si>
-    <t xml:space="preserve">23.6891784667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5670680999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1887149810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6364498138428</t>
+    <t xml:space="preserve">23.6891765594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5670700073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1887130737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6364479064941</t>
   </si>
   <si>
     <t xml:space="preserve">20.7178554534912</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7002792358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.4736347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.2062892913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6540203094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.7354335784912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4273796081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8168354034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.8806648254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.450511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.3283996582031</t>
+    <t xml:space="preserve">19.7002811431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.4736366271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.2062911987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.6540260314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.7354316711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4273834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.816837310791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.8806667327881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4505100250244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.3284034729004</t>
   </si>
   <si>
     <t xml:space="preserve">21.6947288513184</t>
   </si>
   <si>
-    <t xml:space="preserve">22.4680862426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1831645965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.5901927947998</t>
+    <t xml:space="preserve">22.4680843353271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1831665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.5901947021484</t>
   </si>
   <si>
     <t xml:space="preserve">22.0203514099121</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3459796905518</t>
+    <t xml:space="preserve">22.3459777832031</t>
   </si>
   <si>
     <t xml:space="preserve">23.1600379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">22.7123050689697</t>
+    <t xml:space="preserve">22.7123031616211</t>
   </si>
   <si>
     <t xml:space="preserve">23.6077728271484</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8057384490967</t>
+    <t xml:space="preserve">25.8057403564453</t>
   </si>
   <si>
     <t xml:space="preserve">24.7067546844482</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">24.3811283111572</t>
   </si>
   <si>
-    <t xml:space="preserve">24.218318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1776142120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.2997245788574</t>
+    <t xml:space="preserve">24.2183151245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1776103973389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.2997264862061</t>
   </si>
   <si>
     <t xml:space="preserve">24.7881603240967</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">24.705394744873</t>
   </si>
   <si>
-    <t xml:space="preserve">24.1260414123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.6640129089355</t>
+    <t xml:space="preserve">24.1260395050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.6640110015869</t>
   </si>
   <si>
     <t xml:space="preserve">24.9123096466064</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">25.2019863128662</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4089012145996</t>
+    <t xml:space="preserve">25.4088973999023</t>
   </si>
   <si>
     <t xml:space="preserve">25.7813415527344</t>
@@ -1511,28 +1511,28 @@
     <t xml:space="preserve">25.7399578094482</t>
   </si>
   <si>
-    <t xml:space="preserve">25.3261337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.2779331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.1469688415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9400520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1951656341553</t>
+    <t xml:space="preserve">25.326135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.2779312133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.1469650268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9400539398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1951675415039</t>
   </si>
   <si>
     <t xml:space="preserve">25.491662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">25.5330467224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0778369903564</t>
+    <t xml:space="preserve">25.5330448150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.0778388977051</t>
   </si>
   <si>
     <t xml:space="preserve">25.3675155639648</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">25.6985759735107</t>
   </si>
   <si>
-    <t xml:space="preserve">25.2847499847412</t>
+    <t xml:space="preserve">25.2847518920898</t>
   </si>
   <si>
     <t xml:space="preserve">25.6571941375732</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">26.1537857055664</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8227233886719</t>
+    <t xml:space="preserve">25.8227252960205</t>
   </si>
   <si>
     <t xml:space="preserve">25.9468746185303</t>
@@ -1559,25 +1559,25 @@
     <t xml:space="preserve">26.0710182189941</t>
   </si>
   <si>
-    <t xml:space="preserve">25.9054908752441</t>
+    <t xml:space="preserve">25.9054889678955</t>
   </si>
   <si>
     <t xml:space="preserve">26.319314956665</t>
   </si>
   <si>
-    <t xml:space="preserve">27.0642013549805</t>
+    <t xml:space="preserve">27.0642032623291</t>
   </si>
   <si>
     <t xml:space="preserve">27.0228214263916</t>
   </si>
   <si>
-    <t xml:space="preserve">24.2501850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.6294460296631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.7535972595215</t>
+    <t xml:space="preserve">24.250186920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.6294479370117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.7535953521729</t>
   </si>
   <si>
     <t xml:space="preserve">24.0432739257812</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">23.877742767334</t>
   </si>
   <si>
-    <t xml:space="preserve">23.9191246032715</t>
+    <t xml:space="preserve">23.9191265106201</t>
   </si>
   <si>
     <t xml:space="preserve">24.2088050842285</t>
@@ -1604,28 +1604,28 @@
     <t xml:space="preserve">24.3329524993896</t>
   </si>
   <si>
-    <t xml:space="preserve">25.4502811431885</t>
+    <t xml:space="preserve">25.4502830505371</t>
   </si>
   <si>
     <t xml:space="preserve">26.5262279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">25.8641090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.0296401977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.56760597229</t>
+    <t xml:space="preserve">25.864107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.0296363830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.5676097869873</t>
   </si>
   <si>
     <t xml:space="preserve">25.5744304656982</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6089916229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.9814338684082</t>
+    <t xml:space="preserve">26.6089973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.9814357757568</t>
   </si>
   <si>
     <t xml:space="preserve">25.9882526397705</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">26.4434642791748</t>
   </si>
   <si>
-    <t xml:space="preserve">26.6503772735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.3606986999512</t>
+    <t xml:space="preserve">26.6503753662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.3606967926025</t>
   </si>
   <si>
     <t xml:space="preserve">24.4984836578369</t>
@@ -1646,28 +1646,28 @@
     <t xml:space="preserve">23.0914745330811</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7258491516113</t>
+    <t xml:space="preserve">21.72585105896</t>
   </si>
   <si>
     <t xml:space="preserve">21.4361724853516</t>
   </si>
   <si>
-    <t xml:space="preserve">21.89137840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.7740497589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.6430835723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4775543212891</t>
+    <t xml:space="preserve">21.8913803100586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.7740535736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.643087387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4775524139404</t>
   </si>
   <si>
     <t xml:space="preserve">21.105110168457</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8154315948486</t>
+    <t xml:space="preserve">20.8154335021973</t>
   </si>
   <si>
     <t xml:space="preserve">19.6981029510498</t>
@@ -1676,109 +1676,109 @@
     <t xml:space="preserve">19.8636341094971</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3602237701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2360763549805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8086166381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9395809173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9327659606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.0569114685059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9259433746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2638206481934</t>
+    <t xml:space="preserve">20.3602256774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2360782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.808614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9395790100098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9327621459961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.0569076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9259452819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.263822555542</t>
   </si>
   <si>
     <t xml:space="preserve">18.0014190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4634456634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5462093353271</t>
+    <t xml:space="preserve">17.4634437561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5462112426758</t>
   </si>
   <si>
     <t xml:space="preserve">17.6703586578369</t>
   </si>
   <si>
-    <t xml:space="preserve">17.877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2083320617676</t>
+    <t xml:space="preserve">17.8772716522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2083301544189</t>
   </si>
   <si>
     <t xml:space="preserve">18.4980087280273</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7049217224121</t>
+    <t xml:space="preserve">18.7049236297607</t>
   </si>
   <si>
     <t xml:space="preserve">18.8290710449219</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6221561431885</t>
+    <t xml:space="preserve">18.6221542358398</t>
   </si>
   <si>
     <t xml:space="preserve">18.8704509735107</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3670406341553</t>
+    <t xml:space="preserve">19.3670425415039</t>
   </si>
   <si>
     <t xml:space="preserve">19.5325756072998</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4911918640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0773658752441</t>
+    <t xml:space="preserve">19.491189956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0773620605469</t>
   </si>
   <si>
     <t xml:space="preserve">19.1187496185303</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0428009033203</t>
+    <t xml:space="preserve">18.0427989959717</t>
   </si>
   <si>
     <t xml:space="preserve">17.7945079803467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8427085876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7531242370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1737651824951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3806800842285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.966854095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6357917785645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7599391937256</t>
+    <t xml:space="preserve">16.8427066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7531204223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1737670898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3806781768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9668521881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6357936859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7599411010742</t>
   </si>
   <si>
     <t xml:space="preserve">16.8840885162354</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5530319213867</t>
+    <t xml:space="preserve">16.5530281066895</t>
   </si>
   <si>
     <t xml:space="preserve">18.2497119903564</t>
@@ -1790,40 +1790,40 @@
     <t xml:space="preserve">19.1601295471191</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4084281921387</t>
+    <t xml:space="preserve">19.40842628479</t>
   </si>
   <si>
     <t xml:space="preserve">19.5739574432373</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4498062133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9050159454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8222522735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5257549285889</t>
+    <t xml:space="preserve">19.4498081207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9050140380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8222541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5257530212402</t>
   </si>
   <si>
     <t xml:space="preserve">20.64990234375</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3188419342041</t>
+    <t xml:space="preserve">20.3188400268555</t>
   </si>
   <si>
     <t xml:space="preserve">20.111930847168</t>
   </si>
   <si>
-    <t xml:space="preserve">19.7808704376221</t>
+    <t xml:space="preserve">19.7808685302734</t>
   </si>
   <si>
     <t xml:space="preserve">19.2842788696289</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0291652679443</t>
+    <t xml:space="preserve">20.0291633605957</t>
   </si>
   <si>
     <t xml:space="preserve">19.6567211151123</t>
@@ -1844,10 +1844,10 @@
     <t xml:space="preserve">17.2979164123535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5364742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.594409942627</t>
+    <t xml:space="preserve">16.5364761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5944080352783</t>
   </si>
   <si>
     <t xml:space="preserve">16.48681640625</t>
@@ -1856,37 +1856,37 @@
     <t xml:space="preserve">16.4537086486816</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0909996032715</t>
+    <t xml:space="preserve">17.0910015106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.2151508331299</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3310203552246</t>
+    <t xml:space="preserve">17.3310222625732</t>
   </si>
   <si>
     <t xml:space="preserve">17.364128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2910976409912</t>
+    <t xml:space="preserve">18.2910957336426</t>
   </si>
   <si>
     <t xml:space="preserve">18.6056041717529</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3407592773438</t>
+    <t xml:space="preserve">18.3407554626465</t>
   </si>
   <si>
     <t xml:space="preserve">18.0593547821045</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6455307006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2482585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6289730072021</t>
+    <t xml:space="preserve">17.645528793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.248254776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6289749145508</t>
   </si>
   <si>
     <t xml:space="preserve">18.07590675354</t>
@@ -1895,19 +1895,19 @@
     <t xml:space="preserve">18.1255645751953</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6620826721191</t>
+    <t xml:space="preserve">17.6620788574219</t>
   </si>
   <si>
     <t xml:space="preserve">17.7779502868652</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9765872955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2248840332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7613983154297</t>
+    <t xml:space="preserve">17.9765892028809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2248859405518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7614002227783</t>
   </si>
   <si>
     <t xml:space="preserve">16.5861339569092</t>
@@ -1916,73 +1916,73 @@
     <t xml:space="preserve">16.6192398071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5033702850342</t>
+    <t xml:space="preserve">16.5033683776855</t>
   </si>
   <si>
     <t xml:space="preserve">15.5101881027222</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4274225234985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2701692581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8397912979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6328763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6742601394653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6177825927734</t>
+    <t xml:space="preserve">15.4274244308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.270170211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8397903442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6328783035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.674259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6177845001221</t>
   </si>
   <si>
     <t xml:space="preserve">16.0233325958252</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9322929382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0632562637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0549821853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.046703338623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6659832000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8232383728027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3255748748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.342604637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7125539779663</t>
+    <t xml:space="preserve">15.9322910308838</t>
+ 